--- a/CoreRefiner工作表.xlsx
+++ b/CoreRefiner工作表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_HOME_study\CoreRefiner\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04934996-E725-461D-ACB4-E407C6782734}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27379CDB-8BC6-424E-AB04-4595E34B3A9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="任务表" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="248">
   <si>
     <t>内容详情</t>
   </si>
@@ -663,10 +663,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Other_Repeat</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Other_Revive</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -758,17 +754,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>当前攻击节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>节点半径：12.0f
-冷却时间：2.0f
-扩散半径：50.0f
-扩散速度：50.0f</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>增加当前攻击节点的移动速度的倍率rate。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -818,6 +803,178 @@
   </si>
   <si>
     <t>伤害倍率：0.5f→1.0f→1.5f</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回归法则</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>公转法则</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主攻击节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>让攻击节点围绕自己的主体进行公转。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>让这次攻击从瞄准点向角色方向发射。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>让攻击节点围绕自己的主体进行公转。
+子攻击节点绕主攻击节点公转，主攻击节点绕玩家公转。
+失去主体后则向切线发射。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>节点半径：18.0f→14.0f→10.0f</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>节点半径：18.0f
+冷却时间：1.0f
+扩散半径：80.0f
+扩散速度：80.0f</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>扩散半径：50.0f→60.0f→70.0f
+扩散速度：50.0f→75.0f→100.0f</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>节点半径：12.0f
+冷却时间：2.0f
+扩散半径：50.0f
+扩散速度：100.0f</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>节点半径：15.0f
+冷却时间：2.0f
+扩散半径：50.0f
+扩散速度：50.0f</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>固定伤害增幅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果处在仓库中，则给所有攻击节点的伤害提供固定fix增幅。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果处于仓库中，则为所有攻击节点增加固定伤害。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>节点半径：10.0f
+冷却时间：3.0f
+扩散半径：10.0f
+扩散速度：10.0f</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>固定伤害：1.0f→1.5f→2.0f</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>子物体</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重生</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>为主攻击节点开辟新的子物体栏位，并把聚焦的攻击节点转移过来。
+如无外部改动，子物体会均匀地环绕主攻击节点。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>聚焦的攻击节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>所有攻击节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在主攻击节点周围开辟新的子物体栏位，并记录此栏位为聚焦的攻击节点。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>扩散速度：20.0f→50.0f→80.0f</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在攻击销毁后，原地使其重新生成。
+并且将聚焦点重新调回主估计节点并能够填充接受新的节点进入配方。
+多个重生可以重复生效。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使销毁的攻击在原地重新生成。
+重生的攻击可以继续叠加此节点后的其他节点，包括其他的重生节点。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>节点半径：20.0f
+冷却时间：2.0f
+扩散半径：80.0f
+扩散速度：20.0f</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>节点半径：15.0f
+冷却时间：5.0f
+扩散半径：100.0f
+扩散速度：100.0f</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冷却时间：5.0f→4.0f→3.0f</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>节点半径：15.0f
+冷却时间：3.0f
+扩散半径：10.0f
+扩散速度：10.0f</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重复节点个数：1→2→3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>按重复节点个数的值重复执行此次配方中该节点前的节点，若存在的节点超出重复的个数，则结束重复。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重复*重复节点个数*个节点。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同被重复的节点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重复</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Other_Repeat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>建立了Node表。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -877,7 +1034,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -944,6 +1101,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -987,7 +1150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1027,13 +1190,9 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1089,6 +1248,18 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1097,12 +1268,12 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFC8A0FF"/>
+      <color rgb="FFC0C0C0"/>
+      <color rgb="FF8CDC82"/>
       <color rgb="FF78C8FF"/>
       <color rgb="FFFFB43C"/>
       <color rgb="FFFFFF00"/>
-      <color rgb="FFC8A0FF"/>
-      <color rgb="FFC0C0C0"/>
-      <color rgb="FF8CDC82"/>
     </mruColors>
   </colors>
   <extLst>
@@ -3826,7 +3997,7 @@
       <c r="D65" s="7">
         <v>46265</v>
       </c>
-      <c r="E65" s="15" t="s">
+      <c r="E65" s="38" t="s">
         <v>127</v>
       </c>
       <c r="F65" s="2"/>
@@ -4194,13 +4365,21 @@
       <c r="Z74" s="2"/>
     </row>
     <row r="75" spans="1:26">
-      <c r="A75" s="16">
+      <c r="A75" s="6">
         <v>74</v>
       </c>
-      <c r="B75" s="17"/>
-      <c r="C75" s="18"/>
-      <c r="D75" s="18"/>
-      <c r="E75" s="18"/>
+      <c r="B75" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="C75" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D75" s="7">
+        <v>46276</v>
+      </c>
+      <c r="E75" s="4" t="s">
+        <v>247</v>
+      </c>
       <c r="F75" s="2"/>
       <c r="G75" s="2"/>
       <c r="H75" s="2"/>
@@ -4224,15 +4403,12 @@
       <c r="Z75" s="2"/>
     </row>
     <row r="76" spans="1:26">
-      <c r="A76" s="16">
+      <c r="A76" s="15">
         <v>75</v>
       </c>
-      <c r="B76" s="18" t="s">
-        <v>146</v>
-      </c>
-      <c r="C76" s="18"/>
-      <c r="D76" s="18"/>
-      <c r="E76" s="18"/>
+      <c r="C76" s="16"/>
+      <c r="D76" s="16"/>
+      <c r="E76" s="16"/>
       <c r="F76" s="2"/>
       <c r="G76" s="2"/>
       <c r="H76" s="2"/>
@@ -4256,13 +4432,13 @@
       <c r="Z76" s="2"/>
     </row>
     <row r="77" spans="1:26">
-      <c r="A77" s="16">
+      <c r="A77" s="15">
         <v>76</v>
       </c>
-      <c r="B77" s="18"/>
-      <c r="C77" s="18"/>
-      <c r="D77" s="18"/>
-      <c r="E77" s="18"/>
+      <c r="B77" s="16"/>
+      <c r="C77" s="16"/>
+      <c r="D77" s="16"/>
+      <c r="E77" s="16"/>
       <c r="F77" s="2"/>
       <c r="G77" s="2"/>
       <c r="H77" s="2"/>
@@ -4286,13 +4462,13 @@
       <c r="Z77" s="2"/>
     </row>
     <row r="78" spans="1:26">
-      <c r="A78" s="16">
+      <c r="A78" s="15">
         <v>77</v>
       </c>
-      <c r="B78" s="18"/>
-      <c r="C78" s="18"/>
-      <c r="D78" s="18"/>
-      <c r="E78" s="18"/>
+      <c r="B78" s="16"/>
+      <c r="C78" s="16"/>
+      <c r="D78" s="16"/>
+      <c r="E78" s="16"/>
       <c r="F78" s="2"/>
       <c r="G78" s="2"/>
       <c r="H78" s="2"/>
@@ -4316,13 +4492,13 @@
       <c r="Z78" s="2"/>
     </row>
     <row r="79" spans="1:26">
-      <c r="A79" s="16">
+      <c r="A79" s="15">
         <v>78</v>
       </c>
-      <c r="B79" s="18"/>
-      <c r="C79" s="18"/>
-      <c r="D79" s="18"/>
-      <c r="E79" s="18"/>
+      <c r="B79" s="16"/>
+      <c r="C79" s="16"/>
+      <c r="D79" s="16"/>
+      <c r="E79" s="16"/>
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
       <c r="H79" s="2"/>
@@ -4346,13 +4522,13 @@
       <c r="Z79" s="2"/>
     </row>
     <row r="80" spans="1:26">
-      <c r="A80" s="16">
+      <c r="A80" s="15">
         <v>79</v>
       </c>
-      <c r="B80" s="18"/>
-      <c r="C80" s="18"/>
-      <c r="D80" s="18"/>
-      <c r="E80" s="18"/>
+      <c r="B80" s="16"/>
+      <c r="C80" s="16"/>
+      <c r="D80" s="16"/>
+      <c r="E80" s="16"/>
       <c r="F80" s="2"/>
       <c r="G80" s="2"/>
       <c r="H80" s="2"/>
@@ -4376,13 +4552,13 @@
       <c r="Z80" s="2"/>
     </row>
     <row r="81" spans="1:26">
-      <c r="A81" s="16">
+      <c r="A81" s="15">
         <v>80</v>
       </c>
-      <c r="B81" s="18"/>
-      <c r="C81" s="18"/>
-      <c r="D81" s="18"/>
-      <c r="E81" s="18"/>
+      <c r="B81" s="16"/>
+      <c r="C81" s="16"/>
+      <c r="D81" s="16"/>
+      <c r="E81" s="16"/>
       <c r="F81" s="2"/>
       <c r="G81" s="2"/>
       <c r="H81" s="2"/>
@@ -4406,13 +4582,13 @@
       <c r="Z81" s="2"/>
     </row>
     <row r="82" spans="1:26">
-      <c r="A82" s="16">
+      <c r="A82" s="15">
         <v>81</v>
       </c>
-      <c r="B82" s="18"/>
-      <c r="C82" s="18"/>
-      <c r="D82" s="18"/>
-      <c r="E82" s="18"/>
+      <c r="B82" s="16"/>
+      <c r="C82" s="16"/>
+      <c r="D82" s="16"/>
+      <c r="E82" s="16"/>
       <c r="F82" s="2"/>
       <c r="G82" s="2"/>
       <c r="H82" s="2"/>
@@ -4436,13 +4612,13 @@
       <c r="Z82" s="2"/>
     </row>
     <row r="83" spans="1:26">
-      <c r="A83" s="16">
+      <c r="A83" s="15">
         <v>82</v>
       </c>
-      <c r="B83" s="19"/>
-      <c r="C83" s="18"/>
-      <c r="D83" s="18"/>
-      <c r="E83" s="18"/>
+      <c r="B83" s="17"/>
+      <c r="C83" s="16"/>
+      <c r="D83" s="16"/>
+      <c r="E83" s="16"/>
       <c r="F83" s="2"/>
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
@@ -4466,13 +4642,13 @@
       <c r="Z83" s="2"/>
     </row>
     <row r="84" spans="1:26">
-      <c r="A84" s="16">
+      <c r="A84" s="15">
         <v>83</v>
       </c>
-      <c r="B84" s="19"/>
-      <c r="C84" s="18"/>
-      <c r="D84" s="18"/>
-      <c r="E84" s="18"/>
+      <c r="B84" s="17"/>
+      <c r="C84" s="16"/>
+      <c r="D84" s="16"/>
+      <c r="E84" s="16"/>
       <c r="F84" s="2"/>
       <c r="G84" s="2"/>
       <c r="H84" s="2"/>
@@ -4496,15 +4672,15 @@
       <c r="Z84" s="2"/>
     </row>
     <row r="85" spans="1:26">
-      <c r="A85" s="16">
+      <c r="A85" s="15">
         <v>84</v>
       </c>
-      <c r="B85" s="18" t="s">
+      <c r="B85" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="C85" s="18"/>
-      <c r="D85" s="18"/>
-      <c r="E85" s="18"/>
+      <c r="C85" s="16"/>
+      <c r="D85" s="16"/>
+      <c r="E85" s="16"/>
       <c r="F85" s="2"/>
       <c r="G85" s="2"/>
       <c r="H85" s="2"/>
@@ -4528,15 +4704,15 @@
       <c r="Z85" s="2"/>
     </row>
     <row r="86" spans="1:26">
-      <c r="A86" s="16">
+      <c r="A86" s="15">
         <v>85</v>
       </c>
-      <c r="B86" s="18" t="s">
+      <c r="B86" s="16" t="s">
         <v>148</v>
       </c>
-      <c r="C86" s="18"/>
-      <c r="D86" s="18"/>
-      <c r="E86" s="18"/>
+      <c r="C86" s="16"/>
+      <c r="D86" s="16"/>
+      <c r="E86" s="16"/>
       <c r="F86" s="2"/>
       <c r="G86" s="2"/>
       <c r="H86" s="2"/>
@@ -4560,15 +4736,15 @@
       <c r="Z86" s="2"/>
     </row>
     <row r="87" spans="1:26">
-      <c r="A87" s="16">
+      <c r="A87" s="15">
         <v>86</v>
       </c>
-      <c r="B87" s="18" t="s">
+      <c r="B87" s="16" t="s">
         <v>156</v>
       </c>
-      <c r="C87" s="18"/>
-      <c r="D87" s="18"/>
-      <c r="E87" s="18"/>
+      <c r="C87" s="16"/>
+      <c r="D87" s="16"/>
+      <c r="E87" s="16"/>
       <c r="F87" s="2"/>
       <c r="G87" s="2"/>
       <c r="H87" s="2"/>
@@ -4592,13 +4768,13 @@
       <c r="Z87" s="2"/>
     </row>
     <row r="88" spans="1:26">
-      <c r="A88" s="16">
+      <c r="A88" s="15">
         <v>87</v>
       </c>
-      <c r="B88" s="18"/>
-      <c r="C88" s="18"/>
-      <c r="D88" s="18"/>
-      <c r="E88" s="18"/>
+      <c r="B88" s="16"/>
+      <c r="C88" s="16"/>
+      <c r="D88" s="16"/>
+      <c r="E88" s="16"/>
       <c r="F88" s="2"/>
       <c r="G88" s="2"/>
       <c r="H88" s="2"/>
@@ -4622,13 +4798,13 @@
       <c r="Z88" s="2"/>
     </row>
     <row r="89" spans="1:26">
-      <c r="A89" s="16">
+      <c r="A89" s="15">
         <v>88</v>
       </c>
-      <c r="B89" s="18"/>
-      <c r="C89" s="18"/>
-      <c r="D89" s="18"/>
-      <c r="E89" s="18"/>
+      <c r="B89" s="16"/>
+      <c r="C89" s="16"/>
+      <c r="D89" s="16"/>
+      <c r="E89" s="16"/>
       <c r="F89" s="2"/>
       <c r="G89" s="2"/>
       <c r="H89" s="2"/>
@@ -4652,13 +4828,13 @@
       <c r="Z89" s="2"/>
     </row>
     <row r="90" spans="1:26">
-      <c r="A90" s="16">
+      <c r="A90" s="15">
         <v>89</v>
       </c>
-      <c r="B90" s="18"/>
-      <c r="C90" s="18"/>
-      <c r="D90" s="18"/>
-      <c r="E90" s="18"/>
+      <c r="B90" s="16"/>
+      <c r="C90" s="16"/>
+      <c r="D90" s="16"/>
+      <c r="E90" s="16"/>
       <c r="F90" s="2"/>
       <c r="G90" s="2"/>
       <c r="H90" s="2"/>
@@ -4682,13 +4858,13 @@
       <c r="Z90" s="2"/>
     </row>
     <row r="91" spans="1:26">
-      <c r="A91" s="16">
+      <c r="A91" s="15">
         <v>90</v>
       </c>
-      <c r="B91" s="18"/>
-      <c r="C91" s="18"/>
-      <c r="D91" s="18"/>
-      <c r="E91" s="18"/>
+      <c r="B91" s="16"/>
+      <c r="C91" s="16"/>
+      <c r="D91" s="16"/>
+      <c r="E91" s="16"/>
       <c r="F91" s="2"/>
       <c r="G91" s="2"/>
       <c r="H91" s="2"/>
@@ -4712,13 +4888,13 @@
       <c r="Z91" s="2"/>
     </row>
     <row r="92" spans="1:26">
-      <c r="A92" s="16">
+      <c r="A92" s="15">
         <v>91</v>
       </c>
-      <c r="B92" s="18"/>
-      <c r="C92" s="18"/>
-      <c r="D92" s="18"/>
-      <c r="E92" s="18"/>
+      <c r="B92" s="16"/>
+      <c r="C92" s="16"/>
+      <c r="D92" s="16"/>
+      <c r="E92" s="16"/>
       <c r="F92" s="2"/>
       <c r="G92" s="2"/>
       <c r="H92" s="2"/>
@@ -4742,13 +4918,13 @@
       <c r="Z92" s="2"/>
     </row>
     <row r="93" spans="1:26">
-      <c r="A93" s="16">
+      <c r="A93" s="15">
         <v>92</v>
       </c>
-      <c r="B93" s="18"/>
-      <c r="C93" s="18"/>
-      <c r="D93" s="18"/>
-      <c r="E93" s="18"/>
+      <c r="B93" s="16"/>
+      <c r="C93" s="16"/>
+      <c r="D93" s="16"/>
+      <c r="E93" s="16"/>
       <c r="F93" s="2"/>
       <c r="G93" s="2"/>
       <c r="H93" s="2"/>
@@ -4772,13 +4948,13 @@
       <c r="Z93" s="2"/>
     </row>
     <row r="94" spans="1:26">
-      <c r="A94" s="16">
+      <c r="A94" s="15">
         <v>93</v>
       </c>
-      <c r="B94" s="18"/>
-      <c r="C94" s="18"/>
-      <c r="D94" s="18"/>
-      <c r="E94" s="18"/>
+      <c r="B94" s="16"/>
+      <c r="C94" s="16"/>
+      <c r="D94" s="16"/>
+      <c r="E94" s="16"/>
       <c r="F94" s="2"/>
       <c r="G94" s="2"/>
       <c r="H94" s="2"/>
@@ -4802,13 +4978,13 @@
       <c r="Z94" s="2"/>
     </row>
     <row r="95" spans="1:26">
-      <c r="A95" s="16">
+      <c r="A95" s="15">
         <v>94</v>
       </c>
-      <c r="B95" s="18"/>
-      <c r="C95" s="18"/>
-      <c r="D95" s="18"/>
-      <c r="E95" s="18"/>
+      <c r="B95" s="16"/>
+      <c r="C95" s="16"/>
+      <c r="D95" s="16"/>
+      <c r="E95" s="16"/>
       <c r="F95" s="2"/>
       <c r="G95" s="2"/>
       <c r="H95" s="2"/>
@@ -4832,13 +5008,13 @@
       <c r="Z95" s="2"/>
     </row>
     <row r="96" spans="1:26">
-      <c r="A96" s="16">
+      <c r="A96" s="15">
         <v>95</v>
       </c>
-      <c r="B96" s="18"/>
-      <c r="C96" s="18"/>
-      <c r="D96" s="18"/>
-      <c r="E96" s="18"/>
+      <c r="B96" s="16"/>
+      <c r="C96" s="16"/>
+      <c r="D96" s="16"/>
+      <c r="E96" s="16"/>
       <c r="F96" s="2"/>
       <c r="G96" s="2"/>
       <c r="H96" s="2"/>
@@ -4862,13 +5038,13 @@
       <c r="Z96" s="2"/>
     </row>
     <row r="97" spans="1:26">
-      <c r="A97" s="16">
+      <c r="A97" s="15">
         <v>96</v>
       </c>
-      <c r="B97" s="18"/>
-      <c r="C97" s="18"/>
-      <c r="D97" s="18"/>
-      <c r="E97" s="18"/>
+      <c r="B97" s="16"/>
+      <c r="C97" s="16"/>
+      <c r="D97" s="16"/>
+      <c r="E97" s="16"/>
       <c r="F97" s="2"/>
       <c r="G97" s="2"/>
       <c r="H97" s="2"/>
@@ -4892,13 +5068,13 @@
       <c r="Z97" s="2"/>
     </row>
     <row r="98" spans="1:26">
-      <c r="A98" s="16">
+      <c r="A98" s="15">
         <v>97</v>
       </c>
-      <c r="B98" s="18"/>
-      <c r="C98" s="18"/>
-      <c r="D98" s="18"/>
-      <c r="E98" s="18"/>
+      <c r="B98" s="16"/>
+      <c r="C98" s="16"/>
+      <c r="D98" s="16"/>
+      <c r="E98" s="16"/>
       <c r="F98" s="2"/>
       <c r="G98" s="2"/>
       <c r="H98" s="2"/>
@@ -4922,13 +5098,13 @@
       <c r="Z98" s="2"/>
     </row>
     <row r="99" spans="1:26">
-      <c r="A99" s="16">
+      <c r="A99" s="15">
         <v>98</v>
       </c>
-      <c r="B99" s="18"/>
-      <c r="C99" s="18"/>
-      <c r="D99" s="18"/>
-      <c r="E99" s="18"/>
+      <c r="B99" s="16"/>
+      <c r="C99" s="16"/>
+      <c r="D99" s="16"/>
+      <c r="E99" s="16"/>
       <c r="F99" s="2"/>
       <c r="G99" s="2"/>
       <c r="H99" s="2"/>
@@ -4952,13 +5128,13 @@
       <c r="Z99" s="2"/>
     </row>
     <row r="100" spans="1:26">
-      <c r="A100" s="16">
+      <c r="A100" s="15">
         <v>99</v>
       </c>
-      <c r="B100" s="18"/>
-      <c r="C100" s="18"/>
-      <c r="D100" s="18"/>
-      <c r="E100" s="18"/>
+      <c r="B100" s="16"/>
+      <c r="C100" s="16"/>
+      <c r="D100" s="16"/>
+      <c r="E100" s="16"/>
       <c r="F100" s="2"/>
       <c r="G100" s="2"/>
       <c r="H100" s="2"/>
@@ -4982,13 +5158,13 @@
       <c r="Z100" s="2"/>
     </row>
     <row r="101" spans="1:26">
-      <c r="A101" s="16">
+      <c r="A101" s="15">
         <v>100</v>
       </c>
-      <c r="B101" s="18"/>
-      <c r="C101" s="18"/>
-      <c r="D101" s="18"/>
-      <c r="E101" s="18"/>
+      <c r="B101" s="16"/>
+      <c r="C101" s="16"/>
+      <c r="D101" s="16"/>
+      <c r="E101" s="16"/>
       <c r="F101" s="2"/>
       <c r="G101" s="2"/>
       <c r="H101" s="2"/>
@@ -30196,330 +30372,402 @@
   <cols>
     <col min="1" max="1" width="15.58203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="30.58203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="35.58203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="40.83203125" style="1" customWidth="1"/>
     <col min="4" max="4" width="15.58203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="35.5" style="1" customWidth="1"/>
+    <col min="5" max="5" width="50.58203125" style="1" customWidth="1"/>
     <col min="6" max="6" width="15.6640625" style="1" customWidth="1"/>
     <col min="7" max="7" width="10.6640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.58203125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="16.75" style="1" customWidth="1"/>
     <col min="9" max="9" width="30.58203125" style="1" customWidth="1"/>
     <col min="10" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="25.5">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="18" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="25.5">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="18" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="21">
+      <c r="A4" s="25" t="s">
+        <v>158</v>
+      </c>
+      <c r="B4" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="C4" s="25" t="s">
+        <v>161</v>
+      </c>
+      <c r="D4" s="25" t="s">
+        <v>181</v>
+      </c>
+      <c r="E4" s="25" t="s">
+        <v>160</v>
+      </c>
+      <c r="F4" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="G4" s="25" t="s">
+        <v>162</v>
+      </c>
+      <c r="H4" s="25" t="s">
+        <v>163</v>
+      </c>
+      <c r="I4" s="25" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="56">
+      <c r="A5" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="C5" s="26" t="s">
+        <v>184</v>
+      </c>
+      <c r="D5" s="27" t="s">
+        <v>182</v>
+      </c>
+      <c r="E5" s="26" t="s">
+        <v>187</v>
+      </c>
+      <c r="F5" s="26" t="s">
+        <v>196</v>
+      </c>
+      <c r="G5" s="27" t="s">
+        <v>180</v>
+      </c>
+      <c r="H5" s="26" t="s">
+        <v>183</v>
+      </c>
+      <c r="I5" s="26" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="56">
+      <c r="A6" s="20" t="s">
+        <v>165</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="C6" s="28" t="s">
+        <v>185</v>
+      </c>
+      <c r="D6" s="29" t="s">
+        <v>186</v>
+      </c>
+      <c r="E6" s="28" t="s">
+        <v>188</v>
+      </c>
+      <c r="F6" s="28" t="s">
+        <v>196</v>
+      </c>
+      <c r="G6" s="29">
+        <v>4</v>
+      </c>
+      <c r="H6" s="28" t="s">
+        <v>189</v>
+      </c>
+      <c r="I6" s="28" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="56">
+      <c r="A7" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="C7" s="30" t="s">
+        <v>197</v>
+      </c>
+      <c r="D7" s="30" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" ht="21">
-      <c r="A4" s="27" t="s">
-        <v>158</v>
-      </c>
-      <c r="B4" s="27" t="s">
-        <v>159</v>
-      </c>
-      <c r="C4" s="27" t="s">
-        <v>161</v>
-      </c>
-      <c r="D4" s="27" t="s">
-        <v>182</v>
-      </c>
-      <c r="E4" s="27" t="s">
-        <v>160</v>
-      </c>
-      <c r="F4" s="27" t="s">
-        <v>196</v>
-      </c>
-      <c r="G4" s="27" t="s">
-        <v>162</v>
-      </c>
-      <c r="H4" s="27" t="s">
-        <v>163</v>
-      </c>
-      <c r="I4" s="27" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="56">
-      <c r="A5" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="B5" s="21" t="s">
-        <v>170</v>
-      </c>
-      <c r="C5" s="28" t="s">
-        <v>185</v>
-      </c>
-      <c r="D5" s="29" t="s">
-        <v>183</v>
-      </c>
-      <c r="E5" s="28" t="s">
-        <v>188</v>
-      </c>
-      <c r="F5" s="28" t="s">
-        <v>197</v>
-      </c>
-      <c r="G5" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="H5" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="I5" s="28" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="56">
-      <c r="A6" s="22" t="s">
-        <v>165</v>
-      </c>
-      <c r="B6" s="22" t="s">
-        <v>171</v>
-      </c>
-      <c r="C6" s="30" t="s">
-        <v>186</v>
-      </c>
-      <c r="D6" s="31" t="s">
-        <v>187</v>
-      </c>
-      <c r="E6" s="30" t="s">
-        <v>189</v>
-      </c>
-      <c r="F6" s="30" t="s">
-        <v>197</v>
-      </c>
-      <c r="G6" s="31">
+      <c r="E7" s="30" t="s">
+        <v>198</v>
+      </c>
+      <c r="F7" s="30" t="s">
+        <v>231</v>
+      </c>
+      <c r="G7" s="30">
         <v>4</v>
       </c>
-      <c r="H6" s="30" t="s">
-        <v>190</v>
-      </c>
-      <c r="I6" s="30" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="56">
-      <c r="A7" s="23" t="s">
+      <c r="H7" s="34" t="s">
+        <v>221</v>
+      </c>
+      <c r="I7" s="30" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="56">
+      <c r="A8" s="21" t="s">
         <v>166</v>
       </c>
-      <c r="B7" s="23" t="s">
-        <v>193</v>
-      </c>
-      <c r="C7" s="32" t="s">
-        <v>198</v>
-      </c>
-      <c r="D7" s="32" t="s">
-        <v>195</v>
-      </c>
-      <c r="E7" s="32" t="s">
+      <c r="B8" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="C8" s="30" t="s">
         <v>199</v>
       </c>
-      <c r="F7" s="32" t="s">
+      <c r="D8" s="30" t="s">
+        <v>202</v>
+      </c>
+      <c r="E8" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="F8" s="30" t="s">
+        <v>231</v>
+      </c>
+      <c r="G8" s="30">
+        <v>4</v>
+      </c>
+      <c r="H8" s="34" t="s">
+        <v>221</v>
+      </c>
+      <c r="I8" s="30" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="56">
+      <c r="A9" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>174</v>
+      </c>
+      <c r="C9" s="30" t="s">
         <v>200</v>
       </c>
-      <c r="G7" s="32">
+      <c r="D9" s="30" t="s">
+        <v>203</v>
+      </c>
+      <c r="E9" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="F9" s="30" t="s">
+        <v>231</v>
+      </c>
+      <c r="G9" s="30">
         <v>4</v>
       </c>
-      <c r="H7" s="36" t="s">
+      <c r="H9" s="34" t="s">
+        <v>221</v>
+      </c>
+      <c r="I9" s="30" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="56">
+      <c r="A10" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="C10" s="30" t="s">
         <v>201</v>
       </c>
-      <c r="I7" s="32" t="s">
+      <c r="D10" s="30" t="s">
+        <v>204</v>
+      </c>
+      <c r="E10" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="F10" s="30" t="s">
+        <v>231</v>
+      </c>
+      <c r="G10" s="30">
+        <v>4</v>
+      </c>
+      <c r="H10" s="34" t="s">
+        <v>221</v>
+      </c>
+      <c r="I10" s="30" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="56">
-      <c r="A8" s="23" t="s">
-        <v>166</v>
-      </c>
-      <c r="B8" s="23" t="s">
-        <v>173</v>
-      </c>
-      <c r="C8" s="32" t="s">
-        <v>202</v>
-      </c>
-      <c r="D8" s="32" t="s">
-        <v>205</v>
-      </c>
-      <c r="E8" s="32" t="s">
-        <v>208</v>
-      </c>
-      <c r="F8" s="32" t="s">
-        <v>200</v>
-      </c>
-      <c r="G8" s="32">
+    <row r="11" spans="1:9" ht="56">
+      <c r="A11" s="22" t="s">
+        <v>167</v>
+      </c>
+      <c r="B11" s="22" t="s">
+        <v>175</v>
+      </c>
+      <c r="C11" s="35" t="s">
+        <v>217</v>
+      </c>
+      <c r="D11" s="31" t="s">
+        <v>213</v>
+      </c>
+      <c r="E11" s="31" t="s">
+        <v>215</v>
+      </c>
+      <c r="F11" s="31" t="s">
+        <v>231</v>
+      </c>
+      <c r="G11" s="31">
         <v>4</v>
       </c>
-      <c r="H8" s="36" t="s">
-        <v>201</v>
-      </c>
-      <c r="I8" s="32" t="s">
+      <c r="H11" s="35" t="s">
+        <v>219</v>
+      </c>
+      <c r="I11" s="35" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="56">
+      <c r="A12" s="22" t="s">
+        <v>167</v>
+      </c>
+      <c r="B12" s="22" t="s">
+        <v>176</v>
+      </c>
+      <c r="C12" s="31" t="s">
+        <v>216</v>
+      </c>
+      <c r="D12" s="31" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" ht="56">
-      <c r="A9" s="23" t="s">
-        <v>166</v>
-      </c>
-      <c r="B9" s="23" t="s">
-        <v>174</v>
-      </c>
-      <c r="C9" s="32" t="s">
-        <v>203</v>
-      </c>
-      <c r="D9" s="32" t="s">
-        <v>206</v>
-      </c>
-      <c r="E9" s="32" t="s">
-        <v>209</v>
-      </c>
-      <c r="F9" s="32" t="s">
-        <v>200</v>
-      </c>
-      <c r="G9" s="32">
+      <c r="E12" s="31" t="s">
+        <v>216</v>
+      </c>
+      <c r="F12" s="31" t="s">
+        <v>214</v>
+      </c>
+      <c r="G12" s="31">
         <v>4</v>
       </c>
-      <c r="H9" s="36" t="s">
-        <v>201</v>
-      </c>
-      <c r="I9" s="32" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="56">
-      <c r="A10" s="23" t="s">
-        <v>166</v>
-      </c>
-      <c r="B10" s="23" t="s">
-        <v>172</v>
-      </c>
-      <c r="C10" s="32" t="s">
-        <v>204</v>
-      </c>
-      <c r="D10" s="32" t="s">
-        <v>207</v>
-      </c>
-      <c r="E10" s="32" t="s">
-        <v>210</v>
-      </c>
-      <c r="F10" s="32" t="s">
-        <v>200</v>
-      </c>
-      <c r="G10" s="32">
+      <c r="H12" s="35" t="s">
+        <v>222</v>
+      </c>
+      <c r="I12" s="35" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="56">
+      <c r="A13" s="23" t="s">
+        <v>168</v>
+      </c>
+      <c r="B13" s="23" t="s">
+        <v>177</v>
+      </c>
+      <c r="C13" s="36" t="s">
+        <v>224</v>
+      </c>
+      <c r="D13" s="32" t="s">
+        <v>223</v>
+      </c>
+      <c r="E13" s="36" t="s">
+        <v>225</v>
+      </c>
+      <c r="F13" s="32" t="s">
+        <v>232</v>
+      </c>
+      <c r="G13" s="32">
         <v>4</v>
       </c>
-      <c r="H10" s="36" t="s">
-        <v>201</v>
-      </c>
-      <c r="I10" s="32" t="s">
+      <c r="H13" s="36" t="s">
+        <v>226</v>
+      </c>
+      <c r="I13" s="32" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="56">
+      <c r="A14" s="24" t="s">
+        <v>169</v>
+      </c>
+      <c r="B14" s="24" t="s">
+        <v>178</v>
+      </c>
+      <c r="C14" s="37" t="s">
+        <v>230</v>
+      </c>
+      <c r="D14" s="33" t="s">
+        <v>228</v>
+      </c>
+      <c r="E14" s="37" t="s">
+        <v>233</v>
+      </c>
+      <c r="F14" s="33" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" ht="17.5">
-      <c r="A11" s="24" t="s">
-        <v>167</v>
-      </c>
-      <c r="B11" s="24" t="s">
-        <v>175</v>
-      </c>
-      <c r="C11" s="33"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="33"/>
-      <c r="F11" s="33"/>
-      <c r="G11" s="33">
+      <c r="G14" s="33">
         <v>4</v>
       </c>
-      <c r="H11" s="33"/>
-      <c r="I11" s="33"/>
-    </row>
-    <row r="12" spans="1:9" ht="17.5">
-      <c r="A12" s="24" t="s">
-        <v>167</v>
-      </c>
-      <c r="B12" s="24" t="s">
-        <v>176</v>
-      </c>
-      <c r="C12" s="33"/>
-      <c r="D12" s="33"/>
-      <c r="E12" s="33"/>
-      <c r="F12" s="33"/>
-      <c r="G12" s="33">
+      <c r="H14" s="37" t="s">
+        <v>237</v>
+      </c>
+      <c r="I14" s="33" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="56">
+      <c r="A15" s="24" t="s">
+        <v>169</v>
+      </c>
+      <c r="B15" s="24" t="s">
+        <v>179</v>
+      </c>
+      <c r="C15" s="37" t="s">
+        <v>235</v>
+      </c>
+      <c r="D15" s="33" t="s">
+        <v>229</v>
+      </c>
+      <c r="E15" s="37" t="s">
+        <v>236</v>
+      </c>
+      <c r="F15" s="33" t="s">
+        <v>214</v>
+      </c>
+      <c r="G15" s="33">
         <v>4</v>
       </c>
-      <c r="H12" s="33"/>
-      <c r="I12" s="33"/>
-    </row>
-    <row r="13" spans="1:9" ht="17.5">
-      <c r="A13" s="25" t="s">
-        <v>168</v>
-      </c>
-      <c r="B13" s="25" t="s">
-        <v>177</v>
-      </c>
-      <c r="C13" s="34"/>
-      <c r="D13" s="34"/>
-      <c r="E13" s="34"/>
-      <c r="F13" s="34"/>
-      <c r="G13" s="34">
+      <c r="H15" s="37" t="s">
+        <v>238</v>
+      </c>
+      <c r="I15" s="33" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="56">
+      <c r="A16" s="24" t="s">
+        <v>169</v>
+      </c>
+      <c r="B16" s="24" t="s">
+        <v>246</v>
+      </c>
+      <c r="C16" s="37" t="s">
+        <v>242</v>
+      </c>
+      <c r="D16" s="33" t="s">
+        <v>245</v>
+      </c>
+      <c r="E16" s="33" t="s">
+        <v>243</v>
+      </c>
+      <c r="F16" s="33" t="s">
+        <v>244</v>
+      </c>
+      <c r="G16" s="33">
         <v>4</v>
       </c>
-      <c r="H13" s="34"/>
-      <c r="I13" s="34"/>
-    </row>
-    <row r="14" spans="1:9" ht="17.5">
-      <c r="A14" s="26" t="s">
-        <v>169</v>
-      </c>
-      <c r="B14" s="26" t="s">
-        <v>178</v>
-      </c>
-      <c r="C14" s="35"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="35"/>
-      <c r="G14" s="35">
-        <v>4</v>
-      </c>
-      <c r="H14" s="35"/>
-      <c r="I14" s="35"/>
-    </row>
-    <row r="15" spans="1:9" ht="17.5">
-      <c r="A15" s="26" t="s">
-        <v>169</v>
-      </c>
-      <c r="B15" s="26" t="s">
-        <v>180</v>
-      </c>
-      <c r="C15" s="35"/>
-      <c r="D15" s="35"/>
-      <c r="E15" s="35"/>
-      <c r="F15" s="35"/>
-      <c r="G15" s="35">
-        <v>4</v>
-      </c>
-      <c r="H15" s="35"/>
-      <c r="I15" s="35"/>
-    </row>
-    <row r="16" spans="1:9" ht="17.5">
-      <c r="A16" s="26" t="s">
-        <v>169</v>
-      </c>
-      <c r="B16" s="26" t="s">
-        <v>179</v>
-      </c>
-      <c r="C16" s="35"/>
-      <c r="D16" s="35"/>
-      <c r="E16" s="35"/>
-      <c r="F16" s="35"/>
-      <c r="G16" s="35">
-        <v>4</v>
-      </c>
-      <c r="H16" s="35"/>
-      <c r="I16" s="35"/>
+      <c r="H16" s="37" t="s">
+        <v>240</v>
+      </c>
+      <c r="I16" s="33" t="s">
+        <v>241</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:I14" xr:uid="{3258B9DE-144B-4A1D-96F7-444B72BE7902}"/>

--- a/CoreRefiner工作表.xlsx
+++ b/CoreRefiner工作表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_HOME_study\CoreRefiner\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27379CDB-8BC6-424E-AB04-4595E34B3A9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B6CB491-FFE0-45C7-96BA-B0131E3ABB31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="任务表" sheetId="1" r:id="rId1"/>
@@ -494,9 +494,6 @@
     <t>Rule_Return组件开发</t>
   </si>
   <si>
-    <t>让子弹从鼠标点往玩家发射。同时拥有Rule_Return和Rule_Orbit组件会让子弹从远处环绕到玩家。</t>
-  </si>
-  <si>
     <t>Passive_DamageFix组件开发</t>
   </si>
   <si>
@@ -910,10 +907,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>扩散速度：20.0f→50.0f→80.0f</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>在攻击销毁后，原地使其重新生成。
 并且将聚焦点重新调回主估计节点并能够填充接受新的节点进入配方。
 多个重生可以重复生效。</t>
@@ -922,13 +915,6 @@
   <si>
     <t>使销毁的攻击在原地重新生成。
 重生的攻击可以继续叠加此节点后的其他节点，包括其他的重生节点。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>节点半径：20.0f
-冷却时间：2.0f
-扩散半径：80.0f
-扩散速度：20.0f</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -943,22 +929,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>节点半径：15.0f
-冷却时间：3.0f
-扩散半径：10.0f
-扩散速度：10.0f</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>重复节点个数：1→2→3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>按重复节点个数的值重复执行此次配方中该节点前的节点，若存在的节点超出重复的个数，则结束重复。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>重复*重复节点个数*个节点。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -975,6 +950,33 @@
   </si>
   <si>
     <t>建立了Node表。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>让子弹从鼠标点往玩家发射。同时拥有Rule_Return和Rule_Orbit组件会让子弹从远处环绕到玩家。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>节点半径：20.0f
+冷却时间：2.0f
+扩散半径：80.0f
+扩散速度：50.0f</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>扩散速度：50.0f→75.0f→100.0f</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>节点半径：15.0f
+冷却时间：3.0f
+扩散半径：50.0f
+扩散速度：50.0f</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重复*重复节点个数*个节点。
+重复之间不会相互产生效果。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1563,7 +1565,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
       <c r="A1" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>0</v>
@@ -1792,7 +1794,7 @@
         <v>15</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D7" s="7">
         <v>46152</v>
@@ -2203,16 +2205,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D18" s="10">
         <v>46168</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
@@ -3390,7 +3392,7 @@
         <v>46251</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
@@ -4150,7 +4152,7 @@
         <v>46266</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>135</v>
+        <v>243</v>
       </c>
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
@@ -4179,7 +4181,7 @@
         <v>69</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>5</v>
@@ -4188,7 +4190,7 @@
         <v>46267</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F70" s="2"/>
       <c r="G70" s="2"/>
@@ -4217,7 +4219,7 @@
         <v>70</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C71" s="6" t="s">
         <v>5</v>
@@ -4226,7 +4228,7 @@
         <v>46267</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F71" s="2"/>
       <c r="G71" s="2"/>
@@ -4255,7 +4257,7 @@
         <v>71</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>5</v>
@@ -4264,7 +4266,7 @@
         <v>46268</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F72" s="2"/>
       <c r="G72" s="2"/>
@@ -4293,7 +4295,7 @@
         <v>72</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>5</v>
@@ -4302,7 +4304,7 @@
         <v>46269</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F73" s="2"/>
       <c r="G73" s="2"/>
@@ -4331,7 +4333,7 @@
         <v>73</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C74" s="6" t="s">
         <v>5</v>
@@ -4340,7 +4342,7 @@
         <v>46275</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F74" s="2"/>
       <c r="G74" s="2"/>
@@ -4369,7 +4371,7 @@
         <v>74</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C75" s="6" t="s">
         <v>5</v>
@@ -4378,7 +4380,7 @@
         <v>46276</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="F75" s="2"/>
       <c r="G75" s="2"/>
@@ -4676,7 +4678,7 @@
         <v>84</v>
       </c>
       <c r="B85" s="16" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C85" s="16"/>
       <c r="D85" s="16"/>
@@ -4708,7 +4710,7 @@
         <v>85</v>
       </c>
       <c r="B86" s="16" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C86" s="16"/>
       <c r="D86" s="16"/>
@@ -4740,7 +4742,7 @@
         <v>86</v>
       </c>
       <c r="B87" s="16" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C87" s="16"/>
       <c r="D87" s="16"/>
@@ -30384,389 +30386,389 @@
   <sheetData>
     <row r="1" spans="1:9" ht="25.5">
       <c r="A1" s="18" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="25.5">
       <c r="A2" s="18" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="21">
       <c r="A4" s="25" t="s">
+        <v>157</v>
+      </c>
+      <c r="B4" s="25" t="s">
         <v>158</v>
       </c>
-      <c r="B4" s="25" t="s">
+      <c r="C4" s="25" t="s">
+        <v>160</v>
+      </c>
+      <c r="D4" s="25" t="s">
+        <v>180</v>
+      </c>
+      <c r="E4" s="25" t="s">
         <v>159</v>
       </c>
-      <c r="C4" s="25" t="s">
+      <c r="F4" s="25" t="s">
+        <v>194</v>
+      </c>
+      <c r="G4" s="25" t="s">
         <v>161</v>
       </c>
-      <c r="D4" s="25" t="s">
-        <v>181</v>
-      </c>
-      <c r="E4" s="25" t="s">
-        <v>160</v>
-      </c>
-      <c r="F4" s="25" t="s">
-        <v>195</v>
-      </c>
-      <c r="G4" s="25" t="s">
+      <c r="H4" s="25" t="s">
         <v>162</v>
       </c>
-      <c r="H4" s="25" t="s">
+      <c r="I4" s="25" t="s">
         <v>163</v>
-      </c>
-      <c r="I4" s="25" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="56">
       <c r="A5" s="19" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C5" s="26" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D5" s="27" t="s">
+        <v>181</v>
+      </c>
+      <c r="E5" s="26" t="s">
+        <v>186</v>
+      </c>
+      <c r="F5" s="26" t="s">
+        <v>195</v>
+      </c>
+      <c r="G5" s="27" t="s">
+        <v>179</v>
+      </c>
+      <c r="H5" s="26" t="s">
         <v>182</v>
       </c>
-      <c r="E5" s="26" t="s">
-        <v>187</v>
-      </c>
-      <c r="F5" s="26" t="s">
-        <v>196</v>
-      </c>
-      <c r="G5" s="27" t="s">
-        <v>180</v>
-      </c>
-      <c r="H5" s="26" t="s">
-        <v>183</v>
-      </c>
       <c r="I5" s="26" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="56">
       <c r="A6" s="20" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C6" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="D6" s="29" t="s">
         <v>185</v>
       </c>
-      <c r="D6" s="29" t="s">
-        <v>186</v>
-      </c>
       <c r="E6" s="28" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F6" s="28" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G6" s="29">
         <v>4</v>
       </c>
       <c r="H6" s="28" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I6" s="28" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="56">
       <c r="A7" s="21" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C7" s="30" t="s">
+        <v>196</v>
+      </c>
+      <c r="D7" s="30" t="s">
+        <v>193</v>
+      </c>
+      <c r="E7" s="30" t="s">
         <v>197</v>
       </c>
-      <c r="D7" s="30" t="s">
-        <v>194</v>
-      </c>
-      <c r="E7" s="30" t="s">
-        <v>198</v>
-      </c>
       <c r="F7" s="30" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G7" s="30">
         <v>4</v>
       </c>
       <c r="H7" s="34" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I7" s="30" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="56">
       <c r="A8" s="21" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C8" s="30" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D8" s="30" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E8" s="30" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F8" s="30" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G8" s="30">
         <v>4</v>
       </c>
       <c r="H8" s="34" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I8" s="30" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="56">
       <c r="A9" s="21" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C9" s="30" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D9" s="30" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E9" s="30" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F9" s="30" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G9" s="30">
         <v>4</v>
       </c>
       <c r="H9" s="34" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I9" s="30" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="56">
       <c r="A10" s="21" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C10" s="30" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D10" s="30" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E10" s="30" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F10" s="30" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G10" s="30">
         <v>4</v>
       </c>
       <c r="H10" s="34" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I10" s="30" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="56">
       <c r="A11" s="22" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D11" s="31" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E11" s="31" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F11" s="31" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G11" s="31">
         <v>4</v>
       </c>
       <c r="H11" s="35" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I11" s="35" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="56">
       <c r="A12" s="22" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C12" s="31" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D12" s="31" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E12" s="31" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F12" s="31" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G12" s="31">
         <v>4</v>
       </c>
       <c r="H12" s="35" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I12" s="35" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="56">
       <c r="A13" s="23" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C13" s="36" t="s">
+        <v>223</v>
+      </c>
+      <c r="D13" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="E13" s="36" t="s">
         <v>224</v>
       </c>
-      <c r="D13" s="32" t="s">
-        <v>223</v>
-      </c>
-      <c r="E13" s="36" t="s">
-        <v>225</v>
-      </c>
       <c r="F13" s="32" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G13" s="32">
         <v>4</v>
       </c>
       <c r="H13" s="36" t="s">
+        <v>225</v>
+      </c>
+      <c r="I13" s="32" t="s">
         <v>226</v>
-      </c>
-      <c r="I13" s="32" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="56">
       <c r="A14" s="24" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C14" s="37" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D14" s="33" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E14" s="37" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F14" s="33" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G14" s="33">
         <v>4</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="I14" s="33" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="56">
       <c r="A15" s="24" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C15" s="37" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D15" s="33" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E15" s="37" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F15" s="33" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G15" s="33">
         <v>4</v>
       </c>
       <c r="H15" s="37" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="I15" s="33" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="56">
       <c r="A16" s="24" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="C16" s="37" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="D16" s="33" t="s">
-        <v>245</v>
-      </c>
-      <c r="E16" s="33" t="s">
-        <v>243</v>
+        <v>240</v>
+      </c>
+      <c r="E16" s="37" t="s">
+        <v>247</v>
       </c>
       <c r="F16" s="33" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="G16" s="33">
         <v>4</v>
       </c>
       <c r="H16" s="37" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="I16" s="33" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>

--- a/CoreRefiner工作表.xlsx
+++ b/CoreRefiner工作表.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_HOME_study\CoreRefiner\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B6CB491-FFE0-45C7-96BA-B0131E3ABB31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A201695-D644-4B22-ACF1-D0774F8FA472}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="任务表" sheetId="1" r:id="rId1"/>
-    <sheet name="Node表" sheetId="2" r:id="rId2"/>
+    <sheet name="细则表" sheetId="3" r:id="rId2"/>
+    <sheet name="Node表" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Node表!$A$4:$I$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Node表!$A$1:$I$11</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="294">
   <si>
     <t>内容详情</t>
   </si>
@@ -979,12 +980,196 @@
 重复之间不会相互产生效果。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>商店区规则：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>起始价：base =&gt; 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>价格刷新公式为 = base + step * count</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>递增值：step =&gt; 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刷新次：视实际情况而定</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>炼成区规则：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[1级] -&gt; [1级] =&gt; [2级]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[2级] -&gt; [1级] =&gt; [2级]+退回4元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[3级] -&gt; [1级] =&gt; [3级]+退回4元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[2级] -&gt; [2级] =&gt; [3级]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[3级] -&gt; [2级] =&gt; [3级]+退回8元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[3级]无升级需求</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>买卖规则：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>合成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进化1级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8+1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>造价 / 2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>成本 =</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>收入 =</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>造价 + 炼成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16 + 3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>32 + 4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>36 + 5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>44 + 6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进化2级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进化3级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>……</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>升级、合成、进化 均价 = 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>展现：[素材] -&gt; [主体] =&gt; [结果]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Node等级上限为3级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[1级] -&gt; [2级] =&gt; 不成立</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>成立标准：主体等级 &lt;= 素材等级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>成立标准：主体等级 = 素材等级 = 3级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>升级情况说明：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>合成情况说明：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进化情况说明：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>成立标准：主体等级 = 素材等级 = 3级，并且此两者符合进化表的炼成需求</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>结果为一个全新的1级Node。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>规则说明：把素材消耗掉，并让主体提升一个等级。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>结果为一个3级的合成类Node，其包含两个效果，且起作用时以先主体后素材的顺序生效，并且基础数值为平均值，Node渲染也是一半一半。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>规则说明：把两个满级(3级)的Node炼成个复合型的满级(3级)Node。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>规则说明：两个满级(3级)的Node炼成一个全新的1级Node。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>*注：Core类不参与除了升级外，任何Shop区内的事情，Core升级到3级后就和一切炼成区的事情没关系了。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1032,8 +1217,42 @@
       <sz val="20"/>
       <color theme="1"/>
       <name val="黑体"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="黑体"/>
       <family val="3"/>
-      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="黑体"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="黑体"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="黑体"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="黑体"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="黑体"/>
     </font>
   </fonts>
   <fills count="13">
@@ -1152,7 +1371,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1201,7 +1420,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1262,6 +1480,16 @@
     <xf numFmtId="0" fontId="4" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -3999,7 +4227,7 @@
       <c r="D65" s="7">
         <v>46265</v>
       </c>
-      <c r="E65" s="38" t="s">
+      <c r="E65" s="37" t="s">
         <v>127</v>
       </c>
       <c r="F65" s="2"/>
@@ -4407,6 +4635,9 @@
     <row r="76" spans="1:26">
       <c r="A76" s="15">
         <v>75</v>
+      </c>
+      <c r="B76" s="16" t="s">
+        <v>146</v>
       </c>
       <c r="C76" s="16"/>
       <c r="D76" s="16"/>
@@ -4676,9 +4907,6 @@
     <row r="85" spans="1:26">
       <c r="A85" s="15">
         <v>84</v>
-      </c>
-      <c r="B85" s="16" t="s">
-        <v>146</v>
       </c>
       <c r="C85" s="16"/>
       <c r="D85" s="16"/>
@@ -30368,8 +30596,262 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F802CC3A-307A-4FD9-9700-764C18E7FDAA}">
+  <dimension ref="A1:K37"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="16384" width="8.6640625" style="39"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="25.5">
+      <c r="A1" s="38" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="25.5">
+      <c r="A3" s="38" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="25.5">
+      <c r="A5" s="38" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="25.5">
+      <c r="A7" s="38" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="17.5">
+      <c r="A8" s="40" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="17.5">
+      <c r="A9" s="40" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="17.5">
+      <c r="A10" s="40" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="17.5">
+      <c r="A11" s="40" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="17.5">
+      <c r="A12" s="41" t="s">
+        <v>260</v>
+      </c>
+      <c r="D12" s="42" t="s">
+        <v>261</v>
+      </c>
+      <c r="E12" s="42" t="s">
+        <v>262</v>
+      </c>
+      <c r="F12" s="42" t="s">
+        <v>263</v>
+      </c>
+      <c r="G12" s="42" t="s">
+        <v>264</v>
+      </c>
+      <c r="H12" s="42" t="s">
+        <v>265</v>
+      </c>
+      <c r="I12" s="42" t="s">
+        <v>275</v>
+      </c>
+      <c r="J12" s="42" t="s">
+        <v>276</v>
+      </c>
+      <c r="K12" s="42" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="17.5">
+      <c r="A13" s="41" t="s">
+        <v>268</v>
+      </c>
+      <c r="B13" s="41" t="s">
+        <v>270</v>
+      </c>
+      <c r="D13" s="42">
+        <v>4</v>
+      </c>
+      <c r="E13" s="42" t="s">
+        <v>266</v>
+      </c>
+      <c r="F13" s="42" t="s">
+        <v>271</v>
+      </c>
+      <c r="G13" s="42" t="s">
+        <v>272</v>
+      </c>
+      <c r="H13" s="42" t="s">
+        <v>272</v>
+      </c>
+      <c r="I13" s="42" t="s">
+        <v>273</v>
+      </c>
+      <c r="J13" s="42" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="17.5">
+      <c r="A14" s="41" t="s">
+        <v>269</v>
+      </c>
+      <c r="B14" s="41" t="s">
+        <v>267</v>
+      </c>
+      <c r="D14" s="42">
+        <v>2</v>
+      </c>
+      <c r="E14" s="42">
+        <v>4</v>
+      </c>
+      <c r="F14" s="42">
+        <v>8</v>
+      </c>
+      <c r="G14" s="42">
+        <v>16</v>
+      </c>
+      <c r="H14" s="42">
+        <v>16</v>
+      </c>
+      <c r="I14" s="42">
+        <v>18</v>
+      </c>
+      <c r="J14" s="42">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="25.5">
+      <c r="A16" s="38" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="17.5">
+      <c r="A17" s="41" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="17.5">
+      <c r="A18" s="40" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="17.5">
+      <c r="A19" s="43" t="s">
+        <v>284</v>
+      </c>
+      <c r="H19" s="40"/>
+    </row>
+    <row r="20" spans="1:8" ht="17.5">
+      <c r="A20" s="40" t="s">
+        <v>289</v>
+      </c>
+      <c r="H20" s="40"/>
+    </row>
+    <row r="21" spans="1:8" ht="17.5">
+      <c r="A21" s="44" t="s">
+        <v>282</v>
+      </c>
+      <c r="H21" s="40"/>
+    </row>
+    <row r="22" spans="1:8" ht="17.5">
+      <c r="A22" s="40" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="17.5">
+      <c r="A23" s="40" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="17.5">
+      <c r="A24" s="40" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="17.5">
+      <c r="A25" s="40" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="17.5">
+      <c r="A26" s="40" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="17.5">
+      <c r="A27" s="40" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="17.5">
+      <c r="A28" s="40" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="17.5">
+      <c r="A29" s="43" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="17.5">
+      <c r="A30" s="40" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="17.5">
+      <c r="A31" s="44" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="17.5">
+      <c r="A32" s="44" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" ht="17.5">
+      <c r="A33" s="43" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" ht="17.5">
+      <c r="A34" s="40" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" ht="17.5">
+      <c r="A35" s="44" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" ht="17.5">
+      <c r="A36" s="44" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="45" t="s">
+        <v>293</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3258B9DE-144B-4A1D-96F7-444B72BE7902}">
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="15.58203125" style="1" customWidth="1"/>
@@ -30384,147 +30866,224 @@
     <col min="10" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="25.5">
-      <c r="A1" s="18" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="25.5">
+    <row r="1" spans="1:9" ht="21">
+      <c r="A1" s="24" t="s">
+        <v>157</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>158</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>160</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>180</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>159</v>
+      </c>
+      <c r="F1" s="24" t="s">
+        <v>194</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="H1" s="24" t="s">
+        <v>162</v>
+      </c>
+      <c r="I1" s="24" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="56">
       <c r="A2" s="18" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="21">
-      <c r="A4" s="25" t="s">
-        <v>157</v>
-      </c>
-      <c r="B4" s="25" t="s">
-        <v>158</v>
-      </c>
-      <c r="C4" s="25" t="s">
-        <v>160</v>
-      </c>
-      <c r="D4" s="25" t="s">
-        <v>180</v>
-      </c>
-      <c r="E4" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="F4" s="25" t="s">
-        <v>194</v>
-      </c>
-      <c r="G4" s="25" t="s">
-        <v>161</v>
-      </c>
-      <c r="H4" s="25" t="s">
-        <v>162</v>
-      </c>
-      <c r="I4" s="25" t="s">
-        <v>163</v>
+        <v>154</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="C2" s="25" t="s">
+        <v>183</v>
+      </c>
+      <c r="D2" s="26" t="s">
+        <v>181</v>
+      </c>
+      <c r="E2" s="25" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="G2" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="H2" s="25" t="s">
+        <v>182</v>
+      </c>
+      <c r="I2" s="25" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="56">
+      <c r="A3" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="C3" s="27" t="s">
+        <v>184</v>
+      </c>
+      <c r="D3" s="28" t="s">
+        <v>185</v>
+      </c>
+      <c r="E3" s="27" t="s">
+        <v>187</v>
+      </c>
+      <c r="F3" s="27" t="s">
+        <v>195</v>
+      </c>
+      <c r="G3" s="28">
+        <v>4</v>
+      </c>
+      <c r="H3" s="27" t="s">
+        <v>188</v>
+      </c>
+      <c r="I3" s="27" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="56">
+      <c r="A4" s="20" t="s">
+        <v>165</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="C4" s="29" t="s">
+        <v>196</v>
+      </c>
+      <c r="D4" s="29" t="s">
+        <v>193</v>
+      </c>
+      <c r="E4" s="29" t="s">
+        <v>197</v>
+      </c>
+      <c r="F4" s="29" t="s">
+        <v>230</v>
+      </c>
+      <c r="G4" s="29">
+        <v>4</v>
+      </c>
+      <c r="H4" s="33" t="s">
+        <v>220</v>
+      </c>
+      <c r="I4" s="29" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="56">
-      <c r="A5" s="19" t="s">
-        <v>154</v>
-      </c>
-      <c r="B5" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="C5" s="26" t="s">
-        <v>183</v>
-      </c>
-      <c r="D5" s="27" t="s">
-        <v>181</v>
-      </c>
-      <c r="E5" s="26" t="s">
-        <v>186</v>
-      </c>
-      <c r="F5" s="26" t="s">
-        <v>195</v>
-      </c>
-      <c r="G5" s="27" t="s">
-        <v>179</v>
-      </c>
-      <c r="H5" s="26" t="s">
-        <v>182</v>
-      </c>
-      <c r="I5" s="26" t="s">
-        <v>189</v>
+      <c r="A5" s="20" t="s">
+        <v>165</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="C5" s="29" t="s">
+        <v>198</v>
+      </c>
+      <c r="D5" s="29" t="s">
+        <v>201</v>
+      </c>
+      <c r="E5" s="29" t="s">
+        <v>204</v>
+      </c>
+      <c r="F5" s="29" t="s">
+        <v>230</v>
+      </c>
+      <c r="G5" s="29">
+        <v>4</v>
+      </c>
+      <c r="H5" s="33" t="s">
+        <v>220</v>
+      </c>
+      <c r="I5" s="29" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="56">
       <c r="A6" s="20" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="C6" s="28" t="s">
-        <v>184</v>
+        <v>173</v>
+      </c>
+      <c r="C6" s="29" t="s">
+        <v>199</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>185</v>
-      </c>
-      <c r="E6" s="28" t="s">
-        <v>187</v>
-      </c>
-      <c r="F6" s="28" t="s">
-        <v>195</v>
+        <v>202</v>
+      </c>
+      <c r="E6" s="29" t="s">
+        <v>205</v>
+      </c>
+      <c r="F6" s="29" t="s">
+        <v>230</v>
       </c>
       <c r="G6" s="29">
         <v>4</v>
       </c>
-      <c r="H6" s="28" t="s">
-        <v>188</v>
-      </c>
-      <c r="I6" s="28" t="s">
-        <v>190</v>
+      <c r="H6" s="33" t="s">
+        <v>220</v>
+      </c>
+      <c r="I6" s="29" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="56">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="20" t="s">
         <v>165</v>
       </c>
-      <c r="B7" s="21" t="s">
-        <v>191</v>
-      </c>
-      <c r="C7" s="30" t="s">
-        <v>196</v>
-      </c>
-      <c r="D7" s="30" t="s">
-        <v>193</v>
-      </c>
-      <c r="E7" s="30" t="s">
-        <v>197</v>
-      </c>
-      <c r="F7" s="30" t="s">
+      <c r="B7" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="C7" s="29" t="s">
+        <v>200</v>
+      </c>
+      <c r="D7" s="29" t="s">
+        <v>203</v>
+      </c>
+      <c r="E7" s="29" t="s">
+        <v>206</v>
+      </c>
+      <c r="F7" s="29" t="s">
         <v>230</v>
       </c>
-      <c r="G7" s="30">
+      <c r="G7" s="29">
         <v>4</v>
       </c>
-      <c r="H7" s="34" t="s">
+      <c r="H7" s="33" t="s">
         <v>220</v>
       </c>
-      <c r="I7" s="30" t="s">
-        <v>207</v>
+      <c r="I7" s="29" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="56">
       <c r="A8" s="21" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>172</v>
-      </c>
-      <c r="C8" s="30" t="s">
-        <v>198</v>
+        <v>174</v>
+      </c>
+      <c r="C8" s="34" t="s">
+        <v>216</v>
       </c>
       <c r="D8" s="30" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="E8" s="30" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="F8" s="30" t="s">
         <v>230</v>
@@ -30533,246 +31092,159 @@
         <v>4</v>
       </c>
       <c r="H8" s="34" t="s">
-        <v>220</v>
-      </c>
-      <c r="I8" s="30" t="s">
-        <v>208</v>
+        <v>218</v>
+      </c>
+      <c r="I8" s="34" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="56">
       <c r="A9" s="21" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C9" s="30" t="s">
-        <v>199</v>
+        <v>215</v>
       </c>
       <c r="D9" s="30" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="E9" s="30" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="F9" s="30" t="s">
-        <v>230</v>
+        <v>213</v>
       </c>
       <c r="G9" s="30">
         <v>4</v>
       </c>
       <c r="H9" s="34" t="s">
-        <v>220</v>
-      </c>
-      <c r="I9" s="30" t="s">
-        <v>209</v>
+        <v>221</v>
+      </c>
+      <c r="I9" s="34" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="56">
-      <c r="A10" s="21" t="s">
-        <v>165</v>
-      </c>
-      <c r="B10" s="21" t="s">
-        <v>171</v>
-      </c>
-      <c r="C10" s="30" t="s">
-        <v>200</v>
-      </c>
-      <c r="D10" s="30" t="s">
-        <v>203</v>
-      </c>
-      <c r="E10" s="30" t="s">
-        <v>206</v>
-      </c>
-      <c r="F10" s="30" t="s">
-        <v>230</v>
-      </c>
-      <c r="G10" s="30">
+      <c r="A10" s="22" t="s">
+        <v>167</v>
+      </c>
+      <c r="B10" s="22" t="s">
+        <v>176</v>
+      </c>
+      <c r="C10" s="35" t="s">
+        <v>223</v>
+      </c>
+      <c r="D10" s="31" t="s">
+        <v>222</v>
+      </c>
+      <c r="E10" s="35" t="s">
+        <v>224</v>
+      </c>
+      <c r="F10" s="31" t="s">
+        <v>231</v>
+      </c>
+      <c r="G10" s="31">
         <v>4</v>
       </c>
-      <c r="H10" s="34" t="s">
-        <v>220</v>
-      </c>
-      <c r="I10" s="30" t="s">
-        <v>210</v>
+      <c r="H10" s="35" t="s">
+        <v>225</v>
+      </c>
+      <c r="I10" s="31" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="56">
-      <c r="A11" s="22" t="s">
-        <v>166</v>
-      </c>
-      <c r="B11" s="22" t="s">
-        <v>174</v>
-      </c>
-      <c r="C11" s="35" t="s">
-        <v>216</v>
-      </c>
-      <c r="D11" s="31" t="s">
-        <v>212</v>
-      </c>
-      <c r="E11" s="31" t="s">
-        <v>214</v>
-      </c>
-      <c r="F11" s="31" t="s">
-        <v>230</v>
-      </c>
-      <c r="G11" s="31">
+      <c r="A11" s="23" t="s">
+        <v>168</v>
+      </c>
+      <c r="B11" s="23" t="s">
+        <v>177</v>
+      </c>
+      <c r="C11" s="36" t="s">
+        <v>229</v>
+      </c>
+      <c r="D11" s="32" t="s">
+        <v>227</v>
+      </c>
+      <c r="E11" s="36" t="s">
+        <v>232</v>
+      </c>
+      <c r="F11" s="32" t="s">
+        <v>213</v>
+      </c>
+      <c r="G11" s="32">
         <v>4</v>
       </c>
-      <c r="H11" s="35" t="s">
-        <v>218</v>
-      </c>
-      <c r="I11" s="35" t="s">
-        <v>217</v>
+      <c r="H11" s="36" t="s">
+        <v>244</v>
+      </c>
+      <c r="I11" s="32" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="56">
-      <c r="A12" s="22" t="s">
-        <v>166</v>
-      </c>
-      <c r="B12" s="22" t="s">
-        <v>175</v>
-      </c>
-      <c r="C12" s="31" t="s">
-        <v>215</v>
-      </c>
-      <c r="D12" s="31" t="s">
-        <v>211</v>
-      </c>
-      <c r="E12" s="31" t="s">
-        <v>215</v>
-      </c>
-      <c r="F12" s="31" t="s">
+      <c r="A12" s="23" t="s">
+        <v>168</v>
+      </c>
+      <c r="B12" s="23" t="s">
+        <v>178</v>
+      </c>
+      <c r="C12" s="36" t="s">
+        <v>233</v>
+      </c>
+      <c r="D12" s="32" t="s">
+        <v>228</v>
+      </c>
+      <c r="E12" s="36" t="s">
+        <v>234</v>
+      </c>
+      <c r="F12" s="32" t="s">
         <v>213</v>
       </c>
-      <c r="G12" s="31">
+      <c r="G12" s="32">
         <v>4</v>
       </c>
-      <c r="H12" s="35" t="s">
-        <v>221</v>
-      </c>
-      <c r="I12" s="35" t="s">
-        <v>219</v>
+      <c r="H12" s="36" t="s">
+        <v>235</v>
+      </c>
+      <c r="I12" s="32" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="56">
       <c r="A13" s="23" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>176</v>
+        <v>241</v>
       </c>
       <c r="C13" s="36" t="s">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="D13" s="32" t="s">
-        <v>222</v>
+        <v>240</v>
       </c>
       <c r="E13" s="36" t="s">
-        <v>224</v>
+        <v>247</v>
       </c>
       <c r="F13" s="32" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="G13" s="32">
         <v>4</v>
       </c>
       <c r="H13" s="36" t="s">
-        <v>225</v>
+        <v>246</v>
       </c>
       <c r="I13" s="32" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="56">
-      <c r="A14" s="24" t="s">
-        <v>168</v>
-      </c>
-      <c r="B14" s="24" t="s">
-        <v>177</v>
-      </c>
-      <c r="C14" s="37" t="s">
-        <v>229</v>
-      </c>
-      <c r="D14" s="33" t="s">
-        <v>227</v>
-      </c>
-      <c r="E14" s="37" t="s">
-        <v>232</v>
-      </c>
-      <c r="F14" s="33" t="s">
-        <v>213</v>
-      </c>
-      <c r="G14" s="33">
-        <v>4</v>
-      </c>
-      <c r="H14" s="37" t="s">
-        <v>244</v>
-      </c>
-      <c r="I14" s="33" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="56">
-      <c r="A15" s="24" t="s">
-        <v>168</v>
-      </c>
-      <c r="B15" s="24" t="s">
-        <v>178</v>
-      </c>
-      <c r="C15" s="37" t="s">
-        <v>233</v>
-      </c>
-      <c r="D15" s="33" t="s">
-        <v>228</v>
-      </c>
-      <c r="E15" s="37" t="s">
-        <v>234</v>
-      </c>
-      <c r="F15" s="33" t="s">
-        <v>213</v>
-      </c>
-      <c r="G15" s="33">
-        <v>4</v>
-      </c>
-      <c r="H15" s="37" t="s">
-        <v>235</v>
-      </c>
-      <c r="I15" s="33" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="56">
-      <c r="A16" s="24" t="s">
-        <v>168</v>
-      </c>
-      <c r="B16" s="24" t="s">
-        <v>241</v>
-      </c>
-      <c r="C16" s="37" t="s">
-        <v>238</v>
-      </c>
-      <c r="D16" s="33" t="s">
-        <v>240</v>
-      </c>
-      <c r="E16" s="37" t="s">
-        <v>247</v>
-      </c>
-      <c r="F16" s="33" t="s">
-        <v>239</v>
-      </c>
-      <c r="G16" s="33">
-        <v>4</v>
-      </c>
-      <c r="H16" s="37" t="s">
-        <v>246</v>
-      </c>
-      <c r="I16" s="33" t="s">
         <v>237</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:I14" xr:uid="{3258B9DE-144B-4A1D-96F7-444B72BE7902}"/>
+  <autoFilter ref="A1:I11" xr:uid="{3258B9DE-144B-4A1D-96F7-444B72BE7902}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/CoreRefiner工作表.xlsx
+++ b/CoreRefiner工作表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_HOME_study\CoreRefiner\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A201695-D644-4B22-ACF1-D0774F8FA472}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8FAD205-9975-4C63-B1D0-0F95D4086C91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="任务表" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Node表!$A$1:$I$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">任务表!$A$1:$Z$1000</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="306">
   <si>
     <t>内容详情</t>
   </si>
@@ -553,10 +554,6 @@
   </si>
   <si>
     <t>Bug的触发率太高了，而且目前没有必须实现该功能的必要。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Node添加流程：Label→填表→棋盘节点→装配步骤→步骤快照→图标设计→三语词条→价格标注→工厂配置</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1149,19 +1146,81 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>结果为一个3级的合成类Node，其包含两个效果，且起作用时以先主体后素材的顺序生效，并且基础数值为平均值，Node渲染也是一半一半。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>规则说明：把两个满级(3级)的Node炼成个复合型的满级(3级)Node。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>规则说明：两个满级(3级)的Node炼成一个全新的1级Node。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>*注：Core类不参与除了升级外，任何Shop区内的事情，Core升级到3级后就和一切炼成区的事情没关系了。</t>
+    <t>Node添加流程：定义标签→完善表单→棋盘节点→节点模组→装配步骤→步骤快照→图标设计→三语词条→工厂配置→实景测试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fusion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>结果为一个3级的合成类Node。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>*注1：Core类不参与除了升级外，任何Shop区内的事情，Core升级到3级后就和一切炼成区的事情没关系了。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>包含素材和主体双方的两个Node能力，且起作用时以先主体后素材的顺序生效。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>*主体名* &amp; *素材名*</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>*主体描述*
+*素材描述*</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>*主体的作用对象*
+*素材的作用对象*</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>节点半径：平均值
+冷却时间：平均值
+扩散半径：平均值
+扩散速度：平均值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>保留主体和素材独占的数值
+已是满级（3级），无变化空间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>合成类Node规则：包含素材和主体双方的两个Node能力，且起作用时以先主体后素材的顺序生效。基础数值取平均值，独有数值保持原样。Icon渲染对半分，左半边用主体Icon，右半边用素材Icon。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>*注3：类型相同的Node只有可能升级，不能用于合成和进化。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>*注2：Core类永远不会成为素材。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fusion节点框架</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>规则说明：把两个满级(3级)的Node炼成个合成类的满级(3级)Node。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>合成类Node出生即为满级。
+包含素材和主体双方的两个Node能力，且起作用时以先主体后素材的顺序生效。
+基础数值取平均值，独有数值保持原样。
+Icon渲染对半分，左半边用主体Icon，右半边用素材Icon。
+详情见Node表。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1169,7 +1228,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1254,8 +1313,22 @@
       <color theme="1"/>
       <name val="黑体"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color theme="0"/>
+      <name val="黑体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="黑体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1328,6 +1401,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -1371,7 +1450,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1416,9 +1495,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1490,6 +1566,31 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1784,9 +1885,9 @@
   <sheetFormatPr defaultColWidth="19.58203125" defaultRowHeight="21"/>
   <cols>
     <col min="1" max="1" width="15.58203125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="40.58203125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="40.58203125" style="53" customWidth="1"/>
     <col min="3" max="3" width="15.58203125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="20.58203125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="20.58203125" style="51" customWidth="1"/>
     <col min="5" max="5" width="120.58203125" style="3" customWidth="1"/>
     <col min="6" max="16384" width="19.58203125" style="3"/>
   </cols>
@@ -1795,13 +1896,13 @@
       <c r="A1" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="52" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="48" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="5" t="s">
@@ -2736,7 +2837,7 @@
       <c r="A26" s="6">
         <v>25</v>
       </c>
-      <c r="B26" s="14" t="s">
+      <c r="B26" s="4" t="s">
         <v>52</v>
       </c>
       <c r="C26" s="6" t="s">
@@ -3620,7 +3721,7 @@
         <v>46251</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
@@ -4227,7 +4328,7 @@
       <c r="D65" s="7">
         <v>46265</v>
       </c>
-      <c r="E65" s="37" t="s">
+      <c r="E65" s="36" t="s">
         <v>127</v>
       </c>
       <c r="F65" s="2"/>
@@ -4380,7 +4481,7 @@
         <v>46266</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
@@ -4608,7 +4709,7 @@
         <v>46276</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F75" s="2"/>
       <c r="G75" s="2"/>
@@ -4632,16 +4733,22 @@
       <c r="Y75" s="2"/>
       <c r="Z75" s="2"/>
     </row>
-    <row r="76" spans="1:26">
-      <c r="A76" s="15">
+    <row r="76" spans="1:26" ht="105">
+      <c r="A76" s="6">
         <v>75</v>
       </c>
-      <c r="B76" s="16" t="s">
-        <v>146</v>
-      </c>
-      <c r="C76" s="16"/>
-      <c r="D76" s="16"/>
-      <c r="E76" s="16"/>
+      <c r="B76" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="C76" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D76" s="7">
+        <v>46277</v>
+      </c>
+      <c r="E76" s="4" t="s">
+        <v>305</v>
+      </c>
       <c r="F76" s="2"/>
       <c r="G76" s="2"/>
       <c r="H76" s="2"/>
@@ -4668,9 +4775,11 @@
       <c r="A77" s="15">
         <v>76</v>
       </c>
-      <c r="B77" s="16"/>
+      <c r="B77" s="16" t="s">
+        <v>146</v>
+      </c>
       <c r="C77" s="16"/>
-      <c r="D77" s="16"/>
+      <c r="D77" s="49"/>
       <c r="E77" s="16"/>
       <c r="F77" s="2"/>
       <c r="G77" s="2"/>
@@ -4700,7 +4809,7 @@
       </c>
       <c r="B78" s="16"/>
       <c r="C78" s="16"/>
-      <c r="D78" s="16"/>
+      <c r="D78" s="49"/>
       <c r="E78" s="16"/>
       <c r="F78" s="2"/>
       <c r="G78" s="2"/>
@@ -4730,7 +4839,7 @@
       </c>
       <c r="B79" s="16"/>
       <c r="C79" s="16"/>
-      <c r="D79" s="16"/>
+      <c r="D79" s="49"/>
       <c r="E79" s="16"/>
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
@@ -4760,7 +4869,7 @@
       </c>
       <c r="B80" s="16"/>
       <c r="C80" s="16"/>
-      <c r="D80" s="16"/>
+      <c r="D80" s="49"/>
       <c r="E80" s="16"/>
       <c r="F80" s="2"/>
       <c r="G80" s="2"/>
@@ -4790,7 +4899,7 @@
       </c>
       <c r="B81" s="16"/>
       <c r="C81" s="16"/>
-      <c r="D81" s="16"/>
+      <c r="D81" s="49"/>
       <c r="E81" s="16"/>
       <c r="F81" s="2"/>
       <c r="G81" s="2"/>
@@ -4820,7 +4929,7 @@
       </c>
       <c r="B82" s="16"/>
       <c r="C82" s="16"/>
-      <c r="D82" s="16"/>
+      <c r="D82" s="49"/>
       <c r="E82" s="16"/>
       <c r="F82" s="2"/>
       <c r="G82" s="2"/>
@@ -4848,9 +4957,9 @@
       <c r="A83" s="15">
         <v>82</v>
       </c>
-      <c r="B83" s="17"/>
+      <c r="B83" s="16"/>
       <c r="C83" s="16"/>
-      <c r="D83" s="16"/>
+      <c r="D83" s="49"/>
       <c r="E83" s="16"/>
       <c r="F83" s="2"/>
       <c r="G83" s="2"/>
@@ -4878,9 +4987,9 @@
       <c r="A84" s="15">
         <v>83</v>
       </c>
-      <c r="B84" s="17"/>
+      <c r="B84" s="16"/>
       <c r="C84" s="16"/>
-      <c r="D84" s="16"/>
+      <c r="D84" s="49"/>
       <c r="E84" s="16"/>
       <c r="F84" s="2"/>
       <c r="G84" s="2"/>
@@ -4909,7 +5018,7 @@
         <v>84</v>
       </c>
       <c r="C85" s="16"/>
-      <c r="D85" s="16"/>
+      <c r="D85" s="49"/>
       <c r="E85" s="16"/>
       <c r="F85" s="2"/>
       <c r="G85" s="2"/>
@@ -4941,7 +5050,7 @@
         <v>147</v>
       </c>
       <c r="C86" s="16"/>
-      <c r="D86" s="16"/>
+      <c r="D86" s="49"/>
       <c r="E86" s="16"/>
       <c r="F86" s="2"/>
       <c r="G86" s="2"/>
@@ -4970,10 +5079,10 @@
         <v>86</v>
       </c>
       <c r="B87" s="16" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C87" s="16"/>
-      <c r="D87" s="16"/>
+      <c r="D87" s="49"/>
       <c r="E87" s="16"/>
       <c r="F87" s="2"/>
       <c r="G87" s="2"/>
@@ -5003,7 +5112,7 @@
       </c>
       <c r="B88" s="16"/>
       <c r="C88" s="16"/>
-      <c r="D88" s="16"/>
+      <c r="D88" s="49"/>
       <c r="E88" s="16"/>
       <c r="F88" s="2"/>
       <c r="G88" s="2"/>
@@ -5033,7 +5142,7 @@
       </c>
       <c r="B89" s="16"/>
       <c r="C89" s="16"/>
-      <c r="D89" s="16"/>
+      <c r="D89" s="49"/>
       <c r="E89" s="16"/>
       <c r="F89" s="2"/>
       <c r="G89" s="2"/>
@@ -5063,7 +5172,7 @@
       </c>
       <c r="B90" s="16"/>
       <c r="C90" s="16"/>
-      <c r="D90" s="16"/>
+      <c r="D90" s="49"/>
       <c r="E90" s="16"/>
       <c r="F90" s="2"/>
       <c r="G90" s="2"/>
@@ -5093,7 +5202,7 @@
       </c>
       <c r="B91" s="16"/>
       <c r="C91" s="16"/>
-      <c r="D91" s="16"/>
+      <c r="D91" s="49"/>
       <c r="E91" s="16"/>
       <c r="F91" s="2"/>
       <c r="G91" s="2"/>
@@ -5123,7 +5232,7 @@
       </c>
       <c r="B92" s="16"/>
       <c r="C92" s="16"/>
-      <c r="D92" s="16"/>
+      <c r="D92" s="49"/>
       <c r="E92" s="16"/>
       <c r="F92" s="2"/>
       <c r="G92" s="2"/>
@@ -5153,7 +5262,7 @@
       </c>
       <c r="B93" s="16"/>
       <c r="C93" s="16"/>
-      <c r="D93" s="16"/>
+      <c r="D93" s="49"/>
       <c r="E93" s="16"/>
       <c r="F93" s="2"/>
       <c r="G93" s="2"/>
@@ -5183,7 +5292,7 @@
       </c>
       <c r="B94" s="16"/>
       <c r="C94" s="16"/>
-      <c r="D94" s="16"/>
+      <c r="D94" s="49"/>
       <c r="E94" s="16"/>
       <c r="F94" s="2"/>
       <c r="G94" s="2"/>
@@ -5213,7 +5322,7 @@
       </c>
       <c r="B95" s="16"/>
       <c r="C95" s="16"/>
-      <c r="D95" s="16"/>
+      <c r="D95" s="49"/>
       <c r="E95" s="16"/>
       <c r="F95" s="2"/>
       <c r="G95" s="2"/>
@@ -5243,7 +5352,7 @@
       </c>
       <c r="B96" s="16"/>
       <c r="C96" s="16"/>
-      <c r="D96" s="16"/>
+      <c r="D96" s="49"/>
       <c r="E96" s="16"/>
       <c r="F96" s="2"/>
       <c r="G96" s="2"/>
@@ -5273,7 +5382,7 @@
       </c>
       <c r="B97" s="16"/>
       <c r="C97" s="16"/>
-      <c r="D97" s="16"/>
+      <c r="D97" s="49"/>
       <c r="E97" s="16"/>
       <c r="F97" s="2"/>
       <c r="G97" s="2"/>
@@ -5303,7 +5412,7 @@
       </c>
       <c r="B98" s="16"/>
       <c r="C98" s="16"/>
-      <c r="D98" s="16"/>
+      <c r="D98" s="49"/>
       <c r="E98" s="16"/>
       <c r="F98" s="2"/>
       <c r="G98" s="2"/>
@@ -5333,7 +5442,7 @@
       </c>
       <c r="B99" s="16"/>
       <c r="C99" s="16"/>
-      <c r="D99" s="16"/>
+      <c r="D99" s="49"/>
       <c r="E99" s="16"/>
       <c r="F99" s="2"/>
       <c r="G99" s="2"/>
@@ -5363,7 +5472,7 @@
       </c>
       <c r="B100" s="16"/>
       <c r="C100" s="16"/>
-      <c r="D100" s="16"/>
+      <c r="D100" s="49"/>
       <c r="E100" s="16"/>
       <c r="F100" s="2"/>
       <c r="G100" s="2"/>
@@ -5393,7 +5502,7 @@
       </c>
       <c r="B101" s="16"/>
       <c r="C101" s="16"/>
-      <c r="D101" s="16"/>
+      <c r="D101" s="49"/>
       <c r="E101" s="16"/>
       <c r="F101" s="2"/>
       <c r="G101" s="2"/>
@@ -5421,7 +5530,7 @@
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
-      <c r="D102" s="2"/>
+      <c r="D102" s="50"/>
       <c r="E102" s="2"/>
       <c r="F102" s="2"/>
       <c r="G102" s="2"/>
@@ -5449,7 +5558,7 @@
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
-      <c r="D103" s="2"/>
+      <c r="D103" s="50"/>
       <c r="E103" s="2"/>
       <c r="F103" s="2"/>
       <c r="G103" s="2"/>
@@ -5477,7 +5586,7 @@
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
-      <c r="D104" s="2"/>
+      <c r="D104" s="50"/>
       <c r="E104" s="2"/>
       <c r="F104" s="2"/>
       <c r="G104" s="2"/>
@@ -5505,7 +5614,7 @@
       <c r="A105" s="2"/>
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
-      <c r="D105" s="2"/>
+      <c r="D105" s="50"/>
       <c r="E105" s="2"/>
       <c r="F105" s="2"/>
       <c r="G105" s="2"/>
@@ -5533,7 +5642,7 @@
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
-      <c r="D106" s="2"/>
+      <c r="D106" s="50"/>
       <c r="E106" s="2"/>
       <c r="F106" s="2"/>
       <c r="G106" s="2"/>
@@ -5561,7 +5670,7 @@
       <c r="A107" s="2"/>
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
-      <c r="D107" s="2"/>
+      <c r="D107" s="50"/>
       <c r="E107" s="2"/>
       <c r="F107" s="2"/>
       <c r="G107" s="2"/>
@@ -5589,7 +5698,7 @@
       <c r="A108" s="2"/>
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
-      <c r="D108" s="2"/>
+      <c r="D108" s="50"/>
       <c r="E108" s="2"/>
       <c r="F108" s="2"/>
       <c r="G108" s="2"/>
@@ -5617,7 +5726,7 @@
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="2"/>
-      <c r="D109" s="2"/>
+      <c r="D109" s="50"/>
       <c r="E109" s="2"/>
       <c r="F109" s="2"/>
       <c r="G109" s="2"/>
@@ -5645,7 +5754,7 @@
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="2"/>
-      <c r="D110" s="2"/>
+      <c r="D110" s="50"/>
       <c r="E110" s="2"/>
       <c r="F110" s="2"/>
       <c r="G110" s="2"/>
@@ -5673,7 +5782,7 @@
       <c r="A111" s="2"/>
       <c r="B111" s="2"/>
       <c r="C111" s="2"/>
-      <c r="D111" s="2"/>
+      <c r="D111" s="50"/>
       <c r="E111" s="2"/>
       <c r="F111" s="2"/>
       <c r="G111" s="2"/>
@@ -5701,7 +5810,7 @@
       <c r="A112" s="2"/>
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
-      <c r="D112" s="2"/>
+      <c r="D112" s="50"/>
       <c r="E112" s="2"/>
       <c r="F112" s="2"/>
       <c r="G112" s="2"/>
@@ -5729,7 +5838,7 @@
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="2"/>
-      <c r="D113" s="2"/>
+      <c r="D113" s="50"/>
       <c r="E113" s="2"/>
       <c r="F113" s="2"/>
       <c r="G113" s="2"/>
@@ -5757,7 +5866,7 @@
       <c r="A114" s="2"/>
       <c r="B114" s="2"/>
       <c r="C114" s="2"/>
-      <c r="D114" s="2"/>
+      <c r="D114" s="50"/>
       <c r="E114" s="2"/>
       <c r="F114" s="2"/>
       <c r="G114" s="2"/>
@@ -5785,7 +5894,7 @@
       <c r="A115" s="2"/>
       <c r="B115" s="2"/>
       <c r="C115" s="2"/>
-      <c r="D115" s="2"/>
+      <c r="D115" s="50"/>
       <c r="E115" s="2"/>
       <c r="F115" s="2"/>
       <c r="G115" s="2"/>
@@ -5813,7 +5922,7 @@
       <c r="A116" s="2"/>
       <c r="B116" s="2"/>
       <c r="C116" s="2"/>
-      <c r="D116" s="2"/>
+      <c r="D116" s="50"/>
       <c r="E116" s="2"/>
       <c r="F116" s="2"/>
       <c r="G116" s="2"/>
@@ -5841,7 +5950,7 @@
       <c r="A117" s="2"/>
       <c r="B117" s="2"/>
       <c r="C117" s="2"/>
-      <c r="D117" s="2"/>
+      <c r="D117" s="50"/>
       <c r="E117" s="2"/>
       <c r="F117" s="2"/>
       <c r="G117" s="2"/>
@@ -5869,7 +5978,7 @@
       <c r="A118" s="2"/>
       <c r="B118" s="2"/>
       <c r="C118" s="2"/>
-      <c r="D118" s="2"/>
+      <c r="D118" s="50"/>
       <c r="E118" s="2"/>
       <c r="F118" s="2"/>
       <c r="G118" s="2"/>
@@ -5897,7 +6006,7 @@
       <c r="A119" s="2"/>
       <c r="B119" s="2"/>
       <c r="C119" s="2"/>
-      <c r="D119" s="2"/>
+      <c r="D119" s="50"/>
       <c r="E119" s="2"/>
       <c r="F119" s="2"/>
       <c r="G119" s="2"/>
@@ -5925,7 +6034,7 @@
       <c r="A120" s="2"/>
       <c r="B120" s="2"/>
       <c r="C120" s="2"/>
-      <c r="D120" s="2"/>
+      <c r="D120" s="50"/>
       <c r="E120" s="2"/>
       <c r="F120" s="2"/>
       <c r="G120" s="2"/>
@@ -5953,7 +6062,7 @@
       <c r="A121" s="2"/>
       <c r="B121" s="2"/>
       <c r="C121" s="2"/>
-      <c r="D121" s="2"/>
+      <c r="D121" s="50"/>
       <c r="E121" s="2"/>
       <c r="F121" s="2"/>
       <c r="G121" s="2"/>
@@ -5981,7 +6090,7 @@
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="C122" s="2"/>
-      <c r="D122" s="2"/>
+      <c r="D122" s="50"/>
       <c r="E122" s="2"/>
       <c r="F122" s="2"/>
       <c r="G122" s="2"/>
@@ -6009,7 +6118,7 @@
       <c r="A123" s="2"/>
       <c r="B123" s="2"/>
       <c r="C123" s="2"/>
-      <c r="D123" s="2"/>
+      <c r="D123" s="50"/>
       <c r="E123" s="2"/>
       <c r="F123" s="2"/>
       <c r="G123" s="2"/>
@@ -6037,7 +6146,7 @@
       <c r="A124" s="2"/>
       <c r="B124" s="2"/>
       <c r="C124" s="2"/>
-      <c r="D124" s="2"/>
+      <c r="D124" s="50"/>
       <c r="E124" s="2"/>
       <c r="F124" s="2"/>
       <c r="G124" s="2"/>
@@ -6065,7 +6174,7 @@
       <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="C125" s="2"/>
-      <c r="D125" s="2"/>
+      <c r="D125" s="50"/>
       <c r="E125" s="2"/>
       <c r="F125" s="2"/>
       <c r="G125" s="2"/>
@@ -6093,7 +6202,7 @@
       <c r="A126" s="2"/>
       <c r="B126" s="2"/>
       <c r="C126" s="2"/>
-      <c r="D126" s="2"/>
+      <c r="D126" s="50"/>
       <c r="E126" s="2"/>
       <c r="F126" s="2"/>
       <c r="G126" s="2"/>
@@ -6121,7 +6230,7 @@
       <c r="A127" s="2"/>
       <c r="B127" s="2"/>
       <c r="C127" s="2"/>
-      <c r="D127" s="2"/>
+      <c r="D127" s="50"/>
       <c r="E127" s="2"/>
       <c r="F127" s="2"/>
       <c r="G127" s="2"/>
@@ -6149,7 +6258,7 @@
       <c r="A128" s="2"/>
       <c r="B128" s="2"/>
       <c r="C128" s="2"/>
-      <c r="D128" s="2"/>
+      <c r="D128" s="50"/>
       <c r="E128" s="2"/>
       <c r="F128" s="2"/>
       <c r="G128" s="2"/>
@@ -6177,7 +6286,7 @@
       <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="C129" s="2"/>
-      <c r="D129" s="2"/>
+      <c r="D129" s="50"/>
       <c r="E129" s="2"/>
       <c r="F129" s="2"/>
       <c r="G129" s="2"/>
@@ -6205,7 +6314,7 @@
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="2"/>
-      <c r="D130" s="2"/>
+      <c r="D130" s="50"/>
       <c r="E130" s="2"/>
       <c r="F130" s="2"/>
       <c r="G130" s="2"/>
@@ -6233,7 +6342,7 @@
       <c r="A131" s="2"/>
       <c r="B131" s="2"/>
       <c r="C131" s="2"/>
-      <c r="D131" s="2"/>
+      <c r="D131" s="50"/>
       <c r="E131" s="2"/>
       <c r="F131" s="2"/>
       <c r="G131" s="2"/>
@@ -6261,7 +6370,7 @@
       <c r="A132" s="2"/>
       <c r="B132" s="2"/>
       <c r="C132" s="2"/>
-      <c r="D132" s="2"/>
+      <c r="D132" s="50"/>
       <c r="E132" s="2"/>
       <c r="F132" s="2"/>
       <c r="G132" s="2"/>
@@ -6289,7 +6398,7 @@
       <c r="A133" s="2"/>
       <c r="B133" s="2"/>
       <c r="C133" s="2"/>
-      <c r="D133" s="2"/>
+      <c r="D133" s="50"/>
       <c r="E133" s="2"/>
       <c r="F133" s="2"/>
       <c r="G133" s="2"/>
@@ -6317,7 +6426,7 @@
       <c r="A134" s="2"/>
       <c r="B134" s="2"/>
       <c r="C134" s="2"/>
-      <c r="D134" s="2"/>
+      <c r="D134" s="50"/>
       <c r="E134" s="2"/>
       <c r="F134" s="2"/>
       <c r="G134" s="2"/>
@@ -6345,7 +6454,7 @@
       <c r="A135" s="2"/>
       <c r="B135" s="2"/>
       <c r="C135" s="2"/>
-      <c r="D135" s="2"/>
+      <c r="D135" s="50"/>
       <c r="E135" s="2"/>
       <c r="F135" s="2"/>
       <c r="G135" s="2"/>
@@ -6373,7 +6482,7 @@
       <c r="A136" s="2"/>
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
-      <c r="D136" s="2"/>
+      <c r="D136" s="50"/>
       <c r="E136" s="2"/>
       <c r="F136" s="2"/>
       <c r="G136" s="2"/>
@@ -6401,7 +6510,7 @@
       <c r="A137" s="2"/>
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
-      <c r="D137" s="2"/>
+      <c r="D137" s="50"/>
       <c r="E137" s="2"/>
       <c r="F137" s="2"/>
       <c r="G137" s="2"/>
@@ -6429,7 +6538,7 @@
       <c r="A138" s="2"/>
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
-      <c r="D138" s="2"/>
+      <c r="D138" s="50"/>
       <c r="E138" s="2"/>
       <c r="F138" s="2"/>
       <c r="G138" s="2"/>
@@ -6457,7 +6566,7 @@
       <c r="A139" s="2"/>
       <c r="B139" s="2"/>
       <c r="C139" s="2"/>
-      <c r="D139" s="2"/>
+      <c r="D139" s="50"/>
       <c r="E139" s="2"/>
       <c r="F139" s="2"/>
       <c r="G139" s="2"/>
@@ -6485,7 +6594,7 @@
       <c r="A140" s="2"/>
       <c r="B140" s="2"/>
       <c r="C140" s="2"/>
-      <c r="D140" s="2"/>
+      <c r="D140" s="50"/>
       <c r="E140" s="2"/>
       <c r="F140" s="2"/>
       <c r="G140" s="2"/>
@@ -6513,7 +6622,7 @@
       <c r="A141" s="2"/>
       <c r="B141" s="2"/>
       <c r="C141" s="2"/>
-      <c r="D141" s="2"/>
+      <c r="D141" s="50"/>
       <c r="E141" s="2"/>
       <c r="F141" s="2"/>
       <c r="G141" s="2"/>
@@ -6541,7 +6650,7 @@
       <c r="A142" s="2"/>
       <c r="B142" s="2"/>
       <c r="C142" s="2"/>
-      <c r="D142" s="2"/>
+      <c r="D142" s="50"/>
       <c r="E142" s="2"/>
       <c r="F142" s="2"/>
       <c r="G142" s="2"/>
@@ -6569,7 +6678,7 @@
       <c r="A143" s="2"/>
       <c r="B143" s="2"/>
       <c r="C143" s="2"/>
-      <c r="D143" s="2"/>
+      <c r="D143" s="50"/>
       <c r="E143" s="2"/>
       <c r="F143" s="2"/>
       <c r="G143" s="2"/>
@@ -6597,7 +6706,7 @@
       <c r="A144" s="2"/>
       <c r="B144" s="2"/>
       <c r="C144" s="2"/>
-      <c r="D144" s="2"/>
+      <c r="D144" s="50"/>
       <c r="E144" s="2"/>
       <c r="F144" s="2"/>
       <c r="G144" s="2"/>
@@ -6625,7 +6734,7 @@
       <c r="A145" s="2"/>
       <c r="B145" s="2"/>
       <c r="C145" s="2"/>
-      <c r="D145" s="2"/>
+      <c r="D145" s="50"/>
       <c r="E145" s="2"/>
       <c r="F145" s="2"/>
       <c r="G145" s="2"/>
@@ -6653,7 +6762,7 @@
       <c r="A146" s="2"/>
       <c r="B146" s="2"/>
       <c r="C146" s="2"/>
-      <c r="D146" s="2"/>
+      <c r="D146" s="50"/>
       <c r="E146" s="2"/>
       <c r="F146" s="2"/>
       <c r="G146" s="2"/>
@@ -6681,7 +6790,7 @@
       <c r="A147" s="2"/>
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
-      <c r="D147" s="2"/>
+      <c r="D147" s="50"/>
       <c r="E147" s="2"/>
       <c r="F147" s="2"/>
       <c r="G147" s="2"/>
@@ -6709,7 +6818,7 @@
       <c r="A148" s="2"/>
       <c r="B148" s="2"/>
       <c r="C148" s="2"/>
-      <c r="D148" s="2"/>
+      <c r="D148" s="50"/>
       <c r="E148" s="2"/>
       <c r="F148" s="2"/>
       <c r="G148" s="2"/>
@@ -6737,7 +6846,7 @@
       <c r="A149" s="2"/>
       <c r="B149" s="2"/>
       <c r="C149" s="2"/>
-      <c r="D149" s="2"/>
+      <c r="D149" s="50"/>
       <c r="E149" s="2"/>
       <c r="F149" s="2"/>
       <c r="G149" s="2"/>
@@ -6765,7 +6874,7 @@
       <c r="A150" s="2"/>
       <c r="B150" s="2"/>
       <c r="C150" s="2"/>
-      <c r="D150" s="2"/>
+      <c r="D150" s="50"/>
       <c r="E150" s="2"/>
       <c r="F150" s="2"/>
       <c r="G150" s="2"/>
@@ -6793,7 +6902,7 @@
       <c r="A151" s="2"/>
       <c r="B151" s="2"/>
       <c r="C151" s="2"/>
-      <c r="D151" s="2"/>
+      <c r="D151" s="50"/>
       <c r="E151" s="2"/>
       <c r="F151" s="2"/>
       <c r="G151" s="2"/>
@@ -6821,7 +6930,7 @@
       <c r="A152" s="2"/>
       <c r="B152" s="2"/>
       <c r="C152" s="2"/>
-      <c r="D152" s="2"/>
+      <c r="D152" s="50"/>
       <c r="E152" s="2"/>
       <c r="F152" s="2"/>
       <c r="G152" s="2"/>
@@ -6849,7 +6958,7 @@
       <c r="A153" s="2"/>
       <c r="B153" s="2"/>
       <c r="C153" s="2"/>
-      <c r="D153" s="2"/>
+      <c r="D153" s="50"/>
       <c r="E153" s="2"/>
       <c r="F153" s="2"/>
       <c r="G153" s="2"/>
@@ -6877,7 +6986,7 @@
       <c r="A154" s="2"/>
       <c r="B154" s="2"/>
       <c r="C154" s="2"/>
-      <c r="D154" s="2"/>
+      <c r="D154" s="50"/>
       <c r="E154" s="2"/>
       <c r="F154" s="2"/>
       <c r="G154" s="2"/>
@@ -6905,7 +7014,7 @@
       <c r="A155" s="2"/>
       <c r="B155" s="2"/>
       <c r="C155" s="2"/>
-      <c r="D155" s="2"/>
+      <c r="D155" s="50"/>
       <c r="E155" s="2"/>
       <c r="F155" s="2"/>
       <c r="G155" s="2"/>
@@ -6933,7 +7042,7 @@
       <c r="A156" s="2"/>
       <c r="B156" s="2"/>
       <c r="C156" s="2"/>
-      <c r="D156" s="2"/>
+      <c r="D156" s="50"/>
       <c r="E156" s="2"/>
       <c r="F156" s="2"/>
       <c r="G156" s="2"/>
@@ -6961,7 +7070,7 @@
       <c r="A157" s="2"/>
       <c r="B157" s="2"/>
       <c r="C157" s="2"/>
-      <c r="D157" s="2"/>
+      <c r="D157" s="50"/>
       <c r="E157" s="2"/>
       <c r="F157" s="2"/>
       <c r="G157" s="2"/>
@@ -6989,7 +7098,7 @@
       <c r="A158" s="2"/>
       <c r="B158" s="2"/>
       <c r="C158" s="2"/>
-      <c r="D158" s="2"/>
+      <c r="D158" s="50"/>
       <c r="E158" s="2"/>
       <c r="F158" s="2"/>
       <c r="G158" s="2"/>
@@ -7017,7 +7126,7 @@
       <c r="A159" s="2"/>
       <c r="B159" s="2"/>
       <c r="C159" s="2"/>
-      <c r="D159" s="2"/>
+      <c r="D159" s="50"/>
       <c r="E159" s="2"/>
       <c r="F159" s="2"/>
       <c r="G159" s="2"/>
@@ -7045,7 +7154,7 @@
       <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="C160" s="2"/>
-      <c r="D160" s="2"/>
+      <c r="D160" s="50"/>
       <c r="E160" s="2"/>
       <c r="F160" s="2"/>
       <c r="G160" s="2"/>
@@ -7073,7 +7182,7 @@
       <c r="A161" s="2"/>
       <c r="B161" s="2"/>
       <c r="C161" s="2"/>
-      <c r="D161" s="2"/>
+      <c r="D161" s="50"/>
       <c r="E161" s="2"/>
       <c r="F161" s="2"/>
       <c r="G161" s="2"/>
@@ -7101,7 +7210,7 @@
       <c r="A162" s="2"/>
       <c r="B162" s="2"/>
       <c r="C162" s="2"/>
-      <c r="D162" s="2"/>
+      <c r="D162" s="50"/>
       <c r="E162" s="2"/>
       <c r="F162" s="2"/>
       <c r="G162" s="2"/>
@@ -7129,7 +7238,7 @@
       <c r="A163" s="2"/>
       <c r="B163" s="2"/>
       <c r="C163" s="2"/>
-      <c r="D163" s="2"/>
+      <c r="D163" s="50"/>
       <c r="E163" s="2"/>
       <c r="F163" s="2"/>
       <c r="G163" s="2"/>
@@ -7157,7 +7266,7 @@
       <c r="A164" s="2"/>
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
-      <c r="D164" s="2"/>
+      <c r="D164" s="50"/>
       <c r="E164" s="2"/>
       <c r="F164" s="2"/>
       <c r="G164" s="2"/>
@@ -7185,7 +7294,7 @@
       <c r="A165" s="2"/>
       <c r="B165" s="2"/>
       <c r="C165" s="2"/>
-      <c r="D165" s="2"/>
+      <c r="D165" s="50"/>
       <c r="E165" s="2"/>
       <c r="F165" s="2"/>
       <c r="G165" s="2"/>
@@ -7213,7 +7322,7 @@
       <c r="A166" s="2"/>
       <c r="B166" s="2"/>
       <c r="C166" s="2"/>
-      <c r="D166" s="2"/>
+      <c r="D166" s="50"/>
       <c r="E166" s="2"/>
       <c r="F166" s="2"/>
       <c r="G166" s="2"/>
@@ -7241,7 +7350,7 @@
       <c r="A167" s="2"/>
       <c r="B167" s="2"/>
       <c r="C167" s="2"/>
-      <c r="D167" s="2"/>
+      <c r="D167" s="50"/>
       <c r="E167" s="2"/>
       <c r="F167" s="2"/>
       <c r="G167" s="2"/>
@@ -7269,7 +7378,7 @@
       <c r="A168" s="2"/>
       <c r="B168" s="2"/>
       <c r="C168" s="2"/>
-      <c r="D168" s="2"/>
+      <c r="D168" s="50"/>
       <c r="E168" s="2"/>
       <c r="F168" s="2"/>
       <c r="G168" s="2"/>
@@ -7297,7 +7406,7 @@
       <c r="A169" s="2"/>
       <c r="B169" s="2"/>
       <c r="C169" s="2"/>
-      <c r="D169" s="2"/>
+      <c r="D169" s="50"/>
       <c r="E169" s="2"/>
       <c r="F169" s="2"/>
       <c r="G169" s="2"/>
@@ -7325,7 +7434,7 @@
       <c r="A170" s="2"/>
       <c r="B170" s="2"/>
       <c r="C170" s="2"/>
-      <c r="D170" s="2"/>
+      <c r="D170" s="50"/>
       <c r="E170" s="2"/>
       <c r="F170" s="2"/>
       <c r="G170" s="2"/>
@@ -7353,7 +7462,7 @@
       <c r="A171" s="2"/>
       <c r="B171" s="2"/>
       <c r="C171" s="2"/>
-      <c r="D171" s="2"/>
+      <c r="D171" s="50"/>
       <c r="E171" s="2"/>
       <c r="F171" s="2"/>
       <c r="G171" s="2"/>
@@ -7381,7 +7490,7 @@
       <c r="A172" s="2"/>
       <c r="B172" s="2"/>
       <c r="C172" s="2"/>
-      <c r="D172" s="2"/>
+      <c r="D172" s="50"/>
       <c r="E172" s="2"/>
       <c r="F172" s="2"/>
       <c r="G172" s="2"/>
@@ -7409,7 +7518,7 @@
       <c r="A173" s="2"/>
       <c r="B173" s="2"/>
       <c r="C173" s="2"/>
-      <c r="D173" s="2"/>
+      <c r="D173" s="50"/>
       <c r="E173" s="2"/>
       <c r="F173" s="2"/>
       <c r="G173" s="2"/>
@@ -7437,7 +7546,7 @@
       <c r="A174" s="2"/>
       <c r="B174" s="2"/>
       <c r="C174" s="2"/>
-      <c r="D174" s="2"/>
+      <c r="D174" s="50"/>
       <c r="E174" s="2"/>
       <c r="F174" s="2"/>
       <c r="G174" s="2"/>
@@ -7465,7 +7574,7 @@
       <c r="A175" s="2"/>
       <c r="B175" s="2"/>
       <c r="C175" s="2"/>
-      <c r="D175" s="2"/>
+      <c r="D175" s="50"/>
       <c r="E175" s="2"/>
       <c r="F175" s="2"/>
       <c r="G175" s="2"/>
@@ -7493,7 +7602,7 @@
       <c r="A176" s="2"/>
       <c r="B176" s="2"/>
       <c r="C176" s="2"/>
-      <c r="D176" s="2"/>
+      <c r="D176" s="50"/>
       <c r="E176" s="2"/>
       <c r="F176" s="2"/>
       <c r="G176" s="2"/>
@@ -7521,7 +7630,7 @@
       <c r="A177" s="2"/>
       <c r="B177" s="2"/>
       <c r="C177" s="2"/>
-      <c r="D177" s="2"/>
+      <c r="D177" s="50"/>
       <c r="E177" s="2"/>
       <c r="F177" s="2"/>
       <c r="G177" s="2"/>
@@ -7549,7 +7658,7 @@
       <c r="A178" s="2"/>
       <c r="B178" s="2"/>
       <c r="C178" s="2"/>
-      <c r="D178" s="2"/>
+      <c r="D178" s="50"/>
       <c r="E178" s="2"/>
       <c r="F178" s="2"/>
       <c r="G178" s="2"/>
@@ -7577,7 +7686,7 @@
       <c r="A179" s="2"/>
       <c r="B179" s="2"/>
       <c r="C179" s="2"/>
-      <c r="D179" s="2"/>
+      <c r="D179" s="50"/>
       <c r="E179" s="2"/>
       <c r="F179" s="2"/>
       <c r="G179" s="2"/>
@@ -7605,7 +7714,7 @@
       <c r="A180" s="2"/>
       <c r="B180" s="2"/>
       <c r="C180" s="2"/>
-      <c r="D180" s="2"/>
+      <c r="D180" s="50"/>
       <c r="E180" s="2"/>
       <c r="F180" s="2"/>
       <c r="G180" s="2"/>
@@ -7633,7 +7742,7 @@
       <c r="A181" s="2"/>
       <c r="B181" s="2"/>
       <c r="C181" s="2"/>
-      <c r="D181" s="2"/>
+      <c r="D181" s="50"/>
       <c r="E181" s="2"/>
       <c r="F181" s="2"/>
       <c r="G181" s="2"/>
@@ -7661,7 +7770,7 @@
       <c r="A182" s="2"/>
       <c r="B182" s="2"/>
       <c r="C182" s="2"/>
-      <c r="D182" s="2"/>
+      <c r="D182" s="50"/>
       <c r="E182" s="2"/>
       <c r="F182" s="2"/>
       <c r="G182" s="2"/>
@@ -7689,7 +7798,7 @@
       <c r="A183" s="2"/>
       <c r="B183" s="2"/>
       <c r="C183" s="2"/>
-      <c r="D183" s="2"/>
+      <c r="D183" s="50"/>
       <c r="E183" s="2"/>
       <c r="F183" s="2"/>
       <c r="G183" s="2"/>
@@ -7717,7 +7826,7 @@
       <c r="A184" s="2"/>
       <c r="B184" s="2"/>
       <c r="C184" s="2"/>
-      <c r="D184" s="2"/>
+      <c r="D184" s="50"/>
       <c r="E184" s="2"/>
       <c r="F184" s="2"/>
       <c r="G184" s="2"/>
@@ -7745,7 +7854,7 @@
       <c r="A185" s="2"/>
       <c r="B185" s="2"/>
       <c r="C185" s="2"/>
-      <c r="D185" s="2"/>
+      <c r="D185" s="50"/>
       <c r="E185" s="2"/>
       <c r="F185" s="2"/>
       <c r="G185" s="2"/>
@@ -7773,7 +7882,7 @@
       <c r="A186" s="2"/>
       <c r="B186" s="2"/>
       <c r="C186" s="2"/>
-      <c r="D186" s="2"/>
+      <c r="D186" s="50"/>
       <c r="E186" s="2"/>
       <c r="F186" s="2"/>
       <c r="G186" s="2"/>
@@ -7801,7 +7910,7 @@
       <c r="A187" s="2"/>
       <c r="B187" s="2"/>
       <c r="C187" s="2"/>
-      <c r="D187" s="2"/>
+      <c r="D187" s="50"/>
       <c r="E187" s="2"/>
       <c r="F187" s="2"/>
       <c r="G187" s="2"/>
@@ -7829,7 +7938,7 @@
       <c r="A188" s="2"/>
       <c r="B188" s="2"/>
       <c r="C188" s="2"/>
-      <c r="D188" s="2"/>
+      <c r="D188" s="50"/>
       <c r="E188" s="2"/>
       <c r="F188" s="2"/>
       <c r="G188" s="2"/>
@@ -7857,7 +7966,7 @@
       <c r="A189" s="2"/>
       <c r="B189" s="2"/>
       <c r="C189" s="2"/>
-      <c r="D189" s="2"/>
+      <c r="D189" s="50"/>
       <c r="E189" s="2"/>
       <c r="F189" s="2"/>
       <c r="G189" s="2"/>
@@ -7885,7 +7994,7 @@
       <c r="A190" s="2"/>
       <c r="B190" s="2"/>
       <c r="C190" s="2"/>
-      <c r="D190" s="2"/>
+      <c r="D190" s="50"/>
       <c r="E190" s="2"/>
       <c r="F190" s="2"/>
       <c r="G190" s="2"/>
@@ -7913,7 +8022,7 @@
       <c r="A191" s="2"/>
       <c r="B191" s="2"/>
       <c r="C191" s="2"/>
-      <c r="D191" s="2"/>
+      <c r="D191" s="50"/>
       <c r="E191" s="2"/>
       <c r="F191" s="2"/>
       <c r="G191" s="2"/>
@@ -7941,7 +8050,7 @@
       <c r="A192" s="2"/>
       <c r="B192" s="2"/>
       <c r="C192" s="2"/>
-      <c r="D192" s="2"/>
+      <c r="D192" s="50"/>
       <c r="E192" s="2"/>
       <c r="F192" s="2"/>
       <c r="G192" s="2"/>
@@ -7969,7 +8078,7 @@
       <c r="A193" s="2"/>
       <c r="B193" s="2"/>
       <c r="C193" s="2"/>
-      <c r="D193" s="2"/>
+      <c r="D193" s="50"/>
       <c r="E193" s="2"/>
       <c r="F193" s="2"/>
       <c r="G193" s="2"/>
@@ -7997,7 +8106,7 @@
       <c r="A194" s="2"/>
       <c r="B194" s="2"/>
       <c r="C194" s="2"/>
-      <c r="D194" s="2"/>
+      <c r="D194" s="50"/>
       <c r="E194" s="2"/>
       <c r="F194" s="2"/>
       <c r="G194" s="2"/>
@@ -8025,7 +8134,7 @@
       <c r="A195" s="2"/>
       <c r="B195" s="2"/>
       <c r="C195" s="2"/>
-      <c r="D195" s="2"/>
+      <c r="D195" s="50"/>
       <c r="E195" s="2"/>
       <c r="F195" s="2"/>
       <c r="G195" s="2"/>
@@ -8053,7 +8162,7 @@
       <c r="A196" s="2"/>
       <c r="B196" s="2"/>
       <c r="C196" s="2"/>
-      <c r="D196" s="2"/>
+      <c r="D196" s="50"/>
       <c r="E196" s="2"/>
       <c r="F196" s="2"/>
       <c r="G196" s="2"/>
@@ -8081,7 +8190,7 @@
       <c r="A197" s="2"/>
       <c r="B197" s="2"/>
       <c r="C197" s="2"/>
-      <c r="D197" s="2"/>
+      <c r="D197" s="50"/>
       <c r="E197" s="2"/>
       <c r="F197" s="2"/>
       <c r="G197" s="2"/>
@@ -8109,7 +8218,7 @@
       <c r="A198" s="2"/>
       <c r="B198" s="2"/>
       <c r="C198" s="2"/>
-      <c r="D198" s="2"/>
+      <c r="D198" s="50"/>
       <c r="E198" s="2"/>
       <c r="F198" s="2"/>
       <c r="G198" s="2"/>
@@ -8137,7 +8246,7 @@
       <c r="A199" s="2"/>
       <c r="B199" s="2"/>
       <c r="C199" s="2"/>
-      <c r="D199" s="2"/>
+      <c r="D199" s="50"/>
       <c r="E199" s="2"/>
       <c r="F199" s="2"/>
       <c r="G199" s="2"/>
@@ -8165,7 +8274,7 @@
       <c r="A200" s="2"/>
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
-      <c r="D200" s="2"/>
+      <c r="D200" s="50"/>
       <c r="E200" s="2"/>
       <c r="F200" s="2"/>
       <c r="G200" s="2"/>
@@ -8193,7 +8302,7 @@
       <c r="A201" s="2"/>
       <c r="B201" s="2"/>
       <c r="C201" s="2"/>
-      <c r="D201" s="2"/>
+      <c r="D201" s="50"/>
       <c r="E201" s="2"/>
       <c r="F201" s="2"/>
       <c r="G201" s="2"/>
@@ -8221,7 +8330,7 @@
       <c r="A202" s="2"/>
       <c r="B202" s="2"/>
       <c r="C202" s="2"/>
-      <c r="D202" s="2"/>
+      <c r="D202" s="50"/>
       <c r="E202" s="2"/>
       <c r="F202" s="2"/>
       <c r="G202" s="2"/>
@@ -8249,7 +8358,7 @@
       <c r="A203" s="2"/>
       <c r="B203" s="2"/>
       <c r="C203" s="2"/>
-      <c r="D203" s="2"/>
+      <c r="D203" s="50"/>
       <c r="E203" s="2"/>
       <c r="F203" s="2"/>
       <c r="G203" s="2"/>
@@ -8277,7 +8386,7 @@
       <c r="A204" s="2"/>
       <c r="B204" s="2"/>
       <c r="C204" s="2"/>
-      <c r="D204" s="2"/>
+      <c r="D204" s="50"/>
       <c r="E204" s="2"/>
       <c r="F204" s="2"/>
       <c r="G204" s="2"/>
@@ -8305,7 +8414,7 @@
       <c r="A205" s="2"/>
       <c r="B205" s="2"/>
       <c r="C205" s="2"/>
-      <c r="D205" s="2"/>
+      <c r="D205" s="50"/>
       <c r="E205" s="2"/>
       <c r="F205" s="2"/>
       <c r="G205" s="2"/>
@@ -8333,7 +8442,7 @@
       <c r="A206" s="2"/>
       <c r="B206" s="2"/>
       <c r="C206" s="2"/>
-      <c r="D206" s="2"/>
+      <c r="D206" s="50"/>
       <c r="E206" s="2"/>
       <c r="F206" s="2"/>
       <c r="G206" s="2"/>
@@ -8361,7 +8470,7 @@
       <c r="A207" s="2"/>
       <c r="B207" s="2"/>
       <c r="C207" s="2"/>
-      <c r="D207" s="2"/>
+      <c r="D207" s="50"/>
       <c r="E207" s="2"/>
       <c r="F207" s="2"/>
       <c r="G207" s="2"/>
@@ -8389,7 +8498,7 @@
       <c r="A208" s="2"/>
       <c r="B208" s="2"/>
       <c r="C208" s="2"/>
-      <c r="D208" s="2"/>
+      <c r="D208" s="50"/>
       <c r="E208" s="2"/>
       <c r="F208" s="2"/>
       <c r="G208" s="2"/>
@@ -8417,7 +8526,7 @@
       <c r="A209" s="2"/>
       <c r="B209" s="2"/>
       <c r="C209" s="2"/>
-      <c r="D209" s="2"/>
+      <c r="D209" s="50"/>
       <c r="E209" s="2"/>
       <c r="F209" s="2"/>
       <c r="G209" s="2"/>
@@ -8445,7 +8554,7 @@
       <c r="A210" s="2"/>
       <c r="B210" s="2"/>
       <c r="C210" s="2"/>
-      <c r="D210" s="2"/>
+      <c r="D210" s="50"/>
       <c r="E210" s="2"/>
       <c r="F210" s="2"/>
       <c r="G210" s="2"/>
@@ -8473,7 +8582,7 @@
       <c r="A211" s="2"/>
       <c r="B211" s="2"/>
       <c r="C211" s="2"/>
-      <c r="D211" s="2"/>
+      <c r="D211" s="50"/>
       <c r="E211" s="2"/>
       <c r="F211" s="2"/>
       <c r="G211" s="2"/>
@@ -8501,7 +8610,7 @@
       <c r="A212" s="2"/>
       <c r="B212" s="2"/>
       <c r="C212" s="2"/>
-      <c r="D212" s="2"/>
+      <c r="D212" s="50"/>
       <c r="E212" s="2"/>
       <c r="F212" s="2"/>
       <c r="G212" s="2"/>
@@ -8529,7 +8638,7 @@
       <c r="A213" s="2"/>
       <c r="B213" s="2"/>
       <c r="C213" s="2"/>
-      <c r="D213" s="2"/>
+      <c r="D213" s="50"/>
       <c r="E213" s="2"/>
       <c r="F213" s="2"/>
       <c r="G213" s="2"/>
@@ -8557,7 +8666,7 @@
       <c r="A214" s="2"/>
       <c r="B214" s="2"/>
       <c r="C214" s="2"/>
-      <c r="D214" s="2"/>
+      <c r="D214" s="50"/>
       <c r="E214" s="2"/>
       <c r="F214" s="2"/>
       <c r="G214" s="2"/>
@@ -8585,7 +8694,7 @@
       <c r="A215" s="2"/>
       <c r="B215" s="2"/>
       <c r="C215" s="2"/>
-      <c r="D215" s="2"/>
+      <c r="D215" s="50"/>
       <c r="E215" s="2"/>
       <c r="F215" s="2"/>
       <c r="G215" s="2"/>
@@ -8613,7 +8722,7 @@
       <c r="A216" s="2"/>
       <c r="B216" s="2"/>
       <c r="C216" s="2"/>
-      <c r="D216" s="2"/>
+      <c r="D216" s="50"/>
       <c r="E216" s="2"/>
       <c r="F216" s="2"/>
       <c r="G216" s="2"/>
@@ -8641,7 +8750,7 @@
       <c r="A217" s="2"/>
       <c r="B217" s="2"/>
       <c r="C217" s="2"/>
-      <c r="D217" s="2"/>
+      <c r="D217" s="50"/>
       <c r="E217" s="2"/>
       <c r="F217" s="2"/>
       <c r="G217" s="2"/>
@@ -8669,7 +8778,7 @@
       <c r="A218" s="2"/>
       <c r="B218" s="2"/>
       <c r="C218" s="2"/>
-      <c r="D218" s="2"/>
+      <c r="D218" s="50"/>
       <c r="E218" s="2"/>
       <c r="F218" s="2"/>
       <c r="G218" s="2"/>
@@ -8697,7 +8806,7 @@
       <c r="A219" s="2"/>
       <c r="B219" s="2"/>
       <c r="C219" s="2"/>
-      <c r="D219" s="2"/>
+      <c r="D219" s="50"/>
       <c r="E219" s="2"/>
       <c r="F219" s="2"/>
       <c r="G219" s="2"/>
@@ -8725,7 +8834,7 @@
       <c r="A220" s="2"/>
       <c r="B220" s="2"/>
       <c r="C220" s="2"/>
-      <c r="D220" s="2"/>
+      <c r="D220" s="50"/>
       <c r="E220" s="2"/>
       <c r="F220" s="2"/>
       <c r="G220" s="2"/>
@@ -8753,7 +8862,7 @@
       <c r="A221" s="2"/>
       <c r="B221" s="2"/>
       <c r="C221" s="2"/>
-      <c r="D221" s="2"/>
+      <c r="D221" s="50"/>
       <c r="E221" s="2"/>
       <c r="F221" s="2"/>
       <c r="G221" s="2"/>
@@ -8781,7 +8890,7 @@
       <c r="A222" s="2"/>
       <c r="B222" s="2"/>
       <c r="C222" s="2"/>
-      <c r="D222" s="2"/>
+      <c r="D222" s="50"/>
       <c r="E222" s="2"/>
       <c r="F222" s="2"/>
       <c r="G222" s="2"/>
@@ -8809,7 +8918,7 @@
       <c r="A223" s="2"/>
       <c r="B223" s="2"/>
       <c r="C223" s="2"/>
-      <c r="D223" s="2"/>
+      <c r="D223" s="50"/>
       <c r="E223" s="2"/>
       <c r="F223" s="2"/>
       <c r="G223" s="2"/>
@@ -8837,7 +8946,7 @@
       <c r="A224" s="2"/>
       <c r="B224" s="2"/>
       <c r="C224" s="2"/>
-      <c r="D224" s="2"/>
+      <c r="D224" s="50"/>
       <c r="E224" s="2"/>
       <c r="F224" s="2"/>
       <c r="G224" s="2"/>
@@ -8865,7 +8974,7 @@
       <c r="A225" s="2"/>
       <c r="B225" s="2"/>
       <c r="C225" s="2"/>
-      <c r="D225" s="2"/>
+      <c r="D225" s="50"/>
       <c r="E225" s="2"/>
       <c r="F225" s="2"/>
       <c r="G225" s="2"/>
@@ -8893,7 +9002,7 @@
       <c r="A226" s="2"/>
       <c r="B226" s="2"/>
       <c r="C226" s="2"/>
-      <c r="D226" s="2"/>
+      <c r="D226" s="50"/>
       <c r="E226" s="2"/>
       <c r="F226" s="2"/>
       <c r="G226" s="2"/>
@@ -8921,7 +9030,7 @@
       <c r="A227" s="2"/>
       <c r="B227" s="2"/>
       <c r="C227" s="2"/>
-      <c r="D227" s="2"/>
+      <c r="D227" s="50"/>
       <c r="E227" s="2"/>
       <c r="F227" s="2"/>
       <c r="G227" s="2"/>
@@ -8949,7 +9058,7 @@
       <c r="A228" s="2"/>
       <c r="B228" s="2"/>
       <c r="C228" s="2"/>
-      <c r="D228" s="2"/>
+      <c r="D228" s="50"/>
       <c r="E228" s="2"/>
       <c r="F228" s="2"/>
       <c r="G228" s="2"/>
@@ -8977,7 +9086,7 @@
       <c r="A229" s="2"/>
       <c r="B229" s="2"/>
       <c r="C229" s="2"/>
-      <c r="D229" s="2"/>
+      <c r="D229" s="50"/>
       <c r="E229" s="2"/>
       <c r="F229" s="2"/>
       <c r="G229" s="2"/>
@@ -9005,7 +9114,7 @@
       <c r="A230" s="2"/>
       <c r="B230" s="2"/>
       <c r="C230" s="2"/>
-      <c r="D230" s="2"/>
+      <c r="D230" s="50"/>
       <c r="E230" s="2"/>
       <c r="F230" s="2"/>
       <c r="G230" s="2"/>
@@ -9033,7 +9142,7 @@
       <c r="A231" s="2"/>
       <c r="B231" s="2"/>
       <c r="C231" s="2"/>
-      <c r="D231" s="2"/>
+      <c r="D231" s="50"/>
       <c r="E231" s="2"/>
       <c r="F231" s="2"/>
       <c r="G231" s="2"/>
@@ -9061,7 +9170,7 @@
       <c r="A232" s="2"/>
       <c r="B232" s="2"/>
       <c r="C232" s="2"/>
-      <c r="D232" s="2"/>
+      <c r="D232" s="50"/>
       <c r="E232" s="2"/>
       <c r="F232" s="2"/>
       <c r="G232" s="2"/>
@@ -9089,7 +9198,7 @@
       <c r="A233" s="2"/>
       <c r="B233" s="2"/>
       <c r="C233" s="2"/>
-      <c r="D233" s="2"/>
+      <c r="D233" s="50"/>
       <c r="E233" s="2"/>
       <c r="F233" s="2"/>
       <c r="G233" s="2"/>
@@ -9117,7 +9226,7 @@
       <c r="A234" s="2"/>
       <c r="B234" s="2"/>
       <c r="C234" s="2"/>
-      <c r="D234" s="2"/>
+      <c r="D234" s="50"/>
       <c r="E234" s="2"/>
       <c r="F234" s="2"/>
       <c r="G234" s="2"/>
@@ -9145,7 +9254,7 @@
       <c r="A235" s="2"/>
       <c r="B235" s="2"/>
       <c r="C235" s="2"/>
-      <c r="D235" s="2"/>
+      <c r="D235" s="50"/>
       <c r="E235" s="2"/>
       <c r="F235" s="2"/>
       <c r="G235" s="2"/>
@@ -9173,7 +9282,7 @@
       <c r="A236" s="2"/>
       <c r="B236" s="2"/>
       <c r="C236" s="2"/>
-      <c r="D236" s="2"/>
+      <c r="D236" s="50"/>
       <c r="E236" s="2"/>
       <c r="F236" s="2"/>
       <c r="G236" s="2"/>
@@ -9201,7 +9310,7 @@
       <c r="A237" s="2"/>
       <c r="B237" s="2"/>
       <c r="C237" s="2"/>
-      <c r="D237" s="2"/>
+      <c r="D237" s="50"/>
       <c r="E237" s="2"/>
       <c r="F237" s="2"/>
       <c r="G237" s="2"/>
@@ -9229,7 +9338,7 @@
       <c r="A238" s="2"/>
       <c r="B238" s="2"/>
       <c r="C238" s="2"/>
-      <c r="D238" s="2"/>
+      <c r="D238" s="50"/>
       <c r="E238" s="2"/>
       <c r="F238" s="2"/>
       <c r="G238" s="2"/>
@@ -9257,7 +9366,7 @@
       <c r="A239" s="2"/>
       <c r="B239" s="2"/>
       <c r="C239" s="2"/>
-      <c r="D239" s="2"/>
+      <c r="D239" s="50"/>
       <c r="E239" s="2"/>
       <c r="F239" s="2"/>
       <c r="G239" s="2"/>
@@ -9285,7 +9394,7 @@
       <c r="A240" s="2"/>
       <c r="B240" s="2"/>
       <c r="C240" s="2"/>
-      <c r="D240" s="2"/>
+      <c r="D240" s="50"/>
       <c r="E240" s="2"/>
       <c r="F240" s="2"/>
       <c r="G240" s="2"/>
@@ -9313,7 +9422,7 @@
       <c r="A241" s="2"/>
       <c r="B241" s="2"/>
       <c r="C241" s="2"/>
-      <c r="D241" s="2"/>
+      <c r="D241" s="50"/>
       <c r="E241" s="2"/>
       <c r="F241" s="2"/>
       <c r="G241" s="2"/>
@@ -9341,7 +9450,7 @@
       <c r="A242" s="2"/>
       <c r="B242" s="2"/>
       <c r="C242" s="2"/>
-      <c r="D242" s="2"/>
+      <c r="D242" s="50"/>
       <c r="E242" s="2"/>
       <c r="F242" s="2"/>
       <c r="G242" s="2"/>
@@ -9369,7 +9478,7 @@
       <c r="A243" s="2"/>
       <c r="B243" s="2"/>
       <c r="C243" s="2"/>
-      <c r="D243" s="2"/>
+      <c r="D243" s="50"/>
       <c r="E243" s="2"/>
       <c r="F243" s="2"/>
       <c r="G243" s="2"/>
@@ -9397,7 +9506,7 @@
       <c r="A244" s="2"/>
       <c r="B244" s="2"/>
       <c r="C244" s="2"/>
-      <c r="D244" s="2"/>
+      <c r="D244" s="50"/>
       <c r="E244" s="2"/>
       <c r="F244" s="2"/>
       <c r="G244" s="2"/>
@@ -9425,7 +9534,7 @@
       <c r="A245" s="2"/>
       <c r="B245" s="2"/>
       <c r="C245" s="2"/>
-      <c r="D245" s="2"/>
+      <c r="D245" s="50"/>
       <c r="E245" s="2"/>
       <c r="F245" s="2"/>
       <c r="G245" s="2"/>
@@ -9453,7 +9562,7 @@
       <c r="A246" s="2"/>
       <c r="B246" s="2"/>
       <c r="C246" s="2"/>
-      <c r="D246" s="2"/>
+      <c r="D246" s="50"/>
       <c r="E246" s="2"/>
       <c r="F246" s="2"/>
       <c r="G246" s="2"/>
@@ -9481,7 +9590,7 @@
       <c r="A247" s="2"/>
       <c r="B247" s="2"/>
       <c r="C247" s="2"/>
-      <c r="D247" s="2"/>
+      <c r="D247" s="50"/>
       <c r="E247" s="2"/>
       <c r="F247" s="2"/>
       <c r="G247" s="2"/>
@@ -9509,7 +9618,7 @@
       <c r="A248" s="2"/>
       <c r="B248" s="2"/>
       <c r="C248" s="2"/>
-      <c r="D248" s="2"/>
+      <c r="D248" s="50"/>
       <c r="E248" s="2"/>
       <c r="F248" s="2"/>
       <c r="G248" s="2"/>
@@ -9537,7 +9646,7 @@
       <c r="A249" s="2"/>
       <c r="B249" s="2"/>
       <c r="C249" s="2"/>
-      <c r="D249" s="2"/>
+      <c r="D249" s="50"/>
       <c r="E249" s="2"/>
       <c r="F249" s="2"/>
       <c r="G249" s="2"/>
@@ -9565,7 +9674,7 @@
       <c r="A250" s="2"/>
       <c r="B250" s="2"/>
       <c r="C250" s="2"/>
-      <c r="D250" s="2"/>
+      <c r="D250" s="50"/>
       <c r="E250" s="2"/>
       <c r="F250" s="2"/>
       <c r="G250" s="2"/>
@@ -9593,7 +9702,7 @@
       <c r="A251" s="2"/>
       <c r="B251" s="2"/>
       <c r="C251" s="2"/>
-      <c r="D251" s="2"/>
+      <c r="D251" s="50"/>
       <c r="E251" s="2"/>
       <c r="F251" s="2"/>
       <c r="G251" s="2"/>
@@ -9621,7 +9730,7 @@
       <c r="A252" s="2"/>
       <c r="B252" s="2"/>
       <c r="C252" s="2"/>
-      <c r="D252" s="2"/>
+      <c r="D252" s="50"/>
       <c r="E252" s="2"/>
       <c r="F252" s="2"/>
       <c r="G252" s="2"/>
@@ -9649,7 +9758,7 @@
       <c r="A253" s="2"/>
       <c r="B253" s="2"/>
       <c r="C253" s="2"/>
-      <c r="D253" s="2"/>
+      <c r="D253" s="50"/>
       <c r="E253" s="2"/>
       <c r="F253" s="2"/>
       <c r="G253" s="2"/>
@@ -9677,7 +9786,7 @@
       <c r="A254" s="2"/>
       <c r="B254" s="2"/>
       <c r="C254" s="2"/>
-      <c r="D254" s="2"/>
+      <c r="D254" s="50"/>
       <c r="E254" s="2"/>
       <c r="F254" s="2"/>
       <c r="G254" s="2"/>
@@ -9705,7 +9814,7 @@
       <c r="A255" s="2"/>
       <c r="B255" s="2"/>
       <c r="C255" s="2"/>
-      <c r="D255" s="2"/>
+      <c r="D255" s="50"/>
       <c r="E255" s="2"/>
       <c r="F255" s="2"/>
       <c r="G255" s="2"/>
@@ -9733,7 +9842,7 @@
       <c r="A256" s="2"/>
       <c r="B256" s="2"/>
       <c r="C256" s="2"/>
-      <c r="D256" s="2"/>
+      <c r="D256" s="50"/>
       <c r="E256" s="2"/>
       <c r="F256" s="2"/>
       <c r="G256" s="2"/>
@@ -9761,7 +9870,7 @@
       <c r="A257" s="2"/>
       <c r="B257" s="2"/>
       <c r="C257" s="2"/>
-      <c r="D257" s="2"/>
+      <c r="D257" s="50"/>
       <c r="E257" s="2"/>
       <c r="F257" s="2"/>
       <c r="G257" s="2"/>
@@ -9789,7 +9898,7 @@
       <c r="A258" s="2"/>
       <c r="B258" s="2"/>
       <c r="C258" s="2"/>
-      <c r="D258" s="2"/>
+      <c r="D258" s="50"/>
       <c r="E258" s="2"/>
       <c r="F258" s="2"/>
       <c r="G258" s="2"/>
@@ -9817,7 +9926,7 @@
       <c r="A259" s="2"/>
       <c r="B259" s="2"/>
       <c r="C259" s="2"/>
-      <c r="D259" s="2"/>
+      <c r="D259" s="50"/>
       <c r="E259" s="2"/>
       <c r="F259" s="2"/>
       <c r="G259" s="2"/>
@@ -9845,7 +9954,7 @@
       <c r="A260" s="2"/>
       <c r="B260" s="2"/>
       <c r="C260" s="2"/>
-      <c r="D260" s="2"/>
+      <c r="D260" s="50"/>
       <c r="E260" s="2"/>
       <c r="F260" s="2"/>
       <c r="G260" s="2"/>
@@ -9873,7 +9982,7 @@
       <c r="A261" s="2"/>
       <c r="B261" s="2"/>
       <c r="C261" s="2"/>
-      <c r="D261" s="2"/>
+      <c r="D261" s="50"/>
       <c r="E261" s="2"/>
       <c r="F261" s="2"/>
       <c r="G261" s="2"/>
@@ -9901,7 +10010,7 @@
       <c r="A262" s="2"/>
       <c r="B262" s="2"/>
       <c r="C262" s="2"/>
-      <c r="D262" s="2"/>
+      <c r="D262" s="50"/>
       <c r="E262" s="2"/>
       <c r="F262" s="2"/>
       <c r="G262" s="2"/>
@@ -9929,7 +10038,7 @@
       <c r="A263" s="2"/>
       <c r="B263" s="2"/>
       <c r="C263" s="2"/>
-      <c r="D263" s="2"/>
+      <c r="D263" s="50"/>
       <c r="E263" s="2"/>
       <c r="F263" s="2"/>
       <c r="G263" s="2"/>
@@ -9957,7 +10066,7 @@
       <c r="A264" s="2"/>
       <c r="B264" s="2"/>
       <c r="C264" s="2"/>
-      <c r="D264" s="2"/>
+      <c r="D264" s="50"/>
       <c r="E264" s="2"/>
       <c r="F264" s="2"/>
       <c r="G264" s="2"/>
@@ -9985,7 +10094,7 @@
       <c r="A265" s="2"/>
       <c r="B265" s="2"/>
       <c r="C265" s="2"/>
-      <c r="D265" s="2"/>
+      <c r="D265" s="50"/>
       <c r="E265" s="2"/>
       <c r="F265" s="2"/>
       <c r="G265" s="2"/>
@@ -10013,7 +10122,7 @@
       <c r="A266" s="2"/>
       <c r="B266" s="2"/>
       <c r="C266" s="2"/>
-      <c r="D266" s="2"/>
+      <c r="D266" s="50"/>
       <c r="E266" s="2"/>
       <c r="F266" s="2"/>
       <c r="G266" s="2"/>
@@ -10041,7 +10150,7 @@
       <c r="A267" s="2"/>
       <c r="B267" s="2"/>
       <c r="C267" s="2"/>
-      <c r="D267" s="2"/>
+      <c r="D267" s="50"/>
       <c r="E267" s="2"/>
       <c r="F267" s="2"/>
       <c r="G267" s="2"/>
@@ -10069,7 +10178,7 @@
       <c r="A268" s="2"/>
       <c r="B268" s="2"/>
       <c r="C268" s="2"/>
-      <c r="D268" s="2"/>
+      <c r="D268" s="50"/>
       <c r="E268" s="2"/>
       <c r="F268" s="2"/>
       <c r="G268" s="2"/>
@@ -10097,7 +10206,7 @@
       <c r="A269" s="2"/>
       <c r="B269" s="2"/>
       <c r="C269" s="2"/>
-      <c r="D269" s="2"/>
+      <c r="D269" s="50"/>
       <c r="E269" s="2"/>
       <c r="F269" s="2"/>
       <c r="G269" s="2"/>
@@ -10125,7 +10234,7 @@
       <c r="A270" s="2"/>
       <c r="B270" s="2"/>
       <c r="C270" s="2"/>
-      <c r="D270" s="2"/>
+      <c r="D270" s="50"/>
       <c r="E270" s="2"/>
       <c r="F270" s="2"/>
       <c r="G270" s="2"/>
@@ -10153,7 +10262,7 @@
       <c r="A271" s="2"/>
       <c r="B271" s="2"/>
       <c r="C271" s="2"/>
-      <c r="D271" s="2"/>
+      <c r="D271" s="50"/>
       <c r="E271" s="2"/>
       <c r="F271" s="2"/>
       <c r="G271" s="2"/>
@@ -10181,7 +10290,7 @@
       <c r="A272" s="2"/>
       <c r="B272" s="2"/>
       <c r="C272" s="2"/>
-      <c r="D272" s="2"/>
+      <c r="D272" s="50"/>
       <c r="E272" s="2"/>
       <c r="F272" s="2"/>
       <c r="G272" s="2"/>
@@ -10209,7 +10318,7 @@
       <c r="A273" s="2"/>
       <c r="B273" s="2"/>
       <c r="C273" s="2"/>
-      <c r="D273" s="2"/>
+      <c r="D273" s="50"/>
       <c r="E273" s="2"/>
       <c r="F273" s="2"/>
       <c r="G273" s="2"/>
@@ -10237,7 +10346,7 @@
       <c r="A274" s="2"/>
       <c r="B274" s="2"/>
       <c r="C274" s="2"/>
-      <c r="D274" s="2"/>
+      <c r="D274" s="50"/>
       <c r="E274" s="2"/>
       <c r="F274" s="2"/>
       <c r="G274" s="2"/>
@@ -10265,7 +10374,7 @@
       <c r="A275" s="2"/>
       <c r="B275" s="2"/>
       <c r="C275" s="2"/>
-      <c r="D275" s="2"/>
+      <c r="D275" s="50"/>
       <c r="E275" s="2"/>
       <c r="F275" s="2"/>
       <c r="G275" s="2"/>
@@ -10293,7 +10402,7 @@
       <c r="A276" s="2"/>
       <c r="B276" s="2"/>
       <c r="C276" s="2"/>
-      <c r="D276" s="2"/>
+      <c r="D276" s="50"/>
       <c r="E276" s="2"/>
       <c r="F276" s="2"/>
       <c r="G276" s="2"/>
@@ -10321,7 +10430,7 @@
       <c r="A277" s="2"/>
       <c r="B277" s="2"/>
       <c r="C277" s="2"/>
-      <c r="D277" s="2"/>
+      <c r="D277" s="50"/>
       <c r="E277" s="2"/>
       <c r="F277" s="2"/>
       <c r="G277" s="2"/>
@@ -10349,7 +10458,7 @@
       <c r="A278" s="2"/>
       <c r="B278" s="2"/>
       <c r="C278" s="2"/>
-      <c r="D278" s="2"/>
+      <c r="D278" s="50"/>
       <c r="E278" s="2"/>
       <c r="F278" s="2"/>
       <c r="G278" s="2"/>
@@ -10377,7 +10486,7 @@
       <c r="A279" s="2"/>
       <c r="B279" s="2"/>
       <c r="C279" s="2"/>
-      <c r="D279" s="2"/>
+      <c r="D279" s="50"/>
       <c r="E279" s="2"/>
       <c r="F279" s="2"/>
       <c r="G279" s="2"/>
@@ -10405,7 +10514,7 @@
       <c r="A280" s="2"/>
       <c r="B280" s="2"/>
       <c r="C280" s="2"/>
-      <c r="D280" s="2"/>
+      <c r="D280" s="50"/>
       <c r="E280" s="2"/>
       <c r="F280" s="2"/>
       <c r="G280" s="2"/>
@@ -10433,7 +10542,7 @@
       <c r="A281" s="2"/>
       <c r="B281" s="2"/>
       <c r="C281" s="2"/>
-      <c r="D281" s="2"/>
+      <c r="D281" s="50"/>
       <c r="E281" s="2"/>
       <c r="F281" s="2"/>
       <c r="G281" s="2"/>
@@ -10461,7 +10570,7 @@
       <c r="A282" s="2"/>
       <c r="B282" s="2"/>
       <c r="C282" s="2"/>
-      <c r="D282" s="2"/>
+      <c r="D282" s="50"/>
       <c r="E282" s="2"/>
       <c r="F282" s="2"/>
       <c r="G282" s="2"/>
@@ -10489,7 +10598,7 @@
       <c r="A283" s="2"/>
       <c r="B283" s="2"/>
       <c r="C283" s="2"/>
-      <c r="D283" s="2"/>
+      <c r="D283" s="50"/>
       <c r="E283" s="2"/>
       <c r="F283" s="2"/>
       <c r="G283" s="2"/>
@@ -10517,7 +10626,7 @@
       <c r="A284" s="2"/>
       <c r="B284" s="2"/>
       <c r="C284" s="2"/>
-      <c r="D284" s="2"/>
+      <c r="D284" s="50"/>
       <c r="E284" s="2"/>
       <c r="F284" s="2"/>
       <c r="G284" s="2"/>
@@ -10545,7 +10654,7 @@
       <c r="A285" s="2"/>
       <c r="B285" s="2"/>
       <c r="C285" s="2"/>
-      <c r="D285" s="2"/>
+      <c r="D285" s="50"/>
       <c r="E285" s="2"/>
       <c r="F285" s="2"/>
       <c r="G285" s="2"/>
@@ -10573,7 +10682,7 @@
       <c r="A286" s="2"/>
       <c r="B286" s="2"/>
       <c r="C286" s="2"/>
-      <c r="D286" s="2"/>
+      <c r="D286" s="50"/>
       <c r="E286" s="2"/>
       <c r="F286" s="2"/>
       <c r="G286" s="2"/>
@@ -10601,7 +10710,7 @@
       <c r="A287" s="2"/>
       <c r="B287" s="2"/>
       <c r="C287" s="2"/>
-      <c r="D287" s="2"/>
+      <c r="D287" s="50"/>
       <c r="E287" s="2"/>
       <c r="F287" s="2"/>
       <c r="G287" s="2"/>
@@ -10629,7 +10738,7 @@
       <c r="A288" s="2"/>
       <c r="B288" s="2"/>
       <c r="C288" s="2"/>
-      <c r="D288" s="2"/>
+      <c r="D288" s="50"/>
       <c r="E288" s="2"/>
       <c r="F288" s="2"/>
       <c r="G288" s="2"/>
@@ -10657,7 +10766,7 @@
       <c r="A289" s="2"/>
       <c r="B289" s="2"/>
       <c r="C289" s="2"/>
-      <c r="D289" s="2"/>
+      <c r="D289" s="50"/>
       <c r="E289" s="2"/>
       <c r="F289" s="2"/>
       <c r="G289" s="2"/>
@@ -10685,7 +10794,7 @@
       <c r="A290" s="2"/>
       <c r="B290" s="2"/>
       <c r="C290" s="2"/>
-      <c r="D290" s="2"/>
+      <c r="D290" s="50"/>
       <c r="E290" s="2"/>
       <c r="F290" s="2"/>
       <c r="G290" s="2"/>
@@ -10713,7 +10822,7 @@
       <c r="A291" s="2"/>
       <c r="B291" s="2"/>
       <c r="C291" s="2"/>
-      <c r="D291" s="2"/>
+      <c r="D291" s="50"/>
       <c r="E291" s="2"/>
       <c r="F291" s="2"/>
       <c r="G291" s="2"/>
@@ -10741,7 +10850,7 @@
       <c r="A292" s="2"/>
       <c r="B292" s="2"/>
       <c r="C292" s="2"/>
-      <c r="D292" s="2"/>
+      <c r="D292" s="50"/>
       <c r="E292" s="2"/>
       <c r="F292" s="2"/>
       <c r="G292" s="2"/>
@@ -10769,7 +10878,7 @@
       <c r="A293" s="2"/>
       <c r="B293" s="2"/>
       <c r="C293" s="2"/>
-      <c r="D293" s="2"/>
+      <c r="D293" s="50"/>
       <c r="E293" s="2"/>
       <c r="F293" s="2"/>
       <c r="G293" s="2"/>
@@ -10797,7 +10906,7 @@
       <c r="A294" s="2"/>
       <c r="B294" s="2"/>
       <c r="C294" s="2"/>
-      <c r="D294" s="2"/>
+      <c r="D294" s="50"/>
       <c r="E294" s="2"/>
       <c r="F294" s="2"/>
       <c r="G294" s="2"/>
@@ -10825,7 +10934,7 @@
       <c r="A295" s="2"/>
       <c r="B295" s="2"/>
       <c r="C295" s="2"/>
-      <c r="D295" s="2"/>
+      <c r="D295" s="50"/>
       <c r="E295" s="2"/>
       <c r="F295" s="2"/>
       <c r="G295" s="2"/>
@@ -10853,7 +10962,7 @@
       <c r="A296" s="2"/>
       <c r="B296" s="2"/>
       <c r="C296" s="2"/>
-      <c r="D296" s="2"/>
+      <c r="D296" s="50"/>
       <c r="E296" s="2"/>
       <c r="F296" s="2"/>
       <c r="G296" s="2"/>
@@ -10881,7 +10990,7 @@
       <c r="A297" s="2"/>
       <c r="B297" s="2"/>
       <c r="C297" s="2"/>
-      <c r="D297" s="2"/>
+      <c r="D297" s="50"/>
       <c r="E297" s="2"/>
       <c r="F297" s="2"/>
       <c r="G297" s="2"/>
@@ -10909,7 +11018,7 @@
       <c r="A298" s="2"/>
       <c r="B298" s="2"/>
       <c r="C298" s="2"/>
-      <c r="D298" s="2"/>
+      <c r="D298" s="50"/>
       <c r="E298" s="2"/>
       <c r="F298" s="2"/>
       <c r="G298" s="2"/>
@@ -10937,7 +11046,7 @@
       <c r="A299" s="2"/>
       <c r="B299" s="2"/>
       <c r="C299" s="2"/>
-      <c r="D299" s="2"/>
+      <c r="D299" s="50"/>
       <c r="E299" s="2"/>
       <c r="F299" s="2"/>
       <c r="G299" s="2"/>
@@ -10965,7 +11074,7 @@
       <c r="A300" s="2"/>
       <c r="B300" s="2"/>
       <c r="C300" s="2"/>
-      <c r="D300" s="2"/>
+      <c r="D300" s="50"/>
       <c r="E300" s="2"/>
       <c r="F300" s="2"/>
       <c r="G300" s="2"/>
@@ -10993,7 +11102,7 @@
       <c r="A301" s="2"/>
       <c r="B301" s="2"/>
       <c r="C301" s="2"/>
-      <c r="D301" s="2"/>
+      <c r="D301" s="50"/>
       <c r="E301" s="2"/>
       <c r="F301" s="2"/>
       <c r="G301" s="2"/>
@@ -11021,7 +11130,7 @@
       <c r="A302" s="2"/>
       <c r="B302" s="2"/>
       <c r="C302" s="2"/>
-      <c r="D302" s="2"/>
+      <c r="D302" s="50"/>
       <c r="E302" s="2"/>
       <c r="F302" s="2"/>
       <c r="G302" s="2"/>
@@ -11049,7 +11158,7 @@
       <c r="A303" s="2"/>
       <c r="B303" s="2"/>
       <c r="C303" s="2"/>
-      <c r="D303" s="2"/>
+      <c r="D303" s="50"/>
       <c r="E303" s="2"/>
       <c r="F303" s="2"/>
       <c r="G303" s="2"/>
@@ -11077,7 +11186,7 @@
       <c r="A304" s="2"/>
       <c r="B304" s="2"/>
       <c r="C304" s="2"/>
-      <c r="D304" s="2"/>
+      <c r="D304" s="50"/>
       <c r="E304" s="2"/>
       <c r="F304" s="2"/>
       <c r="G304" s="2"/>
@@ -11105,7 +11214,7 @@
       <c r="A305" s="2"/>
       <c r="B305" s="2"/>
       <c r="C305" s="2"/>
-      <c r="D305" s="2"/>
+      <c r="D305" s="50"/>
       <c r="E305" s="2"/>
       <c r="F305" s="2"/>
       <c r="G305" s="2"/>
@@ -11133,7 +11242,7 @@
       <c r="A306" s="2"/>
       <c r="B306" s="2"/>
       <c r="C306" s="2"/>
-      <c r="D306" s="2"/>
+      <c r="D306" s="50"/>
       <c r="E306" s="2"/>
       <c r="F306" s="2"/>
       <c r="G306" s="2"/>
@@ -11161,7 +11270,7 @@
       <c r="A307" s="2"/>
       <c r="B307" s="2"/>
       <c r="C307" s="2"/>
-      <c r="D307" s="2"/>
+      <c r="D307" s="50"/>
       <c r="E307" s="2"/>
       <c r="F307" s="2"/>
       <c r="G307" s="2"/>
@@ -11189,7 +11298,7 @@
       <c r="A308" s="2"/>
       <c r="B308" s="2"/>
       <c r="C308" s="2"/>
-      <c r="D308" s="2"/>
+      <c r="D308" s="50"/>
       <c r="E308" s="2"/>
       <c r="F308" s="2"/>
       <c r="G308" s="2"/>
@@ -11217,7 +11326,7 @@
       <c r="A309" s="2"/>
       <c r="B309" s="2"/>
       <c r="C309" s="2"/>
-      <c r="D309" s="2"/>
+      <c r="D309" s="50"/>
       <c r="E309" s="2"/>
       <c r="F309" s="2"/>
       <c r="G309" s="2"/>
@@ -11245,7 +11354,7 @@
       <c r="A310" s="2"/>
       <c r="B310" s="2"/>
       <c r="C310" s="2"/>
-      <c r="D310" s="2"/>
+      <c r="D310" s="50"/>
       <c r="E310" s="2"/>
       <c r="F310" s="2"/>
       <c r="G310" s="2"/>
@@ -11273,7 +11382,7 @@
       <c r="A311" s="2"/>
       <c r="B311" s="2"/>
       <c r="C311" s="2"/>
-      <c r="D311" s="2"/>
+      <c r="D311" s="50"/>
       <c r="E311" s="2"/>
       <c r="F311" s="2"/>
       <c r="G311" s="2"/>
@@ -11301,7 +11410,7 @@
       <c r="A312" s="2"/>
       <c r="B312" s="2"/>
       <c r="C312" s="2"/>
-      <c r="D312" s="2"/>
+      <c r="D312" s="50"/>
       <c r="E312" s="2"/>
       <c r="F312" s="2"/>
       <c r="G312" s="2"/>
@@ -11329,7 +11438,7 @@
       <c r="A313" s="2"/>
       <c r="B313" s="2"/>
       <c r="C313" s="2"/>
-      <c r="D313" s="2"/>
+      <c r="D313" s="50"/>
       <c r="E313" s="2"/>
       <c r="F313" s="2"/>
       <c r="G313" s="2"/>
@@ -11357,7 +11466,7 @@
       <c r="A314" s="2"/>
       <c r="B314" s="2"/>
       <c r="C314" s="2"/>
-      <c r="D314" s="2"/>
+      <c r="D314" s="50"/>
       <c r="E314" s="2"/>
       <c r="F314" s="2"/>
       <c r="G314" s="2"/>
@@ -11385,7 +11494,7 @@
       <c r="A315" s="2"/>
       <c r="B315" s="2"/>
       <c r="C315" s="2"/>
-      <c r="D315" s="2"/>
+      <c r="D315" s="50"/>
       <c r="E315" s="2"/>
       <c r="F315" s="2"/>
       <c r="G315" s="2"/>
@@ -11413,7 +11522,7 @@
       <c r="A316" s="2"/>
       <c r="B316" s="2"/>
       <c r="C316" s="2"/>
-      <c r="D316" s="2"/>
+      <c r="D316" s="50"/>
       <c r="E316" s="2"/>
       <c r="F316" s="2"/>
       <c r="G316" s="2"/>
@@ -11441,7 +11550,7 @@
       <c r="A317" s="2"/>
       <c r="B317" s="2"/>
       <c r="C317" s="2"/>
-      <c r="D317" s="2"/>
+      <c r="D317" s="50"/>
       <c r="E317" s="2"/>
       <c r="F317" s="2"/>
       <c r="G317" s="2"/>
@@ -11469,7 +11578,7 @@
       <c r="A318" s="2"/>
       <c r="B318" s="2"/>
       <c r="C318" s="2"/>
-      <c r="D318" s="2"/>
+      <c r="D318" s="50"/>
       <c r="E318" s="2"/>
       <c r="F318" s="2"/>
       <c r="G318" s="2"/>
@@ -11497,7 +11606,7 @@
       <c r="A319" s="2"/>
       <c r="B319" s="2"/>
       <c r="C319" s="2"/>
-      <c r="D319" s="2"/>
+      <c r="D319" s="50"/>
       <c r="E319" s="2"/>
       <c r="F319" s="2"/>
       <c r="G319" s="2"/>
@@ -11525,7 +11634,7 @@
       <c r="A320" s="2"/>
       <c r="B320" s="2"/>
       <c r="C320" s="2"/>
-      <c r="D320" s="2"/>
+      <c r="D320" s="50"/>
       <c r="E320" s="2"/>
       <c r="F320" s="2"/>
       <c r="G320" s="2"/>
@@ -11553,7 +11662,7 @@
       <c r="A321" s="2"/>
       <c r="B321" s="2"/>
       <c r="C321" s="2"/>
-      <c r="D321" s="2"/>
+      <c r="D321" s="50"/>
       <c r="E321" s="2"/>
       <c r="F321" s="2"/>
       <c r="G321" s="2"/>
@@ -11581,7 +11690,7 @@
       <c r="A322" s="2"/>
       <c r="B322" s="2"/>
       <c r="C322" s="2"/>
-      <c r="D322" s="2"/>
+      <c r="D322" s="50"/>
       <c r="E322" s="2"/>
       <c r="F322" s="2"/>
       <c r="G322" s="2"/>
@@ -11609,7 +11718,7 @@
       <c r="A323" s="2"/>
       <c r="B323" s="2"/>
       <c r="C323" s="2"/>
-      <c r="D323" s="2"/>
+      <c r="D323" s="50"/>
       <c r="E323" s="2"/>
       <c r="F323" s="2"/>
       <c r="G323" s="2"/>
@@ -11637,7 +11746,7 @@
       <c r="A324" s="2"/>
       <c r="B324" s="2"/>
       <c r="C324" s="2"/>
-      <c r="D324" s="2"/>
+      <c r="D324" s="50"/>
       <c r="E324" s="2"/>
       <c r="F324" s="2"/>
       <c r="G324" s="2"/>
@@ -11665,7 +11774,7 @@
       <c r="A325" s="2"/>
       <c r="B325" s="2"/>
       <c r="C325" s="2"/>
-      <c r="D325" s="2"/>
+      <c r="D325" s="50"/>
       <c r="E325" s="2"/>
       <c r="F325" s="2"/>
       <c r="G325" s="2"/>
@@ -11693,7 +11802,7 @@
       <c r="A326" s="2"/>
       <c r="B326" s="2"/>
       <c r="C326" s="2"/>
-      <c r="D326" s="2"/>
+      <c r="D326" s="50"/>
       <c r="E326" s="2"/>
       <c r="F326" s="2"/>
       <c r="G326" s="2"/>
@@ -11721,7 +11830,7 @@
       <c r="A327" s="2"/>
       <c r="B327" s="2"/>
       <c r="C327" s="2"/>
-      <c r="D327" s="2"/>
+      <c r="D327" s="50"/>
       <c r="E327" s="2"/>
       <c r="F327" s="2"/>
       <c r="G327" s="2"/>
@@ -11749,7 +11858,7 @@
       <c r="A328" s="2"/>
       <c r="B328" s="2"/>
       <c r="C328" s="2"/>
-      <c r="D328" s="2"/>
+      <c r="D328" s="50"/>
       <c r="E328" s="2"/>
       <c r="F328" s="2"/>
       <c r="G328" s="2"/>
@@ -11777,7 +11886,7 @@
       <c r="A329" s="2"/>
       <c r="B329" s="2"/>
       <c r="C329" s="2"/>
-      <c r="D329" s="2"/>
+      <c r="D329" s="50"/>
       <c r="E329" s="2"/>
       <c r="F329" s="2"/>
       <c r="G329" s="2"/>
@@ -11805,7 +11914,7 @@
       <c r="A330" s="2"/>
       <c r="B330" s="2"/>
       <c r="C330" s="2"/>
-      <c r="D330" s="2"/>
+      <c r="D330" s="50"/>
       <c r="E330" s="2"/>
       <c r="F330" s="2"/>
       <c r="G330" s="2"/>
@@ -11833,7 +11942,7 @@
       <c r="A331" s="2"/>
       <c r="B331" s="2"/>
       <c r="C331" s="2"/>
-      <c r="D331" s="2"/>
+      <c r="D331" s="50"/>
       <c r="E331" s="2"/>
       <c r="F331" s="2"/>
       <c r="G331" s="2"/>
@@ -11861,7 +11970,7 @@
       <c r="A332" s="2"/>
       <c r="B332" s="2"/>
       <c r="C332" s="2"/>
-      <c r="D332" s="2"/>
+      <c r="D332" s="50"/>
       <c r="E332" s="2"/>
       <c r="F332" s="2"/>
       <c r="G332" s="2"/>
@@ -11889,7 +11998,7 @@
       <c r="A333" s="2"/>
       <c r="B333" s="2"/>
       <c r="C333" s="2"/>
-      <c r="D333" s="2"/>
+      <c r="D333" s="50"/>
       <c r="E333" s="2"/>
       <c r="F333" s="2"/>
       <c r="G333" s="2"/>
@@ -11917,7 +12026,7 @@
       <c r="A334" s="2"/>
       <c r="B334" s="2"/>
       <c r="C334" s="2"/>
-      <c r="D334" s="2"/>
+      <c r="D334" s="50"/>
       <c r="E334" s="2"/>
       <c r="F334" s="2"/>
       <c r="G334" s="2"/>
@@ -11945,7 +12054,7 @@
       <c r="A335" s="2"/>
       <c r="B335" s="2"/>
       <c r="C335" s="2"/>
-      <c r="D335" s="2"/>
+      <c r="D335" s="50"/>
       <c r="E335" s="2"/>
       <c r="F335" s="2"/>
       <c r="G335" s="2"/>
@@ -11973,7 +12082,7 @@
       <c r="A336" s="2"/>
       <c r="B336" s="2"/>
       <c r="C336" s="2"/>
-      <c r="D336" s="2"/>
+      <c r="D336" s="50"/>
       <c r="E336" s="2"/>
       <c r="F336" s="2"/>
       <c r="G336" s="2"/>
@@ -12001,7 +12110,7 @@
       <c r="A337" s="2"/>
       <c r="B337" s="2"/>
       <c r="C337" s="2"/>
-      <c r="D337" s="2"/>
+      <c r="D337" s="50"/>
       <c r="E337" s="2"/>
       <c r="F337" s="2"/>
       <c r="G337" s="2"/>
@@ -12029,7 +12138,7 @@
       <c r="A338" s="2"/>
       <c r="B338" s="2"/>
       <c r="C338" s="2"/>
-      <c r="D338" s="2"/>
+      <c r="D338" s="50"/>
       <c r="E338" s="2"/>
       <c r="F338" s="2"/>
       <c r="G338" s="2"/>
@@ -12057,7 +12166,7 @@
       <c r="A339" s="2"/>
       <c r="B339" s="2"/>
       <c r="C339" s="2"/>
-      <c r="D339" s="2"/>
+      <c r="D339" s="50"/>
       <c r="E339" s="2"/>
       <c r="F339" s="2"/>
       <c r="G339" s="2"/>
@@ -12085,7 +12194,7 @@
       <c r="A340" s="2"/>
       <c r="B340" s="2"/>
       <c r="C340" s="2"/>
-      <c r="D340" s="2"/>
+      <c r="D340" s="50"/>
       <c r="E340" s="2"/>
       <c r="F340" s="2"/>
       <c r="G340" s="2"/>
@@ -12113,7 +12222,7 @@
       <c r="A341" s="2"/>
       <c r="B341" s="2"/>
       <c r="C341" s="2"/>
-      <c r="D341" s="2"/>
+      <c r="D341" s="50"/>
       <c r="E341" s="2"/>
       <c r="F341" s="2"/>
       <c r="G341" s="2"/>
@@ -12141,7 +12250,7 @@
       <c r="A342" s="2"/>
       <c r="B342" s="2"/>
       <c r="C342" s="2"/>
-      <c r="D342" s="2"/>
+      <c r="D342" s="50"/>
       <c r="E342" s="2"/>
       <c r="F342" s="2"/>
       <c r="G342" s="2"/>
@@ -12169,7 +12278,7 @@
       <c r="A343" s="2"/>
       <c r="B343" s="2"/>
       <c r="C343" s="2"/>
-      <c r="D343" s="2"/>
+      <c r="D343" s="50"/>
       <c r="E343" s="2"/>
       <c r="F343" s="2"/>
       <c r="G343" s="2"/>
@@ -12197,7 +12306,7 @@
       <c r="A344" s="2"/>
       <c r="B344" s="2"/>
       <c r="C344" s="2"/>
-      <c r="D344" s="2"/>
+      <c r="D344" s="50"/>
       <c r="E344" s="2"/>
       <c r="F344" s="2"/>
       <c r="G344" s="2"/>
@@ -12225,7 +12334,7 @@
       <c r="A345" s="2"/>
       <c r="B345" s="2"/>
       <c r="C345" s="2"/>
-      <c r="D345" s="2"/>
+      <c r="D345" s="50"/>
       <c r="E345" s="2"/>
       <c r="F345" s="2"/>
       <c r="G345" s="2"/>
@@ -12253,7 +12362,7 @@
       <c r="A346" s="2"/>
       <c r="B346" s="2"/>
       <c r="C346" s="2"/>
-      <c r="D346" s="2"/>
+      <c r="D346" s="50"/>
       <c r="E346" s="2"/>
       <c r="F346" s="2"/>
       <c r="G346" s="2"/>
@@ -12281,7 +12390,7 @@
       <c r="A347" s="2"/>
       <c r="B347" s="2"/>
       <c r="C347" s="2"/>
-      <c r="D347" s="2"/>
+      <c r="D347" s="50"/>
       <c r="E347" s="2"/>
       <c r="F347" s="2"/>
       <c r="G347" s="2"/>
@@ -12309,7 +12418,7 @@
       <c r="A348" s="2"/>
       <c r="B348" s="2"/>
       <c r="C348" s="2"/>
-      <c r="D348" s="2"/>
+      <c r="D348" s="50"/>
       <c r="E348" s="2"/>
       <c r="F348" s="2"/>
       <c r="G348" s="2"/>
@@ -12337,7 +12446,7 @@
       <c r="A349" s="2"/>
       <c r="B349" s="2"/>
       <c r="C349" s="2"/>
-      <c r="D349" s="2"/>
+      <c r="D349" s="50"/>
       <c r="E349" s="2"/>
       <c r="F349" s="2"/>
       <c r="G349" s="2"/>
@@ -12365,7 +12474,7 @@
       <c r="A350" s="2"/>
       <c r="B350" s="2"/>
       <c r="C350" s="2"/>
-      <c r="D350" s="2"/>
+      <c r="D350" s="50"/>
       <c r="E350" s="2"/>
       <c r="F350" s="2"/>
       <c r="G350" s="2"/>
@@ -12393,7 +12502,7 @@
       <c r="A351" s="2"/>
       <c r="B351" s="2"/>
       <c r="C351" s="2"/>
-      <c r="D351" s="2"/>
+      <c r="D351" s="50"/>
       <c r="E351" s="2"/>
       <c r="F351" s="2"/>
       <c r="G351" s="2"/>
@@ -12421,7 +12530,7 @@
       <c r="A352" s="2"/>
       <c r="B352" s="2"/>
       <c r="C352" s="2"/>
-      <c r="D352" s="2"/>
+      <c r="D352" s="50"/>
       <c r="E352" s="2"/>
       <c r="F352" s="2"/>
       <c r="G352" s="2"/>
@@ -12449,7 +12558,7 @@
       <c r="A353" s="2"/>
       <c r="B353" s="2"/>
       <c r="C353" s="2"/>
-      <c r="D353" s="2"/>
+      <c r="D353" s="50"/>
       <c r="E353" s="2"/>
       <c r="F353" s="2"/>
       <c r="G353" s="2"/>
@@ -12477,7 +12586,7 @@
       <c r="A354" s="2"/>
       <c r="B354" s="2"/>
       <c r="C354" s="2"/>
-      <c r="D354" s="2"/>
+      <c r="D354" s="50"/>
       <c r="E354" s="2"/>
       <c r="F354" s="2"/>
       <c r="G354" s="2"/>
@@ -12505,7 +12614,7 @@
       <c r="A355" s="2"/>
       <c r="B355" s="2"/>
       <c r="C355" s="2"/>
-      <c r="D355" s="2"/>
+      <c r="D355" s="50"/>
       <c r="E355" s="2"/>
       <c r="F355" s="2"/>
       <c r="G355" s="2"/>
@@ -12533,7 +12642,7 @@
       <c r="A356" s="2"/>
       <c r="B356" s="2"/>
       <c r="C356" s="2"/>
-      <c r="D356" s="2"/>
+      <c r="D356" s="50"/>
       <c r="E356" s="2"/>
       <c r="F356" s="2"/>
       <c r="G356" s="2"/>
@@ -12561,7 +12670,7 @@
       <c r="A357" s="2"/>
       <c r="B357" s="2"/>
       <c r="C357" s="2"/>
-      <c r="D357" s="2"/>
+      <c r="D357" s="50"/>
       <c r="E357" s="2"/>
       <c r="F357" s="2"/>
       <c r="G357" s="2"/>
@@ -12589,7 +12698,7 @@
       <c r="A358" s="2"/>
       <c r="B358" s="2"/>
       <c r="C358" s="2"/>
-      <c r="D358" s="2"/>
+      <c r="D358" s="50"/>
       <c r="E358" s="2"/>
       <c r="F358" s="2"/>
       <c r="G358" s="2"/>
@@ -12617,7 +12726,7 @@
       <c r="A359" s="2"/>
       <c r="B359" s="2"/>
       <c r="C359" s="2"/>
-      <c r="D359" s="2"/>
+      <c r="D359" s="50"/>
       <c r="E359" s="2"/>
       <c r="F359" s="2"/>
       <c r="G359" s="2"/>
@@ -12645,7 +12754,7 @@
       <c r="A360" s="2"/>
       <c r="B360" s="2"/>
       <c r="C360" s="2"/>
-      <c r="D360" s="2"/>
+      <c r="D360" s="50"/>
       <c r="E360" s="2"/>
       <c r="F360" s="2"/>
       <c r="G360" s="2"/>
@@ -12673,7 +12782,7 @@
       <c r="A361" s="2"/>
       <c r="B361" s="2"/>
       <c r="C361" s="2"/>
-      <c r="D361" s="2"/>
+      <c r="D361" s="50"/>
       <c r="E361" s="2"/>
       <c r="F361" s="2"/>
       <c r="G361" s="2"/>
@@ -12701,7 +12810,7 @@
       <c r="A362" s="2"/>
       <c r="B362" s="2"/>
       <c r="C362" s="2"/>
-      <c r="D362" s="2"/>
+      <c r="D362" s="50"/>
       <c r="E362" s="2"/>
       <c r="F362" s="2"/>
       <c r="G362" s="2"/>
@@ -12729,7 +12838,7 @@
       <c r="A363" s="2"/>
       <c r="B363" s="2"/>
       <c r="C363" s="2"/>
-      <c r="D363" s="2"/>
+      <c r="D363" s="50"/>
       <c r="E363" s="2"/>
       <c r="F363" s="2"/>
       <c r="G363" s="2"/>
@@ -12757,7 +12866,7 @@
       <c r="A364" s="2"/>
       <c r="B364" s="2"/>
       <c r="C364" s="2"/>
-      <c r="D364" s="2"/>
+      <c r="D364" s="50"/>
       <c r="E364" s="2"/>
       <c r="F364" s="2"/>
       <c r="G364" s="2"/>
@@ -12785,7 +12894,7 @@
       <c r="A365" s="2"/>
       <c r="B365" s="2"/>
       <c r="C365" s="2"/>
-      <c r="D365" s="2"/>
+      <c r="D365" s="50"/>
       <c r="E365" s="2"/>
       <c r="F365" s="2"/>
       <c r="G365" s="2"/>
@@ -12813,7 +12922,7 @@
       <c r="A366" s="2"/>
       <c r="B366" s="2"/>
       <c r="C366" s="2"/>
-      <c r="D366" s="2"/>
+      <c r="D366" s="50"/>
       <c r="E366" s="2"/>
       <c r="F366" s="2"/>
       <c r="G366" s="2"/>
@@ -12841,7 +12950,7 @@
       <c r="A367" s="2"/>
       <c r="B367" s="2"/>
       <c r="C367" s="2"/>
-      <c r="D367" s="2"/>
+      <c r="D367" s="50"/>
       <c r="E367" s="2"/>
       <c r="F367" s="2"/>
       <c r="G367" s="2"/>
@@ -12869,7 +12978,7 @@
       <c r="A368" s="2"/>
       <c r="B368" s="2"/>
       <c r="C368" s="2"/>
-      <c r="D368" s="2"/>
+      <c r="D368" s="50"/>
       <c r="E368" s="2"/>
       <c r="F368" s="2"/>
       <c r="G368" s="2"/>
@@ -12897,7 +13006,7 @@
       <c r="A369" s="2"/>
       <c r="B369" s="2"/>
       <c r="C369" s="2"/>
-      <c r="D369" s="2"/>
+      <c r="D369" s="50"/>
       <c r="E369" s="2"/>
       <c r="F369" s="2"/>
       <c r="G369" s="2"/>
@@ -12925,7 +13034,7 @@
       <c r="A370" s="2"/>
       <c r="B370" s="2"/>
       <c r="C370" s="2"/>
-      <c r="D370" s="2"/>
+      <c r="D370" s="50"/>
       <c r="E370" s="2"/>
       <c r="F370" s="2"/>
       <c r="G370" s="2"/>
@@ -12953,7 +13062,7 @@
       <c r="A371" s="2"/>
       <c r="B371" s="2"/>
       <c r="C371" s="2"/>
-      <c r="D371" s="2"/>
+      <c r="D371" s="50"/>
       <c r="E371" s="2"/>
       <c r="F371" s="2"/>
       <c r="G371" s="2"/>
@@ -12981,7 +13090,7 @@
       <c r="A372" s="2"/>
       <c r="B372" s="2"/>
       <c r="C372" s="2"/>
-      <c r="D372" s="2"/>
+      <c r="D372" s="50"/>
       <c r="E372" s="2"/>
       <c r="F372" s="2"/>
       <c r="G372" s="2"/>
@@ -13009,7 +13118,7 @@
       <c r="A373" s="2"/>
       <c r="B373" s="2"/>
       <c r="C373" s="2"/>
-      <c r="D373" s="2"/>
+      <c r="D373" s="50"/>
       <c r="E373" s="2"/>
       <c r="F373" s="2"/>
       <c r="G373" s="2"/>
@@ -13037,7 +13146,7 @@
       <c r="A374" s="2"/>
       <c r="B374" s="2"/>
       <c r="C374" s="2"/>
-      <c r="D374" s="2"/>
+      <c r="D374" s="50"/>
       <c r="E374" s="2"/>
       <c r="F374" s="2"/>
       <c r="G374" s="2"/>
@@ -13065,7 +13174,7 @@
       <c r="A375" s="2"/>
       <c r="B375" s="2"/>
       <c r="C375" s="2"/>
-      <c r="D375" s="2"/>
+      <c r="D375" s="50"/>
       <c r="E375" s="2"/>
       <c r="F375" s="2"/>
       <c r="G375" s="2"/>
@@ -13093,7 +13202,7 @@
       <c r="A376" s="2"/>
       <c r="B376" s="2"/>
       <c r="C376" s="2"/>
-      <c r="D376" s="2"/>
+      <c r="D376" s="50"/>
       <c r="E376" s="2"/>
       <c r="F376" s="2"/>
       <c r="G376" s="2"/>
@@ -13121,7 +13230,7 @@
       <c r="A377" s="2"/>
       <c r="B377" s="2"/>
       <c r="C377" s="2"/>
-      <c r="D377" s="2"/>
+      <c r="D377" s="50"/>
       <c r="E377" s="2"/>
       <c r="F377" s="2"/>
       <c r="G377" s="2"/>
@@ -13149,7 +13258,7 @@
       <c r="A378" s="2"/>
       <c r="B378" s="2"/>
       <c r="C378" s="2"/>
-      <c r="D378" s="2"/>
+      <c r="D378" s="50"/>
       <c r="E378" s="2"/>
       <c r="F378" s="2"/>
       <c r="G378" s="2"/>
@@ -13177,7 +13286,7 @@
       <c r="A379" s="2"/>
       <c r="B379" s="2"/>
       <c r="C379" s="2"/>
-      <c r="D379" s="2"/>
+      <c r="D379" s="50"/>
       <c r="E379" s="2"/>
       <c r="F379" s="2"/>
       <c r="G379" s="2"/>
@@ -13205,7 +13314,7 @@
       <c r="A380" s="2"/>
       <c r="B380" s="2"/>
       <c r="C380" s="2"/>
-      <c r="D380" s="2"/>
+      <c r="D380" s="50"/>
       <c r="E380" s="2"/>
       <c r="F380" s="2"/>
       <c r="G380" s="2"/>
@@ -13233,7 +13342,7 @@
       <c r="A381" s="2"/>
       <c r="B381" s="2"/>
       <c r="C381" s="2"/>
-      <c r="D381" s="2"/>
+      <c r="D381" s="50"/>
       <c r="E381" s="2"/>
       <c r="F381" s="2"/>
       <c r="G381" s="2"/>
@@ -13261,7 +13370,7 @@
       <c r="A382" s="2"/>
       <c r="B382" s="2"/>
       <c r="C382" s="2"/>
-      <c r="D382" s="2"/>
+      <c r="D382" s="50"/>
       <c r="E382" s="2"/>
       <c r="F382" s="2"/>
       <c r="G382" s="2"/>
@@ -13289,7 +13398,7 @@
       <c r="A383" s="2"/>
       <c r="B383" s="2"/>
       <c r="C383" s="2"/>
-      <c r="D383" s="2"/>
+      <c r="D383" s="50"/>
       <c r="E383" s="2"/>
       <c r="F383" s="2"/>
       <c r="G383" s="2"/>
@@ -13317,7 +13426,7 @@
       <c r="A384" s="2"/>
       <c r="B384" s="2"/>
       <c r="C384" s="2"/>
-      <c r="D384" s="2"/>
+      <c r="D384" s="50"/>
       <c r="E384" s="2"/>
       <c r="F384" s="2"/>
       <c r="G384" s="2"/>
@@ -13345,7 +13454,7 @@
       <c r="A385" s="2"/>
       <c r="B385" s="2"/>
       <c r="C385" s="2"/>
-      <c r="D385" s="2"/>
+      <c r="D385" s="50"/>
       <c r="E385" s="2"/>
       <c r="F385" s="2"/>
       <c r="G385" s="2"/>
@@ -13373,7 +13482,7 @@
       <c r="A386" s="2"/>
       <c r="B386" s="2"/>
       <c r="C386" s="2"/>
-      <c r="D386" s="2"/>
+      <c r="D386" s="50"/>
       <c r="E386" s="2"/>
       <c r="F386" s="2"/>
       <c r="G386" s="2"/>
@@ -13401,7 +13510,7 @@
       <c r="A387" s="2"/>
       <c r="B387" s="2"/>
       <c r="C387" s="2"/>
-      <c r="D387" s="2"/>
+      <c r="D387" s="50"/>
       <c r="E387" s="2"/>
       <c r="F387" s="2"/>
       <c r="G387" s="2"/>
@@ -13429,7 +13538,7 @@
       <c r="A388" s="2"/>
       <c r="B388" s="2"/>
       <c r="C388" s="2"/>
-      <c r="D388" s="2"/>
+      <c r="D388" s="50"/>
       <c r="E388" s="2"/>
       <c r="F388" s="2"/>
       <c r="G388" s="2"/>
@@ -13457,7 +13566,7 @@
       <c r="A389" s="2"/>
       <c r="B389" s="2"/>
       <c r="C389" s="2"/>
-      <c r="D389" s="2"/>
+      <c r="D389" s="50"/>
       <c r="E389" s="2"/>
       <c r="F389" s="2"/>
       <c r="G389" s="2"/>
@@ -13485,7 +13594,7 @@
       <c r="A390" s="2"/>
       <c r="B390" s="2"/>
       <c r="C390" s="2"/>
-      <c r="D390" s="2"/>
+      <c r="D390" s="50"/>
       <c r="E390" s="2"/>
       <c r="F390" s="2"/>
       <c r="G390" s="2"/>
@@ -13513,7 +13622,7 @@
       <c r="A391" s="2"/>
       <c r="B391" s="2"/>
       <c r="C391" s="2"/>
-      <c r="D391" s="2"/>
+      <c r="D391" s="50"/>
       <c r="E391" s="2"/>
       <c r="F391" s="2"/>
       <c r="G391" s="2"/>
@@ -13541,7 +13650,7 @@
       <c r="A392" s="2"/>
       <c r="B392" s="2"/>
       <c r="C392" s="2"/>
-      <c r="D392" s="2"/>
+      <c r="D392" s="50"/>
       <c r="E392" s="2"/>
       <c r="F392" s="2"/>
       <c r="G392" s="2"/>
@@ -13569,7 +13678,7 @@
       <c r="A393" s="2"/>
       <c r="B393" s="2"/>
       <c r="C393" s="2"/>
-      <c r="D393" s="2"/>
+      <c r="D393" s="50"/>
       <c r="E393" s="2"/>
       <c r="F393" s="2"/>
       <c r="G393" s="2"/>
@@ -13597,7 +13706,7 @@
       <c r="A394" s="2"/>
       <c r="B394" s="2"/>
       <c r="C394" s="2"/>
-      <c r="D394" s="2"/>
+      <c r="D394" s="50"/>
       <c r="E394" s="2"/>
       <c r="F394" s="2"/>
       <c r="G394" s="2"/>
@@ -13625,7 +13734,7 @@
       <c r="A395" s="2"/>
       <c r="B395" s="2"/>
       <c r="C395" s="2"/>
-      <c r="D395" s="2"/>
+      <c r="D395" s="50"/>
       <c r="E395" s="2"/>
       <c r="F395" s="2"/>
       <c r="G395" s="2"/>
@@ -13653,7 +13762,7 @@
       <c r="A396" s="2"/>
       <c r="B396" s="2"/>
       <c r="C396" s="2"/>
-      <c r="D396" s="2"/>
+      <c r="D396" s="50"/>
       <c r="E396" s="2"/>
       <c r="F396" s="2"/>
       <c r="G396" s="2"/>
@@ -13681,7 +13790,7 @@
       <c r="A397" s="2"/>
       <c r="B397" s="2"/>
       <c r="C397" s="2"/>
-      <c r="D397" s="2"/>
+      <c r="D397" s="50"/>
       <c r="E397" s="2"/>
       <c r="F397" s="2"/>
       <c r="G397" s="2"/>
@@ -13709,7 +13818,7 @@
       <c r="A398" s="2"/>
       <c r="B398" s="2"/>
       <c r="C398" s="2"/>
-      <c r="D398" s="2"/>
+      <c r="D398" s="50"/>
       <c r="E398" s="2"/>
       <c r="F398" s="2"/>
       <c r="G398" s="2"/>
@@ -13737,7 +13846,7 @@
       <c r="A399" s="2"/>
       <c r="B399" s="2"/>
       <c r="C399" s="2"/>
-      <c r="D399" s="2"/>
+      <c r="D399" s="50"/>
       <c r="E399" s="2"/>
       <c r="F399" s="2"/>
       <c r="G399" s="2"/>
@@ -13765,7 +13874,7 @@
       <c r="A400" s="2"/>
       <c r="B400" s="2"/>
       <c r="C400" s="2"/>
-      <c r="D400" s="2"/>
+      <c r="D400" s="50"/>
       <c r="E400" s="2"/>
       <c r="F400" s="2"/>
       <c r="G400" s="2"/>
@@ -13793,7 +13902,7 @@
       <c r="A401" s="2"/>
       <c r="B401" s="2"/>
       <c r="C401" s="2"/>
-      <c r="D401" s="2"/>
+      <c r="D401" s="50"/>
       <c r="E401" s="2"/>
       <c r="F401" s="2"/>
       <c r="G401" s="2"/>
@@ -13821,7 +13930,7 @@
       <c r="A402" s="2"/>
       <c r="B402" s="2"/>
       <c r="C402" s="2"/>
-      <c r="D402" s="2"/>
+      <c r="D402" s="50"/>
       <c r="E402" s="2"/>
       <c r="F402" s="2"/>
       <c r="G402" s="2"/>
@@ -13849,7 +13958,7 @@
       <c r="A403" s="2"/>
       <c r="B403" s="2"/>
       <c r="C403" s="2"/>
-      <c r="D403" s="2"/>
+      <c r="D403" s="50"/>
       <c r="E403" s="2"/>
       <c r="F403" s="2"/>
       <c r="G403" s="2"/>
@@ -13877,7 +13986,7 @@
       <c r="A404" s="2"/>
       <c r="B404" s="2"/>
       <c r="C404" s="2"/>
-      <c r="D404" s="2"/>
+      <c r="D404" s="50"/>
       <c r="E404" s="2"/>
       <c r="F404" s="2"/>
       <c r="G404" s="2"/>
@@ -13905,7 +14014,7 @@
       <c r="A405" s="2"/>
       <c r="B405" s="2"/>
       <c r="C405" s="2"/>
-      <c r="D405" s="2"/>
+      <c r="D405" s="50"/>
       <c r="E405" s="2"/>
       <c r="F405" s="2"/>
       <c r="G405" s="2"/>
@@ -13933,7 +14042,7 @@
       <c r="A406" s="2"/>
       <c r="B406" s="2"/>
       <c r="C406" s="2"/>
-      <c r="D406" s="2"/>
+      <c r="D406" s="50"/>
       <c r="E406" s="2"/>
       <c r="F406" s="2"/>
       <c r="G406" s="2"/>
@@ -13961,7 +14070,7 @@
       <c r="A407" s="2"/>
       <c r="B407" s="2"/>
       <c r="C407" s="2"/>
-      <c r="D407" s="2"/>
+      <c r="D407" s="50"/>
       <c r="E407" s="2"/>
       <c r="F407" s="2"/>
       <c r="G407" s="2"/>
@@ -13989,7 +14098,7 @@
       <c r="A408" s="2"/>
       <c r="B408" s="2"/>
       <c r="C408" s="2"/>
-      <c r="D408" s="2"/>
+      <c r="D408" s="50"/>
       <c r="E408" s="2"/>
       <c r="F408" s="2"/>
       <c r="G408" s="2"/>
@@ -14017,7 +14126,7 @@
       <c r="A409" s="2"/>
       <c r="B409" s="2"/>
       <c r="C409" s="2"/>
-      <c r="D409" s="2"/>
+      <c r="D409" s="50"/>
       <c r="E409" s="2"/>
       <c r="F409" s="2"/>
       <c r="G409" s="2"/>
@@ -14045,7 +14154,7 @@
       <c r="A410" s="2"/>
       <c r="B410" s="2"/>
       <c r="C410" s="2"/>
-      <c r="D410" s="2"/>
+      <c r="D410" s="50"/>
       <c r="E410" s="2"/>
       <c r="F410" s="2"/>
       <c r="G410" s="2"/>
@@ -14073,7 +14182,7 @@
       <c r="A411" s="2"/>
       <c r="B411" s="2"/>
       <c r="C411" s="2"/>
-      <c r="D411" s="2"/>
+      <c r="D411" s="50"/>
       <c r="E411" s="2"/>
       <c r="F411" s="2"/>
       <c r="G411" s="2"/>
@@ -14101,7 +14210,7 @@
       <c r="A412" s="2"/>
       <c r="B412" s="2"/>
       <c r="C412" s="2"/>
-      <c r="D412" s="2"/>
+      <c r="D412" s="50"/>
       <c r="E412" s="2"/>
       <c r="F412" s="2"/>
       <c r="G412" s="2"/>
@@ -14129,7 +14238,7 @@
       <c r="A413" s="2"/>
       <c r="B413" s="2"/>
       <c r="C413" s="2"/>
-      <c r="D413" s="2"/>
+      <c r="D413" s="50"/>
       <c r="E413" s="2"/>
       <c r="F413" s="2"/>
       <c r="G413" s="2"/>
@@ -14157,7 +14266,7 @@
       <c r="A414" s="2"/>
       <c r="B414" s="2"/>
       <c r="C414" s="2"/>
-      <c r="D414" s="2"/>
+      <c r="D414" s="50"/>
       <c r="E414" s="2"/>
       <c r="F414" s="2"/>
       <c r="G414" s="2"/>
@@ -14185,7 +14294,7 @@
       <c r="A415" s="2"/>
       <c r="B415" s="2"/>
       <c r="C415" s="2"/>
-      <c r="D415" s="2"/>
+      <c r="D415" s="50"/>
       <c r="E415" s="2"/>
       <c r="F415" s="2"/>
       <c r="G415" s="2"/>
@@ -14213,7 +14322,7 @@
       <c r="A416" s="2"/>
       <c r="B416" s="2"/>
       <c r="C416" s="2"/>
-      <c r="D416" s="2"/>
+      <c r="D416" s="50"/>
       <c r="E416" s="2"/>
       <c r="F416" s="2"/>
       <c r="G416" s="2"/>
@@ -14241,7 +14350,7 @@
       <c r="A417" s="2"/>
       <c r="B417" s="2"/>
       <c r="C417" s="2"/>
-      <c r="D417" s="2"/>
+      <c r="D417" s="50"/>
       <c r="E417" s="2"/>
       <c r="F417" s="2"/>
       <c r="G417" s="2"/>
@@ -14269,7 +14378,7 @@
       <c r="A418" s="2"/>
       <c r="B418" s="2"/>
       <c r="C418" s="2"/>
-      <c r="D418" s="2"/>
+      <c r="D418" s="50"/>
       <c r="E418" s="2"/>
       <c r="F418" s="2"/>
       <c r="G418" s="2"/>
@@ -14297,7 +14406,7 @@
       <c r="A419" s="2"/>
       <c r="B419" s="2"/>
       <c r="C419" s="2"/>
-      <c r="D419" s="2"/>
+      <c r="D419" s="50"/>
       <c r="E419" s="2"/>
       <c r="F419" s="2"/>
       <c r="G419" s="2"/>
@@ -14325,7 +14434,7 @@
       <c r="A420" s="2"/>
       <c r="B420" s="2"/>
       <c r="C420" s="2"/>
-      <c r="D420" s="2"/>
+      <c r="D420" s="50"/>
       <c r="E420" s="2"/>
       <c r="F420" s="2"/>
       <c r="G420" s="2"/>
@@ -14353,7 +14462,7 @@
       <c r="A421" s="2"/>
       <c r="B421" s="2"/>
       <c r="C421" s="2"/>
-      <c r="D421" s="2"/>
+      <c r="D421" s="50"/>
       <c r="E421" s="2"/>
       <c r="F421" s="2"/>
       <c r="G421" s="2"/>
@@ -14381,7 +14490,7 @@
       <c r="A422" s="2"/>
       <c r="B422" s="2"/>
       <c r="C422" s="2"/>
-      <c r="D422" s="2"/>
+      <c r="D422" s="50"/>
       <c r="E422" s="2"/>
       <c r="F422" s="2"/>
       <c r="G422" s="2"/>
@@ -14409,7 +14518,7 @@
       <c r="A423" s="2"/>
       <c r="B423" s="2"/>
       <c r="C423" s="2"/>
-      <c r="D423" s="2"/>
+      <c r="D423" s="50"/>
       <c r="E423" s="2"/>
       <c r="F423" s="2"/>
       <c r="G423" s="2"/>
@@ -14437,7 +14546,7 @@
       <c r="A424" s="2"/>
       <c r="B424" s="2"/>
       <c r="C424" s="2"/>
-      <c r="D424" s="2"/>
+      <c r="D424" s="50"/>
       <c r="E424" s="2"/>
       <c r="F424" s="2"/>
       <c r="G424" s="2"/>
@@ -14465,7 +14574,7 @@
       <c r="A425" s="2"/>
       <c r="B425" s="2"/>
       <c r="C425" s="2"/>
-      <c r="D425" s="2"/>
+      <c r="D425" s="50"/>
       <c r="E425" s="2"/>
       <c r="F425" s="2"/>
       <c r="G425" s="2"/>
@@ -14493,7 +14602,7 @@
       <c r="A426" s="2"/>
       <c r="B426" s="2"/>
       <c r="C426" s="2"/>
-      <c r="D426" s="2"/>
+      <c r="D426" s="50"/>
       <c r="E426" s="2"/>
       <c r="F426" s="2"/>
       <c r="G426" s="2"/>
@@ -14521,7 +14630,7 @@
       <c r="A427" s="2"/>
       <c r="B427" s="2"/>
       <c r="C427" s="2"/>
-      <c r="D427" s="2"/>
+      <c r="D427" s="50"/>
       <c r="E427" s="2"/>
       <c r="F427" s="2"/>
       <c r="G427" s="2"/>
@@ -14549,7 +14658,7 @@
       <c r="A428" s="2"/>
       <c r="B428" s="2"/>
       <c r="C428" s="2"/>
-      <c r="D428" s="2"/>
+      <c r="D428" s="50"/>
       <c r="E428" s="2"/>
       <c r="F428" s="2"/>
       <c r="G428" s="2"/>
@@ -14577,7 +14686,7 @@
       <c r="A429" s="2"/>
       <c r="B429" s="2"/>
       <c r="C429" s="2"/>
-      <c r="D429" s="2"/>
+      <c r="D429" s="50"/>
       <c r="E429" s="2"/>
       <c r="F429" s="2"/>
       <c r="G429" s="2"/>
@@ -14605,7 +14714,7 @@
       <c r="A430" s="2"/>
       <c r="B430" s="2"/>
       <c r="C430" s="2"/>
-      <c r="D430" s="2"/>
+      <c r="D430" s="50"/>
       <c r="E430" s="2"/>
       <c r="F430" s="2"/>
       <c r="G430" s="2"/>
@@ -14633,7 +14742,7 @@
       <c r="A431" s="2"/>
       <c r="B431" s="2"/>
       <c r="C431" s="2"/>
-      <c r="D431" s="2"/>
+      <c r="D431" s="50"/>
       <c r="E431" s="2"/>
       <c r="F431" s="2"/>
       <c r="G431" s="2"/>
@@ -14661,7 +14770,7 @@
       <c r="A432" s="2"/>
       <c r="B432" s="2"/>
       <c r="C432" s="2"/>
-      <c r="D432" s="2"/>
+      <c r="D432" s="50"/>
       <c r="E432" s="2"/>
       <c r="F432" s="2"/>
       <c r="G432" s="2"/>
@@ -14689,7 +14798,7 @@
       <c r="A433" s="2"/>
       <c r="B433" s="2"/>
       <c r="C433" s="2"/>
-      <c r="D433" s="2"/>
+      <c r="D433" s="50"/>
       <c r="E433" s="2"/>
       <c r="F433" s="2"/>
       <c r="G433" s="2"/>
@@ -14717,7 +14826,7 @@
       <c r="A434" s="2"/>
       <c r="B434" s="2"/>
       <c r="C434" s="2"/>
-      <c r="D434" s="2"/>
+      <c r="D434" s="50"/>
       <c r="E434" s="2"/>
       <c r="F434" s="2"/>
       <c r="G434" s="2"/>
@@ -14745,7 +14854,7 @@
       <c r="A435" s="2"/>
       <c r="B435" s="2"/>
       <c r="C435" s="2"/>
-      <c r="D435" s="2"/>
+      <c r="D435" s="50"/>
       <c r="E435" s="2"/>
       <c r="F435" s="2"/>
       <c r="G435" s="2"/>
@@ -14773,7 +14882,7 @@
       <c r="A436" s="2"/>
       <c r="B436" s="2"/>
       <c r="C436" s="2"/>
-      <c r="D436" s="2"/>
+      <c r="D436" s="50"/>
       <c r="E436" s="2"/>
       <c r="F436" s="2"/>
       <c r="G436" s="2"/>
@@ -14801,7 +14910,7 @@
       <c r="A437" s="2"/>
       <c r="B437" s="2"/>
       <c r="C437" s="2"/>
-      <c r="D437" s="2"/>
+      <c r="D437" s="50"/>
       <c r="E437" s="2"/>
       <c r="F437" s="2"/>
       <c r="G437" s="2"/>
@@ -14829,7 +14938,7 @@
       <c r="A438" s="2"/>
       <c r="B438" s="2"/>
       <c r="C438" s="2"/>
-      <c r="D438" s="2"/>
+      <c r="D438" s="50"/>
       <c r="E438" s="2"/>
       <c r="F438" s="2"/>
       <c r="G438" s="2"/>
@@ -14857,7 +14966,7 @@
       <c r="A439" s="2"/>
       <c r="B439" s="2"/>
       <c r="C439" s="2"/>
-      <c r="D439" s="2"/>
+      <c r="D439" s="50"/>
       <c r="E439" s="2"/>
       <c r="F439" s="2"/>
       <c r="G439" s="2"/>
@@ -14885,7 +14994,7 @@
       <c r="A440" s="2"/>
       <c r="B440" s="2"/>
       <c r="C440" s="2"/>
-      <c r="D440" s="2"/>
+      <c r="D440" s="50"/>
       <c r="E440" s="2"/>
       <c r="F440" s="2"/>
       <c r="G440" s="2"/>
@@ -14913,7 +15022,7 @@
       <c r="A441" s="2"/>
       <c r="B441" s="2"/>
       <c r="C441" s="2"/>
-      <c r="D441" s="2"/>
+      <c r="D441" s="50"/>
       <c r="E441" s="2"/>
       <c r="F441" s="2"/>
       <c r="G441" s="2"/>
@@ -14941,7 +15050,7 @@
       <c r="A442" s="2"/>
       <c r="B442" s="2"/>
       <c r="C442" s="2"/>
-      <c r="D442" s="2"/>
+      <c r="D442" s="50"/>
       <c r="E442" s="2"/>
       <c r="F442" s="2"/>
       <c r="G442" s="2"/>
@@ -14969,7 +15078,7 @@
       <c r="A443" s="2"/>
       <c r="B443" s="2"/>
       <c r="C443" s="2"/>
-      <c r="D443" s="2"/>
+      <c r="D443" s="50"/>
       <c r="E443" s="2"/>
       <c r="F443" s="2"/>
       <c r="G443" s="2"/>
@@ -14997,7 +15106,7 @@
       <c r="A444" s="2"/>
       <c r="B444" s="2"/>
       <c r="C444" s="2"/>
-      <c r="D444" s="2"/>
+      <c r="D444" s="50"/>
       <c r="E444" s="2"/>
       <c r="F444" s="2"/>
       <c r="G444" s="2"/>
@@ -15025,7 +15134,7 @@
       <c r="A445" s="2"/>
       <c r="B445" s="2"/>
       <c r="C445" s="2"/>
-      <c r="D445" s="2"/>
+      <c r="D445" s="50"/>
       <c r="E445" s="2"/>
       <c r="F445" s="2"/>
       <c r="G445" s="2"/>
@@ -15053,7 +15162,7 @@
       <c r="A446" s="2"/>
       <c r="B446" s="2"/>
       <c r="C446" s="2"/>
-      <c r="D446" s="2"/>
+      <c r="D446" s="50"/>
       <c r="E446" s="2"/>
       <c r="F446" s="2"/>
       <c r="G446" s="2"/>
@@ -15081,7 +15190,7 @@
       <c r="A447" s="2"/>
       <c r="B447" s="2"/>
       <c r="C447" s="2"/>
-      <c r="D447" s="2"/>
+      <c r="D447" s="50"/>
       <c r="E447" s="2"/>
       <c r="F447" s="2"/>
       <c r="G447" s="2"/>
@@ -15109,7 +15218,7 @@
       <c r="A448" s="2"/>
       <c r="B448" s="2"/>
       <c r="C448" s="2"/>
-      <c r="D448" s="2"/>
+      <c r="D448" s="50"/>
       <c r="E448" s="2"/>
       <c r="F448" s="2"/>
       <c r="G448" s="2"/>
@@ -15137,7 +15246,7 @@
       <c r="A449" s="2"/>
       <c r="B449" s="2"/>
       <c r="C449" s="2"/>
-      <c r="D449" s="2"/>
+      <c r="D449" s="50"/>
       <c r="E449" s="2"/>
       <c r="F449" s="2"/>
       <c r="G449" s="2"/>
@@ -15165,7 +15274,7 @@
       <c r="A450" s="2"/>
       <c r="B450" s="2"/>
       <c r="C450" s="2"/>
-      <c r="D450" s="2"/>
+      <c r="D450" s="50"/>
       <c r="E450" s="2"/>
       <c r="F450" s="2"/>
       <c r="G450" s="2"/>
@@ -15193,7 +15302,7 @@
       <c r="A451" s="2"/>
       <c r="B451" s="2"/>
       <c r="C451" s="2"/>
-      <c r="D451" s="2"/>
+      <c r="D451" s="50"/>
       <c r="E451" s="2"/>
       <c r="F451" s="2"/>
       <c r="G451" s="2"/>
@@ -15221,7 +15330,7 @@
       <c r="A452" s="2"/>
       <c r="B452" s="2"/>
       <c r="C452" s="2"/>
-      <c r="D452" s="2"/>
+      <c r="D452" s="50"/>
       <c r="E452" s="2"/>
       <c r="F452" s="2"/>
       <c r="G452" s="2"/>
@@ -15249,7 +15358,7 @@
       <c r="A453" s="2"/>
       <c r="B453" s="2"/>
       <c r="C453" s="2"/>
-      <c r="D453" s="2"/>
+      <c r="D453" s="50"/>
       <c r="E453" s="2"/>
       <c r="F453" s="2"/>
       <c r="G453" s="2"/>
@@ -15277,7 +15386,7 @@
       <c r="A454" s="2"/>
       <c r="B454" s="2"/>
       <c r="C454" s="2"/>
-      <c r="D454" s="2"/>
+      <c r="D454" s="50"/>
       <c r="E454" s="2"/>
       <c r="F454" s="2"/>
       <c r="G454" s="2"/>
@@ -15305,7 +15414,7 @@
       <c r="A455" s="2"/>
       <c r="B455" s="2"/>
       <c r="C455" s="2"/>
-      <c r="D455" s="2"/>
+      <c r="D455" s="50"/>
       <c r="E455" s="2"/>
       <c r="F455" s="2"/>
       <c r="G455" s="2"/>
@@ -15333,7 +15442,7 @@
       <c r="A456" s="2"/>
       <c r="B456" s="2"/>
       <c r="C456" s="2"/>
-      <c r="D456" s="2"/>
+      <c r="D456" s="50"/>
       <c r="E456" s="2"/>
       <c r="F456" s="2"/>
       <c r="G456" s="2"/>
@@ -15361,7 +15470,7 @@
       <c r="A457" s="2"/>
       <c r="B457" s="2"/>
       <c r="C457" s="2"/>
-      <c r="D457" s="2"/>
+      <c r="D457" s="50"/>
       <c r="E457" s="2"/>
       <c r="F457" s="2"/>
       <c r="G457" s="2"/>
@@ -15389,7 +15498,7 @@
       <c r="A458" s="2"/>
       <c r="B458" s="2"/>
       <c r="C458" s="2"/>
-      <c r="D458" s="2"/>
+      <c r="D458" s="50"/>
       <c r="E458" s="2"/>
       <c r="F458" s="2"/>
       <c r="G458" s="2"/>
@@ -15417,7 +15526,7 @@
       <c r="A459" s="2"/>
       <c r="B459" s="2"/>
       <c r="C459" s="2"/>
-      <c r="D459" s="2"/>
+      <c r="D459" s="50"/>
       <c r="E459" s="2"/>
       <c r="F459" s="2"/>
       <c r="G459" s="2"/>
@@ -15445,7 +15554,7 @@
       <c r="A460" s="2"/>
       <c r="B460" s="2"/>
       <c r="C460" s="2"/>
-      <c r="D460" s="2"/>
+      <c r="D460" s="50"/>
       <c r="E460" s="2"/>
       <c r="F460" s="2"/>
       <c r="G460" s="2"/>
@@ -15473,7 +15582,7 @@
       <c r="A461" s="2"/>
       <c r="B461" s="2"/>
       <c r="C461" s="2"/>
-      <c r="D461" s="2"/>
+      <c r="D461" s="50"/>
       <c r="E461" s="2"/>
       <c r="F461" s="2"/>
       <c r="G461" s="2"/>
@@ -15501,7 +15610,7 @@
       <c r="A462" s="2"/>
       <c r="B462" s="2"/>
       <c r="C462" s="2"/>
-      <c r="D462" s="2"/>
+      <c r="D462" s="50"/>
       <c r="E462" s="2"/>
       <c r="F462" s="2"/>
       <c r="G462" s="2"/>
@@ -15529,7 +15638,7 @@
       <c r="A463" s="2"/>
       <c r="B463" s="2"/>
       <c r="C463" s="2"/>
-      <c r="D463" s="2"/>
+      <c r="D463" s="50"/>
       <c r="E463" s="2"/>
       <c r="F463" s="2"/>
       <c r="G463" s="2"/>
@@ -15557,7 +15666,7 @@
       <c r="A464" s="2"/>
       <c r="B464" s="2"/>
       <c r="C464" s="2"/>
-      <c r="D464" s="2"/>
+      <c r="D464" s="50"/>
       <c r="E464" s="2"/>
       <c r="F464" s="2"/>
       <c r="G464" s="2"/>
@@ -15585,7 +15694,7 @@
       <c r="A465" s="2"/>
       <c r="B465" s="2"/>
       <c r="C465" s="2"/>
-      <c r="D465" s="2"/>
+      <c r="D465" s="50"/>
       <c r="E465" s="2"/>
       <c r="F465" s="2"/>
       <c r="G465" s="2"/>
@@ -15613,7 +15722,7 @@
       <c r="A466" s="2"/>
       <c r="B466" s="2"/>
       <c r="C466" s="2"/>
-      <c r="D466" s="2"/>
+      <c r="D466" s="50"/>
       <c r="E466" s="2"/>
       <c r="F466" s="2"/>
       <c r="G466" s="2"/>
@@ -15641,7 +15750,7 @@
       <c r="A467" s="2"/>
       <c r="B467" s="2"/>
       <c r="C467" s="2"/>
-      <c r="D467" s="2"/>
+      <c r="D467" s="50"/>
       <c r="E467" s="2"/>
       <c r="F467" s="2"/>
       <c r="G467" s="2"/>
@@ -15669,7 +15778,7 @@
       <c r="A468" s="2"/>
       <c r="B468" s="2"/>
       <c r="C468" s="2"/>
-      <c r="D468" s="2"/>
+      <c r="D468" s="50"/>
       <c r="E468" s="2"/>
       <c r="F468" s="2"/>
       <c r="G468" s="2"/>
@@ -15697,7 +15806,7 @@
       <c r="A469" s="2"/>
       <c r="B469" s="2"/>
       <c r="C469" s="2"/>
-      <c r="D469" s="2"/>
+      <c r="D469" s="50"/>
       <c r="E469" s="2"/>
       <c r="F469" s="2"/>
       <c r="G469" s="2"/>
@@ -15725,7 +15834,7 @@
       <c r="A470" s="2"/>
       <c r="B470" s="2"/>
       <c r="C470" s="2"/>
-      <c r="D470" s="2"/>
+      <c r="D470" s="50"/>
       <c r="E470" s="2"/>
       <c r="F470" s="2"/>
       <c r="G470" s="2"/>
@@ -15753,7 +15862,7 @@
       <c r="A471" s="2"/>
       <c r="B471" s="2"/>
       <c r="C471" s="2"/>
-      <c r="D471" s="2"/>
+      <c r="D471" s="50"/>
       <c r="E471" s="2"/>
       <c r="F471" s="2"/>
       <c r="G471" s="2"/>
@@ -15781,7 +15890,7 @@
       <c r="A472" s="2"/>
       <c r="B472" s="2"/>
       <c r="C472" s="2"/>
-      <c r="D472" s="2"/>
+      <c r="D472" s="50"/>
       <c r="E472" s="2"/>
       <c r="F472" s="2"/>
       <c r="G472" s="2"/>
@@ -15809,7 +15918,7 @@
       <c r="A473" s="2"/>
       <c r="B473" s="2"/>
       <c r="C473" s="2"/>
-      <c r="D473" s="2"/>
+      <c r="D473" s="50"/>
       <c r="E473" s="2"/>
       <c r="F473" s="2"/>
       <c r="G473" s="2"/>
@@ -15837,7 +15946,7 @@
       <c r="A474" s="2"/>
       <c r="B474" s="2"/>
       <c r="C474" s="2"/>
-      <c r="D474" s="2"/>
+      <c r="D474" s="50"/>
       <c r="E474" s="2"/>
       <c r="F474" s="2"/>
       <c r="G474" s="2"/>
@@ -15865,7 +15974,7 @@
       <c r="A475" s="2"/>
       <c r="B475" s="2"/>
       <c r="C475" s="2"/>
-      <c r="D475" s="2"/>
+      <c r="D475" s="50"/>
       <c r="E475" s="2"/>
       <c r="F475" s="2"/>
       <c r="G475" s="2"/>
@@ -15893,7 +16002,7 @@
       <c r="A476" s="2"/>
       <c r="B476" s="2"/>
       <c r="C476" s="2"/>
-      <c r="D476" s="2"/>
+      <c r="D476" s="50"/>
       <c r="E476" s="2"/>
       <c r="F476" s="2"/>
       <c r="G476" s="2"/>
@@ -15921,7 +16030,7 @@
       <c r="A477" s="2"/>
       <c r="B477" s="2"/>
       <c r="C477" s="2"/>
-      <c r="D477" s="2"/>
+      <c r="D477" s="50"/>
       <c r="E477" s="2"/>
       <c r="F477" s="2"/>
       <c r="G477" s="2"/>
@@ -15949,7 +16058,7 @@
       <c r="A478" s="2"/>
       <c r="B478" s="2"/>
       <c r="C478" s="2"/>
-      <c r="D478" s="2"/>
+      <c r="D478" s="50"/>
       <c r="E478" s="2"/>
       <c r="F478" s="2"/>
       <c r="G478" s="2"/>
@@ -15977,7 +16086,7 @@
       <c r="A479" s="2"/>
       <c r="B479" s="2"/>
       <c r="C479" s="2"/>
-      <c r="D479" s="2"/>
+      <c r="D479" s="50"/>
       <c r="E479" s="2"/>
       <c r="F479" s="2"/>
       <c r="G479" s="2"/>
@@ -16005,7 +16114,7 @@
       <c r="A480" s="2"/>
       <c r="B480" s="2"/>
       <c r="C480" s="2"/>
-      <c r="D480" s="2"/>
+      <c r="D480" s="50"/>
       <c r="E480" s="2"/>
       <c r="F480" s="2"/>
       <c r="G480" s="2"/>
@@ -16033,7 +16142,7 @@
       <c r="A481" s="2"/>
       <c r="B481" s="2"/>
       <c r="C481" s="2"/>
-      <c r="D481" s="2"/>
+      <c r="D481" s="50"/>
       <c r="E481" s="2"/>
       <c r="F481" s="2"/>
       <c r="G481" s="2"/>
@@ -16061,7 +16170,7 @@
       <c r="A482" s="2"/>
       <c r="B482" s="2"/>
       <c r="C482" s="2"/>
-      <c r="D482" s="2"/>
+      <c r="D482" s="50"/>
       <c r="E482" s="2"/>
       <c r="F482" s="2"/>
       <c r="G482" s="2"/>
@@ -16089,7 +16198,7 @@
       <c r="A483" s="2"/>
       <c r="B483" s="2"/>
       <c r="C483" s="2"/>
-      <c r="D483" s="2"/>
+      <c r="D483" s="50"/>
       <c r="E483" s="2"/>
       <c r="F483" s="2"/>
       <c r="G483" s="2"/>
@@ -16117,7 +16226,7 @@
       <c r="A484" s="2"/>
       <c r="B484" s="2"/>
       <c r="C484" s="2"/>
-      <c r="D484" s="2"/>
+      <c r="D484" s="50"/>
       <c r="E484" s="2"/>
       <c r="F484" s="2"/>
       <c r="G484" s="2"/>
@@ -16145,7 +16254,7 @@
       <c r="A485" s="2"/>
       <c r="B485" s="2"/>
       <c r="C485" s="2"/>
-      <c r="D485" s="2"/>
+      <c r="D485" s="50"/>
       <c r="E485" s="2"/>
       <c r="F485" s="2"/>
       <c r="G485" s="2"/>
@@ -16173,7 +16282,7 @@
       <c r="A486" s="2"/>
       <c r="B486" s="2"/>
       <c r="C486" s="2"/>
-      <c r="D486" s="2"/>
+      <c r="D486" s="50"/>
       <c r="E486" s="2"/>
       <c r="F486" s="2"/>
       <c r="G486" s="2"/>
@@ -16201,7 +16310,7 @@
       <c r="A487" s="2"/>
       <c r="B487" s="2"/>
       <c r="C487" s="2"/>
-      <c r="D487" s="2"/>
+      <c r="D487" s="50"/>
       <c r="E487" s="2"/>
       <c r="F487" s="2"/>
       <c r="G487" s="2"/>
@@ -16229,7 +16338,7 @@
       <c r="A488" s="2"/>
       <c r="B488" s="2"/>
       <c r="C488" s="2"/>
-      <c r="D488" s="2"/>
+      <c r="D488" s="50"/>
       <c r="E488" s="2"/>
       <c r="F488" s="2"/>
       <c r="G488" s="2"/>
@@ -16257,7 +16366,7 @@
       <c r="A489" s="2"/>
       <c r="B489" s="2"/>
       <c r="C489" s="2"/>
-      <c r="D489" s="2"/>
+      <c r="D489" s="50"/>
       <c r="E489" s="2"/>
       <c r="F489" s="2"/>
       <c r="G489" s="2"/>
@@ -16285,7 +16394,7 @@
       <c r="A490" s="2"/>
       <c r="B490" s="2"/>
       <c r="C490" s="2"/>
-      <c r="D490" s="2"/>
+      <c r="D490" s="50"/>
       <c r="E490" s="2"/>
       <c r="F490" s="2"/>
       <c r="G490" s="2"/>
@@ -16313,7 +16422,7 @@
       <c r="A491" s="2"/>
       <c r="B491" s="2"/>
       <c r="C491" s="2"/>
-      <c r="D491" s="2"/>
+      <c r="D491" s="50"/>
       <c r="E491" s="2"/>
       <c r="F491" s="2"/>
       <c r="G491" s="2"/>
@@ -16341,7 +16450,7 @@
       <c r="A492" s="2"/>
       <c r="B492" s="2"/>
       <c r="C492" s="2"/>
-      <c r="D492" s="2"/>
+      <c r="D492" s="50"/>
       <c r="E492" s="2"/>
       <c r="F492" s="2"/>
       <c r="G492" s="2"/>
@@ -16369,7 +16478,7 @@
       <c r="A493" s="2"/>
       <c r="B493" s="2"/>
       <c r="C493" s="2"/>
-      <c r="D493" s="2"/>
+      <c r="D493" s="50"/>
       <c r="E493" s="2"/>
       <c r="F493" s="2"/>
       <c r="G493" s="2"/>
@@ -16397,7 +16506,7 @@
       <c r="A494" s="2"/>
       <c r="B494" s="2"/>
       <c r="C494" s="2"/>
-      <c r="D494" s="2"/>
+      <c r="D494" s="50"/>
       <c r="E494" s="2"/>
       <c r="F494" s="2"/>
       <c r="G494" s="2"/>
@@ -16425,7 +16534,7 @@
       <c r="A495" s="2"/>
       <c r="B495" s="2"/>
       <c r="C495" s="2"/>
-      <c r="D495" s="2"/>
+      <c r="D495" s="50"/>
       <c r="E495" s="2"/>
       <c r="F495" s="2"/>
       <c r="G495" s="2"/>
@@ -16453,7 +16562,7 @@
       <c r="A496" s="2"/>
       <c r="B496" s="2"/>
       <c r="C496" s="2"/>
-      <c r="D496" s="2"/>
+      <c r="D496" s="50"/>
       <c r="E496" s="2"/>
       <c r="F496" s="2"/>
       <c r="G496" s="2"/>
@@ -16481,7 +16590,7 @@
       <c r="A497" s="2"/>
       <c r="B497" s="2"/>
       <c r="C497" s="2"/>
-      <c r="D497" s="2"/>
+      <c r="D497" s="50"/>
       <c r="E497" s="2"/>
       <c r="F497" s="2"/>
       <c r="G497" s="2"/>
@@ -16509,7 +16618,7 @@
       <c r="A498" s="2"/>
       <c r="B498" s="2"/>
       <c r="C498" s="2"/>
-      <c r="D498" s="2"/>
+      <c r="D498" s="50"/>
       <c r="E498" s="2"/>
       <c r="F498" s="2"/>
       <c r="G498" s="2"/>
@@ -16537,7 +16646,7 @@
       <c r="A499" s="2"/>
       <c r="B499" s="2"/>
       <c r="C499" s="2"/>
-      <c r="D499" s="2"/>
+      <c r="D499" s="50"/>
       <c r="E499" s="2"/>
       <c r="F499" s="2"/>
       <c r="G499" s="2"/>
@@ -16565,7 +16674,7 @@
       <c r="A500" s="2"/>
       <c r="B500" s="2"/>
       <c r="C500" s="2"/>
-      <c r="D500" s="2"/>
+      <c r="D500" s="50"/>
       <c r="E500" s="2"/>
       <c r="F500" s="2"/>
       <c r="G500" s="2"/>
@@ -16593,7 +16702,7 @@
       <c r="A501" s="2"/>
       <c r="B501" s="2"/>
       <c r="C501" s="2"/>
-      <c r="D501" s="2"/>
+      <c r="D501" s="50"/>
       <c r="E501" s="2"/>
       <c r="F501" s="2"/>
       <c r="G501" s="2"/>
@@ -16621,7 +16730,7 @@
       <c r="A502" s="2"/>
       <c r="B502" s="2"/>
       <c r="C502" s="2"/>
-      <c r="D502" s="2"/>
+      <c r="D502" s="50"/>
       <c r="E502" s="2"/>
       <c r="F502" s="2"/>
       <c r="G502" s="2"/>
@@ -16649,7 +16758,7 @@
       <c r="A503" s="2"/>
       <c r="B503" s="2"/>
       <c r="C503" s="2"/>
-      <c r="D503" s="2"/>
+      <c r="D503" s="50"/>
       <c r="E503" s="2"/>
       <c r="F503" s="2"/>
       <c r="G503" s="2"/>
@@ -16677,7 +16786,7 @@
       <c r="A504" s="2"/>
       <c r="B504" s="2"/>
       <c r="C504" s="2"/>
-      <c r="D504" s="2"/>
+      <c r="D504" s="50"/>
       <c r="E504" s="2"/>
       <c r="F504" s="2"/>
       <c r="G504" s="2"/>
@@ -16705,7 +16814,7 @@
       <c r="A505" s="2"/>
       <c r="B505" s="2"/>
       <c r="C505" s="2"/>
-      <c r="D505" s="2"/>
+      <c r="D505" s="50"/>
       <c r="E505" s="2"/>
       <c r="F505" s="2"/>
       <c r="G505" s="2"/>
@@ -16733,7 +16842,7 @@
       <c r="A506" s="2"/>
       <c r="B506" s="2"/>
       <c r="C506" s="2"/>
-      <c r="D506" s="2"/>
+      <c r="D506" s="50"/>
       <c r="E506" s="2"/>
       <c r="F506" s="2"/>
       <c r="G506" s="2"/>
@@ -16761,7 +16870,7 @@
       <c r="A507" s="2"/>
       <c r="B507" s="2"/>
       <c r="C507" s="2"/>
-      <c r="D507" s="2"/>
+      <c r="D507" s="50"/>
       <c r="E507" s="2"/>
       <c r="F507" s="2"/>
       <c r="G507" s="2"/>
@@ -16789,7 +16898,7 @@
       <c r="A508" s="2"/>
       <c r="B508" s="2"/>
       <c r="C508" s="2"/>
-      <c r="D508" s="2"/>
+      <c r="D508" s="50"/>
       <c r="E508" s="2"/>
       <c r="F508" s="2"/>
       <c r="G508" s="2"/>
@@ -16817,7 +16926,7 @@
       <c r="A509" s="2"/>
       <c r="B509" s="2"/>
       <c r="C509" s="2"/>
-      <c r="D509" s="2"/>
+      <c r="D509" s="50"/>
       <c r="E509" s="2"/>
       <c r="F509" s="2"/>
       <c r="G509" s="2"/>
@@ -16845,7 +16954,7 @@
       <c r="A510" s="2"/>
       <c r="B510" s="2"/>
       <c r="C510" s="2"/>
-      <c r="D510" s="2"/>
+      <c r="D510" s="50"/>
       <c r="E510" s="2"/>
       <c r="F510" s="2"/>
       <c r="G510" s="2"/>
@@ -16873,7 +16982,7 @@
       <c r="A511" s="2"/>
       <c r="B511" s="2"/>
       <c r="C511" s="2"/>
-      <c r="D511" s="2"/>
+      <c r="D511" s="50"/>
       <c r="E511" s="2"/>
       <c r="F511" s="2"/>
       <c r="G511" s="2"/>
@@ -16901,7 +17010,7 @@
       <c r="A512" s="2"/>
       <c r="B512" s="2"/>
       <c r="C512" s="2"/>
-      <c r="D512" s="2"/>
+      <c r="D512" s="50"/>
       <c r="E512" s="2"/>
       <c r="F512" s="2"/>
       <c r="G512" s="2"/>
@@ -16929,7 +17038,7 @@
       <c r="A513" s="2"/>
       <c r="B513" s="2"/>
       <c r="C513" s="2"/>
-      <c r="D513" s="2"/>
+      <c r="D513" s="50"/>
       <c r="E513" s="2"/>
       <c r="F513" s="2"/>
       <c r="G513" s="2"/>
@@ -16957,7 +17066,7 @@
       <c r="A514" s="2"/>
       <c r="B514" s="2"/>
       <c r="C514" s="2"/>
-      <c r="D514" s="2"/>
+      <c r="D514" s="50"/>
       <c r="E514" s="2"/>
       <c r="F514" s="2"/>
       <c r="G514" s="2"/>
@@ -16985,7 +17094,7 @@
       <c r="A515" s="2"/>
       <c r="B515" s="2"/>
       <c r="C515" s="2"/>
-      <c r="D515" s="2"/>
+      <c r="D515" s="50"/>
       <c r="E515" s="2"/>
       <c r="F515" s="2"/>
       <c r="G515" s="2"/>
@@ -17013,7 +17122,7 @@
       <c r="A516" s="2"/>
       <c r="B516" s="2"/>
       <c r="C516" s="2"/>
-      <c r="D516" s="2"/>
+      <c r="D516" s="50"/>
       <c r="E516" s="2"/>
       <c r="F516" s="2"/>
       <c r="G516" s="2"/>
@@ -17041,7 +17150,7 @@
       <c r="A517" s="2"/>
       <c r="B517" s="2"/>
       <c r="C517" s="2"/>
-      <c r="D517" s="2"/>
+      <c r="D517" s="50"/>
       <c r="E517" s="2"/>
       <c r="F517" s="2"/>
       <c r="G517" s="2"/>
@@ -17069,7 +17178,7 @@
       <c r="A518" s="2"/>
       <c r="B518" s="2"/>
       <c r="C518" s="2"/>
-      <c r="D518" s="2"/>
+      <c r="D518" s="50"/>
       <c r="E518" s="2"/>
       <c r="F518" s="2"/>
       <c r="G518" s="2"/>
@@ -17097,7 +17206,7 @@
       <c r="A519" s="2"/>
       <c r="B519" s="2"/>
       <c r="C519" s="2"/>
-      <c r="D519" s="2"/>
+      <c r="D519" s="50"/>
       <c r="E519" s="2"/>
       <c r="F519" s="2"/>
       <c r="G519" s="2"/>
@@ -17125,7 +17234,7 @@
       <c r="A520" s="2"/>
       <c r="B520" s="2"/>
       <c r="C520" s="2"/>
-      <c r="D520" s="2"/>
+      <c r="D520" s="50"/>
       <c r="E520" s="2"/>
       <c r="F520" s="2"/>
       <c r="G520" s="2"/>
@@ -17153,7 +17262,7 @@
       <c r="A521" s="2"/>
       <c r="B521" s="2"/>
       <c r="C521" s="2"/>
-      <c r="D521" s="2"/>
+      <c r="D521" s="50"/>
       <c r="E521" s="2"/>
       <c r="F521" s="2"/>
       <c r="G521" s="2"/>
@@ -17181,7 +17290,7 @@
       <c r="A522" s="2"/>
       <c r="B522" s="2"/>
       <c r="C522" s="2"/>
-      <c r="D522" s="2"/>
+      <c r="D522" s="50"/>
       <c r="E522" s="2"/>
       <c r="F522" s="2"/>
       <c r="G522" s="2"/>
@@ -17209,7 +17318,7 @@
       <c r="A523" s="2"/>
       <c r="B523" s="2"/>
       <c r="C523" s="2"/>
-      <c r="D523" s="2"/>
+      <c r="D523" s="50"/>
       <c r="E523" s="2"/>
       <c r="F523" s="2"/>
       <c r="G523" s="2"/>
@@ -17237,7 +17346,7 @@
       <c r="A524" s="2"/>
       <c r="B524" s="2"/>
       <c r="C524" s="2"/>
-      <c r="D524" s="2"/>
+      <c r="D524" s="50"/>
       <c r="E524" s="2"/>
       <c r="F524" s="2"/>
       <c r="G524" s="2"/>
@@ -17265,7 +17374,7 @@
       <c r="A525" s="2"/>
       <c r="B525" s="2"/>
       <c r="C525" s="2"/>
-      <c r="D525" s="2"/>
+      <c r="D525" s="50"/>
       <c r="E525" s="2"/>
       <c r="F525" s="2"/>
       <c r="G525" s="2"/>
@@ -17293,7 +17402,7 @@
       <c r="A526" s="2"/>
       <c r="B526" s="2"/>
       <c r="C526" s="2"/>
-      <c r="D526" s="2"/>
+      <c r="D526" s="50"/>
       <c r="E526" s="2"/>
       <c r="F526" s="2"/>
       <c r="G526" s="2"/>
@@ -17321,7 +17430,7 @@
       <c r="A527" s="2"/>
       <c r="B527" s="2"/>
       <c r="C527" s="2"/>
-      <c r="D527" s="2"/>
+      <c r="D527" s="50"/>
       <c r="E527" s="2"/>
       <c r="F527" s="2"/>
       <c r="G527" s="2"/>
@@ -17349,7 +17458,7 @@
       <c r="A528" s="2"/>
       <c r="B528" s="2"/>
       <c r="C528" s="2"/>
-      <c r="D528" s="2"/>
+      <c r="D528" s="50"/>
       <c r="E528" s="2"/>
       <c r="F528" s="2"/>
       <c r="G528" s="2"/>
@@ -17377,7 +17486,7 @@
       <c r="A529" s="2"/>
       <c r="B529" s="2"/>
       <c r="C529" s="2"/>
-      <c r="D529" s="2"/>
+      <c r="D529" s="50"/>
       <c r="E529" s="2"/>
       <c r="F529" s="2"/>
       <c r="G529" s="2"/>
@@ -17405,7 +17514,7 @@
       <c r="A530" s="2"/>
       <c r="B530" s="2"/>
       <c r="C530" s="2"/>
-      <c r="D530" s="2"/>
+      <c r="D530" s="50"/>
       <c r="E530" s="2"/>
       <c r="F530" s="2"/>
       <c r="G530" s="2"/>
@@ -17433,7 +17542,7 @@
       <c r="A531" s="2"/>
       <c r="B531" s="2"/>
       <c r="C531" s="2"/>
-      <c r="D531" s="2"/>
+      <c r="D531" s="50"/>
       <c r="E531" s="2"/>
       <c r="F531" s="2"/>
       <c r="G531" s="2"/>
@@ -17461,7 +17570,7 @@
       <c r="A532" s="2"/>
       <c r="B532" s="2"/>
       <c r="C532" s="2"/>
-      <c r="D532" s="2"/>
+      <c r="D532" s="50"/>
       <c r="E532" s="2"/>
       <c r="F532" s="2"/>
       <c r="G532" s="2"/>
@@ -17489,7 +17598,7 @@
       <c r="A533" s="2"/>
       <c r="B533" s="2"/>
       <c r="C533" s="2"/>
-      <c r="D533" s="2"/>
+      <c r="D533" s="50"/>
       <c r="E533" s="2"/>
       <c r="F533" s="2"/>
       <c r="G533" s="2"/>
@@ -17517,7 +17626,7 @@
       <c r="A534" s="2"/>
       <c r="B534" s="2"/>
       <c r="C534" s="2"/>
-      <c r="D534" s="2"/>
+      <c r="D534" s="50"/>
       <c r="E534" s="2"/>
       <c r="F534" s="2"/>
       <c r="G534" s="2"/>
@@ -17545,7 +17654,7 @@
       <c r="A535" s="2"/>
       <c r="B535" s="2"/>
       <c r="C535" s="2"/>
-      <c r="D535" s="2"/>
+      <c r="D535" s="50"/>
       <c r="E535" s="2"/>
       <c r="F535" s="2"/>
       <c r="G535" s="2"/>
@@ -17573,7 +17682,7 @@
       <c r="A536" s="2"/>
       <c r="B536" s="2"/>
       <c r="C536" s="2"/>
-      <c r="D536" s="2"/>
+      <c r="D536" s="50"/>
       <c r="E536" s="2"/>
       <c r="F536" s="2"/>
       <c r="G536" s="2"/>
@@ -17601,7 +17710,7 @@
       <c r="A537" s="2"/>
       <c r="B537" s="2"/>
       <c r="C537" s="2"/>
-      <c r="D537" s="2"/>
+      <c r="D537" s="50"/>
       <c r="E537" s="2"/>
       <c r="F537" s="2"/>
       <c r="G537" s="2"/>
@@ -17629,7 +17738,7 @@
       <c r="A538" s="2"/>
       <c r="B538" s="2"/>
       <c r="C538" s="2"/>
-      <c r="D538" s="2"/>
+      <c r="D538" s="50"/>
       <c r="E538" s="2"/>
       <c r="F538" s="2"/>
       <c r="G538" s="2"/>
@@ -17657,7 +17766,7 @@
       <c r="A539" s="2"/>
       <c r="B539" s="2"/>
       <c r="C539" s="2"/>
-      <c r="D539" s="2"/>
+      <c r="D539" s="50"/>
       <c r="E539" s="2"/>
       <c r="F539" s="2"/>
       <c r="G539" s="2"/>
@@ -17685,7 +17794,7 @@
       <c r="A540" s="2"/>
       <c r="B540" s="2"/>
       <c r="C540" s="2"/>
-      <c r="D540" s="2"/>
+      <c r="D540" s="50"/>
       <c r="E540" s="2"/>
       <c r="F540" s="2"/>
       <c r="G540" s="2"/>
@@ -17713,7 +17822,7 @@
       <c r="A541" s="2"/>
       <c r="B541" s="2"/>
       <c r="C541" s="2"/>
-      <c r="D541" s="2"/>
+      <c r="D541" s="50"/>
       <c r="E541" s="2"/>
       <c r="F541" s="2"/>
       <c r="G541" s="2"/>
@@ -17741,7 +17850,7 @@
       <c r="A542" s="2"/>
       <c r="B542" s="2"/>
       <c r="C542" s="2"/>
-      <c r="D542" s="2"/>
+      <c r="D542" s="50"/>
       <c r="E542" s="2"/>
       <c r="F542" s="2"/>
       <c r="G542" s="2"/>
@@ -17769,7 +17878,7 @@
       <c r="A543" s="2"/>
       <c r="B543" s="2"/>
       <c r="C543" s="2"/>
-      <c r="D543" s="2"/>
+      <c r="D543" s="50"/>
       <c r="E543" s="2"/>
       <c r="F543" s="2"/>
       <c r="G543" s="2"/>
@@ -17797,7 +17906,7 @@
       <c r="A544" s="2"/>
       <c r="B544" s="2"/>
       <c r="C544" s="2"/>
-      <c r="D544" s="2"/>
+      <c r="D544" s="50"/>
       <c r="E544" s="2"/>
       <c r="F544" s="2"/>
       <c r="G544" s="2"/>
@@ -17825,7 +17934,7 @@
       <c r="A545" s="2"/>
       <c r="B545" s="2"/>
       <c r="C545" s="2"/>
-      <c r="D545" s="2"/>
+      <c r="D545" s="50"/>
       <c r="E545" s="2"/>
       <c r="F545" s="2"/>
       <c r="G545" s="2"/>
@@ -17853,7 +17962,7 @@
       <c r="A546" s="2"/>
       <c r="B546" s="2"/>
       <c r="C546" s="2"/>
-      <c r="D546" s="2"/>
+      <c r="D546" s="50"/>
       <c r="E546" s="2"/>
       <c r="F546" s="2"/>
       <c r="G546" s="2"/>
@@ -17881,7 +17990,7 @@
       <c r="A547" s="2"/>
       <c r="B547" s="2"/>
       <c r="C547" s="2"/>
-      <c r="D547" s="2"/>
+      <c r="D547" s="50"/>
       <c r="E547" s="2"/>
       <c r="F547" s="2"/>
       <c r="G547" s="2"/>
@@ -17909,7 +18018,7 @@
       <c r="A548" s="2"/>
       <c r="B548" s="2"/>
       <c r="C548" s="2"/>
-      <c r="D548" s="2"/>
+      <c r="D548" s="50"/>
       <c r="E548" s="2"/>
       <c r="F548" s="2"/>
       <c r="G548" s="2"/>
@@ -17937,7 +18046,7 @@
       <c r="A549" s="2"/>
       <c r="B549" s="2"/>
       <c r="C549" s="2"/>
-      <c r="D549" s="2"/>
+      <c r="D549" s="50"/>
       <c r="E549" s="2"/>
       <c r="F549" s="2"/>
       <c r="G549" s="2"/>
@@ -17965,7 +18074,7 @@
       <c r="A550" s="2"/>
       <c r="B550" s="2"/>
       <c r="C550" s="2"/>
-      <c r="D550" s="2"/>
+      <c r="D550" s="50"/>
       <c r="E550" s="2"/>
       <c r="F550" s="2"/>
       <c r="G550" s="2"/>
@@ -17993,7 +18102,7 @@
       <c r="A551" s="2"/>
       <c r="B551" s="2"/>
       <c r="C551" s="2"/>
-      <c r="D551" s="2"/>
+      <c r="D551" s="50"/>
       <c r="E551" s="2"/>
       <c r="F551" s="2"/>
       <c r="G551" s="2"/>
@@ -18021,7 +18130,7 @@
       <c r="A552" s="2"/>
       <c r="B552" s="2"/>
       <c r="C552" s="2"/>
-      <c r="D552" s="2"/>
+      <c r="D552" s="50"/>
       <c r="E552" s="2"/>
       <c r="F552" s="2"/>
       <c r="G552" s="2"/>
@@ -18049,7 +18158,7 @@
       <c r="A553" s="2"/>
       <c r="B553" s="2"/>
       <c r="C553" s="2"/>
-      <c r="D553" s="2"/>
+      <c r="D553" s="50"/>
       <c r="E553" s="2"/>
       <c r="F553" s="2"/>
       <c r="G553" s="2"/>
@@ -18077,7 +18186,7 @@
       <c r="A554" s="2"/>
       <c r="B554" s="2"/>
       <c r="C554" s="2"/>
-      <c r="D554" s="2"/>
+      <c r="D554" s="50"/>
       <c r="E554" s="2"/>
       <c r="F554" s="2"/>
       <c r="G554" s="2"/>
@@ -18105,7 +18214,7 @@
       <c r="A555" s="2"/>
       <c r="B555" s="2"/>
       <c r="C555" s="2"/>
-      <c r="D555" s="2"/>
+      <c r="D555" s="50"/>
       <c r="E555" s="2"/>
       <c r="F555" s="2"/>
       <c r="G555" s="2"/>
@@ -18133,7 +18242,7 @@
       <c r="A556" s="2"/>
       <c r="B556" s="2"/>
       <c r="C556" s="2"/>
-      <c r="D556" s="2"/>
+      <c r="D556" s="50"/>
       <c r="E556" s="2"/>
       <c r="F556" s="2"/>
       <c r="G556" s="2"/>
@@ -18161,7 +18270,7 @@
       <c r="A557" s="2"/>
       <c r="B557" s="2"/>
       <c r="C557" s="2"/>
-      <c r="D557" s="2"/>
+      <c r="D557" s="50"/>
       <c r="E557" s="2"/>
       <c r="F557" s="2"/>
       <c r="G557" s="2"/>
@@ -18189,7 +18298,7 @@
       <c r="A558" s="2"/>
       <c r="B558" s="2"/>
       <c r="C558" s="2"/>
-      <c r="D558" s="2"/>
+      <c r="D558" s="50"/>
       <c r="E558" s="2"/>
       <c r="F558" s="2"/>
       <c r="G558" s="2"/>
@@ -18217,7 +18326,7 @@
       <c r="A559" s="2"/>
       <c r="B559" s="2"/>
       <c r="C559" s="2"/>
-      <c r="D559" s="2"/>
+      <c r="D559" s="50"/>
       <c r="E559" s="2"/>
       <c r="F559" s="2"/>
       <c r="G559" s="2"/>
@@ -18245,7 +18354,7 @@
       <c r="A560" s="2"/>
       <c r="B560" s="2"/>
       <c r="C560" s="2"/>
-      <c r="D560" s="2"/>
+      <c r="D560" s="50"/>
       <c r="E560" s="2"/>
       <c r="F560" s="2"/>
       <c r="G560" s="2"/>
@@ -18273,7 +18382,7 @@
       <c r="A561" s="2"/>
       <c r="B561" s="2"/>
       <c r="C561" s="2"/>
-      <c r="D561" s="2"/>
+      <c r="D561" s="50"/>
       <c r="E561" s="2"/>
       <c r="F561" s="2"/>
       <c r="G561" s="2"/>
@@ -18301,7 +18410,7 @@
       <c r="A562" s="2"/>
       <c r="B562" s="2"/>
       <c r="C562" s="2"/>
-      <c r="D562" s="2"/>
+      <c r="D562" s="50"/>
       <c r="E562" s="2"/>
       <c r="F562" s="2"/>
       <c r="G562" s="2"/>
@@ -18329,7 +18438,7 @@
       <c r="A563" s="2"/>
       <c r="B563" s="2"/>
       <c r="C563" s="2"/>
-      <c r="D563" s="2"/>
+      <c r="D563" s="50"/>
       <c r="E563" s="2"/>
       <c r="F563" s="2"/>
       <c r="G563" s="2"/>
@@ -18357,7 +18466,7 @@
       <c r="A564" s="2"/>
       <c r="B564" s="2"/>
       <c r="C564" s="2"/>
-      <c r="D564" s="2"/>
+      <c r="D564" s="50"/>
       <c r="E564" s="2"/>
       <c r="F564" s="2"/>
       <c r="G564" s="2"/>
@@ -18385,7 +18494,7 @@
       <c r="A565" s="2"/>
       <c r="B565" s="2"/>
       <c r="C565" s="2"/>
-      <c r="D565" s="2"/>
+      <c r="D565" s="50"/>
       <c r="E565" s="2"/>
       <c r="F565" s="2"/>
       <c r="G565" s="2"/>
@@ -18413,7 +18522,7 @@
       <c r="A566" s="2"/>
       <c r="B566" s="2"/>
       <c r="C566" s="2"/>
-      <c r="D566" s="2"/>
+      <c r="D566" s="50"/>
       <c r="E566" s="2"/>
       <c r="F566" s="2"/>
       <c r="G566" s="2"/>
@@ -18441,7 +18550,7 @@
       <c r="A567" s="2"/>
       <c r="B567" s="2"/>
       <c r="C567" s="2"/>
-      <c r="D567" s="2"/>
+      <c r="D567" s="50"/>
       <c r="E567" s="2"/>
       <c r="F567" s="2"/>
       <c r="G567" s="2"/>
@@ -18469,7 +18578,7 @@
       <c r="A568" s="2"/>
       <c r="B568" s="2"/>
       <c r="C568" s="2"/>
-      <c r="D568" s="2"/>
+      <c r="D568" s="50"/>
       <c r="E568" s="2"/>
       <c r="F568" s="2"/>
       <c r="G568" s="2"/>
@@ -18497,7 +18606,7 @@
       <c r="A569" s="2"/>
       <c r="B569" s="2"/>
       <c r="C569" s="2"/>
-      <c r="D569" s="2"/>
+      <c r="D569" s="50"/>
       <c r="E569" s="2"/>
       <c r="F569" s="2"/>
       <c r="G569" s="2"/>
@@ -18525,7 +18634,7 @@
       <c r="A570" s="2"/>
       <c r="B570" s="2"/>
       <c r="C570" s="2"/>
-      <c r="D570" s="2"/>
+      <c r="D570" s="50"/>
       <c r="E570" s="2"/>
       <c r="F570" s="2"/>
       <c r="G570" s="2"/>
@@ -18553,7 +18662,7 @@
       <c r="A571" s="2"/>
       <c r="B571" s="2"/>
       <c r="C571" s="2"/>
-      <c r="D571" s="2"/>
+      <c r="D571" s="50"/>
       <c r="E571" s="2"/>
       <c r="F571" s="2"/>
       <c r="G571" s="2"/>
@@ -18581,7 +18690,7 @@
       <c r="A572" s="2"/>
       <c r="B572" s="2"/>
       <c r="C572" s="2"/>
-      <c r="D572" s="2"/>
+      <c r="D572" s="50"/>
       <c r="E572" s="2"/>
       <c r="F572" s="2"/>
       <c r="G572" s="2"/>
@@ -18609,7 +18718,7 @@
       <c r="A573" s="2"/>
       <c r="B573" s="2"/>
       <c r="C573" s="2"/>
-      <c r="D573" s="2"/>
+      <c r="D573" s="50"/>
       <c r="E573" s="2"/>
       <c r="F573" s="2"/>
       <c r="G573" s="2"/>
@@ -18637,7 +18746,7 @@
       <c r="A574" s="2"/>
       <c r="B574" s="2"/>
       <c r="C574" s="2"/>
-      <c r="D574" s="2"/>
+      <c r="D574" s="50"/>
       <c r="E574" s="2"/>
       <c r="F574" s="2"/>
       <c r="G574" s="2"/>
@@ -18665,7 +18774,7 @@
       <c r="A575" s="2"/>
       <c r="B575" s="2"/>
       <c r="C575" s="2"/>
-      <c r="D575" s="2"/>
+      <c r="D575" s="50"/>
       <c r="E575" s="2"/>
       <c r="F575" s="2"/>
       <c r="G575" s="2"/>
@@ -18693,7 +18802,7 @@
       <c r="A576" s="2"/>
       <c r="B576" s="2"/>
       <c r="C576" s="2"/>
-      <c r="D576" s="2"/>
+      <c r="D576" s="50"/>
       <c r="E576" s="2"/>
       <c r="F576" s="2"/>
       <c r="G576" s="2"/>
@@ -18721,7 +18830,7 @@
       <c r="A577" s="2"/>
       <c r="B577" s="2"/>
       <c r="C577" s="2"/>
-      <c r="D577" s="2"/>
+      <c r="D577" s="50"/>
       <c r="E577" s="2"/>
       <c r="F577" s="2"/>
       <c r="G577" s="2"/>
@@ -18749,7 +18858,7 @@
       <c r="A578" s="2"/>
       <c r="B578" s="2"/>
       <c r="C578" s="2"/>
-      <c r="D578" s="2"/>
+      <c r="D578" s="50"/>
       <c r="E578" s="2"/>
       <c r="F578" s="2"/>
       <c r="G578" s="2"/>
@@ -18777,7 +18886,7 @@
       <c r="A579" s="2"/>
       <c r="B579" s="2"/>
       <c r="C579" s="2"/>
-      <c r="D579" s="2"/>
+      <c r="D579" s="50"/>
       <c r="E579" s="2"/>
       <c r="F579" s="2"/>
       <c r="G579" s="2"/>
@@ -18805,7 +18914,7 @@
       <c r="A580" s="2"/>
       <c r="B580" s="2"/>
       <c r="C580" s="2"/>
-      <c r="D580" s="2"/>
+      <c r="D580" s="50"/>
       <c r="E580" s="2"/>
       <c r="F580" s="2"/>
       <c r="G580" s="2"/>
@@ -18833,7 +18942,7 @@
       <c r="A581" s="2"/>
       <c r="B581" s="2"/>
       <c r="C581" s="2"/>
-      <c r="D581" s="2"/>
+      <c r="D581" s="50"/>
       <c r="E581" s="2"/>
       <c r="F581" s="2"/>
       <c r="G581" s="2"/>
@@ -18861,7 +18970,7 @@
       <c r="A582" s="2"/>
       <c r="B582" s="2"/>
       <c r="C582" s="2"/>
-      <c r="D582" s="2"/>
+      <c r="D582" s="50"/>
       <c r="E582" s="2"/>
       <c r="F582" s="2"/>
       <c r="G582" s="2"/>
@@ -18889,7 +18998,7 @@
       <c r="A583" s="2"/>
       <c r="B583" s="2"/>
       <c r="C583" s="2"/>
-      <c r="D583" s="2"/>
+      <c r="D583" s="50"/>
       <c r="E583" s="2"/>
       <c r="F583" s="2"/>
       <c r="G583" s="2"/>
@@ -18917,7 +19026,7 @@
       <c r="A584" s="2"/>
       <c r="B584" s="2"/>
       <c r="C584" s="2"/>
-      <c r="D584" s="2"/>
+      <c r="D584" s="50"/>
       <c r="E584" s="2"/>
       <c r="F584" s="2"/>
       <c r="G584" s="2"/>
@@ -18945,7 +19054,7 @@
       <c r="A585" s="2"/>
       <c r="B585" s="2"/>
       <c r="C585" s="2"/>
-      <c r="D585" s="2"/>
+      <c r="D585" s="50"/>
       <c r="E585" s="2"/>
       <c r="F585" s="2"/>
       <c r="G585" s="2"/>
@@ -18973,7 +19082,7 @@
       <c r="A586" s="2"/>
       <c r="B586" s="2"/>
       <c r="C586" s="2"/>
-      <c r="D586" s="2"/>
+      <c r="D586" s="50"/>
       <c r="E586" s="2"/>
       <c r="F586" s="2"/>
       <c r="G586" s="2"/>
@@ -19001,7 +19110,7 @@
       <c r="A587" s="2"/>
       <c r="B587" s="2"/>
       <c r="C587" s="2"/>
-      <c r="D587" s="2"/>
+      <c r="D587" s="50"/>
       <c r="E587" s="2"/>
       <c r="F587" s="2"/>
       <c r="G587" s="2"/>
@@ -19029,7 +19138,7 @@
       <c r="A588" s="2"/>
       <c r="B588" s="2"/>
       <c r="C588" s="2"/>
-      <c r="D588" s="2"/>
+      <c r="D588" s="50"/>
       <c r="E588" s="2"/>
       <c r="F588" s="2"/>
       <c r="G588" s="2"/>
@@ -19057,7 +19166,7 @@
       <c r="A589" s="2"/>
       <c r="B589" s="2"/>
       <c r="C589" s="2"/>
-      <c r="D589" s="2"/>
+      <c r="D589" s="50"/>
       <c r="E589" s="2"/>
       <c r="F589" s="2"/>
       <c r="G589" s="2"/>
@@ -19085,7 +19194,7 @@
       <c r="A590" s="2"/>
       <c r="B590" s="2"/>
       <c r="C590" s="2"/>
-      <c r="D590" s="2"/>
+      <c r="D590" s="50"/>
       <c r="E590" s="2"/>
       <c r="F590" s="2"/>
       <c r="G590" s="2"/>
@@ -19113,7 +19222,7 @@
       <c r="A591" s="2"/>
       <c r="B591" s="2"/>
       <c r="C591" s="2"/>
-      <c r="D591" s="2"/>
+      <c r="D591" s="50"/>
       <c r="E591" s="2"/>
       <c r="F591" s="2"/>
       <c r="G591" s="2"/>
@@ -19141,7 +19250,7 @@
       <c r="A592" s="2"/>
       <c r="B592" s="2"/>
       <c r="C592" s="2"/>
-      <c r="D592" s="2"/>
+      <c r="D592" s="50"/>
       <c r="E592" s="2"/>
       <c r="F592" s="2"/>
       <c r="G592" s="2"/>
@@ -19169,7 +19278,7 @@
       <c r="A593" s="2"/>
       <c r="B593" s="2"/>
       <c r="C593" s="2"/>
-      <c r="D593" s="2"/>
+      <c r="D593" s="50"/>
       <c r="E593" s="2"/>
       <c r="F593" s="2"/>
       <c r="G593" s="2"/>
@@ -19197,7 +19306,7 @@
       <c r="A594" s="2"/>
       <c r="B594" s="2"/>
       <c r="C594" s="2"/>
-      <c r="D594" s="2"/>
+      <c r="D594" s="50"/>
       <c r="E594" s="2"/>
       <c r="F594" s="2"/>
       <c r="G594" s="2"/>
@@ -19225,7 +19334,7 @@
       <c r="A595" s="2"/>
       <c r="B595" s="2"/>
       <c r="C595" s="2"/>
-      <c r="D595" s="2"/>
+      <c r="D595" s="50"/>
       <c r="E595" s="2"/>
       <c r="F595" s="2"/>
       <c r="G595" s="2"/>
@@ -19253,7 +19362,7 @@
       <c r="A596" s="2"/>
       <c r="B596" s="2"/>
       <c r="C596" s="2"/>
-      <c r="D596" s="2"/>
+      <c r="D596" s="50"/>
       <c r="E596" s="2"/>
       <c r="F596" s="2"/>
       <c r="G596" s="2"/>
@@ -19281,7 +19390,7 @@
       <c r="A597" s="2"/>
       <c r="B597" s="2"/>
       <c r="C597" s="2"/>
-      <c r="D597" s="2"/>
+      <c r="D597" s="50"/>
       <c r="E597" s="2"/>
       <c r="F597" s="2"/>
       <c r="G597" s="2"/>
@@ -19309,7 +19418,7 @@
       <c r="A598" s="2"/>
       <c r="B598" s="2"/>
       <c r="C598" s="2"/>
-      <c r="D598" s="2"/>
+      <c r="D598" s="50"/>
       <c r="E598" s="2"/>
       <c r="F598" s="2"/>
       <c r="G598" s="2"/>
@@ -19337,7 +19446,7 @@
       <c r="A599" s="2"/>
       <c r="B599" s="2"/>
       <c r="C599" s="2"/>
-      <c r="D599" s="2"/>
+      <c r="D599" s="50"/>
       <c r="E599" s="2"/>
       <c r="F599" s="2"/>
       <c r="G599" s="2"/>
@@ -19365,7 +19474,7 @@
       <c r="A600" s="2"/>
       <c r="B600" s="2"/>
       <c r="C600" s="2"/>
-      <c r="D600" s="2"/>
+      <c r="D600" s="50"/>
       <c r="E600" s="2"/>
       <c r="F600" s="2"/>
       <c r="G600" s="2"/>
@@ -19393,7 +19502,7 @@
       <c r="A601" s="2"/>
       <c r="B601" s="2"/>
       <c r="C601" s="2"/>
-      <c r="D601" s="2"/>
+      <c r="D601" s="50"/>
       <c r="E601" s="2"/>
       <c r="F601" s="2"/>
       <c r="G601" s="2"/>
@@ -19421,7 +19530,7 @@
       <c r="A602" s="2"/>
       <c r="B602" s="2"/>
       <c r="C602" s="2"/>
-      <c r="D602" s="2"/>
+      <c r="D602" s="50"/>
       <c r="E602" s="2"/>
       <c r="F602" s="2"/>
       <c r="G602" s="2"/>
@@ -19449,7 +19558,7 @@
       <c r="A603" s="2"/>
       <c r="B603" s="2"/>
       <c r="C603" s="2"/>
-      <c r="D603" s="2"/>
+      <c r="D603" s="50"/>
       <c r="E603" s="2"/>
       <c r="F603" s="2"/>
       <c r="G603" s="2"/>
@@ -19477,7 +19586,7 @@
       <c r="A604" s="2"/>
       <c r="B604" s="2"/>
       <c r="C604" s="2"/>
-      <c r="D604" s="2"/>
+      <c r="D604" s="50"/>
       <c r="E604" s="2"/>
       <c r="F604" s="2"/>
       <c r="G604" s="2"/>
@@ -19505,7 +19614,7 @@
       <c r="A605" s="2"/>
       <c r="B605" s="2"/>
       <c r="C605" s="2"/>
-      <c r="D605" s="2"/>
+      <c r="D605" s="50"/>
       <c r="E605" s="2"/>
       <c r="F605" s="2"/>
       <c r="G605" s="2"/>
@@ -19533,7 +19642,7 @@
       <c r="A606" s="2"/>
       <c r="B606" s="2"/>
       <c r="C606" s="2"/>
-      <c r="D606" s="2"/>
+      <c r="D606" s="50"/>
       <c r="E606" s="2"/>
       <c r="F606" s="2"/>
       <c r="G606" s="2"/>
@@ -19561,7 +19670,7 @@
       <c r="A607" s="2"/>
       <c r="B607" s="2"/>
       <c r="C607" s="2"/>
-      <c r="D607" s="2"/>
+      <c r="D607" s="50"/>
       <c r="E607" s="2"/>
       <c r="F607" s="2"/>
       <c r="G607" s="2"/>
@@ -19589,7 +19698,7 @@
       <c r="A608" s="2"/>
       <c r="B608" s="2"/>
       <c r="C608" s="2"/>
-      <c r="D608" s="2"/>
+      <c r="D608" s="50"/>
       <c r="E608" s="2"/>
       <c r="F608" s="2"/>
       <c r="G608" s="2"/>
@@ -19617,7 +19726,7 @@
       <c r="A609" s="2"/>
       <c r="B609" s="2"/>
       <c r="C609" s="2"/>
-      <c r="D609" s="2"/>
+      <c r="D609" s="50"/>
       <c r="E609" s="2"/>
       <c r="F609" s="2"/>
       <c r="G609" s="2"/>
@@ -19645,7 +19754,7 @@
       <c r="A610" s="2"/>
       <c r="B610" s="2"/>
       <c r="C610" s="2"/>
-      <c r="D610" s="2"/>
+      <c r="D610" s="50"/>
       <c r="E610" s="2"/>
       <c r="F610" s="2"/>
       <c r="G610" s="2"/>
@@ -19673,7 +19782,7 @@
       <c r="A611" s="2"/>
       <c r="B611" s="2"/>
       <c r="C611" s="2"/>
-      <c r="D611" s="2"/>
+      <c r="D611" s="50"/>
       <c r="E611" s="2"/>
       <c r="F611" s="2"/>
       <c r="G611" s="2"/>
@@ -19701,7 +19810,7 @@
       <c r="A612" s="2"/>
       <c r="B612" s="2"/>
       <c r="C612" s="2"/>
-      <c r="D612" s="2"/>
+      <c r="D612" s="50"/>
       <c r="E612" s="2"/>
       <c r="F612" s="2"/>
       <c r="G612" s="2"/>
@@ -19729,7 +19838,7 @@
       <c r="A613" s="2"/>
       <c r="B613" s="2"/>
       <c r="C613" s="2"/>
-      <c r="D613" s="2"/>
+      <c r="D613" s="50"/>
       <c r="E613" s="2"/>
       <c r="F613" s="2"/>
       <c r="G613" s="2"/>
@@ -19757,7 +19866,7 @@
       <c r="A614" s="2"/>
       <c r="B614" s="2"/>
       <c r="C614" s="2"/>
-      <c r="D614" s="2"/>
+      <c r="D614" s="50"/>
       <c r="E614" s="2"/>
       <c r="F614" s="2"/>
       <c r="G614" s="2"/>
@@ -19785,7 +19894,7 @@
       <c r="A615" s="2"/>
       <c r="B615" s="2"/>
       <c r="C615" s="2"/>
-      <c r="D615" s="2"/>
+      <c r="D615" s="50"/>
       <c r="E615" s="2"/>
       <c r="F615" s="2"/>
       <c r="G615" s="2"/>
@@ -19813,7 +19922,7 @@
       <c r="A616" s="2"/>
       <c r="B616" s="2"/>
       <c r="C616" s="2"/>
-      <c r="D616" s="2"/>
+      <c r="D616" s="50"/>
       <c r="E616" s="2"/>
       <c r="F616" s="2"/>
       <c r="G616" s="2"/>
@@ -19841,7 +19950,7 @@
       <c r="A617" s="2"/>
       <c r="B617" s="2"/>
       <c r="C617" s="2"/>
-      <c r="D617" s="2"/>
+      <c r="D617" s="50"/>
       <c r="E617" s="2"/>
       <c r="F617" s="2"/>
       <c r="G617" s="2"/>
@@ -19869,7 +19978,7 @@
       <c r="A618" s="2"/>
       <c r="B618" s="2"/>
       <c r="C618" s="2"/>
-      <c r="D618" s="2"/>
+      <c r="D618" s="50"/>
       <c r="E618" s="2"/>
       <c r="F618" s="2"/>
       <c r="G618" s="2"/>
@@ -19897,7 +20006,7 @@
       <c r="A619" s="2"/>
       <c r="B619" s="2"/>
       <c r="C619" s="2"/>
-      <c r="D619" s="2"/>
+      <c r="D619" s="50"/>
       <c r="E619" s="2"/>
       <c r="F619" s="2"/>
       <c r="G619" s="2"/>
@@ -19925,7 +20034,7 @@
       <c r="A620" s="2"/>
       <c r="B620" s="2"/>
       <c r="C620" s="2"/>
-      <c r="D620" s="2"/>
+      <c r="D620" s="50"/>
       <c r="E620" s="2"/>
       <c r="F620" s="2"/>
       <c r="G620" s="2"/>
@@ -19953,7 +20062,7 @@
       <c r="A621" s="2"/>
       <c r="B621" s="2"/>
       <c r="C621" s="2"/>
-      <c r="D621" s="2"/>
+      <c r="D621" s="50"/>
       <c r="E621" s="2"/>
       <c r="F621" s="2"/>
       <c r="G621" s="2"/>
@@ -19981,7 +20090,7 @@
       <c r="A622" s="2"/>
       <c r="B622" s="2"/>
       <c r="C622" s="2"/>
-      <c r="D622" s="2"/>
+      <c r="D622" s="50"/>
       <c r="E622" s="2"/>
       <c r="F622" s="2"/>
       <c r="G622" s="2"/>
@@ -20009,7 +20118,7 @@
       <c r="A623" s="2"/>
       <c r="B623" s="2"/>
       <c r="C623" s="2"/>
-      <c r="D623" s="2"/>
+      <c r="D623" s="50"/>
       <c r="E623" s="2"/>
       <c r="F623" s="2"/>
       <c r="G623" s="2"/>
@@ -20037,7 +20146,7 @@
       <c r="A624" s="2"/>
       <c r="B624" s="2"/>
       <c r="C624" s="2"/>
-      <c r="D624" s="2"/>
+      <c r="D624" s="50"/>
       <c r="E624" s="2"/>
       <c r="F624" s="2"/>
       <c r="G624" s="2"/>
@@ -20065,7 +20174,7 @@
       <c r="A625" s="2"/>
       <c r="B625" s="2"/>
       <c r="C625" s="2"/>
-      <c r="D625" s="2"/>
+      <c r="D625" s="50"/>
       <c r="E625" s="2"/>
       <c r="F625" s="2"/>
       <c r="G625" s="2"/>
@@ -20093,7 +20202,7 @@
       <c r="A626" s="2"/>
       <c r="B626" s="2"/>
       <c r="C626" s="2"/>
-      <c r="D626" s="2"/>
+      <c r="D626" s="50"/>
       <c r="E626" s="2"/>
       <c r="F626" s="2"/>
       <c r="G626" s="2"/>
@@ -20121,7 +20230,7 @@
       <c r="A627" s="2"/>
       <c r="B627" s="2"/>
       <c r="C627" s="2"/>
-      <c r="D627" s="2"/>
+      <c r="D627" s="50"/>
       <c r="E627" s="2"/>
       <c r="F627" s="2"/>
       <c r="G627" s="2"/>
@@ -20149,7 +20258,7 @@
       <c r="A628" s="2"/>
       <c r="B628" s="2"/>
       <c r="C628" s="2"/>
-      <c r="D628" s="2"/>
+      <c r="D628" s="50"/>
       <c r="E628" s="2"/>
       <c r="F628" s="2"/>
       <c r="G628" s="2"/>
@@ -20177,7 +20286,7 @@
       <c r="A629" s="2"/>
       <c r="B629" s="2"/>
       <c r="C629" s="2"/>
-      <c r="D629" s="2"/>
+      <c r="D629" s="50"/>
       <c r="E629" s="2"/>
       <c r="F629" s="2"/>
       <c r="G629" s="2"/>
@@ -20205,7 +20314,7 @@
       <c r="A630" s="2"/>
       <c r="B630" s="2"/>
       <c r="C630" s="2"/>
-      <c r="D630" s="2"/>
+      <c r="D630" s="50"/>
       <c r="E630" s="2"/>
       <c r="F630" s="2"/>
       <c r="G630" s="2"/>
@@ -20233,7 +20342,7 @@
       <c r="A631" s="2"/>
       <c r="B631" s="2"/>
       <c r="C631" s="2"/>
-      <c r="D631" s="2"/>
+      <c r="D631" s="50"/>
       <c r="E631" s="2"/>
       <c r="F631" s="2"/>
       <c r="G631" s="2"/>
@@ -20261,7 +20370,7 @@
       <c r="A632" s="2"/>
       <c r="B632" s="2"/>
       <c r="C632" s="2"/>
-      <c r="D632" s="2"/>
+      <c r="D632" s="50"/>
       <c r="E632" s="2"/>
       <c r="F632" s="2"/>
       <c r="G632" s="2"/>
@@ -20289,7 +20398,7 @@
       <c r="A633" s="2"/>
       <c r="B633" s="2"/>
       <c r="C633" s="2"/>
-      <c r="D633" s="2"/>
+      <c r="D633" s="50"/>
       <c r="E633" s="2"/>
       <c r="F633" s="2"/>
       <c r="G633" s="2"/>
@@ -20317,7 +20426,7 @@
       <c r="A634" s="2"/>
       <c r="B634" s="2"/>
       <c r="C634" s="2"/>
-      <c r="D634" s="2"/>
+      <c r="D634" s="50"/>
       <c r="E634" s="2"/>
       <c r="F634" s="2"/>
       <c r="G634" s="2"/>
@@ -20345,7 +20454,7 @@
       <c r="A635" s="2"/>
       <c r="B635" s="2"/>
       <c r="C635" s="2"/>
-      <c r="D635" s="2"/>
+      <c r="D635" s="50"/>
       <c r="E635" s="2"/>
       <c r="F635" s="2"/>
       <c r="G635" s="2"/>
@@ -20373,7 +20482,7 @@
       <c r="A636" s="2"/>
       <c r="B636" s="2"/>
       <c r="C636" s="2"/>
-      <c r="D636" s="2"/>
+      <c r="D636" s="50"/>
       <c r="E636" s="2"/>
       <c r="F636" s="2"/>
       <c r="G636" s="2"/>
@@ -20401,7 +20510,7 @@
       <c r="A637" s="2"/>
       <c r="B637" s="2"/>
       <c r="C637" s="2"/>
-      <c r="D637" s="2"/>
+      <c r="D637" s="50"/>
       <c r="E637" s="2"/>
       <c r="F637" s="2"/>
       <c r="G637" s="2"/>
@@ -20429,7 +20538,7 @@
       <c r="A638" s="2"/>
       <c r="B638" s="2"/>
       <c r="C638" s="2"/>
-      <c r="D638" s="2"/>
+      <c r="D638" s="50"/>
       <c r="E638" s="2"/>
       <c r="F638" s="2"/>
       <c r="G638" s="2"/>
@@ -20457,7 +20566,7 @@
       <c r="A639" s="2"/>
       <c r="B639" s="2"/>
       <c r="C639" s="2"/>
-      <c r="D639" s="2"/>
+      <c r="D639" s="50"/>
       <c r="E639" s="2"/>
       <c r="F639" s="2"/>
       <c r="G639" s="2"/>
@@ -20485,7 +20594,7 @@
       <c r="A640" s="2"/>
       <c r="B640" s="2"/>
       <c r="C640" s="2"/>
-      <c r="D640" s="2"/>
+      <c r="D640" s="50"/>
       <c r="E640" s="2"/>
       <c r="F640" s="2"/>
       <c r="G640" s="2"/>
@@ -20513,7 +20622,7 @@
       <c r="A641" s="2"/>
       <c r="B641" s="2"/>
       <c r="C641" s="2"/>
-      <c r="D641" s="2"/>
+      <c r="D641" s="50"/>
       <c r="E641" s="2"/>
       <c r="F641" s="2"/>
       <c r="G641" s="2"/>
@@ -20541,7 +20650,7 @@
       <c r="A642" s="2"/>
       <c r="B642" s="2"/>
       <c r="C642" s="2"/>
-      <c r="D642" s="2"/>
+      <c r="D642" s="50"/>
       <c r="E642" s="2"/>
       <c r="F642" s="2"/>
       <c r="G642" s="2"/>
@@ -20569,7 +20678,7 @@
       <c r="A643" s="2"/>
       <c r="B643" s="2"/>
       <c r="C643" s="2"/>
-      <c r="D643" s="2"/>
+      <c r="D643" s="50"/>
       <c r="E643" s="2"/>
       <c r="F643" s="2"/>
       <c r="G643" s="2"/>
@@ -20597,7 +20706,7 @@
       <c r="A644" s="2"/>
       <c r="B644" s="2"/>
       <c r="C644" s="2"/>
-      <c r="D644" s="2"/>
+      <c r="D644" s="50"/>
       <c r="E644" s="2"/>
       <c r="F644" s="2"/>
       <c r="G644" s="2"/>
@@ -20625,7 +20734,7 @@
       <c r="A645" s="2"/>
       <c r="B645" s="2"/>
       <c r="C645" s="2"/>
-      <c r="D645" s="2"/>
+      <c r="D645" s="50"/>
       <c r="E645" s="2"/>
       <c r="F645" s="2"/>
       <c r="G645" s="2"/>
@@ -20653,7 +20762,7 @@
       <c r="A646" s="2"/>
       <c r="B646" s="2"/>
       <c r="C646" s="2"/>
-      <c r="D646" s="2"/>
+      <c r="D646" s="50"/>
       <c r="E646" s="2"/>
       <c r="F646" s="2"/>
       <c r="G646" s="2"/>
@@ -20681,7 +20790,7 @@
       <c r="A647" s="2"/>
       <c r="B647" s="2"/>
       <c r="C647" s="2"/>
-      <c r="D647" s="2"/>
+      <c r="D647" s="50"/>
       <c r="E647" s="2"/>
       <c r="F647" s="2"/>
       <c r="G647" s="2"/>
@@ -20709,7 +20818,7 @@
       <c r="A648" s="2"/>
       <c r="B648" s="2"/>
       <c r="C648" s="2"/>
-      <c r="D648" s="2"/>
+      <c r="D648" s="50"/>
       <c r="E648" s="2"/>
       <c r="F648" s="2"/>
       <c r="G648" s="2"/>
@@ -20737,7 +20846,7 @@
       <c r="A649" s="2"/>
       <c r="B649" s="2"/>
       <c r="C649" s="2"/>
-      <c r="D649" s="2"/>
+      <c r="D649" s="50"/>
       <c r="E649" s="2"/>
       <c r="F649" s="2"/>
       <c r="G649" s="2"/>
@@ -20765,7 +20874,7 @@
       <c r="A650" s="2"/>
       <c r="B650" s="2"/>
       <c r="C650" s="2"/>
-      <c r="D650" s="2"/>
+      <c r="D650" s="50"/>
       <c r="E650" s="2"/>
       <c r="F650" s="2"/>
       <c r="G650" s="2"/>
@@ -20793,7 +20902,7 @@
       <c r="A651" s="2"/>
       <c r="B651" s="2"/>
       <c r="C651" s="2"/>
-      <c r="D651" s="2"/>
+      <c r="D651" s="50"/>
       <c r="E651" s="2"/>
       <c r="F651" s="2"/>
       <c r="G651" s="2"/>
@@ -20821,7 +20930,7 @@
       <c r="A652" s="2"/>
       <c r="B652" s="2"/>
       <c r="C652" s="2"/>
-      <c r="D652" s="2"/>
+      <c r="D652" s="50"/>
       <c r="E652" s="2"/>
       <c r="F652" s="2"/>
       <c r="G652" s="2"/>
@@ -20849,7 +20958,7 @@
       <c r="A653" s="2"/>
       <c r="B653" s="2"/>
       <c r="C653" s="2"/>
-      <c r="D653" s="2"/>
+      <c r="D653" s="50"/>
       <c r="E653" s="2"/>
       <c r="F653" s="2"/>
       <c r="G653" s="2"/>
@@ -20877,7 +20986,7 @@
       <c r="A654" s="2"/>
       <c r="B654" s="2"/>
       <c r="C654" s="2"/>
-      <c r="D654" s="2"/>
+      <c r="D654" s="50"/>
       <c r="E654" s="2"/>
       <c r="F654" s="2"/>
       <c r="G654" s="2"/>
@@ -20905,7 +21014,7 @@
       <c r="A655" s="2"/>
       <c r="B655" s="2"/>
       <c r="C655" s="2"/>
-      <c r="D655" s="2"/>
+      <c r="D655" s="50"/>
       <c r="E655" s="2"/>
       <c r="F655" s="2"/>
       <c r="G655" s="2"/>
@@ -20933,7 +21042,7 @@
       <c r="A656" s="2"/>
       <c r="B656" s="2"/>
       <c r="C656" s="2"/>
-      <c r="D656" s="2"/>
+      <c r="D656" s="50"/>
       <c r="E656" s="2"/>
       <c r="F656" s="2"/>
       <c r="G656" s="2"/>
@@ -20961,7 +21070,7 @@
       <c r="A657" s="2"/>
       <c r="B657" s="2"/>
       <c r="C657" s="2"/>
-      <c r="D657" s="2"/>
+      <c r="D657" s="50"/>
       <c r="E657" s="2"/>
       <c r="F657" s="2"/>
       <c r="G657" s="2"/>
@@ -20989,7 +21098,7 @@
       <c r="A658" s="2"/>
       <c r="B658" s="2"/>
       <c r="C658" s="2"/>
-      <c r="D658" s="2"/>
+      <c r="D658" s="50"/>
       <c r="E658" s="2"/>
       <c r="F658" s="2"/>
       <c r="G658" s="2"/>
@@ -21017,7 +21126,7 @@
       <c r="A659" s="2"/>
       <c r="B659" s="2"/>
       <c r="C659" s="2"/>
-      <c r="D659" s="2"/>
+      <c r="D659" s="50"/>
       <c r="E659" s="2"/>
       <c r="F659" s="2"/>
       <c r="G659" s="2"/>
@@ -21045,7 +21154,7 @@
       <c r="A660" s="2"/>
       <c r="B660" s="2"/>
       <c r="C660" s="2"/>
-      <c r="D660" s="2"/>
+      <c r="D660" s="50"/>
       <c r="E660" s="2"/>
       <c r="F660" s="2"/>
       <c r="G660" s="2"/>
@@ -21073,7 +21182,7 @@
       <c r="A661" s="2"/>
       <c r="B661" s="2"/>
       <c r="C661" s="2"/>
-      <c r="D661" s="2"/>
+      <c r="D661" s="50"/>
       <c r="E661" s="2"/>
       <c r="F661" s="2"/>
       <c r="G661" s="2"/>
@@ -21101,7 +21210,7 @@
       <c r="A662" s="2"/>
       <c r="B662" s="2"/>
       <c r="C662" s="2"/>
-      <c r="D662" s="2"/>
+      <c r="D662" s="50"/>
       <c r="E662" s="2"/>
       <c r="F662" s="2"/>
       <c r="G662" s="2"/>
@@ -21129,7 +21238,7 @@
       <c r="A663" s="2"/>
       <c r="B663" s="2"/>
       <c r="C663" s="2"/>
-      <c r="D663" s="2"/>
+      <c r="D663" s="50"/>
       <c r="E663" s="2"/>
       <c r="F663" s="2"/>
       <c r="G663" s="2"/>
@@ -21157,7 +21266,7 @@
       <c r="A664" s="2"/>
       <c r="B664" s="2"/>
       <c r="C664" s="2"/>
-      <c r="D664" s="2"/>
+      <c r="D664" s="50"/>
       <c r="E664" s="2"/>
       <c r="F664" s="2"/>
       <c r="G664" s="2"/>
@@ -21185,7 +21294,7 @@
       <c r="A665" s="2"/>
       <c r="B665" s="2"/>
       <c r="C665" s="2"/>
-      <c r="D665" s="2"/>
+      <c r="D665" s="50"/>
       <c r="E665" s="2"/>
       <c r="F665" s="2"/>
       <c r="G665" s="2"/>
@@ -21213,7 +21322,7 @@
       <c r="A666" s="2"/>
       <c r="B666" s="2"/>
       <c r="C666" s="2"/>
-      <c r="D666" s="2"/>
+      <c r="D666" s="50"/>
       <c r="E666" s="2"/>
       <c r="F666" s="2"/>
       <c r="G666" s="2"/>
@@ -21241,7 +21350,7 @@
       <c r="A667" s="2"/>
       <c r="B667" s="2"/>
       <c r="C667" s="2"/>
-      <c r="D667" s="2"/>
+      <c r="D667" s="50"/>
       <c r="E667" s="2"/>
       <c r="F667" s="2"/>
       <c r="G667" s="2"/>
@@ -21269,7 +21378,7 @@
       <c r="A668" s="2"/>
       <c r="B668" s="2"/>
       <c r="C668" s="2"/>
-      <c r="D668" s="2"/>
+      <c r="D668" s="50"/>
       <c r="E668" s="2"/>
       <c r="F668" s="2"/>
       <c r="G668" s="2"/>
@@ -21297,7 +21406,7 @@
       <c r="A669" s="2"/>
       <c r="B669" s="2"/>
       <c r="C669" s="2"/>
-      <c r="D669" s="2"/>
+      <c r="D669" s="50"/>
       <c r="E669" s="2"/>
       <c r="F669" s="2"/>
       <c r="G669" s="2"/>
@@ -21325,7 +21434,7 @@
       <c r="A670" s="2"/>
       <c r="B670" s="2"/>
       <c r="C670" s="2"/>
-      <c r="D670" s="2"/>
+      <c r="D670" s="50"/>
       <c r="E670" s="2"/>
       <c r="F670" s="2"/>
       <c r="G670" s="2"/>
@@ -21353,7 +21462,7 @@
       <c r="A671" s="2"/>
       <c r="B671" s="2"/>
       <c r="C671" s="2"/>
-      <c r="D671" s="2"/>
+      <c r="D671" s="50"/>
       <c r="E671" s="2"/>
       <c r="F671" s="2"/>
       <c r="G671" s="2"/>
@@ -21381,7 +21490,7 @@
       <c r="A672" s="2"/>
       <c r="B672" s="2"/>
       <c r="C672" s="2"/>
-      <c r="D672" s="2"/>
+      <c r="D672" s="50"/>
       <c r="E672" s="2"/>
       <c r="F672" s="2"/>
       <c r="G672" s="2"/>
@@ -21409,7 +21518,7 @@
       <c r="A673" s="2"/>
       <c r="B673" s="2"/>
       <c r="C673" s="2"/>
-      <c r="D673" s="2"/>
+      <c r="D673" s="50"/>
       <c r="E673" s="2"/>
       <c r="F673" s="2"/>
       <c r="G673" s="2"/>
@@ -21437,7 +21546,7 @@
       <c r="A674" s="2"/>
       <c r="B674" s="2"/>
       <c r="C674" s="2"/>
-      <c r="D674" s="2"/>
+      <c r="D674" s="50"/>
       <c r="E674" s="2"/>
       <c r="F674" s="2"/>
       <c r="G674" s="2"/>
@@ -21465,7 +21574,7 @@
       <c r="A675" s="2"/>
       <c r="B675" s="2"/>
       <c r="C675" s="2"/>
-      <c r="D675" s="2"/>
+      <c r="D675" s="50"/>
       <c r="E675" s="2"/>
       <c r="F675" s="2"/>
       <c r="G675" s="2"/>
@@ -21493,7 +21602,7 @@
       <c r="A676" s="2"/>
       <c r="B676" s="2"/>
       <c r="C676" s="2"/>
-      <c r="D676" s="2"/>
+      <c r="D676" s="50"/>
       <c r="E676" s="2"/>
       <c r="F676" s="2"/>
       <c r="G676" s="2"/>
@@ -21521,7 +21630,7 @@
       <c r="A677" s="2"/>
       <c r="B677" s="2"/>
       <c r="C677" s="2"/>
-      <c r="D677" s="2"/>
+      <c r="D677" s="50"/>
       <c r="E677" s="2"/>
       <c r="F677" s="2"/>
       <c r="G677" s="2"/>
@@ -21549,7 +21658,7 @@
       <c r="A678" s="2"/>
       <c r="B678" s="2"/>
       <c r="C678" s="2"/>
-      <c r="D678" s="2"/>
+      <c r="D678" s="50"/>
       <c r="E678" s="2"/>
       <c r="F678" s="2"/>
       <c r="G678" s="2"/>
@@ -21577,7 +21686,7 @@
       <c r="A679" s="2"/>
       <c r="B679" s="2"/>
       <c r="C679" s="2"/>
-      <c r="D679" s="2"/>
+      <c r="D679" s="50"/>
       <c r="E679" s="2"/>
       <c r="F679" s="2"/>
       <c r="G679" s="2"/>
@@ -21605,7 +21714,7 @@
       <c r="A680" s="2"/>
       <c r="B680" s="2"/>
       <c r="C680" s="2"/>
-      <c r="D680" s="2"/>
+      <c r="D680" s="50"/>
       <c r="E680" s="2"/>
       <c r="F680" s="2"/>
       <c r="G680" s="2"/>
@@ -21633,7 +21742,7 @@
       <c r="A681" s="2"/>
       <c r="B681" s="2"/>
       <c r="C681" s="2"/>
-      <c r="D681" s="2"/>
+      <c r="D681" s="50"/>
       <c r="E681" s="2"/>
       <c r="F681" s="2"/>
       <c r="G681" s="2"/>
@@ -21661,7 +21770,7 @@
       <c r="A682" s="2"/>
       <c r="B682" s="2"/>
       <c r="C682" s="2"/>
-      <c r="D682" s="2"/>
+      <c r="D682" s="50"/>
       <c r="E682" s="2"/>
       <c r="F682" s="2"/>
       <c r="G682" s="2"/>
@@ -21689,7 +21798,7 @@
       <c r="A683" s="2"/>
       <c r="B683" s="2"/>
       <c r="C683" s="2"/>
-      <c r="D683" s="2"/>
+      <c r="D683" s="50"/>
       <c r="E683" s="2"/>
       <c r="F683" s="2"/>
       <c r="G683" s="2"/>
@@ -21717,7 +21826,7 @@
       <c r="A684" s="2"/>
       <c r="B684" s="2"/>
       <c r="C684" s="2"/>
-      <c r="D684" s="2"/>
+      <c r="D684" s="50"/>
       <c r="E684" s="2"/>
       <c r="F684" s="2"/>
       <c r="G684" s="2"/>
@@ -21745,7 +21854,7 @@
       <c r="A685" s="2"/>
       <c r="B685" s="2"/>
       <c r="C685" s="2"/>
-      <c r="D685" s="2"/>
+      <c r="D685" s="50"/>
       <c r="E685" s="2"/>
       <c r="F685" s="2"/>
       <c r="G685" s="2"/>
@@ -21773,7 +21882,7 @@
       <c r="A686" s="2"/>
       <c r="B686" s="2"/>
       <c r="C686" s="2"/>
-      <c r="D686" s="2"/>
+      <c r="D686" s="50"/>
       <c r="E686" s="2"/>
       <c r="F686" s="2"/>
       <c r="G686" s="2"/>
@@ -21801,7 +21910,7 @@
       <c r="A687" s="2"/>
       <c r="B687" s="2"/>
       <c r="C687" s="2"/>
-      <c r="D687" s="2"/>
+      <c r="D687" s="50"/>
       <c r="E687" s="2"/>
       <c r="F687" s="2"/>
       <c r="G687" s="2"/>
@@ -21829,7 +21938,7 @@
       <c r="A688" s="2"/>
       <c r="B688" s="2"/>
       <c r="C688" s="2"/>
-      <c r="D688" s="2"/>
+      <c r="D688" s="50"/>
       <c r="E688" s="2"/>
       <c r="F688" s="2"/>
       <c r="G688" s="2"/>
@@ -21857,7 +21966,7 @@
       <c r="A689" s="2"/>
       <c r="B689" s="2"/>
       <c r="C689" s="2"/>
-      <c r="D689" s="2"/>
+      <c r="D689" s="50"/>
       <c r="E689" s="2"/>
       <c r="F689" s="2"/>
       <c r="G689" s="2"/>
@@ -21885,7 +21994,7 @@
       <c r="A690" s="2"/>
       <c r="B690" s="2"/>
       <c r="C690" s="2"/>
-      <c r="D690" s="2"/>
+      <c r="D690" s="50"/>
       <c r="E690" s="2"/>
       <c r="F690" s="2"/>
       <c r="G690" s="2"/>
@@ -21913,7 +22022,7 @@
       <c r="A691" s="2"/>
       <c r="B691" s="2"/>
       <c r="C691" s="2"/>
-      <c r="D691" s="2"/>
+      <c r="D691" s="50"/>
       <c r="E691" s="2"/>
       <c r="F691" s="2"/>
       <c r="G691" s="2"/>
@@ -21941,7 +22050,7 @@
       <c r="A692" s="2"/>
       <c r="B692" s="2"/>
       <c r="C692" s="2"/>
-      <c r="D692" s="2"/>
+      <c r="D692" s="50"/>
       <c r="E692" s="2"/>
       <c r="F692" s="2"/>
       <c r="G692" s="2"/>
@@ -21969,7 +22078,7 @@
       <c r="A693" s="2"/>
       <c r="B693" s="2"/>
       <c r="C693" s="2"/>
-      <c r="D693" s="2"/>
+      <c r="D693" s="50"/>
       <c r="E693" s="2"/>
       <c r="F693" s="2"/>
       <c r="G693" s="2"/>
@@ -21997,7 +22106,7 @@
       <c r="A694" s="2"/>
       <c r="B694" s="2"/>
       <c r="C694" s="2"/>
-      <c r="D694" s="2"/>
+      <c r="D694" s="50"/>
       <c r="E694" s="2"/>
       <c r="F694" s="2"/>
       <c r="G694" s="2"/>
@@ -22025,7 +22134,7 @@
       <c r="A695" s="2"/>
       <c r="B695" s="2"/>
       <c r="C695" s="2"/>
-      <c r="D695" s="2"/>
+      <c r="D695" s="50"/>
       <c r="E695" s="2"/>
       <c r="F695" s="2"/>
       <c r="G695" s="2"/>
@@ -22053,7 +22162,7 @@
       <c r="A696" s="2"/>
       <c r="B696" s="2"/>
       <c r="C696" s="2"/>
-      <c r="D696" s="2"/>
+      <c r="D696" s="50"/>
       <c r="E696" s="2"/>
       <c r="F696" s="2"/>
       <c r="G696" s="2"/>
@@ -22081,7 +22190,7 @@
       <c r="A697" s="2"/>
       <c r="B697" s="2"/>
       <c r="C697" s="2"/>
-      <c r="D697" s="2"/>
+      <c r="D697" s="50"/>
       <c r="E697" s="2"/>
       <c r="F697" s="2"/>
       <c r="G697" s="2"/>
@@ -22109,7 +22218,7 @@
       <c r="A698" s="2"/>
       <c r="B698" s="2"/>
       <c r="C698" s="2"/>
-      <c r="D698" s="2"/>
+      <c r="D698" s="50"/>
       <c r="E698" s="2"/>
       <c r="F698" s="2"/>
       <c r="G698" s="2"/>
@@ -22137,7 +22246,7 @@
       <c r="A699" s="2"/>
       <c r="B699" s="2"/>
       <c r="C699" s="2"/>
-      <c r="D699" s="2"/>
+      <c r="D699" s="50"/>
       <c r="E699" s="2"/>
       <c r="F699" s="2"/>
       <c r="G699" s="2"/>
@@ -22165,7 +22274,7 @@
       <c r="A700" s="2"/>
       <c r="B700" s="2"/>
       <c r="C700" s="2"/>
-      <c r="D700" s="2"/>
+      <c r="D700" s="50"/>
       <c r="E700" s="2"/>
       <c r="F700" s="2"/>
       <c r="G700" s="2"/>
@@ -22193,7 +22302,7 @@
       <c r="A701" s="2"/>
       <c r="B701" s="2"/>
       <c r="C701" s="2"/>
-      <c r="D701" s="2"/>
+      <c r="D701" s="50"/>
       <c r="E701" s="2"/>
       <c r="F701" s="2"/>
       <c r="G701" s="2"/>
@@ -22221,7 +22330,7 @@
       <c r="A702" s="2"/>
       <c r="B702" s="2"/>
       <c r="C702" s="2"/>
-      <c r="D702" s="2"/>
+      <c r="D702" s="50"/>
       <c r="E702" s="2"/>
       <c r="F702" s="2"/>
       <c r="G702" s="2"/>
@@ -22249,7 +22358,7 @@
       <c r="A703" s="2"/>
       <c r="B703" s="2"/>
       <c r="C703" s="2"/>
-      <c r="D703" s="2"/>
+      <c r="D703" s="50"/>
       <c r="E703" s="2"/>
       <c r="F703" s="2"/>
       <c r="G703" s="2"/>
@@ -22277,7 +22386,7 @@
       <c r="A704" s="2"/>
       <c r="B704" s="2"/>
       <c r="C704" s="2"/>
-      <c r="D704" s="2"/>
+      <c r="D704" s="50"/>
       <c r="E704" s="2"/>
       <c r="F704" s="2"/>
       <c r="G704" s="2"/>
@@ -22305,7 +22414,7 @@
       <c r="A705" s="2"/>
       <c r="B705" s="2"/>
       <c r="C705" s="2"/>
-      <c r="D705" s="2"/>
+      <c r="D705" s="50"/>
       <c r="E705" s="2"/>
       <c r="F705" s="2"/>
       <c r="G705" s="2"/>
@@ -22333,7 +22442,7 @@
       <c r="A706" s="2"/>
       <c r="B706" s="2"/>
       <c r="C706" s="2"/>
-      <c r="D706" s="2"/>
+      <c r="D706" s="50"/>
       <c r="E706" s="2"/>
       <c r="F706" s="2"/>
       <c r="G706" s="2"/>
@@ -22361,7 +22470,7 @@
       <c r="A707" s="2"/>
       <c r="B707" s="2"/>
       <c r="C707" s="2"/>
-      <c r="D707" s="2"/>
+      <c r="D707" s="50"/>
       <c r="E707" s="2"/>
       <c r="F707" s="2"/>
       <c r="G707" s="2"/>
@@ -22389,7 +22498,7 @@
       <c r="A708" s="2"/>
       <c r="B708" s="2"/>
       <c r="C708" s="2"/>
-      <c r="D708" s="2"/>
+      <c r="D708" s="50"/>
       <c r="E708" s="2"/>
       <c r="F708" s="2"/>
       <c r="G708" s="2"/>
@@ -22417,7 +22526,7 @@
       <c r="A709" s="2"/>
       <c r="B709" s="2"/>
       <c r="C709" s="2"/>
-      <c r="D709" s="2"/>
+      <c r="D709" s="50"/>
       <c r="E709" s="2"/>
       <c r="F709" s="2"/>
       <c r="G709" s="2"/>
@@ -22445,7 +22554,7 @@
       <c r="A710" s="2"/>
       <c r="B710" s="2"/>
       <c r="C710" s="2"/>
-      <c r="D710" s="2"/>
+      <c r="D710" s="50"/>
       <c r="E710" s="2"/>
       <c r="F710" s="2"/>
       <c r="G710" s="2"/>
@@ -22473,7 +22582,7 @@
       <c r="A711" s="2"/>
       <c r="B711" s="2"/>
       <c r="C711" s="2"/>
-      <c r="D711" s="2"/>
+      <c r="D711" s="50"/>
       <c r="E711" s="2"/>
       <c r="F711" s="2"/>
       <c r="G711" s="2"/>
@@ -22501,7 +22610,7 @@
       <c r="A712" s="2"/>
       <c r="B712" s="2"/>
       <c r="C712" s="2"/>
-      <c r="D712" s="2"/>
+      <c r="D712" s="50"/>
       <c r="E712" s="2"/>
       <c r="F712" s="2"/>
       <c r="G712" s="2"/>
@@ -22529,7 +22638,7 @@
       <c r="A713" s="2"/>
       <c r="B713" s="2"/>
       <c r="C713" s="2"/>
-      <c r="D713" s="2"/>
+      <c r="D713" s="50"/>
       <c r="E713" s="2"/>
       <c r="F713" s="2"/>
       <c r="G713" s="2"/>
@@ -22557,7 +22666,7 @@
       <c r="A714" s="2"/>
       <c r="B714" s="2"/>
       <c r="C714" s="2"/>
-      <c r="D714" s="2"/>
+      <c r="D714" s="50"/>
       <c r="E714" s="2"/>
       <c r="F714" s="2"/>
       <c r="G714" s="2"/>
@@ -22585,7 +22694,7 @@
       <c r="A715" s="2"/>
       <c r="B715" s="2"/>
       <c r="C715" s="2"/>
-      <c r="D715" s="2"/>
+      <c r="D715" s="50"/>
       <c r="E715" s="2"/>
       <c r="F715" s="2"/>
       <c r="G715" s="2"/>
@@ -22613,7 +22722,7 @@
       <c r="A716" s="2"/>
       <c r="B716" s="2"/>
       <c r="C716" s="2"/>
-      <c r="D716" s="2"/>
+      <c r="D716" s="50"/>
       <c r="E716" s="2"/>
       <c r="F716" s="2"/>
       <c r="G716" s="2"/>
@@ -22641,7 +22750,7 @@
       <c r="A717" s="2"/>
       <c r="B717" s="2"/>
       <c r="C717" s="2"/>
-      <c r="D717" s="2"/>
+      <c r="D717" s="50"/>
       <c r="E717" s="2"/>
       <c r="F717" s="2"/>
       <c r="G717" s="2"/>
@@ -22669,7 +22778,7 @@
       <c r="A718" s="2"/>
       <c r="B718" s="2"/>
       <c r="C718" s="2"/>
-      <c r="D718" s="2"/>
+      <c r="D718" s="50"/>
       <c r="E718" s="2"/>
       <c r="F718" s="2"/>
       <c r="G718" s="2"/>
@@ -22697,7 +22806,7 @@
       <c r="A719" s="2"/>
       <c r="B719" s="2"/>
       <c r="C719" s="2"/>
-      <c r="D719" s="2"/>
+      <c r="D719" s="50"/>
       <c r="E719" s="2"/>
       <c r="F719" s="2"/>
       <c r="G719" s="2"/>
@@ -22725,7 +22834,7 @@
       <c r="A720" s="2"/>
       <c r="B720" s="2"/>
       <c r="C720" s="2"/>
-      <c r="D720" s="2"/>
+      <c r="D720" s="50"/>
       <c r="E720" s="2"/>
       <c r="F720" s="2"/>
       <c r="G720" s="2"/>
@@ -22753,7 +22862,7 @@
       <c r="A721" s="2"/>
       <c r="B721" s="2"/>
       <c r="C721" s="2"/>
-      <c r="D721" s="2"/>
+      <c r="D721" s="50"/>
       <c r="E721" s="2"/>
       <c r="F721" s="2"/>
       <c r="G721" s="2"/>
@@ -22781,7 +22890,7 @@
       <c r="A722" s="2"/>
       <c r="B722" s="2"/>
       <c r="C722" s="2"/>
-      <c r="D722" s="2"/>
+      <c r="D722" s="50"/>
       <c r="E722" s="2"/>
       <c r="F722" s="2"/>
       <c r="G722" s="2"/>
@@ -22809,7 +22918,7 @@
       <c r="A723" s="2"/>
       <c r="B723" s="2"/>
       <c r="C723" s="2"/>
-      <c r="D723" s="2"/>
+      <c r="D723" s="50"/>
       <c r="E723" s="2"/>
       <c r="F723" s="2"/>
       <c r="G723" s="2"/>
@@ -22837,7 +22946,7 @@
       <c r="A724" s="2"/>
       <c r="B724" s="2"/>
       <c r="C724" s="2"/>
-      <c r="D724" s="2"/>
+      <c r="D724" s="50"/>
       <c r="E724" s="2"/>
       <c r="F724" s="2"/>
       <c r="G724" s="2"/>
@@ -22865,7 +22974,7 @@
       <c r="A725" s="2"/>
       <c r="B725" s="2"/>
       <c r="C725" s="2"/>
-      <c r="D725" s="2"/>
+      <c r="D725" s="50"/>
       <c r="E725" s="2"/>
       <c r="F725" s="2"/>
       <c r="G725" s="2"/>
@@ -22893,7 +23002,7 @@
       <c r="A726" s="2"/>
       <c r="B726" s="2"/>
       <c r="C726" s="2"/>
-      <c r="D726" s="2"/>
+      <c r="D726" s="50"/>
       <c r="E726" s="2"/>
       <c r="F726" s="2"/>
       <c r="G726" s="2"/>
@@ -22921,7 +23030,7 @@
       <c r="A727" s="2"/>
       <c r="B727" s="2"/>
       <c r="C727" s="2"/>
-      <c r="D727" s="2"/>
+      <c r="D727" s="50"/>
       <c r="E727" s="2"/>
       <c r="F727" s="2"/>
       <c r="G727" s="2"/>
@@ -22949,7 +23058,7 @@
       <c r="A728" s="2"/>
       <c r="B728" s="2"/>
       <c r="C728" s="2"/>
-      <c r="D728" s="2"/>
+      <c r="D728" s="50"/>
       <c r="E728" s="2"/>
       <c r="F728" s="2"/>
       <c r="G728" s="2"/>
@@ -22977,7 +23086,7 @@
       <c r="A729" s="2"/>
       <c r="B729" s="2"/>
       <c r="C729" s="2"/>
-      <c r="D729" s="2"/>
+      <c r="D729" s="50"/>
       <c r="E729" s="2"/>
       <c r="F729" s="2"/>
       <c r="G729" s="2"/>
@@ -23005,7 +23114,7 @@
       <c r="A730" s="2"/>
       <c r="B730" s="2"/>
       <c r="C730" s="2"/>
-      <c r="D730" s="2"/>
+      <c r="D730" s="50"/>
       <c r="E730" s="2"/>
       <c r="F730" s="2"/>
       <c r="G730" s="2"/>
@@ -23033,7 +23142,7 @@
       <c r="A731" s="2"/>
       <c r="B731" s="2"/>
       <c r="C731" s="2"/>
-      <c r="D731" s="2"/>
+      <c r="D731" s="50"/>
       <c r="E731" s="2"/>
       <c r="F731" s="2"/>
       <c r="G731" s="2"/>
@@ -23061,7 +23170,7 @@
       <c r="A732" s="2"/>
       <c r="B732" s="2"/>
       <c r="C732" s="2"/>
-      <c r="D732" s="2"/>
+      <c r="D732" s="50"/>
       <c r="E732" s="2"/>
       <c r="F732" s="2"/>
       <c r="G732" s="2"/>
@@ -23089,7 +23198,7 @@
       <c r="A733" s="2"/>
       <c r="B733" s="2"/>
       <c r="C733" s="2"/>
-      <c r="D733" s="2"/>
+      <c r="D733" s="50"/>
       <c r="E733" s="2"/>
       <c r="F733" s="2"/>
       <c r="G733" s="2"/>
@@ -23117,7 +23226,7 @@
       <c r="A734" s="2"/>
       <c r="B734" s="2"/>
       <c r="C734" s="2"/>
-      <c r="D734" s="2"/>
+      <c r="D734" s="50"/>
       <c r="E734" s="2"/>
       <c r="F734" s="2"/>
       <c r="G734" s="2"/>
@@ -23145,7 +23254,7 @@
       <c r="A735" s="2"/>
       <c r="B735" s="2"/>
       <c r="C735" s="2"/>
-      <c r="D735" s="2"/>
+      <c r="D735" s="50"/>
       <c r="E735" s="2"/>
       <c r="F735" s="2"/>
       <c r="G735" s="2"/>
@@ -23173,7 +23282,7 @@
       <c r="A736" s="2"/>
       <c r="B736" s="2"/>
       <c r="C736" s="2"/>
-      <c r="D736" s="2"/>
+      <c r="D736" s="50"/>
       <c r="E736" s="2"/>
       <c r="F736" s="2"/>
       <c r="G736" s="2"/>
@@ -23201,7 +23310,7 @@
       <c r="A737" s="2"/>
       <c r="B737" s="2"/>
       <c r="C737" s="2"/>
-      <c r="D737" s="2"/>
+      <c r="D737" s="50"/>
       <c r="E737" s="2"/>
       <c r="F737" s="2"/>
       <c r="G737" s="2"/>
@@ -23229,7 +23338,7 @@
       <c r="A738" s="2"/>
       <c r="B738" s="2"/>
       <c r="C738" s="2"/>
-      <c r="D738" s="2"/>
+      <c r="D738" s="50"/>
       <c r="E738" s="2"/>
       <c r="F738" s="2"/>
       <c r="G738" s="2"/>
@@ -23257,7 +23366,7 @@
       <c r="A739" s="2"/>
       <c r="B739" s="2"/>
       <c r="C739" s="2"/>
-      <c r="D739" s="2"/>
+      <c r="D739" s="50"/>
       <c r="E739" s="2"/>
       <c r="F739" s="2"/>
       <c r="G739" s="2"/>
@@ -23285,7 +23394,7 @@
       <c r="A740" s="2"/>
       <c r="B740" s="2"/>
       <c r="C740" s="2"/>
-      <c r="D740" s="2"/>
+      <c r="D740" s="50"/>
       <c r="E740" s="2"/>
       <c r="F740" s="2"/>
       <c r="G740" s="2"/>
@@ -23313,7 +23422,7 @@
       <c r="A741" s="2"/>
       <c r="B741" s="2"/>
       <c r="C741" s="2"/>
-      <c r="D741" s="2"/>
+      <c r="D741" s="50"/>
       <c r="E741" s="2"/>
       <c r="F741" s="2"/>
       <c r="G741" s="2"/>
@@ -23341,7 +23450,7 @@
       <c r="A742" s="2"/>
       <c r="B742" s="2"/>
       <c r="C742" s="2"/>
-      <c r="D742" s="2"/>
+      <c r="D742" s="50"/>
       <c r="E742" s="2"/>
       <c r="F742" s="2"/>
       <c r="G742" s="2"/>
@@ -23369,7 +23478,7 @@
       <c r="A743" s="2"/>
       <c r="B743" s="2"/>
       <c r="C743" s="2"/>
-      <c r="D743" s="2"/>
+      <c r="D743" s="50"/>
       <c r="E743" s="2"/>
       <c r="F743" s="2"/>
       <c r="G743" s="2"/>
@@ -23397,7 +23506,7 @@
       <c r="A744" s="2"/>
       <c r="B744" s="2"/>
       <c r="C744" s="2"/>
-      <c r="D744" s="2"/>
+      <c r="D744" s="50"/>
       <c r="E744" s="2"/>
       <c r="F744" s="2"/>
       <c r="G744" s="2"/>
@@ -23425,7 +23534,7 @@
       <c r="A745" s="2"/>
       <c r="B745" s="2"/>
       <c r="C745" s="2"/>
-      <c r="D745" s="2"/>
+      <c r="D745" s="50"/>
       <c r="E745" s="2"/>
       <c r="F745" s="2"/>
       <c r="G745" s="2"/>
@@ -23453,7 +23562,7 @@
       <c r="A746" s="2"/>
       <c r="B746" s="2"/>
       <c r="C746" s="2"/>
-      <c r="D746" s="2"/>
+      <c r="D746" s="50"/>
       <c r="E746" s="2"/>
       <c r="F746" s="2"/>
       <c r="G746" s="2"/>
@@ -23481,7 +23590,7 @@
       <c r="A747" s="2"/>
       <c r="B747" s="2"/>
       <c r="C747" s="2"/>
-      <c r="D747" s="2"/>
+      <c r="D747" s="50"/>
       <c r="E747" s="2"/>
       <c r="F747" s="2"/>
       <c r="G747" s="2"/>
@@ -23509,7 +23618,7 @@
       <c r="A748" s="2"/>
       <c r="B748" s="2"/>
       <c r="C748" s="2"/>
-      <c r="D748" s="2"/>
+      <c r="D748" s="50"/>
       <c r="E748" s="2"/>
       <c r="F748" s="2"/>
       <c r="G748" s="2"/>
@@ -23537,7 +23646,7 @@
       <c r="A749" s="2"/>
       <c r="B749" s="2"/>
       <c r="C749" s="2"/>
-      <c r="D749" s="2"/>
+      <c r="D749" s="50"/>
       <c r="E749" s="2"/>
       <c r="F749" s="2"/>
       <c r="G749" s="2"/>
@@ -23565,7 +23674,7 @@
       <c r="A750" s="2"/>
       <c r="B750" s="2"/>
       <c r="C750" s="2"/>
-      <c r="D750" s="2"/>
+      <c r="D750" s="50"/>
       <c r="E750" s="2"/>
       <c r="F750" s="2"/>
       <c r="G750" s="2"/>
@@ -23593,7 +23702,7 @@
       <c r="A751" s="2"/>
       <c r="B751" s="2"/>
       <c r="C751" s="2"/>
-      <c r="D751" s="2"/>
+      <c r="D751" s="50"/>
       <c r="E751" s="2"/>
       <c r="F751" s="2"/>
       <c r="G751" s="2"/>
@@ -23621,7 +23730,7 @@
       <c r="A752" s="2"/>
       <c r="B752" s="2"/>
       <c r="C752" s="2"/>
-      <c r="D752" s="2"/>
+      <c r="D752" s="50"/>
       <c r="E752" s="2"/>
       <c r="F752" s="2"/>
       <c r="G752" s="2"/>
@@ -23649,7 +23758,7 @@
       <c r="A753" s="2"/>
       <c r="B753" s="2"/>
       <c r="C753" s="2"/>
-      <c r="D753" s="2"/>
+      <c r="D753" s="50"/>
       <c r="E753" s="2"/>
       <c r="F753" s="2"/>
       <c r="G753" s="2"/>
@@ -23677,7 +23786,7 @@
       <c r="A754" s="2"/>
       <c r="B754" s="2"/>
       <c r="C754" s="2"/>
-      <c r="D754" s="2"/>
+      <c r="D754" s="50"/>
       <c r="E754" s="2"/>
       <c r="F754" s="2"/>
       <c r="G754" s="2"/>
@@ -23705,7 +23814,7 @@
       <c r="A755" s="2"/>
       <c r="B755" s="2"/>
       <c r="C755" s="2"/>
-      <c r="D755" s="2"/>
+      <c r="D755" s="50"/>
       <c r="E755" s="2"/>
       <c r="F755" s="2"/>
       <c r="G755" s="2"/>
@@ -23733,7 +23842,7 @@
       <c r="A756" s="2"/>
       <c r="B756" s="2"/>
       <c r="C756" s="2"/>
-      <c r="D756" s="2"/>
+      <c r="D756" s="50"/>
       <c r="E756" s="2"/>
       <c r="F756" s="2"/>
       <c r="G756" s="2"/>
@@ -23761,7 +23870,7 @@
       <c r="A757" s="2"/>
       <c r="B757" s="2"/>
       <c r="C757" s="2"/>
-      <c r="D757" s="2"/>
+      <c r="D757" s="50"/>
       <c r="E757" s="2"/>
       <c r="F757" s="2"/>
       <c r="G757" s="2"/>
@@ -23789,7 +23898,7 @@
       <c r="A758" s="2"/>
       <c r="B758" s="2"/>
       <c r="C758" s="2"/>
-      <c r="D758" s="2"/>
+      <c r="D758" s="50"/>
       <c r="E758" s="2"/>
       <c r="F758" s="2"/>
       <c r="G758" s="2"/>
@@ -23817,7 +23926,7 @@
       <c r="A759" s="2"/>
       <c r="B759" s="2"/>
       <c r="C759" s="2"/>
-      <c r="D759" s="2"/>
+      <c r="D759" s="50"/>
       <c r="E759" s="2"/>
       <c r="F759" s="2"/>
       <c r="G759" s="2"/>
@@ -23845,7 +23954,7 @@
       <c r="A760" s="2"/>
       <c r="B760" s="2"/>
       <c r="C760" s="2"/>
-      <c r="D760" s="2"/>
+      <c r="D760" s="50"/>
       <c r="E760" s="2"/>
       <c r="F760" s="2"/>
       <c r="G760" s="2"/>
@@ -23873,7 +23982,7 @@
       <c r="A761" s="2"/>
       <c r="B761" s="2"/>
       <c r="C761" s="2"/>
-      <c r="D761" s="2"/>
+      <c r="D761" s="50"/>
       <c r="E761" s="2"/>
       <c r="F761" s="2"/>
       <c r="G761" s="2"/>
@@ -23901,7 +24010,7 @@
       <c r="A762" s="2"/>
       <c r="B762" s="2"/>
       <c r="C762" s="2"/>
-      <c r="D762" s="2"/>
+      <c r="D762" s="50"/>
       <c r="E762" s="2"/>
       <c r="F762" s="2"/>
       <c r="G762" s="2"/>
@@ -23929,7 +24038,7 @@
       <c r="A763" s="2"/>
       <c r="B763" s="2"/>
       <c r="C763" s="2"/>
-      <c r="D763" s="2"/>
+      <c r="D763" s="50"/>
       <c r="E763" s="2"/>
       <c r="F763" s="2"/>
       <c r="G763" s="2"/>
@@ -23957,7 +24066,7 @@
       <c r="A764" s="2"/>
       <c r="B764" s="2"/>
       <c r="C764" s="2"/>
-      <c r="D764" s="2"/>
+      <c r="D764" s="50"/>
       <c r="E764" s="2"/>
       <c r="F764" s="2"/>
       <c r="G764" s="2"/>
@@ -23985,7 +24094,7 @@
       <c r="A765" s="2"/>
       <c r="B765" s="2"/>
       <c r="C765" s="2"/>
-      <c r="D765" s="2"/>
+      <c r="D765" s="50"/>
       <c r="E765" s="2"/>
       <c r="F765" s="2"/>
       <c r="G765" s="2"/>
@@ -24013,7 +24122,7 @@
       <c r="A766" s="2"/>
       <c r="B766" s="2"/>
       <c r="C766" s="2"/>
-      <c r="D766" s="2"/>
+      <c r="D766" s="50"/>
       <c r="E766" s="2"/>
       <c r="F766" s="2"/>
       <c r="G766" s="2"/>
@@ -24041,7 +24150,7 @@
       <c r="A767" s="2"/>
       <c r="B767" s="2"/>
       <c r="C767" s="2"/>
-      <c r="D767" s="2"/>
+      <c r="D767" s="50"/>
       <c r="E767" s="2"/>
       <c r="F767" s="2"/>
       <c r="G767" s="2"/>
@@ -24069,7 +24178,7 @@
       <c r="A768" s="2"/>
       <c r="B768" s="2"/>
       <c r="C768" s="2"/>
-      <c r="D768" s="2"/>
+      <c r="D768" s="50"/>
       <c r="E768" s="2"/>
       <c r="F768" s="2"/>
       <c r="G768" s="2"/>
@@ -24097,7 +24206,7 @@
       <c r="A769" s="2"/>
       <c r="B769" s="2"/>
       <c r="C769" s="2"/>
-      <c r="D769" s="2"/>
+      <c r="D769" s="50"/>
       <c r="E769" s="2"/>
       <c r="F769" s="2"/>
       <c r="G769" s="2"/>
@@ -24125,7 +24234,7 @@
       <c r="A770" s="2"/>
       <c r="B770" s="2"/>
       <c r="C770" s="2"/>
-      <c r="D770" s="2"/>
+      <c r="D770" s="50"/>
       <c r="E770" s="2"/>
       <c r="F770" s="2"/>
       <c r="G770" s="2"/>
@@ -24153,7 +24262,7 @@
       <c r="A771" s="2"/>
       <c r="B771" s="2"/>
       <c r="C771" s="2"/>
-      <c r="D771" s="2"/>
+      <c r="D771" s="50"/>
       <c r="E771" s="2"/>
       <c r="F771" s="2"/>
       <c r="G771" s="2"/>
@@ -24181,7 +24290,7 @@
       <c r="A772" s="2"/>
       <c r="B772" s="2"/>
       <c r="C772" s="2"/>
-      <c r="D772" s="2"/>
+      <c r="D772" s="50"/>
       <c r="E772" s="2"/>
       <c r="F772" s="2"/>
       <c r="G772" s="2"/>
@@ -24209,7 +24318,7 @@
       <c r="A773" s="2"/>
       <c r="B773" s="2"/>
       <c r="C773" s="2"/>
-      <c r="D773" s="2"/>
+      <c r="D773" s="50"/>
       <c r="E773" s="2"/>
       <c r="F773" s="2"/>
       <c r="G773" s="2"/>
@@ -24237,7 +24346,7 @@
       <c r="A774" s="2"/>
       <c r="B774" s="2"/>
       <c r="C774" s="2"/>
-      <c r="D774" s="2"/>
+      <c r="D774" s="50"/>
       <c r="E774" s="2"/>
       <c r="F774" s="2"/>
       <c r="G774" s="2"/>
@@ -24265,7 +24374,7 @@
       <c r="A775" s="2"/>
       <c r="B775" s="2"/>
       <c r="C775" s="2"/>
-      <c r="D775" s="2"/>
+      <c r="D775" s="50"/>
       <c r="E775" s="2"/>
       <c r="F775" s="2"/>
       <c r="G775" s="2"/>
@@ -24293,7 +24402,7 @@
       <c r="A776" s="2"/>
       <c r="B776" s="2"/>
       <c r="C776" s="2"/>
-      <c r="D776" s="2"/>
+      <c r="D776" s="50"/>
       <c r="E776" s="2"/>
       <c r="F776" s="2"/>
       <c r="G776" s="2"/>
@@ -24321,7 +24430,7 @@
       <c r="A777" s="2"/>
       <c r="B777" s="2"/>
       <c r="C777" s="2"/>
-      <c r="D777" s="2"/>
+      <c r="D777" s="50"/>
       <c r="E777" s="2"/>
       <c r="F777" s="2"/>
       <c r="G777" s="2"/>
@@ -24349,7 +24458,7 @@
       <c r="A778" s="2"/>
       <c r="B778" s="2"/>
       <c r="C778" s="2"/>
-      <c r="D778" s="2"/>
+      <c r="D778" s="50"/>
       <c r="E778" s="2"/>
       <c r="F778" s="2"/>
       <c r="G778" s="2"/>
@@ -24377,7 +24486,7 @@
       <c r="A779" s="2"/>
       <c r="B779" s="2"/>
       <c r="C779" s="2"/>
-      <c r="D779" s="2"/>
+      <c r="D779" s="50"/>
       <c r="E779" s="2"/>
       <c r="F779" s="2"/>
       <c r="G779" s="2"/>
@@ -24405,7 +24514,7 @@
       <c r="A780" s="2"/>
       <c r="B780" s="2"/>
       <c r="C780" s="2"/>
-      <c r="D780" s="2"/>
+      <c r="D780" s="50"/>
       <c r="E780" s="2"/>
       <c r="F780" s="2"/>
       <c r="G780" s="2"/>
@@ -24433,7 +24542,7 @@
       <c r="A781" s="2"/>
       <c r="B781" s="2"/>
       <c r="C781" s="2"/>
-      <c r="D781" s="2"/>
+      <c r="D781" s="50"/>
       <c r="E781" s="2"/>
       <c r="F781" s="2"/>
       <c r="G781" s="2"/>
@@ -24461,7 +24570,7 @@
       <c r="A782" s="2"/>
       <c r="B782" s="2"/>
       <c r="C782" s="2"/>
-      <c r="D782" s="2"/>
+      <c r="D782" s="50"/>
       <c r="E782" s="2"/>
       <c r="F782" s="2"/>
       <c r="G782" s="2"/>
@@ -24489,7 +24598,7 @@
       <c r="A783" s="2"/>
       <c r="B783" s="2"/>
       <c r="C783" s="2"/>
-      <c r="D783" s="2"/>
+      <c r="D783" s="50"/>
       <c r="E783" s="2"/>
       <c r="F783" s="2"/>
       <c r="G783" s="2"/>
@@ -24517,7 +24626,7 @@
       <c r="A784" s="2"/>
       <c r="B784" s="2"/>
       <c r="C784" s="2"/>
-      <c r="D784" s="2"/>
+      <c r="D784" s="50"/>
       <c r="E784" s="2"/>
       <c r="F784" s="2"/>
       <c r="G784" s="2"/>
@@ -24545,7 +24654,7 @@
       <c r="A785" s="2"/>
       <c r="B785" s="2"/>
       <c r="C785" s="2"/>
-      <c r="D785" s="2"/>
+      <c r="D785" s="50"/>
       <c r="E785" s="2"/>
       <c r="F785" s="2"/>
       <c r="G785" s="2"/>
@@ -24573,7 +24682,7 @@
       <c r="A786" s="2"/>
       <c r="B786" s="2"/>
       <c r="C786" s="2"/>
-      <c r="D786" s="2"/>
+      <c r="D786" s="50"/>
       <c r="E786" s="2"/>
       <c r="F786" s="2"/>
       <c r="G786" s="2"/>
@@ -24601,7 +24710,7 @@
       <c r="A787" s="2"/>
       <c r="B787" s="2"/>
       <c r="C787" s="2"/>
-      <c r="D787" s="2"/>
+      <c r="D787" s="50"/>
       <c r="E787" s="2"/>
       <c r="F787" s="2"/>
       <c r="G787" s="2"/>
@@ -24629,7 +24738,7 @@
       <c r="A788" s="2"/>
       <c r="B788" s="2"/>
       <c r="C788" s="2"/>
-      <c r="D788" s="2"/>
+      <c r="D788" s="50"/>
       <c r="E788" s="2"/>
       <c r="F788" s="2"/>
       <c r="G788" s="2"/>
@@ -24657,7 +24766,7 @@
       <c r="A789" s="2"/>
       <c r="B789" s="2"/>
       <c r="C789" s="2"/>
-      <c r="D789" s="2"/>
+      <c r="D789" s="50"/>
       <c r="E789" s="2"/>
       <c r="F789" s="2"/>
       <c r="G789" s="2"/>
@@ -24685,7 +24794,7 @@
       <c r="A790" s="2"/>
       <c r="B790" s="2"/>
       <c r="C790" s="2"/>
-      <c r="D790" s="2"/>
+      <c r="D790" s="50"/>
       <c r="E790" s="2"/>
       <c r="F790" s="2"/>
       <c r="G790" s="2"/>
@@ -24713,7 +24822,7 @@
       <c r="A791" s="2"/>
       <c r="B791" s="2"/>
       <c r="C791" s="2"/>
-      <c r="D791" s="2"/>
+      <c r="D791" s="50"/>
       <c r="E791" s="2"/>
       <c r="F791" s="2"/>
       <c r="G791" s="2"/>
@@ -24741,7 +24850,7 @@
       <c r="A792" s="2"/>
       <c r="B792" s="2"/>
       <c r="C792" s="2"/>
-      <c r="D792" s="2"/>
+      <c r="D792" s="50"/>
       <c r="E792" s="2"/>
       <c r="F792" s="2"/>
       <c r="G792" s="2"/>
@@ -24769,7 +24878,7 @@
       <c r="A793" s="2"/>
       <c r="B793" s="2"/>
       <c r="C793" s="2"/>
-      <c r="D793" s="2"/>
+      <c r="D793" s="50"/>
       <c r="E793" s="2"/>
       <c r="F793" s="2"/>
       <c r="G793" s="2"/>
@@ -24797,7 +24906,7 @@
       <c r="A794" s="2"/>
       <c r="B794" s="2"/>
       <c r="C794" s="2"/>
-      <c r="D794" s="2"/>
+      <c r="D794" s="50"/>
       <c r="E794" s="2"/>
       <c r="F794" s="2"/>
       <c r="G794" s="2"/>
@@ -24825,7 +24934,7 @@
       <c r="A795" s="2"/>
       <c r="B795" s="2"/>
       <c r="C795" s="2"/>
-      <c r="D795" s="2"/>
+      <c r="D795" s="50"/>
       <c r="E795" s="2"/>
       <c r="F795" s="2"/>
       <c r="G795" s="2"/>
@@ -24853,7 +24962,7 @@
       <c r="A796" s="2"/>
       <c r="B796" s="2"/>
       <c r="C796" s="2"/>
-      <c r="D796" s="2"/>
+      <c r="D796" s="50"/>
       <c r="E796" s="2"/>
       <c r="F796" s="2"/>
       <c r="G796" s="2"/>
@@ -24881,7 +24990,7 @@
       <c r="A797" s="2"/>
       <c r="B797" s="2"/>
       <c r="C797" s="2"/>
-      <c r="D797" s="2"/>
+      <c r="D797" s="50"/>
       <c r="E797" s="2"/>
       <c r="F797" s="2"/>
       <c r="G797" s="2"/>
@@ -24909,7 +25018,7 @@
       <c r="A798" s="2"/>
       <c r="B798" s="2"/>
       <c r="C798" s="2"/>
-      <c r="D798" s="2"/>
+      <c r="D798" s="50"/>
       <c r="E798" s="2"/>
       <c r="F798" s="2"/>
       <c r="G798" s="2"/>
@@ -24937,7 +25046,7 @@
       <c r="A799" s="2"/>
       <c r="B799" s="2"/>
       <c r="C799" s="2"/>
-      <c r="D799" s="2"/>
+      <c r="D799" s="50"/>
       <c r="E799" s="2"/>
       <c r="F799" s="2"/>
       <c r="G799" s="2"/>
@@ -24965,7 +25074,7 @@
       <c r="A800" s="2"/>
       <c r="B800" s="2"/>
       <c r="C800" s="2"/>
-      <c r="D800" s="2"/>
+      <c r="D800" s="50"/>
       <c r="E800" s="2"/>
       <c r="F800" s="2"/>
       <c r="G800" s="2"/>
@@ -24993,7 +25102,7 @@
       <c r="A801" s="2"/>
       <c r="B801" s="2"/>
       <c r="C801" s="2"/>
-      <c r="D801" s="2"/>
+      <c r="D801" s="50"/>
       <c r="E801" s="2"/>
       <c r="F801" s="2"/>
       <c r="G801" s="2"/>
@@ -25021,7 +25130,7 @@
       <c r="A802" s="2"/>
       <c r="B802" s="2"/>
       <c r="C802" s="2"/>
-      <c r="D802" s="2"/>
+      <c r="D802" s="50"/>
       <c r="E802" s="2"/>
       <c r="F802" s="2"/>
       <c r="G802" s="2"/>
@@ -25049,7 +25158,7 @@
       <c r="A803" s="2"/>
       <c r="B803" s="2"/>
       <c r="C803" s="2"/>
-      <c r="D803" s="2"/>
+      <c r="D803" s="50"/>
       <c r="E803" s="2"/>
       <c r="F803" s="2"/>
       <c r="G803" s="2"/>
@@ -25077,7 +25186,7 @@
       <c r="A804" s="2"/>
       <c r="B804" s="2"/>
       <c r="C804" s="2"/>
-      <c r="D804" s="2"/>
+      <c r="D804" s="50"/>
       <c r="E804" s="2"/>
       <c r="F804" s="2"/>
       <c r="G804" s="2"/>
@@ -25105,7 +25214,7 @@
       <c r="A805" s="2"/>
       <c r="B805" s="2"/>
       <c r="C805" s="2"/>
-      <c r="D805" s="2"/>
+      <c r="D805" s="50"/>
       <c r="E805" s="2"/>
       <c r="F805" s="2"/>
       <c r="G805" s="2"/>
@@ -25133,7 +25242,7 @@
       <c r="A806" s="2"/>
       <c r="B806" s="2"/>
       <c r="C806" s="2"/>
-      <c r="D806" s="2"/>
+      <c r="D806" s="50"/>
       <c r="E806" s="2"/>
       <c r="F806" s="2"/>
       <c r="G806" s="2"/>
@@ -25161,7 +25270,7 @@
       <c r="A807" s="2"/>
       <c r="B807" s="2"/>
       <c r="C807" s="2"/>
-      <c r="D807" s="2"/>
+      <c r="D807" s="50"/>
       <c r="E807" s="2"/>
       <c r="F807" s="2"/>
       <c r="G807" s="2"/>
@@ -25189,7 +25298,7 @@
       <c r="A808" s="2"/>
       <c r="B808" s="2"/>
       <c r="C808" s="2"/>
-      <c r="D808" s="2"/>
+      <c r="D808" s="50"/>
       <c r="E808" s="2"/>
       <c r="F808" s="2"/>
       <c r="G808" s="2"/>
@@ -25217,7 +25326,7 @@
       <c r="A809" s="2"/>
       <c r="B809" s="2"/>
       <c r="C809" s="2"/>
-      <c r="D809" s="2"/>
+      <c r="D809" s="50"/>
       <c r="E809" s="2"/>
       <c r="F809" s="2"/>
       <c r="G809" s="2"/>
@@ -25245,7 +25354,7 @@
       <c r="A810" s="2"/>
       <c r="B810" s="2"/>
       <c r="C810" s="2"/>
-      <c r="D810" s="2"/>
+      <c r="D810" s="50"/>
       <c r="E810" s="2"/>
       <c r="F810" s="2"/>
       <c r="G810" s="2"/>
@@ -25273,7 +25382,7 @@
       <c r="A811" s="2"/>
       <c r="B811" s="2"/>
       <c r="C811" s="2"/>
-      <c r="D811" s="2"/>
+      <c r="D811" s="50"/>
       <c r="E811" s="2"/>
       <c r="F811" s="2"/>
       <c r="G811" s="2"/>
@@ -25301,7 +25410,7 @@
       <c r="A812" s="2"/>
       <c r="B812" s="2"/>
       <c r="C812" s="2"/>
-      <c r="D812" s="2"/>
+      <c r="D812" s="50"/>
       <c r="E812" s="2"/>
       <c r="F812" s="2"/>
       <c r="G812" s="2"/>
@@ -25329,7 +25438,7 @@
       <c r="A813" s="2"/>
       <c r="B813" s="2"/>
       <c r="C813" s="2"/>
-      <c r="D813" s="2"/>
+      <c r="D813" s="50"/>
       <c r="E813" s="2"/>
       <c r="F813" s="2"/>
       <c r="G813" s="2"/>
@@ -25357,7 +25466,7 @@
       <c r="A814" s="2"/>
       <c r="B814" s="2"/>
       <c r="C814" s="2"/>
-      <c r="D814" s="2"/>
+      <c r="D814" s="50"/>
       <c r="E814" s="2"/>
       <c r="F814" s="2"/>
       <c r="G814" s="2"/>
@@ -25385,7 +25494,7 @@
       <c r="A815" s="2"/>
       <c r="B815" s="2"/>
       <c r="C815" s="2"/>
-      <c r="D815" s="2"/>
+      <c r="D815" s="50"/>
       <c r="E815" s="2"/>
       <c r="F815" s="2"/>
       <c r="G815" s="2"/>
@@ -25413,7 +25522,7 @@
       <c r="A816" s="2"/>
       <c r="B816" s="2"/>
       <c r="C816" s="2"/>
-      <c r="D816" s="2"/>
+      <c r="D816" s="50"/>
       <c r="E816" s="2"/>
       <c r="F816" s="2"/>
       <c r="G816" s="2"/>
@@ -25441,7 +25550,7 @@
       <c r="A817" s="2"/>
       <c r="B817" s="2"/>
       <c r="C817" s="2"/>
-      <c r="D817" s="2"/>
+      <c r="D817" s="50"/>
       <c r="E817" s="2"/>
       <c r="F817" s="2"/>
       <c r="G817" s="2"/>
@@ -25469,7 +25578,7 @@
       <c r="A818" s="2"/>
       <c r="B818" s="2"/>
       <c r="C818" s="2"/>
-      <c r="D818" s="2"/>
+      <c r="D818" s="50"/>
       <c r="E818" s="2"/>
       <c r="F818" s="2"/>
       <c r="G818" s="2"/>
@@ -25497,7 +25606,7 @@
       <c r="A819" s="2"/>
       <c r="B819" s="2"/>
       <c r="C819" s="2"/>
-      <c r="D819" s="2"/>
+      <c r="D819" s="50"/>
       <c r="E819" s="2"/>
       <c r="F819" s="2"/>
       <c r="G819" s="2"/>
@@ -25525,7 +25634,7 @@
       <c r="A820" s="2"/>
       <c r="B820" s="2"/>
       <c r="C820" s="2"/>
-      <c r="D820" s="2"/>
+      <c r="D820" s="50"/>
       <c r="E820" s="2"/>
       <c r="F820" s="2"/>
       <c r="G820" s="2"/>
@@ -25553,7 +25662,7 @@
       <c r="A821" s="2"/>
       <c r="B821" s="2"/>
       <c r="C821" s="2"/>
-      <c r="D821" s="2"/>
+      <c r="D821" s="50"/>
       <c r="E821" s="2"/>
       <c r="F821" s="2"/>
       <c r="G821" s="2"/>
@@ -25581,7 +25690,7 @@
       <c r="A822" s="2"/>
       <c r="B822" s="2"/>
       <c r="C822" s="2"/>
-      <c r="D822" s="2"/>
+      <c r="D822" s="50"/>
       <c r="E822" s="2"/>
       <c r="F822" s="2"/>
       <c r="G822" s="2"/>
@@ -25609,7 +25718,7 @@
       <c r="A823" s="2"/>
       <c r="B823" s="2"/>
       <c r="C823" s="2"/>
-      <c r="D823" s="2"/>
+      <c r="D823" s="50"/>
       <c r="E823" s="2"/>
       <c r="F823" s="2"/>
       <c r="G823" s="2"/>
@@ -25637,7 +25746,7 @@
       <c r="A824" s="2"/>
       <c r="B824" s="2"/>
       <c r="C824" s="2"/>
-      <c r="D824" s="2"/>
+      <c r="D824" s="50"/>
       <c r="E824" s="2"/>
       <c r="F824" s="2"/>
       <c r="G824" s="2"/>
@@ -25665,7 +25774,7 @@
       <c r="A825" s="2"/>
       <c r="B825" s="2"/>
       <c r="C825" s="2"/>
-      <c r="D825" s="2"/>
+      <c r="D825" s="50"/>
       <c r="E825" s="2"/>
       <c r="F825" s="2"/>
       <c r="G825" s="2"/>
@@ -25693,7 +25802,7 @@
       <c r="A826" s="2"/>
       <c r="B826" s="2"/>
       <c r="C826" s="2"/>
-      <c r="D826" s="2"/>
+      <c r="D826" s="50"/>
       <c r="E826" s="2"/>
       <c r="F826" s="2"/>
       <c r="G826" s="2"/>
@@ -25721,7 +25830,7 @@
       <c r="A827" s="2"/>
       <c r="B827" s="2"/>
       <c r="C827" s="2"/>
-      <c r="D827" s="2"/>
+      <c r="D827" s="50"/>
       <c r="E827" s="2"/>
       <c r="F827" s="2"/>
       <c r="G827" s="2"/>
@@ -25749,7 +25858,7 @@
       <c r="A828" s="2"/>
       <c r="B828" s="2"/>
       <c r="C828" s="2"/>
-      <c r="D828" s="2"/>
+      <c r="D828" s="50"/>
       <c r="E828" s="2"/>
       <c r="F828" s="2"/>
       <c r="G828" s="2"/>
@@ -25777,7 +25886,7 @@
       <c r="A829" s="2"/>
       <c r="B829" s="2"/>
       <c r="C829" s="2"/>
-      <c r="D829" s="2"/>
+      <c r="D829" s="50"/>
       <c r="E829" s="2"/>
       <c r="F829" s="2"/>
       <c r="G829" s="2"/>
@@ -25805,7 +25914,7 @@
       <c r="A830" s="2"/>
       <c r="B830" s="2"/>
       <c r="C830" s="2"/>
-      <c r="D830" s="2"/>
+      <c r="D830" s="50"/>
       <c r="E830" s="2"/>
       <c r="F830" s="2"/>
       <c r="G830" s="2"/>
@@ -25833,7 +25942,7 @@
       <c r="A831" s="2"/>
       <c r="B831" s="2"/>
       <c r="C831" s="2"/>
-      <c r="D831" s="2"/>
+      <c r="D831" s="50"/>
       <c r="E831" s="2"/>
       <c r="F831" s="2"/>
       <c r="G831" s="2"/>
@@ -25861,7 +25970,7 @@
       <c r="A832" s="2"/>
       <c r="B832" s="2"/>
       <c r="C832" s="2"/>
-      <c r="D832" s="2"/>
+      <c r="D832" s="50"/>
       <c r="E832" s="2"/>
       <c r="F832" s="2"/>
       <c r="G832" s="2"/>
@@ -25889,7 +25998,7 @@
       <c r="A833" s="2"/>
       <c r="B833" s="2"/>
       <c r="C833" s="2"/>
-      <c r="D833" s="2"/>
+      <c r="D833" s="50"/>
       <c r="E833" s="2"/>
       <c r="F833" s="2"/>
       <c r="G833" s="2"/>
@@ -25917,7 +26026,7 @@
       <c r="A834" s="2"/>
       <c r="B834" s="2"/>
       <c r="C834" s="2"/>
-      <c r="D834" s="2"/>
+      <c r="D834" s="50"/>
       <c r="E834" s="2"/>
       <c r="F834" s="2"/>
       <c r="G834" s="2"/>
@@ -25945,7 +26054,7 @@
       <c r="A835" s="2"/>
       <c r="B835" s="2"/>
       <c r="C835" s="2"/>
-      <c r="D835" s="2"/>
+      <c r="D835" s="50"/>
       <c r="E835" s="2"/>
       <c r="F835" s="2"/>
       <c r="G835" s="2"/>
@@ -25973,7 +26082,7 @@
       <c r="A836" s="2"/>
       <c r="B836" s="2"/>
       <c r="C836" s="2"/>
-      <c r="D836" s="2"/>
+      <c r="D836" s="50"/>
       <c r="E836" s="2"/>
       <c r="F836" s="2"/>
       <c r="G836" s="2"/>
@@ -26001,7 +26110,7 @@
       <c r="A837" s="2"/>
       <c r="B837" s="2"/>
       <c r="C837" s="2"/>
-      <c r="D837" s="2"/>
+      <c r="D837" s="50"/>
       <c r="E837" s="2"/>
       <c r="F837" s="2"/>
       <c r="G837" s="2"/>
@@ -26029,7 +26138,7 @@
       <c r="A838" s="2"/>
       <c r="B838" s="2"/>
       <c r="C838" s="2"/>
-      <c r="D838" s="2"/>
+      <c r="D838" s="50"/>
       <c r="E838" s="2"/>
       <c r="F838" s="2"/>
       <c r="G838" s="2"/>
@@ -26057,7 +26166,7 @@
       <c r="A839" s="2"/>
       <c r="B839" s="2"/>
       <c r="C839" s="2"/>
-      <c r="D839" s="2"/>
+      <c r="D839" s="50"/>
       <c r="E839" s="2"/>
       <c r="F839" s="2"/>
       <c r="G839" s="2"/>
@@ -26085,7 +26194,7 @@
       <c r="A840" s="2"/>
       <c r="B840" s="2"/>
       <c r="C840" s="2"/>
-      <c r="D840" s="2"/>
+      <c r="D840" s="50"/>
       <c r="E840" s="2"/>
       <c r="F840" s="2"/>
       <c r="G840" s="2"/>
@@ -26113,7 +26222,7 @@
       <c r="A841" s="2"/>
       <c r="B841" s="2"/>
       <c r="C841" s="2"/>
-      <c r="D841" s="2"/>
+      <c r="D841" s="50"/>
       <c r="E841" s="2"/>
       <c r="F841" s="2"/>
       <c r="G841" s="2"/>
@@ -26141,7 +26250,7 @@
       <c r="A842" s="2"/>
       <c r="B842" s="2"/>
       <c r="C842" s="2"/>
-      <c r="D842" s="2"/>
+      <c r="D842" s="50"/>
       <c r="E842" s="2"/>
       <c r="F842" s="2"/>
       <c r="G842" s="2"/>
@@ -26169,7 +26278,7 @@
       <c r="A843" s="2"/>
       <c r="B843" s="2"/>
       <c r="C843" s="2"/>
-      <c r="D843" s="2"/>
+      <c r="D843" s="50"/>
       <c r="E843" s="2"/>
       <c r="F843" s="2"/>
       <c r="G843" s="2"/>
@@ -26197,7 +26306,7 @@
       <c r="A844" s="2"/>
       <c r="B844" s="2"/>
       <c r="C844" s="2"/>
-      <c r="D844" s="2"/>
+      <c r="D844" s="50"/>
       <c r="E844" s="2"/>
       <c r="F844" s="2"/>
       <c r="G844" s="2"/>
@@ -26225,7 +26334,7 @@
       <c r="A845" s="2"/>
       <c r="B845" s="2"/>
       <c r="C845" s="2"/>
-      <c r="D845" s="2"/>
+      <c r="D845" s="50"/>
       <c r="E845" s="2"/>
       <c r="F845" s="2"/>
       <c r="G845" s="2"/>
@@ -26253,7 +26362,7 @@
       <c r="A846" s="2"/>
       <c r="B846" s="2"/>
       <c r="C846" s="2"/>
-      <c r="D846" s="2"/>
+      <c r="D846" s="50"/>
       <c r="E846" s="2"/>
       <c r="F846" s="2"/>
       <c r="G846" s="2"/>
@@ -26281,7 +26390,7 @@
       <c r="A847" s="2"/>
       <c r="B847" s="2"/>
       <c r="C847" s="2"/>
-      <c r="D847" s="2"/>
+      <c r="D847" s="50"/>
       <c r="E847" s="2"/>
       <c r="F847" s="2"/>
       <c r="G847" s="2"/>
@@ -26309,7 +26418,7 @@
       <c r="A848" s="2"/>
       <c r="B848" s="2"/>
       <c r="C848" s="2"/>
-      <c r="D848" s="2"/>
+      <c r="D848" s="50"/>
       <c r="E848" s="2"/>
       <c r="F848" s="2"/>
       <c r="G848" s="2"/>
@@ -26337,7 +26446,7 @@
       <c r="A849" s="2"/>
       <c r="B849" s="2"/>
       <c r="C849" s="2"/>
-      <c r="D849" s="2"/>
+      <c r="D849" s="50"/>
       <c r="E849" s="2"/>
       <c r="F849" s="2"/>
       <c r="G849" s="2"/>
@@ -26365,7 +26474,7 @@
       <c r="A850" s="2"/>
       <c r="B850" s="2"/>
       <c r="C850" s="2"/>
-      <c r="D850" s="2"/>
+      <c r="D850" s="50"/>
       <c r="E850" s="2"/>
       <c r="F850" s="2"/>
       <c r="G850" s="2"/>
@@ -26393,7 +26502,7 @@
       <c r="A851" s="2"/>
       <c r="B851" s="2"/>
       <c r="C851" s="2"/>
-      <c r="D851" s="2"/>
+      <c r="D851" s="50"/>
       <c r="E851" s="2"/>
       <c r="F851" s="2"/>
       <c r="G851" s="2"/>
@@ -26421,7 +26530,7 @@
       <c r="A852" s="2"/>
       <c r="B852" s="2"/>
       <c r="C852" s="2"/>
-      <c r="D852" s="2"/>
+      <c r="D852" s="50"/>
       <c r="E852" s="2"/>
       <c r="F852" s="2"/>
       <c r="G852" s="2"/>
@@ -26449,7 +26558,7 @@
       <c r="A853" s="2"/>
       <c r="B853" s="2"/>
       <c r="C853" s="2"/>
-      <c r="D853" s="2"/>
+      <c r="D853" s="50"/>
       <c r="E853" s="2"/>
       <c r="F853" s="2"/>
       <c r="G853" s="2"/>
@@ -26477,7 +26586,7 @@
       <c r="A854" s="2"/>
       <c r="B854" s="2"/>
       <c r="C854" s="2"/>
-      <c r="D854" s="2"/>
+      <c r="D854" s="50"/>
       <c r="E854" s="2"/>
       <c r="F854" s="2"/>
       <c r="G854" s="2"/>
@@ -26505,7 +26614,7 @@
       <c r="A855" s="2"/>
       <c r="B855" s="2"/>
       <c r="C855" s="2"/>
-      <c r="D855" s="2"/>
+      <c r="D855" s="50"/>
       <c r="E855" s="2"/>
       <c r="F855" s="2"/>
       <c r="G855" s="2"/>
@@ -26533,7 +26642,7 @@
       <c r="A856" s="2"/>
       <c r="B856" s="2"/>
       <c r="C856" s="2"/>
-      <c r="D856" s="2"/>
+      <c r="D856" s="50"/>
       <c r="E856" s="2"/>
       <c r="F856" s="2"/>
       <c r="G856" s="2"/>
@@ -26561,7 +26670,7 @@
       <c r="A857" s="2"/>
       <c r="B857" s="2"/>
       <c r="C857" s="2"/>
-      <c r="D857" s="2"/>
+      <c r="D857" s="50"/>
       <c r="E857" s="2"/>
       <c r="F857" s="2"/>
       <c r="G857" s="2"/>
@@ -26589,7 +26698,7 @@
       <c r="A858" s="2"/>
       <c r="B858" s="2"/>
       <c r="C858" s="2"/>
-      <c r="D858" s="2"/>
+      <c r="D858" s="50"/>
       <c r="E858" s="2"/>
       <c r="F858" s="2"/>
       <c r="G858" s="2"/>
@@ -26617,7 +26726,7 @@
       <c r="A859" s="2"/>
       <c r="B859" s="2"/>
       <c r="C859" s="2"/>
-      <c r="D859" s="2"/>
+      <c r="D859" s="50"/>
       <c r="E859" s="2"/>
       <c r="F859" s="2"/>
       <c r="G859" s="2"/>
@@ -26645,7 +26754,7 @@
       <c r="A860" s="2"/>
       <c r="B860" s="2"/>
       <c r="C860" s="2"/>
-      <c r="D860" s="2"/>
+      <c r="D860" s="50"/>
       <c r="E860" s="2"/>
       <c r="F860" s="2"/>
       <c r="G860" s="2"/>
@@ -26673,7 +26782,7 @@
       <c r="A861" s="2"/>
       <c r="B861" s="2"/>
       <c r="C861" s="2"/>
-      <c r="D861" s="2"/>
+      <c r="D861" s="50"/>
       <c r="E861" s="2"/>
       <c r="F861" s="2"/>
       <c r="G861" s="2"/>
@@ -26701,7 +26810,7 @@
       <c r="A862" s="2"/>
       <c r="B862" s="2"/>
       <c r="C862" s="2"/>
-      <c r="D862" s="2"/>
+      <c r="D862" s="50"/>
       <c r="E862" s="2"/>
       <c r="F862" s="2"/>
       <c r="G862" s="2"/>
@@ -26729,7 +26838,7 @@
       <c r="A863" s="2"/>
       <c r="B863" s="2"/>
       <c r="C863" s="2"/>
-      <c r="D863" s="2"/>
+      <c r="D863" s="50"/>
       <c r="E863" s="2"/>
       <c r="F863" s="2"/>
       <c r="G863" s="2"/>
@@ -26757,7 +26866,7 @@
       <c r="A864" s="2"/>
       <c r="B864" s="2"/>
       <c r="C864" s="2"/>
-      <c r="D864" s="2"/>
+      <c r="D864" s="50"/>
       <c r="E864" s="2"/>
       <c r="F864" s="2"/>
       <c r="G864" s="2"/>
@@ -26785,7 +26894,7 @@
       <c r="A865" s="2"/>
       <c r="B865" s="2"/>
       <c r="C865" s="2"/>
-      <c r="D865" s="2"/>
+      <c r="D865" s="50"/>
       <c r="E865" s="2"/>
       <c r="F865" s="2"/>
       <c r="G865" s="2"/>
@@ -26813,7 +26922,7 @@
       <c r="A866" s="2"/>
       <c r="B866" s="2"/>
       <c r="C866" s="2"/>
-      <c r="D866" s="2"/>
+      <c r="D866" s="50"/>
       <c r="E866" s="2"/>
       <c r="F866" s="2"/>
       <c r="G866" s="2"/>
@@ -26841,7 +26950,7 @@
       <c r="A867" s="2"/>
       <c r="B867" s="2"/>
       <c r="C867" s="2"/>
-      <c r="D867" s="2"/>
+      <c r="D867" s="50"/>
       <c r="E867" s="2"/>
       <c r="F867" s="2"/>
       <c r="G867" s="2"/>
@@ -26869,7 +26978,7 @@
       <c r="A868" s="2"/>
       <c r="B868" s="2"/>
       <c r="C868" s="2"/>
-      <c r="D868" s="2"/>
+      <c r="D868" s="50"/>
       <c r="E868" s="2"/>
       <c r="F868" s="2"/>
       <c r="G868" s="2"/>
@@ -26897,7 +27006,7 @@
       <c r="A869" s="2"/>
       <c r="B869" s="2"/>
       <c r="C869" s="2"/>
-      <c r="D869" s="2"/>
+      <c r="D869" s="50"/>
       <c r="E869" s="2"/>
       <c r="F869" s="2"/>
       <c r="G869" s="2"/>
@@ -26925,7 +27034,7 @@
       <c r="A870" s="2"/>
       <c r="B870" s="2"/>
       <c r="C870" s="2"/>
-      <c r="D870" s="2"/>
+      <c r="D870" s="50"/>
       <c r="E870" s="2"/>
       <c r="F870" s="2"/>
       <c r="G870" s="2"/>
@@ -26953,7 +27062,7 @@
       <c r="A871" s="2"/>
       <c r="B871" s="2"/>
       <c r="C871" s="2"/>
-      <c r="D871" s="2"/>
+      <c r="D871" s="50"/>
       <c r="E871" s="2"/>
       <c r="F871" s="2"/>
       <c r="G871" s="2"/>
@@ -26981,7 +27090,7 @@
       <c r="A872" s="2"/>
       <c r="B872" s="2"/>
       <c r="C872" s="2"/>
-      <c r="D872" s="2"/>
+      <c r="D872" s="50"/>
       <c r="E872" s="2"/>
       <c r="F872" s="2"/>
       <c r="G872" s="2"/>
@@ -27009,7 +27118,7 @@
       <c r="A873" s="2"/>
       <c r="B873" s="2"/>
       <c r="C873" s="2"/>
-      <c r="D873" s="2"/>
+      <c r="D873" s="50"/>
       <c r="E873" s="2"/>
       <c r="F873" s="2"/>
       <c r="G873" s="2"/>
@@ -27037,7 +27146,7 @@
       <c r="A874" s="2"/>
       <c r="B874" s="2"/>
       <c r="C874" s="2"/>
-      <c r="D874" s="2"/>
+      <c r="D874" s="50"/>
       <c r="E874" s="2"/>
       <c r="F874" s="2"/>
       <c r="G874" s="2"/>
@@ -27065,7 +27174,7 @@
       <c r="A875" s="2"/>
       <c r="B875" s="2"/>
       <c r="C875" s="2"/>
-      <c r="D875" s="2"/>
+      <c r="D875" s="50"/>
       <c r="E875" s="2"/>
       <c r="F875" s="2"/>
       <c r="G875" s="2"/>
@@ -27093,7 +27202,7 @@
       <c r="A876" s="2"/>
       <c r="B876" s="2"/>
       <c r="C876" s="2"/>
-      <c r="D876" s="2"/>
+      <c r="D876" s="50"/>
       <c r="E876" s="2"/>
       <c r="F876" s="2"/>
       <c r="G876" s="2"/>
@@ -27121,7 +27230,7 @@
       <c r="A877" s="2"/>
       <c r="B877" s="2"/>
       <c r="C877" s="2"/>
-      <c r="D877" s="2"/>
+      <c r="D877" s="50"/>
       <c r="E877" s="2"/>
       <c r="F877" s="2"/>
       <c r="G877" s="2"/>
@@ -27149,7 +27258,7 @@
       <c r="A878" s="2"/>
       <c r="B878" s="2"/>
       <c r="C878" s="2"/>
-      <c r="D878" s="2"/>
+      <c r="D878" s="50"/>
       <c r="E878" s="2"/>
       <c r="F878" s="2"/>
       <c r="G878" s="2"/>
@@ -27177,7 +27286,7 @@
       <c r="A879" s="2"/>
       <c r="B879" s="2"/>
       <c r="C879" s="2"/>
-      <c r="D879" s="2"/>
+      <c r="D879" s="50"/>
       <c r="E879" s="2"/>
       <c r="F879" s="2"/>
       <c r="G879" s="2"/>
@@ -27205,7 +27314,7 @@
       <c r="A880" s="2"/>
       <c r="B880" s="2"/>
       <c r="C880" s="2"/>
-      <c r="D880" s="2"/>
+      <c r="D880" s="50"/>
       <c r="E880" s="2"/>
       <c r="F880" s="2"/>
       <c r="G880" s="2"/>
@@ -27233,7 +27342,7 @@
       <c r="A881" s="2"/>
       <c r="B881" s="2"/>
       <c r="C881" s="2"/>
-      <c r="D881" s="2"/>
+      <c r="D881" s="50"/>
       <c r="E881" s="2"/>
       <c r="F881" s="2"/>
       <c r="G881" s="2"/>
@@ -27261,7 +27370,7 @@
       <c r="A882" s="2"/>
       <c r="B882" s="2"/>
       <c r="C882" s="2"/>
-      <c r="D882" s="2"/>
+      <c r="D882" s="50"/>
       <c r="E882" s="2"/>
       <c r="F882" s="2"/>
       <c r="G882" s="2"/>
@@ -27289,7 +27398,7 @@
       <c r="A883" s="2"/>
       <c r="B883" s="2"/>
       <c r="C883" s="2"/>
-      <c r="D883" s="2"/>
+      <c r="D883" s="50"/>
       <c r="E883" s="2"/>
       <c r="F883" s="2"/>
       <c r="G883" s="2"/>
@@ -27317,7 +27426,7 @@
       <c r="A884" s="2"/>
       <c r="B884" s="2"/>
       <c r="C884" s="2"/>
-      <c r="D884" s="2"/>
+      <c r="D884" s="50"/>
       <c r="E884" s="2"/>
       <c r="F884" s="2"/>
       <c r="G884" s="2"/>
@@ -27345,7 +27454,7 @@
       <c r="A885" s="2"/>
       <c r="B885" s="2"/>
       <c r="C885" s="2"/>
-      <c r="D885" s="2"/>
+      <c r="D885" s="50"/>
       <c r="E885" s="2"/>
       <c r="F885" s="2"/>
       <c r="G885" s="2"/>
@@ -27373,7 +27482,7 @@
       <c r="A886" s="2"/>
       <c r="B886" s="2"/>
       <c r="C886" s="2"/>
-      <c r="D886" s="2"/>
+      <c r="D886" s="50"/>
       <c r="E886" s="2"/>
       <c r="F886" s="2"/>
       <c r="G886" s="2"/>
@@ -27401,7 +27510,7 @@
       <c r="A887" s="2"/>
       <c r="B887" s="2"/>
       <c r="C887" s="2"/>
-      <c r="D887" s="2"/>
+      <c r="D887" s="50"/>
       <c r="E887" s="2"/>
       <c r="F887" s="2"/>
       <c r="G887" s="2"/>
@@ -27429,7 +27538,7 @@
       <c r="A888" s="2"/>
       <c r="B888" s="2"/>
       <c r="C888" s="2"/>
-      <c r="D888" s="2"/>
+      <c r="D888" s="50"/>
       <c r="E888" s="2"/>
       <c r="F888" s="2"/>
       <c r="G888" s="2"/>
@@ -27457,7 +27566,7 @@
       <c r="A889" s="2"/>
       <c r="B889" s="2"/>
       <c r="C889" s="2"/>
-      <c r="D889" s="2"/>
+      <c r="D889" s="50"/>
       <c r="E889" s="2"/>
       <c r="F889" s="2"/>
       <c r="G889" s="2"/>
@@ -27485,7 +27594,7 @@
       <c r="A890" s="2"/>
       <c r="B890" s="2"/>
       <c r="C890" s="2"/>
-      <c r="D890" s="2"/>
+      <c r="D890" s="50"/>
       <c r="E890" s="2"/>
       <c r="F890" s="2"/>
       <c r="G890" s="2"/>
@@ -27513,7 +27622,7 @@
       <c r="A891" s="2"/>
       <c r="B891" s="2"/>
       <c r="C891" s="2"/>
-      <c r="D891" s="2"/>
+      <c r="D891" s="50"/>
       <c r="E891" s="2"/>
       <c r="F891" s="2"/>
       <c r="G891" s="2"/>
@@ -27541,7 +27650,7 @@
       <c r="A892" s="2"/>
       <c r="B892" s="2"/>
       <c r="C892" s="2"/>
-      <c r="D892" s="2"/>
+      <c r="D892" s="50"/>
       <c r="E892" s="2"/>
       <c r="F892" s="2"/>
       <c r="G892" s="2"/>
@@ -27569,7 +27678,7 @@
       <c r="A893" s="2"/>
       <c r="B893" s="2"/>
       <c r="C893" s="2"/>
-      <c r="D893" s="2"/>
+      <c r="D893" s="50"/>
       <c r="E893" s="2"/>
       <c r="F893" s="2"/>
       <c r="G893" s="2"/>
@@ -27597,7 +27706,7 @@
       <c r="A894" s="2"/>
       <c r="B894" s="2"/>
       <c r="C894" s="2"/>
-      <c r="D894" s="2"/>
+      <c r="D894" s="50"/>
       <c r="E894" s="2"/>
       <c r="F894" s="2"/>
       <c r="G894" s="2"/>
@@ -27625,7 +27734,7 @@
       <c r="A895" s="2"/>
       <c r="B895" s="2"/>
       <c r="C895" s="2"/>
-      <c r="D895" s="2"/>
+      <c r="D895" s="50"/>
       <c r="E895" s="2"/>
       <c r="F895" s="2"/>
       <c r="G895" s="2"/>
@@ -27653,7 +27762,7 @@
       <c r="A896" s="2"/>
       <c r="B896" s="2"/>
       <c r="C896" s="2"/>
-      <c r="D896" s="2"/>
+      <c r="D896" s="50"/>
       <c r="E896" s="2"/>
       <c r="F896" s="2"/>
       <c r="G896" s="2"/>
@@ -27681,7 +27790,7 @@
       <c r="A897" s="2"/>
       <c r="B897" s="2"/>
       <c r="C897" s="2"/>
-      <c r="D897" s="2"/>
+      <c r="D897" s="50"/>
       <c r="E897" s="2"/>
       <c r="F897" s="2"/>
       <c r="G897" s="2"/>
@@ -27709,7 +27818,7 @@
       <c r="A898" s="2"/>
       <c r="B898" s="2"/>
       <c r="C898" s="2"/>
-      <c r="D898" s="2"/>
+      <c r="D898" s="50"/>
       <c r="E898" s="2"/>
       <c r="F898" s="2"/>
       <c r="G898" s="2"/>
@@ -27737,7 +27846,7 @@
       <c r="A899" s="2"/>
       <c r="B899" s="2"/>
       <c r="C899" s="2"/>
-      <c r="D899" s="2"/>
+      <c r="D899" s="50"/>
       <c r="E899" s="2"/>
       <c r="F899" s="2"/>
       <c r="G899" s="2"/>
@@ -27765,7 +27874,7 @@
       <c r="A900" s="2"/>
       <c r="B900" s="2"/>
       <c r="C900" s="2"/>
-      <c r="D900" s="2"/>
+      <c r="D900" s="50"/>
       <c r="E900" s="2"/>
       <c r="F900" s="2"/>
       <c r="G900" s="2"/>
@@ -27793,7 +27902,7 @@
       <c r="A901" s="2"/>
       <c r="B901" s="2"/>
       <c r="C901" s="2"/>
-      <c r="D901" s="2"/>
+      <c r="D901" s="50"/>
       <c r="E901" s="2"/>
       <c r="F901" s="2"/>
       <c r="G901" s="2"/>
@@ -27821,7 +27930,7 @@
       <c r="A902" s="2"/>
       <c r="B902" s="2"/>
       <c r="C902" s="2"/>
-      <c r="D902" s="2"/>
+      <c r="D902" s="50"/>
       <c r="E902" s="2"/>
       <c r="F902" s="2"/>
       <c r="G902" s="2"/>
@@ -27849,7 +27958,7 @@
       <c r="A903" s="2"/>
       <c r="B903" s="2"/>
       <c r="C903" s="2"/>
-      <c r="D903" s="2"/>
+      <c r="D903" s="50"/>
       <c r="E903" s="2"/>
       <c r="F903" s="2"/>
       <c r="G903" s="2"/>
@@ -27877,7 +27986,7 @@
       <c r="A904" s="2"/>
       <c r="B904" s="2"/>
       <c r="C904" s="2"/>
-      <c r="D904" s="2"/>
+      <c r="D904" s="50"/>
       <c r="E904" s="2"/>
       <c r="F904" s="2"/>
       <c r="G904" s="2"/>
@@ -27905,7 +28014,7 @@
       <c r="A905" s="2"/>
       <c r="B905" s="2"/>
       <c r="C905" s="2"/>
-      <c r="D905" s="2"/>
+      <c r="D905" s="50"/>
       <c r="E905" s="2"/>
       <c r="F905" s="2"/>
       <c r="G905" s="2"/>
@@ -27933,7 +28042,7 @@
       <c r="A906" s="2"/>
       <c r="B906" s="2"/>
       <c r="C906" s="2"/>
-      <c r="D906" s="2"/>
+      <c r="D906" s="50"/>
       <c r="E906" s="2"/>
       <c r="F906" s="2"/>
       <c r="G906" s="2"/>
@@ -27961,7 +28070,7 @@
       <c r="A907" s="2"/>
       <c r="B907" s="2"/>
       <c r="C907" s="2"/>
-      <c r="D907" s="2"/>
+      <c r="D907" s="50"/>
       <c r="E907" s="2"/>
       <c r="F907" s="2"/>
       <c r="G907" s="2"/>
@@ -27989,7 +28098,7 @@
       <c r="A908" s="2"/>
       <c r="B908" s="2"/>
       <c r="C908" s="2"/>
-      <c r="D908" s="2"/>
+      <c r="D908" s="50"/>
       <c r="E908" s="2"/>
       <c r="F908" s="2"/>
       <c r="G908" s="2"/>
@@ -28017,7 +28126,7 @@
       <c r="A909" s="2"/>
       <c r="B909" s="2"/>
       <c r="C909" s="2"/>
-      <c r="D909" s="2"/>
+      <c r="D909" s="50"/>
       <c r="E909" s="2"/>
       <c r="F909" s="2"/>
       <c r="G909" s="2"/>
@@ -28045,7 +28154,7 @@
       <c r="A910" s="2"/>
       <c r="B910" s="2"/>
       <c r="C910" s="2"/>
-      <c r="D910" s="2"/>
+      <c r="D910" s="50"/>
       <c r="E910" s="2"/>
       <c r="F910" s="2"/>
       <c r="G910" s="2"/>
@@ -28073,7 +28182,7 @@
       <c r="A911" s="2"/>
       <c r="B911" s="2"/>
       <c r="C911" s="2"/>
-      <c r="D911" s="2"/>
+      <c r="D911" s="50"/>
       <c r="E911" s="2"/>
       <c r="F911" s="2"/>
       <c r="G911" s="2"/>
@@ -28101,7 +28210,7 @@
       <c r="A912" s="2"/>
       <c r="B912" s="2"/>
       <c r="C912" s="2"/>
-      <c r="D912" s="2"/>
+      <c r="D912" s="50"/>
       <c r="E912" s="2"/>
       <c r="F912" s="2"/>
       <c r="G912" s="2"/>
@@ -28129,7 +28238,7 @@
       <c r="A913" s="2"/>
       <c r="B913" s="2"/>
       <c r="C913" s="2"/>
-      <c r="D913" s="2"/>
+      <c r="D913" s="50"/>
       <c r="E913" s="2"/>
       <c r="F913" s="2"/>
       <c r="G913" s="2"/>
@@ -28157,7 +28266,7 @@
       <c r="A914" s="2"/>
       <c r="B914" s="2"/>
       <c r="C914" s="2"/>
-      <c r="D914" s="2"/>
+      <c r="D914" s="50"/>
       <c r="E914" s="2"/>
       <c r="F914" s="2"/>
       <c r="G914" s="2"/>
@@ -28185,7 +28294,7 @@
       <c r="A915" s="2"/>
       <c r="B915" s="2"/>
       <c r="C915" s="2"/>
-      <c r="D915" s="2"/>
+      <c r="D915" s="50"/>
       <c r="E915" s="2"/>
       <c r="F915" s="2"/>
       <c r="G915" s="2"/>
@@ -28213,7 +28322,7 @@
       <c r="A916" s="2"/>
       <c r="B916" s="2"/>
       <c r="C916" s="2"/>
-      <c r="D916" s="2"/>
+      <c r="D916" s="50"/>
       <c r="E916" s="2"/>
       <c r="F916" s="2"/>
       <c r="G916" s="2"/>
@@ -28241,7 +28350,7 @@
       <c r="A917" s="2"/>
       <c r="B917" s="2"/>
       <c r="C917" s="2"/>
-      <c r="D917" s="2"/>
+      <c r="D917" s="50"/>
       <c r="E917" s="2"/>
       <c r="F917" s="2"/>
       <c r="G917" s="2"/>
@@ -28269,7 +28378,7 @@
       <c r="A918" s="2"/>
       <c r="B918" s="2"/>
       <c r="C918" s="2"/>
-      <c r="D918" s="2"/>
+      <c r="D918" s="50"/>
       <c r="E918" s="2"/>
       <c r="F918" s="2"/>
       <c r="G918" s="2"/>
@@ -28297,7 +28406,7 @@
       <c r="A919" s="2"/>
       <c r="B919" s="2"/>
       <c r="C919" s="2"/>
-      <c r="D919" s="2"/>
+      <c r="D919" s="50"/>
       <c r="E919" s="2"/>
       <c r="F919" s="2"/>
       <c r="G919" s="2"/>
@@ -28325,7 +28434,7 @@
       <c r="A920" s="2"/>
       <c r="B920" s="2"/>
       <c r="C920" s="2"/>
-      <c r="D920" s="2"/>
+      <c r="D920" s="50"/>
       <c r="E920" s="2"/>
       <c r="F920" s="2"/>
       <c r="G920" s="2"/>
@@ -28353,7 +28462,7 @@
       <c r="A921" s="2"/>
       <c r="B921" s="2"/>
       <c r="C921" s="2"/>
-      <c r="D921" s="2"/>
+      <c r="D921" s="50"/>
       <c r="E921" s="2"/>
       <c r="F921" s="2"/>
       <c r="G921" s="2"/>
@@ -28381,7 +28490,7 @@
       <c r="A922" s="2"/>
       <c r="B922" s="2"/>
       <c r="C922" s="2"/>
-      <c r="D922" s="2"/>
+      <c r="D922" s="50"/>
       <c r="E922" s="2"/>
       <c r="F922" s="2"/>
       <c r="G922" s="2"/>
@@ -28409,7 +28518,7 @@
       <c r="A923" s="2"/>
       <c r="B923" s="2"/>
       <c r="C923" s="2"/>
-      <c r="D923" s="2"/>
+      <c r="D923" s="50"/>
       <c r="E923" s="2"/>
       <c r="F923" s="2"/>
       <c r="G923" s="2"/>
@@ -28437,7 +28546,7 @@
       <c r="A924" s="2"/>
       <c r="B924" s="2"/>
       <c r="C924" s="2"/>
-      <c r="D924" s="2"/>
+      <c r="D924" s="50"/>
       <c r="E924" s="2"/>
       <c r="F924" s="2"/>
       <c r="G924" s="2"/>
@@ -28465,7 +28574,7 @@
       <c r="A925" s="2"/>
       <c r="B925" s="2"/>
       <c r="C925" s="2"/>
-      <c r="D925" s="2"/>
+      <c r="D925" s="50"/>
       <c r="E925" s="2"/>
       <c r="F925" s="2"/>
       <c r="G925" s="2"/>
@@ -28493,7 +28602,7 @@
       <c r="A926" s="2"/>
       <c r="B926" s="2"/>
       <c r="C926" s="2"/>
-      <c r="D926" s="2"/>
+      <c r="D926" s="50"/>
       <c r="E926" s="2"/>
       <c r="F926" s="2"/>
       <c r="G926" s="2"/>
@@ -28521,7 +28630,7 @@
       <c r="A927" s="2"/>
       <c r="B927" s="2"/>
       <c r="C927" s="2"/>
-      <c r="D927" s="2"/>
+      <c r="D927" s="50"/>
       <c r="E927" s="2"/>
       <c r="F927" s="2"/>
       <c r="G927" s="2"/>
@@ -28549,7 +28658,7 @@
       <c r="A928" s="2"/>
       <c r="B928" s="2"/>
       <c r="C928" s="2"/>
-      <c r="D928" s="2"/>
+      <c r="D928" s="50"/>
       <c r="E928" s="2"/>
       <c r="F928" s="2"/>
       <c r="G928" s="2"/>
@@ -28577,7 +28686,7 @@
       <c r="A929" s="2"/>
       <c r="B929" s="2"/>
       <c r="C929" s="2"/>
-      <c r="D929" s="2"/>
+      <c r="D929" s="50"/>
       <c r="E929" s="2"/>
       <c r="F929" s="2"/>
       <c r="G929" s="2"/>
@@ -28605,7 +28714,7 @@
       <c r="A930" s="2"/>
       <c r="B930" s="2"/>
       <c r="C930" s="2"/>
-      <c r="D930" s="2"/>
+      <c r="D930" s="50"/>
       <c r="E930" s="2"/>
       <c r="F930" s="2"/>
       <c r="G930" s="2"/>
@@ -28633,7 +28742,7 @@
       <c r="A931" s="2"/>
       <c r="B931" s="2"/>
       <c r="C931" s="2"/>
-      <c r="D931" s="2"/>
+      <c r="D931" s="50"/>
       <c r="E931" s="2"/>
       <c r="F931" s="2"/>
       <c r="G931" s="2"/>
@@ -28661,7 +28770,7 @@
       <c r="A932" s="2"/>
       <c r="B932" s="2"/>
       <c r="C932" s="2"/>
-      <c r="D932" s="2"/>
+      <c r="D932" s="50"/>
       <c r="E932" s="2"/>
       <c r="F932" s="2"/>
       <c r="G932" s="2"/>
@@ -28689,7 +28798,7 @@
       <c r="A933" s="2"/>
       <c r="B933" s="2"/>
       <c r="C933" s="2"/>
-      <c r="D933" s="2"/>
+      <c r="D933" s="50"/>
       <c r="E933" s="2"/>
       <c r="F933" s="2"/>
       <c r="G933" s="2"/>
@@ -28717,7 +28826,7 @@
       <c r="A934" s="2"/>
       <c r="B934" s="2"/>
       <c r="C934" s="2"/>
-      <c r="D934" s="2"/>
+      <c r="D934" s="50"/>
       <c r="E934" s="2"/>
       <c r="F934" s="2"/>
       <c r="G934" s="2"/>
@@ -28745,7 +28854,7 @@
       <c r="A935" s="2"/>
       <c r="B935" s="2"/>
       <c r="C935" s="2"/>
-      <c r="D935" s="2"/>
+      <c r="D935" s="50"/>
       <c r="E935" s="2"/>
       <c r="F935" s="2"/>
       <c r="G935" s="2"/>
@@ -28773,7 +28882,7 @@
       <c r="A936" s="2"/>
       <c r="B936" s="2"/>
       <c r="C936" s="2"/>
-      <c r="D936" s="2"/>
+      <c r="D936" s="50"/>
       <c r="E936" s="2"/>
       <c r="F936" s="2"/>
       <c r="G936" s="2"/>
@@ -28801,7 +28910,7 @@
       <c r="A937" s="2"/>
       <c r="B937" s="2"/>
       <c r="C937" s="2"/>
-      <c r="D937" s="2"/>
+      <c r="D937" s="50"/>
       <c r="E937" s="2"/>
       <c r="F937" s="2"/>
       <c r="G937" s="2"/>
@@ -28829,7 +28938,7 @@
       <c r="A938" s="2"/>
       <c r="B938" s="2"/>
       <c r="C938" s="2"/>
-      <c r="D938" s="2"/>
+      <c r="D938" s="50"/>
       <c r="E938" s="2"/>
       <c r="F938" s="2"/>
       <c r="G938" s="2"/>
@@ -28857,7 +28966,7 @@
       <c r="A939" s="2"/>
       <c r="B939" s="2"/>
       <c r="C939" s="2"/>
-      <c r="D939" s="2"/>
+      <c r="D939" s="50"/>
       <c r="E939" s="2"/>
       <c r="F939" s="2"/>
       <c r="G939" s="2"/>
@@ -28885,7 +28994,7 @@
       <c r="A940" s="2"/>
       <c r="B940" s="2"/>
       <c r="C940" s="2"/>
-      <c r="D940" s="2"/>
+      <c r="D940" s="50"/>
       <c r="E940" s="2"/>
       <c r="F940" s="2"/>
       <c r="G940" s="2"/>
@@ -28913,7 +29022,7 @@
       <c r="A941" s="2"/>
       <c r="B941" s="2"/>
       <c r="C941" s="2"/>
-      <c r="D941" s="2"/>
+      <c r="D941" s="50"/>
       <c r="E941" s="2"/>
       <c r="F941" s="2"/>
       <c r="G941" s="2"/>
@@ -28941,7 +29050,7 @@
       <c r="A942" s="2"/>
       <c r="B942" s="2"/>
       <c r="C942" s="2"/>
-      <c r="D942" s="2"/>
+      <c r="D942" s="50"/>
       <c r="E942" s="2"/>
       <c r="F942" s="2"/>
       <c r="G942" s="2"/>
@@ -28969,7 +29078,7 @@
       <c r="A943" s="2"/>
       <c r="B943" s="2"/>
       <c r="C943" s="2"/>
-      <c r="D943" s="2"/>
+      <c r="D943" s="50"/>
       <c r="E943" s="2"/>
       <c r="F943" s="2"/>
       <c r="G943" s="2"/>
@@ -28997,7 +29106,7 @@
       <c r="A944" s="2"/>
       <c r="B944" s="2"/>
       <c r="C944" s="2"/>
-      <c r="D944" s="2"/>
+      <c r="D944" s="50"/>
       <c r="E944" s="2"/>
       <c r="F944" s="2"/>
       <c r="G944" s="2"/>
@@ -29025,7 +29134,7 @@
       <c r="A945" s="2"/>
       <c r="B945" s="2"/>
       <c r="C945" s="2"/>
-      <c r="D945" s="2"/>
+      <c r="D945" s="50"/>
       <c r="E945" s="2"/>
       <c r="F945" s="2"/>
       <c r="G945" s="2"/>
@@ -29053,7 +29162,7 @@
       <c r="A946" s="2"/>
       <c r="B946" s="2"/>
       <c r="C946" s="2"/>
-      <c r="D946" s="2"/>
+      <c r="D946" s="50"/>
       <c r="E946" s="2"/>
       <c r="F946" s="2"/>
       <c r="G946" s="2"/>
@@ -29081,7 +29190,7 @@
       <c r="A947" s="2"/>
       <c r="B947" s="2"/>
       <c r="C947" s="2"/>
-      <c r="D947" s="2"/>
+      <c r="D947" s="50"/>
       <c r="E947" s="2"/>
       <c r="F947" s="2"/>
       <c r="G947" s="2"/>
@@ -29109,7 +29218,7 @@
       <c r="A948" s="2"/>
       <c r="B948" s="2"/>
       <c r="C948" s="2"/>
-      <c r="D948" s="2"/>
+      <c r="D948" s="50"/>
       <c r="E948" s="2"/>
       <c r="F948" s="2"/>
       <c r="G948" s="2"/>
@@ -29137,7 +29246,7 @@
       <c r="A949" s="2"/>
       <c r="B949" s="2"/>
       <c r="C949" s="2"/>
-      <c r="D949" s="2"/>
+      <c r="D949" s="50"/>
       <c r="E949" s="2"/>
       <c r="F949" s="2"/>
       <c r="G949" s="2"/>
@@ -29165,7 +29274,7 @@
       <c r="A950" s="2"/>
       <c r="B950" s="2"/>
       <c r="C950" s="2"/>
-      <c r="D950" s="2"/>
+      <c r="D950" s="50"/>
       <c r="E950" s="2"/>
       <c r="F950" s="2"/>
       <c r="G950" s="2"/>
@@ -29193,7 +29302,7 @@
       <c r="A951" s="2"/>
       <c r="B951" s="2"/>
       <c r="C951" s="2"/>
-      <c r="D951" s="2"/>
+      <c r="D951" s="50"/>
       <c r="E951" s="2"/>
       <c r="F951" s="2"/>
       <c r="G951" s="2"/>
@@ -29221,7 +29330,7 @@
       <c r="A952" s="2"/>
       <c r="B952" s="2"/>
       <c r="C952" s="2"/>
-      <c r="D952" s="2"/>
+      <c r="D952" s="50"/>
       <c r="E952" s="2"/>
       <c r="F952" s="2"/>
       <c r="G952" s="2"/>
@@ -29249,7 +29358,7 @@
       <c r="A953" s="2"/>
       <c r="B953" s="2"/>
       <c r="C953" s="2"/>
-      <c r="D953" s="2"/>
+      <c r="D953" s="50"/>
       <c r="E953" s="2"/>
       <c r="F953" s="2"/>
       <c r="G953" s="2"/>
@@ -29277,7 +29386,7 @@
       <c r="A954" s="2"/>
       <c r="B954" s="2"/>
       <c r="C954" s="2"/>
-      <c r="D954" s="2"/>
+      <c r="D954" s="50"/>
       <c r="E954" s="2"/>
       <c r="F954" s="2"/>
       <c r="G954" s="2"/>
@@ -29305,7 +29414,7 @@
       <c r="A955" s="2"/>
       <c r="B955" s="2"/>
       <c r="C955" s="2"/>
-      <c r="D955" s="2"/>
+      <c r="D955" s="50"/>
       <c r="E955" s="2"/>
       <c r="F955" s="2"/>
       <c r="G955" s="2"/>
@@ -29333,7 +29442,7 @@
       <c r="A956" s="2"/>
       <c r="B956" s="2"/>
       <c r="C956" s="2"/>
-      <c r="D956" s="2"/>
+      <c r="D956" s="50"/>
       <c r="E956" s="2"/>
       <c r="F956" s="2"/>
       <c r="G956" s="2"/>
@@ -29361,7 +29470,7 @@
       <c r="A957" s="2"/>
       <c r="B957" s="2"/>
       <c r="C957" s="2"/>
-      <c r="D957" s="2"/>
+      <c r="D957" s="50"/>
       <c r="E957" s="2"/>
       <c r="F957" s="2"/>
       <c r="G957" s="2"/>
@@ -29389,7 +29498,7 @@
       <c r="A958" s="2"/>
       <c r="B958" s="2"/>
       <c r="C958" s="2"/>
-      <c r="D958" s="2"/>
+      <c r="D958" s="50"/>
       <c r="E958" s="2"/>
       <c r="F958" s="2"/>
       <c r="G958" s="2"/>
@@ -29417,7 +29526,7 @@
       <c r="A959" s="2"/>
       <c r="B959" s="2"/>
       <c r="C959" s="2"/>
-      <c r="D959" s="2"/>
+      <c r="D959" s="50"/>
       <c r="E959" s="2"/>
       <c r="F959" s="2"/>
       <c r="G959" s="2"/>
@@ -29445,7 +29554,7 @@
       <c r="A960" s="2"/>
       <c r="B960" s="2"/>
       <c r="C960" s="2"/>
-      <c r="D960" s="2"/>
+      <c r="D960" s="50"/>
       <c r="E960" s="2"/>
       <c r="F960" s="2"/>
       <c r="G960" s="2"/>
@@ -29473,7 +29582,7 @@
       <c r="A961" s="2"/>
       <c r="B961" s="2"/>
       <c r="C961" s="2"/>
-      <c r="D961" s="2"/>
+      <c r="D961" s="50"/>
       <c r="E961" s="2"/>
       <c r="F961" s="2"/>
       <c r="G961" s="2"/>
@@ -29501,7 +29610,7 @@
       <c r="A962" s="2"/>
       <c r="B962" s="2"/>
       <c r="C962" s="2"/>
-      <c r="D962" s="2"/>
+      <c r="D962" s="50"/>
       <c r="E962" s="2"/>
       <c r="F962" s="2"/>
       <c r="G962" s="2"/>
@@ -29529,7 +29638,7 @@
       <c r="A963" s="2"/>
       <c r="B963" s="2"/>
       <c r="C963" s="2"/>
-      <c r="D963" s="2"/>
+      <c r="D963" s="50"/>
       <c r="E963" s="2"/>
       <c r="F963" s="2"/>
       <c r="G963" s="2"/>
@@ -29557,7 +29666,7 @@
       <c r="A964" s="2"/>
       <c r="B964" s="2"/>
       <c r="C964" s="2"/>
-      <c r="D964" s="2"/>
+      <c r="D964" s="50"/>
       <c r="E964" s="2"/>
       <c r="F964" s="2"/>
       <c r="G964" s="2"/>
@@ -29585,7 +29694,7 @@
       <c r="A965" s="2"/>
       <c r="B965" s="2"/>
       <c r="C965" s="2"/>
-      <c r="D965" s="2"/>
+      <c r="D965" s="50"/>
       <c r="E965" s="2"/>
       <c r="F965" s="2"/>
       <c r="G965" s="2"/>
@@ -29613,7 +29722,7 @@
       <c r="A966" s="2"/>
       <c r="B966" s="2"/>
       <c r="C966" s="2"/>
-      <c r="D966" s="2"/>
+      <c r="D966" s="50"/>
       <c r="E966" s="2"/>
       <c r="F966" s="2"/>
       <c r="G966" s="2"/>
@@ -29641,7 +29750,7 @@
       <c r="A967" s="2"/>
       <c r="B967" s="2"/>
       <c r="C967" s="2"/>
-      <c r="D967" s="2"/>
+      <c r="D967" s="50"/>
       <c r="E967" s="2"/>
       <c r="F967" s="2"/>
       <c r="G967" s="2"/>
@@ -29669,7 +29778,7 @@
       <c r="A968" s="2"/>
       <c r="B968" s="2"/>
       <c r="C968" s="2"/>
-      <c r="D968" s="2"/>
+      <c r="D968" s="50"/>
       <c r="E968" s="2"/>
       <c r="F968" s="2"/>
       <c r="G968" s="2"/>
@@ -29697,7 +29806,7 @@
       <c r="A969" s="2"/>
       <c r="B969" s="2"/>
       <c r="C969" s="2"/>
-      <c r="D969" s="2"/>
+      <c r="D969" s="50"/>
       <c r="E969" s="2"/>
       <c r="F969" s="2"/>
       <c r="G969" s="2"/>
@@ -29725,7 +29834,7 @@
       <c r="A970" s="2"/>
       <c r="B970" s="2"/>
       <c r="C970" s="2"/>
-      <c r="D970" s="2"/>
+      <c r="D970" s="50"/>
       <c r="E970" s="2"/>
       <c r="F970" s="2"/>
       <c r="G970" s="2"/>
@@ -29753,7 +29862,7 @@
       <c r="A971" s="2"/>
       <c r="B971" s="2"/>
       <c r="C971" s="2"/>
-      <c r="D971" s="2"/>
+      <c r="D971" s="50"/>
       <c r="E971" s="2"/>
       <c r="F971" s="2"/>
       <c r="G971" s="2"/>
@@ -29781,7 +29890,7 @@
       <c r="A972" s="2"/>
       <c r="B972" s="2"/>
       <c r="C972" s="2"/>
-      <c r="D972" s="2"/>
+      <c r="D972" s="50"/>
       <c r="E972" s="2"/>
       <c r="F972" s="2"/>
       <c r="G972" s="2"/>
@@ -29809,7 +29918,7 @@
       <c r="A973" s="2"/>
       <c r="B973" s="2"/>
       <c r="C973" s="2"/>
-      <c r="D973" s="2"/>
+      <c r="D973" s="50"/>
       <c r="E973" s="2"/>
       <c r="F973" s="2"/>
       <c r="G973" s="2"/>
@@ -29837,7 +29946,7 @@
       <c r="A974" s="2"/>
       <c r="B974" s="2"/>
       <c r="C974" s="2"/>
-      <c r="D974" s="2"/>
+      <c r="D974" s="50"/>
       <c r="E974" s="2"/>
       <c r="F974" s="2"/>
       <c r="G974" s="2"/>
@@ -29865,7 +29974,7 @@
       <c r="A975" s="2"/>
       <c r="B975" s="2"/>
       <c r="C975" s="2"/>
-      <c r="D975" s="2"/>
+      <c r="D975" s="50"/>
       <c r="E975" s="2"/>
       <c r="F975" s="2"/>
       <c r="G975" s="2"/>
@@ -29893,7 +30002,7 @@
       <c r="A976" s="2"/>
       <c r="B976" s="2"/>
       <c r="C976" s="2"/>
-      <c r="D976" s="2"/>
+      <c r="D976" s="50"/>
       <c r="E976" s="2"/>
       <c r="F976" s="2"/>
       <c r="G976" s="2"/>
@@ -29921,7 +30030,7 @@
       <c r="A977" s="2"/>
       <c r="B977" s="2"/>
       <c r="C977" s="2"/>
-      <c r="D977" s="2"/>
+      <c r="D977" s="50"/>
       <c r="E977" s="2"/>
       <c r="F977" s="2"/>
       <c r="G977" s="2"/>
@@ -29949,7 +30058,7 @@
       <c r="A978" s="2"/>
       <c r="B978" s="2"/>
       <c r="C978" s="2"/>
-      <c r="D978" s="2"/>
+      <c r="D978" s="50"/>
       <c r="E978" s="2"/>
       <c r="F978" s="2"/>
       <c r="G978" s="2"/>
@@ -29977,7 +30086,7 @@
       <c r="A979" s="2"/>
       <c r="B979" s="2"/>
       <c r="C979" s="2"/>
-      <c r="D979" s="2"/>
+      <c r="D979" s="50"/>
       <c r="E979" s="2"/>
       <c r="F979" s="2"/>
       <c r="G979" s="2"/>
@@ -30005,7 +30114,7 @@
       <c r="A980" s="2"/>
       <c r="B980" s="2"/>
       <c r="C980" s="2"/>
-      <c r="D980" s="2"/>
+      <c r="D980" s="50"/>
       <c r="E980" s="2"/>
       <c r="F980" s="2"/>
       <c r="G980" s="2"/>
@@ -30033,7 +30142,7 @@
       <c r="A981" s="2"/>
       <c r="B981" s="2"/>
       <c r="C981" s="2"/>
-      <c r="D981" s="2"/>
+      <c r="D981" s="50"/>
       <c r="E981" s="2"/>
       <c r="F981" s="2"/>
       <c r="G981" s="2"/>
@@ -30061,7 +30170,7 @@
       <c r="A982" s="2"/>
       <c r="B982" s="2"/>
       <c r="C982" s="2"/>
-      <c r="D982" s="2"/>
+      <c r="D982" s="50"/>
       <c r="E982" s="2"/>
       <c r="F982" s="2"/>
       <c r="G982" s="2"/>
@@ -30089,7 +30198,7 @@
       <c r="A983" s="2"/>
       <c r="B983" s="2"/>
       <c r="C983" s="2"/>
-      <c r="D983" s="2"/>
+      <c r="D983" s="50"/>
       <c r="E983" s="2"/>
       <c r="F983" s="2"/>
       <c r="G983" s="2"/>
@@ -30117,7 +30226,7 @@
       <c r="A984" s="2"/>
       <c r="B984" s="2"/>
       <c r="C984" s="2"/>
-      <c r="D984" s="2"/>
+      <c r="D984" s="50"/>
       <c r="E984" s="2"/>
       <c r="F984" s="2"/>
       <c r="G984" s="2"/>
@@ -30145,7 +30254,7 @@
       <c r="A985" s="2"/>
       <c r="B985" s="2"/>
       <c r="C985" s="2"/>
-      <c r="D985" s="2"/>
+      <c r="D985" s="50"/>
       <c r="E985" s="2"/>
       <c r="F985" s="2"/>
       <c r="G985" s="2"/>
@@ -30173,7 +30282,7 @@
       <c r="A986" s="2"/>
       <c r="B986" s="2"/>
       <c r="C986" s="2"/>
-      <c r="D986" s="2"/>
+      <c r="D986" s="50"/>
       <c r="E986" s="2"/>
       <c r="F986" s="2"/>
       <c r="G986" s="2"/>
@@ -30201,7 +30310,7 @@
       <c r="A987" s="2"/>
       <c r="B987" s="2"/>
       <c r="C987" s="2"/>
-      <c r="D987" s="2"/>
+      <c r="D987" s="50"/>
       <c r="E987" s="2"/>
       <c r="F987" s="2"/>
       <c r="G987" s="2"/>
@@ -30229,7 +30338,7 @@
       <c r="A988" s="2"/>
       <c r="B988" s="2"/>
       <c r="C988" s="2"/>
-      <c r="D988" s="2"/>
+      <c r="D988" s="50"/>
       <c r="E988" s="2"/>
       <c r="F988" s="2"/>
       <c r="G988" s="2"/>
@@ -30257,7 +30366,7 @@
       <c r="A989" s="2"/>
       <c r="B989" s="2"/>
       <c r="C989" s="2"/>
-      <c r="D989" s="2"/>
+      <c r="D989" s="50"/>
       <c r="E989" s="2"/>
       <c r="F989" s="2"/>
       <c r="G989" s="2"/>
@@ -30285,7 +30394,7 @@
       <c r="A990" s="2"/>
       <c r="B990" s="2"/>
       <c r="C990" s="2"/>
-      <c r="D990" s="2"/>
+      <c r="D990" s="50"/>
       <c r="E990" s="2"/>
       <c r="F990" s="2"/>
       <c r="G990" s="2"/>
@@ -30313,7 +30422,7 @@
       <c r="A991" s="2"/>
       <c r="B991" s="2"/>
       <c r="C991" s="2"/>
-      <c r="D991" s="2"/>
+      <c r="D991" s="50"/>
       <c r="E991" s="2"/>
       <c r="F991" s="2"/>
       <c r="G991" s="2"/>
@@ -30341,7 +30450,7 @@
       <c r="A992" s="2"/>
       <c r="B992" s="2"/>
       <c r="C992" s="2"/>
-      <c r="D992" s="2"/>
+      <c r="D992" s="50"/>
       <c r="E992" s="2"/>
       <c r="F992" s="2"/>
       <c r="G992" s="2"/>
@@ -30369,7 +30478,7 @@
       <c r="A993" s="2"/>
       <c r="B993" s="2"/>
       <c r="C993" s="2"/>
-      <c r="D993" s="2"/>
+      <c r="D993" s="50"/>
       <c r="E993" s="2"/>
       <c r="F993" s="2"/>
       <c r="G993" s="2"/>
@@ -30397,7 +30506,7 @@
       <c r="A994" s="2"/>
       <c r="B994" s="2"/>
       <c r="C994" s="2"/>
-      <c r="D994" s="2"/>
+      <c r="D994" s="50"/>
       <c r="E994" s="2"/>
       <c r="F994" s="2"/>
       <c r="G994" s="2"/>
@@ -30425,7 +30534,7 @@
       <c r="A995" s="2"/>
       <c r="B995" s="2"/>
       <c r="C995" s="2"/>
-      <c r="D995" s="2"/>
+      <c r="D995" s="50"/>
       <c r="E995" s="2"/>
       <c r="F995" s="2"/>
       <c r="G995" s="2"/>
@@ -30453,7 +30562,7 @@
       <c r="A996" s="2"/>
       <c r="B996" s="2"/>
       <c r="C996" s="2"/>
-      <c r="D996" s="2"/>
+      <c r="D996" s="50"/>
       <c r="E996" s="2"/>
       <c r="F996" s="2"/>
       <c r="G996" s="2"/>
@@ -30481,7 +30590,7 @@
       <c r="A997" s="2"/>
       <c r="B997" s="2"/>
       <c r="C997" s="2"/>
-      <c r="D997" s="2"/>
+      <c r="D997" s="50"/>
       <c r="E997" s="2"/>
       <c r="F997" s="2"/>
       <c r="G997" s="2"/>
@@ -30509,7 +30618,7 @@
       <c r="A998" s="2"/>
       <c r="B998" s="2"/>
       <c r="C998" s="2"/>
-      <c r="D998" s="2"/>
+      <c r="D998" s="50"/>
       <c r="E998" s="2"/>
       <c r="F998" s="2"/>
       <c r="G998" s="2"/>
@@ -30537,7 +30646,7 @@
       <c r="A999" s="2"/>
       <c r="B999" s="2"/>
       <c r="C999" s="2"/>
-      <c r="D999" s="2"/>
+      <c r="D999" s="50"/>
       <c r="E999" s="2"/>
       <c r="F999" s="2"/>
       <c r="G999" s="2"/>
@@ -30565,7 +30674,7 @@
       <c r="A1000" s="2"/>
       <c r="B1000" s="2"/>
       <c r="C1000" s="2"/>
-      <c r="D1000" s="2"/>
+      <c r="D1000" s="50"/>
       <c r="E1000" s="2"/>
       <c r="F1000" s="2"/>
       <c r="G1000" s="2"/>
@@ -30590,6 +30699,7 @@
       <c r="Z1000" s="2"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:Z1000" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -30597,250 +30707,265 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F802CC3A-307A-4FD9-9700-764C18E7FDAA}">
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="16384" width="8.6640625" style="39"/>
+    <col min="1" max="16384" width="8.6640625" style="38"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="25.5">
-      <c r="A1" s="38" t="s">
-        <v>153</v>
+      <c r="A1" s="37" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="25.5">
-      <c r="A3" s="38" t="s">
+      <c r="A3" s="37" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="25.5">
+      <c r="A5" s="37" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="25.5">
+      <c r="A7" s="37" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="17.5">
+      <c r="A8" s="39" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="17.5">
+      <c r="A9" s="39" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="17.5">
+      <c r="A10" s="39" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="17.5">
+      <c r="A11" s="39" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="17.5">
+      <c r="A12" s="40" t="s">
+        <v>259</v>
+      </c>
+      <c r="D12" s="41" t="s">
+        <v>260</v>
+      </c>
+      <c r="E12" s="41" t="s">
+        <v>261</v>
+      </c>
+      <c r="F12" s="41" t="s">
+        <v>262</v>
+      </c>
+      <c r="G12" s="41" t="s">
+        <v>263</v>
+      </c>
+      <c r="H12" s="41" t="s">
+        <v>264</v>
+      </c>
+      <c r="I12" s="41" t="s">
+        <v>274</v>
+      </c>
+      <c r="J12" s="41" t="s">
+        <v>275</v>
+      </c>
+      <c r="K12" s="41" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="17.5">
+      <c r="A13" s="40" t="s">
+        <v>267</v>
+      </c>
+      <c r="B13" s="40" t="s">
+        <v>269</v>
+      </c>
+      <c r="D13" s="41">
+        <v>4</v>
+      </c>
+      <c r="E13" s="41" t="s">
+        <v>265</v>
+      </c>
+      <c r="F13" s="41" t="s">
+        <v>270</v>
+      </c>
+      <c r="G13" s="41" t="s">
+        <v>271</v>
+      </c>
+      <c r="H13" s="41" t="s">
+        <v>271</v>
+      </c>
+      <c r="I13" s="41" t="s">
+        <v>272</v>
+      </c>
+      <c r="J13" s="41" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="17.5">
+      <c r="A14" s="40" t="s">
+        <v>268</v>
+      </c>
+      <c r="B14" s="40" t="s">
+        <v>266</v>
+      </c>
+      <c r="D14" s="41">
+        <v>2</v>
+      </c>
+      <c r="E14" s="41">
+        <v>4</v>
+      </c>
+      <c r="F14" s="41">
+        <v>8</v>
+      </c>
+      <c r="G14" s="41">
+        <v>16</v>
+      </c>
+      <c r="H14" s="41">
+        <v>16</v>
+      </c>
+      <c r="I14" s="41">
+        <v>18</v>
+      </c>
+      <c r="J14" s="41">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="25.5">
+      <c r="A16" s="37" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="17.5">
+      <c r="A17" s="40" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="17.5">
+      <c r="A18" s="39" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="17.5">
+      <c r="A19" s="42" t="s">
+        <v>283</v>
+      </c>
+      <c r="H19" s="39"/>
+    </row>
+    <row r="20" spans="1:8" ht="17.5">
+      <c r="A20" s="39" t="s">
+        <v>288</v>
+      </c>
+      <c r="H20" s="39"/>
+    </row>
+    <row r="21" spans="1:8" ht="17.5">
+      <c r="A21" s="43" t="s">
+        <v>281</v>
+      </c>
+      <c r="H21" s="39"/>
+    </row>
+    <row r="22" spans="1:8" ht="17.5">
+      <c r="A22" s="39" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="17.5">
+      <c r="A23" s="39" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="17.5">
+      <c r="A24" s="39" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="17.5">
+      <c r="A25" s="39" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="25.5">
-      <c r="A5" s="38" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="25.5">
-      <c r="A7" s="38" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="17.5">
-      <c r="A8" s="40" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="17.5">
-      <c r="A9" s="40" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="17.5">
-      <c r="A10" s="40" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="17.5">
-      <c r="A11" s="40" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="17.5">
-      <c r="A12" s="41" t="s">
-        <v>260</v>
-      </c>
-      <c r="D12" s="42" t="s">
-        <v>261</v>
-      </c>
-      <c r="E12" s="42" t="s">
-        <v>262</v>
-      </c>
-      <c r="F12" s="42" t="s">
-        <v>263</v>
-      </c>
-      <c r="G12" s="42" t="s">
-        <v>264</v>
-      </c>
-      <c r="H12" s="42" t="s">
-        <v>265</v>
-      </c>
-      <c r="I12" s="42" t="s">
-        <v>275</v>
-      </c>
-      <c r="J12" s="42" t="s">
-        <v>276</v>
-      </c>
-      <c r="K12" s="42" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="17.5">
-      <c r="A13" s="41" t="s">
-        <v>268</v>
-      </c>
-      <c r="B13" s="41" t="s">
-        <v>270</v>
-      </c>
-      <c r="D13" s="42">
-        <v>4</v>
-      </c>
-      <c r="E13" s="42" t="s">
-        <v>266</v>
-      </c>
-      <c r="F13" s="42" t="s">
-        <v>271</v>
-      </c>
-      <c r="G13" s="42" t="s">
-        <v>272</v>
-      </c>
-      <c r="H13" s="42" t="s">
-        <v>272</v>
-      </c>
-      <c r="I13" s="42" t="s">
-        <v>273</v>
-      </c>
-      <c r="J13" s="42" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="17.5">
-      <c r="A14" s="41" t="s">
-        <v>269</v>
-      </c>
-      <c r="B14" s="41" t="s">
-        <v>267</v>
-      </c>
-      <c r="D14" s="42">
-        <v>2</v>
-      </c>
-      <c r="E14" s="42">
-        <v>4</v>
-      </c>
-      <c r="F14" s="42">
-        <v>8</v>
-      </c>
-      <c r="G14" s="42">
-        <v>16</v>
-      </c>
-      <c r="H14" s="42">
-        <v>16</v>
-      </c>
-      <c r="I14" s="42">
-        <v>18</v>
-      </c>
-      <c r="J14" s="42">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="25.5">
-      <c r="A16" s="38" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="17.5">
-      <c r="A17" s="41" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="17.5">
-      <c r="A18" s="40" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="17.5">
-      <c r="A19" s="43" t="s">
+    <row r="26" spans="1:8" ht="17.5">
+      <c r="A26" s="39" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="17.5">
+      <c r="A27" s="39" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="17.5">
+      <c r="A28" s="39" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="17.5">
+      <c r="A29" s="42" t="s">
         <v>284</v>
       </c>
-      <c r="H19" s="40"/>
-    </row>
-    <row r="20" spans="1:8" ht="17.5">
-      <c r="A20" s="40" t="s">
-        <v>289</v>
-      </c>
-      <c r="H20" s="40"/>
-    </row>
-    <row r="21" spans="1:8" ht="17.5">
-      <c r="A21" s="44" t="s">
+    </row>
+    <row r="30" spans="1:8" ht="17.5">
+      <c r="A30" s="39" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="17.5">
+      <c r="A31" s="43" t="s">
         <v>282</v>
       </c>
-      <c r="H21" s="40"/>
-    </row>
-    <row r="22" spans="1:8" ht="17.5">
-      <c r="A22" s="40" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="17.5">
-      <c r="A23" s="40" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="17.5">
-      <c r="A24" s="40" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="17.5">
-      <c r="A25" s="40" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="17.5">
-      <c r="A26" s="40" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="17.5">
-      <c r="A27" s="40" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="17.5">
-      <c r="A28" s="40" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="17.5">
-      <c r="A29" s="43" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="17.5">
-      <c r="A30" s="40" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="17.5">
-      <c r="A31" s="44" t="s">
-        <v>283</v>
-      </c>
     </row>
     <row r="32" spans="1:8" ht="17.5">
-      <c r="A32" s="44" t="s">
-        <v>290</v>
+      <c r="A32" s="43" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="17.5">
       <c r="A33" s="43" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" ht="17.5">
+      <c r="A34" s="42" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" ht="17.5">
+      <c r="A35" s="39" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" ht="17.5">
+      <c r="A36" s="43" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="34" spans="1:1" ht="17.5">
-      <c r="A34" s="40" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" ht="17.5">
-      <c r="A35" s="44" t="s">
+    <row r="37" spans="1:1" ht="17.5">
+      <c r="A37" s="43" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="36" spans="1:1" ht="17.5">
-      <c r="A36" s="44" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1">
-      <c r="A37" s="45" t="s">
+    <row r="38" spans="1:1">
+      <c r="A38" s="44" t="s">
         <v>293</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="44" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="44" t="s">
+        <v>301</v>
       </c>
     </row>
   </sheetData>
@@ -30851,15 +30976,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3258B9DE-144B-4A1D-96F7-444B72BE7902}">
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="15.58203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="30.58203125" style="1" customWidth="1"/>
     <col min="3" max="3" width="40.83203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.58203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="20.58203125" style="1" customWidth="1"/>
     <col min="5" max="5" width="50.58203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.6640625" style="1" customWidth="1"/>
     <col min="7" max="7" width="10.6640625" style="1" customWidth="1"/>
     <col min="8" max="8" width="16.75" style="1" customWidth="1"/>
     <col min="9" max="9" width="30.58203125" style="1" customWidth="1"/>
@@ -30867,380 +30992,409 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="21">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="B1" s="23" t="s">
         <v>157</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="C1" s="23" t="s">
+        <v>159</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>179</v>
+      </c>
+      <c r="E1" s="23" t="s">
         <v>158</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="F1" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="G1" s="23" t="s">
         <v>160</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="H1" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="I1" s="23" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="56">
+      <c r="A2" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>168</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>182</v>
+      </c>
+      <c r="D2" s="25" t="s">
         <v>180</v>
       </c>
-      <c r="E1" s="24" t="s">
-        <v>159</v>
-      </c>
-      <c r="F1" s="24" t="s">
+      <c r="E2" s="24" t="s">
+        <v>185</v>
+      </c>
+      <c r="F2" s="24" t="s">
         <v>194</v>
       </c>
-      <c r="G1" s="24" t="s">
-        <v>161</v>
-      </c>
-      <c r="H1" s="24" t="s">
-        <v>162</v>
-      </c>
-      <c r="I1" s="24" t="s">
+      <c r="G2" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="H2" s="24" t="s">
+        <v>181</v>
+      </c>
+      <c r="I2" s="24" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="56">
+      <c r="A3" s="18" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" ht="56">
-      <c r="A2" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="B2" s="18" t="s">
+      <c r="B3" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C3" s="26" t="s">
         <v>183</v>
       </c>
-      <c r="D2" s="26" t="s">
-        <v>181</v>
-      </c>
-      <c r="E2" s="25" t="s">
+      <c r="D3" s="27" t="s">
+        <v>184</v>
+      </c>
+      <c r="E3" s="26" t="s">
         <v>186</v>
       </c>
-      <c r="F2" s="25" t="s">
+      <c r="F3" s="26" t="s">
+        <v>194</v>
+      </c>
+      <c r="G3" s="27">
+        <v>4</v>
+      </c>
+      <c r="H3" s="26" t="s">
+        <v>187</v>
+      </c>
+      <c r="I3" s="26" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="56">
+      <c r="A4" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="C4" s="28" t="s">
         <v>195</v>
       </c>
-      <c r="G2" s="26" t="s">
-        <v>179</v>
-      </c>
-      <c r="H2" s="25" t="s">
-        <v>182</v>
-      </c>
-      <c r="I2" s="25" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="56">
-      <c r="A3" s="19" t="s">
+      <c r="D4" s="28" t="s">
+        <v>192</v>
+      </c>
+      <c r="E4" s="28" t="s">
+        <v>196</v>
+      </c>
+      <c r="F4" s="28" t="s">
+        <v>229</v>
+      </c>
+      <c r="G4" s="28">
+        <v>4</v>
+      </c>
+      <c r="H4" s="32" t="s">
+        <v>219</v>
+      </c>
+      <c r="I4" s="28" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="56">
+      <c r="A5" s="19" t="s">
         <v>164</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B5" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>197</v>
+      </c>
+      <c r="D5" s="28" t="s">
+        <v>200</v>
+      </c>
+      <c r="E5" s="28" t="s">
+        <v>203</v>
+      </c>
+      <c r="F5" s="28" t="s">
+        <v>229</v>
+      </c>
+      <c r="G5" s="28">
+        <v>4</v>
+      </c>
+      <c r="H5" s="32" t="s">
+        <v>219</v>
+      </c>
+      <c r="I5" s="28" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="56">
+      <c r="A6" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="C6" s="28" t="s">
+        <v>198</v>
+      </c>
+      <c r="D6" s="28" t="s">
+        <v>201</v>
+      </c>
+      <c r="E6" s="28" t="s">
+        <v>204</v>
+      </c>
+      <c r="F6" s="28" t="s">
+        <v>229</v>
+      </c>
+      <c r="G6" s="28">
+        <v>4</v>
+      </c>
+      <c r="H6" s="32" t="s">
+        <v>219</v>
+      </c>
+      <c r="I6" s="28" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="56">
+      <c r="A7" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="B7" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="C3" s="27" t="s">
-        <v>184</v>
-      </c>
-      <c r="D3" s="28" t="s">
-        <v>185</v>
-      </c>
-      <c r="E3" s="27" t="s">
-        <v>187</v>
-      </c>
-      <c r="F3" s="27" t="s">
-        <v>195</v>
-      </c>
-      <c r="G3" s="28">
+      <c r="C7" s="28" t="s">
+        <v>199</v>
+      </c>
+      <c r="D7" s="28" t="s">
+        <v>202</v>
+      </c>
+      <c r="E7" s="28" t="s">
+        <v>205</v>
+      </c>
+      <c r="F7" s="28" t="s">
+        <v>229</v>
+      </c>
+      <c r="G7" s="28">
         <v>4</v>
       </c>
-      <c r="H3" s="27" t="s">
-        <v>188</v>
-      </c>
-      <c r="I3" s="27" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="56">
-      <c r="A4" s="20" t="s">
+      <c r="H7" s="32" t="s">
+        <v>219</v>
+      </c>
+      <c r="I7" s="28" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="56">
+      <c r="A8" s="20" t="s">
         <v>165</v>
       </c>
-      <c r="B4" s="20" t="s">
-        <v>191</v>
-      </c>
-      <c r="C4" s="29" t="s">
-        <v>196</v>
-      </c>
-      <c r="D4" s="29" t="s">
-        <v>193</v>
-      </c>
-      <c r="E4" s="29" t="s">
-        <v>197</v>
-      </c>
-      <c r="F4" s="29" t="s">
+      <c r="B8" s="20" t="s">
+        <v>173</v>
+      </c>
+      <c r="C8" s="33" t="s">
+        <v>215</v>
+      </c>
+      <c r="D8" s="29" t="s">
+        <v>211</v>
+      </c>
+      <c r="E8" s="29" t="s">
+        <v>213</v>
+      </c>
+      <c r="F8" s="29" t="s">
+        <v>229</v>
+      </c>
+      <c r="G8" s="29">
+        <v>4</v>
+      </c>
+      <c r="H8" s="33" t="s">
+        <v>217</v>
+      </c>
+      <c r="I8" s="33" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="56">
+      <c r="A9" s="20" t="s">
+        <v>165</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>174</v>
+      </c>
+      <c r="C9" s="29" t="s">
+        <v>214</v>
+      </c>
+      <c r="D9" s="29" t="s">
+        <v>210</v>
+      </c>
+      <c r="E9" s="29" t="s">
+        <v>214</v>
+      </c>
+      <c r="F9" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="G9" s="29">
+        <v>4</v>
+      </c>
+      <c r="H9" s="33" t="s">
+        <v>220</v>
+      </c>
+      <c r="I9" s="33" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="56">
+      <c r="A10" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="C10" s="34" t="s">
+        <v>222</v>
+      </c>
+      <c r="D10" s="30" t="s">
+        <v>221</v>
+      </c>
+      <c r="E10" s="34" t="s">
+        <v>223</v>
+      </c>
+      <c r="F10" s="30" t="s">
         <v>230</v>
       </c>
-      <c r="G4" s="29">
+      <c r="G10" s="30">
         <v>4</v>
       </c>
-      <c r="H4" s="33" t="s">
-        <v>220</v>
-      </c>
-      <c r="I4" s="29" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="56">
-      <c r="A5" s="20" t="s">
-        <v>165</v>
-      </c>
-      <c r="B5" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="C5" s="29" t="s">
-        <v>198</v>
-      </c>
-      <c r="D5" s="29" t="s">
-        <v>201</v>
-      </c>
-      <c r="E5" s="29" t="s">
-        <v>204</v>
-      </c>
-      <c r="F5" s="29" t="s">
-        <v>230</v>
-      </c>
-      <c r="G5" s="29">
+      <c r="H10" s="34" t="s">
+        <v>224</v>
+      </c>
+      <c r="I10" s="30" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="56">
+      <c r="A11" s="22" t="s">
+        <v>167</v>
+      </c>
+      <c r="B11" s="22" t="s">
+        <v>176</v>
+      </c>
+      <c r="C11" s="35" t="s">
+        <v>228</v>
+      </c>
+      <c r="D11" s="31" t="s">
+        <v>226</v>
+      </c>
+      <c r="E11" s="35" t="s">
+        <v>231</v>
+      </c>
+      <c r="F11" s="31" t="s">
+        <v>212</v>
+      </c>
+      <c r="G11" s="31">
         <v>4</v>
       </c>
-      <c r="H5" s="33" t="s">
-        <v>220</v>
-      </c>
-      <c r="I5" s="29" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="56">
-      <c r="A6" s="20" t="s">
-        <v>165</v>
-      </c>
-      <c r="B6" s="20" t="s">
-        <v>173</v>
-      </c>
-      <c r="C6" s="29" t="s">
-        <v>199</v>
-      </c>
-      <c r="D6" s="29" t="s">
-        <v>202</v>
-      </c>
-      <c r="E6" s="29" t="s">
-        <v>205</v>
-      </c>
-      <c r="F6" s="29" t="s">
-        <v>230</v>
-      </c>
-      <c r="G6" s="29">
+      <c r="H11" s="35" t="s">
+        <v>243</v>
+      </c>
+      <c r="I11" s="31" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="56">
+      <c r="A12" s="22" t="s">
+        <v>167</v>
+      </c>
+      <c r="B12" s="22" t="s">
+        <v>177</v>
+      </c>
+      <c r="C12" s="35" t="s">
+        <v>232</v>
+      </c>
+      <c r="D12" s="31" t="s">
+        <v>227</v>
+      </c>
+      <c r="E12" s="35" t="s">
+        <v>233</v>
+      </c>
+      <c r="F12" s="31" t="s">
+        <v>212</v>
+      </c>
+      <c r="G12" s="31">
         <v>4</v>
       </c>
-      <c r="H6" s="33" t="s">
-        <v>220</v>
-      </c>
-      <c r="I6" s="29" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="56">
-      <c r="A7" s="20" t="s">
-        <v>165</v>
-      </c>
-      <c r="B7" s="20" t="s">
-        <v>171</v>
-      </c>
-      <c r="C7" s="29" t="s">
-        <v>200</v>
-      </c>
-      <c r="D7" s="29" t="s">
-        <v>203</v>
-      </c>
-      <c r="E7" s="29" t="s">
-        <v>206</v>
-      </c>
-      <c r="F7" s="29" t="s">
-        <v>230</v>
-      </c>
-      <c r="G7" s="29">
+      <c r="H12" s="35" t="s">
+        <v>234</v>
+      </c>
+      <c r="I12" s="31" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="56">
+      <c r="A13" s="22" t="s">
+        <v>167</v>
+      </c>
+      <c r="B13" s="22" t="s">
+        <v>240</v>
+      </c>
+      <c r="C13" s="35" t="s">
+        <v>237</v>
+      </c>
+      <c r="D13" s="31" t="s">
+        <v>239</v>
+      </c>
+      <c r="E13" s="35" t="s">
+        <v>246</v>
+      </c>
+      <c r="F13" s="31" t="s">
+        <v>238</v>
+      </c>
+      <c r="G13" s="31">
         <v>4</v>
       </c>
-      <c r="H7" s="33" t="s">
-        <v>220</v>
-      </c>
-      <c r="I7" s="29" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="56">
-      <c r="A8" s="21" t="s">
-        <v>166</v>
-      </c>
-      <c r="B8" s="21" t="s">
-        <v>174</v>
-      </c>
-      <c r="C8" s="34" t="s">
-        <v>216</v>
-      </c>
-      <c r="D8" s="30" t="s">
-        <v>212</v>
-      </c>
-      <c r="E8" s="30" t="s">
-        <v>214</v>
-      </c>
-      <c r="F8" s="30" t="s">
-        <v>230</v>
-      </c>
-      <c r="G8" s="30">
-        <v>4</v>
-      </c>
-      <c r="H8" s="34" t="s">
-        <v>218</v>
-      </c>
-      <c r="I8" s="34" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="56">
-      <c r="A9" s="21" t="s">
-        <v>166</v>
-      </c>
-      <c r="B9" s="21" t="s">
-        <v>175</v>
-      </c>
-      <c r="C9" s="30" t="s">
-        <v>215</v>
-      </c>
-      <c r="D9" s="30" t="s">
-        <v>211</v>
-      </c>
-      <c r="E9" s="30" t="s">
-        <v>215</v>
-      </c>
-      <c r="F9" s="30" t="s">
-        <v>213</v>
-      </c>
-      <c r="G9" s="30">
-        <v>4</v>
-      </c>
-      <c r="H9" s="34" t="s">
-        <v>221</v>
-      </c>
-      <c r="I9" s="34" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="56">
-      <c r="A10" s="22" t="s">
-        <v>167</v>
-      </c>
-      <c r="B10" s="22" t="s">
-        <v>176</v>
-      </c>
-      <c r="C10" s="35" t="s">
-        <v>223</v>
-      </c>
-      <c r="D10" s="31" t="s">
-        <v>222</v>
-      </c>
-      <c r="E10" s="35" t="s">
-        <v>224</v>
-      </c>
-      <c r="F10" s="31" t="s">
-        <v>231</v>
-      </c>
-      <c r="G10" s="31">
-        <v>4</v>
-      </c>
-      <c r="H10" s="35" t="s">
-        <v>225</v>
-      </c>
-      <c r="I10" s="31" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="56">
-      <c r="A11" s="23" t="s">
-        <v>168</v>
-      </c>
-      <c r="B11" s="23" t="s">
-        <v>177</v>
-      </c>
-      <c r="C11" s="36" t="s">
-        <v>229</v>
-      </c>
-      <c r="D11" s="32" t="s">
-        <v>227</v>
-      </c>
-      <c r="E11" s="36" t="s">
-        <v>232</v>
-      </c>
-      <c r="F11" s="32" t="s">
-        <v>213</v>
-      </c>
-      <c r="G11" s="32">
-        <v>4</v>
-      </c>
-      <c r="H11" s="36" t="s">
-        <v>244</v>
-      </c>
-      <c r="I11" s="32" t="s">
+      <c r="H13" s="35" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" ht="56">
-      <c r="A12" s="23" t="s">
-        <v>168</v>
-      </c>
-      <c r="B12" s="23" t="s">
-        <v>178</v>
-      </c>
-      <c r="C12" s="36" t="s">
-        <v>233</v>
-      </c>
-      <c r="D12" s="32" t="s">
-        <v>228</v>
-      </c>
-      <c r="E12" s="36" t="s">
-        <v>234</v>
-      </c>
-      <c r="F12" s="32" t="s">
-        <v>213</v>
-      </c>
-      <c r="G12" s="32">
-        <v>4</v>
-      </c>
-      <c r="H12" s="36" t="s">
-        <v>235</v>
-      </c>
-      <c r="I12" s="32" t="s">
+      <c r="I13" s="31" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="56">
-      <c r="A13" s="23" t="s">
-        <v>168</v>
-      </c>
-      <c r="B13" s="23" t="s">
-        <v>241</v>
-      </c>
-      <c r="C13" s="36" t="s">
-        <v>238</v>
-      </c>
-      <c r="D13" s="32" t="s">
-        <v>240</v>
-      </c>
-      <c r="E13" s="36" t="s">
-        <v>247</v>
-      </c>
-      <c r="F13" s="32" t="s">
-        <v>239</v>
-      </c>
-      <c r="G13" s="32">
-        <v>4</v>
-      </c>
-      <c r="H13" s="36" t="s">
-        <v>246</v>
-      </c>
-      <c r="I13" s="32" t="s">
-        <v>237</v>
+    <row r="14" spans="1:9" ht="56">
+      <c r="A14" s="45" t="s">
+        <v>291</v>
+      </c>
+      <c r="B14" s="45" t="s">
+        <v>291</v>
+      </c>
+      <c r="C14" s="46" t="s">
+        <v>294</v>
+      </c>
+      <c r="D14" s="47" t="s">
+        <v>295</v>
+      </c>
+      <c r="E14" s="46" t="s">
+        <v>296</v>
+      </c>
+      <c r="F14" s="46" t="s">
+        <v>297</v>
+      </c>
+      <c r="G14" s="47">
+        <v>32</v>
+      </c>
+      <c r="H14" s="46" t="s">
+        <v>298</v>
+      </c>
+      <c r="I14" s="46" t="s">
+        <v>299</v>
       </c>
     </row>
   </sheetData>

--- a/CoreRefiner工作表.xlsx
+++ b/CoreRefiner工作表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_HOME_study\CoreRefiner\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8FAD205-9975-4C63-B1D0-0F95D4086C91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CA46DF8-43A9-4477-BD27-5FC2C9E7D529}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="任务表" sheetId="1" r:id="rId1"/>
@@ -978,10 +978,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>商店区规则：</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>起始价：base =&gt; 1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1221,6 +1217,10 @@
 基础数值取平均值，独有数值保持原样。
 Icon渲染对半分，左半边用主体Icon，右半边用素材Icon。
 详情见Node表。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>买卖区规则：</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4738,7 +4738,7 @@
         <v>75</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>5</v>
@@ -4747,7 +4747,7 @@
         <v>46277</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F76" s="2"/>
       <c r="G76" s="2"/>
@@ -30715,12 +30715,12 @@
   <sheetData>
     <row r="1" spans="1:11" ht="25.5">
       <c r="A1" s="37" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="25.5">
       <c r="A3" s="37" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="25.5">
@@ -30730,93 +30730,93 @@
     </row>
     <row r="7" spans="1:11" ht="25.5">
       <c r="A7" s="37" t="s">
-        <v>247</v>
+        <v>305</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="17.5">
       <c r="A8" s="39" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="17.5">
       <c r="A9" s="39" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="17.5">
       <c r="A10" s="39" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="17.5">
       <c r="A11" s="39" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="17.5">
       <c r="A12" s="40" t="s">
+        <v>258</v>
+      </c>
+      <c r="D12" s="41" t="s">
         <v>259</v>
       </c>
-      <c r="D12" s="41" t="s">
+      <c r="E12" s="41" t="s">
         <v>260</v>
       </c>
-      <c r="E12" s="41" t="s">
+      <c r="F12" s="41" t="s">
         <v>261</v>
       </c>
-      <c r="F12" s="41" t="s">
+      <c r="G12" s="41" t="s">
         <v>262</v>
       </c>
-      <c r="G12" s="41" t="s">
+      <c r="H12" s="41" t="s">
         <v>263</v>
       </c>
-      <c r="H12" s="41" t="s">
-        <v>264</v>
-      </c>
       <c r="I12" s="41" t="s">
+        <v>273</v>
+      </c>
+      <c r="J12" s="41" t="s">
         <v>274</v>
       </c>
-      <c r="J12" s="41" t="s">
+      <c r="K12" s="41" t="s">
         <v>275</v>
-      </c>
-      <c r="K12" s="41" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="17.5">
       <c r="A13" s="40" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B13" s="40" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D13" s="41">
         <v>4</v>
       </c>
       <c r="E13" s="41" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F13" s="41" t="s">
+        <v>269</v>
+      </c>
+      <c r="G13" s="41" t="s">
         <v>270</v>
       </c>
-      <c r="G13" s="41" t="s">
+      <c r="H13" s="41" t="s">
+        <v>270</v>
+      </c>
+      <c r="I13" s="41" t="s">
         <v>271</v>
       </c>
-      <c r="H13" s="41" t="s">
-        <v>271</v>
-      </c>
-      <c r="I13" s="41" t="s">
+      <c r="J13" s="41" t="s">
         <v>272</v>
-      </c>
-      <c r="J13" s="41" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="17.5">
       <c r="A14" s="40" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B14" s="40" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D14" s="41">
         <v>2</v>
@@ -30842,130 +30842,130 @@
     </row>
     <row r="16" spans="1:11" ht="25.5">
       <c r="A16" s="37" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="17.5">
       <c r="A17" s="40" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="17.5">
       <c r="A18" s="39" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="17.5">
       <c r="A19" s="42" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H19" s="39"/>
     </row>
     <row r="20" spans="1:8" ht="17.5">
       <c r="A20" s="39" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H20" s="39"/>
     </row>
     <row r="21" spans="1:8" ht="17.5">
       <c r="A21" s="43" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H21" s="39"/>
     </row>
     <row r="22" spans="1:8" ht="17.5">
       <c r="A22" s="39" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="17.5">
       <c r="A23" s="39" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="17.5">
       <c r="A24" s="39" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="17.5">
       <c r="A25" s="39" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="17.5">
       <c r="A26" s="39" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="17.5">
       <c r="A27" s="39" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="17.5">
       <c r="A28" s="39" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="17.5">
       <c r="A29" s="42" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="17.5">
       <c r="A30" s="39" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="17.5">
       <c r="A31" s="43" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="17.5">
       <c r="A32" s="43" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="17.5">
       <c r="A33" s="43" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="17.5">
       <c r="A34" s="42" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="17.5">
       <c r="A35" s="39" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="36" spans="1:1" ht="17.5">
       <c r="A36" s="43" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="17.5">
       <c r="A37" s="43" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="44" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="44" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="44" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
   </sheetData>
@@ -31370,31 +31370,31 @@
     </row>
     <row r="14" spans="1:9" ht="56">
       <c r="A14" s="45" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B14" s="45" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C14" s="46" t="s">
+        <v>293</v>
+      </c>
+      <c r="D14" s="47" t="s">
         <v>294</v>
       </c>
-      <c r="D14" s="47" t="s">
+      <c r="E14" s="46" t="s">
         <v>295</v>
       </c>
-      <c r="E14" s="46" t="s">
+      <c r="F14" s="46" t="s">
         <v>296</v>
-      </c>
-      <c r="F14" s="46" t="s">
-        <v>297</v>
       </c>
       <c r="G14" s="47">
         <v>32</v>
       </c>
       <c r="H14" s="46" t="s">
+        <v>297</v>
+      </c>
+      <c r="I14" s="46" t="s">
         <v>298</v>
-      </c>
-      <c r="I14" s="46" t="s">
-        <v>299</v>
       </c>
     </row>
   </sheetData>

--- a/CoreRefiner工作表.xlsx
+++ b/CoreRefiner工作表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_HOME_study\CoreRefiner\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CA46DF8-43A9-4477-BD27-5FC2C9E7D529}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{167528C0-8BE8-4FB4-AC8D-F84E32EA987D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="314">
   <si>
     <t>内容详情</t>
   </si>
@@ -592,10 +592,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>价格</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>基础数值</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -659,10 +655,6 @@
   </si>
   <si>
     <t>Other_Revive</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>无</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -998,30 +990,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[1级] -&gt; [1级] =&gt; [2级]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[2级] -&gt; [1级] =&gt; [2级]+退回4元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[3级] -&gt; [1级] =&gt; [3级]+退回4元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[2级] -&gt; [2级] =&gt; [3级]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[3级] -&gt; [2级] =&gt; [3级]+退回8元</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[3级]无升级需求</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>买卖规则：</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1047,22 +1015,6 @@
   </si>
   <si>
     <t>8+1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>造价 / 2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>成本 =</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>收入 =</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>造价 + 炼成</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1094,27 +1046,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>升级、合成、进化 均价 = 1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>展现：[素材] -&gt; [主体] =&gt; [结果]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Node等级上限为3级</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[1级] -&gt; [2级] =&gt; 不成立</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>成立标准：主体等级 &lt;= 素材等级</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>成立标准：主体等级 = 素材等级 = 3级</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1127,10 +1063,6 @@
   </si>
   <si>
     <t>进化情况说明：</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>成立标准：主体等级 = 素材等级 = 3级，并且此两者符合进化表的炼成需求</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1155,10 +1087,6 @@
   </si>
   <si>
     <t>结果为一个3级的合成类Node。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>*注1：Core类不参与除了升级外，任何Shop区内的事情，Core升级到3级后就和一切炼成区的事情没关系了。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1196,10 +1124,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>*注3：类型相同的Node只有可能升级，不能用于合成和进化。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>*注2：Core类永远不会成为素材。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1223,12 +1147,120 @@
     <t>买卖区规则：</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>退回情况说明：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>规则说明：把主体栏和素材栏的Node退回到原来的位置。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>成立标准：主体栏或素材栏有Node。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>成立标准：主体等级 = 素材等级 = 3级，结果栏中为空，拥有至少1元。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>成立标准：主体等级 = 素材等级 = 3级，并且此两者符合进化表的炼成需求，结果栏中为空，拥有至少1元。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>成立标准：主体等级 &lt;= 素材等级，结果栏中为空，拥有至少1元。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>升级、合成、进化价格：使用时必须支出1元，此为固定支出，与Node的造价无关。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>炼成区成功启动后，最终炼成的Node出现在结果栏。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>*注1：Core类有且只有可能成为升级的主体，除此之外不参与任何Shop区内的事情，Core升级到3级后，就和一切炼成区的事情没关系了。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>*注4：Label相同的Node不能被用于合成和进化，只可能有一方成为另一方的素材。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>基础情况说明：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Node只能被拖入拖出素材栏和主体栏，结果栏只能被拖出，无法被拖入。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>补充情况说明：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>*注：买卖区无法刷出需要进化才能获得的Node。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>成本 = 造价 + 炼成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>收入 = 造价 / 2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获取途径</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>游戏开始</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>商店买卖区：4元</t>
+  </si>
+  <si>
+    <t>商店买卖区：4元</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>商店炼成区合成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>商店炼成区进化：
+Other_Child + Other_Repeat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>升级后，素材消失，而主体依然存在，所以完成升级后虽然Node会出现在结果栏，但是仓库区或者扫描区的阴影仍然应该存在。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>退回的是素材溢出的价值,例如“[2级] -&gt; [1级] =&gt; [2级]+退回4元”中，[1级]只需要一个[1级]就能升到[2级]，所以当使用[2级]为一级升级的时候，那么就溢出了4元的价值，需要退回给玩家。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>*注3：Fusion类永远无法再次进入主体栏，它可以成为升级素材，但不能参与合成和进化。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>升级规则：[等级&gt;=主体等级的素材] -&gt; [等级&lt;3级的Node] =&gt; [max(主体等级+1，素材等级)]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>结果造价 = 素材造价 + 主体造价</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1304,12 +1336,6 @@
     </font>
     <font>
       <sz val="14"/>
-      <color theme="1"/>
-      <name val="黑体"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
       <color theme="1"/>
       <name val="黑体"/>
     </font>
@@ -1450,7 +1476,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1565,14 +1591,13 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1885,9 +1910,9 @@
   <sheetFormatPr defaultColWidth="19.58203125" defaultRowHeight="21"/>
   <cols>
     <col min="1" max="1" width="15.58203125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="40.58203125" style="53" customWidth="1"/>
+    <col min="2" max="2" width="40.58203125" style="52" customWidth="1"/>
     <col min="3" max="3" width="15.58203125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="20.58203125" style="51" customWidth="1"/>
+    <col min="4" max="4" width="20.58203125" style="50" customWidth="1"/>
     <col min="5" max="5" width="120.58203125" style="3" customWidth="1"/>
     <col min="6" max="16384" width="19.58203125" style="3"/>
   </cols>
@@ -1896,13 +1921,13 @@
       <c r="A1" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="B1" s="52" t="s">
+      <c r="B1" s="51" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="48" t="s">
+      <c r="D1" s="47" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="5" t="s">
@@ -4481,7 +4506,7 @@
         <v>46266</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
@@ -4709,7 +4734,7 @@
         <v>46276</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F75" s="2"/>
       <c r="G75" s="2"/>
@@ -4738,7 +4763,7 @@
         <v>75</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>302</v>
+        <v>283</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>5</v>
@@ -4747,7 +4772,7 @@
         <v>46277</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>304</v>
+        <v>285</v>
       </c>
       <c r="F76" s="2"/>
       <c r="G76" s="2"/>
@@ -4779,7 +4804,7 @@
         <v>146</v>
       </c>
       <c r="C77" s="16"/>
-      <c r="D77" s="49"/>
+      <c r="D77" s="48"/>
       <c r="E77" s="16"/>
       <c r="F77" s="2"/>
       <c r="G77" s="2"/>
@@ -4809,7 +4834,7 @@
       </c>
       <c r="B78" s="16"/>
       <c r="C78" s="16"/>
-      <c r="D78" s="49"/>
+      <c r="D78" s="48"/>
       <c r="E78" s="16"/>
       <c r="F78" s="2"/>
       <c r="G78" s="2"/>
@@ -4839,7 +4864,7 @@
       </c>
       <c r="B79" s="16"/>
       <c r="C79" s="16"/>
-      <c r="D79" s="49"/>
+      <c r="D79" s="48"/>
       <c r="E79" s="16"/>
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
@@ -4869,7 +4894,7 @@
       </c>
       <c r="B80" s="16"/>
       <c r="C80" s="16"/>
-      <c r="D80" s="49"/>
+      <c r="D80" s="48"/>
       <c r="E80" s="16"/>
       <c r="F80" s="2"/>
       <c r="G80" s="2"/>
@@ -4899,7 +4924,7 @@
       </c>
       <c r="B81" s="16"/>
       <c r="C81" s="16"/>
-      <c r="D81" s="49"/>
+      <c r="D81" s="48"/>
       <c r="E81" s="16"/>
       <c r="F81" s="2"/>
       <c r="G81" s="2"/>
@@ -4929,7 +4954,7 @@
       </c>
       <c r="B82" s="16"/>
       <c r="C82" s="16"/>
-      <c r="D82" s="49"/>
+      <c r="D82" s="48"/>
       <c r="E82" s="16"/>
       <c r="F82" s="2"/>
       <c r="G82" s="2"/>
@@ -4959,7 +4984,7 @@
       </c>
       <c r="B83" s="16"/>
       <c r="C83" s="16"/>
-      <c r="D83" s="49"/>
+      <c r="D83" s="48"/>
       <c r="E83" s="16"/>
       <c r="F83" s="2"/>
       <c r="G83" s="2"/>
@@ -4989,7 +5014,7 @@
       </c>
       <c r="B84" s="16"/>
       <c r="C84" s="16"/>
-      <c r="D84" s="49"/>
+      <c r="D84" s="48"/>
       <c r="E84" s="16"/>
       <c r="F84" s="2"/>
       <c r="G84" s="2"/>
@@ -5018,7 +5043,7 @@
         <v>84</v>
       </c>
       <c r="C85" s="16"/>
-      <c r="D85" s="49"/>
+      <c r="D85" s="48"/>
       <c r="E85" s="16"/>
       <c r="F85" s="2"/>
       <c r="G85" s="2"/>
@@ -5050,7 +5075,7 @@
         <v>147</v>
       </c>
       <c r="C86" s="16"/>
-      <c r="D86" s="49"/>
+      <c r="D86" s="48"/>
       <c r="E86" s="16"/>
       <c r="F86" s="2"/>
       <c r="G86" s="2"/>
@@ -5082,7 +5107,7 @@
         <v>154</v>
       </c>
       <c r="C87" s="16"/>
-      <c r="D87" s="49"/>
+      <c r="D87" s="48"/>
       <c r="E87" s="16"/>
       <c r="F87" s="2"/>
       <c r="G87" s="2"/>
@@ -5112,7 +5137,7 @@
       </c>
       <c r="B88" s="16"/>
       <c r="C88" s="16"/>
-      <c r="D88" s="49"/>
+      <c r="D88" s="48"/>
       <c r="E88" s="16"/>
       <c r="F88" s="2"/>
       <c r="G88" s="2"/>
@@ -5142,7 +5167,7 @@
       </c>
       <c r="B89" s="16"/>
       <c r="C89" s="16"/>
-      <c r="D89" s="49"/>
+      <c r="D89" s="48"/>
       <c r="E89" s="16"/>
       <c r="F89" s="2"/>
       <c r="G89" s="2"/>
@@ -5172,7 +5197,7 @@
       </c>
       <c r="B90" s="16"/>
       <c r="C90" s="16"/>
-      <c r="D90" s="49"/>
+      <c r="D90" s="48"/>
       <c r="E90" s="16"/>
       <c r="F90" s="2"/>
       <c r="G90" s="2"/>
@@ -5202,7 +5227,7 @@
       </c>
       <c r="B91" s="16"/>
       <c r="C91" s="16"/>
-      <c r="D91" s="49"/>
+      <c r="D91" s="48"/>
       <c r="E91" s="16"/>
       <c r="F91" s="2"/>
       <c r="G91" s="2"/>
@@ -5232,7 +5257,7 @@
       </c>
       <c r="B92" s="16"/>
       <c r="C92" s="16"/>
-      <c r="D92" s="49"/>
+      <c r="D92" s="48"/>
       <c r="E92" s="16"/>
       <c r="F92" s="2"/>
       <c r="G92" s="2"/>
@@ -5262,7 +5287,7 @@
       </c>
       <c r="B93" s="16"/>
       <c r="C93" s="16"/>
-      <c r="D93" s="49"/>
+      <c r="D93" s="48"/>
       <c r="E93" s="16"/>
       <c r="F93" s="2"/>
       <c r="G93" s="2"/>
@@ -5292,7 +5317,7 @@
       </c>
       <c r="B94" s="16"/>
       <c r="C94" s="16"/>
-      <c r="D94" s="49"/>
+      <c r="D94" s="48"/>
       <c r="E94" s="16"/>
       <c r="F94" s="2"/>
       <c r="G94" s="2"/>
@@ -5322,7 +5347,7 @@
       </c>
       <c r="B95" s="16"/>
       <c r="C95" s="16"/>
-      <c r="D95" s="49"/>
+      <c r="D95" s="48"/>
       <c r="E95" s="16"/>
       <c r="F95" s="2"/>
       <c r="G95" s="2"/>
@@ -5352,7 +5377,7 @@
       </c>
       <c r="B96" s="16"/>
       <c r="C96" s="16"/>
-      <c r="D96" s="49"/>
+      <c r="D96" s="48"/>
       <c r="E96" s="16"/>
       <c r="F96" s="2"/>
       <c r="G96" s="2"/>
@@ -5382,7 +5407,7 @@
       </c>
       <c r="B97" s="16"/>
       <c r="C97" s="16"/>
-      <c r="D97" s="49"/>
+      <c r="D97" s="48"/>
       <c r="E97" s="16"/>
       <c r="F97" s="2"/>
       <c r="G97" s="2"/>
@@ -5412,7 +5437,7 @@
       </c>
       <c r="B98" s="16"/>
       <c r="C98" s="16"/>
-      <c r="D98" s="49"/>
+      <c r="D98" s="48"/>
       <c r="E98" s="16"/>
       <c r="F98" s="2"/>
       <c r="G98" s="2"/>
@@ -5442,7 +5467,7 @@
       </c>
       <c r="B99" s="16"/>
       <c r="C99" s="16"/>
-      <c r="D99" s="49"/>
+      <c r="D99" s="48"/>
       <c r="E99" s="16"/>
       <c r="F99" s="2"/>
       <c r="G99" s="2"/>
@@ -5472,7 +5497,7 @@
       </c>
       <c r="B100" s="16"/>
       <c r="C100" s="16"/>
-      <c r="D100" s="49"/>
+      <c r="D100" s="48"/>
       <c r="E100" s="16"/>
       <c r="F100" s="2"/>
       <c r="G100" s="2"/>
@@ -5502,7 +5527,7 @@
       </c>
       <c r="B101" s="16"/>
       <c r="C101" s="16"/>
-      <c r="D101" s="49"/>
+      <c r="D101" s="48"/>
       <c r="E101" s="16"/>
       <c r="F101" s="2"/>
       <c r="G101" s="2"/>
@@ -5530,7 +5555,7 @@
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
-      <c r="D102" s="50"/>
+      <c r="D102" s="49"/>
       <c r="E102" s="2"/>
       <c r="F102" s="2"/>
       <c r="G102" s="2"/>
@@ -5558,7 +5583,7 @@
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
-      <c r="D103" s="50"/>
+      <c r="D103" s="49"/>
       <c r="E103" s="2"/>
       <c r="F103" s="2"/>
       <c r="G103" s="2"/>
@@ -5586,7 +5611,7 @@
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
-      <c r="D104" s="50"/>
+      <c r="D104" s="49"/>
       <c r="E104" s="2"/>
       <c r="F104" s="2"/>
       <c r="G104" s="2"/>
@@ -5614,7 +5639,7 @@
       <c r="A105" s="2"/>
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
-      <c r="D105" s="50"/>
+      <c r="D105" s="49"/>
       <c r="E105" s="2"/>
       <c r="F105" s="2"/>
       <c r="G105" s="2"/>
@@ -5642,7 +5667,7 @@
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
-      <c r="D106" s="50"/>
+      <c r="D106" s="49"/>
       <c r="E106" s="2"/>
       <c r="F106" s="2"/>
       <c r="G106" s="2"/>
@@ -5670,7 +5695,7 @@
       <c r="A107" s="2"/>
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
-      <c r="D107" s="50"/>
+      <c r="D107" s="49"/>
       <c r="E107" s="2"/>
       <c r="F107" s="2"/>
       <c r="G107" s="2"/>
@@ -5698,7 +5723,7 @@
       <c r="A108" s="2"/>
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
-      <c r="D108" s="50"/>
+      <c r="D108" s="49"/>
       <c r="E108" s="2"/>
       <c r="F108" s="2"/>
       <c r="G108" s="2"/>
@@ -5726,7 +5751,7 @@
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="2"/>
-      <c r="D109" s="50"/>
+      <c r="D109" s="49"/>
       <c r="E109" s="2"/>
       <c r="F109" s="2"/>
       <c r="G109" s="2"/>
@@ -5754,7 +5779,7 @@
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="2"/>
-      <c r="D110" s="50"/>
+      <c r="D110" s="49"/>
       <c r="E110" s="2"/>
       <c r="F110" s="2"/>
       <c r="G110" s="2"/>
@@ -5782,7 +5807,7 @@
       <c r="A111" s="2"/>
       <c r="B111" s="2"/>
       <c r="C111" s="2"/>
-      <c r="D111" s="50"/>
+      <c r="D111" s="49"/>
       <c r="E111" s="2"/>
       <c r="F111" s="2"/>
       <c r="G111" s="2"/>
@@ -5810,7 +5835,7 @@
       <c r="A112" s="2"/>
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
-      <c r="D112" s="50"/>
+      <c r="D112" s="49"/>
       <c r="E112" s="2"/>
       <c r="F112" s="2"/>
       <c r="G112" s="2"/>
@@ -5838,7 +5863,7 @@
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="2"/>
-      <c r="D113" s="50"/>
+      <c r="D113" s="49"/>
       <c r="E113" s="2"/>
       <c r="F113" s="2"/>
       <c r="G113" s="2"/>
@@ -5866,7 +5891,7 @@
       <c r="A114" s="2"/>
       <c r="B114" s="2"/>
       <c r="C114" s="2"/>
-      <c r="D114" s="50"/>
+      <c r="D114" s="49"/>
       <c r="E114" s="2"/>
       <c r="F114" s="2"/>
       <c r="G114" s="2"/>
@@ -5894,7 +5919,7 @@
       <c r="A115" s="2"/>
       <c r="B115" s="2"/>
       <c r="C115" s="2"/>
-      <c r="D115" s="50"/>
+      <c r="D115" s="49"/>
       <c r="E115" s="2"/>
       <c r="F115" s="2"/>
       <c r="G115" s="2"/>
@@ -5922,7 +5947,7 @@
       <c r="A116" s="2"/>
       <c r="B116" s="2"/>
       <c r="C116" s="2"/>
-      <c r="D116" s="50"/>
+      <c r="D116" s="49"/>
       <c r="E116" s="2"/>
       <c r="F116" s="2"/>
       <c r="G116" s="2"/>
@@ -5950,7 +5975,7 @@
       <c r="A117" s="2"/>
       <c r="B117" s="2"/>
       <c r="C117" s="2"/>
-      <c r="D117" s="50"/>
+      <c r="D117" s="49"/>
       <c r="E117" s="2"/>
       <c r="F117" s="2"/>
       <c r="G117" s="2"/>
@@ -5978,7 +6003,7 @@
       <c r="A118" s="2"/>
       <c r="B118" s="2"/>
       <c r="C118" s="2"/>
-      <c r="D118" s="50"/>
+      <c r="D118" s="49"/>
       <c r="E118" s="2"/>
       <c r="F118" s="2"/>
       <c r="G118" s="2"/>
@@ -6006,7 +6031,7 @@
       <c r="A119" s="2"/>
       <c r="B119" s="2"/>
       <c r="C119" s="2"/>
-      <c r="D119" s="50"/>
+      <c r="D119" s="49"/>
       <c r="E119" s="2"/>
       <c r="F119" s="2"/>
       <c r="G119" s="2"/>
@@ -6034,7 +6059,7 @@
       <c r="A120" s="2"/>
       <c r="B120" s="2"/>
       <c r="C120" s="2"/>
-      <c r="D120" s="50"/>
+      <c r="D120" s="49"/>
       <c r="E120" s="2"/>
       <c r="F120" s="2"/>
       <c r="G120" s="2"/>
@@ -6062,7 +6087,7 @@
       <c r="A121" s="2"/>
       <c r="B121" s="2"/>
       <c r="C121" s="2"/>
-      <c r="D121" s="50"/>
+      <c r="D121" s="49"/>
       <c r="E121" s="2"/>
       <c r="F121" s="2"/>
       <c r="G121" s="2"/>
@@ -6090,7 +6115,7 @@
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="C122" s="2"/>
-      <c r="D122" s="50"/>
+      <c r="D122" s="49"/>
       <c r="E122" s="2"/>
       <c r="F122" s="2"/>
       <c r="G122" s="2"/>
@@ -6118,7 +6143,7 @@
       <c r="A123" s="2"/>
       <c r="B123" s="2"/>
       <c r="C123" s="2"/>
-      <c r="D123" s="50"/>
+      <c r="D123" s="49"/>
       <c r="E123" s="2"/>
       <c r="F123" s="2"/>
       <c r="G123" s="2"/>
@@ -6146,7 +6171,7 @@
       <c r="A124" s="2"/>
       <c r="B124" s="2"/>
       <c r="C124" s="2"/>
-      <c r="D124" s="50"/>
+      <c r="D124" s="49"/>
       <c r="E124" s="2"/>
       <c r="F124" s="2"/>
       <c r="G124" s="2"/>
@@ -6174,7 +6199,7 @@
       <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="C125" s="2"/>
-      <c r="D125" s="50"/>
+      <c r="D125" s="49"/>
       <c r="E125" s="2"/>
       <c r="F125" s="2"/>
       <c r="G125" s="2"/>
@@ -6202,7 +6227,7 @@
       <c r="A126" s="2"/>
       <c r="B126" s="2"/>
       <c r="C126" s="2"/>
-      <c r="D126" s="50"/>
+      <c r="D126" s="49"/>
       <c r="E126" s="2"/>
       <c r="F126" s="2"/>
       <c r="G126" s="2"/>
@@ -6230,7 +6255,7 @@
       <c r="A127" s="2"/>
       <c r="B127" s="2"/>
       <c r="C127" s="2"/>
-      <c r="D127" s="50"/>
+      <c r="D127" s="49"/>
       <c r="E127" s="2"/>
       <c r="F127" s="2"/>
       <c r="G127" s="2"/>
@@ -6258,7 +6283,7 @@
       <c r="A128" s="2"/>
       <c r="B128" s="2"/>
       <c r="C128" s="2"/>
-      <c r="D128" s="50"/>
+      <c r="D128" s="49"/>
       <c r="E128" s="2"/>
       <c r="F128" s="2"/>
       <c r="G128" s="2"/>
@@ -6286,7 +6311,7 @@
       <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="C129" s="2"/>
-      <c r="D129" s="50"/>
+      <c r="D129" s="49"/>
       <c r="E129" s="2"/>
       <c r="F129" s="2"/>
       <c r="G129" s="2"/>
@@ -6314,7 +6339,7 @@
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="2"/>
-      <c r="D130" s="50"/>
+      <c r="D130" s="49"/>
       <c r="E130" s="2"/>
       <c r="F130" s="2"/>
       <c r="G130" s="2"/>
@@ -6342,7 +6367,7 @@
       <c r="A131" s="2"/>
       <c r="B131" s="2"/>
       <c r="C131" s="2"/>
-      <c r="D131" s="50"/>
+      <c r="D131" s="49"/>
       <c r="E131" s="2"/>
       <c r="F131" s="2"/>
       <c r="G131" s="2"/>
@@ -6370,7 +6395,7 @@
       <c r="A132" s="2"/>
       <c r="B132" s="2"/>
       <c r="C132" s="2"/>
-      <c r="D132" s="50"/>
+      <c r="D132" s="49"/>
       <c r="E132" s="2"/>
       <c r="F132" s="2"/>
       <c r="G132" s="2"/>
@@ -6398,7 +6423,7 @@
       <c r="A133" s="2"/>
       <c r="B133" s="2"/>
       <c r="C133" s="2"/>
-      <c r="D133" s="50"/>
+      <c r="D133" s="49"/>
       <c r="E133" s="2"/>
       <c r="F133" s="2"/>
       <c r="G133" s="2"/>
@@ -6426,7 +6451,7 @@
       <c r="A134" s="2"/>
       <c r="B134" s="2"/>
       <c r="C134" s="2"/>
-      <c r="D134" s="50"/>
+      <c r="D134" s="49"/>
       <c r="E134" s="2"/>
       <c r="F134" s="2"/>
       <c r="G134" s="2"/>
@@ -6454,7 +6479,7 @@
       <c r="A135" s="2"/>
       <c r="B135" s="2"/>
       <c r="C135" s="2"/>
-      <c r="D135" s="50"/>
+      <c r="D135" s="49"/>
       <c r="E135" s="2"/>
       <c r="F135" s="2"/>
       <c r="G135" s="2"/>
@@ -6482,7 +6507,7 @@
       <c r="A136" s="2"/>
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
-      <c r="D136" s="50"/>
+      <c r="D136" s="49"/>
       <c r="E136" s="2"/>
       <c r="F136" s="2"/>
       <c r="G136" s="2"/>
@@ -6510,7 +6535,7 @@
       <c r="A137" s="2"/>
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
-      <c r="D137" s="50"/>
+      <c r="D137" s="49"/>
       <c r="E137" s="2"/>
       <c r="F137" s="2"/>
       <c r="G137" s="2"/>
@@ -6538,7 +6563,7 @@
       <c r="A138" s="2"/>
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
-      <c r="D138" s="50"/>
+      <c r="D138" s="49"/>
       <c r="E138" s="2"/>
       <c r="F138" s="2"/>
       <c r="G138" s="2"/>
@@ -6566,7 +6591,7 @@
       <c r="A139" s="2"/>
       <c r="B139" s="2"/>
       <c r="C139" s="2"/>
-      <c r="D139" s="50"/>
+      <c r="D139" s="49"/>
       <c r="E139" s="2"/>
       <c r="F139" s="2"/>
       <c r="G139" s="2"/>
@@ -6594,7 +6619,7 @@
       <c r="A140" s="2"/>
       <c r="B140" s="2"/>
       <c r="C140" s="2"/>
-      <c r="D140" s="50"/>
+      <c r="D140" s="49"/>
       <c r="E140" s="2"/>
       <c r="F140" s="2"/>
       <c r="G140" s="2"/>
@@ -6622,7 +6647,7 @@
       <c r="A141" s="2"/>
       <c r="B141" s="2"/>
       <c r="C141" s="2"/>
-      <c r="D141" s="50"/>
+      <c r="D141" s="49"/>
       <c r="E141" s="2"/>
       <c r="F141" s="2"/>
       <c r="G141" s="2"/>
@@ -6650,7 +6675,7 @@
       <c r="A142" s="2"/>
       <c r="B142" s="2"/>
       <c r="C142" s="2"/>
-      <c r="D142" s="50"/>
+      <c r="D142" s="49"/>
       <c r="E142" s="2"/>
       <c r="F142" s="2"/>
       <c r="G142" s="2"/>
@@ -6678,7 +6703,7 @@
       <c r="A143" s="2"/>
       <c r="B143" s="2"/>
       <c r="C143" s="2"/>
-      <c r="D143" s="50"/>
+      <c r="D143" s="49"/>
       <c r="E143" s="2"/>
       <c r="F143" s="2"/>
       <c r="G143" s="2"/>
@@ -6706,7 +6731,7 @@
       <c r="A144" s="2"/>
       <c r="B144" s="2"/>
       <c r="C144" s="2"/>
-      <c r="D144" s="50"/>
+      <c r="D144" s="49"/>
       <c r="E144" s="2"/>
       <c r="F144" s="2"/>
       <c r="G144" s="2"/>
@@ -6734,7 +6759,7 @@
       <c r="A145" s="2"/>
       <c r="B145" s="2"/>
       <c r="C145" s="2"/>
-      <c r="D145" s="50"/>
+      <c r="D145" s="49"/>
       <c r="E145" s="2"/>
       <c r="F145" s="2"/>
       <c r="G145" s="2"/>
@@ -6762,7 +6787,7 @@
       <c r="A146" s="2"/>
       <c r="B146" s="2"/>
       <c r="C146" s="2"/>
-      <c r="D146" s="50"/>
+      <c r="D146" s="49"/>
       <c r="E146" s="2"/>
       <c r="F146" s="2"/>
       <c r="G146" s="2"/>
@@ -6790,7 +6815,7 @@
       <c r="A147" s="2"/>
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
-      <c r="D147" s="50"/>
+      <c r="D147" s="49"/>
       <c r="E147" s="2"/>
       <c r="F147" s="2"/>
       <c r="G147" s="2"/>
@@ -6818,7 +6843,7 @@
       <c r="A148" s="2"/>
       <c r="B148" s="2"/>
       <c r="C148" s="2"/>
-      <c r="D148" s="50"/>
+      <c r="D148" s="49"/>
       <c r="E148" s="2"/>
       <c r="F148" s="2"/>
       <c r="G148" s="2"/>
@@ -6846,7 +6871,7 @@
       <c r="A149" s="2"/>
       <c r="B149" s="2"/>
       <c r="C149" s="2"/>
-      <c r="D149" s="50"/>
+      <c r="D149" s="49"/>
       <c r="E149" s="2"/>
       <c r="F149" s="2"/>
       <c r="G149" s="2"/>
@@ -6874,7 +6899,7 @@
       <c r="A150" s="2"/>
       <c r="B150" s="2"/>
       <c r="C150" s="2"/>
-      <c r="D150" s="50"/>
+      <c r="D150" s="49"/>
       <c r="E150" s="2"/>
       <c r="F150" s="2"/>
       <c r="G150" s="2"/>
@@ -6902,7 +6927,7 @@
       <c r="A151" s="2"/>
       <c r="B151" s="2"/>
       <c r="C151" s="2"/>
-      <c r="D151" s="50"/>
+      <c r="D151" s="49"/>
       <c r="E151" s="2"/>
       <c r="F151" s="2"/>
       <c r="G151" s="2"/>
@@ -6930,7 +6955,7 @@
       <c r="A152" s="2"/>
       <c r="B152" s="2"/>
       <c r="C152" s="2"/>
-      <c r="D152" s="50"/>
+      <c r="D152" s="49"/>
       <c r="E152" s="2"/>
       <c r="F152" s="2"/>
       <c r="G152" s="2"/>
@@ -6958,7 +6983,7 @@
       <c r="A153" s="2"/>
       <c r="B153" s="2"/>
       <c r="C153" s="2"/>
-      <c r="D153" s="50"/>
+      <c r="D153" s="49"/>
       <c r="E153" s="2"/>
       <c r="F153" s="2"/>
       <c r="G153" s="2"/>
@@ -6986,7 +7011,7 @@
       <c r="A154" s="2"/>
       <c r="B154" s="2"/>
       <c r="C154" s="2"/>
-      <c r="D154" s="50"/>
+      <c r="D154" s="49"/>
       <c r="E154" s="2"/>
       <c r="F154" s="2"/>
       <c r="G154" s="2"/>
@@ -7014,7 +7039,7 @@
       <c r="A155" s="2"/>
       <c r="B155" s="2"/>
       <c r="C155" s="2"/>
-      <c r="D155" s="50"/>
+      <c r="D155" s="49"/>
       <c r="E155" s="2"/>
       <c r="F155" s="2"/>
       <c r="G155" s="2"/>
@@ -7042,7 +7067,7 @@
       <c r="A156" s="2"/>
       <c r="B156" s="2"/>
       <c r="C156" s="2"/>
-      <c r="D156" s="50"/>
+      <c r="D156" s="49"/>
       <c r="E156" s="2"/>
       <c r="F156" s="2"/>
       <c r="G156" s="2"/>
@@ -7070,7 +7095,7 @@
       <c r="A157" s="2"/>
       <c r="B157" s="2"/>
       <c r="C157" s="2"/>
-      <c r="D157" s="50"/>
+      <c r="D157" s="49"/>
       <c r="E157" s="2"/>
       <c r="F157" s="2"/>
       <c r="G157" s="2"/>
@@ -7098,7 +7123,7 @@
       <c r="A158" s="2"/>
       <c r="B158" s="2"/>
       <c r="C158" s="2"/>
-      <c r="D158" s="50"/>
+      <c r="D158" s="49"/>
       <c r="E158" s="2"/>
       <c r="F158" s="2"/>
       <c r="G158" s="2"/>
@@ -7126,7 +7151,7 @@
       <c r="A159" s="2"/>
       <c r="B159" s="2"/>
       <c r="C159" s="2"/>
-      <c r="D159" s="50"/>
+      <c r="D159" s="49"/>
       <c r="E159" s="2"/>
       <c r="F159" s="2"/>
       <c r="G159" s="2"/>
@@ -7154,7 +7179,7 @@
       <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="C160" s="2"/>
-      <c r="D160" s="50"/>
+      <c r="D160" s="49"/>
       <c r="E160" s="2"/>
       <c r="F160" s="2"/>
       <c r="G160" s="2"/>
@@ -7182,7 +7207,7 @@
       <c r="A161" s="2"/>
       <c r="B161" s="2"/>
       <c r="C161" s="2"/>
-      <c r="D161" s="50"/>
+      <c r="D161" s="49"/>
       <c r="E161" s="2"/>
       <c r="F161" s="2"/>
       <c r="G161" s="2"/>
@@ -7210,7 +7235,7 @@
       <c r="A162" s="2"/>
       <c r="B162" s="2"/>
       <c r="C162" s="2"/>
-      <c r="D162" s="50"/>
+      <c r="D162" s="49"/>
       <c r="E162" s="2"/>
       <c r="F162" s="2"/>
       <c r="G162" s="2"/>
@@ -7238,7 +7263,7 @@
       <c r="A163" s="2"/>
       <c r="B163" s="2"/>
       <c r="C163" s="2"/>
-      <c r="D163" s="50"/>
+      <c r="D163" s="49"/>
       <c r="E163" s="2"/>
       <c r="F163" s="2"/>
       <c r="G163" s="2"/>
@@ -7266,7 +7291,7 @@
       <c r="A164" s="2"/>
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
-      <c r="D164" s="50"/>
+      <c r="D164" s="49"/>
       <c r="E164" s="2"/>
       <c r="F164" s="2"/>
       <c r="G164" s="2"/>
@@ -7294,7 +7319,7 @@
       <c r="A165" s="2"/>
       <c r="B165" s="2"/>
       <c r="C165" s="2"/>
-      <c r="D165" s="50"/>
+      <c r="D165" s="49"/>
       <c r="E165" s="2"/>
       <c r="F165" s="2"/>
       <c r="G165" s="2"/>
@@ -7322,7 +7347,7 @@
       <c r="A166" s="2"/>
       <c r="B166" s="2"/>
       <c r="C166" s="2"/>
-      <c r="D166" s="50"/>
+      <c r="D166" s="49"/>
       <c r="E166" s="2"/>
       <c r="F166" s="2"/>
       <c r="G166" s="2"/>
@@ -7350,7 +7375,7 @@
       <c r="A167" s="2"/>
       <c r="B167" s="2"/>
       <c r="C167" s="2"/>
-      <c r="D167" s="50"/>
+      <c r="D167" s="49"/>
       <c r="E167" s="2"/>
       <c r="F167" s="2"/>
       <c r="G167" s="2"/>
@@ -7378,7 +7403,7 @@
       <c r="A168" s="2"/>
       <c r="B168" s="2"/>
       <c r="C168" s="2"/>
-      <c r="D168" s="50"/>
+      <c r="D168" s="49"/>
       <c r="E168" s="2"/>
       <c r="F168" s="2"/>
       <c r="G168" s="2"/>
@@ -7406,7 +7431,7 @@
       <c r="A169" s="2"/>
       <c r="B169" s="2"/>
       <c r="C169" s="2"/>
-      <c r="D169" s="50"/>
+      <c r="D169" s="49"/>
       <c r="E169" s="2"/>
       <c r="F169" s="2"/>
       <c r="G169" s="2"/>
@@ -7434,7 +7459,7 @@
       <c r="A170" s="2"/>
       <c r="B170" s="2"/>
       <c r="C170" s="2"/>
-      <c r="D170" s="50"/>
+      <c r="D170" s="49"/>
       <c r="E170" s="2"/>
       <c r="F170" s="2"/>
       <c r="G170" s="2"/>
@@ -7462,7 +7487,7 @@
       <c r="A171" s="2"/>
       <c r="B171" s="2"/>
       <c r="C171" s="2"/>
-      <c r="D171" s="50"/>
+      <c r="D171" s="49"/>
       <c r="E171" s="2"/>
       <c r="F171" s="2"/>
       <c r="G171" s="2"/>
@@ -7490,7 +7515,7 @@
       <c r="A172" s="2"/>
       <c r="B172" s="2"/>
       <c r="C172" s="2"/>
-      <c r="D172" s="50"/>
+      <c r="D172" s="49"/>
       <c r="E172" s="2"/>
       <c r="F172" s="2"/>
       <c r="G172" s="2"/>
@@ -7518,7 +7543,7 @@
       <c r="A173" s="2"/>
       <c r="B173" s="2"/>
       <c r="C173" s="2"/>
-      <c r="D173" s="50"/>
+      <c r="D173" s="49"/>
       <c r="E173" s="2"/>
       <c r="F173" s="2"/>
       <c r="G173" s="2"/>
@@ -7546,7 +7571,7 @@
       <c r="A174" s="2"/>
       <c r="B174" s="2"/>
       <c r="C174" s="2"/>
-      <c r="D174" s="50"/>
+      <c r="D174" s="49"/>
       <c r="E174" s="2"/>
       <c r="F174" s="2"/>
       <c r="G174" s="2"/>
@@ -7574,7 +7599,7 @@
       <c r="A175" s="2"/>
       <c r="B175" s="2"/>
       <c r="C175" s="2"/>
-      <c r="D175" s="50"/>
+      <c r="D175" s="49"/>
       <c r="E175" s="2"/>
       <c r="F175" s="2"/>
       <c r="G175" s="2"/>
@@ -7602,7 +7627,7 @@
       <c r="A176" s="2"/>
       <c r="B176" s="2"/>
       <c r="C176" s="2"/>
-      <c r="D176" s="50"/>
+      <c r="D176" s="49"/>
       <c r="E176" s="2"/>
       <c r="F176" s="2"/>
       <c r="G176" s="2"/>
@@ -7630,7 +7655,7 @@
       <c r="A177" s="2"/>
       <c r="B177" s="2"/>
       <c r="C177" s="2"/>
-      <c r="D177" s="50"/>
+      <c r="D177" s="49"/>
       <c r="E177" s="2"/>
       <c r="F177" s="2"/>
       <c r="G177" s="2"/>
@@ -7658,7 +7683,7 @@
       <c r="A178" s="2"/>
       <c r="B178" s="2"/>
       <c r="C178" s="2"/>
-      <c r="D178" s="50"/>
+      <c r="D178" s="49"/>
       <c r="E178" s="2"/>
       <c r="F178" s="2"/>
       <c r="G178" s="2"/>
@@ -7686,7 +7711,7 @@
       <c r="A179" s="2"/>
       <c r="B179" s="2"/>
       <c r="C179" s="2"/>
-      <c r="D179" s="50"/>
+      <c r="D179" s="49"/>
       <c r="E179" s="2"/>
       <c r="F179" s="2"/>
       <c r="G179" s="2"/>
@@ -7714,7 +7739,7 @@
       <c r="A180" s="2"/>
       <c r="B180" s="2"/>
       <c r="C180" s="2"/>
-      <c r="D180" s="50"/>
+      <c r="D180" s="49"/>
       <c r="E180" s="2"/>
       <c r="F180" s="2"/>
       <c r="G180" s="2"/>
@@ -7742,7 +7767,7 @@
       <c r="A181" s="2"/>
       <c r="B181" s="2"/>
       <c r="C181" s="2"/>
-      <c r="D181" s="50"/>
+      <c r="D181" s="49"/>
       <c r="E181" s="2"/>
       <c r="F181" s="2"/>
       <c r="G181" s="2"/>
@@ -7770,7 +7795,7 @@
       <c r="A182" s="2"/>
       <c r="B182" s="2"/>
       <c r="C182" s="2"/>
-      <c r="D182" s="50"/>
+      <c r="D182" s="49"/>
       <c r="E182" s="2"/>
       <c r="F182" s="2"/>
       <c r="G182" s="2"/>
@@ -7798,7 +7823,7 @@
       <c r="A183" s="2"/>
       <c r="B183" s="2"/>
       <c r="C183" s="2"/>
-      <c r="D183" s="50"/>
+      <c r="D183" s="49"/>
       <c r="E183" s="2"/>
       <c r="F183" s="2"/>
       <c r="G183" s="2"/>
@@ -7826,7 +7851,7 @@
       <c r="A184" s="2"/>
       <c r="B184" s="2"/>
       <c r="C184" s="2"/>
-      <c r="D184" s="50"/>
+      <c r="D184" s="49"/>
       <c r="E184" s="2"/>
       <c r="F184" s="2"/>
       <c r="G184" s="2"/>
@@ -7854,7 +7879,7 @@
       <c r="A185" s="2"/>
       <c r="B185" s="2"/>
       <c r="C185" s="2"/>
-      <c r="D185" s="50"/>
+      <c r="D185" s="49"/>
       <c r="E185" s="2"/>
       <c r="F185" s="2"/>
       <c r="G185" s="2"/>
@@ -7882,7 +7907,7 @@
       <c r="A186" s="2"/>
       <c r="B186" s="2"/>
       <c r="C186" s="2"/>
-      <c r="D186" s="50"/>
+      <c r="D186" s="49"/>
       <c r="E186" s="2"/>
       <c r="F186" s="2"/>
       <c r="G186" s="2"/>
@@ -7910,7 +7935,7 @@
       <c r="A187" s="2"/>
       <c r="B187" s="2"/>
       <c r="C187" s="2"/>
-      <c r="D187" s="50"/>
+      <c r="D187" s="49"/>
       <c r="E187" s="2"/>
       <c r="F187" s="2"/>
       <c r="G187" s="2"/>
@@ -7938,7 +7963,7 @@
       <c r="A188" s="2"/>
       <c r="B188" s="2"/>
       <c r="C188" s="2"/>
-      <c r="D188" s="50"/>
+      <c r="D188" s="49"/>
       <c r="E188" s="2"/>
       <c r="F188" s="2"/>
       <c r="G188" s="2"/>
@@ -7966,7 +7991,7 @@
       <c r="A189" s="2"/>
       <c r="B189" s="2"/>
       <c r="C189" s="2"/>
-      <c r="D189" s="50"/>
+      <c r="D189" s="49"/>
       <c r="E189" s="2"/>
       <c r="F189" s="2"/>
       <c r="G189" s="2"/>
@@ -7994,7 +8019,7 @@
       <c r="A190" s="2"/>
       <c r="B190" s="2"/>
       <c r="C190" s="2"/>
-      <c r="D190" s="50"/>
+      <c r="D190" s="49"/>
       <c r="E190" s="2"/>
       <c r="F190" s="2"/>
       <c r="G190" s="2"/>
@@ -8022,7 +8047,7 @@
       <c r="A191" s="2"/>
       <c r="B191" s="2"/>
       <c r="C191" s="2"/>
-      <c r="D191" s="50"/>
+      <c r="D191" s="49"/>
       <c r="E191" s="2"/>
       <c r="F191" s="2"/>
       <c r="G191" s="2"/>
@@ -8050,7 +8075,7 @@
       <c r="A192" s="2"/>
       <c r="B192" s="2"/>
       <c r="C192" s="2"/>
-      <c r="D192" s="50"/>
+      <c r="D192" s="49"/>
       <c r="E192" s="2"/>
       <c r="F192" s="2"/>
       <c r="G192" s="2"/>
@@ -8078,7 +8103,7 @@
       <c r="A193" s="2"/>
       <c r="B193" s="2"/>
       <c r="C193" s="2"/>
-      <c r="D193" s="50"/>
+      <c r="D193" s="49"/>
       <c r="E193" s="2"/>
       <c r="F193" s="2"/>
       <c r="G193" s="2"/>
@@ -8106,7 +8131,7 @@
       <c r="A194" s="2"/>
       <c r="B194" s="2"/>
       <c r="C194" s="2"/>
-      <c r="D194" s="50"/>
+      <c r="D194" s="49"/>
       <c r="E194" s="2"/>
       <c r="F194" s="2"/>
       <c r="G194" s="2"/>
@@ -8134,7 +8159,7 @@
       <c r="A195" s="2"/>
       <c r="B195" s="2"/>
       <c r="C195" s="2"/>
-      <c r="D195" s="50"/>
+      <c r="D195" s="49"/>
       <c r="E195" s="2"/>
       <c r="F195" s="2"/>
       <c r="G195" s="2"/>
@@ -8162,7 +8187,7 @@
       <c r="A196" s="2"/>
       <c r="B196" s="2"/>
       <c r="C196" s="2"/>
-      <c r="D196" s="50"/>
+      <c r="D196" s="49"/>
       <c r="E196" s="2"/>
       <c r="F196" s="2"/>
       <c r="G196" s="2"/>
@@ -8190,7 +8215,7 @@
       <c r="A197" s="2"/>
       <c r="B197" s="2"/>
       <c r="C197" s="2"/>
-      <c r="D197" s="50"/>
+      <c r="D197" s="49"/>
       <c r="E197" s="2"/>
       <c r="F197" s="2"/>
       <c r="G197" s="2"/>
@@ -8218,7 +8243,7 @@
       <c r="A198" s="2"/>
       <c r="B198" s="2"/>
       <c r="C198" s="2"/>
-      <c r="D198" s="50"/>
+      <c r="D198" s="49"/>
       <c r="E198" s="2"/>
       <c r="F198" s="2"/>
       <c r="G198" s="2"/>
@@ -8246,7 +8271,7 @@
       <c r="A199" s="2"/>
       <c r="B199" s="2"/>
       <c r="C199" s="2"/>
-      <c r="D199" s="50"/>
+      <c r="D199" s="49"/>
       <c r="E199" s="2"/>
       <c r="F199" s="2"/>
       <c r="G199" s="2"/>
@@ -8274,7 +8299,7 @@
       <c r="A200" s="2"/>
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
-      <c r="D200" s="50"/>
+      <c r="D200" s="49"/>
       <c r="E200" s="2"/>
       <c r="F200" s="2"/>
       <c r="G200" s="2"/>
@@ -8302,7 +8327,7 @@
       <c r="A201" s="2"/>
       <c r="B201" s="2"/>
       <c r="C201" s="2"/>
-      <c r="D201" s="50"/>
+      <c r="D201" s="49"/>
       <c r="E201" s="2"/>
       <c r="F201" s="2"/>
       <c r="G201" s="2"/>
@@ -8330,7 +8355,7 @@
       <c r="A202" s="2"/>
       <c r="B202" s="2"/>
       <c r="C202" s="2"/>
-      <c r="D202" s="50"/>
+      <c r="D202" s="49"/>
       <c r="E202" s="2"/>
       <c r="F202" s="2"/>
       <c r="G202" s="2"/>
@@ -8358,7 +8383,7 @@
       <c r="A203" s="2"/>
       <c r="B203" s="2"/>
       <c r="C203" s="2"/>
-      <c r="D203" s="50"/>
+      <c r="D203" s="49"/>
       <c r="E203" s="2"/>
       <c r="F203" s="2"/>
       <c r="G203" s="2"/>
@@ -8386,7 +8411,7 @@
       <c r="A204" s="2"/>
       <c r="B204" s="2"/>
       <c r="C204" s="2"/>
-      <c r="D204" s="50"/>
+      <c r="D204" s="49"/>
       <c r="E204" s="2"/>
       <c r="F204" s="2"/>
       <c r="G204" s="2"/>
@@ -8414,7 +8439,7 @@
       <c r="A205" s="2"/>
       <c r="B205" s="2"/>
       <c r="C205" s="2"/>
-      <c r="D205" s="50"/>
+      <c r="D205" s="49"/>
       <c r="E205" s="2"/>
       <c r="F205" s="2"/>
       <c r="G205" s="2"/>
@@ -8442,7 +8467,7 @@
       <c r="A206" s="2"/>
       <c r="B206" s="2"/>
       <c r="C206" s="2"/>
-      <c r="D206" s="50"/>
+      <c r="D206" s="49"/>
       <c r="E206" s="2"/>
       <c r="F206" s="2"/>
       <c r="G206" s="2"/>
@@ -8470,7 +8495,7 @@
       <c r="A207" s="2"/>
       <c r="B207" s="2"/>
       <c r="C207" s="2"/>
-      <c r="D207" s="50"/>
+      <c r="D207" s="49"/>
       <c r="E207" s="2"/>
       <c r="F207" s="2"/>
       <c r="G207" s="2"/>
@@ -8498,7 +8523,7 @@
       <c r="A208" s="2"/>
       <c r="B208" s="2"/>
       <c r="C208" s="2"/>
-      <c r="D208" s="50"/>
+      <c r="D208" s="49"/>
       <c r="E208" s="2"/>
       <c r="F208" s="2"/>
       <c r="G208" s="2"/>
@@ -8526,7 +8551,7 @@
       <c r="A209" s="2"/>
       <c r="B209" s="2"/>
       <c r="C209" s="2"/>
-      <c r="D209" s="50"/>
+      <c r="D209" s="49"/>
       <c r="E209" s="2"/>
       <c r="F209" s="2"/>
       <c r="G209" s="2"/>
@@ -8554,7 +8579,7 @@
       <c r="A210" s="2"/>
       <c r="B210" s="2"/>
       <c r="C210" s="2"/>
-      <c r="D210" s="50"/>
+      <c r="D210" s="49"/>
       <c r="E210" s="2"/>
       <c r="F210" s="2"/>
       <c r="G210" s="2"/>
@@ -8582,7 +8607,7 @@
       <c r="A211" s="2"/>
       <c r="B211" s="2"/>
       <c r="C211" s="2"/>
-      <c r="D211" s="50"/>
+      <c r="D211" s="49"/>
       <c r="E211" s="2"/>
       <c r="F211" s="2"/>
       <c r="G211" s="2"/>
@@ -8610,7 +8635,7 @@
       <c r="A212" s="2"/>
       <c r="B212" s="2"/>
       <c r="C212" s="2"/>
-      <c r="D212" s="50"/>
+      <c r="D212" s="49"/>
       <c r="E212" s="2"/>
       <c r="F212" s="2"/>
       <c r="G212" s="2"/>
@@ -8638,7 +8663,7 @@
       <c r="A213" s="2"/>
       <c r="B213" s="2"/>
       <c r="C213" s="2"/>
-      <c r="D213" s="50"/>
+      <c r="D213" s="49"/>
       <c r="E213" s="2"/>
       <c r="F213" s="2"/>
       <c r="G213" s="2"/>
@@ -8666,7 +8691,7 @@
       <c r="A214" s="2"/>
       <c r="B214" s="2"/>
       <c r="C214" s="2"/>
-      <c r="D214" s="50"/>
+      <c r="D214" s="49"/>
       <c r="E214" s="2"/>
       <c r="F214" s="2"/>
       <c r="G214" s="2"/>
@@ -8694,7 +8719,7 @@
       <c r="A215" s="2"/>
       <c r="B215" s="2"/>
       <c r="C215" s="2"/>
-      <c r="D215" s="50"/>
+      <c r="D215" s="49"/>
       <c r="E215" s="2"/>
       <c r="F215" s="2"/>
       <c r="G215" s="2"/>
@@ -8722,7 +8747,7 @@
       <c r="A216" s="2"/>
       <c r="B216" s="2"/>
       <c r="C216" s="2"/>
-      <c r="D216" s="50"/>
+      <c r="D216" s="49"/>
       <c r="E216" s="2"/>
       <c r="F216" s="2"/>
       <c r="G216" s="2"/>
@@ -8750,7 +8775,7 @@
       <c r="A217" s="2"/>
       <c r="B217" s="2"/>
       <c r="C217" s="2"/>
-      <c r="D217" s="50"/>
+      <c r="D217" s="49"/>
       <c r="E217" s="2"/>
       <c r="F217" s="2"/>
       <c r="G217" s="2"/>
@@ -8778,7 +8803,7 @@
       <c r="A218" s="2"/>
       <c r="B218" s="2"/>
       <c r="C218" s="2"/>
-      <c r="D218" s="50"/>
+      <c r="D218" s="49"/>
       <c r="E218" s="2"/>
       <c r="F218" s="2"/>
       <c r="G218" s="2"/>
@@ -8806,7 +8831,7 @@
       <c r="A219" s="2"/>
       <c r="B219" s="2"/>
       <c r="C219" s="2"/>
-      <c r="D219" s="50"/>
+      <c r="D219" s="49"/>
       <c r="E219" s="2"/>
       <c r="F219" s="2"/>
       <c r="G219" s="2"/>
@@ -8834,7 +8859,7 @@
       <c r="A220" s="2"/>
       <c r="B220" s="2"/>
       <c r="C220" s="2"/>
-      <c r="D220" s="50"/>
+      <c r="D220" s="49"/>
       <c r="E220" s="2"/>
       <c r="F220" s="2"/>
       <c r="G220" s="2"/>
@@ -8862,7 +8887,7 @@
       <c r="A221" s="2"/>
       <c r="B221" s="2"/>
       <c r="C221" s="2"/>
-      <c r="D221" s="50"/>
+      <c r="D221" s="49"/>
       <c r="E221" s="2"/>
       <c r="F221" s="2"/>
       <c r="G221" s="2"/>
@@ -8890,7 +8915,7 @@
       <c r="A222" s="2"/>
       <c r="B222" s="2"/>
       <c r="C222" s="2"/>
-      <c r="D222" s="50"/>
+      <c r="D222" s="49"/>
       <c r="E222" s="2"/>
       <c r="F222" s="2"/>
       <c r="G222" s="2"/>
@@ -8918,7 +8943,7 @@
       <c r="A223" s="2"/>
       <c r="B223" s="2"/>
       <c r="C223" s="2"/>
-      <c r="D223" s="50"/>
+      <c r="D223" s="49"/>
       <c r="E223" s="2"/>
       <c r="F223" s="2"/>
       <c r="G223" s="2"/>
@@ -8946,7 +8971,7 @@
       <c r="A224" s="2"/>
       <c r="B224" s="2"/>
       <c r="C224" s="2"/>
-      <c r="D224" s="50"/>
+      <c r="D224" s="49"/>
       <c r="E224" s="2"/>
       <c r="F224" s="2"/>
       <c r="G224" s="2"/>
@@ -8974,7 +8999,7 @@
       <c r="A225" s="2"/>
       <c r="B225" s="2"/>
       <c r="C225" s="2"/>
-      <c r="D225" s="50"/>
+      <c r="D225" s="49"/>
       <c r="E225" s="2"/>
       <c r="F225" s="2"/>
       <c r="G225" s="2"/>
@@ -9002,7 +9027,7 @@
       <c r="A226" s="2"/>
       <c r="B226" s="2"/>
       <c r="C226" s="2"/>
-      <c r="D226" s="50"/>
+      <c r="D226" s="49"/>
       <c r="E226" s="2"/>
       <c r="F226" s="2"/>
       <c r="G226" s="2"/>
@@ -9030,7 +9055,7 @@
       <c r="A227" s="2"/>
       <c r="B227" s="2"/>
       <c r="C227" s="2"/>
-      <c r="D227" s="50"/>
+      <c r="D227" s="49"/>
       <c r="E227" s="2"/>
       <c r="F227" s="2"/>
       <c r="G227" s="2"/>
@@ -9058,7 +9083,7 @@
       <c r="A228" s="2"/>
       <c r="B228" s="2"/>
       <c r="C228" s="2"/>
-      <c r="D228" s="50"/>
+      <c r="D228" s="49"/>
       <c r="E228" s="2"/>
       <c r="F228" s="2"/>
       <c r="G228" s="2"/>
@@ -9086,7 +9111,7 @@
       <c r="A229" s="2"/>
       <c r="B229" s="2"/>
       <c r="C229" s="2"/>
-      <c r="D229" s="50"/>
+      <c r="D229" s="49"/>
       <c r="E229" s="2"/>
       <c r="F229" s="2"/>
       <c r="G229" s="2"/>
@@ -9114,7 +9139,7 @@
       <c r="A230" s="2"/>
       <c r="B230" s="2"/>
       <c r="C230" s="2"/>
-      <c r="D230" s="50"/>
+      <c r="D230" s="49"/>
       <c r="E230" s="2"/>
       <c r="F230" s="2"/>
       <c r="G230" s="2"/>
@@ -9142,7 +9167,7 @@
       <c r="A231" s="2"/>
       <c r="B231" s="2"/>
       <c r="C231" s="2"/>
-      <c r="D231" s="50"/>
+      <c r="D231" s="49"/>
       <c r="E231" s="2"/>
       <c r="F231" s="2"/>
       <c r="G231" s="2"/>
@@ -9170,7 +9195,7 @@
       <c r="A232" s="2"/>
       <c r="B232" s="2"/>
       <c r="C232" s="2"/>
-      <c r="D232" s="50"/>
+      <c r="D232" s="49"/>
       <c r="E232" s="2"/>
       <c r="F232" s="2"/>
       <c r="G232" s="2"/>
@@ -9198,7 +9223,7 @@
       <c r="A233" s="2"/>
       <c r="B233" s="2"/>
       <c r="C233" s="2"/>
-      <c r="D233" s="50"/>
+      <c r="D233" s="49"/>
       <c r="E233" s="2"/>
       <c r="F233" s="2"/>
       <c r="G233" s="2"/>
@@ -9226,7 +9251,7 @@
       <c r="A234" s="2"/>
       <c r="B234" s="2"/>
       <c r="C234" s="2"/>
-      <c r="D234" s="50"/>
+      <c r="D234" s="49"/>
       <c r="E234" s="2"/>
       <c r="F234" s="2"/>
       <c r="G234" s="2"/>
@@ -9254,7 +9279,7 @@
       <c r="A235" s="2"/>
       <c r="B235" s="2"/>
       <c r="C235" s="2"/>
-      <c r="D235" s="50"/>
+      <c r="D235" s="49"/>
       <c r="E235" s="2"/>
       <c r="F235" s="2"/>
       <c r="G235" s="2"/>
@@ -9282,7 +9307,7 @@
       <c r="A236" s="2"/>
       <c r="B236" s="2"/>
       <c r="C236" s="2"/>
-      <c r="D236" s="50"/>
+      <c r="D236" s="49"/>
       <c r="E236" s="2"/>
       <c r="F236" s="2"/>
       <c r="G236" s="2"/>
@@ -9310,7 +9335,7 @@
       <c r="A237" s="2"/>
       <c r="B237" s="2"/>
       <c r="C237" s="2"/>
-      <c r="D237" s="50"/>
+      <c r="D237" s="49"/>
       <c r="E237" s="2"/>
       <c r="F237" s="2"/>
       <c r="G237" s="2"/>
@@ -9338,7 +9363,7 @@
       <c r="A238" s="2"/>
       <c r="B238" s="2"/>
       <c r="C238" s="2"/>
-      <c r="D238" s="50"/>
+      <c r="D238" s="49"/>
       <c r="E238" s="2"/>
       <c r="F238" s="2"/>
       <c r="G238" s="2"/>
@@ -9366,7 +9391,7 @@
       <c r="A239" s="2"/>
       <c r="B239" s="2"/>
       <c r="C239" s="2"/>
-      <c r="D239" s="50"/>
+      <c r="D239" s="49"/>
       <c r="E239" s="2"/>
       <c r="F239" s="2"/>
       <c r="G239" s="2"/>
@@ -9394,7 +9419,7 @@
       <c r="A240" s="2"/>
       <c r="B240" s="2"/>
       <c r="C240" s="2"/>
-      <c r="D240" s="50"/>
+      <c r="D240" s="49"/>
       <c r="E240" s="2"/>
       <c r="F240" s="2"/>
       <c r="G240" s="2"/>
@@ -9422,7 +9447,7 @@
       <c r="A241" s="2"/>
       <c r="B241" s="2"/>
       <c r="C241" s="2"/>
-      <c r="D241" s="50"/>
+      <c r="D241" s="49"/>
       <c r="E241" s="2"/>
       <c r="F241" s="2"/>
       <c r="G241" s="2"/>
@@ -9450,7 +9475,7 @@
       <c r="A242" s="2"/>
       <c r="B242" s="2"/>
       <c r="C242" s="2"/>
-      <c r="D242" s="50"/>
+      <c r="D242" s="49"/>
       <c r="E242" s="2"/>
       <c r="F242" s="2"/>
       <c r="G242" s="2"/>
@@ -9478,7 +9503,7 @@
       <c r="A243" s="2"/>
       <c r="B243" s="2"/>
       <c r="C243" s="2"/>
-      <c r="D243" s="50"/>
+      <c r="D243" s="49"/>
       <c r="E243" s="2"/>
       <c r="F243" s="2"/>
       <c r="G243" s="2"/>
@@ -9506,7 +9531,7 @@
       <c r="A244" s="2"/>
       <c r="B244" s="2"/>
       <c r="C244" s="2"/>
-      <c r="D244" s="50"/>
+      <c r="D244" s="49"/>
       <c r="E244" s="2"/>
       <c r="F244" s="2"/>
       <c r="G244" s="2"/>
@@ -9534,7 +9559,7 @@
       <c r="A245" s="2"/>
       <c r="B245" s="2"/>
       <c r="C245" s="2"/>
-      <c r="D245" s="50"/>
+      <c r="D245" s="49"/>
       <c r="E245" s="2"/>
       <c r="F245" s="2"/>
       <c r="G245" s="2"/>
@@ -9562,7 +9587,7 @@
       <c r="A246" s="2"/>
       <c r="B246" s="2"/>
       <c r="C246" s="2"/>
-      <c r="D246" s="50"/>
+      <c r="D246" s="49"/>
       <c r="E246" s="2"/>
       <c r="F246" s="2"/>
       <c r="G246" s="2"/>
@@ -9590,7 +9615,7 @@
       <c r="A247" s="2"/>
       <c r="B247" s="2"/>
       <c r="C247" s="2"/>
-      <c r="D247" s="50"/>
+      <c r="D247" s="49"/>
       <c r="E247" s="2"/>
       <c r="F247" s="2"/>
       <c r="G247" s="2"/>
@@ -9618,7 +9643,7 @@
       <c r="A248" s="2"/>
       <c r="B248" s="2"/>
       <c r="C248" s="2"/>
-      <c r="D248" s="50"/>
+      <c r="D248" s="49"/>
       <c r="E248" s="2"/>
       <c r="F248" s="2"/>
       <c r="G248" s="2"/>
@@ -9646,7 +9671,7 @@
       <c r="A249" s="2"/>
       <c r="B249" s="2"/>
       <c r="C249" s="2"/>
-      <c r="D249" s="50"/>
+      <c r="D249" s="49"/>
       <c r="E249" s="2"/>
       <c r="F249" s="2"/>
       <c r="G249" s="2"/>
@@ -9674,7 +9699,7 @@
       <c r="A250" s="2"/>
       <c r="B250" s="2"/>
       <c r="C250" s="2"/>
-      <c r="D250" s="50"/>
+      <c r="D250" s="49"/>
       <c r="E250" s="2"/>
       <c r="F250" s="2"/>
       <c r="G250" s="2"/>
@@ -9702,7 +9727,7 @@
       <c r="A251" s="2"/>
       <c r="B251" s="2"/>
       <c r="C251" s="2"/>
-      <c r="D251" s="50"/>
+      <c r="D251" s="49"/>
       <c r="E251" s="2"/>
       <c r="F251" s="2"/>
       <c r="G251" s="2"/>
@@ -9730,7 +9755,7 @@
       <c r="A252" s="2"/>
       <c r="B252" s="2"/>
       <c r="C252" s="2"/>
-      <c r="D252" s="50"/>
+      <c r="D252" s="49"/>
       <c r="E252" s="2"/>
       <c r="F252" s="2"/>
       <c r="G252" s="2"/>
@@ -9758,7 +9783,7 @@
       <c r="A253" s="2"/>
       <c r="B253" s="2"/>
       <c r="C253" s="2"/>
-      <c r="D253" s="50"/>
+      <c r="D253" s="49"/>
       <c r="E253" s="2"/>
       <c r="F253" s="2"/>
       <c r="G253" s="2"/>
@@ -9786,7 +9811,7 @@
       <c r="A254" s="2"/>
       <c r="B254" s="2"/>
       <c r="C254" s="2"/>
-      <c r="D254" s="50"/>
+      <c r="D254" s="49"/>
       <c r="E254" s="2"/>
       <c r="F254" s="2"/>
       <c r="G254" s="2"/>
@@ -9814,7 +9839,7 @@
       <c r="A255" s="2"/>
       <c r="B255" s="2"/>
       <c r="C255" s="2"/>
-      <c r="D255" s="50"/>
+      <c r="D255" s="49"/>
       <c r="E255" s="2"/>
       <c r="F255" s="2"/>
       <c r="G255" s="2"/>
@@ -9842,7 +9867,7 @@
       <c r="A256" s="2"/>
       <c r="B256" s="2"/>
       <c r="C256" s="2"/>
-      <c r="D256" s="50"/>
+      <c r="D256" s="49"/>
       <c r="E256" s="2"/>
       <c r="F256" s="2"/>
       <c r="G256" s="2"/>
@@ -9870,7 +9895,7 @@
       <c r="A257" s="2"/>
       <c r="B257" s="2"/>
       <c r="C257" s="2"/>
-      <c r="D257" s="50"/>
+      <c r="D257" s="49"/>
       <c r="E257" s="2"/>
       <c r="F257" s="2"/>
       <c r="G257" s="2"/>
@@ -9898,7 +9923,7 @@
       <c r="A258" s="2"/>
       <c r="B258" s="2"/>
       <c r="C258" s="2"/>
-      <c r="D258" s="50"/>
+      <c r="D258" s="49"/>
       <c r="E258" s="2"/>
       <c r="F258" s="2"/>
       <c r="G258" s="2"/>
@@ -9926,7 +9951,7 @@
       <c r="A259" s="2"/>
       <c r="B259" s="2"/>
       <c r="C259" s="2"/>
-      <c r="D259" s="50"/>
+      <c r="D259" s="49"/>
       <c r="E259" s="2"/>
       <c r="F259" s="2"/>
       <c r="G259" s="2"/>
@@ -9954,7 +9979,7 @@
       <c r="A260" s="2"/>
       <c r="B260" s="2"/>
       <c r="C260" s="2"/>
-      <c r="D260" s="50"/>
+      <c r="D260" s="49"/>
       <c r="E260" s="2"/>
       <c r="F260" s="2"/>
       <c r="G260" s="2"/>
@@ -9982,7 +10007,7 @@
       <c r="A261" s="2"/>
       <c r="B261" s="2"/>
       <c r="C261" s="2"/>
-      <c r="D261" s="50"/>
+      <c r="D261" s="49"/>
       <c r="E261" s="2"/>
       <c r="F261" s="2"/>
       <c r="G261" s="2"/>
@@ -10010,7 +10035,7 @@
       <c r="A262" s="2"/>
       <c r="B262" s="2"/>
       <c r="C262" s="2"/>
-      <c r="D262" s="50"/>
+      <c r="D262" s="49"/>
       <c r="E262" s="2"/>
       <c r="F262" s="2"/>
       <c r="G262" s="2"/>
@@ -10038,7 +10063,7 @@
       <c r="A263" s="2"/>
       <c r="B263" s="2"/>
       <c r="C263" s="2"/>
-      <c r="D263" s="50"/>
+      <c r="D263" s="49"/>
       <c r="E263" s="2"/>
       <c r="F263" s="2"/>
       <c r="G263" s="2"/>
@@ -10066,7 +10091,7 @@
       <c r="A264" s="2"/>
       <c r="B264" s="2"/>
       <c r="C264" s="2"/>
-      <c r="D264" s="50"/>
+      <c r="D264" s="49"/>
       <c r="E264" s="2"/>
       <c r="F264" s="2"/>
       <c r="G264" s="2"/>
@@ -10094,7 +10119,7 @@
       <c r="A265" s="2"/>
       <c r="B265" s="2"/>
       <c r="C265" s="2"/>
-      <c r="D265" s="50"/>
+      <c r="D265" s="49"/>
       <c r="E265" s="2"/>
       <c r="F265" s="2"/>
       <c r="G265" s="2"/>
@@ -10122,7 +10147,7 @@
       <c r="A266" s="2"/>
       <c r="B266" s="2"/>
       <c r="C266" s="2"/>
-      <c r="D266" s="50"/>
+      <c r="D266" s="49"/>
       <c r="E266" s="2"/>
       <c r="F266" s="2"/>
       <c r="G266" s="2"/>
@@ -10150,7 +10175,7 @@
       <c r="A267" s="2"/>
       <c r="B267" s="2"/>
       <c r="C267" s="2"/>
-      <c r="D267" s="50"/>
+      <c r="D267" s="49"/>
       <c r="E267" s="2"/>
       <c r="F267" s="2"/>
       <c r="G267" s="2"/>
@@ -10178,7 +10203,7 @@
       <c r="A268" s="2"/>
       <c r="B268" s="2"/>
       <c r="C268" s="2"/>
-      <c r="D268" s="50"/>
+      <c r="D268" s="49"/>
       <c r="E268" s="2"/>
       <c r="F268" s="2"/>
       <c r="G268" s="2"/>
@@ -10206,7 +10231,7 @@
       <c r="A269" s="2"/>
       <c r="B269" s="2"/>
       <c r="C269" s="2"/>
-      <c r="D269" s="50"/>
+      <c r="D269" s="49"/>
       <c r="E269" s="2"/>
       <c r="F269" s="2"/>
       <c r="G269" s="2"/>
@@ -10234,7 +10259,7 @@
       <c r="A270" s="2"/>
       <c r="B270" s="2"/>
       <c r="C270" s="2"/>
-      <c r="D270" s="50"/>
+      <c r="D270" s="49"/>
       <c r="E270" s="2"/>
       <c r="F270" s="2"/>
       <c r="G270" s="2"/>
@@ -10262,7 +10287,7 @@
       <c r="A271" s="2"/>
       <c r="B271" s="2"/>
       <c r="C271" s="2"/>
-      <c r="D271" s="50"/>
+      <c r="D271" s="49"/>
       <c r="E271" s="2"/>
       <c r="F271" s="2"/>
       <c r="G271" s="2"/>
@@ -10290,7 +10315,7 @@
       <c r="A272" s="2"/>
       <c r="B272" s="2"/>
       <c r="C272" s="2"/>
-      <c r="D272" s="50"/>
+      <c r="D272" s="49"/>
       <c r="E272" s="2"/>
       <c r="F272" s="2"/>
       <c r="G272" s="2"/>
@@ -10318,7 +10343,7 @@
       <c r="A273" s="2"/>
       <c r="B273" s="2"/>
       <c r="C273" s="2"/>
-      <c r="D273" s="50"/>
+      <c r="D273" s="49"/>
       <c r="E273" s="2"/>
       <c r="F273" s="2"/>
       <c r="G273" s="2"/>
@@ -10346,7 +10371,7 @@
       <c r="A274" s="2"/>
       <c r="B274" s="2"/>
       <c r="C274" s="2"/>
-      <c r="D274" s="50"/>
+      <c r="D274" s="49"/>
       <c r="E274" s="2"/>
       <c r="F274" s="2"/>
       <c r="G274" s="2"/>
@@ -10374,7 +10399,7 @@
       <c r="A275" s="2"/>
       <c r="B275" s="2"/>
       <c r="C275" s="2"/>
-      <c r="D275" s="50"/>
+      <c r="D275" s="49"/>
       <c r="E275" s="2"/>
       <c r="F275" s="2"/>
       <c r="G275" s="2"/>
@@ -10402,7 +10427,7 @@
       <c r="A276" s="2"/>
       <c r="B276" s="2"/>
       <c r="C276" s="2"/>
-      <c r="D276" s="50"/>
+      <c r="D276" s="49"/>
       <c r="E276" s="2"/>
       <c r="F276" s="2"/>
       <c r="G276" s="2"/>
@@ -10430,7 +10455,7 @@
       <c r="A277" s="2"/>
       <c r="B277" s="2"/>
       <c r="C277" s="2"/>
-      <c r="D277" s="50"/>
+      <c r="D277" s="49"/>
       <c r="E277" s="2"/>
       <c r="F277" s="2"/>
       <c r="G277" s="2"/>
@@ -10458,7 +10483,7 @@
       <c r="A278" s="2"/>
       <c r="B278" s="2"/>
       <c r="C278" s="2"/>
-      <c r="D278" s="50"/>
+      <c r="D278" s="49"/>
       <c r="E278" s="2"/>
       <c r="F278" s="2"/>
       <c r="G278" s="2"/>
@@ -10486,7 +10511,7 @@
       <c r="A279" s="2"/>
       <c r="B279" s="2"/>
       <c r="C279" s="2"/>
-      <c r="D279" s="50"/>
+      <c r="D279" s="49"/>
       <c r="E279" s="2"/>
       <c r="F279" s="2"/>
       <c r="G279" s="2"/>
@@ -10514,7 +10539,7 @@
       <c r="A280" s="2"/>
       <c r="B280" s="2"/>
       <c r="C280" s="2"/>
-      <c r="D280" s="50"/>
+      <c r="D280" s="49"/>
       <c r="E280" s="2"/>
       <c r="F280" s="2"/>
       <c r="G280" s="2"/>
@@ -10542,7 +10567,7 @@
       <c r="A281" s="2"/>
       <c r="B281" s="2"/>
       <c r="C281" s="2"/>
-      <c r="D281" s="50"/>
+      <c r="D281" s="49"/>
       <c r="E281" s="2"/>
       <c r="F281" s="2"/>
       <c r="G281" s="2"/>
@@ -10570,7 +10595,7 @@
       <c r="A282" s="2"/>
       <c r="B282" s="2"/>
       <c r="C282" s="2"/>
-      <c r="D282" s="50"/>
+      <c r="D282" s="49"/>
       <c r="E282" s="2"/>
       <c r="F282" s="2"/>
       <c r="G282" s="2"/>
@@ -10598,7 +10623,7 @@
       <c r="A283" s="2"/>
       <c r="B283" s="2"/>
       <c r="C283" s="2"/>
-      <c r="D283" s="50"/>
+      <c r="D283" s="49"/>
       <c r="E283" s="2"/>
       <c r="F283" s="2"/>
       <c r="G283" s="2"/>
@@ -10626,7 +10651,7 @@
       <c r="A284" s="2"/>
       <c r="B284" s="2"/>
       <c r="C284" s="2"/>
-      <c r="D284" s="50"/>
+      <c r="D284" s="49"/>
       <c r="E284" s="2"/>
       <c r="F284" s="2"/>
       <c r="G284" s="2"/>
@@ -10654,7 +10679,7 @@
       <c r="A285" s="2"/>
       <c r="B285" s="2"/>
       <c r="C285" s="2"/>
-      <c r="D285" s="50"/>
+      <c r="D285" s="49"/>
       <c r="E285" s="2"/>
       <c r="F285" s="2"/>
       <c r="G285" s="2"/>
@@ -10682,7 +10707,7 @@
       <c r="A286" s="2"/>
       <c r="B286" s="2"/>
       <c r="C286" s="2"/>
-      <c r="D286" s="50"/>
+      <c r="D286" s="49"/>
       <c r="E286" s="2"/>
       <c r="F286" s="2"/>
       <c r="G286" s="2"/>
@@ -10710,7 +10735,7 @@
       <c r="A287" s="2"/>
       <c r="B287" s="2"/>
       <c r="C287" s="2"/>
-      <c r="D287" s="50"/>
+      <c r="D287" s="49"/>
       <c r="E287" s="2"/>
       <c r="F287" s="2"/>
       <c r="G287" s="2"/>
@@ -10738,7 +10763,7 @@
       <c r="A288" s="2"/>
       <c r="B288" s="2"/>
       <c r="C288" s="2"/>
-      <c r="D288" s="50"/>
+      <c r="D288" s="49"/>
       <c r="E288" s="2"/>
       <c r="F288" s="2"/>
       <c r="G288" s="2"/>
@@ -10766,7 +10791,7 @@
       <c r="A289" s="2"/>
       <c r="B289" s="2"/>
       <c r="C289" s="2"/>
-      <c r="D289" s="50"/>
+      <c r="D289" s="49"/>
       <c r="E289" s="2"/>
       <c r="F289" s="2"/>
       <c r="G289" s="2"/>
@@ -10794,7 +10819,7 @@
       <c r="A290" s="2"/>
       <c r="B290" s="2"/>
       <c r="C290" s="2"/>
-      <c r="D290" s="50"/>
+      <c r="D290" s="49"/>
       <c r="E290" s="2"/>
       <c r="F290" s="2"/>
       <c r="G290" s="2"/>
@@ -10822,7 +10847,7 @@
       <c r="A291" s="2"/>
       <c r="B291" s="2"/>
       <c r="C291" s="2"/>
-      <c r="D291" s="50"/>
+      <c r="D291" s="49"/>
       <c r="E291" s="2"/>
       <c r="F291" s="2"/>
       <c r="G291" s="2"/>
@@ -10850,7 +10875,7 @@
       <c r="A292" s="2"/>
       <c r="B292" s="2"/>
       <c r="C292" s="2"/>
-      <c r="D292" s="50"/>
+      <c r="D292" s="49"/>
       <c r="E292" s="2"/>
       <c r="F292" s="2"/>
       <c r="G292" s="2"/>
@@ -10878,7 +10903,7 @@
       <c r="A293" s="2"/>
       <c r="B293" s="2"/>
       <c r="C293" s="2"/>
-      <c r="D293" s="50"/>
+      <c r="D293" s="49"/>
       <c r="E293" s="2"/>
       <c r="F293" s="2"/>
       <c r="G293" s="2"/>
@@ -10906,7 +10931,7 @@
       <c r="A294" s="2"/>
       <c r="B294" s="2"/>
       <c r="C294" s="2"/>
-      <c r="D294" s="50"/>
+      <c r="D294" s="49"/>
       <c r="E294" s="2"/>
       <c r="F294" s="2"/>
       <c r="G294" s="2"/>
@@ -10934,7 +10959,7 @@
       <c r="A295" s="2"/>
       <c r="B295" s="2"/>
       <c r="C295" s="2"/>
-      <c r="D295" s="50"/>
+      <c r="D295" s="49"/>
       <c r="E295" s="2"/>
       <c r="F295" s="2"/>
       <c r="G295" s="2"/>
@@ -10962,7 +10987,7 @@
       <c r="A296" s="2"/>
       <c r="B296" s="2"/>
       <c r="C296" s="2"/>
-      <c r="D296" s="50"/>
+      <c r="D296" s="49"/>
       <c r="E296" s="2"/>
       <c r="F296" s="2"/>
       <c r="G296" s="2"/>
@@ -10990,7 +11015,7 @@
       <c r="A297" s="2"/>
       <c r="B297" s="2"/>
       <c r="C297" s="2"/>
-      <c r="D297" s="50"/>
+      <c r="D297" s="49"/>
       <c r="E297" s="2"/>
       <c r="F297" s="2"/>
       <c r="G297" s="2"/>
@@ -11018,7 +11043,7 @@
       <c r="A298" s="2"/>
       <c r="B298" s="2"/>
       <c r="C298" s="2"/>
-      <c r="D298" s="50"/>
+      <c r="D298" s="49"/>
       <c r="E298" s="2"/>
       <c r="F298" s="2"/>
       <c r="G298" s="2"/>
@@ -11046,7 +11071,7 @@
       <c r="A299" s="2"/>
       <c r="B299" s="2"/>
       <c r="C299" s="2"/>
-      <c r="D299" s="50"/>
+      <c r="D299" s="49"/>
       <c r="E299" s="2"/>
       <c r="F299" s="2"/>
       <c r="G299" s="2"/>
@@ -11074,7 +11099,7 @@
       <c r="A300" s="2"/>
       <c r="B300" s="2"/>
       <c r="C300" s="2"/>
-      <c r="D300" s="50"/>
+      <c r="D300" s="49"/>
       <c r="E300" s="2"/>
       <c r="F300" s="2"/>
       <c r="G300" s="2"/>
@@ -11102,7 +11127,7 @@
       <c r="A301" s="2"/>
       <c r="B301" s="2"/>
       <c r="C301" s="2"/>
-      <c r="D301" s="50"/>
+      <c r="D301" s="49"/>
       <c r="E301" s="2"/>
       <c r="F301" s="2"/>
       <c r="G301" s="2"/>
@@ -11130,7 +11155,7 @@
       <c r="A302" s="2"/>
       <c r="B302" s="2"/>
       <c r="C302" s="2"/>
-      <c r="D302" s="50"/>
+      <c r="D302" s="49"/>
       <c r="E302" s="2"/>
       <c r="F302" s="2"/>
       <c r="G302" s="2"/>
@@ -11158,7 +11183,7 @@
       <c r="A303" s="2"/>
       <c r="B303" s="2"/>
       <c r="C303" s="2"/>
-      <c r="D303" s="50"/>
+      <c r="D303" s="49"/>
       <c r="E303" s="2"/>
       <c r="F303" s="2"/>
       <c r="G303" s="2"/>
@@ -11186,7 +11211,7 @@
       <c r="A304" s="2"/>
       <c r="B304" s="2"/>
       <c r="C304" s="2"/>
-      <c r="D304" s="50"/>
+      <c r="D304" s="49"/>
       <c r="E304" s="2"/>
       <c r="F304" s="2"/>
       <c r="G304" s="2"/>
@@ -11214,7 +11239,7 @@
       <c r="A305" s="2"/>
       <c r="B305" s="2"/>
       <c r="C305" s="2"/>
-      <c r="D305" s="50"/>
+      <c r="D305" s="49"/>
       <c r="E305" s="2"/>
       <c r="F305" s="2"/>
       <c r="G305" s="2"/>
@@ -11242,7 +11267,7 @@
       <c r="A306" s="2"/>
       <c r="B306" s="2"/>
       <c r="C306" s="2"/>
-      <c r="D306" s="50"/>
+      <c r="D306" s="49"/>
       <c r="E306" s="2"/>
       <c r="F306" s="2"/>
       <c r="G306" s="2"/>
@@ -11270,7 +11295,7 @@
       <c r="A307" s="2"/>
       <c r="B307" s="2"/>
       <c r="C307" s="2"/>
-      <c r="D307" s="50"/>
+      <c r="D307" s="49"/>
       <c r="E307" s="2"/>
       <c r="F307" s="2"/>
       <c r="G307" s="2"/>
@@ -11298,7 +11323,7 @@
       <c r="A308" s="2"/>
       <c r="B308" s="2"/>
       <c r="C308" s="2"/>
-      <c r="D308" s="50"/>
+      <c r="D308" s="49"/>
       <c r="E308" s="2"/>
       <c r="F308" s="2"/>
       <c r="G308" s="2"/>
@@ -11326,7 +11351,7 @@
       <c r="A309" s="2"/>
       <c r="B309" s="2"/>
       <c r="C309" s="2"/>
-      <c r="D309" s="50"/>
+      <c r="D309" s="49"/>
       <c r="E309" s="2"/>
       <c r="F309" s="2"/>
       <c r="G309" s="2"/>
@@ -11354,7 +11379,7 @@
       <c r="A310" s="2"/>
       <c r="B310" s="2"/>
       <c r="C310" s="2"/>
-      <c r="D310" s="50"/>
+      <c r="D310" s="49"/>
       <c r="E310" s="2"/>
       <c r="F310" s="2"/>
       <c r="G310" s="2"/>
@@ -11382,7 +11407,7 @@
       <c r="A311" s="2"/>
       <c r="B311" s="2"/>
       <c r="C311" s="2"/>
-      <c r="D311" s="50"/>
+      <c r="D311" s="49"/>
       <c r="E311" s="2"/>
       <c r="F311" s="2"/>
       <c r="G311" s="2"/>
@@ -11410,7 +11435,7 @@
       <c r="A312" s="2"/>
       <c r="B312" s="2"/>
       <c r="C312" s="2"/>
-      <c r="D312" s="50"/>
+      <c r="D312" s="49"/>
       <c r="E312" s="2"/>
       <c r="F312" s="2"/>
       <c r="G312" s="2"/>
@@ -11438,7 +11463,7 @@
       <c r="A313" s="2"/>
       <c r="B313" s="2"/>
       <c r="C313" s="2"/>
-      <c r="D313" s="50"/>
+      <c r="D313" s="49"/>
       <c r="E313" s="2"/>
       <c r="F313" s="2"/>
       <c r="G313" s="2"/>
@@ -11466,7 +11491,7 @@
       <c r="A314" s="2"/>
       <c r="B314" s="2"/>
       <c r="C314" s="2"/>
-      <c r="D314" s="50"/>
+      <c r="D314" s="49"/>
       <c r="E314" s="2"/>
       <c r="F314" s="2"/>
       <c r="G314" s="2"/>
@@ -11494,7 +11519,7 @@
       <c r="A315" s="2"/>
       <c r="B315" s="2"/>
       <c r="C315" s="2"/>
-      <c r="D315" s="50"/>
+      <c r="D315" s="49"/>
       <c r="E315" s="2"/>
       <c r="F315" s="2"/>
       <c r="G315" s="2"/>
@@ -11522,7 +11547,7 @@
       <c r="A316" s="2"/>
       <c r="B316" s="2"/>
       <c r="C316" s="2"/>
-      <c r="D316" s="50"/>
+      <c r="D316" s="49"/>
       <c r="E316" s="2"/>
       <c r="F316" s="2"/>
       <c r="G316" s="2"/>
@@ -11550,7 +11575,7 @@
       <c r="A317" s="2"/>
       <c r="B317" s="2"/>
       <c r="C317" s="2"/>
-      <c r="D317" s="50"/>
+      <c r="D317" s="49"/>
       <c r="E317" s="2"/>
       <c r="F317" s="2"/>
       <c r="G317" s="2"/>
@@ -11578,7 +11603,7 @@
       <c r="A318" s="2"/>
       <c r="B318" s="2"/>
       <c r="C318" s="2"/>
-      <c r="D318" s="50"/>
+      <c r="D318" s="49"/>
       <c r="E318" s="2"/>
       <c r="F318" s="2"/>
       <c r="G318" s="2"/>
@@ -11606,7 +11631,7 @@
       <c r="A319" s="2"/>
       <c r="B319" s="2"/>
       <c r="C319" s="2"/>
-      <c r="D319" s="50"/>
+      <c r="D319" s="49"/>
       <c r="E319" s="2"/>
       <c r="F319" s="2"/>
       <c r="G319" s="2"/>
@@ -11634,7 +11659,7 @@
       <c r="A320" s="2"/>
       <c r="B320" s="2"/>
       <c r="C320" s="2"/>
-      <c r="D320" s="50"/>
+      <c r="D320" s="49"/>
       <c r="E320" s="2"/>
       <c r="F320" s="2"/>
       <c r="G320" s="2"/>
@@ -11662,7 +11687,7 @@
       <c r="A321" s="2"/>
       <c r="B321" s="2"/>
       <c r="C321" s="2"/>
-      <c r="D321" s="50"/>
+      <c r="D321" s="49"/>
       <c r="E321" s="2"/>
       <c r="F321" s="2"/>
       <c r="G321" s="2"/>
@@ -11690,7 +11715,7 @@
       <c r="A322" s="2"/>
       <c r="B322" s="2"/>
       <c r="C322" s="2"/>
-      <c r="D322" s="50"/>
+      <c r="D322" s="49"/>
       <c r="E322" s="2"/>
       <c r="F322" s="2"/>
       <c r="G322" s="2"/>
@@ -11718,7 +11743,7 @@
       <c r="A323" s="2"/>
       <c r="B323" s="2"/>
       <c r="C323" s="2"/>
-      <c r="D323" s="50"/>
+      <c r="D323" s="49"/>
       <c r="E323" s="2"/>
       <c r="F323" s="2"/>
       <c r="G323" s="2"/>
@@ -11746,7 +11771,7 @@
       <c r="A324" s="2"/>
       <c r="B324" s="2"/>
       <c r="C324" s="2"/>
-      <c r="D324" s="50"/>
+      <c r="D324" s="49"/>
       <c r="E324" s="2"/>
       <c r="F324" s="2"/>
       <c r="G324" s="2"/>
@@ -11774,7 +11799,7 @@
       <c r="A325" s="2"/>
       <c r="B325" s="2"/>
       <c r="C325" s="2"/>
-      <c r="D325" s="50"/>
+      <c r="D325" s="49"/>
       <c r="E325" s="2"/>
       <c r="F325" s="2"/>
       <c r="G325" s="2"/>
@@ -11802,7 +11827,7 @@
       <c r="A326" s="2"/>
       <c r="B326" s="2"/>
       <c r="C326" s="2"/>
-      <c r="D326" s="50"/>
+      <c r="D326" s="49"/>
       <c r="E326" s="2"/>
       <c r="F326" s="2"/>
       <c r="G326" s="2"/>
@@ -11830,7 +11855,7 @@
       <c r="A327" s="2"/>
       <c r="B327" s="2"/>
       <c r="C327" s="2"/>
-      <c r="D327" s="50"/>
+      <c r="D327" s="49"/>
       <c r="E327" s="2"/>
       <c r="F327" s="2"/>
       <c r="G327" s="2"/>
@@ -11858,7 +11883,7 @@
       <c r="A328" s="2"/>
       <c r="B328" s="2"/>
       <c r="C328" s="2"/>
-      <c r="D328" s="50"/>
+      <c r="D328" s="49"/>
       <c r="E328" s="2"/>
       <c r="F328" s="2"/>
       <c r="G328" s="2"/>
@@ -11886,7 +11911,7 @@
       <c r="A329" s="2"/>
       <c r="B329" s="2"/>
       <c r="C329" s="2"/>
-      <c r="D329" s="50"/>
+      <c r="D329" s="49"/>
       <c r="E329" s="2"/>
       <c r="F329" s="2"/>
       <c r="G329" s="2"/>
@@ -11914,7 +11939,7 @@
       <c r="A330" s="2"/>
       <c r="B330" s="2"/>
       <c r="C330" s="2"/>
-      <c r="D330" s="50"/>
+      <c r="D330" s="49"/>
       <c r="E330" s="2"/>
       <c r="F330" s="2"/>
       <c r="G330" s="2"/>
@@ -11942,7 +11967,7 @@
       <c r="A331" s="2"/>
       <c r="B331" s="2"/>
       <c r="C331" s="2"/>
-      <c r="D331" s="50"/>
+      <c r="D331" s="49"/>
       <c r="E331" s="2"/>
       <c r="F331" s="2"/>
       <c r="G331" s="2"/>
@@ -11970,7 +11995,7 @@
       <c r="A332" s="2"/>
       <c r="B332" s="2"/>
       <c r="C332" s="2"/>
-      <c r="D332" s="50"/>
+      <c r="D332" s="49"/>
       <c r="E332" s="2"/>
       <c r="F332" s="2"/>
       <c r="G332" s="2"/>
@@ -11998,7 +12023,7 @@
       <c r="A333" s="2"/>
       <c r="B333" s="2"/>
       <c r="C333" s="2"/>
-      <c r="D333" s="50"/>
+      <c r="D333" s="49"/>
       <c r="E333" s="2"/>
       <c r="F333" s="2"/>
       <c r="G333" s="2"/>
@@ -12026,7 +12051,7 @@
       <c r="A334" s="2"/>
       <c r="B334" s="2"/>
       <c r="C334" s="2"/>
-      <c r="D334" s="50"/>
+      <c r="D334" s="49"/>
       <c r="E334" s="2"/>
       <c r="F334" s="2"/>
       <c r="G334" s="2"/>
@@ -12054,7 +12079,7 @@
       <c r="A335" s="2"/>
       <c r="B335" s="2"/>
       <c r="C335" s="2"/>
-      <c r="D335" s="50"/>
+      <c r="D335" s="49"/>
       <c r="E335" s="2"/>
       <c r="F335" s="2"/>
       <c r="G335" s="2"/>
@@ -12082,7 +12107,7 @@
       <c r="A336" s="2"/>
       <c r="B336" s="2"/>
       <c r="C336" s="2"/>
-      <c r="D336" s="50"/>
+      <c r="D336" s="49"/>
       <c r="E336" s="2"/>
       <c r="F336" s="2"/>
       <c r="G336" s="2"/>
@@ -12110,7 +12135,7 @@
       <c r="A337" s="2"/>
       <c r="B337" s="2"/>
       <c r="C337" s="2"/>
-      <c r="D337" s="50"/>
+      <c r="D337" s="49"/>
       <c r="E337" s="2"/>
       <c r="F337" s="2"/>
       <c r="G337" s="2"/>
@@ -12138,7 +12163,7 @@
       <c r="A338" s="2"/>
       <c r="B338" s="2"/>
       <c r="C338" s="2"/>
-      <c r="D338" s="50"/>
+      <c r="D338" s="49"/>
       <c r="E338" s="2"/>
       <c r="F338" s="2"/>
       <c r="G338" s="2"/>
@@ -12166,7 +12191,7 @@
       <c r="A339" s="2"/>
       <c r="B339" s="2"/>
       <c r="C339" s="2"/>
-      <c r="D339" s="50"/>
+      <c r="D339" s="49"/>
       <c r="E339" s="2"/>
       <c r="F339" s="2"/>
       <c r="G339" s="2"/>
@@ -12194,7 +12219,7 @@
       <c r="A340" s="2"/>
       <c r="B340" s="2"/>
       <c r="C340" s="2"/>
-      <c r="D340" s="50"/>
+      <c r="D340" s="49"/>
       <c r="E340" s="2"/>
       <c r="F340" s="2"/>
       <c r="G340" s="2"/>
@@ -12222,7 +12247,7 @@
       <c r="A341" s="2"/>
       <c r="B341" s="2"/>
       <c r="C341" s="2"/>
-      <c r="D341" s="50"/>
+      <c r="D341" s="49"/>
       <c r="E341" s="2"/>
       <c r="F341" s="2"/>
       <c r="G341" s="2"/>
@@ -12250,7 +12275,7 @@
       <c r="A342" s="2"/>
       <c r="B342" s="2"/>
       <c r="C342" s="2"/>
-      <c r="D342" s="50"/>
+      <c r="D342" s="49"/>
       <c r="E342" s="2"/>
       <c r="F342" s="2"/>
       <c r="G342" s="2"/>
@@ -12278,7 +12303,7 @@
       <c r="A343" s="2"/>
       <c r="B343" s="2"/>
       <c r="C343" s="2"/>
-      <c r="D343" s="50"/>
+      <c r="D343" s="49"/>
       <c r="E343" s="2"/>
       <c r="F343" s="2"/>
       <c r="G343" s="2"/>
@@ -12306,7 +12331,7 @@
       <c r="A344" s="2"/>
       <c r="B344" s="2"/>
       <c r="C344" s="2"/>
-      <c r="D344" s="50"/>
+      <c r="D344" s="49"/>
       <c r="E344" s="2"/>
       <c r="F344" s="2"/>
       <c r="G344" s="2"/>
@@ -12334,7 +12359,7 @@
       <c r="A345" s="2"/>
       <c r="B345" s="2"/>
       <c r="C345" s="2"/>
-      <c r="D345" s="50"/>
+      <c r="D345" s="49"/>
       <c r="E345" s="2"/>
       <c r="F345" s="2"/>
       <c r="G345" s="2"/>
@@ -12362,7 +12387,7 @@
       <c r="A346" s="2"/>
       <c r="B346" s="2"/>
       <c r="C346" s="2"/>
-      <c r="D346" s="50"/>
+      <c r="D346" s="49"/>
       <c r="E346" s="2"/>
       <c r="F346" s="2"/>
       <c r="G346" s="2"/>
@@ -12390,7 +12415,7 @@
       <c r="A347" s="2"/>
       <c r="B347" s="2"/>
       <c r="C347" s="2"/>
-      <c r="D347" s="50"/>
+      <c r="D347" s="49"/>
       <c r="E347" s="2"/>
       <c r="F347" s="2"/>
       <c r="G347" s="2"/>
@@ -12418,7 +12443,7 @@
       <c r="A348" s="2"/>
       <c r="B348" s="2"/>
       <c r="C348" s="2"/>
-      <c r="D348" s="50"/>
+      <c r="D348" s="49"/>
       <c r="E348" s="2"/>
       <c r="F348" s="2"/>
       <c r="G348" s="2"/>
@@ -12446,7 +12471,7 @@
       <c r="A349" s="2"/>
       <c r="B349" s="2"/>
       <c r="C349" s="2"/>
-      <c r="D349" s="50"/>
+      <c r="D349" s="49"/>
       <c r="E349" s="2"/>
       <c r="F349" s="2"/>
       <c r="G349" s="2"/>
@@ -12474,7 +12499,7 @@
       <c r="A350" s="2"/>
       <c r="B350" s="2"/>
       <c r="C350" s="2"/>
-      <c r="D350" s="50"/>
+      <c r="D350" s="49"/>
       <c r="E350" s="2"/>
       <c r="F350" s="2"/>
       <c r="G350" s="2"/>
@@ -12502,7 +12527,7 @@
       <c r="A351" s="2"/>
       <c r="B351" s="2"/>
       <c r="C351" s="2"/>
-      <c r="D351" s="50"/>
+      <c r="D351" s="49"/>
       <c r="E351" s="2"/>
       <c r="F351" s="2"/>
       <c r="G351" s="2"/>
@@ -12530,7 +12555,7 @@
       <c r="A352" s="2"/>
       <c r="B352" s="2"/>
       <c r="C352" s="2"/>
-      <c r="D352" s="50"/>
+      <c r="D352" s="49"/>
       <c r="E352" s="2"/>
       <c r="F352" s="2"/>
       <c r="G352" s="2"/>
@@ -12558,7 +12583,7 @@
       <c r="A353" s="2"/>
       <c r="B353" s="2"/>
       <c r="C353" s="2"/>
-      <c r="D353" s="50"/>
+      <c r="D353" s="49"/>
       <c r="E353" s="2"/>
       <c r="F353" s="2"/>
       <c r="G353" s="2"/>
@@ -12586,7 +12611,7 @@
       <c r="A354" s="2"/>
       <c r="B354" s="2"/>
       <c r="C354" s="2"/>
-      <c r="D354" s="50"/>
+      <c r="D354" s="49"/>
       <c r="E354" s="2"/>
       <c r="F354" s="2"/>
       <c r="G354" s="2"/>
@@ -12614,7 +12639,7 @@
       <c r="A355" s="2"/>
       <c r="B355" s="2"/>
       <c r="C355" s="2"/>
-      <c r="D355" s="50"/>
+      <c r="D355" s="49"/>
       <c r="E355" s="2"/>
       <c r="F355" s="2"/>
       <c r="G355" s="2"/>
@@ -12642,7 +12667,7 @@
       <c r="A356" s="2"/>
       <c r="B356" s="2"/>
       <c r="C356" s="2"/>
-      <c r="D356" s="50"/>
+      <c r="D356" s="49"/>
       <c r="E356" s="2"/>
       <c r="F356" s="2"/>
       <c r="G356" s="2"/>
@@ -12670,7 +12695,7 @@
       <c r="A357" s="2"/>
       <c r="B357" s="2"/>
       <c r="C357" s="2"/>
-      <c r="D357" s="50"/>
+      <c r="D357" s="49"/>
       <c r="E357" s="2"/>
       <c r="F357" s="2"/>
       <c r="G357" s="2"/>
@@ -12698,7 +12723,7 @@
       <c r="A358" s="2"/>
       <c r="B358" s="2"/>
       <c r="C358" s="2"/>
-      <c r="D358" s="50"/>
+      <c r="D358" s="49"/>
       <c r="E358" s="2"/>
       <c r="F358" s="2"/>
       <c r="G358" s="2"/>
@@ -12726,7 +12751,7 @@
       <c r="A359" s="2"/>
       <c r="B359" s="2"/>
       <c r="C359" s="2"/>
-      <c r="D359" s="50"/>
+      <c r="D359" s="49"/>
       <c r="E359" s="2"/>
       <c r="F359" s="2"/>
       <c r="G359" s="2"/>
@@ -12754,7 +12779,7 @@
       <c r="A360" s="2"/>
       <c r="B360" s="2"/>
       <c r="C360" s="2"/>
-      <c r="D360" s="50"/>
+      <c r="D360" s="49"/>
       <c r="E360" s="2"/>
       <c r="F360" s="2"/>
       <c r="G360" s="2"/>
@@ -12782,7 +12807,7 @@
       <c r="A361" s="2"/>
       <c r="B361" s="2"/>
       <c r="C361" s="2"/>
-      <c r="D361" s="50"/>
+      <c r="D361" s="49"/>
       <c r="E361" s="2"/>
       <c r="F361" s="2"/>
       <c r="G361" s="2"/>
@@ -12810,7 +12835,7 @@
       <c r="A362" s="2"/>
       <c r="B362" s="2"/>
       <c r="C362" s="2"/>
-      <c r="D362" s="50"/>
+      <c r="D362" s="49"/>
       <c r="E362" s="2"/>
       <c r="F362" s="2"/>
       <c r="G362" s="2"/>
@@ -12838,7 +12863,7 @@
       <c r="A363" s="2"/>
       <c r="B363" s="2"/>
       <c r="C363" s="2"/>
-      <c r="D363" s="50"/>
+      <c r="D363" s="49"/>
       <c r="E363" s="2"/>
       <c r="F363" s="2"/>
       <c r="G363" s="2"/>
@@ -12866,7 +12891,7 @@
       <c r="A364" s="2"/>
       <c r="B364" s="2"/>
       <c r="C364" s="2"/>
-      <c r="D364" s="50"/>
+      <c r="D364" s="49"/>
       <c r="E364" s="2"/>
       <c r="F364" s="2"/>
       <c r="G364" s="2"/>
@@ -12894,7 +12919,7 @@
       <c r="A365" s="2"/>
       <c r="B365" s="2"/>
       <c r="C365" s="2"/>
-      <c r="D365" s="50"/>
+      <c r="D365" s="49"/>
       <c r="E365" s="2"/>
       <c r="F365" s="2"/>
       <c r="G365" s="2"/>
@@ -12922,7 +12947,7 @@
       <c r="A366" s="2"/>
       <c r="B366" s="2"/>
       <c r="C366" s="2"/>
-      <c r="D366" s="50"/>
+      <c r="D366" s="49"/>
       <c r="E366" s="2"/>
       <c r="F366" s="2"/>
       <c r="G366" s="2"/>
@@ -12950,7 +12975,7 @@
       <c r="A367" s="2"/>
       <c r="B367" s="2"/>
       <c r="C367" s="2"/>
-      <c r="D367" s="50"/>
+      <c r="D367" s="49"/>
       <c r="E367" s="2"/>
       <c r="F367" s="2"/>
       <c r="G367" s="2"/>
@@ -12978,7 +13003,7 @@
       <c r="A368" s="2"/>
       <c r="B368" s="2"/>
       <c r="C368" s="2"/>
-      <c r="D368" s="50"/>
+      <c r="D368" s="49"/>
       <c r="E368" s="2"/>
       <c r="F368" s="2"/>
       <c r="G368" s="2"/>
@@ -13006,7 +13031,7 @@
       <c r="A369" s="2"/>
       <c r="B369" s="2"/>
       <c r="C369" s="2"/>
-      <c r="D369" s="50"/>
+      <c r="D369" s="49"/>
       <c r="E369" s="2"/>
       <c r="F369" s="2"/>
       <c r="G369" s="2"/>
@@ -13034,7 +13059,7 @@
       <c r="A370" s="2"/>
       <c r="B370" s="2"/>
       <c r="C370" s="2"/>
-      <c r="D370" s="50"/>
+      <c r="D370" s="49"/>
       <c r="E370" s="2"/>
       <c r="F370" s="2"/>
       <c r="G370" s="2"/>
@@ -13062,7 +13087,7 @@
       <c r="A371" s="2"/>
       <c r="B371" s="2"/>
       <c r="C371" s="2"/>
-      <c r="D371" s="50"/>
+      <c r="D371" s="49"/>
       <c r="E371" s="2"/>
       <c r="F371" s="2"/>
       <c r="G371" s="2"/>
@@ -13090,7 +13115,7 @@
       <c r="A372" s="2"/>
       <c r="B372" s="2"/>
       <c r="C372" s="2"/>
-      <c r="D372" s="50"/>
+      <c r="D372" s="49"/>
       <c r="E372" s="2"/>
       <c r="F372" s="2"/>
       <c r="G372" s="2"/>
@@ -13118,7 +13143,7 @@
       <c r="A373" s="2"/>
       <c r="B373" s="2"/>
       <c r="C373" s="2"/>
-      <c r="D373" s="50"/>
+      <c r="D373" s="49"/>
       <c r="E373" s="2"/>
       <c r="F373" s="2"/>
       <c r="G373" s="2"/>
@@ -13146,7 +13171,7 @@
       <c r="A374" s="2"/>
       <c r="B374" s="2"/>
       <c r="C374" s="2"/>
-      <c r="D374" s="50"/>
+      <c r="D374" s="49"/>
       <c r="E374" s="2"/>
       <c r="F374" s="2"/>
       <c r="G374" s="2"/>
@@ -13174,7 +13199,7 @@
       <c r="A375" s="2"/>
       <c r="B375" s="2"/>
       <c r="C375" s="2"/>
-      <c r="D375" s="50"/>
+      <c r="D375" s="49"/>
       <c r="E375" s="2"/>
       <c r="F375" s="2"/>
       <c r="G375" s="2"/>
@@ -13202,7 +13227,7 @@
       <c r="A376" s="2"/>
       <c r="B376" s="2"/>
       <c r="C376" s="2"/>
-      <c r="D376" s="50"/>
+      <c r="D376" s="49"/>
       <c r="E376" s="2"/>
       <c r="F376" s="2"/>
       <c r="G376" s="2"/>
@@ -13230,7 +13255,7 @@
       <c r="A377" s="2"/>
       <c r="B377" s="2"/>
       <c r="C377" s="2"/>
-      <c r="D377" s="50"/>
+      <c r="D377" s="49"/>
       <c r="E377" s="2"/>
       <c r="F377" s="2"/>
       <c r="G377" s="2"/>
@@ -13258,7 +13283,7 @@
       <c r="A378" s="2"/>
       <c r="B378" s="2"/>
       <c r="C378" s="2"/>
-      <c r="D378" s="50"/>
+      <c r="D378" s="49"/>
       <c r="E378" s="2"/>
       <c r="F378" s="2"/>
       <c r="G378" s="2"/>
@@ -13286,7 +13311,7 @@
       <c r="A379" s="2"/>
       <c r="B379" s="2"/>
       <c r="C379" s="2"/>
-      <c r="D379" s="50"/>
+      <c r="D379" s="49"/>
       <c r="E379" s="2"/>
       <c r="F379" s="2"/>
       <c r="G379" s="2"/>
@@ -13314,7 +13339,7 @@
       <c r="A380" s="2"/>
       <c r="B380" s="2"/>
       <c r="C380" s="2"/>
-      <c r="D380" s="50"/>
+      <c r="D380" s="49"/>
       <c r="E380" s="2"/>
       <c r="F380" s="2"/>
       <c r="G380" s="2"/>
@@ -13342,7 +13367,7 @@
       <c r="A381" s="2"/>
       <c r="B381" s="2"/>
       <c r="C381" s="2"/>
-      <c r="D381" s="50"/>
+      <c r="D381" s="49"/>
       <c r="E381" s="2"/>
       <c r="F381" s="2"/>
       <c r="G381" s="2"/>
@@ -13370,7 +13395,7 @@
       <c r="A382" s="2"/>
       <c r="B382" s="2"/>
       <c r="C382" s="2"/>
-      <c r="D382" s="50"/>
+      <c r="D382" s="49"/>
       <c r="E382" s="2"/>
       <c r="F382" s="2"/>
       <c r="G382" s="2"/>
@@ -13398,7 +13423,7 @@
       <c r="A383" s="2"/>
       <c r="B383" s="2"/>
       <c r="C383" s="2"/>
-      <c r="D383" s="50"/>
+      <c r="D383" s="49"/>
       <c r="E383" s="2"/>
       <c r="F383" s="2"/>
       <c r="G383" s="2"/>
@@ -13426,7 +13451,7 @@
       <c r="A384" s="2"/>
       <c r="B384" s="2"/>
       <c r="C384" s="2"/>
-      <c r="D384" s="50"/>
+      <c r="D384" s="49"/>
       <c r="E384" s="2"/>
       <c r="F384" s="2"/>
       <c r="G384" s="2"/>
@@ -13454,7 +13479,7 @@
       <c r="A385" s="2"/>
       <c r="B385" s="2"/>
       <c r="C385" s="2"/>
-      <c r="D385" s="50"/>
+      <c r="D385" s="49"/>
       <c r="E385" s="2"/>
       <c r="F385" s="2"/>
       <c r="G385" s="2"/>
@@ -13482,7 +13507,7 @@
       <c r="A386" s="2"/>
       <c r="B386" s="2"/>
       <c r="C386" s="2"/>
-      <c r="D386" s="50"/>
+      <c r="D386" s="49"/>
       <c r="E386" s="2"/>
       <c r="F386" s="2"/>
       <c r="G386" s="2"/>
@@ -13510,7 +13535,7 @@
       <c r="A387" s="2"/>
       <c r="B387" s="2"/>
       <c r="C387" s="2"/>
-      <c r="D387" s="50"/>
+      <c r="D387" s="49"/>
       <c r="E387" s="2"/>
       <c r="F387" s="2"/>
       <c r="G387" s="2"/>
@@ -13538,7 +13563,7 @@
       <c r="A388" s="2"/>
       <c r="B388" s="2"/>
       <c r="C388" s="2"/>
-      <c r="D388" s="50"/>
+      <c r="D388" s="49"/>
       <c r="E388" s="2"/>
       <c r="F388" s="2"/>
       <c r="G388" s="2"/>
@@ -13566,7 +13591,7 @@
       <c r="A389" s="2"/>
       <c r="B389" s="2"/>
       <c r="C389" s="2"/>
-      <c r="D389" s="50"/>
+      <c r="D389" s="49"/>
       <c r="E389" s="2"/>
       <c r="F389" s="2"/>
       <c r="G389" s="2"/>
@@ -13594,7 +13619,7 @@
       <c r="A390" s="2"/>
       <c r="B390" s="2"/>
       <c r="C390" s="2"/>
-      <c r="D390" s="50"/>
+      <c r="D390" s="49"/>
       <c r="E390" s="2"/>
       <c r="F390" s="2"/>
       <c r="G390" s="2"/>
@@ -13622,7 +13647,7 @@
       <c r="A391" s="2"/>
       <c r="B391" s="2"/>
       <c r="C391" s="2"/>
-      <c r="D391" s="50"/>
+      <c r="D391" s="49"/>
       <c r="E391" s="2"/>
       <c r="F391" s="2"/>
       <c r="G391" s="2"/>
@@ -13650,7 +13675,7 @@
       <c r="A392" s="2"/>
       <c r="B392" s="2"/>
       <c r="C392" s="2"/>
-      <c r="D392" s="50"/>
+      <c r="D392" s="49"/>
       <c r="E392" s="2"/>
       <c r="F392" s="2"/>
       <c r="G392" s="2"/>
@@ -13678,7 +13703,7 @@
       <c r="A393" s="2"/>
       <c r="B393" s="2"/>
       <c r="C393" s="2"/>
-      <c r="D393" s="50"/>
+      <c r="D393" s="49"/>
       <c r="E393" s="2"/>
       <c r="F393" s="2"/>
       <c r="G393" s="2"/>
@@ -13706,7 +13731,7 @@
       <c r="A394" s="2"/>
       <c r="B394" s="2"/>
       <c r="C394" s="2"/>
-      <c r="D394" s="50"/>
+      <c r="D394" s="49"/>
       <c r="E394" s="2"/>
       <c r="F394" s="2"/>
       <c r="G394" s="2"/>
@@ -13734,7 +13759,7 @@
       <c r="A395" s="2"/>
       <c r="B395" s="2"/>
       <c r="C395" s="2"/>
-      <c r="D395" s="50"/>
+      <c r="D395" s="49"/>
       <c r="E395" s="2"/>
       <c r="F395" s="2"/>
       <c r="G395" s="2"/>
@@ -13762,7 +13787,7 @@
       <c r="A396" s="2"/>
       <c r="B396" s="2"/>
       <c r="C396" s="2"/>
-      <c r="D396" s="50"/>
+      <c r="D396" s="49"/>
       <c r="E396" s="2"/>
       <c r="F396" s="2"/>
       <c r="G396" s="2"/>
@@ -13790,7 +13815,7 @@
       <c r="A397" s="2"/>
       <c r="B397" s="2"/>
       <c r="C397" s="2"/>
-      <c r="D397" s="50"/>
+      <c r="D397" s="49"/>
       <c r="E397" s="2"/>
       <c r="F397" s="2"/>
       <c r="G397" s="2"/>
@@ -13818,7 +13843,7 @@
       <c r="A398" s="2"/>
       <c r="B398" s="2"/>
       <c r="C398" s="2"/>
-      <c r="D398" s="50"/>
+      <c r="D398" s="49"/>
       <c r="E398" s="2"/>
       <c r="F398" s="2"/>
       <c r="G398" s="2"/>
@@ -13846,7 +13871,7 @@
       <c r="A399" s="2"/>
       <c r="B399" s="2"/>
       <c r="C399" s="2"/>
-      <c r="D399" s="50"/>
+      <c r="D399" s="49"/>
       <c r="E399" s="2"/>
       <c r="F399" s="2"/>
       <c r="G399" s="2"/>
@@ -13874,7 +13899,7 @@
       <c r="A400" s="2"/>
       <c r="B400" s="2"/>
       <c r="C400" s="2"/>
-      <c r="D400" s="50"/>
+      <c r="D400" s="49"/>
       <c r="E400" s="2"/>
       <c r="F400" s="2"/>
       <c r="G400" s="2"/>
@@ -13902,7 +13927,7 @@
       <c r="A401" s="2"/>
       <c r="B401" s="2"/>
       <c r="C401" s="2"/>
-      <c r="D401" s="50"/>
+      <c r="D401" s="49"/>
       <c r="E401" s="2"/>
       <c r="F401" s="2"/>
       <c r="G401" s="2"/>
@@ -13930,7 +13955,7 @@
       <c r="A402" s="2"/>
       <c r="B402" s="2"/>
       <c r="C402" s="2"/>
-      <c r="D402" s="50"/>
+      <c r="D402" s="49"/>
       <c r="E402" s="2"/>
       <c r="F402" s="2"/>
       <c r="G402" s="2"/>
@@ -13958,7 +13983,7 @@
       <c r="A403" s="2"/>
       <c r="B403" s="2"/>
       <c r="C403" s="2"/>
-      <c r="D403" s="50"/>
+      <c r="D403" s="49"/>
       <c r="E403" s="2"/>
       <c r="F403" s="2"/>
       <c r="G403" s="2"/>
@@ -13986,7 +14011,7 @@
       <c r="A404" s="2"/>
       <c r="B404" s="2"/>
       <c r="C404" s="2"/>
-      <c r="D404" s="50"/>
+      <c r="D404" s="49"/>
       <c r="E404" s="2"/>
       <c r="F404" s="2"/>
       <c r="G404" s="2"/>
@@ -14014,7 +14039,7 @@
       <c r="A405" s="2"/>
       <c r="B405" s="2"/>
       <c r="C405" s="2"/>
-      <c r="D405" s="50"/>
+      <c r="D405" s="49"/>
       <c r="E405" s="2"/>
       <c r="F405" s="2"/>
       <c r="G405" s="2"/>
@@ -14042,7 +14067,7 @@
       <c r="A406" s="2"/>
       <c r="B406" s="2"/>
       <c r="C406" s="2"/>
-      <c r="D406" s="50"/>
+      <c r="D406" s="49"/>
       <c r="E406" s="2"/>
       <c r="F406" s="2"/>
       <c r="G406" s="2"/>
@@ -14070,7 +14095,7 @@
       <c r="A407" s="2"/>
       <c r="B407" s="2"/>
       <c r="C407" s="2"/>
-      <c r="D407" s="50"/>
+      <c r="D407" s="49"/>
       <c r="E407" s="2"/>
       <c r="F407" s="2"/>
       <c r="G407" s="2"/>
@@ -14098,7 +14123,7 @@
       <c r="A408" s="2"/>
       <c r="B408" s="2"/>
       <c r="C408" s="2"/>
-      <c r="D408" s="50"/>
+      <c r="D408" s="49"/>
       <c r="E408" s="2"/>
       <c r="F408" s="2"/>
       <c r="G408" s="2"/>
@@ -14126,7 +14151,7 @@
       <c r="A409" s="2"/>
       <c r="B409" s="2"/>
       <c r="C409" s="2"/>
-      <c r="D409" s="50"/>
+      <c r="D409" s="49"/>
       <c r="E409" s="2"/>
       <c r="F409" s="2"/>
       <c r="G409" s="2"/>
@@ -14154,7 +14179,7 @@
       <c r="A410" s="2"/>
       <c r="B410" s="2"/>
       <c r="C410" s="2"/>
-      <c r="D410" s="50"/>
+      <c r="D410" s="49"/>
       <c r="E410" s="2"/>
       <c r="F410" s="2"/>
       <c r="G410" s="2"/>
@@ -14182,7 +14207,7 @@
       <c r="A411" s="2"/>
       <c r="B411" s="2"/>
       <c r="C411" s="2"/>
-      <c r="D411" s="50"/>
+      <c r="D411" s="49"/>
       <c r="E411" s="2"/>
       <c r="F411" s="2"/>
       <c r="G411" s="2"/>
@@ -14210,7 +14235,7 @@
       <c r="A412" s="2"/>
       <c r="B412" s="2"/>
       <c r="C412" s="2"/>
-      <c r="D412" s="50"/>
+      <c r="D412" s="49"/>
       <c r="E412" s="2"/>
       <c r="F412" s="2"/>
       <c r="G412" s="2"/>
@@ -14238,7 +14263,7 @@
       <c r="A413" s="2"/>
       <c r="B413" s="2"/>
       <c r="C413" s="2"/>
-      <c r="D413" s="50"/>
+      <c r="D413" s="49"/>
       <c r="E413" s="2"/>
       <c r="F413" s="2"/>
       <c r="G413" s="2"/>
@@ -14266,7 +14291,7 @@
       <c r="A414" s="2"/>
       <c r="B414" s="2"/>
       <c r="C414" s="2"/>
-      <c r="D414" s="50"/>
+      <c r="D414" s="49"/>
       <c r="E414" s="2"/>
       <c r="F414" s="2"/>
       <c r="G414" s="2"/>
@@ -14294,7 +14319,7 @@
       <c r="A415" s="2"/>
       <c r="B415" s="2"/>
       <c r="C415" s="2"/>
-      <c r="D415" s="50"/>
+      <c r="D415" s="49"/>
       <c r="E415" s="2"/>
       <c r="F415" s="2"/>
       <c r="G415" s="2"/>
@@ -14322,7 +14347,7 @@
       <c r="A416" s="2"/>
       <c r="B416" s="2"/>
       <c r="C416" s="2"/>
-      <c r="D416" s="50"/>
+      <c r="D416" s="49"/>
       <c r="E416" s="2"/>
       <c r="F416" s="2"/>
       <c r="G416" s="2"/>
@@ -14350,7 +14375,7 @@
       <c r="A417" s="2"/>
       <c r="B417" s="2"/>
       <c r="C417" s="2"/>
-      <c r="D417" s="50"/>
+      <c r="D417" s="49"/>
       <c r="E417" s="2"/>
       <c r="F417" s="2"/>
       <c r="G417" s="2"/>
@@ -14378,7 +14403,7 @@
       <c r="A418" s="2"/>
       <c r="B418" s="2"/>
       <c r="C418" s="2"/>
-      <c r="D418" s="50"/>
+      <c r="D418" s="49"/>
       <c r="E418" s="2"/>
       <c r="F418" s="2"/>
       <c r="G418" s="2"/>
@@ -14406,7 +14431,7 @@
       <c r="A419" s="2"/>
       <c r="B419" s="2"/>
       <c r="C419" s="2"/>
-      <c r="D419" s="50"/>
+      <c r="D419" s="49"/>
       <c r="E419" s="2"/>
       <c r="F419" s="2"/>
       <c r="G419" s="2"/>
@@ -14434,7 +14459,7 @@
       <c r="A420" s="2"/>
       <c r="B420" s="2"/>
       <c r="C420" s="2"/>
-      <c r="D420" s="50"/>
+      <c r="D420" s="49"/>
       <c r="E420" s="2"/>
       <c r="F420" s="2"/>
       <c r="G420" s="2"/>
@@ -14462,7 +14487,7 @@
       <c r="A421" s="2"/>
       <c r="B421" s="2"/>
       <c r="C421" s="2"/>
-      <c r="D421" s="50"/>
+      <c r="D421" s="49"/>
       <c r="E421" s="2"/>
       <c r="F421" s="2"/>
       <c r="G421" s="2"/>
@@ -14490,7 +14515,7 @@
       <c r="A422" s="2"/>
       <c r="B422" s="2"/>
       <c r="C422" s="2"/>
-      <c r="D422" s="50"/>
+      <c r="D422" s="49"/>
       <c r="E422" s="2"/>
       <c r="F422" s="2"/>
       <c r="G422" s="2"/>
@@ -14518,7 +14543,7 @@
       <c r="A423" s="2"/>
       <c r="B423" s="2"/>
       <c r="C423" s="2"/>
-      <c r="D423" s="50"/>
+      <c r="D423" s="49"/>
       <c r="E423" s="2"/>
       <c r="F423" s="2"/>
       <c r="G423" s="2"/>
@@ -14546,7 +14571,7 @@
       <c r="A424" s="2"/>
       <c r="B424" s="2"/>
       <c r="C424" s="2"/>
-      <c r="D424" s="50"/>
+      <c r="D424" s="49"/>
       <c r="E424" s="2"/>
       <c r="F424" s="2"/>
       <c r="G424" s="2"/>
@@ -14574,7 +14599,7 @@
       <c r="A425" s="2"/>
       <c r="B425" s="2"/>
       <c r="C425" s="2"/>
-      <c r="D425" s="50"/>
+      <c r="D425" s="49"/>
       <c r="E425" s="2"/>
       <c r="F425" s="2"/>
       <c r="G425" s="2"/>
@@ -14602,7 +14627,7 @@
       <c r="A426" s="2"/>
       <c r="B426" s="2"/>
       <c r="C426" s="2"/>
-      <c r="D426" s="50"/>
+      <c r="D426" s="49"/>
       <c r="E426" s="2"/>
       <c r="F426" s="2"/>
       <c r="G426" s="2"/>
@@ -14630,7 +14655,7 @@
       <c r="A427" s="2"/>
       <c r="B427" s="2"/>
       <c r="C427" s="2"/>
-      <c r="D427" s="50"/>
+      <c r="D427" s="49"/>
       <c r="E427" s="2"/>
       <c r="F427" s="2"/>
       <c r="G427" s="2"/>
@@ -14658,7 +14683,7 @@
       <c r="A428" s="2"/>
       <c r="B428" s="2"/>
       <c r="C428" s="2"/>
-      <c r="D428" s="50"/>
+      <c r="D428" s="49"/>
       <c r="E428" s="2"/>
       <c r="F428" s="2"/>
       <c r="G428" s="2"/>
@@ -14686,7 +14711,7 @@
       <c r="A429" s="2"/>
       <c r="B429" s="2"/>
       <c r="C429" s="2"/>
-      <c r="D429" s="50"/>
+      <c r="D429" s="49"/>
       <c r="E429" s="2"/>
       <c r="F429" s="2"/>
       <c r="G429" s="2"/>
@@ -14714,7 +14739,7 @@
       <c r="A430" s="2"/>
       <c r="B430" s="2"/>
       <c r="C430" s="2"/>
-      <c r="D430" s="50"/>
+      <c r="D430" s="49"/>
       <c r="E430" s="2"/>
       <c r="F430" s="2"/>
       <c r="G430" s="2"/>
@@ -14742,7 +14767,7 @@
       <c r="A431" s="2"/>
       <c r="B431" s="2"/>
       <c r="C431" s="2"/>
-      <c r="D431" s="50"/>
+      <c r="D431" s="49"/>
       <c r="E431" s="2"/>
       <c r="F431" s="2"/>
       <c r="G431" s="2"/>
@@ -14770,7 +14795,7 @@
       <c r="A432" s="2"/>
       <c r="B432" s="2"/>
       <c r="C432" s="2"/>
-      <c r="D432" s="50"/>
+      <c r="D432" s="49"/>
       <c r="E432" s="2"/>
       <c r="F432" s="2"/>
       <c r="G432" s="2"/>
@@ -14798,7 +14823,7 @@
       <c r="A433" s="2"/>
       <c r="B433" s="2"/>
       <c r="C433" s="2"/>
-      <c r="D433" s="50"/>
+      <c r="D433" s="49"/>
       <c r="E433" s="2"/>
       <c r="F433" s="2"/>
       <c r="G433" s="2"/>
@@ -14826,7 +14851,7 @@
       <c r="A434" s="2"/>
       <c r="B434" s="2"/>
       <c r="C434" s="2"/>
-      <c r="D434" s="50"/>
+      <c r="D434" s="49"/>
       <c r="E434" s="2"/>
       <c r="F434" s="2"/>
       <c r="G434" s="2"/>
@@ -14854,7 +14879,7 @@
       <c r="A435" s="2"/>
       <c r="B435" s="2"/>
       <c r="C435" s="2"/>
-      <c r="D435" s="50"/>
+      <c r="D435" s="49"/>
       <c r="E435" s="2"/>
       <c r="F435" s="2"/>
       <c r="G435" s="2"/>
@@ -14882,7 +14907,7 @@
       <c r="A436" s="2"/>
       <c r="B436" s="2"/>
       <c r="C436" s="2"/>
-      <c r="D436" s="50"/>
+      <c r="D436" s="49"/>
       <c r="E436" s="2"/>
       <c r="F436" s="2"/>
       <c r="G436" s="2"/>
@@ -14910,7 +14935,7 @@
       <c r="A437" s="2"/>
       <c r="B437" s="2"/>
       <c r="C437" s="2"/>
-      <c r="D437" s="50"/>
+      <c r="D437" s="49"/>
       <c r="E437" s="2"/>
       <c r="F437" s="2"/>
       <c r="G437" s="2"/>
@@ -14938,7 +14963,7 @@
       <c r="A438" s="2"/>
       <c r="B438" s="2"/>
       <c r="C438" s="2"/>
-      <c r="D438" s="50"/>
+      <c r="D438" s="49"/>
       <c r="E438" s="2"/>
       <c r="F438" s="2"/>
       <c r="G438" s="2"/>
@@ -14966,7 +14991,7 @@
       <c r="A439" s="2"/>
       <c r="B439" s="2"/>
       <c r="C439" s="2"/>
-      <c r="D439" s="50"/>
+      <c r="D439" s="49"/>
       <c r="E439" s="2"/>
       <c r="F439" s="2"/>
       <c r="G439" s="2"/>
@@ -14994,7 +15019,7 @@
       <c r="A440" s="2"/>
       <c r="B440" s="2"/>
       <c r="C440" s="2"/>
-      <c r="D440" s="50"/>
+      <c r="D440" s="49"/>
       <c r="E440" s="2"/>
       <c r="F440" s="2"/>
       <c r="G440" s="2"/>
@@ -15022,7 +15047,7 @@
       <c r="A441" s="2"/>
       <c r="B441" s="2"/>
       <c r="C441" s="2"/>
-      <c r="D441" s="50"/>
+      <c r="D441" s="49"/>
       <c r="E441" s="2"/>
       <c r="F441" s="2"/>
       <c r="G441" s="2"/>
@@ -15050,7 +15075,7 @@
       <c r="A442" s="2"/>
       <c r="B442" s="2"/>
       <c r="C442" s="2"/>
-      <c r="D442" s="50"/>
+      <c r="D442" s="49"/>
       <c r="E442" s="2"/>
       <c r="F442" s="2"/>
       <c r="G442" s="2"/>
@@ -15078,7 +15103,7 @@
       <c r="A443" s="2"/>
       <c r="B443" s="2"/>
       <c r="C443" s="2"/>
-      <c r="D443" s="50"/>
+      <c r="D443" s="49"/>
       <c r="E443" s="2"/>
       <c r="F443" s="2"/>
       <c r="G443" s="2"/>
@@ -15106,7 +15131,7 @@
       <c r="A444" s="2"/>
       <c r="B444" s="2"/>
       <c r="C444" s="2"/>
-      <c r="D444" s="50"/>
+      <c r="D444" s="49"/>
       <c r="E444" s="2"/>
       <c r="F444" s="2"/>
       <c r="G444" s="2"/>
@@ -15134,7 +15159,7 @@
       <c r="A445" s="2"/>
       <c r="B445" s="2"/>
       <c r="C445" s="2"/>
-      <c r="D445" s="50"/>
+      <c r="D445" s="49"/>
       <c r="E445" s="2"/>
       <c r="F445" s="2"/>
       <c r="G445" s="2"/>
@@ -15162,7 +15187,7 @@
       <c r="A446" s="2"/>
       <c r="B446" s="2"/>
       <c r="C446" s="2"/>
-      <c r="D446" s="50"/>
+      <c r="D446" s="49"/>
       <c r="E446" s="2"/>
       <c r="F446" s="2"/>
       <c r="G446" s="2"/>
@@ -15190,7 +15215,7 @@
       <c r="A447" s="2"/>
       <c r="B447" s="2"/>
       <c r="C447" s="2"/>
-      <c r="D447" s="50"/>
+      <c r="D447" s="49"/>
       <c r="E447" s="2"/>
       <c r="F447" s="2"/>
       <c r="G447" s="2"/>
@@ -15218,7 +15243,7 @@
       <c r="A448" s="2"/>
       <c r="B448" s="2"/>
       <c r="C448" s="2"/>
-      <c r="D448" s="50"/>
+      <c r="D448" s="49"/>
       <c r="E448" s="2"/>
       <c r="F448" s="2"/>
       <c r="G448" s="2"/>
@@ -15246,7 +15271,7 @@
       <c r="A449" s="2"/>
       <c r="B449" s="2"/>
       <c r="C449" s="2"/>
-      <c r="D449" s="50"/>
+      <c r="D449" s="49"/>
       <c r="E449" s="2"/>
       <c r="F449" s="2"/>
       <c r="G449" s="2"/>
@@ -15274,7 +15299,7 @@
       <c r="A450" s="2"/>
       <c r="B450" s="2"/>
       <c r="C450" s="2"/>
-      <c r="D450" s="50"/>
+      <c r="D450" s="49"/>
       <c r="E450" s="2"/>
       <c r="F450" s="2"/>
       <c r="G450" s="2"/>
@@ -15302,7 +15327,7 @@
       <c r="A451" s="2"/>
       <c r="B451" s="2"/>
       <c r="C451" s="2"/>
-      <c r="D451" s="50"/>
+      <c r="D451" s="49"/>
       <c r="E451" s="2"/>
       <c r="F451" s="2"/>
       <c r="G451" s="2"/>
@@ -15330,7 +15355,7 @@
       <c r="A452" s="2"/>
       <c r="B452" s="2"/>
       <c r="C452" s="2"/>
-      <c r="D452" s="50"/>
+      <c r="D452" s="49"/>
       <c r="E452" s="2"/>
       <c r="F452" s="2"/>
       <c r="G452" s="2"/>
@@ -15358,7 +15383,7 @@
       <c r="A453" s="2"/>
       <c r="B453" s="2"/>
       <c r="C453" s="2"/>
-      <c r="D453" s="50"/>
+      <c r="D453" s="49"/>
       <c r="E453" s="2"/>
       <c r="F453" s="2"/>
       <c r="G453" s="2"/>
@@ -15386,7 +15411,7 @@
       <c r="A454" s="2"/>
       <c r="B454" s="2"/>
       <c r="C454" s="2"/>
-      <c r="D454" s="50"/>
+      <c r="D454" s="49"/>
       <c r="E454" s="2"/>
       <c r="F454" s="2"/>
       <c r="G454" s="2"/>
@@ -15414,7 +15439,7 @@
       <c r="A455" s="2"/>
       <c r="B455" s="2"/>
       <c r="C455" s="2"/>
-      <c r="D455" s="50"/>
+      <c r="D455" s="49"/>
       <c r="E455" s="2"/>
       <c r="F455" s="2"/>
       <c r="G455" s="2"/>
@@ -15442,7 +15467,7 @@
       <c r="A456" s="2"/>
       <c r="B456" s="2"/>
       <c r="C456" s="2"/>
-      <c r="D456" s="50"/>
+      <c r="D456" s="49"/>
       <c r="E456" s="2"/>
       <c r="F456" s="2"/>
       <c r="G456" s="2"/>
@@ -15470,7 +15495,7 @@
       <c r="A457" s="2"/>
       <c r="B457" s="2"/>
       <c r="C457" s="2"/>
-      <c r="D457" s="50"/>
+      <c r="D457" s="49"/>
       <c r="E457" s="2"/>
       <c r="F457" s="2"/>
       <c r="G457" s="2"/>
@@ -15498,7 +15523,7 @@
       <c r="A458" s="2"/>
       <c r="B458" s="2"/>
       <c r="C458" s="2"/>
-      <c r="D458" s="50"/>
+      <c r="D458" s="49"/>
       <c r="E458" s="2"/>
       <c r="F458" s="2"/>
       <c r="G458" s="2"/>
@@ -15526,7 +15551,7 @@
       <c r="A459" s="2"/>
       <c r="B459" s="2"/>
       <c r="C459" s="2"/>
-      <c r="D459" s="50"/>
+      <c r="D459" s="49"/>
       <c r="E459" s="2"/>
       <c r="F459" s="2"/>
       <c r="G459" s="2"/>
@@ -15554,7 +15579,7 @@
       <c r="A460" s="2"/>
       <c r="B460" s="2"/>
       <c r="C460" s="2"/>
-      <c r="D460" s="50"/>
+      <c r="D460" s="49"/>
       <c r="E460" s="2"/>
       <c r="F460" s="2"/>
       <c r="G460" s="2"/>
@@ -15582,7 +15607,7 @@
       <c r="A461" s="2"/>
       <c r="B461" s="2"/>
       <c r="C461" s="2"/>
-      <c r="D461" s="50"/>
+      <c r="D461" s="49"/>
       <c r="E461" s="2"/>
       <c r="F461" s="2"/>
       <c r="G461" s="2"/>
@@ -15610,7 +15635,7 @@
       <c r="A462" s="2"/>
       <c r="B462" s="2"/>
       <c r="C462" s="2"/>
-      <c r="D462" s="50"/>
+      <c r="D462" s="49"/>
       <c r="E462" s="2"/>
       <c r="F462" s="2"/>
       <c r="G462" s="2"/>
@@ -15638,7 +15663,7 @@
       <c r="A463" s="2"/>
       <c r="B463" s="2"/>
       <c r="C463" s="2"/>
-      <c r="D463" s="50"/>
+      <c r="D463" s="49"/>
       <c r="E463" s="2"/>
       <c r="F463" s="2"/>
       <c r="G463" s="2"/>
@@ -15666,7 +15691,7 @@
       <c r="A464" s="2"/>
       <c r="B464" s="2"/>
       <c r="C464" s="2"/>
-      <c r="D464" s="50"/>
+      <c r="D464" s="49"/>
       <c r="E464" s="2"/>
       <c r="F464" s="2"/>
       <c r="G464" s="2"/>
@@ -15694,7 +15719,7 @@
       <c r="A465" s="2"/>
       <c r="B465" s="2"/>
       <c r="C465" s="2"/>
-      <c r="D465" s="50"/>
+      <c r="D465" s="49"/>
       <c r="E465" s="2"/>
       <c r="F465" s="2"/>
       <c r="G465" s="2"/>
@@ -15722,7 +15747,7 @@
       <c r="A466" s="2"/>
       <c r="B466" s="2"/>
       <c r="C466" s="2"/>
-      <c r="D466" s="50"/>
+      <c r="D466" s="49"/>
       <c r="E466" s="2"/>
       <c r="F466" s="2"/>
       <c r="G466" s="2"/>
@@ -15750,7 +15775,7 @@
       <c r="A467" s="2"/>
       <c r="B467" s="2"/>
       <c r="C467" s="2"/>
-      <c r="D467" s="50"/>
+      <c r="D467" s="49"/>
       <c r="E467" s="2"/>
       <c r="F467" s="2"/>
       <c r="G467" s="2"/>
@@ -15778,7 +15803,7 @@
       <c r="A468" s="2"/>
       <c r="B468" s="2"/>
       <c r="C468" s="2"/>
-      <c r="D468" s="50"/>
+      <c r="D468" s="49"/>
       <c r="E468" s="2"/>
       <c r="F468" s="2"/>
       <c r="G468" s="2"/>
@@ -15806,7 +15831,7 @@
       <c r="A469" s="2"/>
       <c r="B469" s="2"/>
       <c r="C469" s="2"/>
-      <c r="D469" s="50"/>
+      <c r="D469" s="49"/>
       <c r="E469" s="2"/>
       <c r="F469" s="2"/>
       <c r="G469" s="2"/>
@@ -15834,7 +15859,7 @@
       <c r="A470" s="2"/>
       <c r="B470" s="2"/>
       <c r="C470" s="2"/>
-      <c r="D470" s="50"/>
+      <c r="D470" s="49"/>
       <c r="E470" s="2"/>
       <c r="F470" s="2"/>
       <c r="G470" s="2"/>
@@ -15862,7 +15887,7 @@
       <c r="A471" s="2"/>
       <c r="B471" s="2"/>
       <c r="C471" s="2"/>
-      <c r="D471" s="50"/>
+      <c r="D471" s="49"/>
       <c r="E471" s="2"/>
       <c r="F471" s="2"/>
       <c r="G471" s="2"/>
@@ -15890,7 +15915,7 @@
       <c r="A472" s="2"/>
       <c r="B472" s="2"/>
       <c r="C472" s="2"/>
-      <c r="D472" s="50"/>
+      <c r="D472" s="49"/>
       <c r="E472" s="2"/>
       <c r="F472" s="2"/>
       <c r="G472" s="2"/>
@@ -15918,7 +15943,7 @@
       <c r="A473" s="2"/>
       <c r="B473" s="2"/>
       <c r="C473" s="2"/>
-      <c r="D473" s="50"/>
+      <c r="D473" s="49"/>
       <c r="E473" s="2"/>
       <c r="F473" s="2"/>
       <c r="G473" s="2"/>
@@ -15946,7 +15971,7 @@
       <c r="A474" s="2"/>
       <c r="B474" s="2"/>
       <c r="C474" s="2"/>
-      <c r="D474" s="50"/>
+      <c r="D474" s="49"/>
       <c r="E474" s="2"/>
       <c r="F474" s="2"/>
       <c r="G474" s="2"/>
@@ -15974,7 +15999,7 @@
       <c r="A475" s="2"/>
       <c r="B475" s="2"/>
       <c r="C475" s="2"/>
-      <c r="D475" s="50"/>
+      <c r="D475" s="49"/>
       <c r="E475" s="2"/>
       <c r="F475" s="2"/>
       <c r="G475" s="2"/>
@@ -16002,7 +16027,7 @@
       <c r="A476" s="2"/>
       <c r="B476" s="2"/>
       <c r="C476" s="2"/>
-      <c r="D476" s="50"/>
+      <c r="D476" s="49"/>
       <c r="E476" s="2"/>
       <c r="F476" s="2"/>
       <c r="G476" s="2"/>
@@ -16030,7 +16055,7 @@
       <c r="A477" s="2"/>
       <c r="B477" s="2"/>
       <c r="C477" s="2"/>
-      <c r="D477" s="50"/>
+      <c r="D477" s="49"/>
       <c r="E477" s="2"/>
       <c r="F477" s="2"/>
       <c r="G477" s="2"/>
@@ -16058,7 +16083,7 @@
       <c r="A478" s="2"/>
       <c r="B478" s="2"/>
       <c r="C478" s="2"/>
-      <c r="D478" s="50"/>
+      <c r="D478" s="49"/>
       <c r="E478" s="2"/>
       <c r="F478" s="2"/>
       <c r="G478" s="2"/>
@@ -16086,7 +16111,7 @@
       <c r="A479" s="2"/>
       <c r="B479" s="2"/>
       <c r="C479" s="2"/>
-      <c r="D479" s="50"/>
+      <c r="D479" s="49"/>
       <c r="E479" s="2"/>
       <c r="F479" s="2"/>
       <c r="G479" s="2"/>
@@ -16114,7 +16139,7 @@
       <c r="A480" s="2"/>
       <c r="B480" s="2"/>
       <c r="C480" s="2"/>
-      <c r="D480" s="50"/>
+      <c r="D480" s="49"/>
       <c r="E480" s="2"/>
       <c r="F480" s="2"/>
       <c r="G480" s="2"/>
@@ -16142,7 +16167,7 @@
       <c r="A481" s="2"/>
       <c r="B481" s="2"/>
       <c r="C481" s="2"/>
-      <c r="D481" s="50"/>
+      <c r="D481" s="49"/>
       <c r="E481" s="2"/>
       <c r="F481" s="2"/>
       <c r="G481" s="2"/>
@@ -16170,7 +16195,7 @@
       <c r="A482" s="2"/>
       <c r="B482" s="2"/>
       <c r="C482" s="2"/>
-      <c r="D482" s="50"/>
+      <c r="D482" s="49"/>
       <c r="E482" s="2"/>
       <c r="F482" s="2"/>
       <c r="G482" s="2"/>
@@ -16198,7 +16223,7 @@
       <c r="A483" s="2"/>
       <c r="B483" s="2"/>
       <c r="C483" s="2"/>
-      <c r="D483" s="50"/>
+      <c r="D483" s="49"/>
       <c r="E483" s="2"/>
       <c r="F483" s="2"/>
       <c r="G483" s="2"/>
@@ -16226,7 +16251,7 @@
       <c r="A484" s="2"/>
       <c r="B484" s="2"/>
       <c r="C484" s="2"/>
-      <c r="D484" s="50"/>
+      <c r="D484" s="49"/>
       <c r="E484" s="2"/>
       <c r="F484" s="2"/>
       <c r="G484" s="2"/>
@@ -16254,7 +16279,7 @@
       <c r="A485" s="2"/>
       <c r="B485" s="2"/>
       <c r="C485" s="2"/>
-      <c r="D485" s="50"/>
+      <c r="D485" s="49"/>
       <c r="E485" s="2"/>
       <c r="F485" s="2"/>
       <c r="G485" s="2"/>
@@ -16282,7 +16307,7 @@
       <c r="A486" s="2"/>
       <c r="B486" s="2"/>
       <c r="C486" s="2"/>
-      <c r="D486" s="50"/>
+      <c r="D486" s="49"/>
       <c r="E486" s="2"/>
       <c r="F486" s="2"/>
       <c r="G486" s="2"/>
@@ -16310,7 +16335,7 @@
       <c r="A487" s="2"/>
       <c r="B487" s="2"/>
       <c r="C487" s="2"/>
-      <c r="D487" s="50"/>
+      <c r="D487" s="49"/>
       <c r="E487" s="2"/>
       <c r="F487" s="2"/>
       <c r="G487" s="2"/>
@@ -16338,7 +16363,7 @@
       <c r="A488" s="2"/>
       <c r="B488" s="2"/>
       <c r="C488" s="2"/>
-      <c r="D488" s="50"/>
+      <c r="D488" s="49"/>
       <c r="E488" s="2"/>
       <c r="F488" s="2"/>
       <c r="G488" s="2"/>
@@ -16366,7 +16391,7 @@
       <c r="A489" s="2"/>
       <c r="B489" s="2"/>
       <c r="C489" s="2"/>
-      <c r="D489" s="50"/>
+      <c r="D489" s="49"/>
       <c r="E489" s="2"/>
       <c r="F489" s="2"/>
       <c r="G489" s="2"/>
@@ -16394,7 +16419,7 @@
       <c r="A490" s="2"/>
       <c r="B490" s="2"/>
       <c r="C490" s="2"/>
-      <c r="D490" s="50"/>
+      <c r="D490" s="49"/>
       <c r="E490" s="2"/>
       <c r="F490" s="2"/>
       <c r="G490" s="2"/>
@@ -16422,7 +16447,7 @@
       <c r="A491" s="2"/>
       <c r="B491" s="2"/>
       <c r="C491" s="2"/>
-      <c r="D491" s="50"/>
+      <c r="D491" s="49"/>
       <c r="E491" s="2"/>
       <c r="F491" s="2"/>
       <c r="G491" s="2"/>
@@ -16450,7 +16475,7 @@
       <c r="A492" s="2"/>
       <c r="B492" s="2"/>
       <c r="C492" s="2"/>
-      <c r="D492" s="50"/>
+      <c r="D492" s="49"/>
       <c r="E492" s="2"/>
       <c r="F492" s="2"/>
       <c r="G492" s="2"/>
@@ -16478,7 +16503,7 @@
       <c r="A493" s="2"/>
       <c r="B493" s="2"/>
       <c r="C493" s="2"/>
-      <c r="D493" s="50"/>
+      <c r="D493" s="49"/>
       <c r="E493" s="2"/>
       <c r="F493" s="2"/>
       <c r="G493" s="2"/>
@@ -16506,7 +16531,7 @@
       <c r="A494" s="2"/>
       <c r="B494" s="2"/>
       <c r="C494" s="2"/>
-      <c r="D494" s="50"/>
+      <c r="D494" s="49"/>
       <c r="E494" s="2"/>
       <c r="F494" s="2"/>
       <c r="G494" s="2"/>
@@ -16534,7 +16559,7 @@
       <c r="A495" s="2"/>
       <c r="B495" s="2"/>
       <c r="C495" s="2"/>
-      <c r="D495" s="50"/>
+      <c r="D495" s="49"/>
       <c r="E495" s="2"/>
       <c r="F495" s="2"/>
       <c r="G495" s="2"/>
@@ -16562,7 +16587,7 @@
       <c r="A496" s="2"/>
       <c r="B496" s="2"/>
       <c r="C496" s="2"/>
-      <c r="D496" s="50"/>
+      <c r="D496" s="49"/>
       <c r="E496" s="2"/>
       <c r="F496" s="2"/>
       <c r="G496" s="2"/>
@@ -16590,7 +16615,7 @@
       <c r="A497" s="2"/>
       <c r="B497" s="2"/>
       <c r="C497" s="2"/>
-      <c r="D497" s="50"/>
+      <c r="D497" s="49"/>
       <c r="E497" s="2"/>
       <c r="F497" s="2"/>
       <c r="G497" s="2"/>
@@ -16618,7 +16643,7 @@
       <c r="A498" s="2"/>
       <c r="B498" s="2"/>
       <c r="C498" s="2"/>
-      <c r="D498" s="50"/>
+      <c r="D498" s="49"/>
       <c r="E498" s="2"/>
       <c r="F498" s="2"/>
       <c r="G498" s="2"/>
@@ -16646,7 +16671,7 @@
       <c r="A499" s="2"/>
       <c r="B499" s="2"/>
       <c r="C499" s="2"/>
-      <c r="D499" s="50"/>
+      <c r="D499" s="49"/>
       <c r="E499" s="2"/>
       <c r="F499" s="2"/>
       <c r="G499" s="2"/>
@@ -16674,7 +16699,7 @@
       <c r="A500" s="2"/>
       <c r="B500" s="2"/>
       <c r="C500" s="2"/>
-      <c r="D500" s="50"/>
+      <c r="D500" s="49"/>
       <c r="E500" s="2"/>
       <c r="F500" s="2"/>
       <c r="G500" s="2"/>
@@ -16702,7 +16727,7 @@
       <c r="A501" s="2"/>
       <c r="B501" s="2"/>
       <c r="C501" s="2"/>
-      <c r="D501" s="50"/>
+      <c r="D501" s="49"/>
       <c r="E501" s="2"/>
       <c r="F501" s="2"/>
       <c r="G501" s="2"/>
@@ -16730,7 +16755,7 @@
       <c r="A502" s="2"/>
       <c r="B502" s="2"/>
       <c r="C502" s="2"/>
-      <c r="D502" s="50"/>
+      <c r="D502" s="49"/>
       <c r="E502" s="2"/>
       <c r="F502" s="2"/>
       <c r="G502" s="2"/>
@@ -16758,7 +16783,7 @@
       <c r="A503" s="2"/>
       <c r="B503" s="2"/>
       <c r="C503" s="2"/>
-      <c r="D503" s="50"/>
+      <c r="D503" s="49"/>
       <c r="E503" s="2"/>
       <c r="F503" s="2"/>
       <c r="G503" s="2"/>
@@ -16786,7 +16811,7 @@
       <c r="A504" s="2"/>
       <c r="B504" s="2"/>
       <c r="C504" s="2"/>
-      <c r="D504" s="50"/>
+      <c r="D504" s="49"/>
       <c r="E504" s="2"/>
       <c r="F504" s="2"/>
       <c r="G504" s="2"/>
@@ -16814,7 +16839,7 @@
       <c r="A505" s="2"/>
       <c r="B505" s="2"/>
       <c r="C505" s="2"/>
-      <c r="D505" s="50"/>
+      <c r="D505" s="49"/>
       <c r="E505" s="2"/>
       <c r="F505" s="2"/>
       <c r="G505" s="2"/>
@@ -16842,7 +16867,7 @@
       <c r="A506" s="2"/>
       <c r="B506" s="2"/>
       <c r="C506" s="2"/>
-      <c r="D506" s="50"/>
+      <c r="D506" s="49"/>
       <c r="E506" s="2"/>
       <c r="F506" s="2"/>
       <c r="G506" s="2"/>
@@ -16870,7 +16895,7 @@
       <c r="A507" s="2"/>
       <c r="B507" s="2"/>
       <c r="C507" s="2"/>
-      <c r="D507" s="50"/>
+      <c r="D507" s="49"/>
       <c r="E507" s="2"/>
       <c r="F507" s="2"/>
       <c r="G507" s="2"/>
@@ -16898,7 +16923,7 @@
       <c r="A508" s="2"/>
       <c r="B508" s="2"/>
       <c r="C508" s="2"/>
-      <c r="D508" s="50"/>
+      <c r="D508" s="49"/>
       <c r="E508" s="2"/>
       <c r="F508" s="2"/>
       <c r="G508" s="2"/>
@@ -16926,7 +16951,7 @@
       <c r="A509" s="2"/>
       <c r="B509" s="2"/>
       <c r="C509" s="2"/>
-      <c r="D509" s="50"/>
+      <c r="D509" s="49"/>
       <c r="E509" s="2"/>
       <c r="F509" s="2"/>
       <c r="G509" s="2"/>
@@ -16954,7 +16979,7 @@
       <c r="A510" s="2"/>
       <c r="B510" s="2"/>
       <c r="C510" s="2"/>
-      <c r="D510" s="50"/>
+      <c r="D510" s="49"/>
       <c r="E510" s="2"/>
       <c r="F510" s="2"/>
       <c r="G510" s="2"/>
@@ -16982,7 +17007,7 @@
       <c r="A511" s="2"/>
       <c r="B511" s="2"/>
       <c r="C511" s="2"/>
-      <c r="D511" s="50"/>
+      <c r="D511" s="49"/>
       <c r="E511" s="2"/>
       <c r="F511" s="2"/>
       <c r="G511" s="2"/>
@@ -17010,7 +17035,7 @@
       <c r="A512" s="2"/>
       <c r="B512" s="2"/>
       <c r="C512" s="2"/>
-      <c r="D512" s="50"/>
+      <c r="D512" s="49"/>
       <c r="E512" s="2"/>
       <c r="F512" s="2"/>
       <c r="G512" s="2"/>
@@ -17038,7 +17063,7 @@
       <c r="A513" s="2"/>
       <c r="B513" s="2"/>
       <c r="C513" s="2"/>
-      <c r="D513" s="50"/>
+      <c r="D513" s="49"/>
       <c r="E513" s="2"/>
       <c r="F513" s="2"/>
       <c r="G513" s="2"/>
@@ -17066,7 +17091,7 @@
       <c r="A514" s="2"/>
       <c r="B514" s="2"/>
       <c r="C514" s="2"/>
-      <c r="D514" s="50"/>
+      <c r="D514" s="49"/>
       <c r="E514" s="2"/>
       <c r="F514" s="2"/>
       <c r="G514" s="2"/>
@@ -17094,7 +17119,7 @@
       <c r="A515" s="2"/>
       <c r="B515" s="2"/>
       <c r="C515" s="2"/>
-      <c r="D515" s="50"/>
+      <c r="D515" s="49"/>
       <c r="E515" s="2"/>
       <c r="F515" s="2"/>
       <c r="G515" s="2"/>
@@ -17122,7 +17147,7 @@
       <c r="A516" s="2"/>
       <c r="B516" s="2"/>
       <c r="C516" s="2"/>
-      <c r="D516" s="50"/>
+      <c r="D516" s="49"/>
       <c r="E516" s="2"/>
       <c r="F516" s="2"/>
       <c r="G516" s="2"/>
@@ -17150,7 +17175,7 @@
       <c r="A517" s="2"/>
       <c r="B517" s="2"/>
       <c r="C517" s="2"/>
-      <c r="D517" s="50"/>
+      <c r="D517" s="49"/>
       <c r="E517" s="2"/>
       <c r="F517" s="2"/>
       <c r="G517" s="2"/>
@@ -17178,7 +17203,7 @@
       <c r="A518" s="2"/>
       <c r="B518" s="2"/>
       <c r="C518" s="2"/>
-      <c r="D518" s="50"/>
+      <c r="D518" s="49"/>
       <c r="E518" s="2"/>
       <c r="F518" s="2"/>
       <c r="G518" s="2"/>
@@ -17206,7 +17231,7 @@
       <c r="A519" s="2"/>
       <c r="B519" s="2"/>
       <c r="C519" s="2"/>
-      <c r="D519" s="50"/>
+      <c r="D519" s="49"/>
       <c r="E519" s="2"/>
       <c r="F519" s="2"/>
       <c r="G519" s="2"/>
@@ -17234,7 +17259,7 @@
       <c r="A520" s="2"/>
       <c r="B520" s="2"/>
       <c r="C520" s="2"/>
-      <c r="D520" s="50"/>
+      <c r="D520" s="49"/>
       <c r="E520" s="2"/>
       <c r="F520" s="2"/>
       <c r="G520" s="2"/>
@@ -17262,7 +17287,7 @@
       <c r="A521" s="2"/>
       <c r="B521" s="2"/>
       <c r="C521" s="2"/>
-      <c r="D521" s="50"/>
+      <c r="D521" s="49"/>
       <c r="E521" s="2"/>
       <c r="F521" s="2"/>
       <c r="G521" s="2"/>
@@ -17290,7 +17315,7 @@
       <c r="A522" s="2"/>
       <c r="B522" s="2"/>
       <c r="C522" s="2"/>
-      <c r="D522" s="50"/>
+      <c r="D522" s="49"/>
       <c r="E522" s="2"/>
       <c r="F522" s="2"/>
       <c r="G522" s="2"/>
@@ -17318,7 +17343,7 @@
       <c r="A523" s="2"/>
       <c r="B523" s="2"/>
       <c r="C523" s="2"/>
-      <c r="D523" s="50"/>
+      <c r="D523" s="49"/>
       <c r="E523" s="2"/>
       <c r="F523" s="2"/>
       <c r="G523" s="2"/>
@@ -17346,7 +17371,7 @@
       <c r="A524" s="2"/>
       <c r="B524" s="2"/>
       <c r="C524" s="2"/>
-      <c r="D524" s="50"/>
+      <c r="D524" s="49"/>
       <c r="E524" s="2"/>
       <c r="F524" s="2"/>
       <c r="G524" s="2"/>
@@ -17374,7 +17399,7 @@
       <c r="A525" s="2"/>
       <c r="B525" s="2"/>
       <c r="C525" s="2"/>
-      <c r="D525" s="50"/>
+      <c r="D525" s="49"/>
       <c r="E525" s="2"/>
       <c r="F525" s="2"/>
       <c r="G525" s="2"/>
@@ -17402,7 +17427,7 @@
       <c r="A526" s="2"/>
       <c r="B526" s="2"/>
       <c r="C526" s="2"/>
-      <c r="D526" s="50"/>
+      <c r="D526" s="49"/>
       <c r="E526" s="2"/>
       <c r="F526" s="2"/>
       <c r="G526" s="2"/>
@@ -17430,7 +17455,7 @@
       <c r="A527" s="2"/>
       <c r="B527" s="2"/>
       <c r="C527" s="2"/>
-      <c r="D527" s="50"/>
+      <c r="D527" s="49"/>
       <c r="E527" s="2"/>
       <c r="F527" s="2"/>
       <c r="G527" s="2"/>
@@ -17458,7 +17483,7 @@
       <c r="A528" s="2"/>
       <c r="B528" s="2"/>
       <c r="C528" s="2"/>
-      <c r="D528" s="50"/>
+      <c r="D528" s="49"/>
       <c r="E528" s="2"/>
       <c r="F528" s="2"/>
       <c r="G528" s="2"/>
@@ -17486,7 +17511,7 @@
       <c r="A529" s="2"/>
       <c r="B529" s="2"/>
       <c r="C529" s="2"/>
-      <c r="D529" s="50"/>
+      <c r="D529" s="49"/>
       <c r="E529" s="2"/>
       <c r="F529" s="2"/>
       <c r="G529" s="2"/>
@@ -17514,7 +17539,7 @@
       <c r="A530" s="2"/>
       <c r="B530" s="2"/>
       <c r="C530" s="2"/>
-      <c r="D530" s="50"/>
+      <c r="D530" s="49"/>
       <c r="E530" s="2"/>
       <c r="F530" s="2"/>
       <c r="G530" s="2"/>
@@ -17542,7 +17567,7 @@
       <c r="A531" s="2"/>
       <c r="B531" s="2"/>
       <c r="C531" s="2"/>
-      <c r="D531" s="50"/>
+      <c r="D531" s="49"/>
       <c r="E531" s="2"/>
       <c r="F531" s="2"/>
       <c r="G531" s="2"/>
@@ -17570,7 +17595,7 @@
       <c r="A532" s="2"/>
       <c r="B532" s="2"/>
       <c r="C532" s="2"/>
-      <c r="D532" s="50"/>
+      <c r="D532" s="49"/>
       <c r="E532" s="2"/>
       <c r="F532" s="2"/>
       <c r="G532" s="2"/>
@@ -17598,7 +17623,7 @@
       <c r="A533" s="2"/>
       <c r="B533" s="2"/>
       <c r="C533" s="2"/>
-      <c r="D533" s="50"/>
+      <c r="D533" s="49"/>
       <c r="E533" s="2"/>
       <c r="F533" s="2"/>
       <c r="G533" s="2"/>
@@ -17626,7 +17651,7 @@
       <c r="A534" s="2"/>
       <c r="B534" s="2"/>
       <c r="C534" s="2"/>
-      <c r="D534" s="50"/>
+      <c r="D534" s="49"/>
       <c r="E534" s="2"/>
       <c r="F534" s="2"/>
       <c r="G534" s="2"/>
@@ -17654,7 +17679,7 @@
       <c r="A535" s="2"/>
       <c r="B535" s="2"/>
       <c r="C535" s="2"/>
-      <c r="D535" s="50"/>
+      <c r="D535" s="49"/>
       <c r="E535" s="2"/>
       <c r="F535" s="2"/>
       <c r="G535" s="2"/>
@@ -17682,7 +17707,7 @@
       <c r="A536" s="2"/>
       <c r="B536" s="2"/>
       <c r="C536" s="2"/>
-      <c r="D536" s="50"/>
+      <c r="D536" s="49"/>
       <c r="E536" s="2"/>
       <c r="F536" s="2"/>
       <c r="G536" s="2"/>
@@ -17710,7 +17735,7 @@
       <c r="A537" s="2"/>
       <c r="B537" s="2"/>
       <c r="C537" s="2"/>
-      <c r="D537" s="50"/>
+      <c r="D537" s="49"/>
       <c r="E537" s="2"/>
       <c r="F537" s="2"/>
       <c r="G537" s="2"/>
@@ -17738,7 +17763,7 @@
       <c r="A538" s="2"/>
       <c r="B538" s="2"/>
       <c r="C538" s="2"/>
-      <c r="D538" s="50"/>
+      <c r="D538" s="49"/>
       <c r="E538" s="2"/>
       <c r="F538" s="2"/>
       <c r="G538" s="2"/>
@@ -17766,7 +17791,7 @@
       <c r="A539" s="2"/>
       <c r="B539" s="2"/>
       <c r="C539" s="2"/>
-      <c r="D539" s="50"/>
+      <c r="D539" s="49"/>
       <c r="E539" s="2"/>
       <c r="F539" s="2"/>
       <c r="G539" s="2"/>
@@ -17794,7 +17819,7 @@
       <c r="A540" s="2"/>
       <c r="B540" s="2"/>
       <c r="C540" s="2"/>
-      <c r="D540" s="50"/>
+      <c r="D540" s="49"/>
       <c r="E540" s="2"/>
       <c r="F540" s="2"/>
       <c r="G540" s="2"/>
@@ -17822,7 +17847,7 @@
       <c r="A541" s="2"/>
       <c r="B541" s="2"/>
       <c r="C541" s="2"/>
-      <c r="D541" s="50"/>
+      <c r="D541" s="49"/>
       <c r="E541" s="2"/>
       <c r="F541" s="2"/>
       <c r="G541" s="2"/>
@@ -17850,7 +17875,7 @@
       <c r="A542" s="2"/>
       <c r="B542" s="2"/>
       <c r="C542" s="2"/>
-      <c r="D542" s="50"/>
+      <c r="D542" s="49"/>
       <c r="E542" s="2"/>
       <c r="F542" s="2"/>
       <c r="G542" s="2"/>
@@ -17878,7 +17903,7 @@
       <c r="A543" s="2"/>
       <c r="B543" s="2"/>
       <c r="C543" s="2"/>
-      <c r="D543" s="50"/>
+      <c r="D543" s="49"/>
       <c r="E543" s="2"/>
       <c r="F543" s="2"/>
       <c r="G543" s="2"/>
@@ -17906,7 +17931,7 @@
       <c r="A544" s="2"/>
       <c r="B544" s="2"/>
       <c r="C544" s="2"/>
-      <c r="D544" s="50"/>
+      <c r="D544" s="49"/>
       <c r="E544" s="2"/>
       <c r="F544" s="2"/>
       <c r="G544" s="2"/>
@@ -17934,7 +17959,7 @@
       <c r="A545" s="2"/>
       <c r="B545" s="2"/>
       <c r="C545" s="2"/>
-      <c r="D545" s="50"/>
+      <c r="D545" s="49"/>
       <c r="E545" s="2"/>
       <c r="F545" s="2"/>
       <c r="G545" s="2"/>
@@ -17962,7 +17987,7 @@
       <c r="A546" s="2"/>
       <c r="B546" s="2"/>
       <c r="C546" s="2"/>
-      <c r="D546" s="50"/>
+      <c r="D546" s="49"/>
       <c r="E546" s="2"/>
       <c r="F546" s="2"/>
       <c r="G546" s="2"/>
@@ -17990,7 +18015,7 @@
       <c r="A547" s="2"/>
       <c r="B547" s="2"/>
       <c r="C547" s="2"/>
-      <c r="D547" s="50"/>
+      <c r="D547" s="49"/>
       <c r="E547" s="2"/>
       <c r="F547" s="2"/>
       <c r="G547" s="2"/>
@@ -18018,7 +18043,7 @@
       <c r="A548" s="2"/>
       <c r="B548" s="2"/>
       <c r="C548" s="2"/>
-      <c r="D548" s="50"/>
+      <c r="D548" s="49"/>
       <c r="E548" s="2"/>
       <c r="F548" s="2"/>
       <c r="G548" s="2"/>
@@ -18046,7 +18071,7 @@
       <c r="A549" s="2"/>
       <c r="B549" s="2"/>
       <c r="C549" s="2"/>
-      <c r="D549" s="50"/>
+      <c r="D549" s="49"/>
       <c r="E549" s="2"/>
       <c r="F549" s="2"/>
       <c r="G549" s="2"/>
@@ -18074,7 +18099,7 @@
       <c r="A550" s="2"/>
       <c r="B550" s="2"/>
       <c r="C550" s="2"/>
-      <c r="D550" s="50"/>
+      <c r="D550" s="49"/>
       <c r="E550" s="2"/>
       <c r="F550" s="2"/>
       <c r="G550" s="2"/>
@@ -18102,7 +18127,7 @@
       <c r="A551" s="2"/>
       <c r="B551" s="2"/>
       <c r="C551" s="2"/>
-      <c r="D551" s="50"/>
+      <c r="D551" s="49"/>
       <c r="E551" s="2"/>
       <c r="F551" s="2"/>
       <c r="G551" s="2"/>
@@ -18130,7 +18155,7 @@
       <c r="A552" s="2"/>
       <c r="B552" s="2"/>
       <c r="C552" s="2"/>
-      <c r="D552" s="50"/>
+      <c r="D552" s="49"/>
       <c r="E552" s="2"/>
       <c r="F552" s="2"/>
       <c r="G552" s="2"/>
@@ -18158,7 +18183,7 @@
       <c r="A553" s="2"/>
       <c r="B553" s="2"/>
       <c r="C553" s="2"/>
-      <c r="D553" s="50"/>
+      <c r="D553" s="49"/>
       <c r="E553" s="2"/>
       <c r="F553" s="2"/>
       <c r="G553" s="2"/>
@@ -18186,7 +18211,7 @@
       <c r="A554" s="2"/>
       <c r="B554" s="2"/>
       <c r="C554" s="2"/>
-      <c r="D554" s="50"/>
+      <c r="D554" s="49"/>
       <c r="E554" s="2"/>
       <c r="F554" s="2"/>
       <c r="G554" s="2"/>
@@ -18214,7 +18239,7 @@
       <c r="A555" s="2"/>
       <c r="B555" s="2"/>
       <c r="C555" s="2"/>
-      <c r="D555" s="50"/>
+      <c r="D555" s="49"/>
       <c r="E555" s="2"/>
       <c r="F555" s="2"/>
       <c r="G555" s="2"/>
@@ -18242,7 +18267,7 @@
       <c r="A556" s="2"/>
       <c r="B556" s="2"/>
       <c r="C556" s="2"/>
-      <c r="D556" s="50"/>
+      <c r="D556" s="49"/>
       <c r="E556" s="2"/>
       <c r="F556" s="2"/>
       <c r="G556" s="2"/>
@@ -18270,7 +18295,7 @@
       <c r="A557" s="2"/>
       <c r="B557" s="2"/>
       <c r="C557" s="2"/>
-      <c r="D557" s="50"/>
+      <c r="D557" s="49"/>
       <c r="E557" s="2"/>
       <c r="F557" s="2"/>
       <c r="G557" s="2"/>
@@ -18298,7 +18323,7 @@
       <c r="A558" s="2"/>
       <c r="B558" s="2"/>
       <c r="C558" s="2"/>
-      <c r="D558" s="50"/>
+      <c r="D558" s="49"/>
       <c r="E558" s="2"/>
       <c r="F558" s="2"/>
       <c r="G558" s="2"/>
@@ -18326,7 +18351,7 @@
       <c r="A559" s="2"/>
       <c r="B559" s="2"/>
       <c r="C559" s="2"/>
-      <c r="D559" s="50"/>
+      <c r="D559" s="49"/>
       <c r="E559" s="2"/>
       <c r="F559" s="2"/>
       <c r="G559" s="2"/>
@@ -18354,7 +18379,7 @@
       <c r="A560" s="2"/>
       <c r="B560" s="2"/>
       <c r="C560" s="2"/>
-      <c r="D560" s="50"/>
+      <c r="D560" s="49"/>
       <c r="E560" s="2"/>
       <c r="F560" s="2"/>
       <c r="G560" s="2"/>
@@ -18382,7 +18407,7 @@
       <c r="A561" s="2"/>
       <c r="B561" s="2"/>
       <c r="C561" s="2"/>
-      <c r="D561" s="50"/>
+      <c r="D561" s="49"/>
       <c r="E561" s="2"/>
       <c r="F561" s="2"/>
       <c r="G561" s="2"/>
@@ -18410,7 +18435,7 @@
       <c r="A562" s="2"/>
       <c r="B562" s="2"/>
       <c r="C562" s="2"/>
-      <c r="D562" s="50"/>
+      <c r="D562" s="49"/>
       <c r="E562" s="2"/>
       <c r="F562" s="2"/>
       <c r="G562" s="2"/>
@@ -18438,7 +18463,7 @@
       <c r="A563" s="2"/>
       <c r="B563" s="2"/>
       <c r="C563" s="2"/>
-      <c r="D563" s="50"/>
+      <c r="D563" s="49"/>
       <c r="E563" s="2"/>
       <c r="F563" s="2"/>
       <c r="G563" s="2"/>
@@ -18466,7 +18491,7 @@
       <c r="A564" s="2"/>
       <c r="B564" s="2"/>
       <c r="C564" s="2"/>
-      <c r="D564" s="50"/>
+      <c r="D564" s="49"/>
       <c r="E564" s="2"/>
       <c r="F564" s="2"/>
       <c r="G564" s="2"/>
@@ -18494,7 +18519,7 @@
       <c r="A565" s="2"/>
       <c r="B565" s="2"/>
       <c r="C565" s="2"/>
-      <c r="D565" s="50"/>
+      <c r="D565" s="49"/>
       <c r="E565" s="2"/>
       <c r="F565" s="2"/>
       <c r="G565" s="2"/>
@@ -18522,7 +18547,7 @@
       <c r="A566" s="2"/>
       <c r="B566" s="2"/>
       <c r="C566" s="2"/>
-      <c r="D566" s="50"/>
+      <c r="D566" s="49"/>
       <c r="E566" s="2"/>
       <c r="F566" s="2"/>
       <c r="G566" s="2"/>
@@ -18550,7 +18575,7 @@
       <c r="A567" s="2"/>
       <c r="B567" s="2"/>
       <c r="C567" s="2"/>
-      <c r="D567" s="50"/>
+      <c r="D567" s="49"/>
       <c r="E567" s="2"/>
       <c r="F567" s="2"/>
       <c r="G567" s="2"/>
@@ -18578,7 +18603,7 @@
       <c r="A568" s="2"/>
       <c r="B568" s="2"/>
       <c r="C568" s="2"/>
-      <c r="D568" s="50"/>
+      <c r="D568" s="49"/>
       <c r="E568" s="2"/>
       <c r="F568" s="2"/>
       <c r="G568" s="2"/>
@@ -18606,7 +18631,7 @@
       <c r="A569" s="2"/>
       <c r="B569" s="2"/>
       <c r="C569" s="2"/>
-      <c r="D569" s="50"/>
+      <c r="D569" s="49"/>
       <c r="E569" s="2"/>
       <c r="F569" s="2"/>
       <c r="G569" s="2"/>
@@ -18634,7 +18659,7 @@
       <c r="A570" s="2"/>
       <c r="B570" s="2"/>
       <c r="C570" s="2"/>
-      <c r="D570" s="50"/>
+      <c r="D570" s="49"/>
       <c r="E570" s="2"/>
       <c r="F570" s="2"/>
       <c r="G570" s="2"/>
@@ -18662,7 +18687,7 @@
       <c r="A571" s="2"/>
       <c r="B571" s="2"/>
       <c r="C571" s="2"/>
-      <c r="D571" s="50"/>
+      <c r="D571" s="49"/>
       <c r="E571" s="2"/>
       <c r="F571" s="2"/>
       <c r="G571" s="2"/>
@@ -18690,7 +18715,7 @@
       <c r="A572" s="2"/>
       <c r="B572" s="2"/>
       <c r="C572" s="2"/>
-      <c r="D572" s="50"/>
+      <c r="D572" s="49"/>
       <c r="E572" s="2"/>
       <c r="F572" s="2"/>
       <c r="G572" s="2"/>
@@ -18718,7 +18743,7 @@
       <c r="A573" s="2"/>
       <c r="B573" s="2"/>
       <c r="C573" s="2"/>
-      <c r="D573" s="50"/>
+      <c r="D573" s="49"/>
       <c r="E573" s="2"/>
       <c r="F573" s="2"/>
       <c r="G573" s="2"/>
@@ -18746,7 +18771,7 @@
       <c r="A574" s="2"/>
       <c r="B574" s="2"/>
       <c r="C574" s="2"/>
-      <c r="D574" s="50"/>
+      <c r="D574" s="49"/>
       <c r="E574" s="2"/>
       <c r="F574" s="2"/>
       <c r="G574" s="2"/>
@@ -18774,7 +18799,7 @@
       <c r="A575" s="2"/>
       <c r="B575" s="2"/>
       <c r="C575" s="2"/>
-      <c r="D575" s="50"/>
+      <c r="D575" s="49"/>
       <c r="E575" s="2"/>
       <c r="F575" s="2"/>
       <c r="G575" s="2"/>
@@ -18802,7 +18827,7 @@
       <c r="A576" s="2"/>
       <c r="B576" s="2"/>
       <c r="C576" s="2"/>
-      <c r="D576" s="50"/>
+      <c r="D576" s="49"/>
       <c r="E576" s="2"/>
       <c r="F576" s="2"/>
       <c r="G576" s="2"/>
@@ -18830,7 +18855,7 @@
       <c r="A577" s="2"/>
       <c r="B577" s="2"/>
       <c r="C577" s="2"/>
-      <c r="D577" s="50"/>
+      <c r="D577" s="49"/>
       <c r="E577" s="2"/>
       <c r="F577" s="2"/>
       <c r="G577" s="2"/>
@@ -18858,7 +18883,7 @@
       <c r="A578" s="2"/>
       <c r="B578" s="2"/>
       <c r="C578" s="2"/>
-      <c r="D578" s="50"/>
+      <c r="D578" s="49"/>
       <c r="E578" s="2"/>
       <c r="F578" s="2"/>
       <c r="G578" s="2"/>
@@ -18886,7 +18911,7 @@
       <c r="A579" s="2"/>
       <c r="B579" s="2"/>
       <c r="C579" s="2"/>
-      <c r="D579" s="50"/>
+      <c r="D579" s="49"/>
       <c r="E579" s="2"/>
       <c r="F579" s="2"/>
       <c r="G579" s="2"/>
@@ -18914,7 +18939,7 @@
       <c r="A580" s="2"/>
       <c r="B580" s="2"/>
       <c r="C580" s="2"/>
-      <c r="D580" s="50"/>
+      <c r="D580" s="49"/>
       <c r="E580" s="2"/>
       <c r="F580" s="2"/>
       <c r="G580" s="2"/>
@@ -18942,7 +18967,7 @@
       <c r="A581" s="2"/>
       <c r="B581" s="2"/>
       <c r="C581" s="2"/>
-      <c r="D581" s="50"/>
+      <c r="D581" s="49"/>
       <c r="E581" s="2"/>
       <c r="F581" s="2"/>
       <c r="G581" s="2"/>
@@ -18970,7 +18995,7 @@
       <c r="A582" s="2"/>
       <c r="B582" s="2"/>
       <c r="C582" s="2"/>
-      <c r="D582" s="50"/>
+      <c r="D582" s="49"/>
       <c r="E582" s="2"/>
       <c r="F582" s="2"/>
       <c r="G582" s="2"/>
@@ -18998,7 +19023,7 @@
       <c r="A583" s="2"/>
       <c r="B583" s="2"/>
       <c r="C583" s="2"/>
-      <c r="D583" s="50"/>
+      <c r="D583" s="49"/>
       <c r="E583" s="2"/>
       <c r="F583" s="2"/>
       <c r="G583" s="2"/>
@@ -19026,7 +19051,7 @@
       <c r="A584" s="2"/>
       <c r="B584" s="2"/>
       <c r="C584" s="2"/>
-      <c r="D584" s="50"/>
+      <c r="D584" s="49"/>
       <c r="E584" s="2"/>
       <c r="F584" s="2"/>
       <c r="G584" s="2"/>
@@ -19054,7 +19079,7 @@
       <c r="A585" s="2"/>
       <c r="B585" s="2"/>
       <c r="C585" s="2"/>
-      <c r="D585" s="50"/>
+      <c r="D585" s="49"/>
       <c r="E585" s="2"/>
       <c r="F585" s="2"/>
       <c r="G585" s="2"/>
@@ -19082,7 +19107,7 @@
       <c r="A586" s="2"/>
       <c r="B586" s="2"/>
       <c r="C586" s="2"/>
-      <c r="D586" s="50"/>
+      <c r="D586" s="49"/>
       <c r="E586" s="2"/>
       <c r="F586" s="2"/>
       <c r="G586" s="2"/>
@@ -19110,7 +19135,7 @@
       <c r="A587" s="2"/>
       <c r="B587" s="2"/>
       <c r="C587" s="2"/>
-      <c r="D587" s="50"/>
+      <c r="D587" s="49"/>
       <c r="E587" s="2"/>
       <c r="F587" s="2"/>
       <c r="G587" s="2"/>
@@ -19138,7 +19163,7 @@
       <c r="A588" s="2"/>
       <c r="B588" s="2"/>
       <c r="C588" s="2"/>
-      <c r="D588" s="50"/>
+      <c r="D588" s="49"/>
       <c r="E588" s="2"/>
       <c r="F588" s="2"/>
       <c r="G588" s="2"/>
@@ -19166,7 +19191,7 @@
       <c r="A589" s="2"/>
       <c r="B589" s="2"/>
       <c r="C589" s="2"/>
-      <c r="D589" s="50"/>
+      <c r="D589" s="49"/>
       <c r="E589" s="2"/>
       <c r="F589" s="2"/>
       <c r="G589" s="2"/>
@@ -19194,7 +19219,7 @@
       <c r="A590" s="2"/>
       <c r="B590" s="2"/>
       <c r="C590" s="2"/>
-      <c r="D590" s="50"/>
+      <c r="D590" s="49"/>
       <c r="E590" s="2"/>
       <c r="F590" s="2"/>
       <c r="G590" s="2"/>
@@ -19222,7 +19247,7 @@
       <c r="A591" s="2"/>
       <c r="B591" s="2"/>
       <c r="C591" s="2"/>
-      <c r="D591" s="50"/>
+      <c r="D591" s="49"/>
       <c r="E591" s="2"/>
       <c r="F591" s="2"/>
       <c r="G591" s="2"/>
@@ -19250,7 +19275,7 @@
       <c r="A592" s="2"/>
       <c r="B592" s="2"/>
       <c r="C592" s="2"/>
-      <c r="D592" s="50"/>
+      <c r="D592" s="49"/>
       <c r="E592" s="2"/>
       <c r="F592" s="2"/>
       <c r="G592" s="2"/>
@@ -19278,7 +19303,7 @@
       <c r="A593" s="2"/>
       <c r="B593" s="2"/>
       <c r="C593" s="2"/>
-      <c r="D593" s="50"/>
+      <c r="D593" s="49"/>
       <c r="E593" s="2"/>
       <c r="F593" s="2"/>
       <c r="G593" s="2"/>
@@ -19306,7 +19331,7 @@
       <c r="A594" s="2"/>
       <c r="B594" s="2"/>
       <c r="C594" s="2"/>
-      <c r="D594" s="50"/>
+      <c r="D594" s="49"/>
       <c r="E594" s="2"/>
       <c r="F594" s="2"/>
       <c r="G594" s="2"/>
@@ -19334,7 +19359,7 @@
       <c r="A595" s="2"/>
       <c r="B595" s="2"/>
       <c r="C595" s="2"/>
-      <c r="D595" s="50"/>
+      <c r="D595" s="49"/>
       <c r="E595" s="2"/>
       <c r="F595" s="2"/>
       <c r="G595" s="2"/>
@@ -19362,7 +19387,7 @@
       <c r="A596" s="2"/>
       <c r="B596" s="2"/>
       <c r="C596" s="2"/>
-      <c r="D596" s="50"/>
+      <c r="D596" s="49"/>
       <c r="E596" s="2"/>
       <c r="F596" s="2"/>
       <c r="G596" s="2"/>
@@ -19390,7 +19415,7 @@
       <c r="A597" s="2"/>
       <c r="B597" s="2"/>
       <c r="C597" s="2"/>
-      <c r="D597" s="50"/>
+      <c r="D597" s="49"/>
       <c r="E597" s="2"/>
       <c r="F597" s="2"/>
       <c r="G597" s="2"/>
@@ -19418,7 +19443,7 @@
       <c r="A598" s="2"/>
       <c r="B598" s="2"/>
       <c r="C598" s="2"/>
-      <c r="D598" s="50"/>
+      <c r="D598" s="49"/>
       <c r="E598" s="2"/>
       <c r="F598" s="2"/>
       <c r="G598" s="2"/>
@@ -19446,7 +19471,7 @@
       <c r="A599" s="2"/>
       <c r="B599" s="2"/>
       <c r="C599" s="2"/>
-      <c r="D599" s="50"/>
+      <c r="D599" s="49"/>
       <c r="E599" s="2"/>
       <c r="F599" s="2"/>
       <c r="G599" s="2"/>
@@ -19474,7 +19499,7 @@
       <c r="A600" s="2"/>
       <c r="B600" s="2"/>
       <c r="C600" s="2"/>
-      <c r="D600" s="50"/>
+      <c r="D600" s="49"/>
       <c r="E600" s="2"/>
       <c r="F600" s="2"/>
       <c r="G600" s="2"/>
@@ -19502,7 +19527,7 @@
       <c r="A601" s="2"/>
       <c r="B601" s="2"/>
       <c r="C601" s="2"/>
-      <c r="D601" s="50"/>
+      <c r="D601" s="49"/>
       <c r="E601" s="2"/>
       <c r="F601" s="2"/>
       <c r="G601" s="2"/>
@@ -19530,7 +19555,7 @@
       <c r="A602" s="2"/>
       <c r="B602" s="2"/>
       <c r="C602" s="2"/>
-      <c r="D602" s="50"/>
+      <c r="D602" s="49"/>
       <c r="E602" s="2"/>
       <c r="F602" s="2"/>
       <c r="G602" s="2"/>
@@ -19558,7 +19583,7 @@
       <c r="A603" s="2"/>
       <c r="B603" s="2"/>
       <c r="C603" s="2"/>
-      <c r="D603" s="50"/>
+      <c r="D603" s="49"/>
       <c r="E603" s="2"/>
       <c r="F603" s="2"/>
       <c r="G603" s="2"/>
@@ -19586,7 +19611,7 @@
       <c r="A604" s="2"/>
       <c r="B604" s="2"/>
       <c r="C604" s="2"/>
-      <c r="D604" s="50"/>
+      <c r="D604" s="49"/>
       <c r="E604" s="2"/>
       <c r="F604" s="2"/>
       <c r="G604" s="2"/>
@@ -19614,7 +19639,7 @@
       <c r="A605" s="2"/>
       <c r="B605" s="2"/>
       <c r="C605" s="2"/>
-      <c r="D605" s="50"/>
+      <c r="D605" s="49"/>
       <c r="E605" s="2"/>
       <c r="F605" s="2"/>
       <c r="G605" s="2"/>
@@ -19642,7 +19667,7 @@
       <c r="A606" s="2"/>
       <c r="B606" s="2"/>
       <c r="C606" s="2"/>
-      <c r="D606" s="50"/>
+      <c r="D606" s="49"/>
       <c r="E606" s="2"/>
       <c r="F606" s="2"/>
       <c r="G606" s="2"/>
@@ -19670,7 +19695,7 @@
       <c r="A607" s="2"/>
       <c r="B607" s="2"/>
       <c r="C607" s="2"/>
-      <c r="D607" s="50"/>
+      <c r="D607" s="49"/>
       <c r="E607" s="2"/>
       <c r="F607" s="2"/>
       <c r="G607" s="2"/>
@@ -19698,7 +19723,7 @@
       <c r="A608" s="2"/>
       <c r="B608" s="2"/>
       <c r="C608" s="2"/>
-      <c r="D608" s="50"/>
+      <c r="D608" s="49"/>
       <c r="E608" s="2"/>
       <c r="F608" s="2"/>
       <c r="G608" s="2"/>
@@ -19726,7 +19751,7 @@
       <c r="A609" s="2"/>
       <c r="B609" s="2"/>
       <c r="C609" s="2"/>
-      <c r="D609" s="50"/>
+      <c r="D609" s="49"/>
       <c r="E609" s="2"/>
       <c r="F609" s="2"/>
       <c r="G609" s="2"/>
@@ -19754,7 +19779,7 @@
       <c r="A610" s="2"/>
       <c r="B610" s="2"/>
       <c r="C610" s="2"/>
-      <c r="D610" s="50"/>
+      <c r="D610" s="49"/>
       <c r="E610" s="2"/>
       <c r="F610" s="2"/>
       <c r="G610" s="2"/>
@@ -19782,7 +19807,7 @@
       <c r="A611" s="2"/>
       <c r="B611" s="2"/>
       <c r="C611" s="2"/>
-      <c r="D611" s="50"/>
+      <c r="D611" s="49"/>
       <c r="E611" s="2"/>
       <c r="F611" s="2"/>
       <c r="G611" s="2"/>
@@ -19810,7 +19835,7 @@
       <c r="A612" s="2"/>
       <c r="B612" s="2"/>
       <c r="C612" s="2"/>
-      <c r="D612" s="50"/>
+      <c r="D612" s="49"/>
       <c r="E612" s="2"/>
       <c r="F612" s="2"/>
       <c r="G612" s="2"/>
@@ -19838,7 +19863,7 @@
       <c r="A613" s="2"/>
       <c r="B613" s="2"/>
       <c r="C613" s="2"/>
-      <c r="D613" s="50"/>
+      <c r="D613" s="49"/>
       <c r="E613" s="2"/>
       <c r="F613" s="2"/>
       <c r="G613" s="2"/>
@@ -19866,7 +19891,7 @@
       <c r="A614" s="2"/>
       <c r="B614" s="2"/>
       <c r="C614" s="2"/>
-      <c r="D614" s="50"/>
+      <c r="D614" s="49"/>
       <c r="E614" s="2"/>
       <c r="F614" s="2"/>
       <c r="G614" s="2"/>
@@ -19894,7 +19919,7 @@
       <c r="A615" s="2"/>
       <c r="B615" s="2"/>
       <c r="C615" s="2"/>
-      <c r="D615" s="50"/>
+      <c r="D615" s="49"/>
       <c r="E615" s="2"/>
       <c r="F615" s="2"/>
       <c r="G615" s="2"/>
@@ -19922,7 +19947,7 @@
       <c r="A616" s="2"/>
       <c r="B616" s="2"/>
       <c r="C616" s="2"/>
-      <c r="D616" s="50"/>
+      <c r="D616" s="49"/>
       <c r="E616" s="2"/>
       <c r="F616" s="2"/>
       <c r="G616" s="2"/>
@@ -19950,7 +19975,7 @@
       <c r="A617" s="2"/>
       <c r="B617" s="2"/>
       <c r="C617" s="2"/>
-      <c r="D617" s="50"/>
+      <c r="D617" s="49"/>
       <c r="E617" s="2"/>
       <c r="F617" s="2"/>
       <c r="G617" s="2"/>
@@ -19978,7 +20003,7 @@
       <c r="A618" s="2"/>
       <c r="B618" s="2"/>
       <c r="C618" s="2"/>
-      <c r="D618" s="50"/>
+      <c r="D618" s="49"/>
       <c r="E618" s="2"/>
       <c r="F618" s="2"/>
       <c r="G618" s="2"/>
@@ -20006,7 +20031,7 @@
       <c r="A619" s="2"/>
       <c r="B619" s="2"/>
       <c r="C619" s="2"/>
-      <c r="D619" s="50"/>
+      <c r="D619" s="49"/>
       <c r="E619" s="2"/>
       <c r="F619" s="2"/>
       <c r="G619" s="2"/>
@@ -20034,7 +20059,7 @@
       <c r="A620" s="2"/>
       <c r="B620" s="2"/>
       <c r="C620" s="2"/>
-      <c r="D620" s="50"/>
+      <c r="D620" s="49"/>
       <c r="E620" s="2"/>
       <c r="F620" s="2"/>
       <c r="G620" s="2"/>
@@ -20062,7 +20087,7 @@
       <c r="A621" s="2"/>
       <c r="B621" s="2"/>
       <c r="C621" s="2"/>
-      <c r="D621" s="50"/>
+      <c r="D621" s="49"/>
       <c r="E621" s="2"/>
       <c r="F621" s="2"/>
       <c r="G621" s="2"/>
@@ -20090,7 +20115,7 @@
       <c r="A622" s="2"/>
       <c r="B622" s="2"/>
       <c r="C622" s="2"/>
-      <c r="D622" s="50"/>
+      <c r="D622" s="49"/>
       <c r="E622" s="2"/>
       <c r="F622" s="2"/>
       <c r="G622" s="2"/>
@@ -20118,7 +20143,7 @@
       <c r="A623" s="2"/>
       <c r="B623" s="2"/>
       <c r="C623" s="2"/>
-      <c r="D623" s="50"/>
+      <c r="D623" s="49"/>
       <c r="E623" s="2"/>
       <c r="F623" s="2"/>
       <c r="G623" s="2"/>
@@ -20146,7 +20171,7 @@
       <c r="A624" s="2"/>
       <c r="B624" s="2"/>
       <c r="C624" s="2"/>
-      <c r="D624" s="50"/>
+      <c r="D624" s="49"/>
       <c r="E624" s="2"/>
       <c r="F624" s="2"/>
       <c r="G624" s="2"/>
@@ -20174,7 +20199,7 @@
       <c r="A625" s="2"/>
       <c r="B625" s="2"/>
       <c r="C625" s="2"/>
-      <c r="D625" s="50"/>
+      <c r="D625" s="49"/>
       <c r="E625" s="2"/>
       <c r="F625" s="2"/>
       <c r="G625" s="2"/>
@@ -20202,7 +20227,7 @@
       <c r="A626" s="2"/>
       <c r="B626" s="2"/>
       <c r="C626" s="2"/>
-      <c r="D626" s="50"/>
+      <c r="D626" s="49"/>
       <c r="E626" s="2"/>
       <c r="F626" s="2"/>
       <c r="G626" s="2"/>
@@ -20230,7 +20255,7 @@
       <c r="A627" s="2"/>
       <c r="B627" s="2"/>
       <c r="C627" s="2"/>
-      <c r="D627" s="50"/>
+      <c r="D627" s="49"/>
       <c r="E627" s="2"/>
       <c r="F627" s="2"/>
       <c r="G627" s="2"/>
@@ -20258,7 +20283,7 @@
       <c r="A628" s="2"/>
       <c r="B628" s="2"/>
       <c r="C628" s="2"/>
-      <c r="D628" s="50"/>
+      <c r="D628" s="49"/>
       <c r="E628" s="2"/>
       <c r="F628" s="2"/>
       <c r="G628" s="2"/>
@@ -20286,7 +20311,7 @@
       <c r="A629" s="2"/>
       <c r="B629" s="2"/>
       <c r="C629" s="2"/>
-      <c r="D629" s="50"/>
+      <c r="D629" s="49"/>
       <c r="E629" s="2"/>
       <c r="F629" s="2"/>
       <c r="G629" s="2"/>
@@ -20314,7 +20339,7 @@
       <c r="A630" s="2"/>
       <c r="B630" s="2"/>
       <c r="C630" s="2"/>
-      <c r="D630" s="50"/>
+      <c r="D630" s="49"/>
       <c r="E630" s="2"/>
       <c r="F630" s="2"/>
       <c r="G630" s="2"/>
@@ -20342,7 +20367,7 @@
       <c r="A631" s="2"/>
       <c r="B631" s="2"/>
       <c r="C631" s="2"/>
-      <c r="D631" s="50"/>
+      <c r="D631" s="49"/>
       <c r="E631" s="2"/>
       <c r="F631" s="2"/>
       <c r="G631" s="2"/>
@@ -20370,7 +20395,7 @@
       <c r="A632" s="2"/>
       <c r="B632" s="2"/>
       <c r="C632" s="2"/>
-      <c r="D632" s="50"/>
+      <c r="D632" s="49"/>
       <c r="E632" s="2"/>
       <c r="F632" s="2"/>
       <c r="G632" s="2"/>
@@ -20398,7 +20423,7 @@
       <c r="A633" s="2"/>
       <c r="B633" s="2"/>
       <c r="C633" s="2"/>
-      <c r="D633" s="50"/>
+      <c r="D633" s="49"/>
       <c r="E633" s="2"/>
       <c r="F633" s="2"/>
       <c r="G633" s="2"/>
@@ -20426,7 +20451,7 @@
       <c r="A634" s="2"/>
       <c r="B634" s="2"/>
       <c r="C634" s="2"/>
-      <c r="D634" s="50"/>
+      <c r="D634" s="49"/>
       <c r="E634" s="2"/>
       <c r="F634" s="2"/>
       <c r="G634" s="2"/>
@@ -20454,7 +20479,7 @@
       <c r="A635" s="2"/>
       <c r="B635" s="2"/>
       <c r="C635" s="2"/>
-      <c r="D635" s="50"/>
+      <c r="D635" s="49"/>
       <c r="E635" s="2"/>
       <c r="F635" s="2"/>
       <c r="G635" s="2"/>
@@ -20482,7 +20507,7 @@
       <c r="A636" s="2"/>
       <c r="B636" s="2"/>
       <c r="C636" s="2"/>
-      <c r="D636" s="50"/>
+      <c r="D636" s="49"/>
       <c r="E636" s="2"/>
       <c r="F636" s="2"/>
       <c r="G636" s="2"/>
@@ -20510,7 +20535,7 @@
       <c r="A637" s="2"/>
       <c r="B637" s="2"/>
       <c r="C637" s="2"/>
-      <c r="D637" s="50"/>
+      <c r="D637" s="49"/>
       <c r="E637" s="2"/>
       <c r="F637" s="2"/>
       <c r="G637" s="2"/>
@@ -20538,7 +20563,7 @@
       <c r="A638" s="2"/>
       <c r="B638" s="2"/>
       <c r="C638" s="2"/>
-      <c r="D638" s="50"/>
+      <c r="D638" s="49"/>
       <c r="E638" s="2"/>
       <c r="F638" s="2"/>
       <c r="G638" s="2"/>
@@ -20566,7 +20591,7 @@
       <c r="A639" s="2"/>
       <c r="B639" s="2"/>
       <c r="C639" s="2"/>
-      <c r="D639" s="50"/>
+      <c r="D639" s="49"/>
       <c r="E639" s="2"/>
       <c r="F639" s="2"/>
       <c r="G639" s="2"/>
@@ -20594,7 +20619,7 @@
       <c r="A640" s="2"/>
       <c r="B640" s="2"/>
       <c r="C640" s="2"/>
-      <c r="D640" s="50"/>
+      <c r="D640" s="49"/>
       <c r="E640" s="2"/>
       <c r="F640" s="2"/>
       <c r="G640" s="2"/>
@@ -20622,7 +20647,7 @@
       <c r="A641" s="2"/>
       <c r="B641" s="2"/>
       <c r="C641" s="2"/>
-      <c r="D641" s="50"/>
+      <c r="D641" s="49"/>
       <c r="E641" s="2"/>
       <c r="F641" s="2"/>
       <c r="G641" s="2"/>
@@ -20650,7 +20675,7 @@
       <c r="A642" s="2"/>
       <c r="B642" s="2"/>
       <c r="C642" s="2"/>
-      <c r="D642" s="50"/>
+      <c r="D642" s="49"/>
       <c r="E642" s="2"/>
       <c r="F642" s="2"/>
       <c r="G642" s="2"/>
@@ -20678,7 +20703,7 @@
       <c r="A643" s="2"/>
       <c r="B643" s="2"/>
       <c r="C643" s="2"/>
-      <c r="D643" s="50"/>
+      <c r="D643" s="49"/>
       <c r="E643" s="2"/>
       <c r="F643" s="2"/>
       <c r="G643" s="2"/>
@@ -20706,7 +20731,7 @@
       <c r="A644" s="2"/>
       <c r="B644" s="2"/>
       <c r="C644" s="2"/>
-      <c r="D644" s="50"/>
+      <c r="D644" s="49"/>
       <c r="E644" s="2"/>
       <c r="F644" s="2"/>
       <c r="G644" s="2"/>
@@ -20734,7 +20759,7 @@
       <c r="A645" s="2"/>
       <c r="B645" s="2"/>
       <c r="C645" s="2"/>
-      <c r="D645" s="50"/>
+      <c r="D645" s="49"/>
       <c r="E645" s="2"/>
       <c r="F645" s="2"/>
       <c r="G645" s="2"/>
@@ -20762,7 +20787,7 @@
       <c r="A646" s="2"/>
       <c r="B646" s="2"/>
       <c r="C646" s="2"/>
-      <c r="D646" s="50"/>
+      <c r="D646" s="49"/>
       <c r="E646" s="2"/>
       <c r="F646" s="2"/>
       <c r="G646" s="2"/>
@@ -20790,7 +20815,7 @@
       <c r="A647" s="2"/>
       <c r="B647" s="2"/>
       <c r="C647" s="2"/>
-      <c r="D647" s="50"/>
+      <c r="D647" s="49"/>
       <c r="E647" s="2"/>
       <c r="F647" s="2"/>
       <c r="G647" s="2"/>
@@ -20818,7 +20843,7 @@
       <c r="A648" s="2"/>
       <c r="B648" s="2"/>
       <c r="C648" s="2"/>
-      <c r="D648" s="50"/>
+      <c r="D648" s="49"/>
       <c r="E648" s="2"/>
       <c r="F648" s="2"/>
       <c r="G648" s="2"/>
@@ -20846,7 +20871,7 @@
       <c r="A649" s="2"/>
       <c r="B649" s="2"/>
       <c r="C649" s="2"/>
-      <c r="D649" s="50"/>
+      <c r="D649" s="49"/>
       <c r="E649" s="2"/>
       <c r="F649" s="2"/>
       <c r="G649" s="2"/>
@@ -20874,7 +20899,7 @@
       <c r="A650" s="2"/>
       <c r="B650" s="2"/>
       <c r="C650" s="2"/>
-      <c r="D650" s="50"/>
+      <c r="D650" s="49"/>
       <c r="E650" s="2"/>
       <c r="F650" s="2"/>
       <c r="G650" s="2"/>
@@ -20902,7 +20927,7 @@
       <c r="A651" s="2"/>
       <c r="B651" s="2"/>
       <c r="C651" s="2"/>
-      <c r="D651" s="50"/>
+      <c r="D651" s="49"/>
       <c r="E651" s="2"/>
       <c r="F651" s="2"/>
       <c r="G651" s="2"/>
@@ -20930,7 +20955,7 @@
       <c r="A652" s="2"/>
       <c r="B652" s="2"/>
       <c r="C652" s="2"/>
-      <c r="D652" s="50"/>
+      <c r="D652" s="49"/>
       <c r="E652" s="2"/>
       <c r="F652" s="2"/>
       <c r="G652" s="2"/>
@@ -20958,7 +20983,7 @@
       <c r="A653" s="2"/>
       <c r="B653" s="2"/>
       <c r="C653" s="2"/>
-      <c r="D653" s="50"/>
+      <c r="D653" s="49"/>
       <c r="E653" s="2"/>
       <c r="F653" s="2"/>
       <c r="G653" s="2"/>
@@ -20986,7 +21011,7 @@
       <c r="A654" s="2"/>
       <c r="B654" s="2"/>
       <c r="C654" s="2"/>
-      <c r="D654" s="50"/>
+      <c r="D654" s="49"/>
       <c r="E654" s="2"/>
       <c r="F654" s="2"/>
       <c r="G654" s="2"/>
@@ -21014,7 +21039,7 @@
       <c r="A655" s="2"/>
       <c r="B655" s="2"/>
       <c r="C655" s="2"/>
-      <c r="D655" s="50"/>
+      <c r="D655" s="49"/>
       <c r="E655" s="2"/>
       <c r="F655" s="2"/>
       <c r="G655" s="2"/>
@@ -21042,7 +21067,7 @@
       <c r="A656" s="2"/>
       <c r="B656" s="2"/>
       <c r="C656" s="2"/>
-      <c r="D656" s="50"/>
+      <c r="D656" s="49"/>
       <c r="E656" s="2"/>
       <c r="F656" s="2"/>
       <c r="G656" s="2"/>
@@ -21070,7 +21095,7 @@
       <c r="A657" s="2"/>
       <c r="B657" s="2"/>
       <c r="C657" s="2"/>
-      <c r="D657" s="50"/>
+      <c r="D657" s="49"/>
       <c r="E657" s="2"/>
       <c r="F657" s="2"/>
       <c r="G657" s="2"/>
@@ -21098,7 +21123,7 @@
       <c r="A658" s="2"/>
       <c r="B658" s="2"/>
       <c r="C658" s="2"/>
-      <c r="D658" s="50"/>
+      <c r="D658" s="49"/>
       <c r="E658" s="2"/>
       <c r="F658" s="2"/>
       <c r="G658" s="2"/>
@@ -21126,7 +21151,7 @@
       <c r="A659" s="2"/>
       <c r="B659" s="2"/>
       <c r="C659" s="2"/>
-      <c r="D659" s="50"/>
+      <c r="D659" s="49"/>
       <c r="E659" s="2"/>
       <c r="F659" s="2"/>
       <c r="G659" s="2"/>
@@ -21154,7 +21179,7 @@
       <c r="A660" s="2"/>
       <c r="B660" s="2"/>
       <c r="C660" s="2"/>
-      <c r="D660" s="50"/>
+      <c r="D660" s="49"/>
       <c r="E660" s="2"/>
       <c r="F660" s="2"/>
       <c r="G660" s="2"/>
@@ -21182,7 +21207,7 @@
       <c r="A661" s="2"/>
       <c r="B661" s="2"/>
       <c r="C661" s="2"/>
-      <c r="D661" s="50"/>
+      <c r="D661" s="49"/>
       <c r="E661" s="2"/>
       <c r="F661" s="2"/>
       <c r="G661" s="2"/>
@@ -21210,7 +21235,7 @@
       <c r="A662" s="2"/>
       <c r="B662" s="2"/>
       <c r="C662" s="2"/>
-      <c r="D662" s="50"/>
+      <c r="D662" s="49"/>
       <c r="E662" s="2"/>
       <c r="F662" s="2"/>
       <c r="G662" s="2"/>
@@ -21238,7 +21263,7 @@
       <c r="A663" s="2"/>
       <c r="B663" s="2"/>
       <c r="C663" s="2"/>
-      <c r="D663" s="50"/>
+      <c r="D663" s="49"/>
       <c r="E663" s="2"/>
       <c r="F663" s="2"/>
       <c r="G663" s="2"/>
@@ -21266,7 +21291,7 @@
       <c r="A664" s="2"/>
       <c r="B664" s="2"/>
       <c r="C664" s="2"/>
-      <c r="D664" s="50"/>
+      <c r="D664" s="49"/>
       <c r="E664" s="2"/>
       <c r="F664" s="2"/>
       <c r="G664" s="2"/>
@@ -21294,7 +21319,7 @@
       <c r="A665" s="2"/>
       <c r="B665" s="2"/>
       <c r="C665" s="2"/>
-      <c r="D665" s="50"/>
+      <c r="D665" s="49"/>
       <c r="E665" s="2"/>
       <c r="F665" s="2"/>
       <c r="G665" s="2"/>
@@ -21322,7 +21347,7 @@
       <c r="A666" s="2"/>
       <c r="B666" s="2"/>
       <c r="C666" s="2"/>
-      <c r="D666" s="50"/>
+      <c r="D666" s="49"/>
       <c r="E666" s="2"/>
       <c r="F666" s="2"/>
       <c r="G666" s="2"/>
@@ -21350,7 +21375,7 @@
       <c r="A667" s="2"/>
       <c r="B667" s="2"/>
       <c r="C667" s="2"/>
-      <c r="D667" s="50"/>
+      <c r="D667" s="49"/>
       <c r="E667" s="2"/>
       <c r="F667" s="2"/>
       <c r="G667" s="2"/>
@@ -21378,7 +21403,7 @@
       <c r="A668" s="2"/>
       <c r="B668" s="2"/>
       <c r="C668" s="2"/>
-      <c r="D668" s="50"/>
+      <c r="D668" s="49"/>
       <c r="E668" s="2"/>
       <c r="F668" s="2"/>
       <c r="G668" s="2"/>
@@ -21406,7 +21431,7 @@
       <c r="A669" s="2"/>
       <c r="B669" s="2"/>
       <c r="C669" s="2"/>
-      <c r="D669" s="50"/>
+      <c r="D669" s="49"/>
       <c r="E669" s="2"/>
       <c r="F669" s="2"/>
       <c r="G669" s="2"/>
@@ -21434,7 +21459,7 @@
       <c r="A670" s="2"/>
       <c r="B670" s="2"/>
       <c r="C670" s="2"/>
-      <c r="D670" s="50"/>
+      <c r="D670" s="49"/>
       <c r="E670" s="2"/>
       <c r="F670" s="2"/>
       <c r="G670" s="2"/>
@@ -21462,7 +21487,7 @@
       <c r="A671" s="2"/>
       <c r="B671" s="2"/>
       <c r="C671" s="2"/>
-      <c r="D671" s="50"/>
+      <c r="D671" s="49"/>
       <c r="E671" s="2"/>
       <c r="F671" s="2"/>
       <c r="G671" s="2"/>
@@ -21490,7 +21515,7 @@
       <c r="A672" s="2"/>
       <c r="B672" s="2"/>
       <c r="C672" s="2"/>
-      <c r="D672" s="50"/>
+      <c r="D672" s="49"/>
       <c r="E672" s="2"/>
       <c r="F672" s="2"/>
       <c r="G672" s="2"/>
@@ -21518,7 +21543,7 @@
       <c r="A673" s="2"/>
       <c r="B673" s="2"/>
       <c r="C673" s="2"/>
-      <c r="D673" s="50"/>
+      <c r="D673" s="49"/>
       <c r="E673" s="2"/>
       <c r="F673" s="2"/>
       <c r="G673" s="2"/>
@@ -21546,7 +21571,7 @@
       <c r="A674" s="2"/>
       <c r="B674" s="2"/>
       <c r="C674" s="2"/>
-      <c r="D674" s="50"/>
+      <c r="D674" s="49"/>
       <c r="E674" s="2"/>
       <c r="F674" s="2"/>
       <c r="G674" s="2"/>
@@ -21574,7 +21599,7 @@
       <c r="A675" s="2"/>
       <c r="B675" s="2"/>
       <c r="C675" s="2"/>
-      <c r="D675" s="50"/>
+      <c r="D675" s="49"/>
       <c r="E675" s="2"/>
       <c r="F675" s="2"/>
       <c r="G675" s="2"/>
@@ -21602,7 +21627,7 @@
       <c r="A676" s="2"/>
       <c r="B676" s="2"/>
       <c r="C676" s="2"/>
-      <c r="D676" s="50"/>
+      <c r="D676" s="49"/>
       <c r="E676" s="2"/>
       <c r="F676" s="2"/>
       <c r="G676" s="2"/>
@@ -21630,7 +21655,7 @@
       <c r="A677" s="2"/>
       <c r="B677" s="2"/>
       <c r="C677" s="2"/>
-      <c r="D677" s="50"/>
+      <c r="D677" s="49"/>
       <c r="E677" s="2"/>
       <c r="F677" s="2"/>
       <c r="G677" s="2"/>
@@ -21658,7 +21683,7 @@
       <c r="A678" s="2"/>
       <c r="B678" s="2"/>
       <c r="C678" s="2"/>
-      <c r="D678" s="50"/>
+      <c r="D678" s="49"/>
       <c r="E678" s="2"/>
       <c r="F678" s="2"/>
       <c r="G678" s="2"/>
@@ -21686,7 +21711,7 @@
       <c r="A679" s="2"/>
       <c r="B679" s="2"/>
       <c r="C679" s="2"/>
-      <c r="D679" s="50"/>
+      <c r="D679" s="49"/>
       <c r="E679" s="2"/>
       <c r="F679" s="2"/>
       <c r="G679" s="2"/>
@@ -21714,7 +21739,7 @@
       <c r="A680" s="2"/>
       <c r="B680" s="2"/>
       <c r="C680" s="2"/>
-      <c r="D680" s="50"/>
+      <c r="D680" s="49"/>
       <c r="E680" s="2"/>
       <c r="F680" s="2"/>
       <c r="G680" s="2"/>
@@ -21742,7 +21767,7 @@
       <c r="A681" s="2"/>
       <c r="B681" s="2"/>
       <c r="C681" s="2"/>
-      <c r="D681" s="50"/>
+      <c r="D681" s="49"/>
       <c r="E681" s="2"/>
       <c r="F681" s="2"/>
       <c r="G681" s="2"/>
@@ -21770,7 +21795,7 @@
       <c r="A682" s="2"/>
       <c r="B682" s="2"/>
       <c r="C682" s="2"/>
-      <c r="D682" s="50"/>
+      <c r="D682" s="49"/>
       <c r="E682" s="2"/>
       <c r="F682" s="2"/>
       <c r="G682" s="2"/>
@@ -21798,7 +21823,7 @@
       <c r="A683" s="2"/>
       <c r="B683" s="2"/>
       <c r="C683" s="2"/>
-      <c r="D683" s="50"/>
+      <c r="D683" s="49"/>
       <c r="E683" s="2"/>
       <c r="F683" s="2"/>
       <c r="G683" s="2"/>
@@ -21826,7 +21851,7 @@
       <c r="A684" s="2"/>
       <c r="B684" s="2"/>
       <c r="C684" s="2"/>
-      <c r="D684" s="50"/>
+      <c r="D684" s="49"/>
       <c r="E684" s="2"/>
       <c r="F684" s="2"/>
       <c r="G684" s="2"/>
@@ -21854,7 +21879,7 @@
       <c r="A685" s="2"/>
       <c r="B685" s="2"/>
       <c r="C685" s="2"/>
-      <c r="D685" s="50"/>
+      <c r="D685" s="49"/>
       <c r="E685" s="2"/>
       <c r="F685" s="2"/>
       <c r="G685" s="2"/>
@@ -21882,7 +21907,7 @@
       <c r="A686" s="2"/>
       <c r="B686" s="2"/>
       <c r="C686" s="2"/>
-      <c r="D686" s="50"/>
+      <c r="D686" s="49"/>
       <c r="E686" s="2"/>
       <c r="F686" s="2"/>
       <c r="G686" s="2"/>
@@ -21910,7 +21935,7 @@
       <c r="A687" s="2"/>
       <c r="B687" s="2"/>
       <c r="C687" s="2"/>
-      <c r="D687" s="50"/>
+      <c r="D687" s="49"/>
       <c r="E687" s="2"/>
       <c r="F687" s="2"/>
       <c r="G687" s="2"/>
@@ -21938,7 +21963,7 @@
       <c r="A688" s="2"/>
       <c r="B688" s="2"/>
       <c r="C688" s="2"/>
-      <c r="D688" s="50"/>
+      <c r="D688" s="49"/>
       <c r="E688" s="2"/>
       <c r="F688" s="2"/>
       <c r="G688" s="2"/>
@@ -21966,7 +21991,7 @@
       <c r="A689" s="2"/>
       <c r="B689" s="2"/>
       <c r="C689" s="2"/>
-      <c r="D689" s="50"/>
+      <c r="D689" s="49"/>
       <c r="E689" s="2"/>
       <c r="F689" s="2"/>
       <c r="G689" s="2"/>
@@ -21994,7 +22019,7 @@
       <c r="A690" s="2"/>
       <c r="B690" s="2"/>
       <c r="C690" s="2"/>
-      <c r="D690" s="50"/>
+      <c r="D690" s="49"/>
       <c r="E690" s="2"/>
       <c r="F690" s="2"/>
       <c r="G690" s="2"/>
@@ -22022,7 +22047,7 @@
       <c r="A691" s="2"/>
       <c r="B691" s="2"/>
       <c r="C691" s="2"/>
-      <c r="D691" s="50"/>
+      <c r="D691" s="49"/>
       <c r="E691" s="2"/>
       <c r="F691" s="2"/>
       <c r="G691" s="2"/>
@@ -22050,7 +22075,7 @@
       <c r="A692" s="2"/>
       <c r="B692" s="2"/>
       <c r="C692" s="2"/>
-      <c r="D692" s="50"/>
+      <c r="D692" s="49"/>
       <c r="E692" s="2"/>
       <c r="F692" s="2"/>
       <c r="G692" s="2"/>
@@ -22078,7 +22103,7 @@
       <c r="A693" s="2"/>
       <c r="B693" s="2"/>
       <c r="C693" s="2"/>
-      <c r="D693" s="50"/>
+      <c r="D693" s="49"/>
       <c r="E693" s="2"/>
       <c r="F693" s="2"/>
       <c r="G693" s="2"/>
@@ -22106,7 +22131,7 @@
       <c r="A694" s="2"/>
       <c r="B694" s="2"/>
       <c r="C694" s="2"/>
-      <c r="D694" s="50"/>
+      <c r="D694" s="49"/>
       <c r="E694" s="2"/>
       <c r="F694" s="2"/>
       <c r="G694" s="2"/>
@@ -22134,7 +22159,7 @@
       <c r="A695" s="2"/>
       <c r="B695" s="2"/>
       <c r="C695" s="2"/>
-      <c r="D695" s="50"/>
+      <c r="D695" s="49"/>
       <c r="E695" s="2"/>
       <c r="F695" s="2"/>
       <c r="G695" s="2"/>
@@ -22162,7 +22187,7 @@
       <c r="A696" s="2"/>
       <c r="B696" s="2"/>
       <c r="C696" s="2"/>
-      <c r="D696" s="50"/>
+      <c r="D696" s="49"/>
       <c r="E696" s="2"/>
       <c r="F696" s="2"/>
       <c r="G696" s="2"/>
@@ -22190,7 +22215,7 @@
       <c r="A697" s="2"/>
       <c r="B697" s="2"/>
       <c r="C697" s="2"/>
-      <c r="D697" s="50"/>
+      <c r="D697" s="49"/>
       <c r="E697" s="2"/>
       <c r="F697" s="2"/>
       <c r="G697" s="2"/>
@@ -22218,7 +22243,7 @@
       <c r="A698" s="2"/>
       <c r="B698" s="2"/>
       <c r="C698" s="2"/>
-      <c r="D698" s="50"/>
+      <c r="D698" s="49"/>
       <c r="E698" s="2"/>
       <c r="F698" s="2"/>
       <c r="G698" s="2"/>
@@ -22246,7 +22271,7 @@
       <c r="A699" s="2"/>
       <c r="B699" s="2"/>
       <c r="C699" s="2"/>
-      <c r="D699" s="50"/>
+      <c r="D699" s="49"/>
       <c r="E699" s="2"/>
       <c r="F699" s="2"/>
       <c r="G699" s="2"/>
@@ -22274,7 +22299,7 @@
       <c r="A700" s="2"/>
       <c r="B700" s="2"/>
       <c r="C700" s="2"/>
-      <c r="D700" s="50"/>
+      <c r="D700" s="49"/>
       <c r="E700" s="2"/>
       <c r="F700" s="2"/>
       <c r="G700" s="2"/>
@@ -22302,7 +22327,7 @@
       <c r="A701" s="2"/>
       <c r="B701" s="2"/>
       <c r="C701" s="2"/>
-      <c r="D701" s="50"/>
+      <c r="D701" s="49"/>
       <c r="E701" s="2"/>
       <c r="F701" s="2"/>
       <c r="G701" s="2"/>
@@ -22330,7 +22355,7 @@
       <c r="A702" s="2"/>
       <c r="B702" s="2"/>
       <c r="C702" s="2"/>
-      <c r="D702" s="50"/>
+      <c r="D702" s="49"/>
       <c r="E702" s="2"/>
       <c r="F702" s="2"/>
       <c r="G702" s="2"/>
@@ -22358,7 +22383,7 @@
       <c r="A703" s="2"/>
       <c r="B703" s="2"/>
       <c r="C703" s="2"/>
-      <c r="D703" s="50"/>
+      <c r="D703" s="49"/>
       <c r="E703" s="2"/>
       <c r="F703" s="2"/>
       <c r="G703" s="2"/>
@@ -22386,7 +22411,7 @@
       <c r="A704" s="2"/>
       <c r="B704" s="2"/>
       <c r="C704" s="2"/>
-      <c r="D704" s="50"/>
+      <c r="D704" s="49"/>
       <c r="E704" s="2"/>
       <c r="F704" s="2"/>
       <c r="G704" s="2"/>
@@ -22414,7 +22439,7 @@
       <c r="A705" s="2"/>
       <c r="B705" s="2"/>
       <c r="C705" s="2"/>
-      <c r="D705" s="50"/>
+      <c r="D705" s="49"/>
       <c r="E705" s="2"/>
       <c r="F705" s="2"/>
       <c r="G705" s="2"/>
@@ -22442,7 +22467,7 @@
       <c r="A706" s="2"/>
       <c r="B706" s="2"/>
       <c r="C706" s="2"/>
-      <c r="D706" s="50"/>
+      <c r="D706" s="49"/>
       <c r="E706" s="2"/>
       <c r="F706" s="2"/>
       <c r="G706" s="2"/>
@@ -22470,7 +22495,7 @@
       <c r="A707" s="2"/>
       <c r="B707" s="2"/>
       <c r="C707" s="2"/>
-      <c r="D707" s="50"/>
+      <c r="D707" s="49"/>
       <c r="E707" s="2"/>
       <c r="F707" s="2"/>
       <c r="G707" s="2"/>
@@ -22498,7 +22523,7 @@
       <c r="A708" s="2"/>
       <c r="B708" s="2"/>
       <c r="C708" s="2"/>
-      <c r="D708" s="50"/>
+      <c r="D708" s="49"/>
       <c r="E708" s="2"/>
       <c r="F708" s="2"/>
       <c r="G708" s="2"/>
@@ -22526,7 +22551,7 @@
       <c r="A709" s="2"/>
       <c r="B709" s="2"/>
       <c r="C709" s="2"/>
-      <c r="D709" s="50"/>
+      <c r="D709" s="49"/>
       <c r="E709" s="2"/>
       <c r="F709" s="2"/>
       <c r="G709" s="2"/>
@@ -22554,7 +22579,7 @@
       <c r="A710" s="2"/>
       <c r="B710" s="2"/>
       <c r="C710" s="2"/>
-      <c r="D710" s="50"/>
+      <c r="D710" s="49"/>
       <c r="E710" s="2"/>
       <c r="F710" s="2"/>
       <c r="G710" s="2"/>
@@ -22582,7 +22607,7 @@
       <c r="A711" s="2"/>
       <c r="B711" s="2"/>
       <c r="C711" s="2"/>
-      <c r="D711" s="50"/>
+      <c r="D711" s="49"/>
       <c r="E711" s="2"/>
       <c r="F711" s="2"/>
       <c r="G711" s="2"/>
@@ -22610,7 +22635,7 @@
       <c r="A712" s="2"/>
       <c r="B712" s="2"/>
       <c r="C712" s="2"/>
-      <c r="D712" s="50"/>
+      <c r="D712" s="49"/>
       <c r="E712" s="2"/>
       <c r="F712" s="2"/>
       <c r="G712" s="2"/>
@@ -22638,7 +22663,7 @@
       <c r="A713" s="2"/>
       <c r="B713" s="2"/>
       <c r="C713" s="2"/>
-      <c r="D713" s="50"/>
+      <c r="D713" s="49"/>
       <c r="E713" s="2"/>
       <c r="F713" s="2"/>
       <c r="G713" s="2"/>
@@ -22666,7 +22691,7 @@
       <c r="A714" s="2"/>
       <c r="B714" s="2"/>
       <c r="C714" s="2"/>
-      <c r="D714" s="50"/>
+      <c r="D714" s="49"/>
       <c r="E714" s="2"/>
       <c r="F714" s="2"/>
       <c r="G714" s="2"/>
@@ -22694,7 +22719,7 @@
       <c r="A715" s="2"/>
       <c r="B715" s="2"/>
       <c r="C715" s="2"/>
-      <c r="D715" s="50"/>
+      <c r="D715" s="49"/>
       <c r="E715" s="2"/>
       <c r="F715" s="2"/>
       <c r="G715" s="2"/>
@@ -22722,7 +22747,7 @@
       <c r="A716" s="2"/>
       <c r="B716" s="2"/>
       <c r="C716" s="2"/>
-      <c r="D716" s="50"/>
+      <c r="D716" s="49"/>
       <c r="E716" s="2"/>
       <c r="F716" s="2"/>
       <c r="G716" s="2"/>
@@ -22750,7 +22775,7 @@
       <c r="A717" s="2"/>
       <c r="B717" s="2"/>
       <c r="C717" s="2"/>
-      <c r="D717" s="50"/>
+      <c r="D717" s="49"/>
       <c r="E717" s="2"/>
       <c r="F717" s="2"/>
       <c r="G717" s="2"/>
@@ -22778,7 +22803,7 @@
       <c r="A718" s="2"/>
       <c r="B718" s="2"/>
       <c r="C718" s="2"/>
-      <c r="D718" s="50"/>
+      <c r="D718" s="49"/>
       <c r="E718" s="2"/>
       <c r="F718" s="2"/>
       <c r="G718" s="2"/>
@@ -22806,7 +22831,7 @@
       <c r="A719" s="2"/>
       <c r="B719" s="2"/>
       <c r="C719" s="2"/>
-      <c r="D719" s="50"/>
+      <c r="D719" s="49"/>
       <c r="E719" s="2"/>
       <c r="F719" s="2"/>
       <c r="G719" s="2"/>
@@ -22834,7 +22859,7 @@
       <c r="A720" s="2"/>
       <c r="B720" s="2"/>
       <c r="C720" s="2"/>
-      <c r="D720" s="50"/>
+      <c r="D720" s="49"/>
       <c r="E720" s="2"/>
       <c r="F720" s="2"/>
       <c r="G720" s="2"/>
@@ -22862,7 +22887,7 @@
       <c r="A721" s="2"/>
       <c r="B721" s="2"/>
       <c r="C721" s="2"/>
-      <c r="D721" s="50"/>
+      <c r="D721" s="49"/>
       <c r="E721" s="2"/>
       <c r="F721" s="2"/>
       <c r="G721" s="2"/>
@@ -22890,7 +22915,7 @@
       <c r="A722" s="2"/>
       <c r="B722" s="2"/>
       <c r="C722" s="2"/>
-      <c r="D722" s="50"/>
+      <c r="D722" s="49"/>
       <c r="E722" s="2"/>
       <c r="F722" s="2"/>
       <c r="G722" s="2"/>
@@ -22918,7 +22943,7 @@
       <c r="A723" s="2"/>
       <c r="B723" s="2"/>
       <c r="C723" s="2"/>
-      <c r="D723" s="50"/>
+      <c r="D723" s="49"/>
       <c r="E723" s="2"/>
       <c r="F723" s="2"/>
       <c r="G723" s="2"/>
@@ -22946,7 +22971,7 @@
       <c r="A724" s="2"/>
       <c r="B724" s="2"/>
       <c r="C724" s="2"/>
-      <c r="D724" s="50"/>
+      <c r="D724" s="49"/>
       <c r="E724" s="2"/>
       <c r="F724" s="2"/>
       <c r="G724" s="2"/>
@@ -22974,7 +22999,7 @@
       <c r="A725" s="2"/>
       <c r="B725" s="2"/>
       <c r="C725" s="2"/>
-      <c r="D725" s="50"/>
+      <c r="D725" s="49"/>
       <c r="E725" s="2"/>
       <c r="F725" s="2"/>
       <c r="G725" s="2"/>
@@ -23002,7 +23027,7 @@
       <c r="A726" s="2"/>
       <c r="B726" s="2"/>
       <c r="C726" s="2"/>
-      <c r="D726" s="50"/>
+      <c r="D726" s="49"/>
       <c r="E726" s="2"/>
       <c r="F726" s="2"/>
       <c r="G726" s="2"/>
@@ -23030,7 +23055,7 @@
       <c r="A727" s="2"/>
       <c r="B727" s="2"/>
       <c r="C727" s="2"/>
-      <c r="D727" s="50"/>
+      <c r="D727" s="49"/>
       <c r="E727" s="2"/>
       <c r="F727" s="2"/>
       <c r="G727" s="2"/>
@@ -23058,7 +23083,7 @@
       <c r="A728" s="2"/>
       <c r="B728" s="2"/>
       <c r="C728" s="2"/>
-      <c r="D728" s="50"/>
+      <c r="D728" s="49"/>
       <c r="E728" s="2"/>
       <c r="F728" s="2"/>
       <c r="G728" s="2"/>
@@ -23086,7 +23111,7 @@
       <c r="A729" s="2"/>
       <c r="B729" s="2"/>
       <c r="C729" s="2"/>
-      <c r="D729" s="50"/>
+      <c r="D729" s="49"/>
       <c r="E729" s="2"/>
       <c r="F729" s="2"/>
       <c r="G729" s="2"/>
@@ -23114,7 +23139,7 @@
       <c r="A730" s="2"/>
       <c r="B730" s="2"/>
       <c r="C730" s="2"/>
-      <c r="D730" s="50"/>
+      <c r="D730" s="49"/>
       <c r="E730" s="2"/>
       <c r="F730" s="2"/>
       <c r="G730" s="2"/>
@@ -23142,7 +23167,7 @@
       <c r="A731" s="2"/>
       <c r="B731" s="2"/>
       <c r="C731" s="2"/>
-      <c r="D731" s="50"/>
+      <c r="D731" s="49"/>
       <c r="E731" s="2"/>
       <c r="F731" s="2"/>
       <c r="G731" s="2"/>
@@ -23170,7 +23195,7 @@
       <c r="A732" s="2"/>
       <c r="B732" s="2"/>
       <c r="C732" s="2"/>
-      <c r="D732" s="50"/>
+      <c r="D732" s="49"/>
       <c r="E732" s="2"/>
       <c r="F732" s="2"/>
       <c r="G732" s="2"/>
@@ -23198,7 +23223,7 @@
       <c r="A733" s="2"/>
       <c r="B733" s="2"/>
       <c r="C733" s="2"/>
-      <c r="D733" s="50"/>
+      <c r="D733" s="49"/>
       <c r="E733" s="2"/>
       <c r="F733" s="2"/>
       <c r="G733" s="2"/>
@@ -23226,7 +23251,7 @@
       <c r="A734" s="2"/>
       <c r="B734" s="2"/>
       <c r="C734" s="2"/>
-      <c r="D734" s="50"/>
+      <c r="D734" s="49"/>
       <c r="E734" s="2"/>
       <c r="F734" s="2"/>
       <c r="G734" s="2"/>
@@ -23254,7 +23279,7 @@
       <c r="A735" s="2"/>
       <c r="B735" s="2"/>
       <c r="C735" s="2"/>
-      <c r="D735" s="50"/>
+      <c r="D735" s="49"/>
       <c r="E735" s="2"/>
       <c r="F735" s="2"/>
       <c r="G735" s="2"/>
@@ -23282,7 +23307,7 @@
       <c r="A736" s="2"/>
       <c r="B736" s="2"/>
       <c r="C736" s="2"/>
-      <c r="D736" s="50"/>
+      <c r="D736" s="49"/>
       <c r="E736" s="2"/>
       <c r="F736" s="2"/>
       <c r="G736" s="2"/>
@@ -23310,7 +23335,7 @@
       <c r="A737" s="2"/>
       <c r="B737" s="2"/>
       <c r="C737" s="2"/>
-      <c r="D737" s="50"/>
+      <c r="D737" s="49"/>
       <c r="E737" s="2"/>
       <c r="F737" s="2"/>
       <c r="G737" s="2"/>
@@ -23338,7 +23363,7 @@
       <c r="A738" s="2"/>
       <c r="B738" s="2"/>
       <c r="C738" s="2"/>
-      <c r="D738" s="50"/>
+      <c r="D738" s="49"/>
       <c r="E738" s="2"/>
       <c r="F738" s="2"/>
       <c r="G738" s="2"/>
@@ -23366,7 +23391,7 @@
       <c r="A739" s="2"/>
       <c r="B739" s="2"/>
       <c r="C739" s="2"/>
-      <c r="D739" s="50"/>
+      <c r="D739" s="49"/>
       <c r="E739" s="2"/>
       <c r="F739" s="2"/>
       <c r="G739" s="2"/>
@@ -23394,7 +23419,7 @@
       <c r="A740" s="2"/>
       <c r="B740" s="2"/>
       <c r="C740" s="2"/>
-      <c r="D740" s="50"/>
+      <c r="D740" s="49"/>
       <c r="E740" s="2"/>
       <c r="F740" s="2"/>
       <c r="G740" s="2"/>
@@ -23422,7 +23447,7 @@
       <c r="A741" s="2"/>
       <c r="B741" s="2"/>
       <c r="C741" s="2"/>
-      <c r="D741" s="50"/>
+      <c r="D741" s="49"/>
       <c r="E741" s="2"/>
       <c r="F741" s="2"/>
       <c r="G741" s="2"/>
@@ -23450,7 +23475,7 @@
       <c r="A742" s="2"/>
       <c r="B742" s="2"/>
       <c r="C742" s="2"/>
-      <c r="D742" s="50"/>
+      <c r="D742" s="49"/>
       <c r="E742" s="2"/>
       <c r="F742" s="2"/>
       <c r="G742" s="2"/>
@@ -23478,7 +23503,7 @@
       <c r="A743" s="2"/>
       <c r="B743" s="2"/>
       <c r="C743" s="2"/>
-      <c r="D743" s="50"/>
+      <c r="D743" s="49"/>
       <c r="E743" s="2"/>
       <c r="F743" s="2"/>
       <c r="G743" s="2"/>
@@ -23506,7 +23531,7 @@
       <c r="A744" s="2"/>
       <c r="B744" s="2"/>
       <c r="C744" s="2"/>
-      <c r="D744" s="50"/>
+      <c r="D744" s="49"/>
       <c r="E744" s="2"/>
       <c r="F744" s="2"/>
       <c r="G744" s="2"/>
@@ -23534,7 +23559,7 @@
       <c r="A745" s="2"/>
       <c r="B745" s="2"/>
       <c r="C745" s="2"/>
-      <c r="D745" s="50"/>
+      <c r="D745" s="49"/>
       <c r="E745" s="2"/>
       <c r="F745" s="2"/>
       <c r="G745" s="2"/>
@@ -23562,7 +23587,7 @@
       <c r="A746" s="2"/>
       <c r="B746" s="2"/>
       <c r="C746" s="2"/>
-      <c r="D746" s="50"/>
+      <c r="D746" s="49"/>
       <c r="E746" s="2"/>
       <c r="F746" s="2"/>
       <c r="G746" s="2"/>
@@ -23590,7 +23615,7 @@
       <c r="A747" s="2"/>
       <c r="B747" s="2"/>
       <c r="C747" s="2"/>
-      <c r="D747" s="50"/>
+      <c r="D747" s="49"/>
       <c r="E747" s="2"/>
       <c r="F747" s="2"/>
       <c r="G747" s="2"/>
@@ -23618,7 +23643,7 @@
       <c r="A748" s="2"/>
       <c r="B748" s="2"/>
       <c r="C748" s="2"/>
-      <c r="D748" s="50"/>
+      <c r="D748" s="49"/>
       <c r="E748" s="2"/>
       <c r="F748" s="2"/>
       <c r="G748" s="2"/>
@@ -23646,7 +23671,7 @@
       <c r="A749" s="2"/>
       <c r="B749" s="2"/>
       <c r="C749" s="2"/>
-      <c r="D749" s="50"/>
+      <c r="D749" s="49"/>
       <c r="E749" s="2"/>
       <c r="F749" s="2"/>
       <c r="G749" s="2"/>
@@ -23674,7 +23699,7 @@
       <c r="A750" s="2"/>
       <c r="B750" s="2"/>
       <c r="C750" s="2"/>
-      <c r="D750" s="50"/>
+      <c r="D750" s="49"/>
       <c r="E750" s="2"/>
       <c r="F750" s="2"/>
       <c r="G750" s="2"/>
@@ -23702,7 +23727,7 @@
       <c r="A751" s="2"/>
       <c r="B751" s="2"/>
       <c r="C751" s="2"/>
-      <c r="D751" s="50"/>
+      <c r="D751" s="49"/>
       <c r="E751" s="2"/>
       <c r="F751" s="2"/>
       <c r="G751" s="2"/>
@@ -23730,7 +23755,7 @@
       <c r="A752" s="2"/>
       <c r="B752" s="2"/>
       <c r="C752" s="2"/>
-      <c r="D752" s="50"/>
+      <c r="D752" s="49"/>
       <c r="E752" s="2"/>
       <c r="F752" s="2"/>
       <c r="G752" s="2"/>
@@ -23758,7 +23783,7 @@
       <c r="A753" s="2"/>
       <c r="B753" s="2"/>
       <c r="C753" s="2"/>
-      <c r="D753" s="50"/>
+      <c r="D753" s="49"/>
       <c r="E753" s="2"/>
       <c r="F753" s="2"/>
       <c r="G753" s="2"/>
@@ -23786,7 +23811,7 @@
       <c r="A754" s="2"/>
       <c r="B754" s="2"/>
       <c r="C754" s="2"/>
-      <c r="D754" s="50"/>
+      <c r="D754" s="49"/>
       <c r="E754" s="2"/>
       <c r="F754" s="2"/>
       <c r="G754" s="2"/>
@@ -23814,7 +23839,7 @@
       <c r="A755" s="2"/>
       <c r="B755" s="2"/>
       <c r="C755" s="2"/>
-      <c r="D755" s="50"/>
+      <c r="D755" s="49"/>
       <c r="E755" s="2"/>
       <c r="F755" s="2"/>
       <c r="G755" s="2"/>
@@ -23842,7 +23867,7 @@
       <c r="A756" s="2"/>
       <c r="B756" s="2"/>
       <c r="C756" s="2"/>
-      <c r="D756" s="50"/>
+      <c r="D756" s="49"/>
       <c r="E756" s="2"/>
       <c r="F756" s="2"/>
       <c r="G756" s="2"/>
@@ -23870,7 +23895,7 @@
       <c r="A757" s="2"/>
       <c r="B757" s="2"/>
       <c r="C757" s="2"/>
-      <c r="D757" s="50"/>
+      <c r="D757" s="49"/>
       <c r="E757" s="2"/>
       <c r="F757" s="2"/>
       <c r="G757" s="2"/>
@@ -23898,7 +23923,7 @@
       <c r="A758" s="2"/>
       <c r="B758" s="2"/>
       <c r="C758" s="2"/>
-      <c r="D758" s="50"/>
+      <c r="D758" s="49"/>
       <c r="E758" s="2"/>
       <c r="F758" s="2"/>
       <c r="G758" s="2"/>
@@ -23926,7 +23951,7 @@
       <c r="A759" s="2"/>
       <c r="B759" s="2"/>
       <c r="C759" s="2"/>
-      <c r="D759" s="50"/>
+      <c r="D759" s="49"/>
       <c r="E759" s="2"/>
       <c r="F759" s="2"/>
       <c r="G759" s="2"/>
@@ -23954,7 +23979,7 @@
       <c r="A760" s="2"/>
       <c r="B760" s="2"/>
       <c r="C760" s="2"/>
-      <c r="D760" s="50"/>
+      <c r="D760" s="49"/>
       <c r="E760" s="2"/>
       <c r="F760" s="2"/>
       <c r="G760" s="2"/>
@@ -23982,7 +24007,7 @@
       <c r="A761" s="2"/>
       <c r="B761" s="2"/>
       <c r="C761" s="2"/>
-      <c r="D761" s="50"/>
+      <c r="D761" s="49"/>
       <c r="E761" s="2"/>
       <c r="F761" s="2"/>
       <c r="G761" s="2"/>
@@ -24010,7 +24035,7 @@
       <c r="A762" s="2"/>
       <c r="B762" s="2"/>
       <c r="C762" s="2"/>
-      <c r="D762" s="50"/>
+      <c r="D762" s="49"/>
       <c r="E762" s="2"/>
       <c r="F762" s="2"/>
       <c r="G762" s="2"/>
@@ -24038,7 +24063,7 @@
       <c r="A763" s="2"/>
       <c r="B763" s="2"/>
       <c r="C763" s="2"/>
-      <c r="D763" s="50"/>
+      <c r="D763" s="49"/>
       <c r="E763" s="2"/>
       <c r="F763" s="2"/>
       <c r="G763" s="2"/>
@@ -24066,7 +24091,7 @@
       <c r="A764" s="2"/>
       <c r="B764" s="2"/>
       <c r="C764" s="2"/>
-      <c r="D764" s="50"/>
+      <c r="D764" s="49"/>
       <c r="E764" s="2"/>
       <c r="F764" s="2"/>
       <c r="G764" s="2"/>
@@ -24094,7 +24119,7 @@
       <c r="A765" s="2"/>
       <c r="B765" s="2"/>
       <c r="C765" s="2"/>
-      <c r="D765" s="50"/>
+      <c r="D765" s="49"/>
       <c r="E765" s="2"/>
       <c r="F765" s="2"/>
       <c r="G765" s="2"/>
@@ -24122,7 +24147,7 @@
       <c r="A766" s="2"/>
       <c r="B766" s="2"/>
       <c r="C766" s="2"/>
-      <c r="D766" s="50"/>
+      <c r="D766" s="49"/>
       <c r="E766" s="2"/>
       <c r="F766" s="2"/>
       <c r="G766" s="2"/>
@@ -24150,7 +24175,7 @@
       <c r="A767" s="2"/>
       <c r="B767" s="2"/>
       <c r="C767" s="2"/>
-      <c r="D767" s="50"/>
+      <c r="D767" s="49"/>
       <c r="E767" s="2"/>
       <c r="F767" s="2"/>
       <c r="G767" s="2"/>
@@ -24178,7 +24203,7 @@
       <c r="A768" s="2"/>
       <c r="B768" s="2"/>
       <c r="C768" s="2"/>
-      <c r="D768" s="50"/>
+      <c r="D768" s="49"/>
       <c r="E768" s="2"/>
       <c r="F768" s="2"/>
       <c r="G768" s="2"/>
@@ -24206,7 +24231,7 @@
       <c r="A769" s="2"/>
       <c r="B769" s="2"/>
       <c r="C769" s="2"/>
-      <c r="D769" s="50"/>
+      <c r="D769" s="49"/>
       <c r="E769" s="2"/>
       <c r="F769" s="2"/>
       <c r="G769" s="2"/>
@@ -24234,7 +24259,7 @@
       <c r="A770" s="2"/>
       <c r="B770" s="2"/>
       <c r="C770" s="2"/>
-      <c r="D770" s="50"/>
+      <c r="D770" s="49"/>
       <c r="E770" s="2"/>
       <c r="F770" s="2"/>
       <c r="G770" s="2"/>
@@ -24262,7 +24287,7 @@
       <c r="A771" s="2"/>
       <c r="B771" s="2"/>
       <c r="C771" s="2"/>
-      <c r="D771" s="50"/>
+      <c r="D771" s="49"/>
       <c r="E771" s="2"/>
       <c r="F771" s="2"/>
       <c r="G771" s="2"/>
@@ -24290,7 +24315,7 @@
       <c r="A772" s="2"/>
       <c r="B772" s="2"/>
       <c r="C772" s="2"/>
-      <c r="D772" s="50"/>
+      <c r="D772" s="49"/>
       <c r="E772" s="2"/>
       <c r="F772" s="2"/>
       <c r="G772" s="2"/>
@@ -24318,7 +24343,7 @@
       <c r="A773" s="2"/>
       <c r="B773" s="2"/>
       <c r="C773" s="2"/>
-      <c r="D773" s="50"/>
+      <c r="D773" s="49"/>
       <c r="E773" s="2"/>
       <c r="F773" s="2"/>
       <c r="G773" s="2"/>
@@ -24346,7 +24371,7 @@
       <c r="A774" s="2"/>
       <c r="B774" s="2"/>
       <c r="C774" s="2"/>
-      <c r="D774" s="50"/>
+      <c r="D774" s="49"/>
       <c r="E774" s="2"/>
       <c r="F774" s="2"/>
       <c r="G774" s="2"/>
@@ -24374,7 +24399,7 @@
       <c r="A775" s="2"/>
       <c r="B775" s="2"/>
       <c r="C775" s="2"/>
-      <c r="D775" s="50"/>
+      <c r="D775" s="49"/>
       <c r="E775" s="2"/>
       <c r="F775" s="2"/>
       <c r="G775" s="2"/>
@@ -24402,7 +24427,7 @@
       <c r="A776" s="2"/>
       <c r="B776" s="2"/>
       <c r="C776" s="2"/>
-      <c r="D776" s="50"/>
+      <c r="D776" s="49"/>
       <c r="E776" s="2"/>
       <c r="F776" s="2"/>
       <c r="G776" s="2"/>
@@ -24430,7 +24455,7 @@
       <c r="A777" s="2"/>
       <c r="B777" s="2"/>
       <c r="C777" s="2"/>
-      <c r="D777" s="50"/>
+      <c r="D777" s="49"/>
       <c r="E777" s="2"/>
       <c r="F777" s="2"/>
       <c r="G777" s="2"/>
@@ -24458,7 +24483,7 @@
       <c r="A778" s="2"/>
       <c r="B778" s="2"/>
       <c r="C778" s="2"/>
-      <c r="D778" s="50"/>
+      <c r="D778" s="49"/>
       <c r="E778" s="2"/>
       <c r="F778" s="2"/>
       <c r="G778" s="2"/>
@@ -24486,7 +24511,7 @@
       <c r="A779" s="2"/>
       <c r="B779" s="2"/>
       <c r="C779" s="2"/>
-      <c r="D779" s="50"/>
+      <c r="D779" s="49"/>
       <c r="E779" s="2"/>
       <c r="F779" s="2"/>
       <c r="G779" s="2"/>
@@ -24514,7 +24539,7 @@
       <c r="A780" s="2"/>
       <c r="B780" s="2"/>
       <c r="C780" s="2"/>
-      <c r="D780" s="50"/>
+      <c r="D780" s="49"/>
       <c r="E780" s="2"/>
       <c r="F780" s="2"/>
       <c r="G780" s="2"/>
@@ -24542,7 +24567,7 @@
       <c r="A781" s="2"/>
       <c r="B781" s="2"/>
       <c r="C781" s="2"/>
-      <c r="D781" s="50"/>
+      <c r="D781" s="49"/>
       <c r="E781" s="2"/>
       <c r="F781" s="2"/>
       <c r="G781" s="2"/>
@@ -24570,7 +24595,7 @@
       <c r="A782" s="2"/>
       <c r="B782" s="2"/>
       <c r="C782" s="2"/>
-      <c r="D782" s="50"/>
+      <c r="D782" s="49"/>
       <c r="E782" s="2"/>
       <c r="F782" s="2"/>
       <c r="G782" s="2"/>
@@ -24598,7 +24623,7 @@
       <c r="A783" s="2"/>
       <c r="B783" s="2"/>
       <c r="C783" s="2"/>
-      <c r="D783" s="50"/>
+      <c r="D783" s="49"/>
       <c r="E783" s="2"/>
       <c r="F783" s="2"/>
       <c r="G783" s="2"/>
@@ -24626,7 +24651,7 @@
       <c r="A784" s="2"/>
       <c r="B784" s="2"/>
       <c r="C784" s="2"/>
-      <c r="D784" s="50"/>
+      <c r="D784" s="49"/>
       <c r="E784" s="2"/>
       <c r="F784" s="2"/>
       <c r="G784" s="2"/>
@@ -24654,7 +24679,7 @@
       <c r="A785" s="2"/>
       <c r="B785" s="2"/>
       <c r="C785" s="2"/>
-      <c r="D785" s="50"/>
+      <c r="D785" s="49"/>
       <c r="E785" s="2"/>
       <c r="F785" s="2"/>
       <c r="G785" s="2"/>
@@ -24682,7 +24707,7 @@
       <c r="A786" s="2"/>
       <c r="B786" s="2"/>
       <c r="C786" s="2"/>
-      <c r="D786" s="50"/>
+      <c r="D786" s="49"/>
       <c r="E786" s="2"/>
       <c r="F786" s="2"/>
       <c r="G786" s="2"/>
@@ -24710,7 +24735,7 @@
       <c r="A787" s="2"/>
       <c r="B787" s="2"/>
       <c r="C787" s="2"/>
-      <c r="D787" s="50"/>
+      <c r="D787" s="49"/>
       <c r="E787" s="2"/>
       <c r="F787" s="2"/>
       <c r="G787" s="2"/>
@@ -24738,7 +24763,7 @@
       <c r="A788" s="2"/>
       <c r="B788" s="2"/>
       <c r="C788" s="2"/>
-      <c r="D788" s="50"/>
+      <c r="D788" s="49"/>
       <c r="E788" s="2"/>
       <c r="F788" s="2"/>
       <c r="G788" s="2"/>
@@ -24766,7 +24791,7 @@
       <c r="A789" s="2"/>
       <c r="B789" s="2"/>
       <c r="C789" s="2"/>
-      <c r="D789" s="50"/>
+      <c r="D789" s="49"/>
       <c r="E789" s="2"/>
       <c r="F789" s="2"/>
       <c r="G789" s="2"/>
@@ -24794,7 +24819,7 @@
       <c r="A790" s="2"/>
       <c r="B790" s="2"/>
       <c r="C790" s="2"/>
-      <c r="D790" s="50"/>
+      <c r="D790" s="49"/>
       <c r="E790" s="2"/>
       <c r="F790" s="2"/>
       <c r="G790" s="2"/>
@@ -24822,7 +24847,7 @@
       <c r="A791" s="2"/>
       <c r="B791" s="2"/>
       <c r="C791" s="2"/>
-      <c r="D791" s="50"/>
+      <c r="D791" s="49"/>
       <c r="E791" s="2"/>
       <c r="F791" s="2"/>
       <c r="G791" s="2"/>
@@ -24850,7 +24875,7 @@
       <c r="A792" s="2"/>
       <c r="B792" s="2"/>
       <c r="C792" s="2"/>
-      <c r="D792" s="50"/>
+      <c r="D792" s="49"/>
       <c r="E792" s="2"/>
       <c r="F792" s="2"/>
       <c r="G792" s="2"/>
@@ -24878,7 +24903,7 @@
       <c r="A793" s="2"/>
       <c r="B793" s="2"/>
       <c r="C793" s="2"/>
-      <c r="D793" s="50"/>
+      <c r="D793" s="49"/>
       <c r="E793" s="2"/>
       <c r="F793" s="2"/>
       <c r="G793" s="2"/>
@@ -24906,7 +24931,7 @@
       <c r="A794" s="2"/>
       <c r="B794" s="2"/>
       <c r="C794" s="2"/>
-      <c r="D794" s="50"/>
+      <c r="D794" s="49"/>
       <c r="E794" s="2"/>
       <c r="F794" s="2"/>
       <c r="G794" s="2"/>
@@ -24934,7 +24959,7 @@
       <c r="A795" s="2"/>
       <c r="B795" s="2"/>
       <c r="C795" s="2"/>
-      <c r="D795" s="50"/>
+      <c r="D795" s="49"/>
       <c r="E795" s="2"/>
       <c r="F795" s="2"/>
       <c r="G795" s="2"/>
@@ -24962,7 +24987,7 @@
       <c r="A796" s="2"/>
       <c r="B796" s="2"/>
       <c r="C796" s="2"/>
-      <c r="D796" s="50"/>
+      <c r="D796" s="49"/>
       <c r="E796" s="2"/>
       <c r="F796" s="2"/>
       <c r="G796" s="2"/>
@@ -24990,7 +25015,7 @@
       <c r="A797" s="2"/>
       <c r="B797" s="2"/>
       <c r="C797" s="2"/>
-      <c r="D797" s="50"/>
+      <c r="D797" s="49"/>
       <c r="E797" s="2"/>
       <c r="F797" s="2"/>
       <c r="G797" s="2"/>
@@ -25018,7 +25043,7 @@
       <c r="A798" s="2"/>
       <c r="B798" s="2"/>
       <c r="C798" s="2"/>
-      <c r="D798" s="50"/>
+      <c r="D798" s="49"/>
       <c r="E798" s="2"/>
       <c r="F798" s="2"/>
       <c r="G798" s="2"/>
@@ -25046,7 +25071,7 @@
       <c r="A799" s="2"/>
       <c r="B799" s="2"/>
       <c r="C799" s="2"/>
-      <c r="D799" s="50"/>
+      <c r="D799" s="49"/>
       <c r="E799" s="2"/>
       <c r="F799" s="2"/>
       <c r="G799" s="2"/>
@@ -25074,7 +25099,7 @@
       <c r="A800" s="2"/>
       <c r="B800" s="2"/>
       <c r="C800" s="2"/>
-      <c r="D800" s="50"/>
+      <c r="D800" s="49"/>
       <c r="E800" s="2"/>
       <c r="F800" s="2"/>
       <c r="G800" s="2"/>
@@ -25102,7 +25127,7 @@
       <c r="A801" s="2"/>
       <c r="B801" s="2"/>
       <c r="C801" s="2"/>
-      <c r="D801" s="50"/>
+      <c r="D801" s="49"/>
       <c r="E801" s="2"/>
       <c r="F801" s="2"/>
       <c r="G801" s="2"/>
@@ -25130,7 +25155,7 @@
       <c r="A802" s="2"/>
       <c r="B802" s="2"/>
       <c r="C802" s="2"/>
-      <c r="D802" s="50"/>
+      <c r="D802" s="49"/>
       <c r="E802" s="2"/>
       <c r="F802" s="2"/>
       <c r="G802" s="2"/>
@@ -25158,7 +25183,7 @@
       <c r="A803" s="2"/>
       <c r="B803" s="2"/>
       <c r="C803" s="2"/>
-      <c r="D803" s="50"/>
+      <c r="D803" s="49"/>
       <c r="E803" s="2"/>
       <c r="F803" s="2"/>
       <c r="G803" s="2"/>
@@ -25186,7 +25211,7 @@
       <c r="A804" s="2"/>
       <c r="B804" s="2"/>
       <c r="C804" s="2"/>
-      <c r="D804" s="50"/>
+      <c r="D804" s="49"/>
       <c r="E804" s="2"/>
       <c r="F804" s="2"/>
       <c r="G804" s="2"/>
@@ -25214,7 +25239,7 @@
       <c r="A805" s="2"/>
       <c r="B805" s="2"/>
       <c r="C805" s="2"/>
-      <c r="D805" s="50"/>
+      <c r="D805" s="49"/>
       <c r="E805" s="2"/>
       <c r="F805" s="2"/>
       <c r="G805" s="2"/>
@@ -25242,7 +25267,7 @@
       <c r="A806" s="2"/>
       <c r="B806" s="2"/>
       <c r="C806" s="2"/>
-      <c r="D806" s="50"/>
+      <c r="D806" s="49"/>
       <c r="E806" s="2"/>
       <c r="F806" s="2"/>
       <c r="G806" s="2"/>
@@ -25270,7 +25295,7 @@
       <c r="A807" s="2"/>
       <c r="B807" s="2"/>
       <c r="C807" s="2"/>
-      <c r="D807" s="50"/>
+      <c r="D807" s="49"/>
       <c r="E807" s="2"/>
       <c r="F807" s="2"/>
       <c r="G807" s="2"/>
@@ -25298,7 +25323,7 @@
       <c r="A808" s="2"/>
       <c r="B808" s="2"/>
       <c r="C808" s="2"/>
-      <c r="D808" s="50"/>
+      <c r="D808" s="49"/>
       <c r="E808" s="2"/>
       <c r="F808" s="2"/>
       <c r="G808" s="2"/>
@@ -25326,7 +25351,7 @@
       <c r="A809" s="2"/>
       <c r="B809" s="2"/>
       <c r="C809" s="2"/>
-      <c r="D809" s="50"/>
+      <c r="D809" s="49"/>
       <c r="E809" s="2"/>
       <c r="F809" s="2"/>
       <c r="G809" s="2"/>
@@ -25354,7 +25379,7 @@
       <c r="A810" s="2"/>
       <c r="B810" s="2"/>
       <c r="C810" s="2"/>
-      <c r="D810" s="50"/>
+      <c r="D810" s="49"/>
       <c r="E810" s="2"/>
       <c r="F810" s="2"/>
       <c r="G810" s="2"/>
@@ -25382,7 +25407,7 @@
       <c r="A811" s="2"/>
       <c r="B811" s="2"/>
       <c r="C811" s="2"/>
-      <c r="D811" s="50"/>
+      <c r="D811" s="49"/>
       <c r="E811" s="2"/>
       <c r="F811" s="2"/>
       <c r="G811" s="2"/>
@@ -25410,7 +25435,7 @@
       <c r="A812" s="2"/>
       <c r="B812" s="2"/>
       <c r="C812" s="2"/>
-      <c r="D812" s="50"/>
+      <c r="D812" s="49"/>
       <c r="E812" s="2"/>
       <c r="F812" s="2"/>
       <c r="G812" s="2"/>
@@ -25438,7 +25463,7 @@
       <c r="A813" s="2"/>
       <c r="B813" s="2"/>
       <c r="C813" s="2"/>
-      <c r="D813" s="50"/>
+      <c r="D813" s="49"/>
       <c r="E813" s="2"/>
       <c r="F813" s="2"/>
       <c r="G813" s="2"/>
@@ -25466,7 +25491,7 @@
       <c r="A814" s="2"/>
       <c r="B814" s="2"/>
       <c r="C814" s="2"/>
-      <c r="D814" s="50"/>
+      <c r="D814" s="49"/>
       <c r="E814" s="2"/>
       <c r="F814" s="2"/>
       <c r="G814" s="2"/>
@@ -25494,7 +25519,7 @@
       <c r="A815" s="2"/>
       <c r="B815" s="2"/>
       <c r="C815" s="2"/>
-      <c r="D815" s="50"/>
+      <c r="D815" s="49"/>
       <c r="E815" s="2"/>
       <c r="F815" s="2"/>
       <c r="G815" s="2"/>
@@ -25522,7 +25547,7 @@
       <c r="A816" s="2"/>
       <c r="B816" s="2"/>
       <c r="C816" s="2"/>
-      <c r="D816" s="50"/>
+      <c r="D816" s="49"/>
       <c r="E816" s="2"/>
       <c r="F816" s="2"/>
       <c r="G816" s="2"/>
@@ -25550,7 +25575,7 @@
       <c r="A817" s="2"/>
       <c r="B817" s="2"/>
       <c r="C817" s="2"/>
-      <c r="D817" s="50"/>
+      <c r="D817" s="49"/>
       <c r="E817" s="2"/>
       <c r="F817" s="2"/>
       <c r="G817" s="2"/>
@@ -25578,7 +25603,7 @@
       <c r="A818" s="2"/>
       <c r="B818" s="2"/>
       <c r="C818" s="2"/>
-      <c r="D818" s="50"/>
+      <c r="D818" s="49"/>
       <c r="E818" s="2"/>
       <c r="F818" s="2"/>
       <c r="G818" s="2"/>
@@ -25606,7 +25631,7 @@
       <c r="A819" s="2"/>
       <c r="B819" s="2"/>
       <c r="C819" s="2"/>
-      <c r="D819" s="50"/>
+      <c r="D819" s="49"/>
       <c r="E819" s="2"/>
       <c r="F819" s="2"/>
       <c r="G819" s="2"/>
@@ -25634,7 +25659,7 @@
       <c r="A820" s="2"/>
       <c r="B820" s="2"/>
       <c r="C820" s="2"/>
-      <c r="D820" s="50"/>
+      <c r="D820" s="49"/>
       <c r="E820" s="2"/>
       <c r="F820" s="2"/>
       <c r="G820" s="2"/>
@@ -25662,7 +25687,7 @@
       <c r="A821" s="2"/>
       <c r="B821" s="2"/>
       <c r="C821" s="2"/>
-      <c r="D821" s="50"/>
+      <c r="D821" s="49"/>
       <c r="E821" s="2"/>
       <c r="F821" s="2"/>
       <c r="G821" s="2"/>
@@ -25690,7 +25715,7 @@
       <c r="A822" s="2"/>
       <c r="B822" s="2"/>
       <c r="C822" s="2"/>
-      <c r="D822" s="50"/>
+      <c r="D822" s="49"/>
       <c r="E822" s="2"/>
       <c r="F822" s="2"/>
       <c r="G822" s="2"/>
@@ -25718,7 +25743,7 @@
       <c r="A823" s="2"/>
       <c r="B823" s="2"/>
       <c r="C823" s="2"/>
-      <c r="D823" s="50"/>
+      <c r="D823" s="49"/>
       <c r="E823" s="2"/>
       <c r="F823" s="2"/>
       <c r="G823" s="2"/>
@@ -25746,7 +25771,7 @@
       <c r="A824" s="2"/>
       <c r="B824" s="2"/>
       <c r="C824" s="2"/>
-      <c r="D824" s="50"/>
+      <c r="D824" s="49"/>
       <c r="E824" s="2"/>
       <c r="F824" s="2"/>
       <c r="G824" s="2"/>
@@ -25774,7 +25799,7 @@
       <c r="A825" s="2"/>
       <c r="B825" s="2"/>
       <c r="C825" s="2"/>
-      <c r="D825" s="50"/>
+      <c r="D825" s="49"/>
       <c r="E825" s="2"/>
       <c r="F825" s="2"/>
       <c r="G825" s="2"/>
@@ -25802,7 +25827,7 @@
       <c r="A826" s="2"/>
       <c r="B826" s="2"/>
       <c r="C826" s="2"/>
-      <c r="D826" s="50"/>
+      <c r="D826" s="49"/>
       <c r="E826" s="2"/>
       <c r="F826" s="2"/>
       <c r="G826" s="2"/>
@@ -25830,7 +25855,7 @@
       <c r="A827" s="2"/>
       <c r="B827" s="2"/>
       <c r="C827" s="2"/>
-      <c r="D827" s="50"/>
+      <c r="D827" s="49"/>
       <c r="E827" s="2"/>
       <c r="F827" s="2"/>
       <c r="G827" s="2"/>
@@ -25858,7 +25883,7 @@
       <c r="A828" s="2"/>
       <c r="B828" s="2"/>
       <c r="C828" s="2"/>
-      <c r="D828" s="50"/>
+      <c r="D828" s="49"/>
       <c r="E828" s="2"/>
       <c r="F828" s="2"/>
       <c r="G828" s="2"/>
@@ -25886,7 +25911,7 @@
       <c r="A829" s="2"/>
       <c r="B829" s="2"/>
       <c r="C829" s="2"/>
-      <c r="D829" s="50"/>
+      <c r="D829" s="49"/>
       <c r="E829" s="2"/>
       <c r="F829" s="2"/>
       <c r="G829" s="2"/>
@@ -25914,7 +25939,7 @@
       <c r="A830" s="2"/>
       <c r="B830" s="2"/>
       <c r="C830" s="2"/>
-      <c r="D830" s="50"/>
+      <c r="D830" s="49"/>
       <c r="E830" s="2"/>
       <c r="F830" s="2"/>
       <c r="G830" s="2"/>
@@ -25942,7 +25967,7 @@
       <c r="A831" s="2"/>
       <c r="B831" s="2"/>
       <c r="C831" s="2"/>
-      <c r="D831" s="50"/>
+      <c r="D831" s="49"/>
       <c r="E831" s="2"/>
       <c r="F831" s="2"/>
       <c r="G831" s="2"/>
@@ -25970,7 +25995,7 @@
       <c r="A832" s="2"/>
       <c r="B832" s="2"/>
       <c r="C832" s="2"/>
-      <c r="D832" s="50"/>
+      <c r="D832" s="49"/>
       <c r="E832" s="2"/>
       <c r="F832" s="2"/>
       <c r="G832" s="2"/>
@@ -25998,7 +26023,7 @@
       <c r="A833" s="2"/>
       <c r="B833" s="2"/>
       <c r="C833" s="2"/>
-      <c r="D833" s="50"/>
+      <c r="D833" s="49"/>
       <c r="E833" s="2"/>
       <c r="F833" s="2"/>
       <c r="G833" s="2"/>
@@ -26026,7 +26051,7 @@
       <c r="A834" s="2"/>
       <c r="B834" s="2"/>
       <c r="C834" s="2"/>
-      <c r="D834" s="50"/>
+      <c r="D834" s="49"/>
       <c r="E834" s="2"/>
       <c r="F834" s="2"/>
       <c r="G834" s="2"/>
@@ -26054,7 +26079,7 @@
       <c r="A835" s="2"/>
       <c r="B835" s="2"/>
       <c r="C835" s="2"/>
-      <c r="D835" s="50"/>
+      <c r="D835" s="49"/>
       <c r="E835" s="2"/>
       <c r="F835" s="2"/>
       <c r="G835" s="2"/>
@@ -26082,7 +26107,7 @@
       <c r="A836" s="2"/>
       <c r="B836" s="2"/>
       <c r="C836" s="2"/>
-      <c r="D836" s="50"/>
+      <c r="D836" s="49"/>
       <c r="E836" s="2"/>
       <c r="F836" s="2"/>
       <c r="G836" s="2"/>
@@ -26110,7 +26135,7 @@
       <c r="A837" s="2"/>
       <c r="B837" s="2"/>
       <c r="C837" s="2"/>
-      <c r="D837" s="50"/>
+      <c r="D837" s="49"/>
       <c r="E837" s="2"/>
       <c r="F837" s="2"/>
       <c r="G837" s="2"/>
@@ -26138,7 +26163,7 @@
       <c r="A838" s="2"/>
       <c r="B838" s="2"/>
       <c r="C838" s="2"/>
-      <c r="D838" s="50"/>
+      <c r="D838" s="49"/>
       <c r="E838" s="2"/>
       <c r="F838" s="2"/>
       <c r="G838" s="2"/>
@@ -26166,7 +26191,7 @@
       <c r="A839" s="2"/>
       <c r="B839" s="2"/>
       <c r="C839" s="2"/>
-      <c r="D839" s="50"/>
+      <c r="D839" s="49"/>
       <c r="E839" s="2"/>
       <c r="F839" s="2"/>
       <c r="G839" s="2"/>
@@ -26194,7 +26219,7 @@
       <c r="A840" s="2"/>
       <c r="B840" s="2"/>
       <c r="C840" s="2"/>
-      <c r="D840" s="50"/>
+      <c r="D840" s="49"/>
       <c r="E840" s="2"/>
       <c r="F840" s="2"/>
       <c r="G840" s="2"/>
@@ -26222,7 +26247,7 @@
       <c r="A841" s="2"/>
       <c r="B841" s="2"/>
       <c r="C841" s="2"/>
-      <c r="D841" s="50"/>
+      <c r="D841" s="49"/>
       <c r="E841" s="2"/>
       <c r="F841" s="2"/>
       <c r="G841" s="2"/>
@@ -26250,7 +26275,7 @@
       <c r="A842" s="2"/>
       <c r="B842" s="2"/>
       <c r="C842" s="2"/>
-      <c r="D842" s="50"/>
+      <c r="D842" s="49"/>
       <c r="E842" s="2"/>
       <c r="F842" s="2"/>
       <c r="G842" s="2"/>
@@ -26278,7 +26303,7 @@
       <c r="A843" s="2"/>
       <c r="B843" s="2"/>
       <c r="C843" s="2"/>
-      <c r="D843" s="50"/>
+      <c r="D843" s="49"/>
       <c r="E843" s="2"/>
       <c r="F843" s="2"/>
       <c r="G843" s="2"/>
@@ -26306,7 +26331,7 @@
       <c r="A844" s="2"/>
       <c r="B844" s="2"/>
       <c r="C844" s="2"/>
-      <c r="D844" s="50"/>
+      <c r="D844" s="49"/>
       <c r="E844" s="2"/>
       <c r="F844" s="2"/>
       <c r="G844" s="2"/>
@@ -26334,7 +26359,7 @@
       <c r="A845" s="2"/>
       <c r="B845" s="2"/>
       <c r="C845" s="2"/>
-      <c r="D845" s="50"/>
+      <c r="D845" s="49"/>
       <c r="E845" s="2"/>
       <c r="F845" s="2"/>
       <c r="G845" s="2"/>
@@ -26362,7 +26387,7 @@
       <c r="A846" s="2"/>
       <c r="B846" s="2"/>
       <c r="C846" s="2"/>
-      <c r="D846" s="50"/>
+      <c r="D846" s="49"/>
       <c r="E846" s="2"/>
       <c r="F846" s="2"/>
       <c r="G846" s="2"/>
@@ -26390,7 +26415,7 @@
       <c r="A847" s="2"/>
       <c r="B847" s="2"/>
       <c r="C847" s="2"/>
-      <c r="D847" s="50"/>
+      <c r="D847" s="49"/>
       <c r="E847" s="2"/>
       <c r="F847" s="2"/>
       <c r="G847" s="2"/>
@@ -26418,7 +26443,7 @@
       <c r="A848" s="2"/>
       <c r="B848" s="2"/>
       <c r="C848" s="2"/>
-      <c r="D848" s="50"/>
+      <c r="D848" s="49"/>
       <c r="E848" s="2"/>
       <c r="F848" s="2"/>
       <c r="G848" s="2"/>
@@ -26446,7 +26471,7 @@
       <c r="A849" s="2"/>
       <c r="B849" s="2"/>
       <c r="C849" s="2"/>
-      <c r="D849" s="50"/>
+      <c r="D849" s="49"/>
       <c r="E849" s="2"/>
       <c r="F849" s="2"/>
       <c r="G849" s="2"/>
@@ -26474,7 +26499,7 @@
       <c r="A850" s="2"/>
       <c r="B850" s="2"/>
       <c r="C850" s="2"/>
-      <c r="D850" s="50"/>
+      <c r="D850" s="49"/>
       <c r="E850" s="2"/>
       <c r="F850" s="2"/>
       <c r="G850" s="2"/>
@@ -26502,7 +26527,7 @@
       <c r="A851" s="2"/>
       <c r="B851" s="2"/>
       <c r="C851" s="2"/>
-      <c r="D851" s="50"/>
+      <c r="D851" s="49"/>
       <c r="E851" s="2"/>
       <c r="F851" s="2"/>
       <c r="G851" s="2"/>
@@ -26530,7 +26555,7 @@
       <c r="A852" s="2"/>
       <c r="B852" s="2"/>
       <c r="C852" s="2"/>
-      <c r="D852" s="50"/>
+      <c r="D852" s="49"/>
       <c r="E852" s="2"/>
       <c r="F852" s="2"/>
       <c r="G852" s="2"/>
@@ -26558,7 +26583,7 @@
       <c r="A853" s="2"/>
       <c r="B853" s="2"/>
       <c r="C853" s="2"/>
-      <c r="D853" s="50"/>
+      <c r="D853" s="49"/>
       <c r="E853" s="2"/>
       <c r="F853" s="2"/>
       <c r="G853" s="2"/>
@@ -26586,7 +26611,7 @@
       <c r="A854" s="2"/>
       <c r="B854" s="2"/>
       <c r="C854" s="2"/>
-      <c r="D854" s="50"/>
+      <c r="D854" s="49"/>
       <c r="E854" s="2"/>
       <c r="F854" s="2"/>
       <c r="G854" s="2"/>
@@ -26614,7 +26639,7 @@
       <c r="A855" s="2"/>
       <c r="B855" s="2"/>
       <c r="C855" s="2"/>
-      <c r="D855" s="50"/>
+      <c r="D855" s="49"/>
       <c r="E855" s="2"/>
       <c r="F855" s="2"/>
       <c r="G855" s="2"/>
@@ -26642,7 +26667,7 @@
       <c r="A856" s="2"/>
       <c r="B856" s="2"/>
       <c r="C856" s="2"/>
-      <c r="D856" s="50"/>
+      <c r="D856" s="49"/>
       <c r="E856" s="2"/>
       <c r="F856" s="2"/>
       <c r="G856" s="2"/>
@@ -26670,7 +26695,7 @@
       <c r="A857" s="2"/>
       <c r="B857" s="2"/>
       <c r="C857" s="2"/>
-      <c r="D857" s="50"/>
+      <c r="D857" s="49"/>
       <c r="E857" s="2"/>
       <c r="F857" s="2"/>
       <c r="G857" s="2"/>
@@ -26698,7 +26723,7 @@
       <c r="A858" s="2"/>
       <c r="B858" s="2"/>
       <c r="C858" s="2"/>
-      <c r="D858" s="50"/>
+      <c r="D858" s="49"/>
       <c r="E858" s="2"/>
       <c r="F858" s="2"/>
       <c r="G858" s="2"/>
@@ -26726,7 +26751,7 @@
       <c r="A859" s="2"/>
       <c r="B859" s="2"/>
       <c r="C859" s="2"/>
-      <c r="D859" s="50"/>
+      <c r="D859" s="49"/>
       <c r="E859" s="2"/>
       <c r="F859" s="2"/>
       <c r="G859" s="2"/>
@@ -26754,7 +26779,7 @@
       <c r="A860" s="2"/>
       <c r="B860" s="2"/>
       <c r="C860" s="2"/>
-      <c r="D860" s="50"/>
+      <c r="D860" s="49"/>
       <c r="E860" s="2"/>
       <c r="F860" s="2"/>
       <c r="G860" s="2"/>
@@ -26782,7 +26807,7 @@
       <c r="A861" s="2"/>
       <c r="B861" s="2"/>
       <c r="C861" s="2"/>
-      <c r="D861" s="50"/>
+      <c r="D861" s="49"/>
       <c r="E861" s="2"/>
       <c r="F861" s="2"/>
       <c r="G861" s="2"/>
@@ -26810,7 +26835,7 @@
       <c r="A862" s="2"/>
       <c r="B862" s="2"/>
       <c r="C862" s="2"/>
-      <c r="D862" s="50"/>
+      <c r="D862" s="49"/>
       <c r="E862" s="2"/>
       <c r="F862" s="2"/>
       <c r="G862" s="2"/>
@@ -26838,7 +26863,7 @@
       <c r="A863" s="2"/>
       <c r="B863" s="2"/>
       <c r="C863" s="2"/>
-      <c r="D863" s="50"/>
+      <c r="D863" s="49"/>
       <c r="E863" s="2"/>
       <c r="F863" s="2"/>
       <c r="G863" s="2"/>
@@ -26866,7 +26891,7 @@
       <c r="A864" s="2"/>
       <c r="B864" s="2"/>
       <c r="C864" s="2"/>
-      <c r="D864" s="50"/>
+      <c r="D864" s="49"/>
       <c r="E864" s="2"/>
       <c r="F864" s="2"/>
       <c r="G864" s="2"/>
@@ -26894,7 +26919,7 @@
       <c r="A865" s="2"/>
       <c r="B865" s="2"/>
       <c r="C865" s="2"/>
-      <c r="D865" s="50"/>
+      <c r="D865" s="49"/>
       <c r="E865" s="2"/>
       <c r="F865" s="2"/>
       <c r="G865" s="2"/>
@@ -26922,7 +26947,7 @@
       <c r="A866" s="2"/>
       <c r="B866" s="2"/>
       <c r="C866" s="2"/>
-      <c r="D866" s="50"/>
+      <c r="D866" s="49"/>
       <c r="E866" s="2"/>
       <c r="F866" s="2"/>
       <c r="G866" s="2"/>
@@ -26950,7 +26975,7 @@
       <c r="A867" s="2"/>
       <c r="B867" s="2"/>
       <c r="C867" s="2"/>
-      <c r="D867" s="50"/>
+      <c r="D867" s="49"/>
       <c r="E867" s="2"/>
       <c r="F867" s="2"/>
       <c r="G867" s="2"/>
@@ -26978,7 +27003,7 @@
       <c r="A868" s="2"/>
       <c r="B868" s="2"/>
       <c r="C868" s="2"/>
-      <c r="D868" s="50"/>
+      <c r="D868" s="49"/>
       <c r="E868" s="2"/>
       <c r="F868" s="2"/>
       <c r="G868" s="2"/>
@@ -27006,7 +27031,7 @@
       <c r="A869" s="2"/>
       <c r="B869" s="2"/>
       <c r="C869" s="2"/>
-      <c r="D869" s="50"/>
+      <c r="D869" s="49"/>
       <c r="E869" s="2"/>
       <c r="F869" s="2"/>
       <c r="G869" s="2"/>
@@ -27034,7 +27059,7 @@
       <c r="A870" s="2"/>
       <c r="B870" s="2"/>
       <c r="C870" s="2"/>
-      <c r="D870" s="50"/>
+      <c r="D870" s="49"/>
       <c r="E870" s="2"/>
       <c r="F870" s="2"/>
       <c r="G870" s="2"/>
@@ -27062,7 +27087,7 @@
       <c r="A871" s="2"/>
       <c r="B871" s="2"/>
       <c r="C871" s="2"/>
-      <c r="D871" s="50"/>
+      <c r="D871" s="49"/>
       <c r="E871" s="2"/>
       <c r="F871" s="2"/>
       <c r="G871" s="2"/>
@@ -27090,7 +27115,7 @@
       <c r="A872" s="2"/>
       <c r="B872" s="2"/>
       <c r="C872" s="2"/>
-      <c r="D872" s="50"/>
+      <c r="D872" s="49"/>
       <c r="E872" s="2"/>
       <c r="F872" s="2"/>
       <c r="G872" s="2"/>
@@ -27118,7 +27143,7 @@
       <c r="A873" s="2"/>
       <c r="B873" s="2"/>
       <c r="C873" s="2"/>
-      <c r="D873" s="50"/>
+      <c r="D873" s="49"/>
       <c r="E873" s="2"/>
       <c r="F873" s="2"/>
       <c r="G873" s="2"/>
@@ -27146,7 +27171,7 @@
       <c r="A874" s="2"/>
       <c r="B874" s="2"/>
       <c r="C874" s="2"/>
-      <c r="D874" s="50"/>
+      <c r="D874" s="49"/>
       <c r="E874" s="2"/>
       <c r="F874" s="2"/>
       <c r="G874" s="2"/>
@@ -27174,7 +27199,7 @@
       <c r="A875" s="2"/>
       <c r="B875" s="2"/>
       <c r="C875" s="2"/>
-      <c r="D875" s="50"/>
+      <c r="D875" s="49"/>
       <c r="E875" s="2"/>
       <c r="F875" s="2"/>
       <c r="G875" s="2"/>
@@ -27202,7 +27227,7 @@
       <c r="A876" s="2"/>
       <c r="B876" s="2"/>
       <c r="C876" s="2"/>
-      <c r="D876" s="50"/>
+      <c r="D876" s="49"/>
       <c r="E876" s="2"/>
       <c r="F876" s="2"/>
       <c r="G876" s="2"/>
@@ -27230,7 +27255,7 @@
       <c r="A877" s="2"/>
       <c r="B877" s="2"/>
       <c r="C877" s="2"/>
-      <c r="D877" s="50"/>
+      <c r="D877" s="49"/>
       <c r="E877" s="2"/>
       <c r="F877" s="2"/>
       <c r="G877" s="2"/>
@@ -27258,7 +27283,7 @@
       <c r="A878" s="2"/>
       <c r="B878" s="2"/>
       <c r="C878" s="2"/>
-      <c r="D878" s="50"/>
+      <c r="D878" s="49"/>
       <c r="E878" s="2"/>
       <c r="F878" s="2"/>
       <c r="G878" s="2"/>
@@ -27286,7 +27311,7 @@
       <c r="A879" s="2"/>
       <c r="B879" s="2"/>
       <c r="C879" s="2"/>
-      <c r="D879" s="50"/>
+      <c r="D879" s="49"/>
       <c r="E879" s="2"/>
       <c r="F879" s="2"/>
       <c r="G879" s="2"/>
@@ -27314,7 +27339,7 @@
       <c r="A880" s="2"/>
       <c r="B880" s="2"/>
       <c r="C880" s="2"/>
-      <c r="D880" s="50"/>
+      <c r="D880" s="49"/>
       <c r="E880" s="2"/>
       <c r="F880" s="2"/>
       <c r="G880" s="2"/>
@@ -27342,7 +27367,7 @@
       <c r="A881" s="2"/>
       <c r="B881" s="2"/>
       <c r="C881" s="2"/>
-      <c r="D881" s="50"/>
+      <c r="D881" s="49"/>
       <c r="E881" s="2"/>
       <c r="F881" s="2"/>
       <c r="G881" s="2"/>
@@ -27370,7 +27395,7 @@
       <c r="A882" s="2"/>
       <c r="B882" s="2"/>
       <c r="C882" s="2"/>
-      <c r="D882" s="50"/>
+      <c r="D882" s="49"/>
       <c r="E882" s="2"/>
       <c r="F882" s="2"/>
       <c r="G882" s="2"/>
@@ -27398,7 +27423,7 @@
       <c r="A883" s="2"/>
       <c r="B883" s="2"/>
       <c r="C883" s="2"/>
-      <c r="D883" s="50"/>
+      <c r="D883" s="49"/>
       <c r="E883" s="2"/>
       <c r="F883" s="2"/>
       <c r="G883" s="2"/>
@@ -27426,7 +27451,7 @@
       <c r="A884" s="2"/>
       <c r="B884" s="2"/>
       <c r="C884" s="2"/>
-      <c r="D884" s="50"/>
+      <c r="D884" s="49"/>
       <c r="E884" s="2"/>
       <c r="F884" s="2"/>
       <c r="G884" s="2"/>
@@ -27454,7 +27479,7 @@
       <c r="A885" s="2"/>
       <c r="B885" s="2"/>
       <c r="C885" s="2"/>
-      <c r="D885" s="50"/>
+      <c r="D885" s="49"/>
       <c r="E885" s="2"/>
       <c r="F885" s="2"/>
       <c r="G885" s="2"/>
@@ -27482,7 +27507,7 @@
       <c r="A886" s="2"/>
       <c r="B886" s="2"/>
       <c r="C886" s="2"/>
-      <c r="D886" s="50"/>
+      <c r="D886" s="49"/>
       <c r="E886" s="2"/>
       <c r="F886" s="2"/>
       <c r="G886" s="2"/>
@@ -27510,7 +27535,7 @@
       <c r="A887" s="2"/>
       <c r="B887" s="2"/>
       <c r="C887" s="2"/>
-      <c r="D887" s="50"/>
+      <c r="D887" s="49"/>
       <c r="E887" s="2"/>
       <c r="F887" s="2"/>
       <c r="G887" s="2"/>
@@ -27538,7 +27563,7 @@
       <c r="A888" s="2"/>
       <c r="B888" s="2"/>
       <c r="C888" s="2"/>
-      <c r="D888" s="50"/>
+      <c r="D888" s="49"/>
       <c r="E888" s="2"/>
       <c r="F888" s="2"/>
       <c r="G888" s="2"/>
@@ -27566,7 +27591,7 @@
       <c r="A889" s="2"/>
       <c r="B889" s="2"/>
       <c r="C889" s="2"/>
-      <c r="D889" s="50"/>
+      <c r="D889" s="49"/>
       <c r="E889" s="2"/>
       <c r="F889" s="2"/>
       <c r="G889" s="2"/>
@@ -27594,7 +27619,7 @@
       <c r="A890" s="2"/>
       <c r="B890" s="2"/>
       <c r="C890" s="2"/>
-      <c r="D890" s="50"/>
+      <c r="D890" s="49"/>
       <c r="E890" s="2"/>
       <c r="F890" s="2"/>
       <c r="G890" s="2"/>
@@ -27622,7 +27647,7 @@
       <c r="A891" s="2"/>
       <c r="B891" s="2"/>
       <c r="C891" s="2"/>
-      <c r="D891" s="50"/>
+      <c r="D891" s="49"/>
       <c r="E891" s="2"/>
       <c r="F891" s="2"/>
       <c r="G891" s="2"/>
@@ -27650,7 +27675,7 @@
       <c r="A892" s="2"/>
       <c r="B892" s="2"/>
       <c r="C892" s="2"/>
-      <c r="D892" s="50"/>
+      <c r="D892" s="49"/>
       <c r="E892" s="2"/>
       <c r="F892" s="2"/>
       <c r="G892" s="2"/>
@@ -27678,7 +27703,7 @@
       <c r="A893" s="2"/>
       <c r="B893" s="2"/>
       <c r="C893" s="2"/>
-      <c r="D893" s="50"/>
+      <c r="D893" s="49"/>
       <c r="E893" s="2"/>
       <c r="F893" s="2"/>
       <c r="G893" s="2"/>
@@ -27706,7 +27731,7 @@
       <c r="A894" s="2"/>
       <c r="B894" s="2"/>
       <c r="C894" s="2"/>
-      <c r="D894" s="50"/>
+      <c r="D894" s="49"/>
       <c r="E894" s="2"/>
       <c r="F894" s="2"/>
       <c r="G894" s="2"/>
@@ -27734,7 +27759,7 @@
       <c r="A895" s="2"/>
       <c r="B895" s="2"/>
       <c r="C895" s="2"/>
-      <c r="D895" s="50"/>
+      <c r="D895" s="49"/>
       <c r="E895" s="2"/>
       <c r="F895" s="2"/>
       <c r="G895" s="2"/>
@@ -27762,7 +27787,7 @@
       <c r="A896" s="2"/>
       <c r="B896" s="2"/>
       <c r="C896" s="2"/>
-      <c r="D896" s="50"/>
+      <c r="D896" s="49"/>
       <c r="E896" s="2"/>
       <c r="F896" s="2"/>
       <c r="G896" s="2"/>
@@ -27790,7 +27815,7 @@
       <c r="A897" s="2"/>
       <c r="B897" s="2"/>
       <c r="C897" s="2"/>
-      <c r="D897" s="50"/>
+      <c r="D897" s="49"/>
       <c r="E897" s="2"/>
       <c r="F897" s="2"/>
       <c r="G897" s="2"/>
@@ -27818,7 +27843,7 @@
       <c r="A898" s="2"/>
       <c r="B898" s="2"/>
       <c r="C898" s="2"/>
-      <c r="D898" s="50"/>
+      <c r="D898" s="49"/>
       <c r="E898" s="2"/>
       <c r="F898" s="2"/>
       <c r="G898" s="2"/>
@@ -27846,7 +27871,7 @@
       <c r="A899" s="2"/>
       <c r="B899" s="2"/>
       <c r="C899" s="2"/>
-      <c r="D899" s="50"/>
+      <c r="D899" s="49"/>
       <c r="E899" s="2"/>
       <c r="F899" s="2"/>
       <c r="G899" s="2"/>
@@ -27874,7 +27899,7 @@
       <c r="A900" s="2"/>
       <c r="B900" s="2"/>
       <c r="C900" s="2"/>
-      <c r="D900" s="50"/>
+      <c r="D900" s="49"/>
       <c r="E900" s="2"/>
       <c r="F900" s="2"/>
       <c r="G900" s="2"/>
@@ -27902,7 +27927,7 @@
       <c r="A901" s="2"/>
       <c r="B901" s="2"/>
       <c r="C901" s="2"/>
-      <c r="D901" s="50"/>
+      <c r="D901" s="49"/>
       <c r="E901" s="2"/>
       <c r="F901" s="2"/>
       <c r="G901" s="2"/>
@@ -27930,7 +27955,7 @@
       <c r="A902" s="2"/>
       <c r="B902" s="2"/>
       <c r="C902" s="2"/>
-      <c r="D902" s="50"/>
+      <c r="D902" s="49"/>
       <c r="E902" s="2"/>
       <c r="F902" s="2"/>
       <c r="G902" s="2"/>
@@ -27958,7 +27983,7 @@
       <c r="A903" s="2"/>
       <c r="B903" s="2"/>
       <c r="C903" s="2"/>
-      <c r="D903" s="50"/>
+      <c r="D903" s="49"/>
       <c r="E903" s="2"/>
       <c r="F903" s="2"/>
       <c r="G903" s="2"/>
@@ -27986,7 +28011,7 @@
       <c r="A904" s="2"/>
       <c r="B904" s="2"/>
       <c r="C904" s="2"/>
-      <c r="D904" s="50"/>
+      <c r="D904" s="49"/>
       <c r="E904" s="2"/>
       <c r="F904" s="2"/>
       <c r="G904" s="2"/>
@@ -28014,7 +28039,7 @@
       <c r="A905" s="2"/>
       <c r="B905" s="2"/>
       <c r="C905" s="2"/>
-      <c r="D905" s="50"/>
+      <c r="D905" s="49"/>
       <c r="E905" s="2"/>
       <c r="F905" s="2"/>
       <c r="G905" s="2"/>
@@ -28042,7 +28067,7 @@
       <c r="A906" s="2"/>
       <c r="B906" s="2"/>
       <c r="C906" s="2"/>
-      <c r="D906" s="50"/>
+      <c r="D906" s="49"/>
       <c r="E906" s="2"/>
       <c r="F906" s="2"/>
       <c r="G906" s="2"/>
@@ -28070,7 +28095,7 @@
       <c r="A907" s="2"/>
       <c r="B907" s="2"/>
       <c r="C907" s="2"/>
-      <c r="D907" s="50"/>
+      <c r="D907" s="49"/>
       <c r="E907" s="2"/>
       <c r="F907" s="2"/>
       <c r="G907" s="2"/>
@@ -28098,7 +28123,7 @@
       <c r="A908" s="2"/>
       <c r="B908" s="2"/>
       <c r="C908" s="2"/>
-      <c r="D908" s="50"/>
+      <c r="D908" s="49"/>
       <c r="E908" s="2"/>
       <c r="F908" s="2"/>
       <c r="G908" s="2"/>
@@ -28126,7 +28151,7 @@
       <c r="A909" s="2"/>
       <c r="B909" s="2"/>
       <c r="C909" s="2"/>
-      <c r="D909" s="50"/>
+      <c r="D909" s="49"/>
       <c r="E909" s="2"/>
       <c r="F909" s="2"/>
       <c r="G909" s="2"/>
@@ -28154,7 +28179,7 @@
       <c r="A910" s="2"/>
       <c r="B910" s="2"/>
       <c r="C910" s="2"/>
-      <c r="D910" s="50"/>
+      <c r="D910" s="49"/>
       <c r="E910" s="2"/>
       <c r="F910" s="2"/>
       <c r="G910" s="2"/>
@@ -28182,7 +28207,7 @@
       <c r="A911" s="2"/>
       <c r="B911" s="2"/>
       <c r="C911" s="2"/>
-      <c r="D911" s="50"/>
+      <c r="D911" s="49"/>
       <c r="E911" s="2"/>
       <c r="F911" s="2"/>
       <c r="G911" s="2"/>
@@ -28210,7 +28235,7 @@
       <c r="A912" s="2"/>
       <c r="B912" s="2"/>
       <c r="C912" s="2"/>
-      <c r="D912" s="50"/>
+      <c r="D912" s="49"/>
       <c r="E912" s="2"/>
       <c r="F912" s="2"/>
       <c r="G912" s="2"/>
@@ -28238,7 +28263,7 @@
       <c r="A913" s="2"/>
       <c r="B913" s="2"/>
       <c r="C913" s="2"/>
-      <c r="D913" s="50"/>
+      <c r="D913" s="49"/>
       <c r="E913" s="2"/>
       <c r="F913" s="2"/>
       <c r="G913" s="2"/>
@@ -28266,7 +28291,7 @@
       <c r="A914" s="2"/>
       <c r="B914" s="2"/>
       <c r="C914" s="2"/>
-      <c r="D914" s="50"/>
+      <c r="D914" s="49"/>
       <c r="E914" s="2"/>
       <c r="F914" s="2"/>
       <c r="G914" s="2"/>
@@ -28294,7 +28319,7 @@
       <c r="A915" s="2"/>
       <c r="B915" s="2"/>
       <c r="C915" s="2"/>
-      <c r="D915" s="50"/>
+      <c r="D915" s="49"/>
       <c r="E915" s="2"/>
       <c r="F915" s="2"/>
       <c r="G915" s="2"/>
@@ -28322,7 +28347,7 @@
       <c r="A916" s="2"/>
       <c r="B916" s="2"/>
       <c r="C916" s="2"/>
-      <c r="D916" s="50"/>
+      <c r="D916" s="49"/>
       <c r="E916" s="2"/>
       <c r="F916" s="2"/>
       <c r="G916" s="2"/>
@@ -28350,7 +28375,7 @@
       <c r="A917" s="2"/>
       <c r="B917" s="2"/>
       <c r="C917" s="2"/>
-      <c r="D917" s="50"/>
+      <c r="D917" s="49"/>
       <c r="E917" s="2"/>
       <c r="F917" s="2"/>
       <c r="G917" s="2"/>
@@ -28378,7 +28403,7 @@
       <c r="A918" s="2"/>
       <c r="B918" s="2"/>
       <c r="C918" s="2"/>
-      <c r="D918" s="50"/>
+      <c r="D918" s="49"/>
       <c r="E918" s="2"/>
       <c r="F918" s="2"/>
       <c r="G918" s="2"/>
@@ -28406,7 +28431,7 @@
       <c r="A919" s="2"/>
       <c r="B919" s="2"/>
       <c r="C919" s="2"/>
-      <c r="D919" s="50"/>
+      <c r="D919" s="49"/>
       <c r="E919" s="2"/>
       <c r="F919" s="2"/>
       <c r="G919" s="2"/>
@@ -28434,7 +28459,7 @@
       <c r="A920" s="2"/>
       <c r="B920" s="2"/>
       <c r="C920" s="2"/>
-      <c r="D920" s="50"/>
+      <c r="D920" s="49"/>
       <c r="E920" s="2"/>
       <c r="F920" s="2"/>
       <c r="G920" s="2"/>
@@ -28462,7 +28487,7 @@
       <c r="A921" s="2"/>
       <c r="B921" s="2"/>
       <c r="C921" s="2"/>
-      <c r="D921" s="50"/>
+      <c r="D921" s="49"/>
       <c r="E921" s="2"/>
       <c r="F921" s="2"/>
       <c r="G921" s="2"/>
@@ -28490,7 +28515,7 @@
       <c r="A922" s="2"/>
       <c r="B922" s="2"/>
       <c r="C922" s="2"/>
-      <c r="D922" s="50"/>
+      <c r="D922" s="49"/>
       <c r="E922" s="2"/>
       <c r="F922" s="2"/>
       <c r="G922" s="2"/>
@@ -28518,7 +28543,7 @@
       <c r="A923" s="2"/>
       <c r="B923" s="2"/>
       <c r="C923" s="2"/>
-      <c r="D923" s="50"/>
+      <c r="D923" s="49"/>
       <c r="E923" s="2"/>
       <c r="F923" s="2"/>
       <c r="G923" s="2"/>
@@ -28546,7 +28571,7 @@
       <c r="A924" s="2"/>
       <c r="B924" s="2"/>
       <c r="C924" s="2"/>
-      <c r="D924" s="50"/>
+      <c r="D924" s="49"/>
       <c r="E924" s="2"/>
       <c r="F924" s="2"/>
       <c r="G924" s="2"/>
@@ -28574,7 +28599,7 @@
       <c r="A925" s="2"/>
       <c r="B925" s="2"/>
       <c r="C925" s="2"/>
-      <c r="D925" s="50"/>
+      <c r="D925" s="49"/>
       <c r="E925" s="2"/>
       <c r="F925" s="2"/>
       <c r="G925" s="2"/>
@@ -28602,7 +28627,7 @@
       <c r="A926" s="2"/>
       <c r="B926" s="2"/>
       <c r="C926" s="2"/>
-      <c r="D926" s="50"/>
+      <c r="D926" s="49"/>
       <c r="E926" s="2"/>
       <c r="F926" s="2"/>
       <c r="G926" s="2"/>
@@ -28630,7 +28655,7 @@
       <c r="A927" s="2"/>
       <c r="B927" s="2"/>
       <c r="C927" s="2"/>
-      <c r="D927" s="50"/>
+      <c r="D927" s="49"/>
       <c r="E927" s="2"/>
       <c r="F927" s="2"/>
       <c r="G927" s="2"/>
@@ -28658,7 +28683,7 @@
       <c r="A928" s="2"/>
       <c r="B928" s="2"/>
       <c r="C928" s="2"/>
-      <c r="D928" s="50"/>
+      <c r="D928" s="49"/>
       <c r="E928" s="2"/>
       <c r="F928" s="2"/>
       <c r="G928" s="2"/>
@@ -28686,7 +28711,7 @@
       <c r="A929" s="2"/>
       <c r="B929" s="2"/>
       <c r="C929" s="2"/>
-      <c r="D929" s="50"/>
+      <c r="D929" s="49"/>
       <c r="E929" s="2"/>
       <c r="F929" s="2"/>
       <c r="G929" s="2"/>
@@ -28714,7 +28739,7 @@
       <c r="A930" s="2"/>
       <c r="B930" s="2"/>
       <c r="C930" s="2"/>
-      <c r="D930" s="50"/>
+      <c r="D930" s="49"/>
       <c r="E930" s="2"/>
       <c r="F930" s="2"/>
       <c r="G930" s="2"/>
@@ -28742,7 +28767,7 @@
       <c r="A931" s="2"/>
       <c r="B931" s="2"/>
       <c r="C931" s="2"/>
-      <c r="D931" s="50"/>
+      <c r="D931" s="49"/>
       <c r="E931" s="2"/>
       <c r="F931" s="2"/>
       <c r="G931" s="2"/>
@@ -28770,7 +28795,7 @@
       <c r="A932" s="2"/>
       <c r="B932" s="2"/>
       <c r="C932" s="2"/>
-      <c r="D932" s="50"/>
+      <c r="D932" s="49"/>
       <c r="E932" s="2"/>
       <c r="F932" s="2"/>
       <c r="G932" s="2"/>
@@ -28798,7 +28823,7 @@
       <c r="A933" s="2"/>
       <c r="B933" s="2"/>
       <c r="C933" s="2"/>
-      <c r="D933" s="50"/>
+      <c r="D933" s="49"/>
       <c r="E933" s="2"/>
       <c r="F933" s="2"/>
       <c r="G933" s="2"/>
@@ -28826,7 +28851,7 @@
       <c r="A934" s="2"/>
       <c r="B934" s="2"/>
       <c r="C934" s="2"/>
-      <c r="D934" s="50"/>
+      <c r="D934" s="49"/>
       <c r="E934" s="2"/>
       <c r="F934" s="2"/>
       <c r="G934" s="2"/>
@@ -28854,7 +28879,7 @@
       <c r="A935" s="2"/>
       <c r="B935" s="2"/>
       <c r="C935" s="2"/>
-      <c r="D935" s="50"/>
+      <c r="D935" s="49"/>
       <c r="E935" s="2"/>
       <c r="F935" s="2"/>
       <c r="G935" s="2"/>
@@ -28882,7 +28907,7 @@
       <c r="A936" s="2"/>
       <c r="B936" s="2"/>
       <c r="C936" s="2"/>
-      <c r="D936" s="50"/>
+      <c r="D936" s="49"/>
       <c r="E936" s="2"/>
       <c r="F936" s="2"/>
       <c r="G936" s="2"/>
@@ -28910,7 +28935,7 @@
       <c r="A937" s="2"/>
       <c r="B937" s="2"/>
       <c r="C937" s="2"/>
-      <c r="D937" s="50"/>
+      <c r="D937" s="49"/>
       <c r="E937" s="2"/>
       <c r="F937" s="2"/>
       <c r="G937" s="2"/>
@@ -28938,7 +28963,7 @@
       <c r="A938" s="2"/>
       <c r="B938" s="2"/>
       <c r="C938" s="2"/>
-      <c r="D938" s="50"/>
+      <c r="D938" s="49"/>
       <c r="E938" s="2"/>
       <c r="F938" s="2"/>
       <c r="G938" s="2"/>
@@ -28966,7 +28991,7 @@
       <c r="A939" s="2"/>
       <c r="B939" s="2"/>
       <c r="C939" s="2"/>
-      <c r="D939" s="50"/>
+      <c r="D939" s="49"/>
       <c r="E939" s="2"/>
       <c r="F939" s="2"/>
       <c r="G939" s="2"/>
@@ -28994,7 +29019,7 @@
       <c r="A940" s="2"/>
       <c r="B940" s="2"/>
       <c r="C940" s="2"/>
-      <c r="D940" s="50"/>
+      <c r="D940" s="49"/>
       <c r="E940" s="2"/>
       <c r="F940" s="2"/>
       <c r="G940" s="2"/>
@@ -29022,7 +29047,7 @@
       <c r="A941" s="2"/>
       <c r="B941" s="2"/>
       <c r="C941" s="2"/>
-      <c r="D941" s="50"/>
+      <c r="D941" s="49"/>
       <c r="E941" s="2"/>
       <c r="F941" s="2"/>
       <c r="G941" s="2"/>
@@ -29050,7 +29075,7 @@
       <c r="A942" s="2"/>
       <c r="B942" s="2"/>
       <c r="C942" s="2"/>
-      <c r="D942" s="50"/>
+      <c r="D942" s="49"/>
       <c r="E942" s="2"/>
       <c r="F942" s="2"/>
       <c r="G942" s="2"/>
@@ -29078,7 +29103,7 @@
       <c r="A943" s="2"/>
       <c r="B943" s="2"/>
       <c r="C943" s="2"/>
-      <c r="D943" s="50"/>
+      <c r="D943" s="49"/>
       <c r="E943" s="2"/>
       <c r="F943" s="2"/>
       <c r="G943" s="2"/>
@@ -29106,7 +29131,7 @@
       <c r="A944" s="2"/>
       <c r="B944" s="2"/>
       <c r="C944" s="2"/>
-      <c r="D944" s="50"/>
+      <c r="D944" s="49"/>
       <c r="E944" s="2"/>
       <c r="F944" s="2"/>
       <c r="G944" s="2"/>
@@ -29134,7 +29159,7 @@
       <c r="A945" s="2"/>
       <c r="B945" s="2"/>
       <c r="C945" s="2"/>
-      <c r="D945" s="50"/>
+      <c r="D945" s="49"/>
       <c r="E945" s="2"/>
       <c r="F945" s="2"/>
       <c r="G945" s="2"/>
@@ -29162,7 +29187,7 @@
       <c r="A946" s="2"/>
       <c r="B946" s="2"/>
       <c r="C946" s="2"/>
-      <c r="D946" s="50"/>
+      <c r="D946" s="49"/>
       <c r="E946" s="2"/>
       <c r="F946" s="2"/>
       <c r="G946" s="2"/>
@@ -29190,7 +29215,7 @@
       <c r="A947" s="2"/>
       <c r="B947" s="2"/>
       <c r="C947" s="2"/>
-      <c r="D947" s="50"/>
+      <c r="D947" s="49"/>
       <c r="E947" s="2"/>
       <c r="F947" s="2"/>
       <c r="G947" s="2"/>
@@ -29218,7 +29243,7 @@
       <c r="A948" s="2"/>
       <c r="B948" s="2"/>
       <c r="C948" s="2"/>
-      <c r="D948" s="50"/>
+      <c r="D948" s="49"/>
       <c r="E948" s="2"/>
       <c r="F948" s="2"/>
       <c r="G948" s="2"/>
@@ -29246,7 +29271,7 @@
       <c r="A949" s="2"/>
       <c r="B949" s="2"/>
       <c r="C949" s="2"/>
-      <c r="D949" s="50"/>
+      <c r="D949" s="49"/>
       <c r="E949" s="2"/>
       <c r="F949" s="2"/>
       <c r="G949" s="2"/>
@@ -29274,7 +29299,7 @@
       <c r="A950" s="2"/>
       <c r="B950" s="2"/>
       <c r="C950" s="2"/>
-      <c r="D950" s="50"/>
+      <c r="D950" s="49"/>
       <c r="E950" s="2"/>
       <c r="F950" s="2"/>
       <c r="G950" s="2"/>
@@ -29302,7 +29327,7 @@
       <c r="A951" s="2"/>
       <c r="B951" s="2"/>
       <c r="C951" s="2"/>
-      <c r="D951" s="50"/>
+      <c r="D951" s="49"/>
       <c r="E951" s="2"/>
       <c r="F951" s="2"/>
       <c r="G951" s="2"/>
@@ -29330,7 +29355,7 @@
       <c r="A952" s="2"/>
       <c r="B952" s="2"/>
       <c r="C952" s="2"/>
-      <c r="D952" s="50"/>
+      <c r="D952" s="49"/>
       <c r="E952" s="2"/>
       <c r="F952" s="2"/>
       <c r="G952" s="2"/>
@@ -29358,7 +29383,7 @@
       <c r="A953" s="2"/>
       <c r="B953" s="2"/>
       <c r="C953" s="2"/>
-      <c r="D953" s="50"/>
+      <c r="D953" s="49"/>
       <c r="E953" s="2"/>
       <c r="F953" s="2"/>
       <c r="G953" s="2"/>
@@ -29386,7 +29411,7 @@
       <c r="A954" s="2"/>
       <c r="B954" s="2"/>
       <c r="C954" s="2"/>
-      <c r="D954" s="50"/>
+      <c r="D954" s="49"/>
       <c r="E954" s="2"/>
       <c r="F954" s="2"/>
       <c r="G954" s="2"/>
@@ -29414,7 +29439,7 @@
       <c r="A955" s="2"/>
       <c r="B955" s="2"/>
       <c r="C955" s="2"/>
-      <c r="D955" s="50"/>
+      <c r="D955" s="49"/>
       <c r="E955" s="2"/>
       <c r="F955" s="2"/>
       <c r="G955" s="2"/>
@@ -29442,7 +29467,7 @@
       <c r="A956" s="2"/>
       <c r="B956" s="2"/>
       <c r="C956" s="2"/>
-      <c r="D956" s="50"/>
+      <c r="D956" s="49"/>
       <c r="E956" s="2"/>
       <c r="F956" s="2"/>
       <c r="G956" s="2"/>
@@ -29470,7 +29495,7 @@
       <c r="A957" s="2"/>
       <c r="B957" s="2"/>
       <c r="C957" s="2"/>
-      <c r="D957" s="50"/>
+      <c r="D957" s="49"/>
       <c r="E957" s="2"/>
       <c r="F957" s="2"/>
       <c r="G957" s="2"/>
@@ -29498,7 +29523,7 @@
       <c r="A958" s="2"/>
       <c r="B958" s="2"/>
       <c r="C958" s="2"/>
-      <c r="D958" s="50"/>
+      <c r="D958" s="49"/>
       <c r="E958" s="2"/>
       <c r="F958" s="2"/>
       <c r="G958" s="2"/>
@@ -29526,7 +29551,7 @@
       <c r="A959" s="2"/>
       <c r="B959" s="2"/>
       <c r="C959" s="2"/>
-      <c r="D959" s="50"/>
+      <c r="D959" s="49"/>
       <c r="E959" s="2"/>
       <c r="F959" s="2"/>
       <c r="G959" s="2"/>
@@ -29554,7 +29579,7 @@
       <c r="A960" s="2"/>
       <c r="B960" s="2"/>
       <c r="C960" s="2"/>
-      <c r="D960" s="50"/>
+      <c r="D960" s="49"/>
       <c r="E960" s="2"/>
       <c r="F960" s="2"/>
       <c r="G960" s="2"/>
@@ -29582,7 +29607,7 @@
       <c r="A961" s="2"/>
       <c r="B961" s="2"/>
       <c r="C961" s="2"/>
-      <c r="D961" s="50"/>
+      <c r="D961" s="49"/>
       <c r="E961" s="2"/>
       <c r="F961" s="2"/>
       <c r="G961" s="2"/>
@@ -29610,7 +29635,7 @@
       <c r="A962" s="2"/>
       <c r="B962" s="2"/>
       <c r="C962" s="2"/>
-      <c r="D962" s="50"/>
+      <c r="D962" s="49"/>
       <c r="E962" s="2"/>
       <c r="F962" s="2"/>
       <c r="G962" s="2"/>
@@ -29638,7 +29663,7 @@
       <c r="A963" s="2"/>
       <c r="B963" s="2"/>
       <c r="C963" s="2"/>
-      <c r="D963" s="50"/>
+      <c r="D963" s="49"/>
       <c r="E963" s="2"/>
       <c r="F963" s="2"/>
       <c r="G963" s="2"/>
@@ -29666,7 +29691,7 @@
       <c r="A964" s="2"/>
       <c r="B964" s="2"/>
       <c r="C964" s="2"/>
-      <c r="D964" s="50"/>
+      <c r="D964" s="49"/>
       <c r="E964" s="2"/>
       <c r="F964" s="2"/>
       <c r="G964" s="2"/>
@@ -29694,7 +29719,7 @@
       <c r="A965" s="2"/>
       <c r="B965" s="2"/>
       <c r="C965" s="2"/>
-      <c r="D965" s="50"/>
+      <c r="D965" s="49"/>
       <c r="E965" s="2"/>
       <c r="F965" s="2"/>
       <c r="G965" s="2"/>
@@ -29722,7 +29747,7 @@
       <c r="A966" s="2"/>
       <c r="B966" s="2"/>
       <c r="C966" s="2"/>
-      <c r="D966" s="50"/>
+      <c r="D966" s="49"/>
       <c r="E966" s="2"/>
       <c r="F966" s="2"/>
       <c r="G966" s="2"/>
@@ -29750,7 +29775,7 @@
       <c r="A967" s="2"/>
       <c r="B967" s="2"/>
       <c r="C967" s="2"/>
-      <c r="D967" s="50"/>
+      <c r="D967" s="49"/>
       <c r="E967" s="2"/>
       <c r="F967" s="2"/>
       <c r="G967" s="2"/>
@@ -29778,7 +29803,7 @@
       <c r="A968" s="2"/>
       <c r="B968" s="2"/>
       <c r="C968" s="2"/>
-      <c r="D968" s="50"/>
+      <c r="D968" s="49"/>
       <c r="E968" s="2"/>
       <c r="F968" s="2"/>
       <c r="G968" s="2"/>
@@ -29806,7 +29831,7 @@
       <c r="A969" s="2"/>
       <c r="B969" s="2"/>
       <c r="C969" s="2"/>
-      <c r="D969" s="50"/>
+      <c r="D969" s="49"/>
       <c r="E969" s="2"/>
       <c r="F969" s="2"/>
       <c r="G969" s="2"/>
@@ -29834,7 +29859,7 @@
       <c r="A970" s="2"/>
       <c r="B970" s="2"/>
       <c r="C970" s="2"/>
-      <c r="D970" s="50"/>
+      <c r="D970" s="49"/>
       <c r="E970" s="2"/>
       <c r="F970" s="2"/>
       <c r="G970" s="2"/>
@@ -29862,7 +29887,7 @@
       <c r="A971" s="2"/>
       <c r="B971" s="2"/>
       <c r="C971" s="2"/>
-      <c r="D971" s="50"/>
+      <c r="D971" s="49"/>
       <c r="E971" s="2"/>
       <c r="F971" s="2"/>
       <c r="G971" s="2"/>
@@ -29890,7 +29915,7 @@
       <c r="A972" s="2"/>
       <c r="B972" s="2"/>
       <c r="C972" s="2"/>
-      <c r="D972" s="50"/>
+      <c r="D972" s="49"/>
       <c r="E972" s="2"/>
       <c r="F972" s="2"/>
       <c r="G972" s="2"/>
@@ -29918,7 +29943,7 @@
       <c r="A973" s="2"/>
       <c r="B973" s="2"/>
       <c r="C973" s="2"/>
-      <c r="D973" s="50"/>
+      <c r="D973" s="49"/>
       <c r="E973" s="2"/>
       <c r="F973" s="2"/>
       <c r="G973" s="2"/>
@@ -29946,7 +29971,7 @@
       <c r="A974" s="2"/>
       <c r="B974" s="2"/>
       <c r="C974" s="2"/>
-      <c r="D974" s="50"/>
+      <c r="D974" s="49"/>
       <c r="E974" s="2"/>
       <c r="F974" s="2"/>
       <c r="G974" s="2"/>
@@ -29974,7 +29999,7 @@
       <c r="A975" s="2"/>
       <c r="B975" s="2"/>
       <c r="C975" s="2"/>
-      <c r="D975" s="50"/>
+      <c r="D975" s="49"/>
       <c r="E975" s="2"/>
       <c r="F975" s="2"/>
       <c r="G975" s="2"/>
@@ -30002,7 +30027,7 @@
       <c r="A976" s="2"/>
       <c r="B976" s="2"/>
       <c r="C976" s="2"/>
-      <c r="D976" s="50"/>
+      <c r="D976" s="49"/>
       <c r="E976" s="2"/>
       <c r="F976" s="2"/>
       <c r="G976" s="2"/>
@@ -30030,7 +30055,7 @@
       <c r="A977" s="2"/>
       <c r="B977" s="2"/>
       <c r="C977" s="2"/>
-      <c r="D977" s="50"/>
+      <c r="D977" s="49"/>
       <c r="E977" s="2"/>
       <c r="F977" s="2"/>
       <c r="G977" s="2"/>
@@ -30058,7 +30083,7 @@
       <c r="A978" s="2"/>
       <c r="B978" s="2"/>
       <c r="C978" s="2"/>
-      <c r="D978" s="50"/>
+      <c r="D978" s="49"/>
       <c r="E978" s="2"/>
       <c r="F978" s="2"/>
       <c r="G978" s="2"/>
@@ -30086,7 +30111,7 @@
       <c r="A979" s="2"/>
       <c r="B979" s="2"/>
       <c r="C979" s="2"/>
-      <c r="D979" s="50"/>
+      <c r="D979" s="49"/>
       <c r="E979" s="2"/>
       <c r="F979" s="2"/>
       <c r="G979" s="2"/>
@@ -30114,7 +30139,7 @@
       <c r="A980" s="2"/>
       <c r="B980" s="2"/>
       <c r="C980" s="2"/>
-      <c r="D980" s="50"/>
+      <c r="D980" s="49"/>
       <c r="E980" s="2"/>
       <c r="F980" s="2"/>
       <c r="G980" s="2"/>
@@ -30142,7 +30167,7 @@
       <c r="A981" s="2"/>
       <c r="B981" s="2"/>
       <c r="C981" s="2"/>
-      <c r="D981" s="50"/>
+      <c r="D981" s="49"/>
       <c r="E981" s="2"/>
       <c r="F981" s="2"/>
       <c r="G981" s="2"/>
@@ -30170,7 +30195,7 @@
       <c r="A982" s="2"/>
       <c r="B982" s="2"/>
       <c r="C982" s="2"/>
-      <c r="D982" s="50"/>
+      <c r="D982" s="49"/>
       <c r="E982" s="2"/>
       <c r="F982" s="2"/>
       <c r="G982" s="2"/>
@@ -30198,7 +30223,7 @@
       <c r="A983" s="2"/>
       <c r="B983" s="2"/>
       <c r="C983" s="2"/>
-      <c r="D983" s="50"/>
+      <c r="D983" s="49"/>
       <c r="E983" s="2"/>
       <c r="F983" s="2"/>
       <c r="G983" s="2"/>
@@ -30226,7 +30251,7 @@
       <c r="A984" s="2"/>
       <c r="B984" s="2"/>
       <c r="C984" s="2"/>
-      <c r="D984" s="50"/>
+      <c r="D984" s="49"/>
       <c r="E984" s="2"/>
       <c r="F984" s="2"/>
       <c r="G984" s="2"/>
@@ -30254,7 +30279,7 @@
       <c r="A985" s="2"/>
       <c r="B985" s="2"/>
       <c r="C985" s="2"/>
-      <c r="D985" s="50"/>
+      <c r="D985" s="49"/>
       <c r="E985" s="2"/>
       <c r="F985" s="2"/>
       <c r="G985" s="2"/>
@@ -30282,7 +30307,7 @@
       <c r="A986" s="2"/>
       <c r="B986" s="2"/>
       <c r="C986" s="2"/>
-      <c r="D986" s="50"/>
+      <c r="D986" s="49"/>
       <c r="E986" s="2"/>
       <c r="F986" s="2"/>
       <c r="G986" s="2"/>
@@ -30310,7 +30335,7 @@
       <c r="A987" s="2"/>
       <c r="B987" s="2"/>
       <c r="C987" s="2"/>
-      <c r="D987" s="50"/>
+      <c r="D987" s="49"/>
       <c r="E987" s="2"/>
       <c r="F987" s="2"/>
       <c r="G987" s="2"/>
@@ -30338,7 +30363,7 @@
       <c r="A988" s="2"/>
       <c r="B988" s="2"/>
       <c r="C988" s="2"/>
-      <c r="D988" s="50"/>
+      <c r="D988" s="49"/>
       <c r="E988" s="2"/>
       <c r="F988" s="2"/>
       <c r="G988" s="2"/>
@@ -30366,7 +30391,7 @@
       <c r="A989" s="2"/>
       <c r="B989" s="2"/>
       <c r="C989" s="2"/>
-      <c r="D989" s="50"/>
+      <c r="D989" s="49"/>
       <c r="E989" s="2"/>
       <c r="F989" s="2"/>
       <c r="G989" s="2"/>
@@ -30394,7 +30419,7 @@
       <c r="A990" s="2"/>
       <c r="B990" s="2"/>
       <c r="C990" s="2"/>
-      <c r="D990" s="50"/>
+      <c r="D990" s="49"/>
       <c r="E990" s="2"/>
       <c r="F990" s="2"/>
       <c r="G990" s="2"/>
@@ -30422,7 +30447,7 @@
       <c r="A991" s="2"/>
       <c r="B991" s="2"/>
       <c r="C991" s="2"/>
-      <c r="D991" s="50"/>
+      <c r="D991" s="49"/>
       <c r="E991" s="2"/>
       <c r="F991" s="2"/>
       <c r="G991" s="2"/>
@@ -30450,7 +30475,7 @@
       <c r="A992" s="2"/>
       <c r="B992" s="2"/>
       <c r="C992" s="2"/>
-      <c r="D992" s="50"/>
+      <c r="D992" s="49"/>
       <c r="E992" s="2"/>
       <c r="F992" s="2"/>
       <c r="G992" s="2"/>
@@ -30478,7 +30503,7 @@
       <c r="A993" s="2"/>
       <c r="B993" s="2"/>
       <c r="C993" s="2"/>
-      <c r="D993" s="50"/>
+      <c r="D993" s="49"/>
       <c r="E993" s="2"/>
       <c r="F993" s="2"/>
       <c r="G993" s="2"/>
@@ -30506,7 +30531,7 @@
       <c r="A994" s="2"/>
       <c r="B994" s="2"/>
       <c r="C994" s="2"/>
-      <c r="D994" s="50"/>
+      <c r="D994" s="49"/>
       <c r="E994" s="2"/>
       <c r="F994" s="2"/>
       <c r="G994" s="2"/>
@@ -30534,7 +30559,7 @@
       <c r="A995" s="2"/>
       <c r="B995" s="2"/>
       <c r="C995" s="2"/>
-      <c r="D995" s="50"/>
+      <c r="D995" s="49"/>
       <c r="E995" s="2"/>
       <c r="F995" s="2"/>
       <c r="G995" s="2"/>
@@ -30562,7 +30587,7 @@
       <c r="A996" s="2"/>
       <c r="B996" s="2"/>
       <c r="C996" s="2"/>
-      <c r="D996" s="50"/>
+      <c r="D996" s="49"/>
       <c r="E996" s="2"/>
       <c r="F996" s="2"/>
       <c r="G996" s="2"/>
@@ -30590,7 +30615,7 @@
       <c r="A997" s="2"/>
       <c r="B997" s="2"/>
       <c r="C997" s="2"/>
-      <c r="D997" s="50"/>
+      <c r="D997" s="49"/>
       <c r="E997" s="2"/>
       <c r="F997" s="2"/>
       <c r="G997" s="2"/>
@@ -30618,7 +30643,7 @@
       <c r="A998" s="2"/>
       <c r="B998" s="2"/>
       <c r="C998" s="2"/>
-      <c r="D998" s="50"/>
+      <c r="D998" s="49"/>
       <c r="E998" s="2"/>
       <c r="F998" s="2"/>
       <c r="G998" s="2"/>
@@ -30646,7 +30671,7 @@
       <c r="A999" s="2"/>
       <c r="B999" s="2"/>
       <c r="C999" s="2"/>
-      <c r="D999" s="50"/>
+      <c r="D999" s="49"/>
       <c r="E999" s="2"/>
       <c r="F999" s="2"/>
       <c r="G999" s="2"/>
@@ -30674,7 +30699,7 @@
       <c r="A1000" s="2"/>
       <c r="B1000" s="2"/>
       <c r="C1000" s="2"/>
-      <c r="D1000" s="50"/>
+      <c r="D1000" s="49"/>
       <c r="E1000" s="2"/>
       <c r="F1000" s="2"/>
       <c r="G1000" s="2"/>
@@ -30707,265 +30732,303 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F802CC3A-307A-4FD9-9700-764C18E7FDAA}">
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:J48"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="16384" width="8.6640625" style="38"/>
+    <col min="1" max="1" width="14.4140625" style="38" customWidth="1"/>
+    <col min="2" max="16384" width="8.6640625" style="38"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="25.5">
+    <row r="1" spans="1:10" ht="25.5">
       <c r="A1" s="37" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="25.5">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="25.5">
       <c r="A3" s="37" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="25.5">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="25.5">
       <c r="A5" s="37" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="25.5">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="25.5">
       <c r="A7" s="37" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="17.5">
-      <c r="A8" s="39" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="17.5">
+      <c r="A8" s="42" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="17.5">
+      <c r="A9" s="39" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="17.5">
+      <c r="A10" s="39" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="17.5">
+      <c r="A11" s="39" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="17.5">
+      <c r="A12" s="39" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="17.5">
-      <c r="A9" s="39" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="17.5">
-      <c r="A10" s="39" t="s">
+    <row r="13" spans="1:10" ht="17.5">
+      <c r="A13" s="40" t="s">
+        <v>250</v>
+      </c>
+      <c r="C13" s="41" t="s">
+        <v>251</v>
+      </c>
+      <c r="D13" s="41" t="s">
+        <v>252</v>
+      </c>
+      <c r="E13" s="41" t="s">
+        <v>253</v>
+      </c>
+      <c r="F13" s="41" t="s">
+        <v>254</v>
+      </c>
+      <c r="G13" s="41" t="s">
+        <v>255</v>
+      </c>
+      <c r="H13" s="41" t="s">
+        <v>261</v>
+      </c>
+      <c r="I13" s="41" t="s">
+        <v>262</v>
+      </c>
+      <c r="J13" s="41" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="17.5">
+      <c r="A14" s="40" t="s">
+        <v>301</v>
+      </c>
+      <c r="B14" s="40"/>
+      <c r="C14" s="41">
+        <v>4</v>
+      </c>
+      <c r="D14" s="41" t="s">
+        <v>256</v>
+      </c>
+      <c r="E14" s="41" t="s">
+        <v>257</v>
+      </c>
+      <c r="F14" s="41" t="s">
+        <v>258</v>
+      </c>
+      <c r="G14" s="41" t="s">
+        <v>258</v>
+      </c>
+      <c r="H14" s="41" t="s">
+        <v>259</v>
+      </c>
+      <c r="I14" s="41" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="17.5">
+      <c r="A15" s="40" t="s">
+        <v>302</v>
+      </c>
+      <c r="B15" s="40"/>
+      <c r="C15" s="41">
+        <v>2</v>
+      </c>
+      <c r="D15" s="41">
+        <v>4</v>
+      </c>
+      <c r="E15" s="41">
+        <v>8</v>
+      </c>
+      <c r="F15" s="41">
+        <v>16</v>
+      </c>
+      <c r="G15" s="41">
+        <v>16</v>
+      </c>
+      <c r="H15" s="41">
+        <v>18</v>
+      </c>
+      <c r="I15" s="41">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="17.5">
+      <c r="A16" s="42" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="17.5">
+      <c r="A17" s="43" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="25.5">
+      <c r="A19" s="37" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="17.5">
-      <c r="A11" s="39" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="17.5">
-      <c r="A12" s="40" t="s">
-        <v>258</v>
-      </c>
-      <c r="D12" s="41" t="s">
-        <v>259</v>
-      </c>
-      <c r="E12" s="41" t="s">
-        <v>260</v>
-      </c>
-      <c r="F12" s="41" t="s">
-        <v>261</v>
-      </c>
-      <c r="G12" s="41" t="s">
-        <v>262</v>
-      </c>
-      <c r="H12" s="41" t="s">
-        <v>263</v>
-      </c>
-      <c r="I12" s="41" t="s">
-        <v>273</v>
-      </c>
-      <c r="J12" s="41" t="s">
-        <v>274</v>
-      </c>
-      <c r="K12" s="41" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="17.5">
-      <c r="A13" s="40" t="s">
-        <v>266</v>
-      </c>
-      <c r="B13" s="40" t="s">
-        <v>268</v>
-      </c>
-      <c r="D13" s="41">
-        <v>4</v>
-      </c>
-      <c r="E13" s="41" t="s">
+    <row r="20" spans="1:8" ht="17.5">
+      <c r="A20" s="42" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="17.5">
+      <c r="A21" s="40" t="s">
         <v>264</v>
       </c>
-      <c r="F13" s="41" t="s">
-        <v>269</v>
-      </c>
-      <c r="G13" s="41" t="s">
-        <v>270</v>
-      </c>
-      <c r="H13" s="41" t="s">
-        <v>270</v>
-      </c>
-      <c r="I13" s="41" t="s">
-        <v>271</v>
-      </c>
-      <c r="J13" s="41" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="17.5">
-      <c r="A14" s="40" t="s">
-        <v>267</v>
-      </c>
-      <c r="B14" s="40" t="s">
-        <v>265</v>
-      </c>
-      <c r="D14" s="41">
-        <v>2</v>
-      </c>
-      <c r="E14" s="41">
-        <v>4</v>
-      </c>
-      <c r="F14" s="41">
-        <v>8</v>
-      </c>
-      <c r="G14" s="41">
-        <v>16</v>
-      </c>
-      <c r="H14" s="41">
-        <v>16</v>
-      </c>
-      <c r="I14" s="41">
-        <v>18</v>
-      </c>
-      <c r="J14" s="41">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="25.5">
-      <c r="A16" s="37" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="17.5">
-      <c r="A17" s="40" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="17.5">
-      <c r="A18" s="39" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="17.5">
-      <c r="A19" s="42" t="s">
-        <v>282</v>
-      </c>
-      <c r="H19" s="39"/>
-    </row>
-    <row r="20" spans="1:8" ht="17.5">
-      <c r="A20" s="39" t="s">
-        <v>287</v>
-      </c>
-      <c r="H20" s="39"/>
-    </row>
-    <row r="21" spans="1:8" ht="17.5">
-      <c r="A21" s="43" t="s">
-        <v>280</v>
-      </c>
-      <c r="H21" s="39"/>
     </row>
     <row r="22" spans="1:8" ht="17.5">
       <c r="A22" s="39" t="s">
-        <v>252</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="H22" s="39"/>
     </row>
     <row r="23" spans="1:8" ht="17.5">
       <c r="A23" s="39" t="s">
-        <v>253</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="H23" s="39"/>
     </row>
     <row r="24" spans="1:8" ht="17.5">
       <c r="A24" s="39" t="s">
-        <v>254</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="H24" s="39"/>
     </row>
     <row r="25" spans="1:8" ht="17.5">
       <c r="A25" s="39" t="s">
-        <v>279</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="H25" s="39"/>
     </row>
     <row r="26" spans="1:8" ht="17.5">
-      <c r="A26" s="39" t="s">
-        <v>255</v>
+      <c r="A26" s="42" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="17.5">
       <c r="A27" s="39" t="s">
-        <v>256</v>
+        <v>270</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="17.5">
-      <c r="A28" s="39" t="s">
-        <v>257</v>
+      <c r="A28" s="43" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="17.5">
-      <c r="A29" s="42" t="s">
-        <v>283</v>
+      <c r="A29" s="39" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="17.5">
       <c r="A30" s="39" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="17.5">
-      <c r="A31" s="43" t="s">
-        <v>281</v>
+      <c r="A31" s="39" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="17.5">
-      <c r="A32" s="43" t="s">
-        <v>291</v>
+      <c r="A32" s="42" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="17.5">
-      <c r="A33" s="43" t="s">
-        <v>299</v>
+      <c r="A33" s="39" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="17.5">
-      <c r="A34" s="42" t="s">
-        <v>284</v>
+      <c r="A34" s="43" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="17.5">
-      <c r="A35" s="39" t="s">
-        <v>288</v>
+      <c r="A35" s="43" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="36" spans="1:1" ht="17.5">
       <c r="A36" s="43" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="17.5">
-      <c r="A37" s="43" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" s="44" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" s="44" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1">
-      <c r="A40" s="44" t="s">
-        <v>300</v>
+      <c r="A37" s="42" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" ht="17.5">
+      <c r="A38" s="39" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" ht="17.5">
+      <c r="A39" s="43" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" ht="17.5">
+      <c r="A40" s="43" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" ht="17.5">
+      <c r="A41" s="42" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" ht="17.5">
+      <c r="A42" s="39" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" ht="17.5">
+      <c r="A43" s="43" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" ht="17.5">
+      <c r="A44" s="42" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" ht="17.5">
+      <c r="A45" s="43" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" ht="17.5">
+      <c r="A46" s="43" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" ht="17.5">
+      <c r="A47" s="43" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" ht="17.5">
+      <c r="A48" s="43" t="s">
+        <v>296</v>
       </c>
     </row>
   </sheetData>
@@ -30985,7 +31048,7 @@
     <col min="4" max="4" width="20.58203125" style="1" customWidth="1"/>
     <col min="5" max="5" width="50.58203125" style="1" customWidth="1"/>
     <col min="6" max="6" width="20.6640625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10.6640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="30.58203125" style="1" customWidth="1"/>
     <col min="8" max="8" width="16.75" style="1" customWidth="1"/>
     <col min="9" max="9" width="30.58203125" style="1" customWidth="1"/>
     <col min="10" max="16384" width="8.6640625" style="1"/>
@@ -31002,22 +31065,22 @@
         <v>159</v>
       </c>
       <c r="D1" s="23" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E1" s="23" t="s">
         <v>158</v>
       </c>
       <c r="F1" s="23" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G1" s="23" t="s">
+        <v>303</v>
+      </c>
+      <c r="H1" s="23" t="s">
         <v>160</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="I1" s="23" t="s">
         <v>161</v>
-      </c>
-      <c r="I1" s="23" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="56">
@@ -31025,376 +31088,376 @@
         <v>153</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C2" s="24" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D2" s="25" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E2" s="24" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="F2" s="24" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G2" s="25" t="s">
-        <v>178</v>
+        <v>304</v>
       </c>
       <c r="H2" s="24" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I2" s="24" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="56">
       <c r="A3" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C3" s="26" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D3" s="27" t="s">
+        <v>182</v>
+      </c>
+      <c r="E3" s="26" t="s">
         <v>184</v>
       </c>
-      <c r="E3" s="26" t="s">
-        <v>186</v>
-      </c>
       <c r="F3" s="26" t="s">
-        <v>194</v>
-      </c>
-      <c r="G3" s="27">
-        <v>4</v>
+        <v>192</v>
+      </c>
+      <c r="G3" s="27" t="s">
+        <v>306</v>
       </c>
       <c r="H3" s="26" t="s">
+        <v>185</v>
+      </c>
+      <c r="I3" s="26" t="s">
         <v>187</v>
-      </c>
-      <c r="I3" s="26" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="56">
       <c r="A4" s="19" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B4" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>193</v>
+      </c>
+      <c r="D4" s="28" t="s">
         <v>190</v>
       </c>
-      <c r="C4" s="28" t="s">
-        <v>195</v>
-      </c>
-      <c r="D4" s="28" t="s">
-        <v>192</v>
-      </c>
       <c r="E4" s="28" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F4" s="28" t="s">
-        <v>229</v>
-      </c>
-      <c r="G4" s="28">
-        <v>4</v>
+        <v>227</v>
+      </c>
+      <c r="G4" s="28" t="s">
+        <v>305</v>
       </c>
       <c r="H4" s="32" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="I4" s="28" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="56">
       <c r="A5" s="19" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D5" s="28" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E5" s="28" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F5" s="28" t="s">
-        <v>229</v>
-      </c>
-      <c r="G5" s="28">
-        <v>4</v>
+        <v>227</v>
+      </c>
+      <c r="G5" s="28" t="s">
+        <v>305</v>
       </c>
       <c r="H5" s="32" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="I5" s="28" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="56">
       <c r="A6" s="19" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C6" s="28" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D6" s="28" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E6" s="28" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="F6" s="28" t="s">
-        <v>229</v>
-      </c>
-      <c r="G6" s="28">
-        <v>4</v>
+        <v>227</v>
+      </c>
+      <c r="G6" s="28" t="s">
+        <v>305</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="I6" s="28" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="56">
       <c r="A7" s="19" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C7" s="28" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D7" s="28" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E7" s="28" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F7" s="28" t="s">
-        <v>229</v>
-      </c>
-      <c r="G7" s="28">
-        <v>4</v>
+        <v>227</v>
+      </c>
+      <c r="G7" s="28" t="s">
+        <v>306</v>
       </c>
       <c r="H7" s="32" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="I7" s="28" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="56">
       <c r="A8" s="20" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C8" s="33" t="s">
+        <v>213</v>
+      </c>
+      <c r="D8" s="29" t="s">
+        <v>209</v>
+      </c>
+      <c r="E8" s="29" t="s">
+        <v>211</v>
+      </c>
+      <c r="F8" s="29" t="s">
+        <v>227</v>
+      </c>
+      <c r="G8" s="29" t="s">
+        <v>305</v>
+      </c>
+      <c r="H8" s="33" t="s">
         <v>215</v>
       </c>
-      <c r="D8" s="29" t="s">
-        <v>211</v>
-      </c>
-      <c r="E8" s="29" t="s">
-        <v>213</v>
-      </c>
-      <c r="F8" s="29" t="s">
-        <v>229</v>
-      </c>
-      <c r="G8" s="29">
-        <v>4</v>
-      </c>
-      <c r="H8" s="33" t="s">
-        <v>217</v>
-      </c>
       <c r="I8" s="33" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="56">
       <c r="A9" s="20" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D9" s="29" t="s">
+        <v>208</v>
+      </c>
+      <c r="E9" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="F9" s="29" t="s">
         <v>210</v>
       </c>
-      <c r="E9" s="29" t="s">
-        <v>214</v>
-      </c>
-      <c r="F9" s="29" t="s">
-        <v>212</v>
-      </c>
-      <c r="G9" s="29">
-        <v>4</v>
+      <c r="G9" s="29" t="s">
+        <v>305</v>
       </c>
       <c r="H9" s="33" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="I9" s="33" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="56">
       <c r="A10" s="21" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C10" s="34" t="s">
+        <v>220</v>
+      </c>
+      <c r="D10" s="30" t="s">
+        <v>219</v>
+      </c>
+      <c r="E10" s="34" t="s">
+        <v>221</v>
+      </c>
+      <c r="F10" s="30" t="s">
+        <v>228</v>
+      </c>
+      <c r="G10" s="30" t="s">
+        <v>305</v>
+      </c>
+      <c r="H10" s="34" t="s">
         <v>222</v>
       </c>
-      <c r="D10" s="30" t="s">
-        <v>221</v>
-      </c>
-      <c r="E10" s="34" t="s">
+      <c r="I10" s="30" t="s">
         <v>223</v>
-      </c>
-      <c r="F10" s="30" t="s">
-        <v>230</v>
-      </c>
-      <c r="G10" s="30">
-        <v>4</v>
-      </c>
-      <c r="H10" s="34" t="s">
-        <v>224</v>
-      </c>
-      <c r="I10" s="30" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="56">
       <c r="A11" s="22" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D11" s="31" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E11" s="35" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F11" s="31" t="s">
-        <v>212</v>
-      </c>
-      <c r="G11" s="31">
-        <v>4</v>
+        <v>210</v>
+      </c>
+      <c r="G11" s="31" t="s">
+        <v>306</v>
       </c>
       <c r="H11" s="35" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="I11" s="31" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="56">
       <c r="A12" s="22" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C12" s="35" t="s">
+        <v>230</v>
+      </c>
+      <c r="D12" s="31" t="s">
+        <v>225</v>
+      </c>
+      <c r="E12" s="35" t="s">
+        <v>231</v>
+      </c>
+      <c r="F12" s="31" t="s">
+        <v>210</v>
+      </c>
+      <c r="G12" s="35" t="s">
+        <v>308</v>
+      </c>
+      <c r="H12" s="35" t="s">
         <v>232</v>
       </c>
-      <c r="D12" s="31" t="s">
-        <v>227</v>
-      </c>
-      <c r="E12" s="35" t="s">
+      <c r="I12" s="31" t="s">
         <v>233</v>
-      </c>
-      <c r="F12" s="31" t="s">
-        <v>212</v>
-      </c>
-      <c r="G12" s="31">
-        <v>4</v>
-      </c>
-      <c r="H12" s="35" t="s">
-        <v>234</v>
-      </c>
-      <c r="I12" s="31" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="56">
       <c r="A13" s="22" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C13" s="35" t="s">
+        <v>235</v>
+      </c>
+      <c r="D13" s="31" t="s">
         <v>237</v>
       </c>
-      <c r="D13" s="31" t="s">
-        <v>239</v>
-      </c>
       <c r="E13" s="35" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F13" s="31" t="s">
-        <v>238</v>
-      </c>
-      <c r="G13" s="31">
-        <v>4</v>
+        <v>236</v>
+      </c>
+      <c r="G13" s="31" t="s">
+        <v>305</v>
       </c>
       <c r="H13" s="35" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I13" s="31" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="56">
-      <c r="A14" s="45" t="s">
-        <v>290</v>
-      </c>
-      <c r="B14" s="45" t="s">
-        <v>290</v>
-      </c>
-      <c r="C14" s="46" t="s">
-        <v>293</v>
-      </c>
-      <c r="D14" s="47" t="s">
-        <v>294</v>
-      </c>
-      <c r="E14" s="46" t="s">
-        <v>295</v>
-      </c>
-      <c r="F14" s="46" t="s">
-        <v>296</v>
-      </c>
-      <c r="G14" s="47">
-        <v>32</v>
-      </c>
-      <c r="H14" s="46" t="s">
-        <v>297</v>
-      </c>
-      <c r="I14" s="46" t="s">
-        <v>298</v>
+      <c r="A14" s="44" t="s">
+        <v>273</v>
+      </c>
+      <c r="B14" s="44" t="s">
+        <v>273</v>
+      </c>
+      <c r="C14" s="45" t="s">
+        <v>275</v>
+      </c>
+      <c r="D14" s="46" t="s">
+        <v>276</v>
+      </c>
+      <c r="E14" s="45" t="s">
+        <v>277</v>
+      </c>
+      <c r="F14" s="45" t="s">
+        <v>278</v>
+      </c>
+      <c r="G14" s="46" t="s">
+        <v>307</v>
+      </c>
+      <c r="H14" s="45" t="s">
+        <v>279</v>
+      </c>
+      <c r="I14" s="45" t="s">
+        <v>280</v>
       </c>
     </row>
   </sheetData>

--- a/CoreRefiner工作表.xlsx
+++ b/CoreRefiner工作表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_HOME_study\CoreRefiner\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{167528C0-8BE8-4FB4-AC8D-F84E32EA987D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFA749CF-F128-475A-818B-D4B2B41D0EED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="任务表" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="318">
   <si>
     <t>内容详情</t>
   </si>
@@ -531,9 +531,6 @@
     <t>按等级制度重新设计组件数值</t>
   </si>
   <si>
-    <t>Shop升级系统</t>
-  </si>
-  <si>
     <t>组件描述重制</t>
   </si>
   <si>
@@ -1253,6 +1250,26 @@
   </si>
   <si>
     <t>结果造价 = 素材造价 + 主体造价</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shop炼成区功能定义</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>*注5：不论是升级、合成、进化，只要完成一次炼成后，出来到结果里的Node的所有权就归结果栏所有。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shop炼成区功能-退回</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shop炼成区功能-升级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>详见细则表。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1919,7 +1936,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
       <c r="A1" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B1" s="51" t="s">
         <v>0</v>
@@ -2148,7 +2165,7 @@
         <v>15</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D7" s="7">
         <v>46152</v>
@@ -2559,16 +2576,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D18" s="10">
         <v>46168</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
@@ -3746,7 +3763,7 @@
         <v>46251</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
@@ -4506,7 +4523,7 @@
         <v>46266</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
@@ -4734,7 +4751,7 @@
         <v>46276</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F75" s="2"/>
       <c r="G75" s="2"/>
@@ -4763,7 +4780,7 @@
         <v>75</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>5</v>
@@ -4772,7 +4789,7 @@
         <v>46277</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F76" s="2"/>
       <c r="G76" s="2"/>
@@ -4797,15 +4814,21 @@
       <c r="Z76" s="2"/>
     </row>
     <row r="77" spans="1:26">
-      <c r="A77" s="15">
+      <c r="A77" s="6">
         <v>76</v>
       </c>
-      <c r="B77" s="16" t="s">
-        <v>146</v>
-      </c>
-      <c r="C77" s="16"/>
-      <c r="D77" s="48"/>
-      <c r="E77" s="16"/>
+      <c r="B77" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="C77" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D77" s="7">
+        <v>46278</v>
+      </c>
+      <c r="E77" s="4" t="s">
+        <v>317</v>
+      </c>
       <c r="F77" s="2"/>
       <c r="G77" s="2"/>
       <c r="H77" s="2"/>
@@ -4829,13 +4852,21 @@
       <c r="Z77" s="2"/>
     </row>
     <row r="78" spans="1:26">
-      <c r="A78" s="15">
+      <c r="A78" s="6">
         <v>77</v>
       </c>
-      <c r="B78" s="16"/>
-      <c r="C78" s="16"/>
-      <c r="D78" s="48"/>
-      <c r="E78" s="16"/>
+      <c r="B78" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D78" s="7">
+        <v>46278</v>
+      </c>
+      <c r="E78" s="4" t="s">
+        <v>317</v>
+      </c>
       <c r="F78" s="2"/>
       <c r="G78" s="2"/>
       <c r="H78" s="2"/>
@@ -4859,13 +4890,21 @@
       <c r="Z78" s="2"/>
     </row>
     <row r="79" spans="1:26">
-      <c r="A79" s="15">
+      <c r="A79" s="6">
         <v>78</v>
       </c>
-      <c r="B79" s="16"/>
-      <c r="C79" s="16"/>
-      <c r="D79" s="48"/>
-      <c r="E79" s="16"/>
+      <c r="B79" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D79" s="7">
+        <v>46278</v>
+      </c>
+      <c r="E79" s="4" t="s">
+        <v>317</v>
+      </c>
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
       <c r="H79" s="2"/>
@@ -5072,7 +5111,7 @@
         <v>85</v>
       </c>
       <c r="B86" s="16" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C86" s="16"/>
       <c r="D86" s="48"/>
@@ -5104,7 +5143,7 @@
         <v>86</v>
       </c>
       <c r="B87" s="16" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C87" s="16"/>
       <c r="D87" s="48"/>
@@ -30732,7 +30771,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F802CC3A-307A-4FD9-9700-764C18E7FDAA}">
-  <dimension ref="A1:J48"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="14.4140625" style="38" customWidth="1"/>
@@ -30741,108 +30780,108 @@
   <sheetData>
     <row r="1" spans="1:10" ht="25.5">
       <c r="A1" s="37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="25.5">
       <c r="A3" s="37" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="25.5">
       <c r="A5" s="37" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="25.5">
       <c r="A7" s="37" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="17.5">
       <c r="A8" s="42" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="17.5">
       <c r="A9" s="39" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="17.5">
       <c r="A10" s="39" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="17.5">
       <c r="A11" s="39" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="17.5">
       <c r="A12" s="39" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="17.5">
       <c r="A13" s="40" t="s">
+        <v>249</v>
+      </c>
+      <c r="C13" s="41" t="s">
         <v>250</v>
       </c>
-      <c r="C13" s="41" t="s">
+      <c r="D13" s="41" t="s">
         <v>251</v>
       </c>
-      <c r="D13" s="41" t="s">
+      <c r="E13" s="41" t="s">
         <v>252</v>
       </c>
-      <c r="E13" s="41" t="s">
+      <c r="F13" s="41" t="s">
         <v>253</v>
       </c>
-      <c r="F13" s="41" t="s">
+      <c r="G13" s="41" t="s">
         <v>254</v>
       </c>
-      <c r="G13" s="41" t="s">
-        <v>255</v>
-      </c>
       <c r="H13" s="41" t="s">
+        <v>260</v>
+      </c>
+      <c r="I13" s="41" t="s">
         <v>261</v>
       </c>
-      <c r="I13" s="41" t="s">
+      <c r="J13" s="41" t="s">
         <v>262</v>
-      </c>
-      <c r="J13" s="41" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="17.5">
       <c r="A14" s="40" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B14" s="40"/>
       <c r="C14" s="41">
         <v>4</v>
       </c>
       <c r="D14" s="41" t="s">
+        <v>255</v>
+      </c>
+      <c r="E14" s="41" t="s">
         <v>256</v>
       </c>
-      <c r="E14" s="41" t="s">
+      <c r="F14" s="41" t="s">
         <v>257</v>
       </c>
-      <c r="F14" s="41" t="s">
+      <c r="G14" s="41" t="s">
+        <v>257</v>
+      </c>
+      <c r="H14" s="41" t="s">
         <v>258</v>
       </c>
-      <c r="G14" s="41" t="s">
-        <v>258</v>
-      </c>
-      <c r="H14" s="41" t="s">
+      <c r="I14" s="41" t="s">
         <v>259</v>
-      </c>
-      <c r="I14" s="41" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="17.5">
       <c r="A15" s="40" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B15" s="40"/>
       <c r="C15" s="41">
@@ -30869,166 +30908,171 @@
     </row>
     <row r="16" spans="1:10" ht="17.5">
       <c r="A16" s="42" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="17.5">
       <c r="A17" s="43" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="25.5">
       <c r="A19" s="37" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="17.5">
       <c r="A20" s="42" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="17.5">
       <c r="A21" s="40" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="17.5">
       <c r="A22" s="39" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H22" s="39"/>
     </row>
     <row r="23" spans="1:8" ht="17.5">
       <c r="A23" s="39" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H23" s="39"/>
     </row>
     <row r="24" spans="1:8" ht="17.5">
       <c r="A24" s="39" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H24" s="39"/>
     </row>
     <row r="25" spans="1:8" ht="17.5">
       <c r="A25" s="39" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H25" s="39"/>
     </row>
     <row r="26" spans="1:8" ht="17.5">
       <c r="A26" s="42" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="17.5">
       <c r="A27" s="39" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="17.5">
       <c r="A28" s="43" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="17.5">
       <c r="A29" s="39" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="17.5">
       <c r="A30" s="39" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="17.5">
       <c r="A31" s="39" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="17.5">
       <c r="A32" s="42" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="17.5">
       <c r="A33" s="39" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="17.5">
       <c r="A34" s="43" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="17.5">
       <c r="A35" s="43" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="36" spans="1:1" ht="17.5">
       <c r="A36" s="43" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="17.5">
       <c r="A37" s="42" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="38" spans="1:1" ht="17.5">
       <c r="A38" s="39" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="39" spans="1:1" ht="17.5">
       <c r="A39" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="40" spans="1:1" ht="17.5">
       <c r="A40" s="43" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="41" spans="1:1" ht="17.5">
       <c r="A41" s="42" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="42" spans="1:1" ht="17.5">
       <c r="A42" s="39" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="43" spans="1:1" ht="17.5">
       <c r="A43" s="43" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="44" spans="1:1" ht="17.5">
       <c r="A44" s="42" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="45" spans="1:1" ht="17.5">
       <c r="A45" s="43" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="46" spans="1:1" ht="17.5">
       <c r="A46" s="43" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="47" spans="1:1" ht="17.5">
       <c r="A47" s="43" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="48" spans="1:1" ht="17.5">
       <c r="A48" s="43" t="s">
-        <v>296</v>
+        <v>295</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" ht="17.5">
+      <c r="A49" s="43" t="s">
+        <v>314</v>
       </c>
     </row>
   </sheetData>
@@ -31056,408 +31100,408 @@
   <sheetData>
     <row r="1" spans="1:9" ht="21">
       <c r="A1" s="23" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1" s="23" t="s">
         <v>156</v>
       </c>
-      <c r="B1" s="23" t="s">
+      <c r="C1" s="23" t="s">
+        <v>158</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>176</v>
+      </c>
+      <c r="E1" s="23" t="s">
         <v>157</v>
       </c>
-      <c r="C1" s="23" t="s">
+      <c r="F1" s="23" t="s">
+        <v>190</v>
+      </c>
+      <c r="G1" s="23" t="s">
+        <v>302</v>
+      </c>
+      <c r="H1" s="23" t="s">
         <v>159</v>
       </c>
-      <c r="D1" s="23" t="s">
-        <v>177</v>
-      </c>
-      <c r="E1" s="23" t="s">
-        <v>158</v>
-      </c>
-      <c r="F1" s="23" t="s">
-        <v>191</v>
-      </c>
-      <c r="G1" s="23" t="s">
-        <v>303</v>
-      </c>
-      <c r="H1" s="23" t="s">
+      <c r="I1" s="23" t="s">
         <v>160</v>
-      </c>
-      <c r="I1" s="23" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="56">
       <c r="A2" s="17" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C2" s="24" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D2" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="E2" s="24" t="s">
+        <v>182</v>
+      </c>
+      <c r="F2" s="24" t="s">
+        <v>191</v>
+      </c>
+      <c r="G2" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="H2" s="24" t="s">
         <v>178</v>
       </c>
-      <c r="E2" s="24" t="s">
-        <v>183</v>
-      </c>
-      <c r="F2" s="24" t="s">
-        <v>192</v>
-      </c>
-      <c r="G2" s="25" t="s">
-        <v>304</v>
-      </c>
-      <c r="H2" s="24" t="s">
-        <v>179</v>
-      </c>
       <c r="I2" s="24" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="56">
       <c r="A3" s="18" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C3" s="26" t="s">
+        <v>180</v>
+      </c>
+      <c r="D3" s="27" t="s">
         <v>181</v>
       </c>
-      <c r="D3" s="27" t="s">
-        <v>182</v>
-      </c>
       <c r="E3" s="26" t="s">
+        <v>183</v>
+      </c>
+      <c r="F3" s="26" t="s">
+        <v>191</v>
+      </c>
+      <c r="G3" s="27" t="s">
+        <v>305</v>
+      </c>
+      <c r="H3" s="26" t="s">
         <v>184</v>
       </c>
-      <c r="F3" s="26" t="s">
-        <v>192</v>
-      </c>
-      <c r="G3" s="27" t="s">
-        <v>306</v>
-      </c>
-      <c r="H3" s="26" t="s">
-        <v>185</v>
-      </c>
       <c r="I3" s="26" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="56">
       <c r="A4" s="19" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C4" s="28" t="s">
+        <v>192</v>
+      </c>
+      <c r="D4" s="28" t="s">
+        <v>189</v>
+      </c>
+      <c r="E4" s="28" t="s">
         <v>193</v>
       </c>
-      <c r="D4" s="28" t="s">
-        <v>190</v>
-      </c>
-      <c r="E4" s="28" t="s">
-        <v>194</v>
-      </c>
       <c r="F4" s="28" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G4" s="28" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H4" s="32" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I4" s="28" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="56">
       <c r="A5" s="19" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D5" s="28" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E5" s="28" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F5" s="28" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G5" s="28" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H5" s="32" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I5" s="28" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="56">
       <c r="A6" s="19" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C6" s="28" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D6" s="28" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E6" s="28" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F6" s="28" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G6" s="28" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I6" s="28" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="56">
       <c r="A7" s="19" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C7" s="28" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D7" s="28" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E7" s="28" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F7" s="28" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G7" s="28" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H7" s="32" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I7" s="28" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="56">
       <c r="A8" s="20" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C8" s="33" t="s">
+        <v>212</v>
+      </c>
+      <c r="D8" s="29" t="s">
+        <v>208</v>
+      </c>
+      <c r="E8" s="29" t="s">
+        <v>210</v>
+      </c>
+      <c r="F8" s="29" t="s">
+        <v>226</v>
+      </c>
+      <c r="G8" s="29" t="s">
+        <v>304</v>
+      </c>
+      <c r="H8" s="33" t="s">
+        <v>214</v>
+      </c>
+      <c r="I8" s="33" t="s">
         <v>213</v>
-      </c>
-      <c r="D8" s="29" t="s">
-        <v>209</v>
-      </c>
-      <c r="E8" s="29" t="s">
-        <v>211</v>
-      </c>
-      <c r="F8" s="29" t="s">
-        <v>227</v>
-      </c>
-      <c r="G8" s="29" t="s">
-        <v>305</v>
-      </c>
-      <c r="H8" s="33" t="s">
-        <v>215</v>
-      </c>
-      <c r="I8" s="33" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="56">
       <c r="A9" s="20" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D9" s="29" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E9" s="29" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F9" s="29" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H9" s="33" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I9" s="33" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="56">
       <c r="A10" s="21" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C10" s="34" t="s">
+        <v>219</v>
+      </c>
+      <c r="D10" s="30" t="s">
+        <v>218</v>
+      </c>
+      <c r="E10" s="34" t="s">
         <v>220</v>
       </c>
-      <c r="D10" s="30" t="s">
-        <v>219</v>
-      </c>
-      <c r="E10" s="34" t="s">
+      <c r="F10" s="30" t="s">
+        <v>227</v>
+      </c>
+      <c r="G10" s="30" t="s">
+        <v>304</v>
+      </c>
+      <c r="H10" s="34" t="s">
         <v>221</v>
       </c>
-      <c r="F10" s="30" t="s">
-        <v>228</v>
-      </c>
-      <c r="G10" s="30" t="s">
-        <v>305</v>
-      </c>
-      <c r="H10" s="34" t="s">
+      <c r="I10" s="30" t="s">
         <v>222</v>
-      </c>
-      <c r="I10" s="30" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="56">
       <c r="A11" s="22" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D11" s="31" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E11" s="35" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F11" s="31" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G11" s="31" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H11" s="35" t="s">
+        <v>240</v>
+      </c>
+      <c r="I11" s="31" t="s">
         <v>241</v>
-      </c>
-      <c r="I11" s="31" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="56">
       <c r="A12" s="22" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C12" s="35" t="s">
+        <v>229</v>
+      </c>
+      <c r="D12" s="31" t="s">
+        <v>224</v>
+      </c>
+      <c r="E12" s="35" t="s">
         <v>230</v>
       </c>
-      <c r="D12" s="31" t="s">
-        <v>225</v>
-      </c>
-      <c r="E12" s="35" t="s">
+      <c r="F12" s="31" t="s">
+        <v>209</v>
+      </c>
+      <c r="G12" s="35" t="s">
+        <v>307</v>
+      </c>
+      <c r="H12" s="35" t="s">
         <v>231</v>
       </c>
-      <c r="F12" s="31" t="s">
-        <v>210</v>
-      </c>
-      <c r="G12" s="35" t="s">
-        <v>308</v>
-      </c>
-      <c r="H12" s="35" t="s">
+      <c r="I12" s="31" t="s">
         <v>232</v>
-      </c>
-      <c r="I12" s="31" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="56">
       <c r="A13" s="22" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C13" s="35" t="s">
+        <v>234</v>
+      </c>
+      <c r="D13" s="31" t="s">
+        <v>236</v>
+      </c>
+      <c r="E13" s="35" t="s">
+        <v>243</v>
+      </c>
+      <c r="F13" s="31" t="s">
         <v>235</v>
       </c>
-      <c r="D13" s="31" t="s">
-        <v>237</v>
-      </c>
-      <c r="E13" s="35" t="s">
-        <v>244</v>
-      </c>
-      <c r="F13" s="31" t="s">
-        <v>236</v>
-      </c>
       <c r="G13" s="31" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H13" s="35" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I13" s="31" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="56">
       <c r="A14" s="44" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B14" s="44" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C14" s="45" t="s">
+        <v>274</v>
+      </c>
+      <c r="D14" s="46" t="s">
         <v>275</v>
       </c>
-      <c r="D14" s="46" t="s">
+      <c r="E14" s="45" t="s">
         <v>276</v>
       </c>
-      <c r="E14" s="45" t="s">
+      <c r="F14" s="45" t="s">
         <v>277</v>
       </c>
-      <c r="F14" s="45" t="s">
+      <c r="G14" s="46" t="s">
+        <v>306</v>
+      </c>
+      <c r="H14" s="45" t="s">
         <v>278</v>
       </c>
-      <c r="G14" s="46" t="s">
-        <v>307</v>
-      </c>
-      <c r="H14" s="45" t="s">
+      <c r="I14" s="45" t="s">
         <v>279</v>
-      </c>
-      <c r="I14" s="45" t="s">
-        <v>280</v>
       </c>
     </row>
   </sheetData>

--- a/CoreRefiner工作表.xlsx
+++ b/CoreRefiner工作表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_HOME_study\CoreRefiner\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFA749CF-F128-475A-818B-D4B2B41D0EED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CC15B23-DC58-437A-9F78-C1C19DDA0B8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="319">
   <si>
     <t>内容详情</t>
   </si>
@@ -1270,6 +1270,10 @@
   </si>
   <si>
     <t>详见细则表。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shop炼成区功能-合成</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4928,13 +4932,21 @@
       <c r="Z79" s="2"/>
     </row>
     <row r="80" spans="1:26">
-      <c r="A80" s="15">
+      <c r="A80" s="6">
         <v>79</v>
       </c>
-      <c r="B80" s="16"/>
-      <c r="C80" s="16"/>
-      <c r="D80" s="48"/>
-      <c r="E80" s="16"/>
+      <c r="B80" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D80" s="7">
+        <v>46278</v>
+      </c>
+      <c r="E80" s="4" t="s">
+        <v>317</v>
+      </c>
       <c r="F80" s="2"/>
       <c r="G80" s="2"/>
       <c r="H80" s="2"/>

--- a/CoreRefiner工作表.xlsx
+++ b/CoreRefiner工作表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_HOME_study\CoreRefiner\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CC15B23-DC58-437A-9F78-C1C19DDA0B8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AFED065-01E2-482D-88D3-121557C8600A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="Node表" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Node表!$A$1:$I$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Node表!$A$1:$I$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">任务表!$A$1:$Z$1000</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="320">
   <si>
     <t>内容详情</t>
   </si>
@@ -647,14 +647,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Other_Child</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Other_Revive</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>标题</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -790,14 +782,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>回归法则</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>公转法则</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>主攻击节点</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1072,10 +1056,6 @@
   </si>
   <si>
     <t>规则说明：两个满级(3级)的Node炼成一个全新的1级Node。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Node添加流程：定义标签→完善表单→棋盘节点→节点模组→装配步骤→步骤快照→图标设计→三语词条→工厂配置→实景测试</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1228,11 +1208,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>商店炼成区进化：
-Other_Child + Other_Repeat</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>升级后，素材消失，而主体依然存在，所以完成升级后虽然Node会出现在结果栏，但是仓库区或者扫描区的阴影仍然应该存在。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1274,6 +1249,35 @@
   </si>
   <si>
     <t>Shop炼成区功能-合成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shop炼成区功能-进化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Node添加流程：定义标签→完善表单→场地节点→节点模组→装配步骤→步骤快照→图标设计→描述文案→工厂配置→实景测试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rule_Child</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rule_Revive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>公转</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>逆向发射</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>商店炼成区进化：
+Rule_Child + Other_Repeat</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1938,7 +1942,7 @@
     <col min="6" max="16384" width="19.58203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="15" customHeight="1">
+    <row r="1" spans="1:26">
       <c r="A1" s="5" t="s">
         <v>147</v>
       </c>
@@ -4527,7 +4531,7 @@
         <v>46266</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
@@ -4755,7 +4759,7 @@
         <v>46276</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="F75" s="2"/>
       <c r="G75" s="2"/>
@@ -4784,7 +4788,7 @@
         <v>75</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>5</v>
@@ -4793,7 +4797,7 @@
         <v>46277</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="F76" s="2"/>
       <c r="G76" s="2"/>
@@ -4822,7 +4826,7 @@
         <v>76</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>5</v>
@@ -4831,7 +4835,7 @@
         <v>46278</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F77" s="2"/>
       <c r="G77" s="2"/>
@@ -4860,7 +4864,7 @@
         <v>77</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>5</v>
@@ -4869,7 +4873,7 @@
         <v>46278</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F78" s="2"/>
       <c r="G78" s="2"/>
@@ -4898,7 +4902,7 @@
         <v>78</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>5</v>
@@ -4907,7 +4911,7 @@
         <v>46278</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
@@ -4936,7 +4940,7 @@
         <v>79</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>5</v>
@@ -4945,7 +4949,7 @@
         <v>46278</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="F80" s="2"/>
       <c r="G80" s="2"/>
@@ -4970,13 +4974,21 @@
       <c r="Z80" s="2"/>
     </row>
     <row r="81" spans="1:26">
-      <c r="A81" s="15">
+      <c r="A81" s="6">
         <v>80</v>
       </c>
-      <c r="B81" s="16"/>
-      <c r="C81" s="16"/>
-      <c r="D81" s="48"/>
-      <c r="E81" s="16"/>
+      <c r="B81" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="C81" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D81" s="7">
+        <v>46279</v>
+      </c>
+      <c r="E81" s="4" t="s">
+        <v>311</v>
+      </c>
       <c r="F81" s="2"/>
       <c r="G81" s="2"/>
       <c r="H81" s="2"/>
@@ -5003,7 +5015,9 @@
       <c r="A82" s="15">
         <v>81</v>
       </c>
-      <c r="B82" s="16"/>
+      <c r="B82" s="16" t="s">
+        <v>146</v>
+      </c>
       <c r="C82" s="16"/>
       <c r="D82" s="48"/>
       <c r="E82" s="16"/>
@@ -5033,7 +5047,9 @@
       <c r="A83" s="15">
         <v>82</v>
       </c>
-      <c r="B83" s="16"/>
+      <c r="B83" s="16" t="s">
+        <v>153</v>
+      </c>
       <c r="C83" s="16"/>
       <c r="D83" s="48"/>
       <c r="E83" s="16"/>
@@ -5122,9 +5138,6 @@
       <c r="A86" s="15">
         <v>85</v>
       </c>
-      <c r="B86" s="16" t="s">
-        <v>146</v>
-      </c>
       <c r="C86" s="16"/>
       <c r="D86" s="48"/>
       <c r="E86" s="16"/>
@@ -5153,9 +5166,6 @@
     <row r="87" spans="1:26">
       <c r="A87" s="15">
         <v>86</v>
-      </c>
-      <c r="B87" s="16" t="s">
-        <v>153</v>
       </c>
       <c r="C87" s="16"/>
       <c r="D87" s="48"/>
@@ -30792,108 +30802,108 @@
   <sheetData>
     <row r="1" spans="1:10" ht="25.5">
       <c r="A1" s="37" t="s">
-        <v>271</v>
+        <v>314</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="25.5">
       <c r="A3" s="37" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="25.5">
       <c r="A5" s="37" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="25.5">
       <c r="A7" s="37" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="17.5">
       <c r="A8" s="42" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="17.5">
       <c r="A9" s="39" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="17.5">
       <c r="A10" s="39" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="17.5">
       <c r="A11" s="39" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="17.5">
       <c r="A12" s="39" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="17.5">
       <c r="A13" s="40" t="s">
+        <v>245</v>
+      </c>
+      <c r="C13" s="41" t="s">
+        <v>246</v>
+      </c>
+      <c r="D13" s="41" t="s">
+        <v>247</v>
+      </c>
+      <c r="E13" s="41" t="s">
+        <v>248</v>
+      </c>
+      <c r="F13" s="41" t="s">
         <v>249</v>
       </c>
-      <c r="C13" s="41" t="s">
+      <c r="G13" s="41" t="s">
         <v>250</v>
       </c>
-      <c r="D13" s="41" t="s">
-        <v>251</v>
-      </c>
-      <c r="E13" s="41" t="s">
-        <v>252</v>
-      </c>
-      <c r="F13" s="41" t="s">
-        <v>253</v>
-      </c>
-      <c r="G13" s="41" t="s">
-        <v>254</v>
-      </c>
       <c r="H13" s="41" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="I13" s="41" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="J13" s="41" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="17.5">
       <c r="A14" s="40" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="B14" s="40"/>
       <c r="C14" s="41">
         <v>4</v>
       </c>
       <c r="D14" s="41" t="s">
+        <v>251</v>
+      </c>
+      <c r="E14" s="41" t="s">
+        <v>252</v>
+      </c>
+      <c r="F14" s="41" t="s">
+        <v>253</v>
+      </c>
+      <c r="G14" s="41" t="s">
+        <v>253</v>
+      </c>
+      <c r="H14" s="41" t="s">
+        <v>254</v>
+      </c>
+      <c r="I14" s="41" t="s">
         <v>255</v>
-      </c>
-      <c r="E14" s="41" t="s">
-        <v>256</v>
-      </c>
-      <c r="F14" s="41" t="s">
-        <v>257</v>
-      </c>
-      <c r="G14" s="41" t="s">
-        <v>257</v>
-      </c>
-      <c r="H14" s="41" t="s">
-        <v>258</v>
-      </c>
-      <c r="I14" s="41" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="17.5">
       <c r="A15" s="40" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="B15" s="40"/>
       <c r="C15" s="41">
@@ -30920,171 +30930,171 @@
     </row>
     <row r="16" spans="1:10" ht="17.5">
       <c r="A16" s="42" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="17.5">
       <c r="A17" s="43" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="25.5">
       <c r="A19" s="37" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="17.5">
       <c r="A20" s="42" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="17.5">
       <c r="A21" s="40" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="17.5">
       <c r="A22" s="39" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="H22" s="39"/>
     </row>
     <row r="23" spans="1:8" ht="17.5">
       <c r="A23" s="39" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="H23" s="39"/>
     </row>
     <row r="24" spans="1:8" ht="17.5">
       <c r="A24" s="39" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="H24" s="39"/>
     </row>
     <row r="25" spans="1:8" ht="17.5">
       <c r="A25" s="39" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="H25" s="39"/>
     </row>
     <row r="26" spans="1:8" ht="17.5">
       <c r="A26" s="42" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="17.5">
       <c r="A27" s="39" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="17.5">
       <c r="A28" s="43" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="17.5">
       <c r="A29" s="39" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="17.5">
       <c r="A30" s="39" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="17.5">
       <c r="A31" s="39" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="17.5">
       <c r="A32" s="42" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="17.5">
       <c r="A33" s="39" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="17.5">
       <c r="A34" s="43" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="17.5">
       <c r="A35" s="43" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
     </row>
     <row r="36" spans="1:1" ht="17.5">
       <c r="A36" s="43" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="17.5">
       <c r="A37" s="42" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
     </row>
     <row r="38" spans="1:1" ht="17.5">
       <c r="A38" s="39" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="39" spans="1:1" ht="17.5">
       <c r="A39" s="43" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
     </row>
     <row r="40" spans="1:1" ht="17.5">
       <c r="A40" s="43" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
     </row>
     <row r="41" spans="1:1" ht="17.5">
       <c r="A41" s="42" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
     </row>
     <row r="42" spans="1:1" ht="17.5">
       <c r="A42" s="39" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
     </row>
     <row r="43" spans="1:1" ht="17.5">
       <c r="A43" s="43" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
     </row>
     <row r="44" spans="1:1" ht="17.5">
       <c r="A44" s="42" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
     </row>
     <row r="45" spans="1:1" ht="17.5">
       <c r="A45" s="43" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
     </row>
     <row r="46" spans="1:1" ht="17.5">
       <c r="A46" s="43" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
     </row>
     <row r="47" spans="1:1" ht="17.5">
       <c r="A47" s="43" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
     </row>
     <row r="48" spans="1:1" ht="17.5">
       <c r="A48" s="43" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
     </row>
     <row r="49" spans="1:1" ht="17.5">
       <c r="A49" s="43" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
     </row>
   </sheetData>
@@ -31121,16 +31131,16 @@
         <v>158</v>
       </c>
       <c r="D1" s="23" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E1" s="23" t="s">
         <v>157</v>
       </c>
       <c r="F1" s="23" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G1" s="23" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="H1" s="23" t="s">
         <v>159</v>
@@ -31147,25 +31157,25 @@
         <v>166</v>
       </c>
       <c r="C2" s="24" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D2" s="25" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E2" s="24" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F2" s="24" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G2" s="25" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="H2" s="24" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="I2" s="24" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="56">
@@ -31176,25 +31186,25 @@
         <v>167</v>
       </c>
       <c r="C3" s="26" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D3" s="27" t="s">
+        <v>179</v>
+      </c>
+      <c r="E3" s="26" t="s">
         <v>181</v>
       </c>
-      <c r="E3" s="26" t="s">
-        <v>183</v>
-      </c>
       <c r="F3" s="26" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G3" s="27" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="H3" s="26" t="s">
+        <v>182</v>
+      </c>
+      <c r="I3" s="26" t="s">
         <v>184</v>
-      </c>
-      <c r="I3" s="26" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="56">
@@ -31202,28 +31212,28 @@
         <v>162</v>
       </c>
       <c r="B4" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>190</v>
+      </c>
+      <c r="D4" s="28" t="s">
         <v>187</v>
       </c>
-      <c r="C4" s="28" t="s">
-        <v>192</v>
-      </c>
-      <c r="D4" s="28" t="s">
-        <v>189</v>
-      </c>
       <c r="E4" s="28" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F4" s="28" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="G4" s="28" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="H4" s="32" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="I4" s="28" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="56">
@@ -31234,25 +31244,25 @@
         <v>169</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D5" s="28" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E5" s="28" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F5" s="28" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="G5" s="28" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="H5" s="32" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="I5" s="28" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="56">
@@ -31263,25 +31273,25 @@
         <v>170</v>
       </c>
       <c r="C6" s="28" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D6" s="28" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E6" s="28" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F6" s="28" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="G6" s="28" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="I6" s="28" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="56">
@@ -31292,25 +31302,25 @@
         <v>168</v>
       </c>
       <c r="C7" s="28" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D7" s="28" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E7" s="28" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F7" s="28" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="G7" s="28" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="H7" s="32" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="I7" s="28" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="56">
@@ -31321,25 +31331,25 @@
         <v>171</v>
       </c>
       <c r="C8" s="33" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="D8" s="29" t="s">
-        <v>208</v>
+        <v>317</v>
       </c>
       <c r="E8" s="29" t="s">
+        <v>206</v>
+      </c>
+      <c r="F8" s="29" t="s">
+        <v>222</v>
+      </c>
+      <c r="G8" s="29" t="s">
+        <v>300</v>
+      </c>
+      <c r="H8" s="33" t="s">
         <v>210</v>
       </c>
-      <c r="F8" s="29" t="s">
-        <v>226</v>
-      </c>
-      <c r="G8" s="29" t="s">
-        <v>304</v>
-      </c>
-      <c r="H8" s="33" t="s">
-        <v>214</v>
-      </c>
       <c r="I8" s="33" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="56">
@@ -31350,112 +31360,112 @@
         <v>172</v>
       </c>
       <c r="C9" s="29" t="s">
+        <v>207</v>
+      </c>
+      <c r="D9" s="29" t="s">
+        <v>318</v>
+      </c>
+      <c r="E9" s="29" t="s">
+        <v>207</v>
+      </c>
+      <c r="F9" s="29" t="s">
+        <v>205</v>
+      </c>
+      <c r="G9" s="29" t="s">
+        <v>299</v>
+      </c>
+      <c r="H9" s="33" t="s">
+        <v>213</v>
+      </c>
+      <c r="I9" s="33" t="s">
         <v>211</v>
       </c>
-      <c r="D9" s="29" t="s">
-        <v>207</v>
-      </c>
-      <c r="E9" s="29" t="s">
-        <v>211</v>
-      </c>
-      <c r="F9" s="29" t="s">
-        <v>209</v>
-      </c>
-      <c r="G9" s="29" t="s">
-        <v>304</v>
-      </c>
-      <c r="H9" s="33" t="s">
+    </row>
+    <row r="10" spans="1:9" ht="56">
+      <c r="A10" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>315</v>
+      </c>
+      <c r="C10" s="33" t="s">
+        <v>221</v>
+      </c>
+      <c r="D10" s="29" t="s">
+        <v>219</v>
+      </c>
+      <c r="E10" s="33" t="s">
+        <v>224</v>
+      </c>
+      <c r="F10" s="29" t="s">
+        <v>205</v>
+      </c>
+      <c r="G10" s="29" t="s">
+        <v>300</v>
+      </c>
+      <c r="H10" s="33" t="s">
+        <v>236</v>
+      </c>
+      <c r="I10" s="33" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="56">
+      <c r="A11" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="B11" s="20" t="s">
+        <v>316</v>
+      </c>
+      <c r="C11" s="33" t="s">
+        <v>225</v>
+      </c>
+      <c r="D11" s="29" t="s">
+        <v>220</v>
+      </c>
+      <c r="E11" s="33" t="s">
+        <v>226</v>
+      </c>
+      <c r="F11" s="29" t="s">
+        <v>205</v>
+      </c>
+      <c r="G11" s="33" t="s">
+        <v>319</v>
+      </c>
+      <c r="H11" s="33" t="s">
+        <v>227</v>
+      </c>
+      <c r="I11" s="33" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="56">
+      <c r="A12" s="21" t="s">
+        <v>164</v>
+      </c>
+      <c r="B12" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="C12" s="34" t="s">
+        <v>215</v>
+      </c>
+      <c r="D12" s="30" t="s">
+        <v>214</v>
+      </c>
+      <c r="E12" s="34" t="s">
+        <v>216</v>
+      </c>
+      <c r="F12" s="30" t="s">
+        <v>223</v>
+      </c>
+      <c r="G12" s="30" t="s">
+        <v>299</v>
+      </c>
+      <c r="H12" s="34" t="s">
         <v>217</v>
       </c>
-      <c r="I9" s="33" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="56">
-      <c r="A10" s="21" t="s">
-        <v>164</v>
-      </c>
-      <c r="B10" s="21" t="s">
-        <v>173</v>
-      </c>
-      <c r="C10" s="34" t="s">
-        <v>219</v>
-      </c>
-      <c r="D10" s="30" t="s">
+      <c r="I12" s="30" t="s">
         <v>218</v>
-      </c>
-      <c r="E10" s="34" t="s">
-        <v>220</v>
-      </c>
-      <c r="F10" s="30" t="s">
-        <v>227</v>
-      </c>
-      <c r="G10" s="30" t="s">
-        <v>304</v>
-      </c>
-      <c r="H10" s="34" t="s">
-        <v>221</v>
-      </c>
-      <c r="I10" s="30" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="56">
-      <c r="A11" s="22" t="s">
-        <v>165</v>
-      </c>
-      <c r="B11" s="22" t="s">
-        <v>174</v>
-      </c>
-      <c r="C11" s="35" t="s">
-        <v>225</v>
-      </c>
-      <c r="D11" s="31" t="s">
-        <v>223</v>
-      </c>
-      <c r="E11" s="35" t="s">
-        <v>228</v>
-      </c>
-      <c r="F11" s="31" t="s">
-        <v>209</v>
-      </c>
-      <c r="G11" s="31" t="s">
-        <v>305</v>
-      </c>
-      <c r="H11" s="35" t="s">
-        <v>240</v>
-      </c>
-      <c r="I11" s="31" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="56">
-      <c r="A12" s="22" t="s">
-        <v>165</v>
-      </c>
-      <c r="B12" s="22" t="s">
-        <v>175</v>
-      </c>
-      <c r="C12" s="35" t="s">
-        <v>229</v>
-      </c>
-      <c r="D12" s="31" t="s">
-        <v>224</v>
-      </c>
-      <c r="E12" s="35" t="s">
-        <v>230</v>
-      </c>
-      <c r="F12" s="31" t="s">
-        <v>209</v>
-      </c>
-      <c r="G12" s="35" t="s">
-        <v>307</v>
-      </c>
-      <c r="H12" s="35" t="s">
-        <v>231</v>
-      </c>
-      <c r="I12" s="31" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="56">
@@ -31463,61 +31473,61 @@
         <v>165</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="C13" s="35" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="D13" s="31" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="E13" s="35" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="F13" s="31" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="G13" s="31" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="H13" s="35" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="I13" s="31" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="56">
       <c r="A14" s="44" t="s">
+        <v>267</v>
+      </c>
+      <c r="B14" s="44" t="s">
+        <v>267</v>
+      </c>
+      <c r="C14" s="45" t="s">
+        <v>269</v>
+      </c>
+      <c r="D14" s="46" t="s">
+        <v>270</v>
+      </c>
+      <c r="E14" s="45" t="s">
+        <v>271</v>
+      </c>
+      <c r="F14" s="45" t="s">
         <v>272</v>
       </c>
-      <c r="B14" s="44" t="s">
-        <v>272</v>
-      </c>
-      <c r="C14" s="45" t="s">
+      <c r="G14" s="46" t="s">
+        <v>301</v>
+      </c>
+      <c r="H14" s="45" t="s">
+        <v>273</v>
+      </c>
+      <c r="I14" s="45" t="s">
         <v>274</v>
       </c>
-      <c r="D14" s="46" t="s">
-        <v>275</v>
-      </c>
-      <c r="E14" s="45" t="s">
-        <v>276</v>
-      </c>
-      <c r="F14" s="45" t="s">
-        <v>277</v>
-      </c>
-      <c r="G14" s="46" t="s">
-        <v>306</v>
-      </c>
-      <c r="H14" s="45" t="s">
-        <v>278</v>
-      </c>
-      <c r="I14" s="45" t="s">
-        <v>279</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I11" xr:uid="{3258B9DE-144B-4A1D-96F7-444B72BE7902}"/>
+  <autoFilter ref="A1:I12" xr:uid="{3258B9DE-144B-4A1D-96F7-444B72BE7902}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/CoreRefiner工作表.xlsx
+++ b/CoreRefiner工作表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_HOME_study\CoreRefiner\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AFED065-01E2-482D-88D3-121557C8600A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF9AAB9A-CF03-48D1-BFC4-D3167644EF01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="任务表" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="321">
   <si>
     <t>内容详情</t>
   </si>
@@ -1278,6 +1278,12 @@
   <si>
     <t>商店炼成区进化：
 Rule_Child + Other_Repeat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fusion
+主体Kind
+素材Kind</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1501,7 +1507,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1640,6 +1646,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -31498,8 +31507,8 @@
       </c>
     </row>
     <row r="14" spans="1:9" ht="56">
-      <c r="A14" s="44" t="s">
-        <v>267</v>
+      <c r="A14" s="53" t="s">
+        <v>320</v>
       </c>
       <c r="B14" s="44" t="s">
         <v>267</v>

--- a/CoreRefiner工作表.xlsx
+++ b/CoreRefiner工作表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_HOME_study\CoreRefiner\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF9AAB9A-CF03-48D1-BFC4-D3167644EF01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96D1BB66-1E31-4C68-A59C-2D1C7E9ECE76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -554,10 +554,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Core</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>代表等级的视觉内容</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -597,25 +593,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Spawn</t>
-  </si>
-  <si>
-    <t>Attribute</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Rule</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Passive</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Other</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Core_Ball</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1284,6 +1261,35 @@
     <t>Fusion
 主体Kind
 素材Kind</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>核心类
+Core</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>生成类
+Spawn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>属性类Attribute</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>规则类
+Rule</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>被动类
+Passive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>其他类
+Other</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1507,7 +1513,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1648,6 +1654,24 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3780,7 +3804,7 @@
         <v>46251</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
@@ -4540,7 +4564,7 @@
         <v>46266</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
@@ -4768,7 +4792,7 @@
         <v>46276</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="F75" s="2"/>
       <c r="G75" s="2"/>
@@ -4797,7 +4821,7 @@
         <v>75</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>5</v>
@@ -4806,7 +4830,7 @@
         <v>46277</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="F76" s="2"/>
       <c r="G76" s="2"/>
@@ -4835,7 +4859,7 @@
         <v>76</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>5</v>
@@ -4844,7 +4868,7 @@
         <v>46278</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="F77" s="2"/>
       <c r="G77" s="2"/>
@@ -4873,7 +4897,7 @@
         <v>77</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>5</v>
@@ -4882,7 +4906,7 @@
         <v>46278</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="F78" s="2"/>
       <c r="G78" s="2"/>
@@ -4911,7 +4935,7 @@
         <v>78</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>5</v>
@@ -4920,7 +4944,7 @@
         <v>46278</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
@@ -4949,7 +4973,7 @@
         <v>79</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>5</v>
@@ -4958,7 +4982,7 @@
         <v>46278</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="F80" s="2"/>
       <c r="G80" s="2"/>
@@ -4987,7 +5011,7 @@
         <v>80</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>5</v>
@@ -4996,7 +5020,7 @@
         <v>46279</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="F81" s="2"/>
       <c r="G81" s="2"/>
@@ -5057,7 +5081,7 @@
         <v>82</v>
       </c>
       <c r="B83" s="16" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C83" s="16"/>
       <c r="D83" s="48"/>
@@ -30811,108 +30835,108 @@
   <sheetData>
     <row r="1" spans="1:10" ht="25.5">
       <c r="A1" s="37" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="25.5">
       <c r="A3" s="37" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="25.5">
       <c r="A5" s="37" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="25.5">
       <c r="A7" s="37" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="17.5">
       <c r="A8" s="42" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="17.5">
       <c r="A9" s="39" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="17.5">
       <c r="A10" s="39" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="17.5">
       <c r="A11" s="39" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="17.5">
       <c r="A12" s="39" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="17.5">
       <c r="A13" s="40" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="C13" s="41" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="D13" s="41" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="E13" s="41" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="F13" s="41" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="G13" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="H13" s="41" t="s">
         <v>250</v>
       </c>
-      <c r="H13" s="41" t="s">
-        <v>256</v>
-      </c>
       <c r="I13" s="41" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="J13" s="41" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="17.5">
       <c r="A14" s="40" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="B14" s="40"/>
       <c r="C14" s="41">
         <v>4</v>
       </c>
       <c r="D14" s="41" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="E14" s="41" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="F14" s="41" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="G14" s="41" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="H14" s="41" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="I14" s="41" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="17.5">
       <c r="A15" s="40" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="B15" s="40"/>
       <c r="C15" s="41">
@@ -30939,171 +30963,171 @@
     </row>
     <row r="16" spans="1:10" ht="17.5">
       <c r="A16" s="42" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="17.5">
       <c r="A17" s="43" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="25.5">
       <c r="A19" s="37" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="17.5">
       <c r="A20" s="42" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="17.5">
       <c r="A21" s="40" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="17.5">
       <c r="A22" s="39" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="H22" s="39"/>
     </row>
     <row r="23" spans="1:8" ht="17.5">
       <c r="A23" s="39" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="H23" s="39"/>
     </row>
     <row r="24" spans="1:8" ht="17.5">
       <c r="A24" s="39" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="H24" s="39"/>
     </row>
     <row r="25" spans="1:8" ht="17.5">
       <c r="A25" s="39" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="H25" s="39"/>
     </row>
     <row r="26" spans="1:8" ht="17.5">
       <c r="A26" s="42" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="17.5">
       <c r="A27" s="39" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="17.5">
       <c r="A28" s="43" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="17.5">
       <c r="A29" s="39" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="17.5">
       <c r="A30" s="39" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="17.5">
       <c r="A31" s="39" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="17.5">
       <c r="A32" s="42" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="17.5">
       <c r="A33" s="39" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="17.5">
       <c r="A34" s="43" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="17.5">
       <c r="A35" s="43" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
     </row>
     <row r="36" spans="1:1" ht="17.5">
       <c r="A36" s="43" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="17.5">
       <c r="A37" s="42" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
     </row>
     <row r="38" spans="1:1" ht="17.5">
       <c r="A38" s="39" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
     </row>
     <row r="39" spans="1:1" ht="17.5">
       <c r="A39" s="43" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
     </row>
     <row r="40" spans="1:1" ht="17.5">
       <c r="A40" s="43" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
     </row>
     <row r="41" spans="1:1" ht="17.5">
       <c r="A41" s="42" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
     </row>
     <row r="42" spans="1:1" ht="17.5">
       <c r="A42" s="39" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
     </row>
     <row r="43" spans="1:1" ht="17.5">
       <c r="A43" s="43" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
     </row>
     <row r="44" spans="1:1" ht="17.5">
       <c r="A44" s="42" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
     </row>
     <row r="45" spans="1:1" ht="17.5">
       <c r="A45" s="43" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
     </row>
     <row r="46" spans="1:1" ht="17.5">
       <c r="A46" s="43" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
     </row>
     <row r="47" spans="1:1" ht="17.5">
       <c r="A47" s="43" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
     </row>
     <row r="48" spans="1:1" ht="17.5">
       <c r="A48" s="43" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
     </row>
     <row r="49" spans="1:1" ht="17.5">
       <c r="A49" s="43" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
     </row>
   </sheetData>
@@ -31131,408 +31155,408 @@
   <sheetData>
     <row r="1" spans="1:9" ht="21">
       <c r="A1" s="23" t="s">
+        <v>154</v>
+      </c>
+      <c r="B1" s="23" t="s">
         <v>155</v>
       </c>
-      <c r="B1" s="23" t="s">
+      <c r="C1" s="23" t="s">
+        <v>157</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>168</v>
+      </c>
+      <c r="E1" s="23" t="s">
         <v>156</v>
       </c>
-      <c r="C1" s="23" t="s">
+      <c r="F1" s="23" t="s">
+        <v>182</v>
+      </c>
+      <c r="G1" s="23" t="s">
+        <v>291</v>
+      </c>
+      <c r="H1" s="23" t="s">
         <v>158</v>
       </c>
-      <c r="D1" s="23" t="s">
+      <c r="I1" s="23" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="56">
+      <c r="A2" s="54" t="s">
+        <v>315</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>171</v>
+      </c>
+      <c r="D2" s="25" t="s">
+        <v>169</v>
+      </c>
+      <c r="E2" s="24" t="s">
         <v>174</v>
       </c>
-      <c r="E1" s="23" t="s">
-        <v>157</v>
-      </c>
-      <c r="F1" s="23" t="s">
+      <c r="F2" s="24" t="s">
+        <v>183</v>
+      </c>
+      <c r="G2" s="25" t="s">
+        <v>292</v>
+      </c>
+      <c r="H2" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="I2" s="24" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="56">
+      <c r="A3" s="55" t="s">
+        <v>316</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="D3" s="27" t="s">
+        <v>173</v>
+      </c>
+      <c r="E3" s="26" t="s">
+        <v>175</v>
+      </c>
+      <c r="F3" s="26" t="s">
+        <v>183</v>
+      </c>
+      <c r="G3" s="27" t="s">
+        <v>294</v>
+      </c>
+      <c r="H3" s="26" t="s">
+        <v>176</v>
+      </c>
+      <c r="I3" s="26" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="56">
+      <c r="A4" s="56" t="s">
+        <v>317</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="D4" s="28" t="s">
+        <v>181</v>
+      </c>
+      <c r="E4" s="28" t="s">
+        <v>185</v>
+      </c>
+      <c r="F4" s="28" t="s">
+        <v>216</v>
+      </c>
+      <c r="G4" s="28" t="s">
+        <v>293</v>
+      </c>
+      <c r="H4" s="32" t="s">
+        <v>206</v>
+      </c>
+      <c r="I4" s="28" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="56">
+      <c r="A5" s="56" t="s">
+        <v>317</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>186</v>
+      </c>
+      <c r="D5" s="28" t="s">
+        <v>189</v>
+      </c>
+      <c r="E5" s="28" t="s">
+        <v>192</v>
+      </c>
+      <c r="F5" s="28" t="s">
+        <v>216</v>
+      </c>
+      <c r="G5" s="28" t="s">
+        <v>293</v>
+      </c>
+      <c r="H5" s="32" t="s">
+        <v>206</v>
+      </c>
+      <c r="I5" s="28" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="56">
+      <c r="A6" s="56" t="s">
+        <v>317</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="C6" s="28" t="s">
+        <v>187</v>
+      </c>
+      <c r="D6" s="28" t="s">
+        <v>190</v>
+      </c>
+      <c r="E6" s="28" t="s">
+        <v>193</v>
+      </c>
+      <c r="F6" s="28" t="s">
+        <v>216</v>
+      </c>
+      <c r="G6" s="28" t="s">
+        <v>293</v>
+      </c>
+      <c r="H6" s="32" t="s">
+        <v>206</v>
+      </c>
+      <c r="I6" s="28" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="56">
+      <c r="A7" s="56" t="s">
+        <v>317</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="C7" s="28" t="s">
         <v>188</v>
       </c>
-      <c r="G1" s="23" t="s">
-        <v>297</v>
-      </c>
-      <c r="H1" s="23" t="s">
-        <v>159</v>
-      </c>
-      <c r="I1" s="23" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="56">
-      <c r="A2" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="B2" s="17" t="s">
+      <c r="D7" s="28" t="s">
+        <v>191</v>
+      </c>
+      <c r="E7" s="28" t="s">
+        <v>194</v>
+      </c>
+      <c r="F7" s="28" t="s">
+        <v>216</v>
+      </c>
+      <c r="G7" s="28" t="s">
+        <v>294</v>
+      </c>
+      <c r="H7" s="32" t="s">
+        <v>206</v>
+      </c>
+      <c r="I7" s="28" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="56">
+      <c r="A8" s="57" t="s">
+        <v>318</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>165</v>
+      </c>
+      <c r="C8" s="33" t="s">
+        <v>202</v>
+      </c>
+      <c r="D8" s="29" t="s">
+        <v>311</v>
+      </c>
+      <c r="E8" s="29" t="s">
+        <v>200</v>
+      </c>
+      <c r="F8" s="29" t="s">
+        <v>216</v>
+      </c>
+      <c r="G8" s="29" t="s">
+        <v>294</v>
+      </c>
+      <c r="H8" s="33" t="s">
+        <v>204</v>
+      </c>
+      <c r="I8" s="33" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="56">
+      <c r="A9" s="57" t="s">
+        <v>318</v>
+      </c>
+      <c r="B9" s="20" t="s">
         <v>166</v>
       </c>
-      <c r="C2" s="24" t="s">
-        <v>177</v>
-      </c>
-      <c r="D2" s="25" t="s">
-        <v>175</v>
-      </c>
-      <c r="E2" s="24" t="s">
-        <v>180</v>
-      </c>
-      <c r="F2" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="G2" s="25" t="s">
-        <v>298</v>
-      </c>
-      <c r="H2" s="24" t="s">
-        <v>176</v>
-      </c>
-      <c r="I2" s="24" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="56">
-      <c r="A3" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="B3" s="18" t="s">
+      <c r="C9" s="29" t="s">
+        <v>201</v>
+      </c>
+      <c r="D9" s="29" t="s">
+        <v>312</v>
+      </c>
+      <c r="E9" s="29" t="s">
+        <v>201</v>
+      </c>
+      <c r="F9" s="29" t="s">
+        <v>199</v>
+      </c>
+      <c r="G9" s="29" t="s">
+        <v>293</v>
+      </c>
+      <c r="H9" s="33" t="s">
+        <v>207</v>
+      </c>
+      <c r="I9" s="33" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="56">
+      <c r="A10" s="57" t="s">
+        <v>318</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>309</v>
+      </c>
+      <c r="C10" s="33" t="s">
+        <v>215</v>
+      </c>
+      <c r="D10" s="29" t="s">
+        <v>213</v>
+      </c>
+      <c r="E10" s="33" t="s">
+        <v>218</v>
+      </c>
+      <c r="F10" s="29" t="s">
+        <v>199</v>
+      </c>
+      <c r="G10" s="29" t="s">
+        <v>294</v>
+      </c>
+      <c r="H10" s="33" t="s">
+        <v>230</v>
+      </c>
+      <c r="I10" s="33" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="56">
+      <c r="A11" s="57" t="s">
+        <v>318</v>
+      </c>
+      <c r="B11" s="20" t="s">
+        <v>310</v>
+      </c>
+      <c r="C11" s="33" t="s">
+        <v>219</v>
+      </c>
+      <c r="D11" s="29" t="s">
+        <v>214</v>
+      </c>
+      <c r="E11" s="33" t="s">
+        <v>220</v>
+      </c>
+      <c r="F11" s="29" t="s">
+        <v>199</v>
+      </c>
+      <c r="G11" s="33" t="s">
+        <v>313</v>
+      </c>
+      <c r="H11" s="33" t="s">
+        <v>221</v>
+      </c>
+      <c r="I11" s="33" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="56">
+      <c r="A12" s="58" t="s">
+        <v>319</v>
+      </c>
+      <c r="B12" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="C3" s="26" t="s">
-        <v>178</v>
-      </c>
-      <c r="D3" s="27" t="s">
-        <v>179</v>
-      </c>
-      <c r="E3" s="26" t="s">
-        <v>181</v>
-      </c>
-      <c r="F3" s="26" t="s">
-        <v>189</v>
-      </c>
-      <c r="G3" s="27" t="s">
-        <v>300</v>
-      </c>
-      <c r="H3" s="26" t="s">
-        <v>182</v>
-      </c>
-      <c r="I3" s="26" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="56">
-      <c r="A4" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="B4" s="19" t="s">
-        <v>185</v>
-      </c>
-      <c r="C4" s="28" t="s">
-        <v>190</v>
-      </c>
-      <c r="D4" s="28" t="s">
-        <v>187</v>
-      </c>
-      <c r="E4" s="28" t="s">
-        <v>191</v>
-      </c>
-      <c r="F4" s="28" t="s">
-        <v>222</v>
-      </c>
-      <c r="G4" s="28" t="s">
-        <v>299</v>
-      </c>
-      <c r="H4" s="32" t="s">
+      <c r="C12" s="34" t="s">
+        <v>209</v>
+      </c>
+      <c r="D12" s="30" t="s">
+        <v>208</v>
+      </c>
+      <c r="E12" s="34" t="s">
+        <v>210</v>
+      </c>
+      <c r="F12" s="30" t="s">
+        <v>217</v>
+      </c>
+      <c r="G12" s="30" t="s">
+        <v>293</v>
+      </c>
+      <c r="H12" s="34" t="s">
+        <v>211</v>
+      </c>
+      <c r="I12" s="30" t="s">
         <v>212</v>
       </c>
-      <c r="I4" s="28" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="56">
-      <c r="A5" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="B5" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="C5" s="28" t="s">
-        <v>192</v>
-      </c>
-      <c r="D5" s="28" t="s">
-        <v>195</v>
-      </c>
-      <c r="E5" s="28" t="s">
-        <v>198</v>
-      </c>
-      <c r="F5" s="28" t="s">
-        <v>222</v>
-      </c>
-      <c r="G5" s="28" t="s">
-        <v>299</v>
-      </c>
-      <c r="H5" s="32" t="s">
-        <v>212</v>
-      </c>
-      <c r="I5" s="28" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="56">
-      <c r="A6" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="B6" s="19" t="s">
-        <v>170</v>
-      </c>
-      <c r="C6" s="28" t="s">
-        <v>193</v>
-      </c>
-      <c r="D6" s="28" t="s">
-        <v>196</v>
-      </c>
-      <c r="E6" s="28" t="s">
-        <v>199</v>
-      </c>
-      <c r="F6" s="28" t="s">
-        <v>222</v>
-      </c>
-      <c r="G6" s="28" t="s">
-        <v>299</v>
-      </c>
-      <c r="H6" s="32" t="s">
-        <v>212</v>
-      </c>
-      <c r="I6" s="28" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="56">
-      <c r="A7" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="B7" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="C7" s="28" t="s">
-        <v>194</v>
-      </c>
-      <c r="D7" s="28" t="s">
-        <v>197</v>
-      </c>
-      <c r="E7" s="28" t="s">
-        <v>200</v>
-      </c>
-      <c r="F7" s="28" t="s">
-        <v>222</v>
-      </c>
-      <c r="G7" s="28" t="s">
-        <v>300</v>
-      </c>
-      <c r="H7" s="32" t="s">
-        <v>212</v>
-      </c>
-      <c r="I7" s="28" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="56">
-      <c r="A8" s="20" t="s">
-        <v>163</v>
-      </c>
-      <c r="B8" s="20" t="s">
-        <v>171</v>
-      </c>
-      <c r="C8" s="33" t="s">
-        <v>208</v>
-      </c>
-      <c r="D8" s="29" t="s">
-        <v>317</v>
-      </c>
-      <c r="E8" s="29" t="s">
-        <v>206</v>
-      </c>
-      <c r="F8" s="29" t="s">
-        <v>222</v>
-      </c>
-      <c r="G8" s="29" t="s">
-        <v>300</v>
-      </c>
-      <c r="H8" s="33" t="s">
-        <v>210</v>
-      </c>
-      <c r="I8" s="33" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="56">
-      <c r="A9" s="20" t="s">
-        <v>163</v>
-      </c>
-      <c r="B9" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="C9" s="29" t="s">
-        <v>207</v>
-      </c>
-      <c r="D9" s="29" t="s">
-        <v>318</v>
-      </c>
-      <c r="E9" s="29" t="s">
-        <v>207</v>
-      </c>
-      <c r="F9" s="29" t="s">
-        <v>205</v>
-      </c>
-      <c r="G9" s="29" t="s">
-        <v>299</v>
-      </c>
-      <c r="H9" s="33" t="s">
-        <v>213</v>
-      </c>
-      <c r="I9" s="33" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="56">
-      <c r="A10" s="20" t="s">
-        <v>163</v>
-      </c>
-      <c r="B10" s="20" t="s">
-        <v>315</v>
-      </c>
-      <c r="C10" s="33" t="s">
-        <v>221</v>
-      </c>
-      <c r="D10" s="29" t="s">
-        <v>219</v>
-      </c>
-      <c r="E10" s="33" t="s">
+    </row>
+    <row r="13" spans="1:9" ht="56">
+      <c r="A13" s="59" t="s">
+        <v>320</v>
+      </c>
+      <c r="B13" s="22" t="s">
+        <v>227</v>
+      </c>
+      <c r="C13" s="35" t="s">
         <v>224</v>
       </c>
-      <c r="F10" s="29" t="s">
-        <v>205</v>
-      </c>
-      <c r="G10" s="29" t="s">
-        <v>300</v>
-      </c>
-      <c r="H10" s="33" t="s">
-        <v>236</v>
-      </c>
-      <c r="I10" s="33" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="56">
-      <c r="A11" s="20" t="s">
-        <v>163</v>
-      </c>
-      <c r="B11" s="20" t="s">
-        <v>316</v>
-      </c>
-      <c r="C11" s="33" t="s">
+      <c r="D13" s="31" t="s">
+        <v>226</v>
+      </c>
+      <c r="E13" s="35" t="s">
+        <v>233</v>
+      </c>
+      <c r="F13" s="31" t="s">
         <v>225</v>
       </c>
-      <c r="D11" s="29" t="s">
-        <v>220</v>
-      </c>
-      <c r="E11" s="33" t="s">
-        <v>226</v>
-      </c>
-      <c r="F11" s="29" t="s">
-        <v>205</v>
-      </c>
-      <c r="G11" s="33" t="s">
-        <v>319</v>
-      </c>
-      <c r="H11" s="33" t="s">
-        <v>227</v>
-      </c>
-      <c r="I11" s="33" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="56">
-      <c r="A12" s="21" t="s">
-        <v>164</v>
-      </c>
-      <c r="B12" s="21" t="s">
-        <v>173</v>
-      </c>
-      <c r="C12" s="34" t="s">
-        <v>215</v>
-      </c>
-      <c r="D12" s="30" t="s">
-        <v>214</v>
-      </c>
-      <c r="E12" s="34" t="s">
-        <v>216</v>
-      </c>
-      <c r="F12" s="30" t="s">
+      <c r="G13" s="31" t="s">
+        <v>293</v>
+      </c>
+      <c r="H13" s="35" t="s">
+        <v>232</v>
+      </c>
+      <c r="I13" s="31" t="s">
         <v>223</v>
-      </c>
-      <c r="G12" s="30" t="s">
-        <v>299</v>
-      </c>
-      <c r="H12" s="34" t="s">
-        <v>217</v>
-      </c>
-      <c r="I12" s="30" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="56">
-      <c r="A13" s="22" t="s">
-        <v>165</v>
-      </c>
-      <c r="B13" s="22" t="s">
-        <v>233</v>
-      </c>
-      <c r="C13" s="35" t="s">
-        <v>230</v>
-      </c>
-      <c r="D13" s="31" t="s">
-        <v>232</v>
-      </c>
-      <c r="E13" s="35" t="s">
-        <v>239</v>
-      </c>
-      <c r="F13" s="31" t="s">
-        <v>231</v>
-      </c>
-      <c r="G13" s="31" t="s">
-        <v>299</v>
-      </c>
-      <c r="H13" s="35" t="s">
-        <v>238</v>
-      </c>
-      <c r="I13" s="31" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="56">
       <c r="A14" s="53" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="B14" s="44" t="s">
+        <v>261</v>
+      </c>
+      <c r="C14" s="45" t="s">
+        <v>263</v>
+      </c>
+      <c r="D14" s="46" t="s">
+        <v>264</v>
+      </c>
+      <c r="E14" s="45" t="s">
+        <v>265</v>
+      </c>
+      <c r="F14" s="45" t="s">
+        <v>266</v>
+      </c>
+      <c r="G14" s="46" t="s">
+        <v>295</v>
+      </c>
+      <c r="H14" s="45" t="s">
         <v>267</v>
       </c>
-      <c r="C14" s="45" t="s">
-        <v>269</v>
-      </c>
-      <c r="D14" s="46" t="s">
-        <v>270</v>
-      </c>
-      <c r="E14" s="45" t="s">
-        <v>271</v>
-      </c>
-      <c r="F14" s="45" t="s">
-        <v>272</v>
-      </c>
-      <c r="G14" s="46" t="s">
-        <v>301</v>
-      </c>
-      <c r="H14" s="45" t="s">
-        <v>273</v>
-      </c>
       <c r="I14" s="45" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
     </row>
   </sheetData>

--- a/CoreRefiner工作表.xlsx
+++ b/CoreRefiner工作表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_HOME_study\CoreRefiner\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96D1BB66-1E31-4C68-A59C-2D1C7E9ECE76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD6D8AC1-591F-4F16-A098-3C771BB13730}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="Node表" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Node表!$A$1:$I$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Node表!$A$1:$J$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">任务表!$A$1:$Z$1000</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="331">
   <si>
     <t>内容详情</t>
   </si>
@@ -531,9 +531,6 @@
     <t>按等级制度重新设计组件数值</t>
   </si>
   <si>
-    <t>组件描述重制</t>
-  </si>
-  <si>
     <t>任务编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -585,14 +582,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>基础数值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>变化数值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Core_Ball</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -743,22 +732,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>生命周期倍率：0.5f→1.0f→1.5f</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>移动速度倍率：0.5f→1.0f→1.5f</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>体积倍率：0.5f→1.0f→1.5f</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>伤害倍率：0.5f→1.0f→1.5f</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>主攻击节点</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -920,11 +893,6 @@
 冷却时间：3.0f
 扩散半径：50.0f
 扩散速度：50.0f</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>重复*重复节点个数*个节点。
-重复之间不会相互产生效果。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1290,6 +1258,79 @@
   <si>
     <t>其他类
 Other</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重复之前的节点，但重复之间不会相互产生效果。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>因为已经在Node面板里标注了等级，所以再加个视觉效果的意义已经不大了，而且暂时也没有好的灵感，就搁置了。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>组件描述重制</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>描述的从上到下应该依次是：【Icon，标题，Kind，造价】算一个区块在最上面，右侧是Icon，然后左侧从上到下是标题、Kind、等级、造价；之后是作用描述在中间部分；最后，放在最下面是所有的属性（包括四个基础属性，若有独有属性的则另外添加）；每个部分之间都要有横线隔开。
+Fusion类拥有多个Kind，比如一个Rule和一个Spawn合成后，出来的Node，应该有Fusion、Rule和Spawn三个Kind，并且以主体在上、素材在下的顺序写入作用描述。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>基础词条</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>变化词条</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>特殊词条</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>*主体词条*
+*素材词条*</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重复节点个数</t>
+  </si>
+  <si>
+    <t>固定伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>生命周期倍率增幅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>移动速度倍率增幅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>伤害倍率增幅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>伤害倍率增幅：0.5f→1.0f→1.5f</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>体积倍率增幅：0.5f→1.0f→1.5f</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>移动速度倍率增幅：0.5f→1.0f→1.5f</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>生命周期倍率增幅：0.5f→1.0f→1.5f</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1977,7 +2018,7 @@
   <sheetData>
     <row r="1" spans="1:26">
       <c r="A1" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B1" s="51" t="s">
         <v>0</v>
@@ -2206,7 +2247,7 @@
         <v>15</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D7" s="7">
         <v>46152</v>
@@ -2617,16 +2658,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D18" s="10">
         <v>46168</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
@@ -3804,7 +3845,7 @@
         <v>46251</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
@@ -4564,7 +4605,7 @@
         <v>46266</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
@@ -4792,7 +4833,7 @@
         <v>46276</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="F75" s="2"/>
       <c r="G75" s="2"/>
@@ -4821,7 +4862,7 @@
         <v>75</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>5</v>
@@ -4830,7 +4871,7 @@
         <v>46277</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F76" s="2"/>
       <c r="G76" s="2"/>
@@ -4859,7 +4900,7 @@
         <v>76</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>5</v>
@@ -4868,7 +4909,7 @@
         <v>46278</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="F77" s="2"/>
       <c r="G77" s="2"/>
@@ -4897,7 +4938,7 @@
         <v>77</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>5</v>
@@ -4906,7 +4947,7 @@
         <v>46278</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="F78" s="2"/>
       <c r="G78" s="2"/>
@@ -4935,7 +4976,7 @@
         <v>78</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>5</v>
@@ -4944,7 +4985,7 @@
         <v>46278</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
@@ -4973,7 +5014,7 @@
         <v>79</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>5</v>
@@ -4982,7 +5023,7 @@
         <v>46278</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="F80" s="2"/>
       <c r="G80" s="2"/>
@@ -5011,7 +5052,7 @@
         <v>80</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>5</v>
@@ -5020,7 +5061,7 @@
         <v>46279</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="F81" s="2"/>
       <c r="G81" s="2"/>
@@ -5044,16 +5085,22 @@
       <c r="Y81" s="2"/>
       <c r="Z81" s="2"/>
     </row>
-    <row r="82" spans="1:26">
-      <c r="A82" s="15">
+    <row r="82" spans="1:26" ht="105">
+      <c r="A82" s="6">
         <v>81</v>
       </c>
-      <c r="B82" s="16" t="s">
-        <v>146</v>
-      </c>
-      <c r="C82" s="16"/>
-      <c r="D82" s="48"/>
-      <c r="E82" s="16"/>
+      <c r="B82" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D82" s="7">
+        <v>46280</v>
+      </c>
+      <c r="E82" s="4" t="s">
+        <v>316</v>
+      </c>
       <c r="F82" s="2"/>
       <c r="G82" s="2"/>
       <c r="H82" s="2"/>
@@ -5076,16 +5123,22 @@
       <c r="Y82" s="2"/>
       <c r="Z82" s="2"/>
     </row>
-    <row r="83" spans="1:26">
-      <c r="A83" s="15">
+    <row r="83" spans="1:26" ht="42">
+      <c r="A83" s="11">
         <v>82</v>
       </c>
-      <c r="B83" s="16" t="s">
-        <v>152</v>
-      </c>
-      <c r="C83" s="16"/>
-      <c r="D83" s="48"/>
-      <c r="E83" s="16"/>
+      <c r="B83" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="C83" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="D83" s="13">
+        <v>46280</v>
+      </c>
+      <c r="E83" s="12" t="s">
+        <v>314</v>
+      </c>
       <c r="F83" s="2"/>
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
@@ -30835,108 +30888,108 @@
   <sheetData>
     <row r="1" spans="1:10" ht="25.5">
       <c r="A1" s="37" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="25.5">
       <c r="A3" s="37" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="25.5">
       <c r="A5" s="37" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="25.5">
       <c r="A7" s="37" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="17.5">
       <c r="A8" s="42" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="17.5">
       <c r="A9" s="39" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="17.5">
       <c r="A10" s="39" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="17.5">
       <c r="A11" s="39" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="17.5">
       <c r="A12" s="39" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="17.5">
       <c r="A13" s="40" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="C13" s="41" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="D13" s="41" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="E13" s="41" t="s">
+        <v>234</v>
+      </c>
+      <c r="F13" s="41" t="s">
+        <v>235</v>
+      </c>
+      <c r="G13" s="41" t="s">
+        <v>236</v>
+      </c>
+      <c r="H13" s="41" t="s">
         <v>242</v>
       </c>
-      <c r="F13" s="41" t="s">
+      <c r="I13" s="41" t="s">
         <v>243</v>
       </c>
-      <c r="G13" s="41" t="s">
+      <c r="J13" s="41" t="s">
         <v>244</v>
-      </c>
-      <c r="H13" s="41" t="s">
-        <v>250</v>
-      </c>
-      <c r="I13" s="41" t="s">
-        <v>251</v>
-      </c>
-      <c r="J13" s="41" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="17.5">
       <c r="A14" s="40" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="B14" s="40"/>
       <c r="C14" s="41">
         <v>4</v>
       </c>
       <c r="D14" s="41" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="E14" s="41" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="F14" s="41" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="G14" s="41" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="H14" s="41" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="I14" s="41" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="17.5">
       <c r="A15" s="40" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="B15" s="40"/>
       <c r="C15" s="41">
@@ -30963,171 +31016,171 @@
     </row>
     <row r="16" spans="1:10" ht="17.5">
       <c r="A16" s="42" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="17.5">
       <c r="A17" s="43" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="25.5">
       <c r="A19" s="37" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="17.5">
       <c r="A20" s="42" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="17.5">
       <c r="A21" s="40" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="17.5">
       <c r="A22" s="39" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="H22" s="39"/>
     </row>
     <row r="23" spans="1:8" ht="17.5">
       <c r="A23" s="39" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="H23" s="39"/>
     </row>
     <row r="24" spans="1:8" ht="17.5">
       <c r="A24" s="39" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="H24" s="39"/>
     </row>
     <row r="25" spans="1:8" ht="17.5">
       <c r="A25" s="39" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="H25" s="39"/>
     </row>
     <row r="26" spans="1:8" ht="17.5">
       <c r="A26" s="42" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="17.5">
       <c r="A27" s="39" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="17.5">
       <c r="A28" s="43" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="17.5">
       <c r="A29" s="39" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="17.5">
       <c r="A30" s="39" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="17.5">
       <c r="A31" s="39" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="17.5">
       <c r="A32" s="42" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="17.5">
       <c r="A33" s="39" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="17.5">
       <c r="A34" s="43" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="17.5">
       <c r="A35" s="43" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
     </row>
     <row r="36" spans="1:1" ht="17.5">
       <c r="A36" s="43" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="17.5">
       <c r="A37" s="42" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
     </row>
     <row r="38" spans="1:1" ht="17.5">
       <c r="A38" s="39" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
     </row>
     <row r="39" spans="1:1" ht="17.5">
       <c r="A39" s="43" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
     </row>
     <row r="40" spans="1:1" ht="17.5">
       <c r="A40" s="43" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
     </row>
     <row r="41" spans="1:1" ht="17.5">
       <c r="A41" s="42" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
     </row>
     <row r="42" spans="1:1" ht="17.5">
       <c r="A42" s="39" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
     </row>
     <row r="43" spans="1:1" ht="17.5">
       <c r="A43" s="43" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
     </row>
     <row r="44" spans="1:1" ht="17.5">
       <c r="A44" s="42" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
     </row>
     <row r="45" spans="1:1" ht="17.5">
       <c r="A45" s="43" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
     </row>
     <row r="46" spans="1:1" ht="17.5">
       <c r="A46" s="43" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
     </row>
     <row r="47" spans="1:1" ht="17.5">
       <c r="A47" s="43" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
     </row>
     <row r="48" spans="1:1" ht="17.5">
       <c r="A48" s="43" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
     </row>
     <row r="49" spans="1:1" ht="17.5">
       <c r="A49" s="43" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
     </row>
   </sheetData>
@@ -31138,429 +31191,472 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3258B9DE-144B-4A1D-96F7-444B72BE7902}">
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="15.58203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="30.58203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="40.83203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="20.58203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="50.58203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20.6640625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="30.58203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="12.25" style="1" customWidth="1"/>
+    <col min="2" max="2" width="28.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="39.9140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="50.08203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="26.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16.75" style="1" customWidth="1"/>
-    <col min="9" max="9" width="30.58203125" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.6640625" style="1"/>
+    <col min="9" max="9" width="18" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="35.58203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="21">
+    <row r="1" spans="1:10" ht="21">
       <c r="A1" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="B1" s="23" t="s">
         <v>154</v>
       </c>
-      <c r="B1" s="23" t="s">
+      <c r="C1" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>165</v>
+      </c>
+      <c r="E1" s="23" t="s">
         <v>155</v>
       </c>
-      <c r="C1" s="23" t="s">
+      <c r="F1" s="23" t="s">
+        <v>179</v>
+      </c>
+      <c r="G1" s="23" t="s">
+        <v>283</v>
+      </c>
+      <c r="H1" s="23" t="s">
+        <v>317</v>
+      </c>
+      <c r="I1" s="23" t="s">
+        <v>319</v>
+      </c>
+      <c r="J1" s="23" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="56">
+      <c r="A2" s="54" t="s">
+        <v>307</v>
+      </c>
+      <c r="B2" s="17" t="s">
         <v>157</v>
       </c>
-      <c r="D1" s="23" t="s">
+      <c r="C2" s="24" t="s">
         <v>168</v>
       </c>
-      <c r="E1" s="23" t="s">
-        <v>156</v>
-      </c>
-      <c r="F1" s="23" t="s">
+      <c r="D2" s="25" t="s">
+        <v>166</v>
+      </c>
+      <c r="E2" s="24" t="s">
+        <v>171</v>
+      </c>
+      <c r="F2" s="24" t="s">
+        <v>180</v>
+      </c>
+      <c r="G2" s="25" t="s">
+        <v>284</v>
+      </c>
+      <c r="H2" s="24" t="s">
+        <v>167</v>
+      </c>
+      <c r="I2" s="24" t="s">
+        <v>320</v>
+      </c>
+      <c r="J2" s="24" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="56">
+      <c r="A3" s="55" t="s">
+        <v>308</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>169</v>
+      </c>
+      <c r="D3" s="27" t="s">
+        <v>170</v>
+      </c>
+      <c r="E3" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="F3" s="26" t="s">
+        <v>180</v>
+      </c>
+      <c r="G3" s="27" t="s">
+        <v>286</v>
+      </c>
+      <c r="H3" s="26" t="s">
+        <v>173</v>
+      </c>
+      <c r="I3" s="26" t="s">
+        <v>320</v>
+      </c>
+      <c r="J3" s="26" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="56">
+      <c r="A4" s="56" t="s">
+        <v>309</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>181</v>
+      </c>
+      <c r="D4" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="E4" s="28" t="s">
         <v>182</v>
       </c>
-      <c r="G1" s="23" t="s">
-        <v>291</v>
-      </c>
-      <c r="H1" s="23" t="s">
-        <v>158</v>
-      </c>
-      <c r="I1" s="23" t="s">
+      <c r="F4" s="28" t="s">
+        <v>209</v>
+      </c>
+      <c r="G4" s="28" t="s">
+        <v>285</v>
+      </c>
+      <c r="H4" s="32" t="s">
+        <v>199</v>
+      </c>
+      <c r="I4" s="32" t="s">
+        <v>324</v>
+      </c>
+      <c r="J4" s="28" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="56">
+      <c r="A5" s="56" t="s">
+        <v>309</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>183</v>
+      </c>
+      <c r="D5" s="28" t="s">
+        <v>186</v>
+      </c>
+      <c r="E5" s="28" t="s">
+        <v>189</v>
+      </c>
+      <c r="F5" s="28" t="s">
+        <v>209</v>
+      </c>
+      <c r="G5" s="28" t="s">
+        <v>285</v>
+      </c>
+      <c r="H5" s="32" t="s">
+        <v>199</v>
+      </c>
+      <c r="I5" s="32" t="s">
+        <v>325</v>
+      </c>
+      <c r="J5" s="28" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="56">
+      <c r="A6" s="56" t="s">
+        <v>309</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="C6" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="D6" s="28" t="s">
+        <v>187</v>
+      </c>
+      <c r="E6" s="28" t="s">
+        <v>190</v>
+      </c>
+      <c r="F6" s="28" t="s">
+        <v>209</v>
+      </c>
+      <c r="G6" s="28" t="s">
+        <v>285</v>
+      </c>
+      <c r="H6" s="32" t="s">
+        <v>199</v>
+      </c>
+      <c r="I6" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="J6" s="28" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="56">
+      <c r="A7" s="56" t="s">
+        <v>309</v>
+      </c>
+      <c r="B7" s="19" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" ht="56">
-      <c r="A2" s="54" t="s">
-        <v>315</v>
-      </c>
-      <c r="B2" s="17" t="s">
-        <v>160</v>
-      </c>
-      <c r="C2" s="24" t="s">
-        <v>171</v>
-      </c>
-      <c r="D2" s="25" t="s">
-        <v>169</v>
-      </c>
-      <c r="E2" s="24" t="s">
-        <v>174</v>
-      </c>
-      <c r="F2" s="24" t="s">
-        <v>183</v>
-      </c>
-      <c r="G2" s="25" t="s">
-        <v>292</v>
-      </c>
-      <c r="H2" s="24" t="s">
-        <v>170</v>
-      </c>
-      <c r="I2" s="24" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="56">
-      <c r="A3" s="55" t="s">
-        <v>316</v>
-      </c>
-      <c r="B3" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="C3" s="26" t="s">
-        <v>172</v>
-      </c>
-      <c r="D3" s="27" t="s">
-        <v>173</v>
-      </c>
-      <c r="E3" s="26" t="s">
-        <v>175</v>
-      </c>
-      <c r="F3" s="26" t="s">
-        <v>183</v>
-      </c>
-      <c r="G3" s="27" t="s">
-        <v>294</v>
-      </c>
-      <c r="H3" s="26" t="s">
-        <v>176</v>
-      </c>
-      <c r="I3" s="26" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="56">
-      <c r="A4" s="56" t="s">
-        <v>317</v>
-      </c>
-      <c r="B4" s="19" t="s">
-        <v>179</v>
-      </c>
-      <c r="C4" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="D4" s="28" t="s">
-        <v>181</v>
-      </c>
-      <c r="E4" s="28" t="s">
+      <c r="C7" s="28" t="s">
         <v>185</v>
       </c>
-      <c r="F4" s="28" t="s">
+      <c r="D7" s="28" t="s">
+        <v>188</v>
+      </c>
+      <c r="E7" s="28" t="s">
+        <v>191</v>
+      </c>
+      <c r="F7" s="28" t="s">
+        <v>209</v>
+      </c>
+      <c r="G7" s="28" t="s">
+        <v>286</v>
+      </c>
+      <c r="H7" s="32" t="s">
+        <v>199</v>
+      </c>
+      <c r="I7" s="32" t="s">
+        <v>326</v>
+      </c>
+      <c r="J7" s="28" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="56">
+      <c r="A8" s="57" t="s">
+        <v>310</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="C8" s="33" t="s">
+        <v>195</v>
+      </c>
+      <c r="D8" s="29" t="s">
+        <v>303</v>
+      </c>
+      <c r="E8" s="29" t="s">
+        <v>193</v>
+      </c>
+      <c r="F8" s="29" t="s">
+        <v>209</v>
+      </c>
+      <c r="G8" s="29" t="s">
+        <v>286</v>
+      </c>
+      <c r="H8" s="33" t="s">
+        <v>197</v>
+      </c>
+      <c r="I8" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="J8" s="33" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="56">
+      <c r="A9" s="57" t="s">
+        <v>310</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="C9" s="29" t="s">
+        <v>194</v>
+      </c>
+      <c r="D9" s="29" t="s">
+        <v>304</v>
+      </c>
+      <c r="E9" s="29" t="s">
+        <v>194</v>
+      </c>
+      <c r="F9" s="29" t="s">
+        <v>192</v>
+      </c>
+      <c r="G9" s="29" t="s">
+        <v>285</v>
+      </c>
+      <c r="H9" s="33" t="s">
+        <v>200</v>
+      </c>
+      <c r="I9" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="J9" s="33" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="56">
+      <c r="A10" s="57" t="s">
+        <v>310</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>301</v>
+      </c>
+      <c r="C10" s="33" t="s">
+        <v>208</v>
+      </c>
+      <c r="D10" s="29" t="s">
+        <v>206</v>
+      </c>
+      <c r="E10" s="33" t="s">
+        <v>211</v>
+      </c>
+      <c r="F10" s="29" t="s">
+        <v>192</v>
+      </c>
+      <c r="G10" s="29" t="s">
+        <v>286</v>
+      </c>
+      <c r="H10" s="33" t="s">
+        <v>223</v>
+      </c>
+      <c r="I10" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="J10" s="33" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="56">
+      <c r="A11" s="57" t="s">
+        <v>310</v>
+      </c>
+      <c r="B11" s="20" t="s">
+        <v>302</v>
+      </c>
+      <c r="C11" s="33" t="s">
+        <v>212</v>
+      </c>
+      <c r="D11" s="29" t="s">
+        <v>207</v>
+      </c>
+      <c r="E11" s="33" t="s">
+        <v>213</v>
+      </c>
+      <c r="F11" s="29" t="s">
+        <v>192</v>
+      </c>
+      <c r="G11" s="33" t="s">
+        <v>305</v>
+      </c>
+      <c r="H11" s="33" t="s">
+        <v>214</v>
+      </c>
+      <c r="I11" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="J11" s="33" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="56">
+      <c r="A12" s="58" t="s">
+        <v>311</v>
+      </c>
+      <c r="B12" s="21" t="s">
+        <v>164</v>
+      </c>
+      <c r="C12" s="34" t="s">
+        <v>202</v>
+      </c>
+      <c r="D12" s="30" t="s">
+        <v>201</v>
+      </c>
+      <c r="E12" s="34" t="s">
+        <v>203</v>
+      </c>
+      <c r="F12" s="30" t="s">
+        <v>210</v>
+      </c>
+      <c r="G12" s="30" t="s">
+        <v>285</v>
+      </c>
+      <c r="H12" s="34" t="s">
+        <v>204</v>
+      </c>
+      <c r="I12" s="34" t="s">
+        <v>323</v>
+      </c>
+      <c r="J12" s="30" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="56">
+      <c r="A13" s="59" t="s">
+        <v>312</v>
+      </c>
+      <c r="B13" s="22" t="s">
+        <v>220</v>
+      </c>
+      <c r="C13" s="35" t="s">
+        <v>217</v>
+      </c>
+      <c r="D13" s="31" t="s">
+        <v>219</v>
+      </c>
+      <c r="E13" s="35" t="s">
+        <v>313</v>
+      </c>
+      <c r="F13" s="31" t="s">
+        <v>218</v>
+      </c>
+      <c r="G13" s="31" t="s">
+        <v>285</v>
+      </c>
+      <c r="H13" s="35" t="s">
+        <v>225</v>
+      </c>
+      <c r="I13" s="35" t="s">
+        <v>322</v>
+      </c>
+      <c r="J13" s="31" t="s">
         <v>216</v>
       </c>
-      <c r="G4" s="28" t="s">
-        <v>293</v>
-      </c>
-      <c r="H4" s="32" t="s">
-        <v>206</v>
-      </c>
-      <c r="I4" s="28" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="56">
-      <c r="A5" s="56" t="s">
-        <v>317</v>
-      </c>
-      <c r="B5" s="19" t="s">
-        <v>163</v>
-      </c>
-      <c r="C5" s="28" t="s">
-        <v>186</v>
-      </c>
-      <c r="D5" s="28" t="s">
-        <v>189</v>
-      </c>
-      <c r="E5" s="28" t="s">
-        <v>192</v>
-      </c>
-      <c r="F5" s="28" t="s">
-        <v>216</v>
-      </c>
-      <c r="G5" s="28" t="s">
-        <v>293</v>
-      </c>
-      <c r="H5" s="32" t="s">
-        <v>206</v>
-      </c>
-      <c r="I5" s="28" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="56">
-      <c r="A6" s="56" t="s">
-        <v>317</v>
-      </c>
-      <c r="B6" s="19" t="s">
-        <v>164</v>
-      </c>
-      <c r="C6" s="28" t="s">
-        <v>187</v>
-      </c>
-      <c r="D6" s="28" t="s">
-        <v>190</v>
-      </c>
-      <c r="E6" s="28" t="s">
-        <v>193</v>
-      </c>
-      <c r="F6" s="28" t="s">
-        <v>216</v>
-      </c>
-      <c r="G6" s="28" t="s">
-        <v>293</v>
-      </c>
-      <c r="H6" s="32" t="s">
-        <v>206</v>
-      </c>
-      <c r="I6" s="28" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="56">
-      <c r="A7" s="56" t="s">
-        <v>317</v>
-      </c>
-      <c r="B7" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="C7" s="28" t="s">
-        <v>188</v>
-      </c>
-      <c r="D7" s="28" t="s">
-        <v>191</v>
-      </c>
-      <c r="E7" s="28" t="s">
-        <v>194</v>
-      </c>
-      <c r="F7" s="28" t="s">
-        <v>216</v>
-      </c>
-      <c r="G7" s="28" t="s">
-        <v>294</v>
-      </c>
-      <c r="H7" s="32" t="s">
-        <v>206</v>
-      </c>
-      <c r="I7" s="28" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="56">
-      <c r="A8" s="57" t="s">
-        <v>318</v>
-      </c>
-      <c r="B8" s="20" t="s">
-        <v>165</v>
-      </c>
-      <c r="C8" s="33" t="s">
-        <v>202</v>
-      </c>
-      <c r="D8" s="29" t="s">
-        <v>311</v>
-      </c>
-      <c r="E8" s="29" t="s">
-        <v>200</v>
-      </c>
-      <c r="F8" s="29" t="s">
-        <v>216</v>
-      </c>
-      <c r="G8" s="29" t="s">
-        <v>294</v>
-      </c>
-      <c r="H8" s="33" t="s">
-        <v>204</v>
-      </c>
-      <c r="I8" s="33" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="56">
-      <c r="A9" s="57" t="s">
-        <v>318</v>
-      </c>
-      <c r="B9" s="20" t="s">
-        <v>166</v>
-      </c>
-      <c r="C9" s="29" t="s">
-        <v>201</v>
-      </c>
-      <c r="D9" s="29" t="s">
-        <v>312</v>
-      </c>
-      <c r="E9" s="29" t="s">
-        <v>201</v>
-      </c>
-      <c r="F9" s="29" t="s">
-        <v>199</v>
-      </c>
-      <c r="G9" s="29" t="s">
-        <v>293</v>
-      </c>
-      <c r="H9" s="33" t="s">
-        <v>207</v>
-      </c>
-      <c r="I9" s="33" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="56">
-      <c r="A10" s="57" t="s">
-        <v>318</v>
-      </c>
-      <c r="B10" s="20" t="s">
-        <v>309</v>
-      </c>
-      <c r="C10" s="33" t="s">
-        <v>215</v>
-      </c>
-      <c r="D10" s="29" t="s">
-        <v>213</v>
-      </c>
-      <c r="E10" s="33" t="s">
-        <v>218</v>
-      </c>
-      <c r="F10" s="29" t="s">
-        <v>199</v>
-      </c>
-      <c r="G10" s="29" t="s">
-        <v>294</v>
-      </c>
-      <c r="H10" s="33" t="s">
-        <v>230</v>
-      </c>
-      <c r="I10" s="33" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="56">
-      <c r="A11" s="57" t="s">
-        <v>318</v>
-      </c>
-      <c r="B11" s="20" t="s">
-        <v>310</v>
-      </c>
-      <c r="C11" s="33" t="s">
-        <v>219</v>
-      </c>
-      <c r="D11" s="29" t="s">
-        <v>214</v>
-      </c>
-      <c r="E11" s="33" t="s">
-        <v>220</v>
-      </c>
-      <c r="F11" s="29" t="s">
-        <v>199</v>
-      </c>
-      <c r="G11" s="33" t="s">
-        <v>313</v>
-      </c>
-      <c r="H11" s="33" t="s">
-        <v>221</v>
-      </c>
-      <c r="I11" s="33" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="56">
-      <c r="A12" s="58" t="s">
-        <v>319</v>
-      </c>
-      <c r="B12" s="21" t="s">
-        <v>167</v>
-      </c>
-      <c r="C12" s="34" t="s">
-        <v>209</v>
-      </c>
-      <c r="D12" s="30" t="s">
-        <v>208</v>
-      </c>
-      <c r="E12" s="34" t="s">
-        <v>210</v>
-      </c>
-      <c r="F12" s="30" t="s">
-        <v>217</v>
-      </c>
-      <c r="G12" s="30" t="s">
-        <v>293</v>
-      </c>
-      <c r="H12" s="34" t="s">
-        <v>211</v>
-      </c>
-      <c r="I12" s="30" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="56">
-      <c r="A13" s="59" t="s">
-        <v>320</v>
-      </c>
-      <c r="B13" s="22" t="s">
-        <v>227</v>
-      </c>
-      <c r="C13" s="35" t="s">
-        <v>224</v>
-      </c>
-      <c r="D13" s="31" t="s">
-        <v>226</v>
-      </c>
-      <c r="E13" s="35" t="s">
-        <v>233</v>
-      </c>
-      <c r="F13" s="31" t="s">
-        <v>225</v>
-      </c>
-      <c r="G13" s="31" t="s">
-        <v>293</v>
-      </c>
-      <c r="H13" s="35" t="s">
-        <v>232</v>
-      </c>
-      <c r="I13" s="31" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="56">
+    </row>
+    <row r="14" spans="1:10" ht="56">
       <c r="A14" s="53" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="B14" s="44" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="C14" s="45" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="D14" s="46" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="E14" s="45" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="F14" s="45" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="G14" s="46" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="H14" s="45" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="I14" s="45" t="s">
-        <v>268</v>
+        <v>321</v>
+      </c>
+      <c r="J14" s="45" t="s">
+        <v>260</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I12" xr:uid="{3258B9DE-144B-4A1D-96F7-444B72BE7902}"/>
+  <autoFilter ref="A1:J12" xr:uid="{3258B9DE-144B-4A1D-96F7-444B72BE7902}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/CoreRefiner工作表.xlsx
+++ b/CoreRefiner工作表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_HOME_study\CoreRefiner\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD6D8AC1-591F-4F16-A098-3C771BB13730}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB097FA1-A9E1-447B-9238-F4D7B36B6AE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="361">
   <si>
     <t>内容详情</t>
   </si>
@@ -1261,10 +1261,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>重复之前的节点，但重复之间不会相互产生效果。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>因为已经在Node面板里标注了等级，所以再加个视觉效果的意义已经不大了，而且暂时也没有好的灵感，就搁置了。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1331,6 +1327,128 @@
   </si>
   <si>
     <t>生命周期倍率增幅：0.5f→1.0f→1.5f</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>元素类 两仪四相八卦</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shop奥义区</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>奥义区规则：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这种Node的Kind为奥义类、Ultra类、奥義类。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在扫描到它的时候，会按顺序把所有其中包含的Node都写入本次攻击的配方。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>锻造情况说明：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>展现：分为无奥义Node和有奥义Node。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无奥义Node：区域内正中间存在一个锻造的按键，提示需要3元。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>核心功能是可以让玩家自定义一个奥义Node，它能够将多个不同的Node集成化为一个Node，也就是将所有其他类型的Node收集起来，并被视为一个集体。</t>
+  </si>
+  <si>
+    <t>让奥义区识别到接下来要编辑的奥义Node对象的功能。识别的方法有两种，锻造新的奥义Node和玩家拖入已有奥义Node。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>打孔情况说明：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当在有奥义Node的情况下，点击时，会让对象Node升一级，并开辟出一个新的Node栏位。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>价格为1元。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更名情况说明：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>价格为免费，无需标注。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重绘情况说明：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当在有奥义Node的情况下，点击时，会打开一个新的叠加式UI，仅输入栏、确定和退出三个按键，在输入栏中写入文案后按确定可以重命名当前的奥义Node；按退出则是直接回到当前画面。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当在有奥义Node的情况下，点击时，会打开一个新的叠加式UI，仅一个16*16的像素面板、确定和退出三个按键，点击像素可以使其切换绘制和不绘制两种状态，完成绘制后按确定可以重制当前的奥义Node的Icon；按退出则是直接回到当前画面。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拖入已有奥义Node：只要玩家拖入后，直接进入有奥义Node的编辑状态，对象位被拖入的奥义Node，且此奥义Node的所有权切换为奥义区。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>有奥义Node：区域内最左侧栏位是这个奥义Node的Icon，然后开始从左到右依次排出其中容纳的各个Node，这些栏位比奥义Node的栏位小一圈，最右侧从上到下是：打孔、更名、重绘，三个按键。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>包含的核心功能：锻造、打孔、更名、重绘</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>锻造新的奥义Node：价格设定为3元，购买后区域自动切换为有奥义Node的状态，然后按照规则绘制，并将新建的Node置于最左侧栏位内。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在进入有奥义Node的阶段后，玩家可以在Node栏位中自由拖入拖出所有存在于场地和仓库中的Node，并且这些修改如果被是为可通过的情况下，会直接修改归属权。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在完成修改后，可以将奥义Node从奥义区拖出，然后奥义区恢复到无奥义Node状态。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>奥义Node中的Node依然遵循现有的攻击组装的基础规则，也就是达到配方上限或者没有攻击槽位就发射，然后截止到被发射的Node后，开一个新的攻击配方把剩下的Node写入，并继续扫描。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>*注1：奥义Node的等级为其可以容纳Node的数量，天生为3级，显示时只显示数字不显示Max，可以通过打孔功能升级，也就是开辟更多容纳其他Node的空间。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>*注2：奥义类的Node永远不能进入炼成区，但可以被卖出。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>*注3：核心类不可以被放入奥义Node。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>买卖提示框</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>详见细则表。</t>
+  </si>
+  <si>
+    <t>重复之前的节点。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1512,7 +1630,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1550,11 +1668,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </left>
+      <right style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </right>
+      <top style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1713,6 +1844,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5090,7 +5230,7 @@
         <v>81</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C82" s="6" t="s">
         <v>5</v>
@@ -5099,7 +5239,7 @@
         <v>46280</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F82" s="2"/>
       <c r="G82" s="2"/>
@@ -5124,20 +5264,20 @@
       <c r="Z82" s="2"/>
     </row>
     <row r="83" spans="1:26" ht="42">
-      <c r="A83" s="11">
+      <c r="A83" s="60">
         <v>82</v>
       </c>
-      <c r="B83" s="12" t="s">
+      <c r="B83" s="61" t="s">
         <v>151</v>
       </c>
-      <c r="C83" s="11" t="s">
+      <c r="C83" s="60" t="s">
         <v>48</v>
       </c>
-      <c r="D83" s="13">
+      <c r="D83" s="62">
         <v>46280</v>
       </c>
-      <c r="E83" s="12" t="s">
-        <v>314</v>
+      <c r="E83" s="61" t="s">
+        <v>313</v>
       </c>
       <c r="F83" s="2"/>
       <c r="G83" s="2"/>
@@ -5165,10 +5305,14 @@
       <c r="A84" s="15">
         <v>83</v>
       </c>
-      <c r="B84" s="16"/>
+      <c r="B84" s="16" t="s">
+        <v>331</v>
+      </c>
       <c r="C84" s="16"/>
-      <c r="D84" s="48"/>
-      <c r="E84" s="16"/>
+      <c r="D84" s="16"/>
+      <c r="E84" s="16" t="s">
+        <v>359</v>
+      </c>
       <c r="F84" s="2"/>
       <c r="G84" s="2"/>
       <c r="H84" s="2"/>
@@ -5195,8 +5339,11 @@
       <c r="A85" s="15">
         <v>84</v>
       </c>
+      <c r="B85" s="16" t="s">
+        <v>358</v>
+      </c>
       <c r="C85" s="16"/>
-      <c r="D85" s="48"/>
+      <c r="D85" s="16"/>
       <c r="E85" s="16"/>
       <c r="F85" s="2"/>
       <c r="G85" s="2"/>
@@ -5224,8 +5371,9 @@
       <c r="A86" s="15">
         <v>85</v>
       </c>
+      <c r="B86" s="16"/>
       <c r="C86" s="16"/>
-      <c r="D86" s="48"/>
+      <c r="D86" s="16"/>
       <c r="E86" s="16"/>
       <c r="F86" s="2"/>
       <c r="G86" s="2"/>
@@ -5253,8 +5401,9 @@
       <c r="A87" s="15">
         <v>86</v>
       </c>
+      <c r="B87" s="16"/>
       <c r="C87" s="16"/>
-      <c r="D87" s="48"/>
+      <c r="D87" s="16"/>
       <c r="E87" s="16"/>
       <c r="F87" s="2"/>
       <c r="G87" s="2"/>
@@ -5282,9 +5431,11 @@
       <c r="A88" s="15">
         <v>87</v>
       </c>
-      <c r="B88" s="16"/>
+      <c r="B88" s="16" t="s">
+        <v>330</v>
+      </c>
       <c r="C88" s="16"/>
-      <c r="D88" s="48"/>
+      <c r="D88" s="16"/>
       <c r="E88" s="16"/>
       <c r="F88" s="2"/>
       <c r="G88" s="2"/>
@@ -5314,7 +5465,7 @@
       </c>
       <c r="B89" s="16"/>
       <c r="C89" s="16"/>
-      <c r="D89" s="48"/>
+      <c r="D89" s="16"/>
       <c r="E89" s="16"/>
       <c r="F89" s="2"/>
       <c r="G89" s="2"/>
@@ -5344,7 +5495,7 @@
       </c>
       <c r="B90" s="16"/>
       <c r="C90" s="16"/>
-      <c r="D90" s="48"/>
+      <c r="D90" s="16"/>
       <c r="E90" s="16"/>
       <c r="F90" s="2"/>
       <c r="G90" s="2"/>
@@ -5374,7 +5525,7 @@
       </c>
       <c r="B91" s="16"/>
       <c r="C91" s="16"/>
-      <c r="D91" s="48"/>
+      <c r="D91" s="16"/>
       <c r="E91" s="16"/>
       <c r="F91" s="2"/>
       <c r="G91" s="2"/>
@@ -5404,7 +5555,7 @@
       </c>
       <c r="B92" s="16"/>
       <c r="C92" s="16"/>
-      <c r="D92" s="48"/>
+      <c r="D92" s="16"/>
       <c r="E92" s="16"/>
       <c r="F92" s="2"/>
       <c r="G92" s="2"/>
@@ -5434,7 +5585,7 @@
       </c>
       <c r="B93" s="16"/>
       <c r="C93" s="16"/>
-      <c r="D93" s="48"/>
+      <c r="D93" s="16"/>
       <c r="E93" s="16"/>
       <c r="F93" s="2"/>
       <c r="G93" s="2"/>
@@ -30879,7 +31030,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F802CC3A-307A-4FD9-9700-764C18E7FDAA}">
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:J97"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="14.4140625" style="38" customWidth="1"/>
@@ -31182,6 +31333,205 @@
       <c r="A49" s="43" t="s">
         <v>294</v>
       </c>
+    </row>
+    <row r="51" spans="1:1" ht="25.5">
+      <c r="A51" s="37" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" ht="17.5">
+      <c r="A52" s="42" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" ht="17.5">
+      <c r="A53" s="40" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" ht="17.5">
+      <c r="A54" s="40" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" ht="17.5">
+      <c r="A55" s="40" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" ht="17.5">
+      <c r="A56" s="40" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" ht="17.5">
+      <c r="A57" s="39" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" ht="17.5">
+      <c r="A58" s="39" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" ht="17.5">
+      <c r="A59" s="39" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" ht="17.5">
+      <c r="A60" s="39" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" ht="17.5">
+      <c r="A61" s="42" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" ht="17.5">
+      <c r="A62" s="39" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" ht="17.5">
+      <c r="A63" s="39" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" ht="17.5">
+      <c r="A64" s="39" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" ht="17.5">
+      <c r="A65" s="39" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" ht="17.5">
+      <c r="A66" s="39" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" ht="17.5">
+      <c r="A67" s="42" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" ht="17.5">
+      <c r="A68" s="39" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" ht="17.5">
+      <c r="A69" s="39" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" ht="17.5">
+      <c r="A70" s="42" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" ht="17.5">
+      <c r="A71" s="39" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" ht="17.5">
+      <c r="A72" s="39" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" ht="17.5">
+      <c r="A73" s="42" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" ht="17.5">
+      <c r="A74" s="39" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" ht="17.5">
+      <c r="A75" s="39" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" ht="17.5">
+      <c r="A76" s="42" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" ht="17.5">
+      <c r="A77" s="43" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" ht="17.5">
+      <c r="A78" s="43" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" ht="17.5">
+      <c r="A79" s="43" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" ht="17.5">
+      <c r="A80" s="43"/>
+    </row>
+    <row r="81" spans="1:1" ht="17.5">
+      <c r="A81" s="43"/>
+    </row>
+    <row r="82" spans="1:1" ht="17.5">
+      <c r="A82" s="39"/>
+    </row>
+    <row r="83" spans="1:1" ht="17.5">
+      <c r="A83" s="39"/>
+    </row>
+    <row r="84" spans="1:1" ht="17.5">
+      <c r="A84" s="39"/>
+    </row>
+    <row r="85" spans="1:1" ht="17.5">
+      <c r="A85" s="39"/>
+    </row>
+    <row r="86" spans="1:1" ht="17.5">
+      <c r="A86" s="39"/>
+    </row>
+    <row r="87" spans="1:1" ht="17.5">
+      <c r="A87" s="39"/>
+    </row>
+    <row r="88" spans="1:1" ht="17.5">
+      <c r="A88" s="39"/>
+    </row>
+    <row r="89" spans="1:1" ht="17.5">
+      <c r="A89" s="39"/>
+    </row>
+    <row r="90" spans="1:1" ht="17.5">
+      <c r="A90" s="39"/>
+    </row>
+    <row r="91" spans="1:1" ht="17.5">
+      <c r="A91" s="39"/>
+    </row>
+    <row r="92" spans="1:1" ht="17.5">
+      <c r="A92" s="39"/>
+    </row>
+    <row r="93" spans="1:1" ht="17.5">
+      <c r="A93" s="39"/>
+    </row>
+    <row r="94" spans="1:1" ht="17.5">
+      <c r="A94" s="39"/>
+    </row>
+    <row r="95" spans="1:1" ht="17.5">
+      <c r="A95" s="39"/>
+    </row>
+    <row r="96" spans="1:1" ht="17.5">
+      <c r="A96" s="39"/>
+    </row>
+    <row r="97" spans="1:1" ht="17.5">
+      <c r="A97" s="39"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -31230,13 +31580,13 @@
         <v>283</v>
       </c>
       <c r="H1" s="23" t="s">
+        <v>316</v>
+      </c>
+      <c r="I1" s="23" t="s">
+        <v>318</v>
+      </c>
+      <c r="J1" s="23" t="s">
         <v>317</v>
-      </c>
-      <c r="I1" s="23" t="s">
-        <v>319</v>
-      </c>
-      <c r="J1" s="23" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="56">
@@ -31265,7 +31615,7 @@
         <v>167</v>
       </c>
       <c r="I2" s="24" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="J2" s="24" t="s">
         <v>174</v>
@@ -31297,7 +31647,7 @@
         <v>173</v>
       </c>
       <c r="I3" s="26" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="J3" s="26" t="s">
         <v>175</v>
@@ -31329,10 +31679,10 @@
         <v>199</v>
       </c>
       <c r="I4" s="32" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="J4" s="28" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="56">
@@ -31361,10 +31711,10 @@
         <v>199</v>
       </c>
       <c r="I5" s="32" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J5" s="28" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="56">
@@ -31396,7 +31746,7 @@
         <v>187</v>
       </c>
       <c r="J6" s="28" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="56">
@@ -31425,10 +31775,10 @@
         <v>199</v>
       </c>
       <c r="I7" s="32" t="s">
+        <v>325</v>
+      </c>
+      <c r="J7" s="28" t="s">
         <v>326</v>
-      </c>
-      <c r="J7" s="28" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="56">
@@ -31585,7 +31935,7 @@
         <v>204</v>
       </c>
       <c r="I12" s="34" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="J12" s="30" t="s">
         <v>205</v>
@@ -31605,7 +31955,7 @@
         <v>219</v>
       </c>
       <c r="E13" s="35" t="s">
-        <v>313</v>
+        <v>360</v>
       </c>
       <c r="F13" s="31" t="s">
         <v>218</v>
@@ -31617,7 +31967,7 @@
         <v>225</v>
       </c>
       <c r="I13" s="35" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="J13" s="31" t="s">
         <v>216</v>
@@ -31649,7 +31999,7 @@
         <v>259</v>
       </c>
       <c r="I14" s="45" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="J14" s="45" t="s">
         <v>260</v>

--- a/CoreRefiner工作表.xlsx
+++ b/CoreRefiner工作表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_HOME_study\CoreRefiner\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB097FA1-A9E1-447B-9238-F4D7B36B6AE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E3D92C9-32FD-4D27-A957-DDB8EB903C41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="任务表" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="362">
   <si>
     <t>内容详情</t>
   </si>
@@ -1445,10 +1445,17 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>详见细则表。</t>
-  </si>
-  <si>
     <t>重复之前的节点。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ultra节点框架</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>奥义类出生为3级，可以无限升级。
+可以用于统合其他的类。
+名称和Icon都可以自定义。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5301,17 +5308,21 @@
       <c r="Y83" s="2"/>
       <c r="Z83" s="2"/>
     </row>
-    <row r="84" spans="1:26">
-      <c r="A84" s="15">
+    <row r="84" spans="1:26" ht="63">
+      <c r="A84" s="6">
         <v>83</v>
       </c>
-      <c r="B84" s="16" t="s">
-        <v>331</v>
-      </c>
-      <c r="C84" s="16"/>
-      <c r="D84" s="16"/>
-      <c r="E84" s="16" t="s">
-        <v>359</v>
+      <c r="B84" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="C84" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D84" s="7">
+        <v>46299</v>
+      </c>
+      <c r="E84" s="4" t="s">
+        <v>361</v>
       </c>
       <c r="F84" s="2"/>
       <c r="G84" s="2"/>
@@ -5339,9 +5350,7 @@
       <c r="A85" s="15">
         <v>84</v>
       </c>
-      <c r="B85" s="16" t="s">
-        <v>358</v>
-      </c>
+      <c r="B85" s="16"/>
       <c r="C85" s="16"/>
       <c r="D85" s="16"/>
       <c r="E85" s="16"/>
@@ -5371,7 +5380,6 @@
       <c r="A86" s="15">
         <v>85</v>
       </c>
-      <c r="B86" s="16"/>
       <c r="C86" s="16"/>
       <c r="D86" s="16"/>
       <c r="E86" s="16"/>
@@ -5401,7 +5409,9 @@
       <c r="A87" s="15">
         <v>86</v>
       </c>
-      <c r="B87" s="16"/>
+      <c r="B87" s="16" t="s">
+        <v>331</v>
+      </c>
       <c r="C87" s="16"/>
       <c r="D87" s="16"/>
       <c r="E87" s="16"/>
@@ -5432,7 +5442,7 @@
         <v>87</v>
       </c>
       <c r="B88" s="16" t="s">
-        <v>330</v>
+        <v>358</v>
       </c>
       <c r="C88" s="16"/>
       <c r="D88" s="16"/>
@@ -5493,7 +5503,9 @@
       <c r="A90" s="15">
         <v>89</v>
       </c>
-      <c r="B90" s="16"/>
+      <c r="B90" s="16" t="s">
+        <v>330</v>
+      </c>
       <c r="C90" s="16"/>
       <c r="D90" s="16"/>
       <c r="E90" s="16"/>
@@ -31955,7 +31967,7 @@
         <v>219</v>
       </c>
       <c r="E13" s="35" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F13" s="31" t="s">
         <v>218</v>

--- a/CoreRefiner工作表.xlsx
+++ b/CoreRefiner工作表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_HOME_study\CoreRefiner\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E3D92C9-32FD-4D27-A957-DDB8EB903C41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF52B389-1304-4717-86DE-ABC669118B78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="363">
   <si>
     <t>内容详情</t>
   </si>
@@ -1456,6 +1456,10 @@
     <t>奥义类出生为3级，可以无限升级。
 可以用于统合其他的类。
 名称和Icon都可以自定义。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>子弹同时发射时会完全重叠</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5565,7 +5569,9 @@
       <c r="A92" s="15">
         <v>91</v>
       </c>
-      <c r="B92" s="16"/>
+      <c r="B92" s="16" t="s">
+        <v>362</v>
+      </c>
       <c r="C92" s="16"/>
       <c r="D92" s="16"/>
       <c r="E92" s="16"/>

--- a/CoreRefiner工作表.xlsx
+++ b/CoreRefiner工作表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_HOME_study\CoreRefiner\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF52B389-1304-4717-86DE-ABC669118B78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{322A42E9-F181-4D19-9197-3B887943335F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="364">
   <si>
     <t>内容详情</t>
   </si>
@@ -1460,6 +1460,10 @@
   </si>
   <si>
     <t>子弹同时发射时会完全重叠</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Node的扩散起点是从半径开始的</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5507,8 +5511,8 @@
       <c r="A90" s="15">
         <v>89</v>
       </c>
-      <c r="B90" s="16" t="s">
-        <v>330</v>
+      <c r="B90" s="52" t="s">
+        <v>363</v>
       </c>
       <c r="C90" s="16"/>
       <c r="D90" s="16"/>
@@ -5539,7 +5543,9 @@
       <c r="A91" s="15">
         <v>90</v>
       </c>
-      <c r="B91" s="16"/>
+      <c r="B91" s="16" t="s">
+        <v>330</v>
+      </c>
       <c r="C91" s="16"/>
       <c r="D91" s="16"/>
       <c r="E91" s="16"/>
@@ -5569,9 +5575,7 @@
       <c r="A92" s="15">
         <v>91</v>
       </c>
-      <c r="B92" s="16" t="s">
-        <v>362</v>
-      </c>
+      <c r="B92" s="16"/>
       <c r="C92" s="16"/>
       <c r="D92" s="16"/>
       <c r="E92" s="16"/>
@@ -5601,7 +5605,9 @@
       <c r="A93" s="15">
         <v>92</v>
       </c>
-      <c r="B93" s="16"/>
+      <c r="B93" s="16" t="s">
+        <v>362</v>
+      </c>
       <c r="C93" s="16"/>
       <c r="D93" s="16"/>
       <c r="E93" s="16"/>
